--- a/produtos_cadastrados.xlsx
+++ b/produtos_cadastrados.xlsx
@@ -9,7 +9,7 @@
     <sheet name="Produtos" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Produtos'!$A$1:$D$3083</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Produtos'!$A$1:$D$3087</definedName>
   </definedNames>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="11">
+  <fonts count="13">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -29,6 +29,16 @@
     <font>
       <name val="Calibri"/>
       <b val="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="FF000000"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="FF000000"/>
       <sz val="11"/>
     </font>
     <font>
@@ -136,7 +146,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
@@ -146,20 +156,24 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -525,7 +539,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3083"/>
+  <dimension ref="A1:D3087"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7.42578125" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -577,20 +591,20 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="n">
+      <c r="A3" s="21" t="n">
         <v>100038</v>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="21" t="inlineStr">
         <is>
           <t>#01 MERCEARIA - #01 CEREAIS E GRÃOS</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C3" s="21" t="inlineStr">
         <is>
           <t>ARROZ BREJEIRO 5KG BRANCO TIPO 1</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D3" s="21" t="inlineStr">
         <is>
           <t>ARROZ BREJEIRO PCT 5KG TIPO 1 BRANCO</t>
         </is>
@@ -717,20 +731,20 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="n">
+      <c r="A10" s="21" t="n">
         <v>325990</v>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B10" s="21" t="inlineStr">
         <is>
           <t>#01 MERCEARIA - #01 CEREAIS E GRÃOS</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C10" s="21" t="inlineStr">
         <is>
           <t>ARROZ BRANCO FLORA 5KG TIPO 1</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D10" s="21" t="inlineStr">
         <is>
           <t>ARROZ FLORA PCT 5KG TIPO 1 BRANCO</t>
         </is>
@@ -757,10 +771,10 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="19" t="n">
+      <c r="A12" s="13" t="n">
         <v>229173</v>
       </c>
-      <c r="B12" s="19" t="inlineStr">
+      <c r="B12" s="13" t="inlineStr">
         <is>
           <t>#01 MERCEARIA - #01 CEREAIS E GRÃOS</t>
         </is>
@@ -770,7 +784,7 @@
           <t>ARROZ TIPO 1 KIDELICIA BRANCO 5KG</t>
         </is>
       </c>
-      <c r="D12" s="19" t="inlineStr">
+      <c r="D12" s="13" t="inlineStr">
         <is>
           <t>ARROZ KIDELICIA PCT 5KG TIPO 1 BRANCO</t>
         </is>
@@ -897,20 +911,20 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="n">
+      <c r="A19" s="21" t="n">
         <v>225003</v>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B19" s="21" t="inlineStr">
         <is>
           <t>#01 MERCEARIA - #01 CEREAIS E GRÃOS</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C19" s="21" t="inlineStr">
         <is>
           <t>ARROZ RAMPINELLI 5KG TIPO1</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="D19" s="21" t="inlineStr">
         <is>
           <t>ARROZ RAMPINELLI PCT 5KG TIPO 1 BRANCO</t>
         </is>
@@ -1237,20 +1251,20 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="19" t="n">
+      <c r="A36" s="13" t="n">
         <v>279573</v>
       </c>
-      <c r="B36" s="19" t="inlineStr">
+      <c r="B36" s="13" t="inlineStr">
         <is>
           <t>#01 MERCEARIA - #02 FEIJÕES E LEGUMINOSAS</t>
         </is>
       </c>
-      <c r="C36" s="19" t="inlineStr">
+      <c r="C36" s="13" t="inlineStr">
         <is>
           <t>FEIJÃO DONA MARIA 1KG CARIOCA</t>
         </is>
       </c>
-      <c r="D36" s="19" t="inlineStr">
+      <c r="D36" s="13" t="inlineStr">
         <is>
           <t>FEIJÃO CARIOCA DONA MARIA 1KG</t>
         </is>
@@ -1277,20 +1291,20 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" t="n">
+      <c r="A38" s="21" t="n">
         <v>327443</v>
       </c>
-      <c r="B38" t="inlineStr">
+      <c r="B38" s="21" t="inlineStr">
         <is>
           <t>#01 MERCEARIA - #02 FEIJÕES E LEGUMINOSAS</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
+      <c r="C38" s="21" t="inlineStr">
         <is>
           <t>FEIJAO KALDINHO 1KG CARIOCA</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr">
+      <c r="D38" s="21" t="inlineStr">
         <is>
           <t>FEIJÃO CARIOCA KALDINHO 1KG</t>
         </is>
@@ -1777,20 +1791,20 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" t="n">
+      <c r="A63" s="21" t="n">
         <v>167128</v>
       </c>
-      <c r="B63" t="inlineStr">
+      <c r="B63" s="21" t="inlineStr">
         <is>
           <t>#01 MERCEARIA - #03 ÓLEOS E GORDURAS</t>
         </is>
       </c>
-      <c r="C63" t="inlineStr">
+      <c r="C63" s="21" t="inlineStr">
         <is>
           <t>ÓLEO SOJA REFINADO CONCORDIA 900ML</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr">
+      <c r="D63" s="21" t="inlineStr">
         <is>
           <t>ÓLEO DE SOJA CONCORDIA 900ML</t>
         </is>
@@ -1977,20 +1991,20 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="5" t="n">
+      <c r="A73" s="21" t="n">
         <v>345404</v>
       </c>
-      <c r="B73" s="5" t="inlineStr">
+      <c r="B73" s="21" t="inlineStr">
         <is>
           <t>#01 MERCEARIA - #04 AÇÚCAR E ADOÇANTES</t>
         </is>
       </c>
-      <c r="C73" s="5" t="inlineStr">
+      <c r="C73" s="21" t="inlineStr">
         <is>
           <t>ACUCAR ECO ACUCAR 2KG CRISTAL</t>
         </is>
       </c>
-      <c r="D73" s="5" t="inlineStr">
+      <c r="D73" s="21" t="inlineStr">
         <is>
           <t>AÇUCAR ECOÇUCAR 2KG CRISTAL</t>
         </is>
@@ -2377,20 +2391,20 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="5" t="n">
+      <c r="A93" s="21" t="n">
         <v>255232</v>
       </c>
-      <c r="B93" s="5" t="inlineStr">
+      <c r="B93" s="21" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - ACHOCOLATADOS E CAFÉ</t>
         </is>
       </c>
-      <c r="C93" s="5" t="inlineStr">
+      <c r="C93" s="21" t="inlineStr">
         <is>
           <t>ACHOCOLATADO EM PÓ TODDY 750G</t>
         </is>
       </c>
-      <c r="D93" s="5" t="inlineStr">
+      <c r="D93" s="21" t="inlineStr">
         <is>
           <t>ACHOCOLATADO EM PÓ TODDY 750G</t>
         </is>
@@ -2557,20 +2571,20 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="5" t="n">
+      <c r="A102" s="21" t="n">
         <v>101137</v>
       </c>
-      <c r="B102" s="5" t="inlineStr">
+      <c r="B102" s="21" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - ACHOCOLATADOS E CAFÉ</t>
         </is>
       </c>
-      <c r="C102" s="5" t="inlineStr">
+      <c r="C102" s="21" t="inlineStr">
         <is>
           <t>CAFÉ MARATA 250GR A VACUO TRADIC</t>
         </is>
       </c>
-      <c r="D102" s="5" t="inlineStr">
+      <c r="D102" s="21" t="inlineStr">
         <is>
           <t>CAFÉ MARATA 250G TRADICIONAL</t>
         </is>
@@ -2637,40 +2651,40 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="19" t="n">
+      <c r="A106" s="13" t="n">
         <v>174298</v>
       </c>
-      <c r="B106" s="19" t="inlineStr">
+      <c r="B106" s="13" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - ACHOCOLATADOS E CAFÉ</t>
         </is>
       </c>
-      <c r="C106" s="19" t="inlineStr">
+      <c r="C106" s="13" t="inlineStr">
         <is>
           <t>CAFE MOIDO RANCHEIRO 250GR TRAD</t>
         </is>
       </c>
-      <c r="D106" s="19" t="inlineStr">
+      <c r="D106" s="13" t="inlineStr">
         <is>
           <t>CAFÉ RANCHEIRO 250G TRADICIONAL</t>
         </is>
       </c>
     </row>
     <row r="107">
-      <c r="A107" t="n">
+      <c r="A107" s="21" t="n">
         <v>114037</v>
       </c>
-      <c r="B107" t="inlineStr">
+      <c r="B107" s="21" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - ACHOCOLATADOS E CAFÉ</t>
         </is>
       </c>
-      <c r="C107" t="inlineStr">
+      <c r="C107" s="21" t="inlineStr">
         <is>
           <t>CAFÉ SANTA CLARA 250GR CLASSICO</t>
         </is>
       </c>
-      <c r="D107" t="inlineStr">
+      <c r="D107" s="21" t="inlineStr">
         <is>
           <t>CAFÉ SANTA CLARA 250G CLASSICO</t>
         </is>
@@ -2997,20 +3011,20 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="9" t="n">
+      <c r="A124" s="7" t="n">
         <v>336144</v>
       </c>
-      <c r="B124" s="9" t="inlineStr">
+      <c r="B124" s="7" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - BISCOITOS E SALGADINHOS</t>
         </is>
       </c>
-      <c r="C124" s="9" t="inlineStr">
+      <c r="C124" s="7" t="inlineStr">
         <is>
           <t>BISCOITO BUTTER COOKIES DANESITA 340GR CLASSIC</t>
         </is>
       </c>
-      <c r="D124" s="9" t="inlineStr">
+      <c r="D124" s="7" t="inlineStr">
         <is>
           <t>BISCOITO BUTTER COOKIES DANESITA 340G CLASSIC</t>
         </is>
@@ -3057,20 +3071,20 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="19" t="n">
+      <c r="A127" s="13" t="n">
         <v>261728</v>
       </c>
-      <c r="B127" s="19" t="inlineStr">
+      <c r="B127" s="13" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - BISCOITOS E SALGADINHOS</t>
         </is>
       </c>
-      <c r="C127" s="19" t="inlineStr">
+      <c r="C127" s="13" t="inlineStr">
         <is>
           <t>BISCOITO FORTALEZA 350GR CREAM CRACKER</t>
         </is>
       </c>
-      <c r="D127" s="19" t="inlineStr">
+      <c r="D127" s="13" t="inlineStr">
         <is>
           <t>BISCOITO CREAM CRACKER FORTALEZA 350G</t>
         </is>
@@ -3097,20 +3111,20 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" t="n">
+      <c r="A129" s="21" t="n">
         <v>186826</v>
       </c>
-      <c r="B129" t="inlineStr">
+      <c r="B129" s="21" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - BISCOITOS E SALGADINHOS</t>
         </is>
       </c>
-      <c r="C129" t="inlineStr">
+      <c r="C129" s="21" t="inlineStr">
         <is>
           <t>BISCOITO CREAM CRACKER GALLO 360GR</t>
         </is>
       </c>
-      <c r="D129" t="inlineStr">
+      <c r="D129" s="21" t="inlineStr">
         <is>
           <t>BISCOITO CREAM CRACKER GALLO 360G</t>
         </is>
@@ -3697,10 +3711,10 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="18" t="n">
+      <c r="A159" s="13" t="n">
         <v>263612</v>
       </c>
-      <c r="B159" s="18" t="inlineStr">
+      <c r="B159" s="13" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - BISCOITOS E SALGADINHOS</t>
         </is>
@@ -3710,27 +3724,27 @@
           <t>BISCOITO VITARELLA 350GR MAIZENA CHOCOLATE</t>
         </is>
       </c>
-      <c r="D159" s="18" t="inlineStr">
+      <c r="D159" s="13" t="inlineStr">
         <is>
           <t>BISCOITO MAISENA VITARELLA 350G CHOCOLATE</t>
         </is>
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="9" t="n">
+      <c r="A160" s="7" t="n">
         <v>264770</v>
       </c>
-      <c r="B160" s="9" t="inlineStr">
+      <c r="B160" s="7" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - BISCOITOS E SALGADINHOS</t>
         </is>
       </c>
-      <c r="C160" s="9" t="inlineStr">
+      <c r="C160" s="7" t="inlineStr">
         <is>
           <t>BISCOITO VITARELLA MAIZENA 350GR LEITE</t>
         </is>
       </c>
-      <c r="D160" s="9" t="inlineStr">
+      <c r="D160" s="7" t="inlineStr">
         <is>
           <t>BISCOITO MAISENA VITARELLA 350G LEITE</t>
         </is>
@@ -3777,20 +3791,20 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="9" t="n">
+      <c r="A163" s="7" t="n">
         <v>286613</v>
       </c>
-      <c r="B163" s="9" t="inlineStr">
+      <c r="B163" s="7" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - BISCOITOS E SALGADINHOS</t>
         </is>
       </c>
-      <c r="C163" s="9" t="inlineStr">
+      <c r="C163" s="7" t="inlineStr">
         <is>
           <t>BISCOITO VITARELLA 350GR MAIZENA  TRADIC</t>
         </is>
       </c>
-      <c r="D163" s="9" t="inlineStr">
+      <c r="D163" s="7" t="inlineStr">
         <is>
           <t>BISCOITO MAISENA VITARELLA 350G TRADICIONAL</t>
         </is>
@@ -3857,60 +3871,60 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="9" t="n">
+      <c r="A167" s="7" t="n">
         <v>264678</v>
       </c>
-      <c r="B167" s="9" t="inlineStr">
+      <c r="B167" s="7" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - BISCOITOS E SALGADINHOS</t>
         </is>
       </c>
-      <c r="C167" s="9" t="inlineStr">
+      <c r="C167" s="7" t="inlineStr">
         <is>
           <t>BISCOITO VITARELLA MARIA 350GR CHOCOLATE</t>
         </is>
       </c>
-      <c r="D167" s="9" t="inlineStr">
+      <c r="D167" s="7" t="inlineStr">
         <is>
           <t>BISCOITO MARIA VITARELLA 350G CHOCOLATE</t>
         </is>
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="9" t="n">
+      <c r="A168" s="7" t="n">
         <v>264771</v>
       </c>
-      <c r="B168" s="9" t="inlineStr">
+      <c r="B168" s="7" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - BISCOITOS E SALGADINHOS</t>
         </is>
       </c>
-      <c r="C168" s="9" t="inlineStr">
+      <c r="C168" s="7" t="inlineStr">
         <is>
           <t>BISCOITO VITARELLA MARIA 350GR LEITE</t>
         </is>
       </c>
-      <c r="D168" s="9" t="inlineStr">
+      <c r="D168" s="7" t="inlineStr">
         <is>
           <t>BISCOITO MARIA VITARELLA 350G LEITE</t>
         </is>
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="9" t="n">
+      <c r="A169" s="7" t="n">
         <v>264773</v>
       </c>
-      <c r="B169" s="9" t="inlineStr">
+      <c r="B169" s="7" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - BISCOITOS E SALGADINHOS</t>
         </is>
       </c>
-      <c r="C169" s="9" t="inlineStr">
+      <c r="C169" s="7" t="inlineStr">
         <is>
           <t>BISCOITO VITARELLA MARIA 350GR TRADICIONAL</t>
         </is>
       </c>
-      <c r="D169" s="9" t="inlineStr">
+      <c r="D169" s="7" t="inlineStr">
         <is>
           <t>BISCOITO MARIA VITARELLA 350G TRADICIONAL</t>
         </is>
@@ -4337,20 +4351,20 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="19" t="n">
+      <c r="A191" s="13" t="n">
         <v>286197</v>
       </c>
-      <c r="B191" s="19" t="inlineStr">
+      <c r="B191" s="13" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - BISCOITOS E SALGADINHOS</t>
         </is>
       </c>
-      <c r="C191" s="19" t="inlineStr">
+      <c r="C191" s="13" t="inlineStr">
         <is>
           <t>BISCOITO MABEL 600GR ROSCA COCO</t>
         </is>
       </c>
-      <c r="D191" s="19" t="inlineStr">
+      <c r="D191" s="13" t="inlineStr">
         <is>
           <t>BISCOITO ROSQUINHA MABEL 600G COCO</t>
         </is>
@@ -4397,20 +4411,20 @@
       </c>
     </row>
     <row r="194">
-      <c r="A194" t="n">
+      <c r="A194" s="21" t="n">
         <v>257157</v>
       </c>
-      <c r="B194" t="inlineStr">
+      <c r="B194" s="21" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - BISCOITOS E SALGADINHOS</t>
         </is>
       </c>
-      <c r="C194" t="inlineStr">
+      <c r="C194" s="21" t="inlineStr">
         <is>
           <t>ROSCA MICOS DE COCO 600G</t>
         </is>
       </c>
-      <c r="D194" t="inlineStr">
+      <c r="D194" s="21" t="inlineStr">
         <is>
           <t>BISCOITO ROSQUINHA MICOS 600G COCO</t>
         </is>
@@ -5017,40 +5031,40 @@
       </c>
     </row>
     <row r="225">
-      <c r="A225" s="9" t="n">
+      <c r="A225" s="7" t="n">
         <v>342798</v>
       </c>
-      <c r="B225" s="9" t="inlineStr">
+      <c r="B225" s="7" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - BISCOITOS E SALGADINHOS</t>
         </is>
       </c>
-      <c r="C225" s="9" t="inlineStr">
+      <c r="C225" s="7" t="inlineStr">
         <is>
           <t>TAPIOCA GOMAC 130GR C/COCO E GOIABADA</t>
         </is>
       </c>
-      <c r="D225" s="9" t="inlineStr">
+      <c r="D225" s="7" t="inlineStr">
         <is>
           <t>TAPIOCA GOMAC 130G COCO E GOIABADA</t>
         </is>
       </c>
     </row>
     <row r="226">
-      <c r="A226" s="9" t="n">
+      <c r="A226" s="7" t="n">
         <v>342796</v>
       </c>
-      <c r="B226" s="9" t="inlineStr">
+      <c r="B226" s="7" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - BISCOITOS E SALGADINHOS</t>
         </is>
       </c>
-      <c r="C226" s="9" t="inlineStr">
+      <c r="C226" s="7" t="inlineStr">
         <is>
           <t>TAPIOCA GOMAC 130GR C/COCO E LEITE CONDENSADO</t>
         </is>
       </c>
-      <c r="D226" s="9" t="inlineStr">
+      <c r="D226" s="7" t="inlineStr">
         <is>
           <t>TAPIOCA GOMAC 130G COCO E LEITE CONDENSADO</t>
         </is>
@@ -5117,40 +5131,40 @@
       </c>
     </row>
     <row r="230">
-      <c r="A230" s="9" t="n">
+      <c r="A230" s="7" t="n">
         <v>342790</v>
       </c>
-      <c r="B230" s="9" t="inlineStr">
+      <c r="B230" s="7" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - BISCOITOS E SALGADINHOS</t>
         </is>
       </c>
-      <c r="C230" s="9" t="inlineStr">
+      <c r="C230" s="7" t="inlineStr">
         <is>
           <t>TAPIOCA GOMAC 150GR AMENDOIM C/GOIABADA CROCANTE</t>
         </is>
       </c>
-      <c r="D230" s="9" t="inlineStr">
+      <c r="D230" s="7" t="inlineStr">
         <is>
           <t>TAPIOCA GOMAC 150G AMENDOIM E GOIABADA CROCANTE</t>
         </is>
       </c>
     </row>
     <row r="231">
-      <c r="A231" s="9" t="n">
+      <c r="A231" s="7" t="n">
         <v>342800</v>
       </c>
-      <c r="B231" s="9" t="inlineStr">
+      <c r="B231" s="7" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - BISCOITOS E SALGADINHOS</t>
         </is>
       </c>
-      <c r="C231" s="9" t="inlineStr">
+      <c r="C231" s="7" t="inlineStr">
         <is>
           <t>TAPIOCA GOMAC 150GR COCO C/BANANADA CROCANTE</t>
         </is>
       </c>
-      <c r="D231" s="9" t="inlineStr">
+      <c r="D231" s="7" t="inlineStr">
         <is>
           <t>TAPIOCA GOMAC 150G COCO E BANANADA CROCANTE</t>
         </is>
@@ -5177,80 +5191,80 @@
       </c>
     </row>
     <row r="233">
-      <c r="A233" s="9" t="n">
+      <c r="A233" s="7" t="n">
         <v>342797</v>
       </c>
-      <c r="B233" s="9" t="inlineStr">
+      <c r="B233" s="7" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - BISCOITOS E SALGADINHOS</t>
         </is>
       </c>
-      <c r="C233" s="9" t="inlineStr">
+      <c r="C233" s="7" t="inlineStr">
         <is>
           <t>TAPIOCA GOMAC 230GR C/COCO E GOIABADA</t>
         </is>
       </c>
-      <c r="D233" s="9" t="inlineStr">
+      <c r="D233" s="7" t="inlineStr">
         <is>
           <t>TAPIOCA GOMAC 230G COCO E GOIABADA</t>
         </is>
       </c>
     </row>
     <row r="234">
-      <c r="A234" s="9" t="n">
+      <c r="A234" s="7" t="n">
         <v>342801</v>
       </c>
-      <c r="B234" s="9" t="inlineStr">
+      <c r="B234" s="7" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - BISCOITOS E SALGADINHOS</t>
         </is>
       </c>
-      <c r="C234" s="9" t="inlineStr">
+      <c r="C234" s="7" t="inlineStr">
         <is>
           <t>TAPIOCA GOMAC 230GR COCO C/LEITE CONDENSADO</t>
         </is>
       </c>
-      <c r="D234" s="9" t="inlineStr">
+      <c r="D234" s="7" t="inlineStr">
         <is>
           <t>TAPIOCA GOMAC 230G COCO E LEITE CONDENSADO</t>
         </is>
       </c>
     </row>
     <row r="235">
-      <c r="A235" s="9" t="n">
+      <c r="A235" s="7" t="n">
         <v>342794</v>
       </c>
-      <c r="B235" s="9" t="inlineStr">
+      <c r="B235" s="7" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - BISCOITOS E SALGADINHOS</t>
         </is>
       </c>
-      <c r="C235" s="9" t="inlineStr">
+      <c r="C235" s="7" t="inlineStr">
         <is>
           <t>TAPIOCA GOMAC 230GR C/COCO QUEIMADO</t>
         </is>
       </c>
-      <c r="D235" s="9" t="inlineStr">
+      <c r="D235" s="7" t="inlineStr">
         <is>
           <t>TAPIOCA GOMAC 230G COCO QUEIMADO</t>
         </is>
       </c>
     </row>
     <row r="236">
-      <c r="A236" s="9" t="n">
+      <c r="A236" s="7" t="n">
         <v>342792</v>
       </c>
-      <c r="B236" s="9" t="inlineStr">
+      <c r="B236" s="7" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - BISCOITOS E SALGADINHOS</t>
         </is>
       </c>
-      <c r="C236" s="9" t="inlineStr">
+      <c r="C236" s="7" t="inlineStr">
         <is>
           <t>TAPIOCA GOMAC 230GR C/COCO QUEIMADO ZR ACUCAR</t>
         </is>
       </c>
-      <c r="D236" s="9" t="inlineStr">
+      <c r="D236" s="7" t="inlineStr">
         <is>
           <t>TAPIOCA GOMAC 230G ZERO AÇUCAR COCO QUEIMADO</t>
         </is>
@@ -5357,20 +5371,20 @@
       </c>
     </row>
     <row r="242">
-      <c r="A242" s="9" t="n">
+      <c r="A242" s="7" t="n">
         <v>339456</v>
       </c>
-      <c r="B242" s="9" t="inlineStr">
+      <c r="B242" s="7" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - CEREAIS MATINAIS</t>
         </is>
       </c>
-      <c r="C242" s="9" t="inlineStr">
+      <c r="C242" s="7" t="inlineStr">
         <is>
           <t>CASTANHA DE CAJU DUNORTE 50G CARAMELIZADA</t>
         </is>
       </c>
-      <c r="D242" s="9" t="inlineStr">
+      <c r="D242" s="7" t="inlineStr">
         <is>
           <t>CASTANHA DE CAJU DUNORTE 50G CARAMELIZADA</t>
         </is>
@@ -5577,20 +5591,20 @@
       </c>
     </row>
     <row r="253">
-      <c r="A253" s="9" t="n">
+      <c r="A253" s="7" t="n">
         <v>339483</v>
       </c>
-      <c r="B253" s="9" t="inlineStr">
+      <c r="B253" s="7" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - CEREAIS MATINAIS</t>
         </is>
       </c>
-      <c r="C253" s="9" t="inlineStr">
+      <c r="C253" s="7" t="inlineStr">
         <is>
           <t>MIX DO CORACAO LOVE NUTS 40G DUNORTE</t>
         </is>
       </c>
-      <c r="D253" s="9" t="inlineStr">
+      <c r="D253" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">LOVE NUTS 40G MIX DO CORAÇÃO </t>
         </is>
@@ -5617,20 +5631,20 @@
       </c>
     </row>
     <row r="255">
-      <c r="A255" s="19" t="n">
+      <c r="A255" s="21" t="n">
         <v>341362</v>
       </c>
-      <c r="B255" s="19" t="inlineStr">
+      <c r="B255" s="21" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - CHOCOLATES E DOCES</t>
         </is>
       </c>
-      <c r="C255" s="19" t="inlineStr">
+      <c r="C255" s="21" t="inlineStr">
         <is>
           <t>BOMBONS GAROTO 220G SORTIDOS CAIXA</t>
         </is>
       </c>
-      <c r="D255" s="19" t="inlineStr">
+      <c r="D255" s="21" t="inlineStr">
         <is>
           <t>BOMBOM GAROTO CAIXA 220G SORTIDOS</t>
         </is>
@@ -5697,20 +5711,20 @@
       </c>
     </row>
     <row r="259">
-      <c r="A259" s="9" t="n">
+      <c r="A259" s="7" t="n">
         <v>221534</v>
       </c>
-      <c r="B259" s="9" t="inlineStr">
+      <c r="B259" s="7" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - CHOCOLATES E DOCES</t>
         </is>
       </c>
-      <c r="C259" s="9" t="inlineStr">
+      <c r="C259" s="7" t="inlineStr">
         <is>
           <t>BOMBOM NESTLE ALPINO CHOC 195GR BAG</t>
         </is>
       </c>
-      <c r="D259" s="9" t="inlineStr">
+      <c r="D259" s="7" t="inlineStr">
         <is>
           <t>BOMBOM NESTLE ALPINO BAG 195G CHOCOLATE</t>
         </is>
@@ -6157,20 +6171,20 @@
       </c>
     </row>
     <row r="282">
-      <c r="A282" s="9" t="n">
+      <c r="A282" s="7" t="n">
         <v>185461</v>
       </c>
-      <c r="B282" s="9" t="inlineStr">
+      <c r="B282" s="7" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - CHOCOLATES E DOCES</t>
         </is>
       </c>
-      <c r="C282" s="9" t="inlineStr">
+      <c r="C282" s="7" t="inlineStr">
         <is>
           <t>DOCE DE LEITE ITALAC 350GR</t>
         </is>
       </c>
-      <c r="D282" s="9" t="inlineStr">
+      <c r="D282" s="7" t="inlineStr">
         <is>
           <t>DOCE DE LEITE ITALAC 350G</t>
         </is>
@@ -6577,220 +6591,220 @@
       </c>
     </row>
     <row r="303">
-      <c r="A303" s="17" t="n">
+      <c r="A303" s="8" t="n">
         <v>259168</v>
       </c>
-      <c r="B303" s="17" t="inlineStr">
+      <c r="B303" s="8" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - CHOCOLATES E DOCES</t>
         </is>
       </c>
-      <c r="C303" s="17" t="inlineStr">
+      <c r="C303" s="8" t="inlineStr">
         <is>
           <t>CHOC.MILKA OREO BRANCO 100,0G</t>
         </is>
       </c>
-      <c r="D303" s="17" t="inlineStr">
+      <c r="D303" s="8" t="inlineStr">
         <is>
           <t>CHOCOLATE MILKA 100G OREO BRANCO</t>
         </is>
       </c>
     </row>
     <row r="304">
-      <c r="A304" s="17" t="n">
+      <c r="A304" s="8" t="n">
         <v>347699</v>
       </c>
-      <c r="B304" s="17" t="inlineStr">
+      <c r="B304" s="8" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - CHOCOLATES E DOCES</t>
         </is>
       </c>
-      <c r="C304" s="17" t="inlineStr">
+      <c r="C304" s="8" t="inlineStr">
         <is>
           <t>CHOCOLATE MILKA 100G OREO BROWNIE</t>
         </is>
       </c>
-      <c r="D304" s="17" t="inlineStr">
+      <c r="D304" s="8" t="inlineStr">
         <is>
           <t>CHOCOLATE MILKA 100G OREO BROWNIE</t>
         </is>
       </c>
     </row>
     <row r="305">
-      <c r="A305" s="17" t="n">
+      <c r="A305" s="8" t="n">
         <v>347702</v>
       </c>
-      <c r="B305" s="17" t="inlineStr">
+      <c r="B305" s="8" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - CHOCOLATES E DOCES</t>
         </is>
       </c>
-      <c r="C305" s="17" t="inlineStr">
+      <c r="C305" s="8" t="inlineStr">
         <is>
           <t>CHOCOLATE MILKA 100G WITH TOFFE CARAMEL</t>
         </is>
       </c>
-      <c r="D305" s="17" t="inlineStr">
+      <c r="D305" s="8" t="inlineStr">
         <is>
           <t>CHOCOLATE MILKA 100G WITH TOFFE CARAMEL</t>
         </is>
       </c>
     </row>
     <row r="306">
-      <c r="A306" s="17" t="n">
+      <c r="A306" s="8" t="n">
         <v>347696</v>
       </c>
-      <c r="B306" s="17" t="inlineStr">
+      <c r="B306" s="8" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - CHOCOLATES E DOCES</t>
         </is>
       </c>
-      <c r="C306" s="17" t="inlineStr">
+      <c r="C306" s="8" t="inlineStr">
         <is>
           <t>CHOCOLATE MILKA 90G BUBBLY ALPINE MILK</t>
         </is>
       </c>
-      <c r="D306" s="17" t="inlineStr">
+      <c r="D306" s="8" t="inlineStr">
         <is>
           <t>CHOCOLATE MILKA 90G BUBBLY ALPINE MILK</t>
         </is>
       </c>
     </row>
     <row r="307">
-      <c r="A307" s="17" t="n">
+      <c r="A307" s="8" t="n">
         <v>347698</v>
       </c>
-      <c r="B307" s="17" t="inlineStr">
+      <c r="B307" s="8" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - CHOCOLATES E DOCES</t>
         </is>
       </c>
-      <c r="C307" s="17" t="inlineStr">
+      <c r="C307" s="8" t="inlineStr">
         <is>
           <t>CHOCOLATE MILKA 90G HAPPY COWS</t>
         </is>
       </c>
-      <c r="D307" s="17" t="inlineStr">
+      <c r="D307" s="8" t="inlineStr">
         <is>
           <t>CHOCOLATE MILKA 90G HAPPY COWS</t>
         </is>
       </c>
     </row>
     <row r="308">
-      <c r="A308" s="17" t="n">
+      <c r="A308" s="8" t="n">
         <v>347695</v>
       </c>
-      <c r="B308" s="17" t="inlineStr">
+      <c r="B308" s="8" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - CHOCOLATES E DOCES</t>
         </is>
       </c>
-      <c r="C308" s="17" t="inlineStr">
+      <c r="C308" s="8" t="inlineStr">
         <is>
           <t>CHOCOLATE MILKA 90G HAZELNUT AVELÃ</t>
         </is>
       </c>
-      <c r="D308" s="17" t="inlineStr">
+      <c r="D308" s="8" t="inlineStr">
         <is>
           <t>CHOCOLATE MILKA 90G HAZELNUT AVELÃ</t>
         </is>
       </c>
     </row>
     <row r="309">
-      <c r="A309" s="17" t="n">
+      <c r="A309" s="8" t="n">
         <v>268109</v>
       </c>
-      <c r="B309" s="17" t="inlineStr">
+      <c r="B309" s="8" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - CHOCOLATES E DOCES</t>
         </is>
       </c>
-      <c r="C309" s="17" t="inlineStr">
+      <c r="C309" s="8" t="inlineStr">
         <is>
           <t>CHOCOLATE MILKA 92GR OREO SANDWICH</t>
         </is>
       </c>
-      <c r="D309" s="17" t="inlineStr">
+      <c r="D309" s="8" t="inlineStr">
         <is>
           <t>CHOCOLATE MILKA 92G OREO SANDWICH</t>
         </is>
       </c>
     </row>
     <row r="310">
-      <c r="A310" s="17" t="n">
+      <c r="A310" s="8" t="n">
         <v>347694</v>
       </c>
-      <c r="B310" s="17" t="inlineStr">
+      <c r="B310" s="8" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - CHOCOLATES E DOCES</t>
         </is>
       </c>
-      <c r="C310" s="17" t="inlineStr">
+      <c r="C310" s="8" t="inlineStr">
         <is>
           <t>CHOCOLATE MILKA 95G BUBBLY WHITE</t>
         </is>
       </c>
-      <c r="D310" s="17" t="inlineStr">
+      <c r="D310" s="8" t="inlineStr">
         <is>
           <t>CHOCOLATE MILKA 95G BUBBLY WHITE</t>
         </is>
       </c>
     </row>
     <row r="311">
-      <c r="A311" s="17" t="n">
+      <c r="A311" s="8" t="n">
         <v>347693</v>
       </c>
-      <c r="B311" s="17" t="inlineStr">
+      <c r="B311" s="8" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - CHOCOLATES E DOCES</t>
         </is>
       </c>
-      <c r="C311" s="17" t="inlineStr">
+      <c r="C311" s="8" t="inlineStr">
         <is>
           <t>CHOCOLATE MILKA ALPINE MILK 90G AO LEITE</t>
         </is>
       </c>
-      <c r="D311" s="17" t="inlineStr">
+      <c r="D311" s="8" t="inlineStr">
         <is>
           <t>CHOCOLATE MILKA 90G AO LEITE ALPINE MILK</t>
         </is>
       </c>
     </row>
     <row r="312">
-      <c r="A312" s="17" t="n">
+      <c r="A312" s="8" t="n">
         <v>347692</v>
       </c>
-      <c r="B312" s="17" t="inlineStr">
+      <c r="B312" s="8" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - CHOCOLATES E DOCES</t>
         </is>
       </c>
-      <c r="C312" s="17" t="inlineStr">
+      <c r="C312" s="8" t="inlineStr">
         <is>
           <t>CHOCOLATE MILKA STRAWBERRY 100G MOR/IORG</t>
         </is>
       </c>
-      <c r="D312" s="17" t="inlineStr">
+      <c r="D312" s="8" t="inlineStr">
         <is>
           <t>CHOCOLATE MILKA 100G STRAWBERRY MORANGO IORGURTE</t>
         </is>
       </c>
     </row>
     <row r="313">
-      <c r="A313" s="17" t="n">
+      <c r="A313" s="8" t="n">
         <v>347691</v>
       </c>
-      <c r="B313" s="17" t="inlineStr">
+      <c r="B313" s="8" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - CHOCOLATES E DOCES</t>
         </is>
       </c>
-      <c r="C313" s="17" t="inlineStr">
+      <c r="C313" s="8" t="inlineStr">
         <is>
           <t>TABLETE CHOCOLATE OREO BISC 100G MILKA</t>
         </is>
       </c>
-      <c r="D313" s="17" t="inlineStr">
+      <c r="D313" s="8" t="inlineStr">
         <is>
           <t>TABLETE DE CHOCOLATE MILKA 100G BISCOITO OREO</t>
         </is>
@@ -6897,20 +6911,20 @@
       </c>
     </row>
     <row r="319">
-      <c r="A319" t="n">
+      <c r="A319" s="21" t="n">
         <v>132657</v>
       </c>
-      <c r="B319" t="inlineStr">
+      <c r="B319" s="21" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - CONDIMENTOS E TEMPEROS</t>
         </is>
       </c>
-      <c r="C319" t="inlineStr">
+      <c r="C319" s="21" t="inlineStr">
         <is>
           <t>AZEITE GALLO 500ML EXTRA VIRGEM</t>
         </is>
       </c>
-      <c r="D319" t="inlineStr">
+      <c r="D319" s="21" t="inlineStr">
         <is>
           <t>AZEITE DE OLIVA GALLO VIDRO 500ML EXTRA VIRGEM</t>
         </is>
@@ -7377,20 +7391,20 @@
       </c>
     </row>
     <row r="343">
-      <c r="A343" s="19" t="n">
+      <c r="A343" s="13" t="n">
         <v>190801</v>
       </c>
-      <c r="B343" s="19" t="inlineStr">
+      <c r="B343" s="13" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - CONDIMENTOS E TEMPEROS</t>
         </is>
       </c>
-      <c r="C343" s="19" t="inlineStr">
+      <c r="C343" s="13" t="inlineStr">
         <is>
           <t>AZEITONAS VERDES INTEIRAS MARATA SACHET</t>
         </is>
       </c>
-      <c r="D343" s="19" t="inlineStr">
+      <c r="D343" s="13" t="inlineStr">
         <is>
           <t>AZEITONAS VERDES MARATA SACHE 210G INTEIRAS</t>
         </is>
@@ -8157,20 +8171,20 @@
       </c>
     </row>
     <row r="382">
-      <c r="A382" t="n">
+      <c r="A382" s="21" t="n">
         <v>273714</v>
       </c>
-      <c r="B382" t="inlineStr">
+      <c r="B382" s="21" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - CONDIMENTOS E TEMPEROS</t>
         </is>
       </c>
-      <c r="C382" t="inlineStr">
+      <c r="C382" s="21" t="inlineStr">
         <is>
           <t>EXTRATO TOMATE ELEFANTE 300G POTE</t>
         </is>
       </c>
-      <c r="D382" t="inlineStr">
+      <c r="D382" s="21" t="inlineStr">
         <is>
           <t>EXTRATO DE TOMATE ELEFANTE POTE 300G</t>
         </is>
@@ -8817,20 +8831,20 @@
       </c>
     </row>
     <row r="415">
-      <c r="A415" s="19" t="n">
+      <c r="A415" s="21" t="n">
         <v>101728</v>
       </c>
-      <c r="B415" s="19" t="inlineStr">
+      <c r="B415" s="21" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - CONDIMENTOS E TEMPEROS</t>
         </is>
       </c>
-      <c r="C415" s="19" t="inlineStr">
+      <c r="C415" s="21" t="inlineStr">
         <is>
           <t>MAIONESE HELLMANNS 500GR TRADICIONAL</t>
         </is>
       </c>
-      <c r="D415" s="19" t="inlineStr">
+      <c r="D415" s="21" t="inlineStr">
         <is>
           <t>MAIONESE HELLMANNS 500G TRADICIONAL</t>
         </is>
@@ -9657,20 +9671,20 @@
       </c>
     </row>
     <row r="457">
-      <c r="A457" s="19" t="n">
+      <c r="A457" s="21" t="n">
         <v>321107</v>
       </c>
-      <c r="B457" s="19" t="inlineStr">
+      <c r="B457" s="21" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - CONDIMENTOS E TEMPEROS</t>
         </is>
       </c>
-      <c r="C457" s="19" t="inlineStr">
+      <c r="C457" s="21" t="inlineStr">
         <is>
           <t>MOLHO PRONTO QUERO 240GR TRADICIONAL SCH</t>
         </is>
       </c>
-      <c r="D457" s="19" t="inlineStr">
+      <c r="D457" s="21" t="inlineStr">
         <is>
           <t>MOLHO QUERO PRONTO SACHÊ 240G TRADICIONAL</t>
         </is>
@@ -10137,20 +10151,20 @@
       </c>
     </row>
     <row r="481">
-      <c r="A481" s="5" t="n">
+      <c r="A481" s="21" t="n">
         <v>100876</v>
       </c>
-      <c r="B481" s="5" t="inlineStr">
+      <c r="B481" s="21" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - CONDIMENTOS E TEMPEROS</t>
         </is>
       </c>
-      <c r="C481" s="5" t="inlineStr">
+      <c r="C481" s="21" t="inlineStr">
         <is>
           <t>TEMPERO ARISCO 1KG COMPLETO C/ PIMENTA</t>
         </is>
       </c>
-      <c r="D481" s="5" t="inlineStr">
+      <c r="D481" s="21" t="inlineStr">
         <is>
           <t>TEMPERO COMPLETO ARISCO 1KG COM PIMENTA</t>
         </is>
@@ -11097,20 +11111,20 @@
       </c>
     </row>
     <row r="529">
-      <c r="A529" t="n">
+      <c r="A529" s="21" t="n">
         <v>141367</v>
       </c>
-      <c r="B529" t="inlineStr">
+      <c r="B529" s="21" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - CONDIMENTOS E TEMPEROS</t>
         </is>
       </c>
-      <c r="C529" t="inlineStr">
+      <c r="C529" s="21" t="inlineStr">
         <is>
           <t>VINAGRE ALCOOL MARATA 750ML COLORIDO</t>
         </is>
       </c>
-      <c r="D529" t="inlineStr">
+      <c r="D529" s="21" t="inlineStr">
         <is>
           <t>VINAGRE MARATÁ 750ML ALCOOL COLORIDO</t>
         </is>
@@ -11257,20 +11271,20 @@
       </c>
     </row>
     <row r="537">
-      <c r="A537" t="n">
+      <c r="A537" s="18" t="n">
         <v>230387</v>
       </c>
-      <c r="B537" t="inlineStr">
+      <c r="B537" s="18" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - CONGELADOS - BATATAS</t>
         </is>
       </c>
-      <c r="C537" t="inlineStr">
+      <c r="C537" s="18" t="inlineStr">
         <is>
           <t>BATATAS PRE-FRITAS CONG BOUA 1,05 KG</t>
         </is>
       </c>
-      <c r="D537" t="inlineStr">
+      <c r="D537" s="18" t="inlineStr">
         <is>
           <t>BATATAS CONGELADAS BOUA PCT 1,05KG PRE-FRITAS</t>
         </is>
@@ -11477,20 +11491,20 @@
       </c>
     </row>
     <row r="548">
-      <c r="A548" s="17" t="n">
+      <c r="A548" s="13" t="n">
         <v>227503</v>
       </c>
-      <c r="B548" s="17" t="inlineStr">
+      <c r="B548" s="13" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - CONGELADOS - BATATAS</t>
         </is>
       </c>
-      <c r="C548" s="17" t="inlineStr">
+      <c r="C548" s="13" t="inlineStr">
         <is>
           <t>BATATA PALITO PRE-FRITA CONG. SADIA PT 4</t>
         </is>
       </c>
-      <c r="D548" s="17" t="inlineStr">
+      <c r="D548" s="13" t="inlineStr">
         <is>
           <t>BATATAS CONGELADAS SADIA PCT 400G PALITO PRE-FRITA</t>
         </is>
@@ -12357,20 +12371,20 @@
       </c>
     </row>
     <row r="592">
-      <c r="A592" t="n">
+      <c r="A592" s="21" t="n">
         <v>130920</v>
       </c>
-      <c r="B592" t="inlineStr">
+      <c r="B592" s="21" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - CONSERVAS - HORTIFRUTI</t>
         </is>
       </c>
-      <c r="C592" t="inlineStr">
+      <c r="C592" s="21" t="inlineStr">
         <is>
           <t>MILHO VERDE FUGINI VAPOR LT 200GR</t>
         </is>
       </c>
-      <c r="D592" t="inlineStr">
+      <c r="D592" s="21" t="inlineStr">
         <is>
           <t>MILHO VERDE FUGINI LATA 200G VAPOR</t>
         </is>
@@ -12977,20 +12991,20 @@
       </c>
     </row>
     <row r="623">
-      <c r="A623" t="n">
+      <c r="A623" s="21" t="n">
         <v>100706</v>
       </c>
-      <c r="B623" t="inlineStr">
+      <c r="B623" s="21" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - CONSERVAS - SARDINHAS</t>
         </is>
       </c>
-      <c r="C623" t="inlineStr">
+      <c r="C623" s="21" t="inlineStr">
         <is>
           <t>SARDINHA COQUEIRO 125GR MOLHO DE TOMATE</t>
         </is>
       </c>
-      <c r="D623" t="inlineStr">
+      <c r="D623" s="21" t="inlineStr">
         <is>
           <t>SARDINHA COQUEIRO 125G MOLHO DE TOMATE</t>
         </is>
@@ -13017,20 +13031,20 @@
       </c>
     </row>
     <row r="625">
-      <c r="A625" t="n">
+      <c r="A625" s="21" t="n">
         <v>221089</v>
       </c>
-      <c r="B625" t="inlineStr">
+      <c r="B625" s="21" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - CONSERVAS - SARDINHAS</t>
         </is>
       </c>
-      <c r="C625" t="inlineStr">
+      <c r="C625" s="21" t="inlineStr">
         <is>
           <t>SARDINHA COQUEIRO ÓLEO 125G</t>
         </is>
       </c>
-      <c r="D625" t="inlineStr">
+      <c r="D625" s="21" t="inlineStr">
         <is>
           <t>SARDINHA COQUEIRO 125G ÓLEO</t>
         </is>
@@ -13577,20 +13591,20 @@
       </c>
     </row>
     <row r="653">
-      <c r="A653" s="17" t="n">
+      <c r="A653" s="8" t="n">
         <v>112978</v>
       </c>
-      <c r="B653" s="17" t="inlineStr">
+      <c r="B653" s="8" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - FARINHAS E DERIVADOS</t>
         </is>
       </c>
-      <c r="C653" s="17" t="inlineStr">
+      <c r="C653" s="8" t="inlineStr">
         <is>
           <t>CUSCUZ DE MILHO SINHA 500GR</t>
         </is>
       </c>
-      <c r="D653" s="17" t="inlineStr">
+      <c r="D653" s="8" t="inlineStr">
         <is>
           <t>CUSCUZ DE MILHO SINHA 500G</t>
         </is>
@@ -14277,20 +14291,20 @@
       </c>
     </row>
     <row r="688">
-      <c r="A688" s="17" t="n">
+      <c r="A688" s="21" t="n">
         <v>100027</v>
       </c>
-      <c r="B688" s="17" t="inlineStr">
+      <c r="B688" s="21" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - FARINHAS E DERIVADOS</t>
         </is>
       </c>
-      <c r="C688" s="17" t="inlineStr">
+      <c r="C688" s="21" t="inlineStr">
         <is>
           <t>FARINHA TRIGO ORQUIDEA 1KG SEM FERMENTO</t>
         </is>
       </c>
-      <c r="D688" s="17" t="inlineStr">
+      <c r="D688" s="21" t="inlineStr">
         <is>
           <t>FARINHA DE TRIGO ORQUIDEA 1KG SEM FERMENTO</t>
         </is>
@@ -14897,20 +14911,20 @@
       </c>
     </row>
     <row r="719">
-      <c r="A719" t="n">
+      <c r="A719" s="21" t="n">
         <v>100120</v>
       </c>
-      <c r="B719" t="inlineStr">
+      <c r="B719" s="21" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - FARINHAS E DERIVADOS</t>
         </is>
       </c>
-      <c r="C719" t="inlineStr">
+      <c r="C719" s="21" t="inlineStr">
         <is>
           <t>FLOCÃO DE MILHO BONOMILHO 500G</t>
         </is>
       </c>
-      <c r="D719" t="inlineStr">
+      <c r="D719" s="21" t="inlineStr">
         <is>
           <t>FLOCÃO DE MILHO BONOMILHO 500G</t>
         </is>
@@ -15297,40 +15311,40 @@
       </c>
     </row>
     <row r="739">
-      <c r="A739" s="17" t="n">
+      <c r="A739" s="8" t="n">
         <v>149122</v>
       </c>
-      <c r="B739" s="17" t="inlineStr">
+      <c r="B739" s="8" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - FARINHAS E DERIVADOS</t>
         </is>
       </c>
-      <c r="C739" s="17" t="inlineStr">
+      <c r="C739" s="8" t="inlineStr">
         <is>
           <t>MASSA P/ TAPIOCA AMAFIL 1KG</t>
         </is>
       </c>
-      <c r="D739" s="17" t="inlineStr">
+      <c r="D739" s="8" t="inlineStr">
         <is>
           <t>MASSA PARA TAPIOCA AMAFIL 1KG</t>
         </is>
       </c>
     </row>
     <row r="740">
-      <c r="A740" t="n">
+      <c r="A740" s="21" t="n">
         <v>149121</v>
       </c>
-      <c r="B740" t="inlineStr">
+      <c r="B740" s="21" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - FARINHAS E DERIVADOS</t>
         </is>
       </c>
-      <c r="C740" t="inlineStr">
+      <c r="C740" s="21" t="inlineStr">
         <is>
           <t>MASSA P/ TAPIOCA AMAFIL 500G</t>
         </is>
       </c>
-      <c r="D740" t="inlineStr">
+      <c r="D740" s="21" t="inlineStr">
         <is>
           <t>MASSA PARA TAPIOCA AMAFIL 500G</t>
         </is>
@@ -16217,20 +16231,20 @@
       </c>
     </row>
     <row r="785">
-      <c r="A785" s="9" t="n">
+      <c r="A785" s="7" t="n">
         <v>100074</v>
       </c>
-      <c r="B785" s="9" t="inlineStr">
+      <c r="B785" s="7" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - FARINHAS E DERIVADOS</t>
         </is>
       </c>
-      <c r="C785" s="9" t="inlineStr">
+      <c r="C785" s="7" t="inlineStr">
         <is>
           <t>POLVILHO AMAFIL 1KG AZEDO EMB PAPEL</t>
         </is>
       </c>
-      <c r="D785" s="9" t="inlineStr">
+      <c r="D785" s="7" t="inlineStr">
         <is>
           <t>POLVILHO AZEDO AMAFIL PAPEL 1KG</t>
         </is>
@@ -16377,20 +16391,20 @@
       </c>
     </row>
     <row r="793">
-      <c r="A793" t="n">
+      <c r="A793" s="21" t="n">
         <v>128920</v>
       </c>
-      <c r="B793" t="inlineStr">
+      <c r="B793" s="21" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - FARINHAS E DERIVADOS</t>
         </is>
       </c>
-      <c r="C793" t="inlineStr">
+      <c r="C793" s="21" t="inlineStr">
         <is>
           <t>POLVILHO MATUTO 1KG DOCE</t>
         </is>
       </c>
-      <c r="D793" t="inlineStr">
+      <c r="D793" s="21" t="inlineStr">
         <is>
           <t>POLVILHO MATUTO 1KG DOCE</t>
         </is>
@@ -16617,20 +16631,20 @@
       </c>
     </row>
     <row r="805">
-      <c r="A805" s="17" t="n">
+      <c r="A805" s="13" t="n">
         <v>284048</v>
       </c>
-      <c r="B805" s="17" t="inlineStr">
+      <c r="B805" s="13" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - GORDURAS E MARGARINAS</t>
         </is>
       </c>
-      <c r="C805" s="17" t="inlineStr">
+      <c r="C805" s="13" t="inlineStr">
         <is>
           <t>MANTEIGA DE COCO PUROCOCO OHANA 200G</t>
         </is>
       </c>
-      <c r="D805" s="17" t="inlineStr">
+      <c r="D805" s="13" t="inlineStr">
         <is>
           <t>MANTEIGA DE COCO PUROCOCO OHANA 200G</t>
         </is>
@@ -16777,20 +16791,20 @@
       </c>
     </row>
     <row r="813">
-      <c r="A813" s="17" t="n">
+      <c r="A813" s="18" t="n">
         <v>336816</v>
       </c>
-      <c r="B813" s="17" t="inlineStr">
+      <c r="B813" s="18" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - GORDURAS E MARGARINAS</t>
         </is>
       </c>
-      <c r="C813" s="17" t="inlineStr">
+      <c r="C813" s="18" t="inlineStr">
         <is>
           <t>MANTEIGA QUEIJOLEITE 200GR DE PRIMEIRA Q</t>
         </is>
       </c>
-      <c r="D813" s="17" t="inlineStr">
+      <c r="D813" s="18" t="inlineStr">
         <is>
           <t>MANTEIGA QUEIJOLEITE 200G PRIMEIRA QUALIDADE</t>
         </is>
@@ -16897,20 +16911,20 @@
       </c>
     </row>
     <row r="819">
-      <c r="A819" t="n">
+      <c r="A819" s="18" t="n">
         <v>276943</v>
       </c>
-      <c r="B819" t="inlineStr">
+      <c r="B819" s="18" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - GORDURAS E MARGARINAS</t>
         </is>
       </c>
-      <c r="C819" t="inlineStr">
+      <c r="C819" s="18" t="inlineStr">
         <is>
           <t>MARGARINA DELICIA 1KG C CREME DE LEITE</t>
         </is>
       </c>
-      <c r="D819" t="inlineStr">
+      <c r="D819" s="18" t="inlineStr">
         <is>
           <t>MARGARINA DELICIA 1KG COM CREME DE LEITE</t>
         </is>
@@ -17017,20 +17031,20 @@
       </c>
     </row>
     <row r="825">
-      <c r="A825" s="17" t="n">
+      <c r="A825" s="13" t="n">
         <v>104651</v>
       </c>
-      <c r="B825" s="17" t="inlineStr">
+      <c r="B825" s="13" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - GORDURAS E MARGARINAS</t>
         </is>
       </c>
-      <c r="C825" s="17" t="inlineStr">
+      <c r="C825" s="13" t="inlineStr">
         <is>
           <t>MARGARINA DELINE C/SAL 500G</t>
         </is>
       </c>
-      <c r="D825" s="17" t="inlineStr">
+      <c r="D825" s="13" t="inlineStr">
         <is>
           <t>MARGARINA DELINE 500G COM SAL</t>
         </is>
@@ -17077,20 +17091,20 @@
       </c>
     </row>
     <row r="828">
-      <c r="A828" s="9" t="n">
+      <c r="A828" s="7" t="n">
         <v>146752</v>
       </c>
-      <c r="B828" s="9" t="inlineStr">
+      <c r="B828" s="7" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - GORDURAS E MARGARINAS</t>
         </is>
       </c>
-      <c r="C828" s="9" t="inlineStr">
+      <c r="C828" s="7" t="inlineStr">
         <is>
           <t>MARGARINA DORIANA CR 500 GR</t>
         </is>
       </c>
-      <c r="D828" s="9" t="inlineStr">
+      <c r="D828" s="7" t="inlineStr">
         <is>
           <t>MARGARINA DORIANA 500G CREMOSA</t>
         </is>
@@ -17257,20 +17271,20 @@
       </c>
     </row>
     <row r="837">
-      <c r="A837" s="17" t="n">
+      <c r="A837" s="13" t="n">
         <v>182503</v>
       </c>
-      <c r="B837" s="17" t="inlineStr">
+      <c r="B837" s="13" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - GORDURAS E MARGARINAS</t>
         </is>
       </c>
-      <c r="C837" s="17" t="inlineStr">
+      <c r="C837" s="13" t="inlineStr">
         <is>
           <t>MARGARINA 77% C/ SAL VIGOR 250G SABOR MA</t>
         </is>
       </c>
-      <c r="D837" s="17" t="inlineStr">
+      <c r="D837" s="13" t="inlineStr">
         <is>
           <t>MARGARINA VIGOR 77% 250G COM SAL SABOR MANTEIGA</t>
         </is>
@@ -17497,20 +17511,20 @@
       </c>
     </row>
     <row r="849">
-      <c r="A849" s="9" t="n">
+      <c r="A849" s="7" t="n">
         <v>298970</v>
       </c>
-      <c r="B849" s="9" t="inlineStr">
+      <c r="B849" s="7" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - LATICÍNIOS - BEBIDAS LACTEAS</t>
         </is>
       </c>
-      <c r="C849" s="9" t="inlineStr">
+      <c r="C849" s="7" t="inlineStr">
         <is>
           <t>BEBIDA LACTEA PIRACANJUBA 1LT WHEY COCO</t>
         </is>
       </c>
-      <c r="D849" s="9" t="inlineStr">
+      <c r="D849" s="7" t="inlineStr">
         <is>
           <t>BEBIDA LACTEA PIRACANJUBA 1L WHEY COCO</t>
         </is>
@@ -17617,40 +17631,40 @@
       </c>
     </row>
     <row r="855">
-      <c r="A855" t="n">
+      <c r="A855" s="18" t="n">
         <v>173935</v>
       </c>
-      <c r="B855" t="inlineStr">
+      <c r="B855" s="18" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - LATICÍNIOS - BEBIDAS LACTEAS</t>
         </is>
       </c>
-      <c r="C855" t="inlineStr">
+      <c r="C855" s="18" t="inlineStr">
         <is>
           <t>DANONINHO 320G MORANGO</t>
         </is>
       </c>
-      <c r="D855" t="inlineStr">
+      <c r="D855" s="18" t="inlineStr">
         <is>
           <t>DANONINHO 320G MORANGO</t>
         </is>
       </c>
     </row>
     <row r="856">
-      <c r="A856" s="9" t="n">
+      <c r="A856" s="18" t="n">
         <v>173606</v>
       </c>
-      <c r="B856" s="9" t="inlineStr">
+      <c r="B856" s="18" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - LATICÍNIOS - BEBIDAS LACTEAS</t>
         </is>
       </c>
-      <c r="C856" s="9" t="inlineStr">
+      <c r="C856" s="18" t="inlineStr">
         <is>
           <t>DANONINHO 320G MULTIFRUTAS</t>
         </is>
       </c>
-      <c r="D856" s="9" t="inlineStr">
+      <c r="D856" s="18" t="inlineStr">
         <is>
           <t>DANONINHO 320G MULTIFRUTAS</t>
         </is>
@@ -17897,20 +17911,20 @@
       </c>
     </row>
     <row r="869">
-      <c r="A869" s="9" t="n">
+      <c r="A869" s="7" t="n">
         <v>246976</v>
       </c>
-      <c r="B869" s="9" t="inlineStr">
+      <c r="B869" s="7" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - LATICÍNIOS - BEBIDAS LACTEAS</t>
         </is>
       </c>
-      <c r="C869" s="9" t="inlineStr">
+      <c r="C869" s="7" t="inlineStr">
         <is>
           <t>IOGURTE DANONE 1250GR VITAINA DE FRUTAS</t>
         </is>
       </c>
-      <c r="D869" s="9" t="inlineStr">
+      <c r="D869" s="7" t="inlineStr">
         <is>
           <t>IOGURTE DANONE 1250G VITAMINA DE FRUTAS</t>
         </is>
@@ -18237,40 +18251,40 @@
       </c>
     </row>
     <row r="886">
-      <c r="A886" s="19" t="n">
+      <c r="A886" s="13" t="n">
         <v>101063</v>
       </c>
-      <c r="B886" s="19" t="inlineStr">
+      <c r="B886" s="13" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - LATICÍNIOS - DERIVADOS LACTEOS</t>
         </is>
       </c>
-      <c r="C886" s="19" t="inlineStr">
+      <c r="C886" s="13" t="inlineStr">
         <is>
           <t>CREME LEITE PIRACANJUBA 200GR UHT</t>
         </is>
       </c>
-      <c r="D886" s="19" t="inlineStr">
+      <c r="D886" s="13" t="inlineStr">
         <is>
           <t>CREME DE LEITE PIRACANJUBA 200G</t>
         </is>
       </c>
     </row>
     <row r="887">
-      <c r="A887" t="n">
+      <c r="A887" s="21" t="n">
         <v>193295</v>
       </c>
-      <c r="B887" t="inlineStr">
+      <c r="B887" s="21" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - LATICÍNIOS - DERIVADOS LACTEOS</t>
         </is>
       </c>
-      <c r="C887" t="inlineStr">
+      <c r="C887" s="21" t="inlineStr">
         <is>
           <t>CREME DE LEITE TRIANGULO 200GR 17%GORDUR</t>
         </is>
       </c>
-      <c r="D887" t="inlineStr">
+      <c r="D887" s="21" t="inlineStr">
         <is>
           <t>CREME DE LEITE TRIANGULO 200G 17% GORDURA</t>
         </is>
@@ -18497,40 +18511,40 @@
       </c>
     </row>
     <row r="899">
-      <c r="A899" s="19" t="n">
+      <c r="A899" s="13" t="n">
         <v>101083</v>
       </c>
-      <c r="B899" s="19" t="inlineStr">
+      <c r="B899" s="13" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - LATICÍNIOS - DERIVADOS LACTEOS</t>
         </is>
       </c>
-      <c r="C899" s="19" t="inlineStr">
+      <c r="C899" s="13" t="inlineStr">
         <is>
           <t>LEITE CONDENSADO PIRACANJUBA 395GR TP</t>
         </is>
       </c>
-      <c r="D899" s="19" t="inlineStr">
+      <c r="D899" s="13" t="inlineStr">
         <is>
           <t>LEITE CONDENSADO PIRACANJUBA 395G</t>
         </is>
       </c>
     </row>
     <row r="900">
-      <c r="A900" t="n">
+      <c r="A900" s="21" t="n">
         <v>220451</v>
       </c>
-      <c r="B900" t="inlineStr">
+      <c r="B900" s="21" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - LATICÍNIOS - DERIVADOS LACTEOS</t>
         </is>
       </c>
-      <c r="C900" t="inlineStr">
+      <c r="C900" s="21" t="inlineStr">
         <is>
           <t>LEITE COND. TRIANGULO 395G TP SEMI</t>
         </is>
       </c>
-      <c r="D900" t="inlineStr">
+      <c r="D900" s="21" t="inlineStr">
         <is>
           <t>LEITE CONDENSADO TRIANGULO 395G SEMIDESNATADO</t>
         </is>
@@ -18817,40 +18831,40 @@
       </c>
     </row>
     <row r="915">
-      <c r="A915" s="9" t="n">
+      <c r="A915" s="7" t="n">
         <v>238317</v>
       </c>
-      <c r="B915" s="9" t="inlineStr">
+      <c r="B915" s="7" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - LATICÍNIOS - LEITE</t>
         </is>
       </c>
-      <c r="C915" s="9" t="inlineStr">
+      <c r="C915" s="7" t="inlineStr">
         <is>
           <t>LEITE MOLICO 1LT ZERO LACTOSE +PROTEINA</t>
         </is>
       </c>
-      <c r="D915" s="9" t="inlineStr">
+      <c r="D915" s="7" t="inlineStr">
         <is>
           <t>LEITE LONGA VIDA MOLICO 1L ZERO LACTOSE +PROTEINA</t>
         </is>
       </c>
     </row>
     <row r="916">
-      <c r="A916" s="9" t="n">
+      <c r="A916" s="7" t="n">
         <v>228090</v>
       </c>
-      <c r="B916" s="9" t="inlineStr">
+      <c r="B916" s="7" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - LATICÍNIOS - LEITE</t>
         </is>
       </c>
-      <c r="C916" s="9" t="inlineStr">
+      <c r="C916" s="7" t="inlineStr">
         <is>
           <t>LEITE MOLICO 1L DESNATADO ZERO LACTOSE E</t>
         </is>
       </c>
-      <c r="D916" s="9" t="inlineStr">
+      <c r="D916" s="7" t="inlineStr">
         <is>
           <t>LEITE LONGA VIDA MOLICO 1L ZERO LACTOSE DESNATADO</t>
         </is>
@@ -18897,10 +18911,10 @@
       </c>
     </row>
     <row r="919">
-      <c r="A919" s="19" t="n">
+      <c r="A919" s="13" t="n">
         <v>108252</v>
       </c>
-      <c r="B919" s="19" t="inlineStr">
+      <c r="B919" s="13" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - LATICÍNIOS - LEITE</t>
         </is>
@@ -18910,7 +18924,7 @@
           <t>LEITE PIRACANJUBA TP 1L EDGE DESNATADO</t>
         </is>
       </c>
-      <c r="D919" s="19" t="inlineStr">
+      <c r="D919" s="13" t="inlineStr">
         <is>
           <t>LEITE LONGA VIDA PIRACANJUBA 1L EDGE DESNATADO</t>
         </is>
@@ -18977,20 +18991,20 @@
       </c>
     </row>
     <row r="923">
-      <c r="A923" s="9" t="n">
+      <c r="A923" s="7" t="n">
         <v>328879</v>
       </c>
-      <c r="B923" s="9" t="inlineStr">
+      <c r="B923" s="7" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - LATICÍNIOS - LEITE</t>
         </is>
       </c>
-      <c r="C923" s="9" t="inlineStr">
+      <c r="C923" s="7" t="inlineStr">
         <is>
           <t>LEITE LV PIRACANJUBA 1L +PROTEIN SEMI ZERO LAC</t>
         </is>
       </c>
-      <c r="D923" s="9" t="inlineStr">
+      <c r="D923" s="7" t="inlineStr">
         <is>
           <t>LEITE LONGA VIDA PIRACANJUBA ZERO LACTOSE 1L SEMI DESNATADO +PROTEIN</t>
         </is>
@@ -19017,20 +19031,20 @@
       </c>
     </row>
     <row r="925">
-      <c r="A925" t="n">
+      <c r="A925" s="21" t="n">
         <v>106922</v>
       </c>
-      <c r="B925" t="inlineStr">
+      <c r="B925" s="21" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - LATICÍNIOS - LEITE EM PÓ</t>
         </is>
       </c>
-      <c r="C925" t="inlineStr">
+      <c r="C925" s="21" t="inlineStr">
         <is>
           <t>LEITE EM PÓ CCGL INTEGRAL 1KG</t>
         </is>
       </c>
-      <c r="D925" t="inlineStr">
+      <c r="D925" s="21" t="inlineStr">
         <is>
           <t>LEITE EM PÓ CCGL 1KG INTEGRAL</t>
         </is>
@@ -19137,20 +19151,20 @@
       </c>
     </row>
     <row r="931">
-      <c r="A931" t="n">
+      <c r="A931" s="21" t="n">
         <v>307145</v>
       </c>
-      <c r="B931" t="inlineStr">
+      <c r="B931" s="21" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - LATICÍNIOS - LEITE EM PÓ</t>
         </is>
       </c>
-      <c r="C931" t="inlineStr">
+      <c r="C931" s="21" t="inlineStr">
         <is>
           <t>LEITE EM PÓ NINHO 380GR INTEGRAL INSTANTANE</t>
         </is>
       </c>
-      <c r="D931" t="inlineStr">
+      <c r="D931" s="21" t="inlineStr">
         <is>
           <t>LEITE EM PÓ NINHO LATA 380G INTEGRAL INSTANTANEO</t>
         </is>
@@ -19217,20 +19231,20 @@
       </c>
     </row>
     <row r="935">
-      <c r="A935" s="9" t="n">
+      <c r="A935" s="7" t="n">
         <v>325485</v>
       </c>
-      <c r="B935" s="9" t="inlineStr">
+      <c r="B935" s="7" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - LATICÍNIOS - LEITE EM PÓ</t>
         </is>
       </c>
-      <c r="C935" s="9" t="inlineStr">
+      <c r="C935" s="7" t="inlineStr">
         <is>
           <t>LEITE EM PO PIRACANJUBA 380GR INTEGRAL INST.</t>
         </is>
       </c>
-      <c r="D935" s="9" t="inlineStr">
+      <c r="D935" s="7" t="inlineStr">
         <is>
           <t>LEITE EM PÓ PIRACANJUBA 380G INTEGRAL INSTANTANEO</t>
         </is>
@@ -19497,20 +19511,20 @@
       </c>
     </row>
     <row r="949">
-      <c r="A949" t="n">
+      <c r="A949" s="18" t="n">
         <v>158733</v>
       </c>
-      <c r="B949" t="inlineStr">
+      <c r="B949" s="18" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - LATICÍNIOS - QUEIJO</t>
         </is>
       </c>
-      <c r="C949" t="inlineStr">
+      <c r="C949" s="18" t="inlineStr">
         <is>
           <t>QUEIJO MUSSARELA PIRAC FATIADO 150GR</t>
         </is>
       </c>
-      <c r="D949" t="inlineStr">
+      <c r="D949" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">QUEIJO MUSSARELA PIRACANJUBA 150G FATIADO </t>
         </is>
@@ -19957,40 +19971,40 @@
       </c>
     </row>
     <row r="972">
-      <c r="A972" s="17" t="n">
+      <c r="A972" s="18" t="n">
         <v>104770</v>
       </c>
-      <c r="B972" s="17" t="inlineStr">
+      <c r="B972" s="18" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - LATICÍNIOS - QUEIJO</t>
         </is>
       </c>
-      <c r="C972" s="17" t="inlineStr">
+      <c r="C972" s="18" t="inlineStr">
         <is>
           <t>REQUEIJAO CREM TIROLEZ 200GR</t>
         </is>
       </c>
-      <c r="D972" s="17" t="inlineStr">
+      <c r="D972" s="18" t="inlineStr">
         <is>
           <t>REQUEIJAO CREMOSO TIROLEZ 200G</t>
         </is>
       </c>
     </row>
     <row r="973">
-      <c r="A973" t="n">
+      <c r="A973" s="18" t="n">
         <v>133484</v>
       </c>
-      <c r="B973" t="inlineStr">
+      <c r="B973" s="18" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - LATICÍNIOS - QUEIJO</t>
         </is>
       </c>
-      <c r="C973" t="inlineStr">
+      <c r="C973" s="18" t="inlineStr">
         <is>
           <t>REQUEIJAO CREMOSO TIROLEZ LIGHT 200GR</t>
         </is>
       </c>
-      <c r="D973" t="inlineStr">
+      <c r="D973" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">REQUEIJÃO CREMOSO TIROLEZ 200G LIGHT </t>
         </is>
@@ -20077,20 +20091,20 @@
       </c>
     </row>
     <row r="978">
-      <c r="A978" s="17" t="n">
+      <c r="A978" s="13" t="n">
         <v>222973</v>
       </c>
-      <c r="B978" s="17" t="inlineStr">
+      <c r="B978" s="13" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - LATICÍNIOS - QUEIJO</t>
         </is>
       </c>
-      <c r="C978" s="17" t="inlineStr">
+      <c r="C978" s="13" t="inlineStr">
         <is>
           <t>QUEIJO MUSSARELA BOUA 150GR FATIADA</t>
         </is>
       </c>
-      <c r="D978" s="17" t="inlineStr">
+      <c r="D978" s="13" t="inlineStr">
         <is>
           <t>QUEIJO MUSSARELA BOUA 150G FATIADA</t>
         </is>
@@ -20177,20 +20191,20 @@
       </c>
     </row>
     <row r="983">
-      <c r="A983" s="9" t="n">
+      <c r="A983" s="7" t="n">
         <v>173725</v>
       </c>
-      <c r="B983" s="9" t="inlineStr">
+      <c r="B983" s="7" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - MASSAS</t>
         </is>
       </c>
-      <c r="C983" s="9" t="inlineStr">
+      <c r="C983" s="7" t="inlineStr">
         <is>
           <t>MACARRAO CRISTAL 500GR INTEGRAL  ESPAGUETE</t>
         </is>
       </c>
-      <c r="D983" s="9" t="inlineStr">
+      <c r="D983" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">MACARRÃO CRISTAL ESPAGUETE 500G INTEGRAL </t>
         </is>
@@ -20237,20 +20251,20 @@
       </c>
     </row>
     <row r="986">
-      <c r="A986" t="n">
+      <c r="A986" s="21" t="n">
         <v>290255</v>
       </c>
-      <c r="B986" t="inlineStr">
+      <c r="B986" s="21" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - MASSAS</t>
         </is>
       </c>
-      <c r="C986" t="inlineStr">
+      <c r="C986" s="21" t="inlineStr">
         <is>
           <t>MACARRÃO CRISTAL 500GR SEMOLA ESPAGUETE</t>
         </is>
       </c>
-      <c r="D986" t="inlineStr">
+      <c r="D986" s="21" t="inlineStr">
         <is>
           <t>MACARRÃO CRISTAL SEMOLA ESPAGUETE 500G</t>
         </is>
@@ -20677,20 +20691,20 @@
       </c>
     </row>
     <row r="1008">
-      <c r="A1008" s="19" t="n">
+      <c r="A1008" s="13" t="n">
         <v>100642</v>
       </c>
-      <c r="B1008" s="19" t="inlineStr">
+      <c r="B1008" s="13" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - MASSAS</t>
         </is>
       </c>
-      <c r="C1008" s="19" t="inlineStr">
+      <c r="C1008" s="13" t="inlineStr">
         <is>
           <t>MAC PAULISTA ESPAGUETE 500GR SEMOLA</t>
         </is>
       </c>
-      <c r="D1008" s="19" t="inlineStr">
+      <c r="D1008" s="13" t="inlineStr">
         <is>
           <t>MACARRÃO PAULISTA ESPAGUETE SEMOLA 500G</t>
         </is>
@@ -20897,20 +20911,20 @@
       </c>
     </row>
     <row r="1019">
-      <c r="A1019" t="n">
+      <c r="A1019" s="21" t="n">
         <v>106791</v>
       </c>
-      <c r="B1019" t="inlineStr">
+      <c r="B1019" s="21" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - MASSAS</t>
         </is>
       </c>
-      <c r="C1019" t="inlineStr">
+      <c r="C1019" s="21" t="inlineStr">
         <is>
           <t>MAC PAULISTA PADRE NOSSO SEMOLA 500GR</t>
         </is>
       </c>
-      <c r="D1019" t="inlineStr">
+      <c r="D1019" s="21" t="inlineStr">
         <is>
           <t>MACARRÃO PAULISTA SEMOLA PADRE NOSSO 500G</t>
         </is>
@@ -21357,20 +21371,20 @@
       </c>
     </row>
     <row r="1042">
-      <c r="A1042" s="9" t="n">
+      <c r="A1042" s="7" t="n">
         <v>203414</v>
       </c>
-      <c r="B1042" s="9" t="inlineStr">
+      <c r="B1042" s="7" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - MASSAS</t>
         </is>
       </c>
-      <c r="C1042" s="9" t="inlineStr">
+      <c r="C1042" s="7" t="inlineStr">
         <is>
           <t>RAVIOLI MEZZANI 4 QUEIJOS 400G</t>
         </is>
       </c>
-      <c r="D1042" s="9" t="inlineStr">
+      <c r="D1042" s="7" t="inlineStr">
         <is>
           <t>RAVIOLI MEZZANI 400G 4 QUEIJOS</t>
         </is>
@@ -21397,20 +21411,20 @@
       </c>
     </row>
     <row r="1044">
-      <c r="A1044" s="9" t="n">
+      <c r="A1044" s="7" t="n">
         <v>104812</v>
       </c>
-      <c r="B1044" s="9" t="inlineStr">
+      <c r="B1044" s="7" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - MASSAS</t>
         </is>
       </c>
-      <c r="C1044" s="9" t="inlineStr">
+      <c r="C1044" s="7" t="inlineStr">
         <is>
           <t>RAVIOLI MEZZANI FRANGO 400G</t>
         </is>
       </c>
-      <c r="D1044" s="9" t="inlineStr">
+      <c r="D1044" s="7" t="inlineStr">
         <is>
           <t>RAVIOLI MEZZANI 400G FRANGO</t>
         </is>
@@ -23057,20 +23071,20 @@
       </c>
     </row>
     <row r="1127">
-      <c r="A1127" s="17" t="n">
+      <c r="A1127" s="13" t="n">
         <v>220822</v>
       </c>
-      <c r="B1127" s="17" t="inlineStr">
+      <c r="B1127" s="13" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - PÃES E BOLOS</t>
         </is>
       </c>
-      <c r="C1127" s="17" t="inlineStr">
+      <c r="C1127" s="13" t="inlineStr">
         <is>
           <t>PAO DE ALHO DI NAPOLI 350GR C/ QJO ERVAS</t>
         </is>
       </c>
-      <c r="D1127" s="17" t="inlineStr">
+      <c r="D1127" s="13" t="inlineStr">
         <is>
           <t>PÃO DE ALHO DI NAPOLI 350G QUEIJO E ERVAS</t>
         </is>
@@ -23337,20 +23351,20 @@
       </c>
     </row>
     <row r="1141">
-      <c r="A1141" s="17" t="n">
+      <c r="A1141" s="8" t="n">
         <v>110095</v>
       </c>
-      <c r="B1141" s="17" t="inlineStr">
+      <c r="B1141" s="8" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - PÃES E BOLOS</t>
         </is>
       </c>
-      <c r="C1141" s="17" t="inlineStr">
+      <c r="C1141" s="8" t="inlineStr">
         <is>
           <t>PAO FORMA PULLMAN 480GR TRADICIONAL</t>
         </is>
       </c>
-      <c r="D1141" s="17" t="inlineStr">
+      <c r="D1141" s="8" t="inlineStr">
         <is>
           <t>PÃO DE FORMA PULLMAN 480G TRADICIONAL</t>
         </is>
@@ -23417,20 +23431,20 @@
       </c>
     </row>
     <row r="1145">
-      <c r="A1145" s="9" t="n">
+      <c r="A1145" s="7" t="n">
         <v>346333</v>
       </c>
-      <c r="B1145" s="9" t="inlineStr">
+      <c r="B1145" s="7" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - PASTAS E CREMES</t>
         </is>
       </c>
-      <c r="C1145" s="9" t="inlineStr">
+      <c r="C1145" s="7" t="inlineStr">
         <is>
           <t>PASTA LA GANEXA 450GR CARAMEL FLOR SAL</t>
         </is>
       </c>
-      <c r="D1145" s="9" t="inlineStr">
+      <c r="D1145" s="7" t="inlineStr">
         <is>
           <t>PASTA DE AMENDOIM LA GANEXA 450G CARAMELO E FLOR SAL</t>
         </is>
@@ -23457,20 +23471,20 @@
       </c>
     </row>
     <row r="1147">
-      <c r="A1147" s="9" t="n">
+      <c r="A1147" s="7" t="n">
         <v>335885</v>
       </c>
-      <c r="B1147" s="9" t="inlineStr">
+      <c r="B1147" s="7" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - PASTAS E CREMES</t>
         </is>
       </c>
-      <c r="C1147" s="9" t="inlineStr">
+      <c r="C1147" s="7" t="inlineStr">
         <is>
           <t>PASTA LA GANEXA 450GR CHOCOLATE CROC</t>
         </is>
       </c>
-      <c r="D1147" s="9" t="inlineStr">
+      <c r="D1147" s="7" t="inlineStr">
         <is>
           <t>PASTA DE AMENDOIM LA GANEXA 450G CHOCOLATE CROCANTE</t>
         </is>
@@ -23517,20 +23531,20 @@
       </c>
     </row>
     <row r="1150">
-      <c r="A1150" s="9" t="n">
+      <c r="A1150" s="7" t="n">
         <v>335893</v>
       </c>
-      <c r="B1150" s="9" t="inlineStr">
+      <c r="B1150" s="7" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - PASTAS E CREMES</t>
         </is>
       </c>
-      <c r="C1150" s="9" t="inlineStr">
+      <c r="C1150" s="7" t="inlineStr">
         <is>
           <t>PASTA LA GANEXA 450GR PISTACHE</t>
         </is>
       </c>
-      <c r="D1150" s="9" t="inlineStr">
+      <c r="D1150" s="7" t="inlineStr">
         <is>
           <t>PASTA DE AMENDOIM LA GANEXA 450G PISTACHE</t>
         </is>
@@ -24237,20 +24251,20 @@
       </c>
     </row>
     <row r="1186">
-      <c r="A1186" t="n">
+      <c r="A1186" s="21" t="n">
         <v>105842</v>
       </c>
-      <c r="B1186" t="inlineStr">
+      <c r="B1186" s="21" t="inlineStr">
         <is>
           <t>#03 AÇOUGUE - #01 AVES</t>
         </is>
       </c>
-      <c r="C1186" t="inlineStr">
+      <c r="C1186" s="21" t="inlineStr">
         <is>
           <t>ASA FRANGO KG</t>
         </is>
       </c>
-      <c r="D1186" t="inlineStr">
+      <c r="D1186" s="21" t="inlineStr">
         <is>
           <t>ASA DE FRANGO KG</t>
         </is>
@@ -24297,20 +24311,20 @@
       </c>
     </row>
     <row r="1189">
-      <c r="A1189" s="17" t="n">
+      <c r="A1189" s="18" t="n">
         <v>224719</v>
       </c>
-      <c r="B1189" s="17" t="inlineStr">
+      <c r="B1189" s="18" t="inlineStr">
         <is>
           <t>#03 AÇOUGUE - #01 AVES</t>
         </is>
       </c>
-      <c r="C1189" s="17" t="inlineStr">
+      <c r="C1189" s="18" t="inlineStr">
         <is>
           <t>CORACAO BAND CONG BONASA 1KG</t>
         </is>
       </c>
-      <c r="D1189" s="17" t="inlineStr">
+      <c r="D1189" s="18" t="inlineStr">
         <is>
           <t>CORAÇÃO DE FRANGO BONASA BDJ 1KG</t>
         </is>
@@ -24417,20 +24431,20 @@
       </c>
     </row>
     <row r="1195">
-      <c r="A1195" t="n">
+      <c r="A1195" s="21" t="n">
         <v>105838</v>
       </c>
-      <c r="B1195" t="inlineStr">
+      <c r="B1195" s="21" t="inlineStr">
         <is>
           <t>#03 AÇOUGUE - #01 AVES</t>
         </is>
       </c>
-      <c r="C1195" t="inlineStr">
+      <c r="C1195" s="21" t="inlineStr">
         <is>
           <t>COXA/SOBRECOXA FRANGO KG</t>
         </is>
       </c>
-      <c r="D1195" t="inlineStr">
+      <c r="D1195" s="21" t="inlineStr">
         <is>
           <t>COXA COM SOBRECOXA DE FRANGO KG</t>
         </is>
@@ -24677,20 +24691,20 @@
       </c>
     </row>
     <row r="1208">
-      <c r="A1208" t="n">
+      <c r="A1208" s="21" t="n">
         <v>105840</v>
       </c>
-      <c r="B1208" t="inlineStr">
+      <c r="B1208" s="21" t="inlineStr">
         <is>
           <t>#03 AÇOUGUE - #01 AVES</t>
         </is>
       </c>
-      <c r="C1208" t="inlineStr">
+      <c r="C1208" s="21" t="inlineStr">
         <is>
           <t>COXINHA DA ASA FRANGO KG</t>
         </is>
       </c>
-      <c r="D1208" t="inlineStr">
+      <c r="D1208" s="21" t="inlineStr">
         <is>
           <t>COXINHA DA ASA DE FRANGO KG</t>
         </is>
@@ -24837,20 +24851,20 @@
       </c>
     </row>
     <row r="1216">
-      <c r="A1216" t="n">
+      <c r="A1216" s="18" t="n">
         <v>306504</v>
       </c>
-      <c r="B1216" t="inlineStr">
+      <c r="B1216" s="18" t="inlineStr">
         <is>
           <t>#03 AÇOUGUE - #01 AVES</t>
         </is>
       </c>
-      <c r="C1216" t="inlineStr">
+      <c r="C1216" s="18" t="inlineStr">
         <is>
           <t>FIGADO FRANGO CONGELADO PERDIGAO 1KG</t>
         </is>
       </c>
-      <c r="D1216" t="inlineStr">
+      <c r="D1216" s="18" t="inlineStr">
         <is>
           <t>FIGADO DE FRANGO PERDIGAO KG</t>
         </is>
@@ -24917,20 +24931,20 @@
       </c>
     </row>
     <row r="1220">
-      <c r="A1220" t="n">
+      <c r="A1220" s="21" t="n">
         <v>109597</v>
       </c>
-      <c r="B1220" t="inlineStr">
+      <c r="B1220" s="21" t="inlineStr">
         <is>
           <t>#03 AÇOUGUE - #01 AVES</t>
         </is>
       </c>
-      <c r="C1220" t="inlineStr">
+      <c r="C1220" s="21" t="inlineStr">
         <is>
           <t>FILE PEITO FRANGO KG</t>
         </is>
       </c>
-      <c r="D1220" t="inlineStr">
+      <c r="D1220" s="21" t="inlineStr">
         <is>
           <t>FILÉ DE PEITO DE FRANGO KG</t>
         </is>
@@ -24957,20 +24971,20 @@
       </c>
     </row>
     <row r="1222">
-      <c r="A1222" s="17" t="n">
+      <c r="A1222" s="13" t="n">
         <v>108770</v>
       </c>
-      <c r="B1222" s="17" t="inlineStr">
+      <c r="B1222" s="13" t="inlineStr">
         <is>
           <t>#03 AÇOUGUE - #01 AVES</t>
         </is>
       </c>
-      <c r="C1222" s="17" t="inlineStr">
+      <c r="C1222" s="13" t="inlineStr">
         <is>
           <t>FILE PEITO S/OP FGO CONG BDJ SADIA 1KG</t>
         </is>
       </c>
-      <c r="D1222" s="17" t="inlineStr">
+      <c r="D1222" s="13" t="inlineStr">
         <is>
           <t>FILÉ DE PEITO DE FRANGO SADIA BDJ 1KG</t>
         </is>
@@ -25037,20 +25051,20 @@
       </c>
     </row>
     <row r="1226">
-      <c r="A1226" s="17" t="n">
+      <c r="A1226" s="18" t="n">
         <v>298784</v>
       </c>
-      <c r="B1226" s="17" t="inlineStr">
+      <c r="B1226" s="18" t="inlineStr">
         <is>
           <t>#03 AÇOUGUE - #01 AVES</t>
         </is>
       </c>
-      <c r="C1226" s="17" t="inlineStr">
+      <c r="C1226" s="19" t="inlineStr">
         <is>
           <t>FILE DE PEITO FRANGO SEARA 1KG BANDEJA</t>
         </is>
       </c>
-      <c r="D1226" s="17" t="inlineStr">
+      <c r="D1226" s="18" t="inlineStr">
         <is>
           <t>FILE DE PEITO DE FRANGO SEARA PCT 1KG</t>
         </is>
@@ -25077,20 +25091,20 @@
       </c>
     </row>
     <row r="1228">
-      <c r="A1228" s="17" t="n">
+      <c r="A1228" s="13" t="n">
         <v>108856</v>
       </c>
-      <c r="B1228" s="17" t="inlineStr">
+      <c r="B1228" s="13" t="inlineStr">
         <is>
           <t>#03 AÇOUGUE - #01 AVES</t>
         </is>
       </c>
-      <c r="C1228" s="17" t="inlineStr">
+      <c r="C1228" s="13" t="inlineStr">
         <is>
           <t>FILE PEITO SADIA PCT S/OPC 1KG PFFZP</t>
         </is>
       </c>
-      <c r="D1228" s="17" t="inlineStr">
+      <c r="D1228" s="13" t="inlineStr">
         <is>
           <t>FILE PEITO DE FRANGO SADIA PCT 1KG</t>
         </is>
@@ -25197,20 +25211,20 @@
       </c>
     </row>
     <row r="1234">
-      <c r="A1234" s="17" t="n">
+      <c r="A1234" s="21" t="n">
         <v>119927</v>
       </c>
-      <c r="B1234" s="17" t="inlineStr">
+      <c r="B1234" s="21" t="inlineStr">
         <is>
           <t>#03 AÇOUGUE - #01 AVES</t>
         </is>
       </c>
-      <c r="C1234" s="17" t="inlineStr">
+      <c r="C1234" s="21" t="inlineStr">
         <is>
           <t>FRANGO CONG AMERICANO KG</t>
         </is>
       </c>
-      <c r="D1234" s="17" t="inlineStr">
+      <c r="D1234" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">FRANGO AMERICANO KG CONGELADO </t>
         </is>
@@ -25337,20 +25351,20 @@
       </c>
     </row>
     <row r="1241">
-      <c r="A1241" t="n">
+      <c r="A1241" s="21" t="n">
         <v>228289</v>
       </c>
-      <c r="B1241" t="inlineStr">
+      <c r="B1241" s="21" t="inlineStr">
         <is>
           <t>#03 AÇOUGUE - #01 AVES</t>
         </is>
       </c>
-      <c r="C1241" t="inlineStr">
+      <c r="C1241" s="21" t="inlineStr">
         <is>
           <t>FRANGO INTEIRO SADIA KG S/ MIUDOS TEMPER</t>
         </is>
       </c>
-      <c r="D1241" t="inlineStr">
+      <c r="D1241" s="21" t="inlineStr">
         <is>
           <t>FRANGO SADIA KG CONGELADO TEMPERADO SEM MIUDOS</t>
         </is>
@@ -25397,20 +25411,20 @@
       </c>
     </row>
     <row r="1244">
-      <c r="A1244" t="n">
+      <c r="A1244" s="21" t="n">
         <v>185934</v>
       </c>
-      <c r="B1244" t="inlineStr">
+      <c r="B1244" s="21" t="inlineStr">
         <is>
           <t>#03 AÇOUGUE - #01 AVES</t>
         </is>
       </c>
-      <c r="C1244" t="inlineStr">
+      <c r="C1244" s="21" t="inlineStr">
         <is>
           <t>GALINHA LEVE NOROESTE CONG KG</t>
         </is>
       </c>
-      <c r="D1244" t="inlineStr">
+      <c r="D1244" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">GALINHA NOROESTE KG CONGELADA </t>
         </is>
@@ -25477,20 +25491,20 @@
       </c>
     </row>
     <row r="1248">
-      <c r="A1248" t="n">
+      <c r="A1248" s="18" t="n">
         <v>289794</v>
       </c>
-      <c r="B1248" t="inlineStr">
+      <c r="B1248" s="18" t="inlineStr">
         <is>
           <t>#03 AÇOUGUE - #01 AVES</t>
         </is>
       </c>
-      <c r="C1248" t="inlineStr">
+      <c r="C1248" s="19" t="inlineStr">
         <is>
           <t>MEIO DA ASA SEARA1KG</t>
         </is>
       </c>
-      <c r="D1248" t="inlineStr">
+      <c r="D1248" s="18" t="inlineStr">
         <is>
           <t>MEIO DA ASA DE FRANGO SEARA 1KG</t>
         </is>
@@ -25537,20 +25551,20 @@
       </c>
     </row>
     <row r="1251">
-      <c r="A1251" t="n">
+      <c r="A1251" s="18" t="n">
         <v>195365</v>
       </c>
-      <c r="B1251" t="inlineStr">
+      <c r="B1251" s="18" t="inlineStr">
         <is>
           <t>#03 AÇOUGUE - #01 AVES</t>
         </is>
       </c>
-      <c r="C1251" t="inlineStr">
+      <c r="C1251" s="19" t="inlineStr">
         <is>
           <t>MIUDOS CONG FGO (MOELA) PCT 1KG PERDIGAO</t>
         </is>
       </c>
-      <c r="D1251" t="inlineStr">
+      <c r="D1251" s="18" t="inlineStr">
         <is>
           <t>MOELA DE FRANGO PERDIGÃO BDJ 1KG</t>
         </is>
@@ -25637,40 +25651,40 @@
       </c>
     </row>
     <row r="1256">
-      <c r="A1256" t="n">
+      <c r="A1256" s="21" t="n">
         <v>150768</v>
       </c>
-      <c r="B1256" t="inlineStr">
+      <c r="B1256" s="21" t="inlineStr">
         <is>
           <t>#03 AÇOUGUE - #01 AVES</t>
         </is>
       </c>
-      <c r="C1256" t="inlineStr">
+      <c r="C1256" s="21" t="inlineStr">
         <is>
           <t>PEITO DE FRANGO INTEIRO KG</t>
         </is>
       </c>
-      <c r="D1256" t="inlineStr">
+      <c r="D1256" s="21" t="inlineStr">
         <is>
           <t>PEITO DE FRANGO KG INTEIRO</t>
         </is>
       </c>
     </row>
     <row r="1257">
-      <c r="A1257" s="17" t="n">
+      <c r="A1257" s="13" t="n">
         <v>302029</v>
       </c>
-      <c r="B1257" s="17" t="inlineStr">
+      <c r="B1257" s="13" t="inlineStr">
         <is>
           <t>#03 AÇOUGUE - #01 AVES</t>
         </is>
       </c>
-      <c r="C1257" s="17" t="inlineStr">
+      <c r="C1257" s="13" t="inlineStr">
         <is>
           <t>PEITO FRANGO SADIA 1KG A PASSARINHO</t>
         </is>
       </c>
-      <c r="D1257" s="17" t="inlineStr">
+      <c r="D1257" s="13" t="inlineStr">
         <is>
           <t>PEITO DE FRANGO SADIA 1KG A PASSARINHO</t>
         </is>
@@ -25817,60 +25831,60 @@
       </c>
     </row>
     <row r="1265">
-      <c r="A1265" s="17" t="n">
+      <c r="A1265" s="18" t="n">
         <v>314513</v>
       </c>
-      <c r="B1265" s="17" t="inlineStr">
+      <c r="B1265" s="18" t="inlineStr">
         <is>
           <t>#03 AÇOUGUE - #01 AVES</t>
         </is>
       </c>
-      <c r="C1265" s="17" t="inlineStr">
+      <c r="C1265" s="19" t="inlineStr">
         <is>
           <t>FILEZINHO DE PEITO FRANGO SEARA 1KG CONG</t>
         </is>
       </c>
-      <c r="D1265" s="17" t="inlineStr">
+      <c r="D1265" s="18" t="inlineStr">
         <is>
           <t>FILEZINHO DE PEITO DE FRANGO SEARA 1KG</t>
         </is>
       </c>
     </row>
     <row r="1266">
-      <c r="A1266" t="n">
+      <c r="A1266" s="20" t="n">
         <v>157014</v>
       </c>
-      <c r="B1266" t="inlineStr">
+      <c r="B1266" s="20" t="inlineStr">
         <is>
           <t>#03 AÇOUGUE - #02 BOVINA</t>
         </is>
       </c>
-      <c r="C1266" t="inlineStr">
+      <c r="C1266" s="20" t="inlineStr">
         <is>
           <t>BOVINO - ACEM C/ OSSO KG</t>
         </is>
       </c>
-      <c r="D1266" t="inlineStr">
+      <c r="D1266" s="20" t="inlineStr">
         <is>
           <t>ACEM BOVINO COM OSSO KG</t>
         </is>
       </c>
     </row>
     <row r="1267">
-      <c r="A1267" s="17" t="n">
+      <c r="A1267" s="8" t="n">
         <v>105470</v>
       </c>
-      <c r="B1267" s="17" t="inlineStr">
+      <c r="B1267" s="8" t="inlineStr">
         <is>
           <t>#03 AÇOUGUE - #02 BOVINA</t>
         </is>
       </c>
-      <c r="C1267" s="17" t="inlineStr">
+      <c r="C1267" s="8" t="inlineStr">
         <is>
           <t>BOVINO - ACEM KG</t>
         </is>
       </c>
-      <c r="D1267" s="17" t="inlineStr">
+      <c r="D1267" s="8" t="inlineStr">
         <is>
           <t>ACEM BOVINO KG</t>
         </is>
@@ -25937,20 +25951,20 @@
       </c>
     </row>
     <row r="1271">
-      <c r="A1271" s="3" t="n">
+      <c r="A1271" s="22" t="n">
         <v>105460</v>
       </c>
-      <c r="B1271" s="3" t="inlineStr">
+      <c r="B1271" s="22" t="inlineStr">
         <is>
           <t>#03 AÇOUGUE - #02 BOVINA</t>
         </is>
       </c>
-      <c r="C1271" s="3" t="inlineStr">
+      <c r="C1271" s="22" t="inlineStr">
         <is>
           <t>BOVINA - BISTECA PALETA KG</t>
         </is>
       </c>
-      <c r="D1271" s="3" t="inlineStr">
+      <c r="D1271" s="22" t="inlineStr">
         <is>
           <t>BISTECA BOVINA DA PALETA KG</t>
         </is>
@@ -25977,20 +25991,20 @@
       </c>
     </row>
     <row r="1273">
-      <c r="A1273" t="n">
+      <c r="A1273" s="21" t="n">
         <v>105461</v>
       </c>
-      <c r="B1273" t="inlineStr">
+      <c r="B1273" s="21" t="inlineStr">
         <is>
           <t>#03 AÇOUGUE - #02 BOVINA</t>
         </is>
       </c>
-      <c r="C1273" t="inlineStr">
+      <c r="C1273" s="21" t="inlineStr">
         <is>
           <t>BOVINO - BISTECA CONTRA FILE KG</t>
         </is>
       </c>
-      <c r="D1273" t="inlineStr">
+      <c r="D1273" s="21" t="inlineStr">
         <is>
           <t>BISTECA BOVINA DO CONTRA FILE KG</t>
         </is>
@@ -26017,40 +26031,40 @@
       </c>
     </row>
     <row r="1275">
-      <c r="A1275" s="16" t="n">
+      <c r="A1275" s="13" t="n">
         <v>239334</v>
       </c>
-      <c r="B1275" s="16" t="inlineStr">
+      <c r="B1275" s="13" t="inlineStr">
         <is>
           <t>#03 AÇOUGUE - #02 BOVINA</t>
         </is>
       </c>
-      <c r="C1275" s="16" t="inlineStr">
+      <c r="C1275" s="13" t="inlineStr">
         <is>
           <t>BOVINO - CAPA DO CONTRA FILE KG</t>
         </is>
       </c>
-      <c r="D1275" s="16" t="inlineStr">
+      <c r="D1275" s="13" t="inlineStr">
         <is>
           <t>CAPA DO CONTRA FILE KG</t>
         </is>
       </c>
     </row>
     <row r="1276">
-      <c r="A1276" s="14" t="n">
+      <c r="A1276" s="13" t="n">
         <v>105457</v>
       </c>
-      <c r="B1276" s="14" t="inlineStr">
+      <c r="B1276" s="13" t="inlineStr">
         <is>
           <t>#03 AÇOUGUE - #02 BOVINA</t>
         </is>
       </c>
-      <c r="C1276" s="14" t="inlineStr">
+      <c r="C1276" s="13" t="inlineStr">
         <is>
           <t>BOVINO - CARNE SERENADA KG</t>
         </is>
       </c>
-      <c r="D1276" s="14" t="inlineStr">
+      <c r="D1276" s="13" t="inlineStr">
         <is>
           <t>CARNE BOVINA SERENADA KG</t>
         </is>
@@ -26077,20 +26091,20 @@
       </c>
     </row>
     <row r="1278">
-      <c r="A1278" t="n">
+      <c r="A1278" s="20" t="n">
         <v>322584</v>
       </c>
-      <c r="B1278" t="inlineStr">
+      <c r="B1278" s="20" t="inlineStr">
         <is>
           <t>#03 AÇOUGUE - #02 BOVINA</t>
         </is>
       </c>
-      <c r="C1278" t="inlineStr">
+      <c r="C1278" s="19" t="inlineStr">
         <is>
           <t>BOVINO - CARNE DE SOL KG PRIMEIRA</t>
         </is>
       </c>
-      <c r="D1278" t="inlineStr">
+      <c r="D1278" s="20" t="inlineStr">
         <is>
           <t>CARNE DE SOL KG PRIMEIRA</t>
         </is>
@@ -26117,60 +26131,60 @@
       </c>
     </row>
     <row r="1280">
-      <c r="A1280" s="17" t="n">
+      <c r="A1280" s="21" t="n">
         <v>105468</v>
       </c>
-      <c r="B1280" s="17" t="inlineStr">
+      <c r="B1280" s="21" t="inlineStr">
         <is>
           <t>#03 AÇOUGUE - #02 BOVINA</t>
         </is>
       </c>
-      <c r="C1280" s="17" t="inlineStr">
+      <c r="C1280" s="21" t="inlineStr">
         <is>
           <t>BOVINO - CARNE MOIDA KG</t>
         </is>
       </c>
-      <c r="D1280" s="17" t="inlineStr">
+      <c r="D1280" s="21" t="inlineStr">
         <is>
           <t>CARNE MOIDA KG</t>
         </is>
       </c>
     </row>
     <row r="1281">
-      <c r="A1281" s="17" t="n">
+      <c r="A1281" s="23" t="n">
         <v>105458</v>
       </c>
-      <c r="B1281" s="17" t="inlineStr">
+      <c r="B1281" s="23" t="inlineStr">
         <is>
           <t>#03 AÇOUGUE - #02 BOVINA</t>
         </is>
       </c>
-      <c r="C1281" s="17" t="inlineStr">
+      <c r="C1281" s="23" t="inlineStr">
         <is>
           <t>BOVINO - CHAMBARI KG</t>
         </is>
       </c>
-      <c r="D1281" s="17" t="inlineStr">
+      <c r="D1281" s="23" t="inlineStr">
         <is>
           <t>CHAMBARI KG</t>
         </is>
       </c>
     </row>
     <row r="1282">
-      <c r="A1282" s="14" t="n">
+      <c r="A1282" s="13" t="n">
         <v>105451</v>
       </c>
-      <c r="B1282" s="14" t="inlineStr">
+      <c r="B1282" s="13" t="inlineStr">
         <is>
           <t>#03 AÇOUGUE - #02 BOVINA</t>
         </is>
       </c>
-      <c r="C1282" s="14" t="inlineStr">
+      <c r="C1282" s="13" t="inlineStr">
         <is>
           <t>BOVINO - CONTRA FILE KG</t>
         </is>
       </c>
-      <c r="D1282" s="14" t="inlineStr">
+      <c r="D1282" s="13" t="inlineStr">
         <is>
           <t>CONTRA FILÉ KG</t>
         </is>
@@ -26237,20 +26251,20 @@
       </c>
     </row>
     <row r="1286">
-      <c r="A1286" s="17" t="n">
+      <c r="A1286" s="8" t="n">
         <v>105471</v>
       </c>
-      <c r="B1286" s="17" t="inlineStr">
+      <c r="B1286" s="8" t="inlineStr">
         <is>
           <t>#03 AÇOUGUE - #02 BOVINA</t>
         </is>
       </c>
-      <c r="C1286" s="17" t="inlineStr">
+      <c r="C1286" s="8" t="inlineStr">
         <is>
           <t>BOVINO - COSTELA KG</t>
         </is>
       </c>
-      <c r="D1286" s="17" t="inlineStr">
+      <c r="D1286" s="8" t="inlineStr">
         <is>
           <t>COSTELA BOVINA KG</t>
         </is>
@@ -26277,40 +26291,40 @@
       </c>
     </row>
     <row r="1288">
-      <c r="A1288" s="18" t="n">
+      <c r="A1288" s="24" t="n">
         <v>105449</v>
       </c>
-      <c r="B1288" s="18" t="inlineStr">
+      <c r="B1288" s="24" t="inlineStr">
         <is>
           <t>#03 AÇOUGUE - #02 BOVINA</t>
         </is>
       </c>
-      <c r="C1288" s="18" t="inlineStr">
+      <c r="C1288" s="24" t="inlineStr">
         <is>
           <t>BOVINO - COXAO DURO KG</t>
         </is>
       </c>
-      <c r="D1288" s="18" t="inlineStr">
+      <c r="D1288" s="24" t="inlineStr">
         <is>
           <t>COXÃO DURO KG</t>
         </is>
       </c>
     </row>
     <row r="1289">
-      <c r="A1289" s="17" t="n">
+      <c r="A1289" s="21" t="n">
         <v>105435</v>
       </c>
-      <c r="B1289" s="17" t="inlineStr">
+      <c r="B1289" s="21" t="inlineStr">
         <is>
           <t>#03 AÇOUGUE - #02 BOVINA</t>
         </is>
       </c>
-      <c r="C1289" s="17" t="inlineStr">
+      <c r="C1289" s="21" t="inlineStr">
         <is>
           <t>BOVINO - COXAO MOLE KG</t>
         </is>
       </c>
-      <c r="D1289" s="17" t="inlineStr">
+      <c r="D1289" s="21" t="inlineStr">
         <is>
           <t>COXÃO MOLE KG</t>
         </is>
@@ -26477,20 +26491,20 @@
       </c>
     </row>
     <row r="1298">
-      <c r="A1298" s="14" t="n">
+      <c r="A1298" s="13" t="n">
         <v>107260</v>
       </c>
-      <c r="B1298" s="14" t="inlineStr">
+      <c r="B1298" s="13" t="inlineStr">
         <is>
           <t>#03 AÇOUGUE - #02 BOVINA</t>
         </is>
       </c>
-      <c r="C1298" s="14" t="inlineStr">
+      <c r="C1298" s="13" t="inlineStr">
         <is>
           <t>BOVINO - MACA DO PEITO KG</t>
         </is>
       </c>
-      <c r="D1298" s="14" t="inlineStr">
+      <c r="D1298" s="13" t="inlineStr">
         <is>
           <t>MAÇÃ DO PEITO KG</t>
         </is>
@@ -26637,20 +26651,20 @@
       </c>
     </row>
     <row r="1306">
-      <c r="A1306" s="9" t="n">
+      <c r="A1306" s="21" t="n">
         <v>105452</v>
       </c>
-      <c r="B1306" s="9" t="inlineStr">
+      <c r="B1306" s="21" t="inlineStr">
         <is>
           <t>#03 AÇOUGUE - #02 BOVINA</t>
         </is>
       </c>
-      <c r="C1306" s="9" t="inlineStr">
+      <c r="C1306" s="21" t="inlineStr">
         <is>
           <t>BOVINO - PATINHO KG</t>
         </is>
       </c>
-      <c r="D1306" s="9" t="inlineStr">
+      <c r="D1306" s="21" t="inlineStr">
         <is>
           <t>PATINHO BOVINO KG</t>
         </is>
@@ -26757,40 +26771,40 @@
       </c>
     </row>
     <row r="1312">
-      <c r="A1312" s="18" t="n">
+      <c r="A1312" s="13" t="n">
         <v>106053</v>
       </c>
-      <c r="B1312" s="18" t="inlineStr">
+      <c r="B1312" s="13" t="inlineStr">
         <is>
           <t>#03 AÇOUGUE - #03 SUÍNA</t>
         </is>
       </c>
-      <c r="C1312" s="18" t="inlineStr">
+      <c r="C1312" s="13" t="inlineStr">
         <is>
           <t>SUINO - BISTECA CARRE FRESCA KG</t>
         </is>
       </c>
-      <c r="D1312" s="18" t="inlineStr">
+      <c r="D1312" s="13" t="inlineStr">
         <is>
           <t>BISTECA SUINA CARRE KG</t>
         </is>
       </c>
     </row>
     <row r="1313">
-      <c r="A1313" s="17" t="n">
+      <c r="A1313" s="18" t="n">
         <v>105062</v>
       </c>
-      <c r="B1313" s="17" t="inlineStr">
+      <c r="B1313" s="18" t="inlineStr">
         <is>
           <t>#03 AÇOUGUE - #03 SUÍNA</t>
         </is>
       </c>
-      <c r="C1313" s="17" t="inlineStr">
+      <c r="C1313" s="18" t="inlineStr">
         <is>
           <t>SUINO - BISTECA PERNIL FRESCA KG</t>
         </is>
       </c>
-      <c r="D1313" s="17" t="inlineStr">
+      <c r="D1313" s="18" t="inlineStr">
         <is>
           <t>BISTECA SUINA DO PERNIL KG</t>
         </is>
@@ -26817,20 +26831,20 @@
       </c>
     </row>
     <row r="1315">
-      <c r="A1315" s="17" t="n">
+      <c r="A1315" s="8" t="n">
         <v>105433</v>
       </c>
-      <c r="B1315" s="17" t="inlineStr">
+      <c r="B1315" s="8" t="inlineStr">
         <is>
           <t>#03 AÇOUGUE - #03 SUÍNA</t>
         </is>
       </c>
-      <c r="C1315" s="17" t="inlineStr">
+      <c r="C1315" s="8" t="inlineStr">
         <is>
           <t>SUINO - COSTELA SUINA KG</t>
         </is>
       </c>
-      <c r="D1315" s="17" t="inlineStr">
+      <c r="D1315" s="8" t="inlineStr">
         <is>
           <t>COSTELA SUINA KG</t>
         </is>
@@ -26897,20 +26911,20 @@
       </c>
     </row>
     <row r="1319">
-      <c r="A1319" s="14" t="n">
+      <c r="A1319" s="13" t="n">
         <v>106008</v>
       </c>
-      <c r="B1319" s="14" t="inlineStr">
+      <c r="B1319" s="13" t="inlineStr">
         <is>
           <t>#03 AÇOUGUE - #03 SUÍNA</t>
         </is>
       </c>
-      <c r="C1319" s="14" t="inlineStr">
+      <c r="C1319" s="13" t="inlineStr">
         <is>
           <t>INGREDIENTES P/ FEIJOADA KG</t>
         </is>
       </c>
-      <c r="D1319" s="14" t="inlineStr">
+      <c r="D1319" s="13" t="inlineStr">
         <is>
           <t>INGREDIENTES PARA FEIJOADA KG</t>
         </is>
@@ -26957,20 +26971,20 @@
       </c>
     </row>
     <row r="1322">
-      <c r="A1322" s="9" t="n">
+      <c r="A1322" s="7" t="n">
         <v>302572</v>
       </c>
-      <c r="B1322" s="9" t="inlineStr">
+      <c r="B1322" s="7" t="inlineStr">
         <is>
           <t>#03 AÇOUGUE - #03 SUÍNA</t>
         </is>
       </c>
-      <c r="C1322" s="9" t="inlineStr">
+      <c r="C1322" s="7" t="inlineStr">
         <is>
           <t>PANCETA  FRIMESA  1KG APERITIVO TEMPERAD</t>
         </is>
       </c>
-      <c r="D1322" s="9" t="inlineStr">
+      <c r="D1322" s="7" t="inlineStr">
         <is>
           <t>PANCETA FRIMESA 1KG APERITIVO TEMPERADO</t>
         </is>
@@ -26997,60 +27011,60 @@
       </c>
     </row>
     <row r="1324">
-      <c r="A1324" s="14" t="n">
+      <c r="A1324" s="13" t="n">
         <v>258810</v>
       </c>
-      <c r="B1324" s="14" t="inlineStr">
+      <c r="B1324" s="13" t="inlineStr">
         <is>
           <t>#03 AÇOUGUE - #03 SUÍNA</t>
         </is>
       </c>
-      <c r="C1324" s="14" t="inlineStr">
+      <c r="C1324" s="13" t="inlineStr">
         <is>
           <t>SUINO - PANCETA KG</t>
         </is>
       </c>
-      <c r="D1324" s="14" t="inlineStr">
+      <c r="D1324" s="13" t="inlineStr">
         <is>
           <t>PANCETA SUINA KG</t>
         </is>
       </c>
     </row>
     <row r="1325">
-      <c r="A1325" t="n">
+      <c r="A1325" s="20" t="n">
         <v>106050</v>
       </c>
-      <c r="B1325" t="inlineStr">
+      <c r="B1325" s="20" t="inlineStr">
         <is>
           <t>#03 AÇOUGUE - #03 SUÍNA</t>
         </is>
       </c>
-      <c r="C1325" t="inlineStr">
+      <c r="C1325" s="20" t="inlineStr">
         <is>
           <t>SUINO - PE SUINO FRESCO KG</t>
         </is>
       </c>
-      <c r="D1325" t="inlineStr">
+      <c r="D1325" s="20" t="inlineStr">
         <is>
           <t>PÉ SUINO KG</t>
         </is>
       </c>
     </row>
     <row r="1326">
-      <c r="A1326" s="9" t="n">
+      <c r="A1326" s="7" t="n">
         <v>106052</v>
       </c>
-      <c r="B1326" s="9" t="inlineStr">
+      <c r="B1326" s="7" t="inlineStr">
         <is>
           <t>#03 AÇOUGUE - #03 SUÍNA</t>
         </is>
       </c>
-      <c r="C1326" s="9" t="inlineStr">
+      <c r="C1326" s="7" t="inlineStr">
         <is>
           <t>SUINO - PELE SUINA FRESCA KG</t>
         </is>
       </c>
-      <c r="D1326" s="9" t="inlineStr">
+      <c r="D1326" s="7" t="inlineStr">
         <is>
           <t>PELE SUINA KG</t>
         </is>
@@ -27077,40 +27091,40 @@
       </c>
     </row>
     <row r="1328">
-      <c r="A1328" s="9" t="n">
+      <c r="A1328" s="7" t="n">
         <v>341509</v>
       </c>
-      <c r="B1328" s="9" t="inlineStr">
+      <c r="B1328" s="7" t="inlineStr">
         <is>
           <t>#03 AÇOUGUE - #03 SUÍNA</t>
         </is>
       </c>
-      <c r="C1328" s="9" t="inlineStr">
+      <c r="C1328" s="7" t="inlineStr">
         <is>
           <t>PORCO A PASSARINHO FRIMESA 1KG C/ PIMENT</t>
         </is>
       </c>
-      <c r="D1328" s="9" t="inlineStr">
+      <c r="D1328" s="7" t="inlineStr">
         <is>
           <t>PORCO A PASSARINHO FRIMESA 1KG COM PIMENTA</t>
         </is>
       </c>
     </row>
     <row r="1329">
-      <c r="A1329" s="9" t="n">
+      <c r="A1329" s="7" t="n">
         <v>209691</v>
       </c>
-      <c r="B1329" s="9" t="inlineStr">
+      <c r="B1329" s="7" t="inlineStr">
         <is>
           <t>#03 AÇOUGUE - #03 SUÍNA</t>
         </is>
       </c>
-      <c r="C1329" s="9" t="inlineStr">
+      <c r="C1329" s="7" t="inlineStr">
         <is>
           <t>PORCO A PASSARINHO TEMP. FRIMESA 1KG</t>
         </is>
       </c>
-      <c r="D1329" s="9" t="inlineStr">
+      <c r="D1329" s="7" t="inlineStr">
         <is>
           <t>PORCO A PASSARINHO FRIMESA 1KG TEMPERADO</t>
         </is>
@@ -27157,20 +27171,20 @@
       </c>
     </row>
     <row r="1332">
-      <c r="A1332" s="9" t="n">
+      <c r="A1332" s="21" t="n">
         <v>106034</v>
       </c>
-      <c r="B1332" s="9" t="inlineStr">
+      <c r="B1332" s="21" t="inlineStr">
         <is>
           <t>#03 AÇOUGUE - #03 SUÍNA</t>
         </is>
       </c>
-      <c r="C1332" s="9" t="inlineStr">
+      <c r="C1332" s="21" t="inlineStr">
         <is>
           <t>SUINO - SUAN FRESCA KG</t>
         </is>
       </c>
-      <c r="D1332" s="9" t="inlineStr">
+      <c r="D1332" s="21" t="inlineStr">
         <is>
           <t>SUAN SUINA KG</t>
         </is>
@@ -27197,40 +27211,40 @@
       </c>
     </row>
     <row r="1334">
-      <c r="A1334" s="9" t="n">
+      <c r="A1334" s="7" t="n">
         <v>341522</v>
       </c>
-      <c r="B1334" s="9" t="inlineStr">
+      <c r="B1334" s="7" t="inlineStr">
         <is>
           <t>#03 AÇOUGUE - #03 SUÍNA</t>
         </is>
       </c>
-      <c r="C1334" s="9" t="inlineStr">
+      <c r="C1334" s="7" t="inlineStr">
         <is>
           <t>ALCATRA CONGELADO SUINO SEM OSSO FOGO E</t>
         </is>
       </c>
-      <c r="D1334" s="9" t="inlineStr">
+      <c r="D1334" s="7" t="inlineStr">
         <is>
           <t>ALCATRA SUÍNA FRIMESA 800G SEM OSSO</t>
         </is>
       </c>
     </row>
     <row r="1335">
-      <c r="A1335" s="9" t="n">
+      <c r="A1335" s="7" t="n">
         <v>347787</v>
       </c>
-      <c r="B1335" s="9" t="inlineStr">
+      <c r="B1335" s="7" t="inlineStr">
         <is>
           <t>#03 AÇOUGUE - #03 SUÍNA</t>
         </is>
       </c>
-      <c r="C1335" s="9" t="inlineStr">
+      <c r="C1335" s="7" t="inlineStr">
         <is>
           <t>SUINO - FILEZINHO FRIMESA KG</t>
         </is>
       </c>
-      <c r="D1335" s="9" t="inlineStr">
+      <c r="D1335" s="7" t="inlineStr">
         <is>
           <t>FILEZINHO SUÍNO FRIMESA KG</t>
         </is>
@@ -28437,20 +28451,20 @@
       </c>
     </row>
     <row r="1396">
-      <c r="A1396" t="n">
+      <c r="A1396" s="18" t="n">
         <v>305039</v>
       </c>
-      <c r="B1396" t="inlineStr">
+      <c r="B1396" s="18" t="inlineStr">
         <is>
           <t>#03 AÇOUGUE - #06 EMBUTIDOS E FRIOS</t>
         </is>
       </c>
-      <c r="C1396" t="inlineStr">
+      <c r="C1396" s="18" t="inlineStr">
         <is>
           <t>LINGUIÇA BOVINA KG CASEIRA</t>
         </is>
       </c>
-      <c r="D1396" t="inlineStr">
+      <c r="D1396" s="18" t="inlineStr">
         <is>
           <t>LINGUIÇA CASEIRA BOVINA KG</t>
         </is>
@@ -28557,20 +28571,20 @@
       </c>
     </row>
     <row r="1402">
-      <c r="A1402" t="n">
+      <c r="A1402" s="21" t="n">
         <v>228422</v>
       </c>
-      <c r="B1402" t="inlineStr">
+      <c r="B1402" s="21" t="inlineStr">
         <is>
           <t>#03 AÇOUGUE - #06 EMBUTIDOS E FRIOS</t>
         </is>
       </c>
-      <c r="C1402" t="inlineStr">
+      <c r="C1402" s="21" t="inlineStr">
         <is>
           <t>LINGUIÇA SUPER FRANGO KG FRANGO GROSSA</t>
         </is>
       </c>
-      <c r="D1402" t="inlineStr">
+      <c r="D1402" s="21" t="inlineStr">
         <is>
           <t>LINGUIÇA GROSSA SUPER FRANGO KG</t>
         </is>
@@ -28817,20 +28831,20 @@
       </c>
     </row>
     <row r="1415">
-      <c r="A1415" s="17" t="n">
+      <c r="A1415" s="13" t="n">
         <v>301962</v>
       </c>
-      <c r="B1415" s="17" t="inlineStr">
+      <c r="B1415" s="13" t="inlineStr">
         <is>
           <t>#03 AÇOUGUE - #06 EMBUTIDOS E FRIOS</t>
         </is>
       </c>
-      <c r="C1415" s="17" t="inlineStr">
+      <c r="C1415" s="13" t="inlineStr">
         <is>
           <t>LINGUICA BONFRIGO SUINA KG</t>
         </is>
       </c>
-      <c r="D1415" s="17" t="inlineStr">
+      <c r="D1415" s="13" t="inlineStr">
         <is>
           <t>LINGUIÇA SUÍNA BONFRIGO KG</t>
         </is>
@@ -28897,20 +28911,20 @@
       </c>
     </row>
     <row r="1419">
-      <c r="A1419" s="9" t="n">
+      <c r="A1419" s="7" t="n">
         <v>146785</v>
       </c>
-      <c r="B1419" s="9" t="inlineStr">
+      <c r="B1419" s="7" t="inlineStr">
         <is>
           <t>#03 AÇOUGUE - #06 EMBUTIDOS E FRIOS</t>
         </is>
       </c>
-      <c r="C1419" s="9" t="inlineStr">
+      <c r="C1419" s="7" t="inlineStr">
         <is>
           <t>LING PERDIGAO CARNE SUINA KG</t>
         </is>
       </c>
-      <c r="D1419" s="9" t="inlineStr">
+      <c r="D1419" s="7" t="inlineStr">
         <is>
           <t>LINGUIÇA SUINA PERDIGÃO KG</t>
         </is>
@@ -28937,20 +28951,20 @@
       </c>
     </row>
     <row r="1421">
-      <c r="A1421" s="17" t="n">
+      <c r="A1421" s="18" t="n">
         <v>292399</v>
       </c>
-      <c r="B1421" s="17" t="inlineStr">
+      <c r="B1421" s="18" t="inlineStr">
         <is>
           <t>#03 AÇOUGUE - #06 EMBUTIDOS E FRIOS</t>
         </is>
       </c>
-      <c r="C1421" s="17" t="inlineStr">
+      <c r="C1421" s="18" t="inlineStr">
         <is>
           <t>LINGUICA SUPER FRANGO 400GR DEFUMADA FRA</t>
         </is>
       </c>
-      <c r="D1421" s="17" t="inlineStr">
+      <c r="D1421" s="18" t="inlineStr">
         <is>
           <t>LINGUIÇA SUPER FRANGO 400G DEFUMADA</t>
         </is>
@@ -29497,20 +29511,20 @@
       </c>
     </row>
     <row r="1449">
-      <c r="A1449" s="17" t="n">
+      <c r="A1449" s="13" t="n">
         <v>170705</v>
       </c>
-      <c r="B1449" s="17" t="inlineStr">
+      <c r="B1449" s="13" t="inlineStr">
         <is>
           <t>#03 AÇOUGUE - #06 EMBUTIDOS E FRIOS</t>
         </is>
       </c>
-      <c r="C1449" s="17" t="inlineStr">
+      <c r="C1449" s="13" t="inlineStr">
         <is>
           <t>MORTADELA MISTA  SADIA 400GR</t>
         </is>
       </c>
-      <c r="D1449" s="17" t="inlineStr">
+      <c r="D1449" s="13" t="inlineStr">
         <is>
           <t>MORTADELA MISTA SADIA 400G</t>
         </is>
@@ -29557,20 +29571,20 @@
       </c>
     </row>
     <row r="1452">
-      <c r="A1452" t="n">
+      <c r="A1452" s="21" t="n">
         <v>105765</v>
       </c>
-      <c r="B1452" t="inlineStr">
+      <c r="B1452" s="21" t="inlineStr">
         <is>
           <t>#03 AÇOUGUE - #06 EMBUTIDOS E FRIOS</t>
         </is>
       </c>
-      <c r="C1452" t="inlineStr">
+      <c r="C1452" s="21" t="inlineStr">
         <is>
           <t>MORTADELA MISTA PERDIGAO KG</t>
         </is>
       </c>
-      <c r="D1452" t="inlineStr">
+      <c r="D1452" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">MORTADELA PERDIGÃO KG MISTA </t>
         </is>
@@ -29637,20 +29651,20 @@
       </c>
     </row>
     <row r="1456">
-      <c r="A1456" s="9" t="n">
+      <c r="A1456" s="18" t="n">
         <v>108558</v>
       </c>
-      <c r="B1456" s="9" t="inlineStr">
+      <c r="B1456" s="18" t="inlineStr">
         <is>
           <t>#03 AÇOUGUE - #06 EMBUTIDOS E FRIOS</t>
         </is>
       </c>
-      <c r="C1456" s="9" t="inlineStr">
+      <c r="C1456" s="18" t="inlineStr">
         <is>
           <t>MORTADELA SADIA  1KG SUINA</t>
         </is>
       </c>
-      <c r="D1456" s="9" t="inlineStr">
+      <c r="D1456" s="18" t="inlineStr">
         <is>
           <t>MORTADELA SUÍNA SADIA 1KG</t>
         </is>
@@ -29837,20 +29851,20 @@
       </c>
     </row>
     <row r="1466">
-      <c r="A1466" t="n">
+      <c r="A1466" s="18" t="n">
         <v>184045</v>
       </c>
-      <c r="B1466" t="inlineStr">
+      <c r="B1466" s="18" t="inlineStr">
         <is>
           <t>#03 AÇOUGUE - #06 EMBUTIDOS E FRIOS</t>
         </is>
       </c>
-      <c r="C1466" t="inlineStr">
+      <c r="C1466" s="18" t="inlineStr">
         <is>
           <t>SALAME PERDIGAO FATIADO 100GR SALF10</t>
         </is>
       </c>
-      <c r="D1466" t="inlineStr">
+      <c r="D1466" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">SALAME PERDIGÃO 100GR FATIADO </t>
         </is>
@@ -29877,20 +29891,20 @@
       </c>
     </row>
     <row r="1468">
-      <c r="A1468" s="9" t="n">
+      <c r="A1468" s="7" t="n">
         <v>117826</v>
       </c>
-      <c r="B1468" s="9" t="inlineStr">
+      <c r="B1468" s="7" t="inlineStr">
         <is>
           <t>#03 AÇOUGUE - #06 EMBUTIDOS E FRIOS</t>
         </is>
       </c>
-      <c r="C1468" s="9" t="inlineStr">
+      <c r="C1468" s="7" t="inlineStr">
         <is>
           <t>SALAMINHO SADIA KG 220 A 330G SLS</t>
         </is>
       </c>
-      <c r="D1468" s="9" t="inlineStr">
+      <c r="D1468" s="7" t="inlineStr">
         <is>
           <t>SALAMINHO SADIA KG 220G A 330G</t>
         </is>
@@ -29957,20 +29971,20 @@
       </c>
     </row>
     <row r="1472">
-      <c r="A1472" t="n">
+      <c r="A1472" s="21" t="n">
         <v>227341</v>
       </c>
-      <c r="B1472" t="inlineStr">
+      <c r="B1472" s="21" t="inlineStr">
         <is>
           <t>#03 AÇOUGUE - #06 EMBUTIDOS E FRIOS</t>
         </is>
       </c>
-      <c r="C1472" t="inlineStr">
+      <c r="C1472" s="21" t="inlineStr">
         <is>
           <t>SALSICHA HOT DOG AMERICANO KG</t>
         </is>
       </c>
-      <c r="D1472" t="inlineStr">
+      <c r="D1472" s="21" t="inlineStr">
         <is>
           <t>SALSICHA AMERICANO KG PARA HOT DOG</t>
         </is>
@@ -30137,20 +30151,20 @@
       </c>
     </row>
     <row r="1481">
-      <c r="A1481" s="17" t="n">
+      <c r="A1481" s="13" t="n">
         <v>158192</v>
       </c>
-      <c r="B1481" s="17" t="inlineStr">
+      <c r="B1481" s="13" t="inlineStr">
         <is>
           <t>#03 AÇOUGUE - #06 EMBUTIDOS E FRIOS</t>
         </is>
       </c>
-      <c r="C1481" s="17" t="inlineStr">
+      <c r="C1481" s="13" t="inlineStr">
         <is>
           <t>MORTADELA FRICO 400GR MINI MISTA</t>
         </is>
       </c>
-      <c r="D1481" s="17" t="inlineStr">
+      <c r="D1481" s="13" t="inlineStr">
         <is>
           <t>MORTADELA MISTA FRICO 400G MINI</t>
         </is>
@@ -30197,20 +30211,20 @@
       </c>
     </row>
     <row r="1484">
-      <c r="A1484" s="17" t="n">
+      <c r="A1484" s="13" t="n">
         <v>345268</v>
       </c>
-      <c r="B1484" s="17" t="inlineStr">
+      <c r="B1484" s="13" t="inlineStr">
         <is>
           <t>#03 AÇOUGUE - #07 EMPANADOS E PRATOS PRONTOS</t>
         </is>
       </c>
-      <c r="C1484" s="17" t="inlineStr">
+      <c r="C1484" s="13" t="inlineStr">
         <is>
           <t>MINI HAMBURGUER SEARA 300G BOV/SUI CHURR</t>
         </is>
       </c>
-      <c r="D1484" s="17" t="inlineStr">
+      <c r="D1484" s="13" t="inlineStr">
         <is>
           <t>MINI HAMBURGUER SEARA 300G CHURRASCO BOVINO E SUINO</t>
         </is>
@@ -30297,40 +30311,40 @@
       </c>
     </row>
     <row r="1489">
-      <c r="A1489" t="n">
+      <c r="A1489" s="18" t="n">
         <v>138538</v>
       </c>
-      <c r="B1489" t="inlineStr">
+      <c r="B1489" s="18" t="inlineStr">
         <is>
           <t>#03 AÇOUGUE - #07 EMPANADOS E PRATOS PRONTOS</t>
         </is>
       </c>
-      <c r="C1489" t="inlineStr">
+      <c r="C1489" s="18" t="inlineStr">
         <is>
           <t>TEKITOS SEARA FRANGO 300G</t>
         </is>
       </c>
-      <c r="D1489" t="inlineStr">
+      <c r="D1489" s="18" t="inlineStr">
         <is>
           <t>TEKITOS SEARA 300G FRANGO</t>
         </is>
       </c>
     </row>
     <row r="1490">
-      <c r="A1490" t="n">
+      <c r="A1490" s="18" t="n">
         <v>127328</v>
       </c>
-      <c r="B1490" t="inlineStr">
+      <c r="B1490" s="18" t="inlineStr">
         <is>
           <t>#03 AÇOUGUE - #07 EMPANADOS E PRATOS PRONTOS</t>
         </is>
       </c>
-      <c r="C1490" t="inlineStr">
+      <c r="C1490" s="18" t="inlineStr">
         <is>
           <t>TEKITOS SEARA QUEIJO OREGANO 300GR</t>
         </is>
       </c>
-      <c r="D1490" t="inlineStr">
+      <c r="D1490" s="18" t="inlineStr">
         <is>
           <t>TEKITOS SEARA 300G QUEIJO COM OREGANO</t>
         </is>
@@ -30357,140 +30371,140 @@
       </c>
     </row>
     <row r="1492">
-      <c r="A1492" s="17" t="n">
+      <c r="A1492" s="13" t="n">
         <v>328607</v>
       </c>
-      <c r="B1492" s="17" t="inlineStr">
+      <c r="B1492" s="13" t="inlineStr">
         <is>
           <t>#03 AÇOUGUE - #07 EMPANADOS E PRATOS PRONTOS</t>
         </is>
       </c>
-      <c r="C1492" s="17" t="inlineStr">
+      <c r="C1492" s="13" t="inlineStr">
         <is>
           <t>BOLINHO DE CARNE SUINA SEARA 270GR COM</t>
         </is>
       </c>
-      <c r="D1492" s="17" t="inlineStr">
+      <c r="D1492" s="13" t="inlineStr">
         <is>
           <t>BOLINHO DE CARNE SUINA SEARA 270G MOLHO BARBECUE</t>
         </is>
       </c>
     </row>
     <row r="1493">
-      <c r="A1493" s="17" t="n">
+      <c r="A1493" s="13" t="n">
         <v>116233</v>
       </c>
-      <c r="B1493" s="17" t="inlineStr">
+      <c r="B1493" s="13" t="inlineStr">
         <is>
           <t>#03 AÇOUGUE - #07 EMPANADOS E PRATOS PRONTOS</t>
         </is>
       </c>
-      <c r="C1493" s="17" t="inlineStr">
+      <c r="C1493" s="13" t="inlineStr">
         <is>
           <t>HOT POCKET SADIA 145GR X FRANGO</t>
         </is>
       </c>
-      <c r="D1493" s="17" t="inlineStr">
+      <c r="D1493" s="13" t="inlineStr">
         <is>
           <t>HOT POCKET SADIA 145G X-FRANGO</t>
         </is>
       </c>
     </row>
     <row r="1494">
-      <c r="A1494" s="17" t="n">
+      <c r="A1494" s="8" t="n">
         <v>104931</v>
       </c>
-      <c r="B1494" s="17" t="inlineStr">
+      <c r="B1494" s="8" t="inlineStr">
         <is>
           <t>#04 HORTIFRUTI - #01 FRUTAS</t>
         </is>
       </c>
-      <c r="C1494" s="17" t="inlineStr">
+      <c r="C1494" s="8" t="inlineStr">
         <is>
           <t>LARANJA KG</t>
         </is>
       </c>
-      <c r="D1494" s="17" t="inlineStr">
+      <c r="D1494" s="8" t="inlineStr">
         <is>
           <t>LARANJA KG</t>
         </is>
       </c>
     </row>
     <row r="1495">
-      <c r="A1495" s="17" t="n">
+      <c r="A1495" s="23" t="n">
         <v>105010</v>
       </c>
-      <c r="B1495" s="17" t="inlineStr">
+      <c r="B1495" s="23" t="inlineStr">
         <is>
           <t>#04 HORTIFRUTI - #01 LEGUMES E TUBÉRCULOS</t>
         </is>
       </c>
-      <c r="C1495" s="17" t="inlineStr">
+      <c r="C1495" s="23" t="inlineStr">
         <is>
           <t>BATATA MONALISA KG</t>
         </is>
       </c>
-      <c r="D1495" s="17" t="inlineStr">
+      <c r="D1495" s="23" t="inlineStr">
         <is>
           <t>BATATA MONALISA KG</t>
         </is>
       </c>
     </row>
     <row r="1496">
-      <c r="A1496" s="17" t="n">
+      <c r="A1496" s="8" t="n">
         <v>104961</v>
       </c>
-      <c r="B1496" s="17" t="inlineStr">
+      <c r="B1496" s="8" t="inlineStr">
         <is>
           <t>#04 HORTIFRUTI - #01 LEGUMES E TUBÉRCULOS</t>
         </is>
       </c>
-      <c r="C1496" s="17" t="inlineStr">
+      <c r="C1496" s="8" t="inlineStr">
         <is>
           <t>TOMATE CARMEM KG</t>
         </is>
       </c>
-      <c r="D1496" s="17" t="inlineStr">
+      <c r="D1496" s="8" t="inlineStr">
         <is>
           <t>TOMATE CARMEM KG</t>
         </is>
       </c>
     </row>
     <row r="1497">
-      <c r="A1497" s="17" t="n">
+      <c r="A1497" s="8" t="n">
         <v>104919</v>
       </c>
-      <c r="B1497" s="17" t="inlineStr">
+      <c r="B1497" s="8" t="inlineStr">
         <is>
           <t>#04 HORTIFRUTI - #01 TEMPEROS FRESCOS</t>
         </is>
       </c>
-      <c r="C1497" s="17" t="inlineStr">
+      <c r="C1497" s="8" t="inlineStr">
         <is>
           <t>CEBOLA NACIONAL KG</t>
         </is>
       </c>
-      <c r="D1497" s="17" t="inlineStr">
+      <c r="D1497" s="8" t="inlineStr">
         <is>
           <t>CEBOLA NACIONAL KG</t>
         </is>
       </c>
     </row>
     <row r="1498">
-      <c r="A1498" s="17" t="n">
+      <c r="A1498" s="8" t="n">
         <v>104864</v>
       </c>
-      <c r="B1498" s="17" t="inlineStr">
+      <c r="B1498" s="8" t="inlineStr">
         <is>
           <t>#04 HORTIFRUTI - FRUTAS</t>
         </is>
       </c>
-      <c r="C1498" s="17" t="inlineStr">
+      <c r="C1498" s="8" t="inlineStr">
         <is>
           <t>ABACATE KG</t>
         </is>
       </c>
-      <c r="D1498" s="17" t="inlineStr">
+      <c r="D1498" s="8" t="inlineStr">
         <is>
           <t>ABACATE KG</t>
         </is>
@@ -30677,20 +30691,20 @@
       </c>
     </row>
     <row r="1508">
-      <c r="A1508" s="17" t="n">
+      <c r="A1508" s="23" t="n">
         <v>104855</v>
       </c>
-      <c r="B1508" s="17" t="inlineStr">
+      <c r="B1508" s="23" t="inlineStr">
         <is>
           <t>#04 HORTIFRUTI - FRUTAS</t>
         </is>
       </c>
-      <c r="C1508" s="17" t="inlineStr">
+      <c r="C1508" s="23" t="inlineStr">
         <is>
           <t>LIMAO TAITI KG</t>
         </is>
       </c>
-      <c r="D1508" s="17" t="inlineStr">
+      <c r="D1508" s="23" t="inlineStr">
         <is>
           <t>LIMÃO TAITI KG</t>
         </is>
@@ -30717,60 +30731,60 @@
       </c>
     </row>
     <row r="1510">
-      <c r="A1510" s="17" t="n">
+      <c r="A1510" s="23" t="n">
         <v>104881</v>
       </c>
-      <c r="B1510" s="17" t="inlineStr">
+      <c r="B1510" s="23" t="inlineStr">
         <is>
           <t>#04 HORTIFRUTI - FRUTAS</t>
         </is>
       </c>
-      <c r="C1510" s="17" t="inlineStr">
+      <c r="C1510" s="23" t="inlineStr">
         <is>
           <t>MAMAO FORMOSA KG</t>
         </is>
       </c>
-      <c r="D1510" s="17" t="inlineStr">
+      <c r="D1510" s="23" t="inlineStr">
         <is>
           <t>MAMÃO FORMOSA KG</t>
         </is>
       </c>
     </row>
     <row r="1511">
-      <c r="A1511" s="17" t="n">
+      <c r="A1511" s="8" t="n">
         <v>104928</v>
       </c>
-      <c r="B1511" s="17" t="inlineStr">
+      <c r="B1511" s="8" t="inlineStr">
         <is>
           <t>#04 HORTIFRUTI - FRUTAS</t>
         </is>
       </c>
-      <c r="C1511" s="17" t="inlineStr">
+      <c r="C1511" s="8" t="inlineStr">
         <is>
           <t>MANGA PALMER KG</t>
         </is>
       </c>
-      <c r="D1511" s="17" t="inlineStr">
+      <c r="D1511" s="8" t="inlineStr">
         <is>
           <t>MANGA KG PALMER</t>
         </is>
       </c>
     </row>
     <row r="1512">
-      <c r="A1512" s="17" t="n">
+      <c r="A1512" s="23" t="n">
         <v>104883</v>
       </c>
-      <c r="B1512" s="17" t="inlineStr">
+      <c r="B1512" s="23" t="inlineStr">
         <is>
           <t>#04 HORTIFRUTI - FRUTAS</t>
         </is>
       </c>
-      <c r="C1512" s="17" t="inlineStr">
+      <c r="C1512" s="23" t="inlineStr">
         <is>
           <t>MANGA TOMY KG</t>
         </is>
       </c>
-      <c r="D1512" s="17" t="inlineStr">
+      <c r="D1512" s="23" t="inlineStr">
         <is>
           <t>MANGA KG TOMY</t>
         </is>
@@ -30817,20 +30831,20 @@
       </c>
     </row>
     <row r="1515">
-      <c r="A1515" s="17" t="n">
+      <c r="A1515" s="8" t="n">
         <v>104947</v>
       </c>
-      <c r="B1515" s="17" t="inlineStr">
+      <c r="B1515" s="8" t="inlineStr">
         <is>
           <t>#04 HORTIFRUTI - FRUTAS</t>
         </is>
       </c>
-      <c r="C1515" s="17" t="inlineStr">
+      <c r="C1515" s="8" t="inlineStr">
         <is>
           <t>MELANCIA INTEIRA KG</t>
         </is>
       </c>
-      <c r="D1515" s="17" t="inlineStr">
+      <c r="D1515" s="8" t="inlineStr">
         <is>
           <t>MELANCIA INTEIRA KG</t>
         </is>
@@ -31277,20 +31291,20 @@
       </c>
     </row>
     <row r="1538">
-      <c r="A1538" s="17" t="n">
+      <c r="A1538" s="8" t="n">
         <v>104903</v>
       </c>
-      <c r="B1538" s="17" t="inlineStr">
+      <c r="B1538" s="8" t="inlineStr">
         <is>
           <t>#04 HORTIFRUTI - LEGUMES E TUBÉRCULOS</t>
         </is>
       </c>
-      <c r="C1538" s="17" t="inlineStr">
+      <c r="C1538" s="8" t="inlineStr">
         <is>
           <t>BATATA DOCE ROSA KG</t>
         </is>
       </c>
-      <c r="D1538" s="17" t="inlineStr">
+      <c r="D1538" s="8" t="inlineStr">
         <is>
           <t>BATATA DOCE KG ROSA</t>
         </is>
@@ -31337,40 +31351,40 @@
       </c>
     </row>
     <row r="1541">
-      <c r="A1541" s="17" t="n">
+      <c r="A1541" s="8" t="n">
         <v>104862</v>
       </c>
-      <c r="B1541" s="17" t="inlineStr">
+      <c r="B1541" s="8" t="inlineStr">
         <is>
           <t>#04 HORTIFRUTI - LEGUMES E TUBÉRCULOS</t>
         </is>
       </c>
-      <c r="C1541" s="17" t="inlineStr">
+      <c r="C1541" s="8" t="inlineStr">
         <is>
           <t>CENOURA KG</t>
         </is>
       </c>
-      <c r="D1541" s="17" t="inlineStr">
+      <c r="D1541" s="8" t="inlineStr">
         <is>
           <t>CENOURA KG</t>
         </is>
       </c>
     </row>
     <row r="1542">
-      <c r="A1542" s="17" t="n">
+      <c r="A1542" s="8" t="n">
         <v>111131</v>
       </c>
-      <c r="B1542" s="17" t="inlineStr">
+      <c r="B1542" s="8" t="inlineStr">
         <is>
           <t>#04 HORTIFRUTI - LEGUMES E TUBÉRCULOS</t>
         </is>
       </c>
-      <c r="C1542" s="17" t="inlineStr">
+      <c r="C1542" s="8" t="inlineStr">
         <is>
           <t>CHUCHU VERDE KG</t>
         </is>
       </c>
-      <c r="D1542" s="17" t="inlineStr">
+      <c r="D1542" s="8" t="inlineStr">
         <is>
           <t>CHUCHU VERDE KG</t>
         </is>
@@ -31517,20 +31531,20 @@
       </c>
     </row>
     <row r="1550">
-      <c r="A1550" s="17" t="n">
+      <c r="A1550" s="8" t="n">
         <v>104993</v>
       </c>
-      <c r="B1550" s="17" t="inlineStr">
+      <c r="B1550" s="8" t="inlineStr">
         <is>
           <t>#04 HORTIFRUTI - VERDURAS E FOLHAGENS</t>
         </is>
       </c>
-      <c r="C1550" s="17" t="inlineStr">
+      <c r="C1550" s="8" t="inlineStr">
         <is>
           <t>BROCOLIS NINJA KG</t>
         </is>
       </c>
-      <c r="D1550" s="17" t="inlineStr">
+      <c r="D1550" s="8" t="inlineStr">
         <is>
           <t>BROCOLIS NINJA KG</t>
         </is>
@@ -32337,20 +32351,20 @@
       </c>
     </row>
     <row r="1591">
-      <c r="A1591" s="5" t="n">
+      <c r="A1591" s="21" t="n">
         <v>104406</v>
       </c>
-      <c r="B1591" s="5" t="inlineStr">
+      <c r="B1591" s="21" t="inlineStr">
         <is>
           <t>#05 BEBIDA - #00 BEBIDAS GASEIFICADAS</t>
         </is>
       </c>
-      <c r="C1591" s="5" t="inlineStr">
+      <c r="C1591" s="21" t="inlineStr">
         <is>
           <t>REFRIGERANTE COCA COLA 2L</t>
         </is>
       </c>
-      <c r="D1591" s="5" t="inlineStr">
+      <c r="D1591" s="21" t="inlineStr">
         <is>
           <t>REFRIGERANTE COCA COLA 2L</t>
         </is>
@@ -32457,40 +32471,40 @@
       </c>
     </row>
     <row r="1597">
-      <c r="A1597" t="n">
+      <c r="A1597" s="21" t="n">
         <v>104404</v>
       </c>
-      <c r="B1597" t="inlineStr">
+      <c r="B1597" s="21" t="inlineStr">
         <is>
           <t>#05 BEBIDA - #00 BEBIDAS GASEIFICADAS</t>
         </is>
       </c>
-      <c r="C1597" t="inlineStr">
+      <c r="C1597" s="21" t="inlineStr">
         <is>
           <t>REFRIG FANTA LARANJA 2L</t>
         </is>
       </c>
-      <c r="D1597" t="inlineStr">
+      <c r="D1597" s="21" t="inlineStr">
         <is>
           <t>REFRIGERANTE FANTA 2L LARANJA</t>
         </is>
       </c>
     </row>
     <row r="1598">
-      <c r="A1598" s="19" t="n">
+      <c r="A1598" s="13" t="n">
         <v>104403</v>
       </c>
-      <c r="B1598" s="19" t="inlineStr">
+      <c r="B1598" s="13" t="inlineStr">
         <is>
           <t>#05 BEBIDA - #00 BEBIDAS GASEIFICADAS</t>
         </is>
       </c>
-      <c r="C1598" s="19" t="inlineStr">
+      <c r="C1598" s="13" t="inlineStr">
         <is>
           <t>REFRIG FANTA UVA 2L</t>
         </is>
       </c>
-      <c r="D1598" s="19" t="inlineStr">
+      <c r="D1598" s="13" t="inlineStr">
         <is>
           <t>REFRIGERANTE FANTA 2L UVA</t>
         </is>
@@ -32517,40 +32531,40 @@
       </c>
     </row>
     <row r="1600">
-      <c r="A1600" t="n">
+      <c r="A1600" s="21" t="n">
         <v>104410</v>
       </c>
-      <c r="B1600" t="inlineStr">
+      <c r="B1600" s="21" t="inlineStr">
         <is>
           <t>#05 BEBIDA - #00 BEBIDAS GASEIFICADAS</t>
         </is>
       </c>
-      <c r="C1600" t="inlineStr">
+      <c r="C1600" s="21" t="inlineStr">
         <is>
           <t>REFRIG GUARANA ANTARCTICA 2L PET ORIG</t>
         </is>
       </c>
-      <c r="D1600" t="inlineStr">
+      <c r="D1600" s="21" t="inlineStr">
         <is>
           <t>REFRIGERANTE GUARANA ANTARCTICA 2L</t>
         </is>
       </c>
     </row>
     <row r="1601">
-      <c r="A1601" s="9" t="n">
+      <c r="A1601" s="7" t="n">
         <v>275857</v>
       </c>
-      <c r="B1601" s="9" t="inlineStr">
+      <c r="B1601" s="7" t="inlineStr">
         <is>
           <t>#05 BEBIDA - #00 BEBIDAS GASEIFICADAS</t>
         </is>
       </c>
-      <c r="C1601" s="9" t="inlineStr">
+      <c r="C1601" s="7" t="inlineStr">
         <is>
           <t>REFRIGERANTE GUARANA ANTARCTICA ZERO PET 200ML</t>
         </is>
       </c>
-      <c r="D1601" s="9" t="inlineStr">
+      <c r="D1601" s="7" t="inlineStr">
         <is>
           <t>REFRIGERANTE GUARANA ANTARCTICA ZERO PET 200ML</t>
         </is>
@@ -33617,30 +33631,30 @@
       </c>
     </row>
     <row r="1655">
-      <c r="A1655" s="14" t="n">
+      <c r="A1655" s="13" t="n">
         <v>156763</v>
       </c>
-      <c r="B1655" s="14" t="inlineStr">
+      <c r="B1655" s="13" t="inlineStr">
         <is>
           <t>#05 BEBIDA - #00 ENERGÉTICOS</t>
         </is>
       </c>
-      <c r="C1655" s="14" t="inlineStr">
+      <c r="C1655" s="13" t="inlineStr">
         <is>
           <t>ENERGETICO EXTRA POWER 1LT 250 ML GRATIS</t>
         </is>
       </c>
-      <c r="D1655" s="14" t="inlineStr">
+      <c r="D1655" s="13" t="inlineStr">
         <is>
           <t>ENERGETICO EXTRA POWER 1L PROMOCIONAL</t>
         </is>
       </c>
     </row>
     <row r="1656">
-      <c r="A1656" s="19" t="n">
+      <c r="A1656" s="13" t="n">
         <v>102287</v>
       </c>
-      <c r="B1656" s="19" t="inlineStr">
+      <c r="B1656" s="13" t="inlineStr">
         <is>
           <t>#05 BEBIDA - #00 ENERGÉTICOS</t>
         </is>
@@ -33650,7 +33664,7 @@
           <t>ENERGETICO EXTRA POWER 270ML UNID</t>
         </is>
       </c>
-      <c r="D1656" s="19" t="inlineStr">
+      <c r="D1656" s="13" t="inlineStr">
         <is>
           <t>ENERGETICO EXTRA POWER 270ML</t>
         </is>
@@ -33697,20 +33711,20 @@
       </c>
     </row>
     <row r="1659">
-      <c r="A1659" s="9" t="n">
+      <c r="A1659" s="7" t="n">
         <v>286959</v>
       </c>
-      <c r="B1659" s="9" t="inlineStr">
+      <c r="B1659" s="7" t="inlineStr">
         <is>
           <t>#05 BEBIDA - #00 ENERGÉTICOS</t>
         </is>
       </c>
-      <c r="C1659" s="9" t="inlineStr">
+      <c r="C1659" s="7" t="inlineStr">
         <is>
           <t>ENERGETICO EXTRA POWER 2L TROPICAL</t>
         </is>
       </c>
-      <c r="D1659" s="9" t="inlineStr">
+      <c r="D1659" s="7" t="inlineStr">
         <is>
           <t>ENERGETICO EXTRA POWER 2L TROPICAL</t>
         </is>
@@ -34017,60 +34031,60 @@
       </c>
     </row>
     <row r="1675">
-      <c r="A1675" s="9" t="n">
+      <c r="A1675" s="7" t="n">
         <v>198516</v>
       </c>
-      <c r="B1675" s="9" t="inlineStr">
+      <c r="B1675" s="7" t="inlineStr">
         <is>
           <t>#05 BEBIDA - #01 SUCOS PRONTOS</t>
         </is>
       </c>
-      <c r="C1675" s="9" t="inlineStr">
+      <c r="C1675" s="7" t="inlineStr">
         <is>
           <t>SUCO ADORALLE 200ML  LARANJA</t>
         </is>
       </c>
-      <c r="D1675" s="9" t="inlineStr">
+      <c r="D1675" s="7" t="inlineStr">
         <is>
           <t>SUCO ADORALLE 200ML LARANJA</t>
         </is>
       </c>
     </row>
     <row r="1676">
-      <c r="A1676" s="19" t="n">
+      <c r="A1676" s="13" t="n">
         <v>286325</v>
       </c>
-      <c r="B1676" s="19" t="inlineStr">
+      <c r="B1676" s="13" t="inlineStr">
         <is>
           <t>#05 BEBIDA - #01 SUCOS PRONTOS</t>
         </is>
       </c>
-      <c r="C1676" s="19" t="inlineStr">
+      <c r="C1676" s="13" t="inlineStr">
         <is>
           <t>SUCO DE UVA AURORA 1,5LT TINTO TP</t>
         </is>
       </c>
-      <c r="D1676" s="19" t="inlineStr">
+      <c r="D1676" s="13" t="inlineStr">
         <is>
           <t>SUCO AURORA TP 1,5L UVA TINTO</t>
         </is>
       </c>
     </row>
     <row r="1677">
-      <c r="A1677" t="n">
+      <c r="A1677" s="21" t="n">
         <v>102237</v>
       </c>
-      <c r="B1677" t="inlineStr">
+      <c r="B1677" s="21" t="inlineStr">
         <is>
           <t>#05 BEBIDA - #01 SUCOS PRONTOS</t>
         </is>
       </c>
-      <c r="C1677" t="inlineStr">
+      <c r="C1677" s="21" t="inlineStr">
         <is>
           <t>SUCO UVA INTEGRAL TINTO AURORA 1,5L VD</t>
         </is>
       </c>
-      <c r="D1677" t="inlineStr">
+      <c r="D1677" s="21" t="inlineStr">
         <is>
           <t>SUCO AURORA VIDRO 1,5L UVA INTEGRAL TINTO</t>
         </is>
@@ -34617,20 +34631,20 @@
       </c>
     </row>
     <row r="1705">
-      <c r="A1705" t="n">
+      <c r="A1705" s="21" t="n">
         <v>102149</v>
       </c>
-      <c r="B1705" t="inlineStr">
+      <c r="B1705" s="21" t="inlineStr">
         <is>
           <t>#05 BEBIDA - #01 SUCOS PRONTOS</t>
         </is>
       </c>
-      <c r="C1705" t="inlineStr">
+      <c r="C1705" s="21" t="inlineStr">
         <is>
           <t>SUCO PRONTO DAFRUTA 1L CAJU</t>
         </is>
       </c>
-      <c r="D1705" t="inlineStr">
+      <c r="D1705" s="21" t="inlineStr">
         <is>
           <t>SUCO PRONTO DAFRUTA 1L CAJU</t>
         </is>
@@ -34697,40 +34711,40 @@
       </c>
     </row>
     <row r="1709">
-      <c r="A1709" s="19" t="n">
+      <c r="A1709" s="13" t="n">
         <v>264452</v>
       </c>
-      <c r="B1709" s="19" t="inlineStr">
+      <c r="B1709" s="13" t="inlineStr">
         <is>
           <t>#05 BEBIDA - #01 SUCOS PRONTOS</t>
         </is>
       </c>
-      <c r="C1709" s="19" t="inlineStr">
+      <c r="C1709" s="13" t="inlineStr">
         <is>
           <t>SUCO PRONTO DAFRUTA 1L NECTAR UVA</t>
         </is>
       </c>
-      <c r="D1709" s="19" t="inlineStr">
+      <c r="D1709" s="13" t="inlineStr">
         <is>
           <t>SUCO PRONTO DAFRUTA 1L NECTAR UVA</t>
         </is>
       </c>
     </row>
     <row r="1710">
-      <c r="A1710" s="17" t="n">
+      <c r="A1710" s="8" t="n">
         <v>288980</v>
       </c>
-      <c r="B1710" s="17" t="inlineStr">
+      <c r="B1710" s="8" t="inlineStr">
         <is>
           <t>#05 BEBIDA - #01 SUCOS PRONTOS</t>
         </is>
       </c>
-      <c r="C1710" s="17" t="inlineStr">
+      <c r="C1710" s="8" t="inlineStr">
         <is>
           <t>AGUA DE COCO COPRA 1L C/POLPA TP</t>
         </is>
       </c>
-      <c r="D1710" s="17" t="inlineStr">
+      <c r="D1710" s="8" t="inlineStr">
         <is>
           <t>ÁGUA DE COCO COPRA TP 1L COM POLPA</t>
         </is>
@@ -35277,20 +35291,20 @@
       </c>
     </row>
     <row r="1738">
-      <c r="A1738" t="n">
+      <c r="A1738" s="21" t="n">
         <v>247799</v>
       </c>
-      <c r="B1738" t="inlineStr">
+      <c r="B1738" s="21" t="inlineStr">
         <is>
           <t>#05 BEBIDA - CERVEJAS</t>
         </is>
       </c>
-      <c r="C1738" t="inlineStr">
+      <c r="C1738" s="21" t="inlineStr">
         <is>
           <t>CERV BUDWEISER 330ML LAGER LN C/ 6 UNID</t>
         </is>
       </c>
-      <c r="D1738" t="inlineStr">
+      <c r="D1738" s="21" t="inlineStr">
         <is>
           <t>CERVEJA BUDWEISER LAGER LONG NECK 330ML</t>
         </is>
@@ -35397,20 +35411,20 @@
       </c>
     </row>
     <row r="1744">
-      <c r="A1744" s="14" t="n">
+      <c r="A1744" s="13" t="n">
         <v>220499</v>
       </c>
-      <c r="B1744" s="14" t="inlineStr">
+      <c r="B1744" s="13" t="inlineStr">
         <is>
           <t>#05 BEBIDA - CERVEJAS</t>
         </is>
       </c>
-      <c r="C1744" s="14" t="inlineStr">
+      <c r="C1744" s="13" t="inlineStr">
         <is>
           <t>CORONA EXTRA N LONG NECK 330ML</t>
         </is>
       </c>
-      <c r="D1744" s="14" t="inlineStr">
+      <c r="D1744" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">CERVEJA CORONA EXTRA LONG NECK 330ML </t>
         </is>
@@ -35777,20 +35791,20 @@
       </c>
     </row>
     <row r="1763">
-      <c r="A1763" s="9" t="n">
+      <c r="A1763" s="7" t="n">
         <v>117413</v>
       </c>
-      <c r="B1763" s="9" t="inlineStr">
+      <c r="B1763" s="7" t="inlineStr">
         <is>
           <t>#05 BEBIDA - CERVEJAS</t>
         </is>
       </c>
-      <c r="C1763" s="9" t="inlineStr">
+      <c r="C1763" s="7" t="inlineStr">
         <is>
           <t>CERV ITAIPAVA LONG NECK 250ML C/ 6UNID</t>
         </is>
       </c>
-      <c r="D1763" s="9" t="inlineStr">
+      <c r="D1763" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">CERVEJA ITAIPAVA LONG NECK 250ML </t>
         </is>
@@ -35997,40 +36011,40 @@
       </c>
     </row>
     <row r="1774">
-      <c r="A1774" s="14" t="n">
+      <c r="A1774" s="13" t="n">
         <v>259589</v>
       </c>
-      <c r="B1774" s="14" t="inlineStr">
+      <c r="B1774" s="13" t="inlineStr">
         <is>
           <t>#05 BEBIDA - CERVEJAS</t>
         </is>
       </c>
-      <c r="C1774" s="14" t="inlineStr">
+      <c r="C1774" s="13" t="inlineStr">
         <is>
           <t>STELLA ARTOIS ONE WAY 600ML</t>
         </is>
       </c>
-      <c r="D1774" s="14" t="inlineStr">
+      <c r="D1774" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">CERVEJA STELLA ARTOIS ONE WAY 600ML </t>
         </is>
       </c>
     </row>
     <row r="1775">
-      <c r="A1775" s="14" t="n">
+      <c r="A1775" s="13" t="n">
         <v>288739</v>
       </c>
-      <c r="B1775" s="14" t="inlineStr">
+      <c r="B1775" s="13" t="inlineStr">
         <is>
           <t>#05 BEBIDA - CERVEJAS</t>
         </is>
       </c>
-      <c r="C1775" s="14" t="inlineStr">
+      <c r="C1775" s="13" t="inlineStr">
         <is>
           <t>CERV STELLA ARTOIS 330ML PURE GOLD UNID</t>
         </is>
       </c>
-      <c r="D1775" s="14" t="inlineStr">
+      <c r="D1775" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">CERVEJA STELLA ARTOIS PURE GOLD LONG NECK 330ML </t>
         </is>
@@ -36177,10 +36191,10 @@
       </c>
     </row>
     <row r="1783">
-      <c r="A1783" s="14" t="n">
+      <c r="A1783" s="13" t="n">
         <v>258893</v>
       </c>
-      <c r="B1783" s="14" t="inlineStr">
+      <c r="B1783" s="13" t="inlineStr">
         <is>
           <t>#05 BEBIDA - CERVEJAS CX</t>
         </is>
@@ -36190,7 +36204,7 @@
           <t>CERV ANTARCTICA ORIGINAL LT 269ML C/8</t>
         </is>
       </c>
-      <c r="D1783" s="14" t="inlineStr">
+      <c r="D1783" s="13" t="inlineStr">
         <is>
           <t>CERVEJA ANTARCTICA ORIGINAL 15 X 269ML</t>
         </is>
@@ -36257,20 +36271,20 @@
       </c>
     </row>
     <row r="1787">
-      <c r="A1787" t="n">
+      <c r="A1787" s="21" t="n">
         <v>168712</v>
       </c>
-      <c r="B1787" t="inlineStr">
+      <c r="B1787" s="21" t="inlineStr">
         <is>
           <t>#05 BEBIDA - CERVEJAS CX</t>
         </is>
       </c>
-      <c r="C1787" t="inlineStr">
+      <c r="C1787" s="21" t="inlineStr">
         <is>
           <t>CERV ANTARCTICA 269ML C/ 15UND</t>
         </is>
       </c>
-      <c r="D1787" t="inlineStr">
+      <c r="D1787" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">CERVEJA ANTARCTICA PILSEN 15 X 269ML </t>
         </is>
@@ -36317,10 +36331,10 @@
       </c>
     </row>
     <row r="1790">
-      <c r="A1790" s="14" t="n">
+      <c r="A1790" s="13" t="n">
         <v>170451</v>
       </c>
-      <c r="B1790" s="14" t="inlineStr">
+      <c r="B1790" s="13" t="inlineStr">
         <is>
           <t>#05 BEBIDA - CERVEJAS CX</t>
         </is>
@@ -36330,7 +36344,7 @@
           <t>CERV BRAHMA CHOPP LATA 269ML C/ 15 UNID</t>
         </is>
       </c>
-      <c r="D1790" s="14" t="inlineStr">
+      <c r="D1790" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">CERVEJA BRAHMA CHOPP 15 X 269ML </t>
         </is>
@@ -36577,10 +36591,10 @@
       </c>
     </row>
     <row r="1803">
-      <c r="A1803" s="14" t="n">
+      <c r="A1803" s="13" t="n">
         <v>271001</v>
       </c>
-      <c r="B1803" s="14" t="inlineStr">
+      <c r="B1803" s="13" t="inlineStr">
         <is>
           <t>#05 BEBIDA - CERVEJAS CX</t>
         </is>
@@ -36590,7 +36604,7 @@
           <t>CERVEJA IMPERIO 15X269ML PURO MALTE</t>
         </is>
       </c>
-      <c r="D1803" s="14" t="inlineStr">
+      <c r="D1803" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">CERVEJA IMPERIO PURO MALTE 12 X 269ML </t>
         </is>
@@ -36697,20 +36711,20 @@
       </c>
     </row>
     <row r="1809">
-      <c r="A1809" s="5" t="n">
+      <c r="A1809" s="21" t="n">
         <v>324556</v>
       </c>
-      <c r="B1809" s="5" t="inlineStr">
+      <c r="B1809" s="21" t="inlineStr">
         <is>
           <t>#05 BEBIDA - CERVEJAS CX</t>
         </is>
       </c>
-      <c r="C1809" s="5" t="inlineStr">
+      <c r="C1809" s="21" t="inlineStr">
         <is>
           <t>CERVEJA SKOL PILSEN 269ML CAIXA C/15 MUL</t>
         </is>
       </c>
-      <c r="D1809" s="5" t="inlineStr">
+      <c r="D1809" s="21" t="inlineStr">
         <is>
           <t>CERVEJA SKOL PILSEN 15 X 269ML</t>
         </is>
@@ -36997,20 +37011,20 @@
       </c>
     </row>
     <row r="1824">
-      <c r="A1824" s="14" t="n">
+      <c r="A1824" s="13" t="n">
         <v>236673</v>
       </c>
-      <c r="B1824" s="14" t="inlineStr">
+      <c r="B1824" s="13" t="inlineStr">
         <is>
           <t>#05 BEBIDA - DESTILADOS</t>
         </is>
       </c>
-      <c r="C1824" s="14" t="inlineStr">
+      <c r="C1824" s="13" t="inlineStr">
         <is>
           <t>BEB FIU FIU TANGERINA ACEROLA 750ML</t>
         </is>
       </c>
-      <c r="D1824" s="14" t="inlineStr">
+      <c r="D1824" s="13" t="inlineStr">
         <is>
           <t>BEBIDA ALCOOLICA FIU FIU 750ML TANGERINA ACEROLA</t>
         </is>
@@ -37097,20 +37111,20 @@
       </c>
     </row>
     <row r="1829">
-      <c r="A1829" s="5" t="n">
+      <c r="A1829" s="21" t="n">
         <v>102085</v>
       </c>
-      <c r="B1829" s="5" t="inlineStr">
+      <c r="B1829" s="21" t="inlineStr">
         <is>
           <t>#05 BEBIDA - DESTILADOS</t>
         </is>
       </c>
-      <c r="C1829" s="5" t="inlineStr">
+      <c r="C1829" s="21" t="inlineStr">
         <is>
           <t>CACHACA 51 PIRASSUNUNGA 965ML TRAD</t>
         </is>
       </c>
-      <c r="D1829" s="5" t="inlineStr">
+      <c r="D1829" s="21" t="inlineStr">
         <is>
           <t>CACHAÇA 51 965ML</t>
         </is>
@@ -37177,20 +37191,20 @@
       </c>
     </row>
     <row r="1833">
-      <c r="A1833" s="14" t="n">
+      <c r="A1833" s="13" t="n">
         <v>265045</v>
       </c>
-      <c r="B1833" s="14" t="inlineStr">
+      <c r="B1833" s="13" t="inlineStr">
         <is>
           <t>#05 BEBIDA - DESTILADOS</t>
         </is>
       </c>
-      <c r="C1833" s="14" t="inlineStr">
+      <c r="C1833" s="13" t="inlineStr">
         <is>
           <t>CACHACA INDIAZINHA 750ML BANANINHA MISTA</t>
         </is>
       </c>
-      <c r="D1833" s="14" t="inlineStr">
+      <c r="D1833" s="13" t="inlineStr">
         <is>
           <t>CACHAÇA INDIAZINHA 750ML BANANINHA MISTA</t>
         </is>
@@ -37497,20 +37511,20 @@
       </c>
     </row>
     <row r="1849">
-      <c r="A1849" s="14" t="n">
+      <c r="A1849" s="13" t="n">
         <v>301843</v>
       </c>
-      <c r="B1849" s="14" t="inlineStr">
+      <c r="B1849" s="13" t="inlineStr">
         <is>
           <t>#05 BEBIDA - DESTILADOS</t>
         </is>
       </c>
-      <c r="C1849" s="14" t="inlineStr">
+      <c r="C1849" s="13" t="inlineStr">
         <is>
           <t>APERITIVO BITER CAMPARI 998ML</t>
         </is>
       </c>
-      <c r="D1849" s="14" t="inlineStr">
+      <c r="D1849" s="13" t="inlineStr">
         <is>
           <t>CAMPARI 998ML</t>
         </is>
@@ -37557,20 +37571,20 @@
       </c>
     </row>
     <row r="1852">
-      <c r="A1852" s="14" t="n">
+      <c r="A1852" s="13" t="n">
         <v>284865</v>
       </c>
-      <c r="B1852" s="14" t="inlineStr">
+      <c r="B1852" s="13" t="inlineStr">
         <is>
           <t>#05 BEBIDA - DESTILADOS</t>
         </is>
       </c>
-      <c r="C1852" s="14" t="inlineStr">
+      <c r="C1852" s="13" t="inlineStr">
         <is>
           <t>CONHAQUE DREHER 900ML ORIGINAL</t>
         </is>
       </c>
-      <c r="D1852" s="14" t="inlineStr">
+      <c r="D1852" s="13" t="inlineStr">
         <is>
           <t>CONHAQUE DREHER 900ML ORIGINAL</t>
         </is>
@@ -37597,20 +37611,20 @@
       </c>
     </row>
     <row r="1854">
-      <c r="A1854" s="14" t="n">
+      <c r="A1854" s="13" t="n">
         <v>102243</v>
       </c>
-      <c r="B1854" s="14" t="inlineStr">
+      <c r="B1854" s="13" t="inlineStr">
         <is>
           <t>#05 BEBIDA - DESTILADOS</t>
         </is>
       </c>
-      <c r="C1854" s="14" t="inlineStr">
+      <c r="C1854" s="13" t="inlineStr">
         <is>
           <t>CONHAQUE SAO JOAO DA BARRA 900ML TRAD</t>
         </is>
       </c>
-      <c r="D1854" s="14" t="inlineStr">
+      <c r="D1854" s="13" t="inlineStr">
         <is>
           <t>CONHAQUE SÃO JOÃO DA BARRA 900ML TRADICIONAL</t>
         </is>
@@ -37777,20 +37791,20 @@
       </c>
     </row>
     <row r="1863">
-      <c r="A1863" s="14" t="n">
+      <c r="A1863" s="13" t="n">
         <v>230698</v>
       </c>
-      <c r="B1863" s="14" t="inlineStr">
+      <c r="B1863" s="13" t="inlineStr">
         <is>
           <t>#05 BEBIDA - DESTILADOS</t>
         </is>
       </c>
-      <c r="C1863" s="14" t="inlineStr">
+      <c r="C1863" s="13" t="inlineStr">
         <is>
           <t>BE GIN TANQUERAI TEN 750 ML 750 ML</t>
         </is>
       </c>
-      <c r="D1863" s="14" t="inlineStr">
+      <c r="D1863" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">GIN TANQUERAI 750ML TEN </t>
         </is>
@@ -38097,20 +38111,20 @@
       </c>
     </row>
     <row r="1879">
-      <c r="A1879" s="14" t="n">
+      <c r="A1879" s="13" t="n">
         <v>134156</v>
       </c>
-      <c r="B1879" s="14" t="inlineStr">
+      <c r="B1879" s="13" t="inlineStr">
         <is>
           <t>#05 BEBIDA - DESTILADOS</t>
         </is>
       </c>
-      <c r="C1879" s="14" t="inlineStr">
+      <c r="C1879" s="13" t="inlineStr">
         <is>
           <t>VODKA SKYY 980ML</t>
         </is>
       </c>
-      <c r="D1879" s="14" t="inlineStr">
+      <c r="D1879" s="13" t="inlineStr">
         <is>
           <t>VODKA SKYY 980ML</t>
         </is>
@@ -38337,40 +38351,40 @@
       </c>
     </row>
     <row r="1891">
-      <c r="A1891" s="14" t="n">
+      <c r="A1891" s="13" t="n">
         <v>262730</v>
       </c>
-      <c r="B1891" s="14" t="inlineStr">
+      <c r="B1891" s="13" t="inlineStr">
         <is>
           <t>#05 BEBIDA - DESTILADOS</t>
         </is>
       </c>
-      <c r="C1891" s="14" t="inlineStr">
+      <c r="C1891" s="13" t="inlineStr">
         <is>
           <t>WHISKY BUCHANANS 750ML DELUXE 12 ANOS</t>
         </is>
       </c>
-      <c r="D1891" s="14" t="inlineStr">
+      <c r="D1891" s="13" t="inlineStr">
         <is>
           <t>WHISKY BUCHANANS 750ML DELUXE 12 ANOS</t>
         </is>
       </c>
     </row>
     <row r="1892">
-      <c r="A1892" s="14" t="n">
+      <c r="A1892" s="13" t="n">
         <v>109727</v>
       </c>
-      <c r="B1892" s="14" t="inlineStr">
+      <c r="B1892" s="13" t="inlineStr">
         <is>
           <t>#05 BEBIDA - DESTILADOS</t>
         </is>
       </c>
-      <c r="C1892" s="14" t="inlineStr">
+      <c r="C1892" s="13" t="inlineStr">
         <is>
           <t>WHISKY CHIVAS REGAL 12ANOS 1LT</t>
         </is>
       </c>
-      <c r="D1892" s="14" t="inlineStr">
+      <c r="D1892" s="13" t="inlineStr">
         <is>
           <t>WHISKY CHIVAS REGAL 1L 12 ANOS</t>
         </is>
@@ -38537,20 +38551,20 @@
       </c>
     </row>
     <row r="1901">
-      <c r="A1901" s="14" t="n">
+      <c r="A1901" s="13" t="n">
         <v>102077</v>
       </c>
-      <c r="B1901" s="14" t="inlineStr">
+      <c r="B1901" s="13" t="inlineStr">
         <is>
           <t>#05 BEBIDA - DESTILADOS</t>
         </is>
       </c>
-      <c r="C1901" s="14" t="inlineStr">
+      <c r="C1901" s="13" t="inlineStr">
         <is>
           <t>WHISKY OLD PARR 12 ANOS 1L</t>
         </is>
       </c>
-      <c r="D1901" s="14" t="inlineStr">
+      <c r="D1901" s="13" t="inlineStr">
         <is>
           <t>WHISKY OLD PARR 1L 12 ANOS</t>
         </is>
@@ -38737,20 +38751,20 @@
       </c>
     </row>
     <row r="1911">
-      <c r="A1911" s="14" t="n">
+      <c r="A1911" s="21" t="n">
         <v>295198</v>
       </c>
-      <c r="B1911" s="14" t="inlineStr">
+      <c r="B1911" s="21" t="inlineStr">
         <is>
           <t>#05 BEBIDA - FERMENTADOS</t>
         </is>
       </c>
-      <c r="C1911" s="14" t="inlineStr">
+      <c r="C1911" s="21" t="inlineStr">
         <is>
           <t>CHOPP DE VINHO STEMPEL 600ML RED</t>
         </is>
       </c>
-      <c r="D1911" s="14" t="inlineStr">
+      <c r="D1911" s="21" t="inlineStr">
         <is>
           <t>CHOPP DE VINHO STEMPEL 600ML RED</t>
         </is>
@@ -39177,20 +39191,20 @@
       </c>
     </row>
     <row r="1933">
-      <c r="A1933" s="14" t="n">
+      <c r="A1933" s="13" t="n">
         <v>147495</v>
       </c>
-      <c r="B1933" s="14" t="inlineStr">
+      <c r="B1933" s="13" t="inlineStr">
         <is>
           <t>#05 BEBIDA - FERMENTADOS</t>
         </is>
       </c>
-      <c r="C1933" s="14" t="inlineStr">
+      <c r="C1933" s="13" t="inlineStr">
         <is>
           <t>VINHO PERGOLA 2LT TINTO SUAVE</t>
         </is>
       </c>
-      <c r="D1933" s="14" t="inlineStr">
+      <c r="D1933" s="13" t="inlineStr">
         <is>
           <t>VINHO PERGOLA 2L TINTO SUAVE</t>
         </is>
@@ -39637,40 +39651,40 @@
       </c>
     </row>
     <row r="1956">
-      <c r="A1956" t="n">
+      <c r="A1956" s="21" t="n">
         <v>207640</v>
       </c>
-      <c r="B1956" t="inlineStr">
+      <c r="B1956" s="21" t="inlineStr">
         <is>
           <t>#06 LIMPEZA - ALVEJANTES E ÁGUA SANITÁRIA</t>
         </is>
       </c>
-      <c r="C1956" t="inlineStr">
+      <c r="C1956" s="21" t="inlineStr">
         <is>
           <t>ÁGUA SANITÁRIA LAVABEM 2L</t>
         </is>
       </c>
-      <c r="D1956" t="inlineStr">
+      <c r="D1956" s="21" t="inlineStr">
         <is>
           <t>ÁGUA SANITÁRIA LAVABEM 2L</t>
         </is>
       </c>
     </row>
     <row r="1957">
-      <c r="A1957" s="17" t="n">
+      <c r="A1957" s="8" t="n">
         <v>100426</v>
       </c>
-      <c r="B1957" s="17" t="inlineStr">
+      <c r="B1957" s="8" t="inlineStr">
         <is>
           <t>#06 LIMPEZA - ALVEJANTES E ÁGUA SANITÁRIA</t>
         </is>
       </c>
-      <c r="C1957" s="17" t="inlineStr">
+      <c r="C1957" s="8" t="inlineStr">
         <is>
           <t>ÁGUA SANIT QBOA 1L MULTIPLO USO</t>
         </is>
       </c>
-      <c r="D1957" s="17" t="inlineStr">
+      <c r="D1957" s="8" t="inlineStr">
         <is>
           <t>ÁGUA SANITÁRIA QBOA 1L</t>
         </is>
@@ -39717,20 +39731,20 @@
       </c>
     </row>
     <row r="1960">
-      <c r="A1960" s="19" t="n">
+      <c r="A1960" s="13" t="n">
         <v>257145</v>
       </c>
-      <c r="B1960" s="19" t="inlineStr">
+      <c r="B1960" s="13" t="inlineStr">
         <is>
           <t>#06 LIMPEZA - ALVEJANTES E ÁGUA SANITÁRIA</t>
         </is>
       </c>
-      <c r="C1960" s="19" t="inlineStr">
+      <c r="C1960" s="13" t="inlineStr">
         <is>
           <t>AGUA SANITARIA TUBARAO 1L</t>
         </is>
       </c>
-      <c r="D1960" s="19" t="inlineStr">
+      <c r="D1960" s="13" t="inlineStr">
         <is>
           <t>ÁGUA SANITARIA TUBARÃO 1L</t>
         </is>
@@ -41097,20 +41111,20 @@
       </c>
     </row>
     <row r="2029">
-      <c r="A2029" t="n">
+      <c r="A2029" s="21" t="n">
         <v>330053</v>
       </c>
-      <c r="B2029" t="inlineStr">
+      <c r="B2029" s="21" t="inlineStr">
         <is>
           <t>#06 LIMPEZA - AMACIANTES</t>
         </is>
       </c>
-      <c r="C2029" t="inlineStr">
+      <c r="C2029" s="21" t="inlineStr">
         <is>
           <t>AMACIANTE ROU YPÊ 1,6L ACONCHEGO</t>
         </is>
       </c>
-      <c r="D2029" t="inlineStr">
+      <c r="D2029" s="21" t="inlineStr">
         <is>
           <t>AMACIANTE DE ROUPAS YPÊ 1,6L ACONCHEGO</t>
         </is>
@@ -42637,40 +42651,40 @@
       </c>
     </row>
     <row r="2106">
-      <c r="A2106" t="n">
+      <c r="A2106" s="21" t="n">
         <v>148554</v>
       </c>
-      <c r="B2106" t="inlineStr">
+      <c r="B2106" s="21" t="inlineStr">
         <is>
           <t>#06 LIMPEZA - DESINFETANTES</t>
         </is>
       </c>
-      <c r="C2106" t="inlineStr">
+      <c r="C2106" s="21" t="inlineStr">
         <is>
           <t>DESINFETANTE BAK YPÊ EUCALIPTO 2LTS</t>
         </is>
       </c>
-      <c r="D2106" t="inlineStr">
+      <c r="D2106" s="21" t="inlineStr">
         <is>
           <t>DESINFETANTE YPÊ BAK 2L EUCALIPTO</t>
         </is>
       </c>
     </row>
     <row r="2107">
-      <c r="A2107" t="n">
+      <c r="A2107" s="21" t="n">
         <v>134193</v>
       </c>
-      <c r="B2107" t="inlineStr">
+      <c r="B2107" s="21" t="inlineStr">
         <is>
           <t>#06 LIMPEZA - DESINFETANTES</t>
         </is>
       </c>
-      <c r="C2107" t="inlineStr">
+      <c r="C2107" s="21" t="inlineStr">
         <is>
           <t>DESINFETANTE BAK YPÊ FLORAL 2LTS</t>
         </is>
       </c>
-      <c r="D2107" t="inlineStr">
+      <c r="D2107" s="21" t="inlineStr">
         <is>
           <t>DESINFETANTE YPÊ BAK 2L FLORAL</t>
         </is>
@@ -42837,140 +42851,140 @@
       </c>
     </row>
     <row r="2116">
-      <c r="A2116" s="17" t="n">
+      <c r="A2116" s="8" t="n">
         <v>100423</v>
       </c>
-      <c r="B2116" s="17" t="inlineStr">
+      <c r="B2116" s="8" t="inlineStr">
         <is>
           <t>#06 LIMPEZA - DETERGENTES</t>
         </is>
       </c>
-      <c r="C2116" s="17" t="inlineStr">
+      <c r="C2116" s="8" t="inlineStr">
         <is>
           <t>DETERGENTE LIQUIDO LIMPOL 500ML COCO</t>
         </is>
       </c>
-      <c r="D2116" s="17" t="inlineStr">
+      <c r="D2116" s="8" t="inlineStr">
         <is>
           <t>DETERGENTE LIQUIDO LIMPOL 500ML COCO</t>
         </is>
       </c>
     </row>
     <row r="2117">
-      <c r="A2117" s="17" t="n">
+      <c r="A2117" s="8" t="n">
         <v>100419</v>
       </c>
-      <c r="B2117" s="17" t="inlineStr">
+      <c r="B2117" s="8" t="inlineStr">
         <is>
           <t>#06 LIMPEZA - DETERGENTES</t>
         </is>
       </c>
-      <c r="C2117" s="17" t="inlineStr">
+      <c r="C2117" s="8" t="inlineStr">
         <is>
           <t>DETERGENTE LIQUIDO LIMPOL 500ML CRISTAL</t>
         </is>
       </c>
-      <c r="D2117" s="17" t="inlineStr">
+      <c r="D2117" s="8" t="inlineStr">
         <is>
           <t>DETERGENTE LIQUIDO LIMPOL 500ML CRISTAL</t>
         </is>
       </c>
     </row>
     <row r="2118">
-      <c r="A2118" s="17" t="n">
+      <c r="A2118" s="8" t="n">
         <v>220037</v>
       </c>
-      <c r="B2118" s="17" t="inlineStr">
+      <c r="B2118" s="8" t="inlineStr">
         <is>
           <t>#06 LIMPEZA - DETERGENTES</t>
         </is>
       </c>
-      <c r="C2118" s="17" t="inlineStr">
+      <c r="C2118" s="8" t="inlineStr">
         <is>
           <t>DETERGENTE LIQUIDO LIMPOL 500ML JABOTICABA</t>
         </is>
       </c>
-      <c r="D2118" s="17" t="inlineStr">
+      <c r="D2118" s="8" t="inlineStr">
         <is>
           <t>DETERGENTE LIQUIDO LIMPOL 500ML JABOTICABA</t>
         </is>
       </c>
     </row>
     <row r="2119">
-      <c r="A2119" s="17" t="n">
+      <c r="A2119" s="8" t="n">
         <v>204461</v>
       </c>
-      <c r="B2119" s="17" t="inlineStr">
+      <c r="B2119" s="8" t="inlineStr">
         <is>
           <t>#06 LIMPEZA - DETERGENTES</t>
         </is>
       </c>
-      <c r="C2119" s="17" t="inlineStr">
+      <c r="C2119" s="8" t="inlineStr">
         <is>
           <t>DETERGENTE LIQUIDO LIMPOL 500ML LAVANDA</t>
         </is>
       </c>
-      <c r="D2119" s="17" t="inlineStr">
+      <c r="D2119" s="8" t="inlineStr">
         <is>
           <t>DETERGENTE LIQUIDO LIMPOL 500ML LAVANDA</t>
         </is>
       </c>
     </row>
     <row r="2120">
-      <c r="A2120" s="17" t="n">
+      <c r="A2120" s="8" t="n">
         <v>100420</v>
       </c>
-      <c r="B2120" s="17" t="inlineStr">
+      <c r="B2120" s="8" t="inlineStr">
         <is>
           <t>#06 LIMPEZA - DETERGENTES</t>
         </is>
       </c>
-      <c r="C2120" s="17" t="inlineStr">
+      <c r="C2120" s="8" t="inlineStr">
         <is>
           <t>DETERGENTE LIQUIDO LIMPOL 500ML LIMÃO</t>
         </is>
       </c>
-      <c r="D2120" s="17" t="inlineStr">
+      <c r="D2120" s="8" t="inlineStr">
         <is>
           <t>DETERGENTE LIQUIDO LIMPOL 500ML LIMÃO</t>
         </is>
       </c>
     </row>
     <row r="2121">
-      <c r="A2121" s="17" t="n">
+      <c r="A2121" s="8" t="n">
         <v>100417</v>
       </c>
-      <c r="B2121" s="17" t="inlineStr">
+      <c r="B2121" s="8" t="inlineStr">
         <is>
           <t>#06 LIMPEZA - DETERGENTES</t>
         </is>
       </c>
-      <c r="C2121" s="17" t="inlineStr">
+      <c r="C2121" s="8" t="inlineStr">
         <is>
           <t>DETERGENTE LIQUIDO LIMPOL 500ML MAÇÃ</t>
         </is>
       </c>
-      <c r="D2121" s="17" t="inlineStr">
+      <c r="D2121" s="8" t="inlineStr">
         <is>
           <t>DETERGENTE LIQUIDO LIMPOL 500ML MAÇÃ</t>
         </is>
       </c>
     </row>
     <row r="2122">
-      <c r="A2122" s="17" t="n">
+      <c r="A2122" s="8" t="n">
         <v>106661</v>
       </c>
-      <c r="B2122" s="17" t="inlineStr">
+      <c r="B2122" s="8" t="inlineStr">
         <is>
           <t>#06 LIMPEZA - DETERGENTES</t>
         </is>
       </c>
-      <c r="C2122" s="17" t="inlineStr">
+      <c r="C2122" s="8" t="inlineStr">
         <is>
           <t>DETERGENTE LIQUIDO LIMPOL 500ML NEUTRO</t>
         </is>
       </c>
-      <c r="D2122" s="17" t="inlineStr">
+      <c r="D2122" s="8" t="inlineStr">
         <is>
           <t>DETERGENTE LIQUIDO LIMPOL 500ML NEUTRO</t>
         </is>
@@ -43177,100 +43191,100 @@
       </c>
     </row>
     <row r="2133">
-      <c r="A2133" t="n">
+      <c r="A2133" s="21" t="n">
         <v>100391</v>
       </c>
-      <c r="B2133" t="inlineStr">
+      <c r="B2133" s="21" t="inlineStr">
         <is>
           <t>#06 LIMPEZA - DETERGENTES</t>
         </is>
       </c>
-      <c r="C2133" t="inlineStr">
+      <c r="C2133" s="21" t="inlineStr">
         <is>
           <t>DETERGENTE LIQUIDO YPÊ 500ML CAPIM LIMAO</t>
         </is>
       </c>
-      <c r="D2133" t="inlineStr">
+      <c r="D2133" s="21" t="inlineStr">
         <is>
           <t>DETERGENTE LIQUIDO YPÊ 500ML CAPIM LIMÃO</t>
         </is>
       </c>
     </row>
     <row r="2134">
-      <c r="A2134" t="n">
+      <c r="A2134" s="21" t="n">
         <v>100394</v>
       </c>
-      <c r="B2134" t="inlineStr">
+      <c r="B2134" s="21" t="inlineStr">
         <is>
           <t>#06 LIMPEZA - DETERGENTES</t>
         </is>
       </c>
-      <c r="C2134" t="inlineStr">
+      <c r="C2134" s="21" t="inlineStr">
         <is>
           <t>DETERGENTE LIQUIDO YPÊ 500ML CLEAR</t>
         </is>
       </c>
-      <c r="D2134" t="inlineStr">
+      <c r="D2134" s="21" t="inlineStr">
         <is>
           <t>DETERGENTE LIQUIDO YPÊ 500ML CLEAR</t>
         </is>
       </c>
     </row>
     <row r="2135">
-      <c r="A2135" t="n">
+      <c r="A2135" s="21" t="n">
         <v>100392</v>
       </c>
-      <c r="B2135" t="inlineStr">
+      <c r="B2135" s="21" t="inlineStr">
         <is>
           <t>#06 LIMPEZA - DETERGENTES</t>
         </is>
       </c>
-      <c r="C2135" t="inlineStr">
+      <c r="C2135" s="21" t="inlineStr">
         <is>
           <t>DETERGENTE LIQUIDO YPÊ 500ML CLEAR CARE</t>
         </is>
       </c>
-      <c r="D2135" t="inlineStr">
+      <c r="D2135" s="21" t="inlineStr">
         <is>
           <t>DETERGENTE LIQUIDO YPÊ 500ML CLEAR CARE</t>
         </is>
       </c>
     </row>
     <row r="2136">
-      <c r="A2136" t="n">
+      <c r="A2136" s="21" t="n">
         <v>100402</v>
       </c>
-      <c r="B2136" t="inlineStr">
+      <c r="B2136" s="21" t="inlineStr">
         <is>
           <t>#06 LIMPEZA - DETERGENTES</t>
         </is>
       </c>
-      <c r="C2136" t="inlineStr">
+      <c r="C2136" s="21" t="inlineStr">
         <is>
           <t>DETERGENTE LIQUIDO YPÊ 500ML COCO</t>
         </is>
       </c>
-      <c r="D2136" t="inlineStr">
+      <c r="D2136" s="21" t="inlineStr">
         <is>
           <t>DETERGENTE LIQUIDO YPÊ 500ML COCO</t>
         </is>
       </c>
     </row>
     <row r="2137">
-      <c r="A2137" t="n">
+      <c r="A2137" s="21" t="n">
         <v>100403</v>
       </c>
-      <c r="B2137" t="inlineStr">
+      <c r="B2137" s="21" t="inlineStr">
         <is>
           <t>#06 LIMPEZA - DETERGENTES</t>
         </is>
       </c>
-      <c r="C2137" t="inlineStr">
+      <c r="C2137" s="21" t="inlineStr">
         <is>
           <t>DETERGENTE LIQUIDO YPÊ 500ML LIMAO</t>
         </is>
       </c>
-      <c r="D2137" t="inlineStr">
+      <c r="D2137" s="21" t="inlineStr">
         <is>
           <t>DETERGENTE LIQUIDO YPÊ 500ML LIMAO</t>
         </is>
@@ -43297,40 +43311,40 @@
       </c>
     </row>
     <row r="2139">
-      <c r="A2139" t="n">
+      <c r="A2139" s="21" t="n">
         <v>100393</v>
       </c>
-      <c r="B2139" t="inlineStr">
+      <c r="B2139" s="21" t="inlineStr">
         <is>
           <t>#06 LIMPEZA - DETERGENTES</t>
         </is>
       </c>
-      <c r="C2139" t="inlineStr">
+      <c r="C2139" s="21" t="inlineStr">
         <is>
           <t>DETERGENTE LIQUIDO YPÊ 500ML MACA</t>
         </is>
       </c>
-      <c r="D2139" t="inlineStr">
+      <c r="D2139" s="21" t="inlineStr">
         <is>
           <t>DETERGENTE LIQUIDO YPÊ 500ML MACA</t>
         </is>
       </c>
     </row>
     <row r="2140">
-      <c r="A2140" t="n">
+      <c r="A2140" s="21" t="n">
         <v>100390</v>
       </c>
-      <c r="B2140" t="inlineStr">
+      <c r="B2140" s="21" t="inlineStr">
         <is>
           <t>#06 LIMPEZA - DETERGENTES</t>
         </is>
       </c>
-      <c r="C2140" t="inlineStr">
+      <c r="C2140" s="21" t="inlineStr">
         <is>
           <t>DETERGENTE LIQUIDO YPÊ 500ML NEUTRO</t>
         </is>
       </c>
-      <c r="D2140" t="inlineStr">
+      <c r="D2140" s="21" t="inlineStr">
         <is>
           <t>DETERGENTE LIQUIDO YPÊ 500ML NEUTRO</t>
         </is>
@@ -43717,80 +43731,80 @@
       </c>
     </row>
     <row r="2160">
-      <c r="A2160" t="n">
+      <c r="A2160" s="21" t="n">
         <v>100511</v>
       </c>
-      <c r="B2160" t="inlineStr">
+      <c r="B2160" s="21" t="inlineStr">
         <is>
           <t>#06 LIMPEZA - LIMPA ALUMINIO</t>
         </is>
       </c>
-      <c r="C2160" t="inlineStr">
+      <c r="C2160" s="21" t="inlineStr">
         <is>
           <t>LIMPA ALUMINIO POLITRIZ 500ML LIMAO</t>
         </is>
       </c>
-      <c r="D2160" t="inlineStr">
+      <c r="D2160" s="21" t="inlineStr">
         <is>
           <t>LIMPA ALUMINIO POLITRIZ 500ML LIMÃO</t>
         </is>
       </c>
     </row>
     <row r="2161">
-      <c r="A2161" t="n">
+      <c r="A2161" s="21" t="n">
         <v>122716</v>
       </c>
-      <c r="B2161" t="inlineStr">
+      <c r="B2161" s="21" t="inlineStr">
         <is>
           <t>#06 LIMPEZA - LIMPA ALUMINIO</t>
         </is>
       </c>
-      <c r="C2161" t="inlineStr">
+      <c r="C2161" s="21" t="inlineStr">
         <is>
           <t>LIMPA ALUMINIO POLITRIZ 500ML TRADICIONA</t>
         </is>
       </c>
-      <c r="D2161" t="inlineStr">
+      <c r="D2161" s="21" t="inlineStr">
         <is>
           <t>LIMPA ALUMINIO POLITRIZ 500ML TRADICIONAL</t>
         </is>
       </c>
     </row>
     <row r="2162">
-      <c r="A2162" s="17" t="n">
+      <c r="A2162" s="8" t="n">
         <v>118939</v>
       </c>
-      <c r="B2162" s="17" t="inlineStr">
+      <c r="B2162" s="8" t="inlineStr">
         <is>
           <t>#06 LIMPEZA - LIMPA ALUMINIO</t>
         </is>
       </c>
-      <c r="C2162" s="17" t="inlineStr">
+      <c r="C2162" s="8" t="inlineStr">
         <is>
           <t>LIMPA ALUMINIO POLYLAR 500ML LIMAO</t>
         </is>
       </c>
-      <c r="D2162" s="17" t="inlineStr">
+      <c r="D2162" s="8" t="inlineStr">
         <is>
           <t>LIMPA ALUMINIO POLYLAR 500ML LIMÃO</t>
         </is>
       </c>
     </row>
     <row r="2163">
-      <c r="A2163" s="17" t="n">
+      <c r="A2163" s="8" t="n">
         <v>118940</v>
       </c>
-      <c r="B2163" s="17" t="inlineStr">
+      <c r="B2163" s="8" t="inlineStr">
         <is>
           <t>#06 LIMPEZA - LIMPA ALUMINIO</t>
         </is>
       </c>
-      <c r="C2163" s="17" t="inlineStr">
+      <c r="C2163" s="8" t="inlineStr">
         <is>
           <t>LIMPA ALUMINIO POLYLAR 500ML MACA</t>
         </is>
       </c>
-      <c r="D2163" s="17" t="inlineStr">
+      <c r="D2163" s="8" t="inlineStr">
         <is>
           <t>LIMPA ALUMINIO POLYLAR 500ML MAÇÃ</t>
         </is>
@@ -44497,20 +44511,20 @@
       </c>
     </row>
     <row r="2199">
-      <c r="A2199" s="17" t="n">
+      <c r="A2199" s="8" t="n">
         <v>107645</v>
       </c>
-      <c r="B2199" s="17" t="inlineStr">
+      <c r="B2199" s="8" t="inlineStr">
         <is>
           <t>#06 LIMPEZA - LIMPADORES</t>
         </is>
       </c>
-      <c r="C2199" s="17" t="inlineStr">
+      <c r="C2199" s="8" t="inlineStr">
         <is>
           <t>LIMP VEJA MULTI USO 500ML ORIGINAL</t>
         </is>
       </c>
-      <c r="D2199" s="17" t="inlineStr">
+      <c r="D2199" s="8" t="inlineStr">
         <is>
           <t>LIMPADOR VEJA MULTI USO 500ML ORIGINAL</t>
         </is>
@@ -44657,20 +44671,20 @@
       </c>
     </row>
     <row r="2207">
-      <c r="A2207" s="17" t="n">
+      <c r="A2207" s="8" t="n">
         <v>318739</v>
       </c>
-      <c r="B2207" s="17" t="inlineStr">
+      <c r="B2207" s="8" t="inlineStr">
         <is>
           <t>#06 LIMPEZA - LIMPADORES</t>
         </is>
       </c>
-      <c r="C2207" s="17" t="inlineStr">
+      <c r="C2207" s="8" t="inlineStr">
         <is>
           <t>LIMPADOR EM PO CIF 2,4KG LIMPEZA PESADA</t>
         </is>
       </c>
-      <c r="D2207" s="17" t="inlineStr">
+      <c r="D2207" s="8" t="inlineStr">
         <is>
           <t>LIMPADOR EM PÓ CIF 2,4KG LIMPEZA PESADA</t>
         </is>
@@ -45137,20 +45151,20 @@
       </c>
     </row>
     <row r="2231">
-      <c r="A2231" s="17" t="n">
+      <c r="A2231" s="8" t="n">
         <v>257710</v>
       </c>
-      <c r="B2231" s="17" t="inlineStr">
+      <c r="B2231" s="8" t="inlineStr">
         <is>
           <t>#06 LIMPEZA - SABÃO</t>
         </is>
       </c>
-      <c r="C2231" s="17" t="inlineStr">
+      <c r="C2231" s="8" t="inlineStr">
         <is>
           <t>SABAO BARRA YPÊ 5X180GR NEUTRO GLICERINA</t>
         </is>
       </c>
-      <c r="D2231" s="17" t="inlineStr">
+      <c r="D2231" s="8" t="inlineStr">
         <is>
           <t>SABÃO EM BARRA YPÊ 900G NEUTRO</t>
         </is>
@@ -45217,20 +45231,20 @@
       </c>
     </row>
     <row r="2235">
-      <c r="A2235" t="n">
+      <c r="A2235" s="21" t="n">
         <v>261980</v>
       </c>
-      <c r="B2235" t="inlineStr">
+      <c r="B2235" s="21" t="inlineStr">
         <is>
           <t>#06 LIMPEZA - SABÃO</t>
         </is>
       </c>
-      <c r="C2235" t="inlineStr">
+      <c r="C2235" s="21" t="inlineStr">
         <is>
           <t>SABÃO EM PÓ BRILHANTE 1,6KG LIMPEZA TOTA</t>
         </is>
       </c>
-      <c r="D2235" t="inlineStr">
+      <c r="D2235" s="21" t="inlineStr">
         <is>
           <t>SABÃO EM PÓ BRILHANTE CAIXA 1,6KG LIMPEZA TOTAL</t>
         </is>
@@ -45637,20 +45651,20 @@
       </c>
     </row>
     <row r="2256">
-      <c r="A2256" s="17" t="n">
+      <c r="A2256" s="8" t="n">
         <v>286199</v>
       </c>
-      <c r="B2256" s="17" t="inlineStr">
+      <c r="B2256" s="8" t="inlineStr">
         <is>
           <t>#06 LIMPEZA - SABÃO</t>
         </is>
       </c>
-      <c r="C2256" s="17" t="inlineStr">
+      <c r="C2256" s="8" t="inlineStr">
         <is>
           <t>SABÃO EM PÓ TIXAN YPÊ 800GR MACIEZ CAIXA</t>
         </is>
       </c>
-      <c r="D2256" s="17" t="inlineStr">
+      <c r="D2256" s="8" t="inlineStr">
         <is>
           <t>SABÃO EM PÓ TIXAN YPÊ CAIXA 800G MACIEZ</t>
         </is>
@@ -45917,20 +45931,20 @@
       </c>
     </row>
     <row r="2270">
-      <c r="A2270" s="17" t="n">
+      <c r="A2270" s="8" t="n">
         <v>135352</v>
       </c>
-      <c r="B2270" s="17" t="inlineStr">
+      <c r="B2270" s="8" t="inlineStr">
         <is>
           <t>#06 LIMPEZA - SODAS CAUSTICAS</t>
         </is>
       </c>
-      <c r="C2270" s="17" t="inlineStr">
+      <c r="C2270" s="8" t="inlineStr">
         <is>
           <t>SODA CAUSTICA TROVAO 1KG</t>
         </is>
       </c>
-      <c r="D2270" s="17" t="inlineStr">
+      <c r="D2270" s="8" t="inlineStr">
         <is>
           <t>SODA CAUSTICA TROVÃO 1KG</t>
         </is>
@@ -48337,20 +48351,20 @@
       </c>
     </row>
     <row r="2391">
-      <c r="A2391" s="9" t="n">
+      <c r="A2391" s="7" t="n">
         <v>265622</v>
       </c>
-      <c r="B2391" s="9" t="inlineStr">
+      <c r="B2391" s="7" t="inlineStr">
         <is>
           <t>#07 HIGIENE PESSOAL - CABELOS</t>
         </is>
       </c>
-      <c r="C2391" s="9" t="inlineStr">
+      <c r="C2391" s="7" t="inlineStr">
         <is>
           <t>CREME LOREAL ELSEVE 200GR NOTURNO CACHOS SONHOS ANTI</t>
         </is>
       </c>
-      <c r="D2391" s="9" t="inlineStr">
+      <c r="D2391" s="7" t="inlineStr">
         <is>
           <t>CREME LOREAL ELSEVE NOTURNO 200G CACHOS SONHOS ANTI-TRAVESSEIRO</t>
         </is>
@@ -49477,20 +49491,20 @@
       </c>
     </row>
     <row r="2448">
-      <c r="A2448" s="9" t="n">
+      <c r="A2448" s="7" t="n">
         <v>311070</v>
       </c>
-      <c r="B2448" s="9" t="inlineStr">
+      <c r="B2448" s="7" t="inlineStr">
         <is>
           <t>#07 HIGIENE PESSOAL - CABELOS</t>
         </is>
       </c>
-      <c r="C2448" s="9" t="inlineStr">
+      <c r="C2448" s="7" t="inlineStr">
         <is>
           <t>MASCARA CAPILAR CHIKAS 700GR ACORDA CACH</t>
         </is>
       </c>
-      <c r="D2448" s="9" t="inlineStr">
+      <c r="D2448" s="7" t="inlineStr">
         <is>
           <t>MÁSCARA CAPILAR CHIKAS 700G ACORDA CACHOS ARIBA</t>
         </is>
@@ -49537,20 +49551,20 @@
       </c>
     </row>
     <row r="2451">
-      <c r="A2451" s="9" t="n">
+      <c r="A2451" s="7" t="n">
         <v>318658</v>
       </c>
-      <c r="B2451" s="9" t="inlineStr">
+      <c r="B2451" s="7" t="inlineStr">
         <is>
           <t>#07 HIGIENE PESSOAL - CABELOS</t>
         </is>
       </c>
-      <c r="C2451" s="9" t="inlineStr">
+      <c r="C2451" s="7" t="inlineStr">
         <is>
           <t>MASCARA CAPILAR CHIKAS 700GR CRESPO PODE</t>
         </is>
       </c>
-      <c r="D2451" s="9" t="inlineStr">
+      <c r="D2451" s="7" t="inlineStr">
         <is>
           <t>MÁSCARA CAPILAR CHIKAS 700G CRESPO PODEROSO</t>
         </is>
@@ -50657,20 +50671,20 @@
       </c>
     </row>
     <row r="2507">
-      <c r="A2507" s="9" t="n">
+      <c r="A2507" s="7" t="n">
         <v>308254</v>
       </c>
-      <c r="B2507" s="9" t="inlineStr">
+      <c r="B2507" s="7" t="inlineStr">
         <is>
           <t>#07 HIGIENE PESSOAL - CABELOS</t>
         </is>
       </c>
-      <c r="C2507" s="9" t="inlineStr">
+      <c r="C2507" s="7" t="inlineStr">
         <is>
           <t>TINT BIOCOLOR MINI KIT 1UN 5.3 CAST CLAR/DOU</t>
         </is>
       </c>
-      <c r="D2507" s="9" t="inlineStr">
+      <c r="D2507" s="7" t="inlineStr">
         <is>
           <t>TINTURA CAPILAR BIOCOLOR MINI KIT 1UN 5.3 CASTANHA CLARO DOURADO</t>
         </is>
@@ -51137,20 +51151,20 @@
       </c>
     </row>
     <row r="2531">
-      <c r="A2531" s="9" t="n">
+      <c r="A2531" s="7" t="n">
         <v>308784</v>
       </c>
-      <c r="B2531" s="9" t="inlineStr">
+      <c r="B2531" s="7" t="inlineStr">
         <is>
           <t>#07 HIGIENE PESSOAL - DESODORANTE</t>
         </is>
       </c>
-      <c r="C2531" s="9" t="inlineStr">
+      <c r="C2531" s="7" t="inlineStr">
         <is>
           <t>DESODORANTE GB MEN 50ML ROLL-ON 72H  SPORT S/PERFUME</t>
         </is>
       </c>
-      <c r="D2531" s="9" t="inlineStr">
+      <c r="D2531" s="7" t="inlineStr">
         <is>
           <t>DESODORANTE GB MEN ROLL-ON 50ML 72H SPORT SEM PERFUME</t>
         </is>
@@ -52797,20 +52811,20 @@
       </c>
     </row>
     <row r="2614">
-      <c r="A2614" s="9" t="n">
+      <c r="A2614" s="7" t="n">
         <v>308386</v>
       </c>
-      <c r="B2614" s="9" t="inlineStr">
+      <c r="B2614" s="7" t="inlineStr">
         <is>
           <t>#07 HIGIENE PESSOAL - ESMALTES</t>
         </is>
       </c>
-      <c r="C2614" s="9" t="inlineStr">
+      <c r="C2614" s="7" t="inlineStr">
         <is>
           <t>ESMALTE RISQUE 8ML A ARTISTA SOU EU</t>
         </is>
       </c>
-      <c r="D2614" s="9" t="inlineStr">
+      <c r="D2614" s="7" t="inlineStr">
         <is>
           <t>ESMALTE RISQUE 8ML A ARTISTA SOU EU</t>
         </is>
@@ -53857,20 +53871,20 @@
       </c>
     </row>
     <row r="2667">
-      <c r="A2667" s="9" t="n">
+      <c r="A2667" s="7" t="n">
         <v>308394</v>
       </c>
-      <c r="B2667" s="9" t="inlineStr">
+      <c r="B2667" s="7" t="inlineStr">
         <is>
           <t>#07 HIGIENE PESSOAL - ESMALTES</t>
         </is>
       </c>
-      <c r="C2667" s="9" t="inlineStr">
+      <c r="C2667" s="7" t="inlineStr">
         <is>
           <t>ESMALTE RISQUE 8ML FICA, VAI TER ARCO IR</t>
         </is>
       </c>
-      <c r="D2667" s="9" t="inlineStr">
+      <c r="D2667" s="7" t="inlineStr">
         <is>
           <t>ESMALTE RISQUE 8ML FICA, VAI TER ARCO IRIS</t>
         </is>
@@ -54277,20 +54291,20 @@
       </c>
     </row>
     <row r="2688">
-      <c r="A2688" s="9" t="n">
+      <c r="A2688" s="7" t="n">
         <v>308385</v>
       </c>
-      <c r="B2688" s="9" t="inlineStr">
+      <c r="B2688" s="7" t="inlineStr">
         <is>
           <t>#07 HIGIENE PESSOAL - ESMALTES</t>
         </is>
       </c>
-      <c r="C2688" s="9" t="inlineStr">
+      <c r="C2688" s="7" t="inlineStr">
         <is>
           <t>ESMALTE RISQUE 8ML MAR DE POSSIBILIDADES</t>
         </is>
       </c>
-      <c r="D2688" s="9" t="inlineStr">
+      <c r="D2688" s="7" t="inlineStr">
         <is>
           <t>ESMALTE RISQUE 8ML MAR DE POSSIBILIDADES</t>
         </is>
@@ -54877,20 +54891,20 @@
       </c>
     </row>
     <row r="2718">
-      <c r="A2718" s="9" t="n">
+      <c r="A2718" s="7" t="n">
         <v>162175</v>
       </c>
-      <c r="B2718" s="9" t="inlineStr">
+      <c r="B2718" s="7" t="inlineStr">
         <is>
           <t>#07 HIGIENE PESSOAL - ESMALTES</t>
         </is>
       </c>
-      <c r="C2718" s="9" t="inlineStr">
+      <c r="C2718" s="7" t="inlineStr">
         <is>
           <t>ESM RISQUE 8MLBL TECNOLOGY SERUM REPARAD</t>
         </is>
       </c>
-      <c r="D2718" s="9" t="inlineStr">
+      <c r="D2718" s="7" t="inlineStr">
         <is>
           <t>ESMALTE RISQUE 8ML SERUM HIDRATANTE</t>
         </is>
@@ -54977,20 +54991,20 @@
       </c>
     </row>
     <row r="2723">
-      <c r="A2723" s="9" t="n">
+      <c r="A2723" s="7" t="n">
         <v>308383</v>
       </c>
-      <c r="B2723" s="9" t="inlineStr">
+      <c r="B2723" s="7" t="inlineStr">
         <is>
           <t>#07 HIGIENE PESSOAL - ESMALTES</t>
         </is>
       </c>
-      <c r="C2723" s="9" t="inlineStr">
+      <c r="C2723" s="7" t="inlineStr">
         <is>
           <t>ESMALTE RISQUE 8ML VIVENDO DA MINHA ARTE</t>
         </is>
       </c>
-      <c r="D2723" s="9" t="inlineStr">
+      <c r="D2723" s="7" t="inlineStr">
         <is>
           <t>ESMALTE RISQUE 8ML VIVENDO DA MINHA ARTE</t>
         </is>
@@ -55397,40 +55411,40 @@
       </c>
     </row>
     <row r="2744">
-      <c r="A2744" s="9" t="n">
+      <c r="A2744" s="7" t="n">
         <v>256740</v>
       </c>
-      <c r="B2744" s="9" t="inlineStr">
+      <c r="B2744" s="7" t="inlineStr">
         <is>
           <t>#07 HIGIENE PESSOAL - HIGIENE</t>
         </is>
       </c>
-      <c r="C2744" s="9" t="inlineStr">
+      <c r="C2744" s="7" t="inlineStr">
         <is>
           <t>HASTES FLEX COTTONBABY C/150 POTE</t>
         </is>
       </c>
-      <c r="D2744" s="9" t="inlineStr">
+      <c r="D2744" s="7" t="inlineStr">
         <is>
           <t>HASTES FLEXIVEIS COTTONBABY POTE 150UN</t>
         </is>
       </c>
     </row>
     <row r="2745">
-      <c r="A2745" s="9" t="n">
+      <c r="A2745" s="7" t="n">
         <v>182485</v>
       </c>
-      <c r="B2745" s="9" t="inlineStr">
+      <c r="B2745" s="7" t="inlineStr">
         <is>
           <t>#07 HIGIENE PESSOAL - HIGIENE</t>
         </is>
       </c>
-      <c r="C2745" s="9" t="inlineStr">
+      <c r="C2745" s="7" t="inlineStr">
         <is>
           <t>HASTES FLEX COTTON BABY POT L 150 PG100</t>
         </is>
       </c>
-      <c r="D2745" s="9" t="inlineStr">
+      <c r="D2745" s="7" t="inlineStr">
         <is>
           <t>HASTES FLEXIVEIS COTTONBABY POTE PROMOCIONAL 150UN</t>
         </is>
@@ -55477,20 +55491,20 @@
       </c>
     </row>
     <row r="2748">
-      <c r="A2748" s="9" t="n">
+      <c r="A2748" s="7" t="n">
         <v>299853</v>
       </c>
-      <c r="B2748" s="9" t="inlineStr">
+      <c r="B2748" s="7" t="inlineStr">
         <is>
           <t>#07 HIGIENE PESSOAL - HIGIENE BUCAL</t>
         </is>
       </c>
-      <c r="C2748" s="9" t="inlineStr">
+      <c r="C2748" s="7" t="inlineStr">
         <is>
           <t>ANTISSEPTICO BUCAL CEPACOL 250ML CITRUS</t>
         </is>
       </c>
-      <c r="D2748" s="9" t="inlineStr">
+      <c r="D2748" s="7" t="inlineStr">
         <is>
           <t>ANTISSEPTICO BUCAL CEPACOL 250ML CITRUS</t>
         </is>
@@ -55517,20 +55531,20 @@
       </c>
     </row>
     <row r="2750">
-      <c r="A2750" s="9" t="n">
+      <c r="A2750" s="7" t="n">
         <v>297554</v>
       </c>
-      <c r="B2750" s="9" t="inlineStr">
+      <c r="B2750" s="7" t="inlineStr">
         <is>
           <t>#07 HIGIENE PESSOAL - HIGIENE BUCAL</t>
         </is>
       </c>
-      <c r="C2750" s="9" t="inlineStr">
+      <c r="C2750" s="7" t="inlineStr">
         <is>
           <t>ANTISSEPTICO BUCAL CEPACOL 250ML MENTA ICE</t>
         </is>
       </c>
-      <c r="D2750" s="9" t="inlineStr">
+      <c r="D2750" s="7" t="inlineStr">
         <is>
           <t>ANTISSEPTICO BUCAL CEPACOL 250ML MENTA ICE</t>
         </is>
@@ -56297,40 +56311,40 @@
       </c>
     </row>
     <row r="2789">
-      <c r="A2789" s="9" t="n">
+      <c r="A2789" s="7" t="n">
         <v>303529</v>
       </c>
-      <c r="B2789" s="9" t="inlineStr">
+      <c r="B2789" s="7" t="inlineStr">
         <is>
           <t>#07 HIGIENE PESSOAL - INTIMA</t>
         </is>
       </c>
-      <c r="C2789" s="9" t="inlineStr">
+      <c r="C2789" s="7" t="inlineStr">
         <is>
           <t>HIDRATANTE MONANGE 400ML FIRM Q10 PELE EXTRA SECA</t>
         </is>
       </c>
-      <c r="D2789" s="9" t="inlineStr">
+      <c r="D2789" s="7" t="inlineStr">
         <is>
           <t>CREME HIDRATANTE MONANGE 400ML Q10 FIRMADOR PELE EXTRA SECA</t>
         </is>
       </c>
     </row>
     <row r="2790">
-      <c r="A2790" s="9" t="n">
+      <c r="A2790" s="7" t="n">
         <v>293647</v>
       </c>
-      <c r="B2790" s="9" t="inlineStr">
+      <c r="B2790" s="7" t="inlineStr">
         <is>
           <t>#07 HIGIENE PESSOAL - INTIMA</t>
         </is>
       </c>
-      <c r="C2790" s="9" t="inlineStr">
+      <c r="C2790" s="7" t="inlineStr">
         <is>
           <t>CREME HIDRATANTE MONANGE 50GR OLEO DE AB</t>
         </is>
       </c>
-      <c r="D2790" s="9" t="inlineStr">
+      <c r="D2790" s="7" t="inlineStr">
         <is>
           <t>CREME HIDRATANTE MONANGE 50G OLEO DE ABACATE</t>
         </is>
@@ -57457,20 +57471,20 @@
       </c>
     </row>
     <row r="2847">
-      <c r="A2847" s="19" t="n">
+      <c r="A2847" s="13" t="n">
         <v>219705</v>
       </c>
-      <c r="B2847" s="19" t="inlineStr">
+      <c r="B2847" s="13" t="inlineStr">
         <is>
           <t>#07 HIGIENE PESSOAL - PAPEL HIGIENICO</t>
         </is>
       </c>
-      <c r="C2847" s="19" t="inlineStr">
+      <c r="C2847" s="13" t="inlineStr">
         <is>
           <t>PAPEL HIG MIMMO 30MTS LEV12 PAG11</t>
         </is>
       </c>
-      <c r="D2847" s="19" t="inlineStr">
+      <c r="D2847" s="13" t="inlineStr">
         <is>
           <t>PAPEL HIGIENICO MIMMO 12 X 30M PROMOCIONAL NEUTRO</t>
         </is>
@@ -57577,20 +57591,20 @@
       </c>
     </row>
     <row r="2853">
-      <c r="A2853" t="n">
+      <c r="A2853" s="21" t="n">
         <v>346964</v>
       </c>
-      <c r="B2853" t="inlineStr">
+      <c r="B2853" s="21" t="inlineStr">
         <is>
           <t>#07 HIGIENE PESSOAL - PAPEL HIGIENICO</t>
         </is>
       </c>
-      <c r="C2853" t="inlineStr">
+      <c r="C2853" s="21" t="inlineStr">
         <is>
           <t>PAPEL HIG NOBLE FD 20M</t>
         </is>
       </c>
-      <c r="D2853" t="inlineStr">
+      <c r="D2853" s="21" t="inlineStr">
         <is>
           <t>PAPEL HIGIENICO NOBLE 12 X 20M FOLHA DUPLA</t>
         </is>
@@ -58897,20 +58911,20 @@
       </c>
     </row>
     <row r="2919">
-      <c r="A2919" s="9" t="n">
+      <c r="A2919" s="7" t="n">
         <v>289231</v>
       </c>
-      <c r="B2919" s="9" t="inlineStr">
+      <c r="B2919" s="7" t="inlineStr">
         <is>
           <t>#07 HIGIENE PESSOAL - SABONETE</t>
         </is>
       </c>
-      <c r="C2919" s="9" t="inlineStr">
+      <c r="C2919" s="7" t="inlineStr">
         <is>
           <t>SABONETE LIQUIDO INFANTIL T XUXINHA 400ML SONO TRANQUILO</t>
         </is>
       </c>
-      <c r="D2919" s="9" t="inlineStr">
+      <c r="D2919" s="7" t="inlineStr">
         <is>
           <t>SABONETE LIQUIDO INFANTIL TURMA DA XUXINHA 400ML SONO TRANQUILO</t>
         </is>
@@ -62177,27 +62191,107 @@
       </c>
     </row>
     <row r="3083">
-      <c r="A3083" s="20" t="n">
+      <c r="A3083" s="13" t="n">
         <v>343857</v>
       </c>
-      <c r="B3083" s="14" t="inlineStr">
-        <is>
-          <t>SEÇÃO NÃO ESPECIFICADA</t>
-        </is>
-      </c>
-      <c r="C3083" s="20" t="inlineStr">
+      <c r="B3083" s="13" t="inlineStr">
+        <is>
+          <t>#05 BEBIDA - DESTILADOS</t>
+        </is>
+      </c>
+      <c r="C3083" s="13" t="inlineStr">
         <is>
           <t>RUM BACARDI 700ML C ORO</t>
         </is>
       </c>
-      <c r="D3083" s="20" t="inlineStr">
-        <is>
-          <t>RUM BACARDI 700ML C ORO</t>
+      <c r="D3083" s="13" t="inlineStr">
+        <is>
+          <t>RUM BACARDI 700ML CARTA ORO</t>
+        </is>
+      </c>
+    </row>
+    <row r="3084">
+      <c r="A3084" s="18" t="n">
+        <v>231729</v>
+      </c>
+      <c r="B3084" s="18" t="inlineStr">
+        <is>
+          <t>#03 AÇOUGUE - #06 EMBUTIDOS E FRIOS</t>
+        </is>
+      </c>
+      <c r="C3084" s="18" t="inlineStr">
+        <is>
+          <t>HAMBURGUER  56GR SADIA AVES E BOVINO</t>
+        </is>
+      </c>
+      <c r="D3084" s="18" t="inlineStr">
+        <is>
+          <t>HAMBURGUER SADIA 56G AVES E BOVINO</t>
+        </is>
+      </c>
+    </row>
+    <row r="3085">
+      <c r="A3085" s="21" t="n">
+        <v>337322</v>
+      </c>
+      <c r="B3085" s="21" t="inlineStr">
+        <is>
+          <t>#02 MERCEARIA - CONDIMENTOS E TEMPEROS</t>
+        </is>
+      </c>
+      <c r="C3085" s="21" t="inlineStr">
+        <is>
+          <t>AZEITONA VERDE GUNE 200GR S/ CAROCO</t>
+        </is>
+      </c>
+      <c r="D3085" s="21" t="inlineStr">
+        <is>
+          <t>AZEITONAS VERDES GUNE 200G SEM CAROÇO</t>
+        </is>
+      </c>
+    </row>
+    <row r="3086">
+      <c r="A3086" s="21" t="n">
+        <v>135408</v>
+      </c>
+      <c r="B3086" s="21" t="inlineStr">
+        <is>
+          <t>#02 MERCEARIA - CONDIMENTOS E TEMPEROS</t>
+        </is>
+      </c>
+      <c r="C3086" s="21" t="inlineStr">
+        <is>
+          <t>KETCHUP TRAD. QUERO 1,150KG</t>
+        </is>
+      </c>
+      <c r="D3086" s="21" t="inlineStr">
+        <is>
+          <t>KETCHUP QUERO QUERO 1,150KG TRADICIONAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="3087">
+      <c r="A3087" s="21" t="n">
+        <v>111530</v>
+      </c>
+      <c r="B3087" s="21" t="inlineStr">
+        <is>
+          <t>#02 MERCEARIA - LATICÍNIOS - LEITE</t>
+        </is>
+      </c>
+      <c r="C3087" s="21" t="inlineStr">
+        <is>
+          <t>LEITE TP TRIANGULO 1 LT INTEGRAL</t>
+        </is>
+      </c>
+      <c r="D3087" s="21" t="inlineStr">
+        <is>
+          <t>LEITE LONGA VIDA TRIANGULO 1L INTEGRAL</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D3083">
+  <autoFilter ref="A1:D3087">
     <sortState ref="A2:D3082">
       <sortCondition ref="B1:B3082"/>
     </sortState>

--- a/produtos_cadastrados.xlsx
+++ b/produtos_cadastrados.xlsx
@@ -9,7 +9,7 @@
     <sheet name="Produtos" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Produtos'!$A$1:$D$3087</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Produtos'!$A$1:$D$3100</definedName>
   </definedNames>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="13">
+  <fonts count="14">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -73,18 +73,23 @@
     </font>
     <font>
       <name val="Calibri"/>
+      <color rgb="FF000000"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
       <b val="1"/>
       <color rgb="FF9C0006"/>
       <sz val="11"/>
     </font>
     <font>
+      <b val="1"/>
+      <color rgb="009C0006"/>
+    </font>
+    <font>
       <name val="Calibri"/>
       <color rgb="00000000"/>
       <sz val="11"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <color rgb="009C0006"/>
     </font>
   </fonts>
   <fills count="6">
@@ -146,7 +151,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
@@ -158,22 +163,21 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="12" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -539,7 +543,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3087"/>
+  <dimension ref="A1:D3100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7.42578125" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -591,20 +595,20 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="21" t="n">
+      <c r="A3" s="13" t="n">
         <v>100038</v>
       </c>
-      <c r="B3" s="21" t="inlineStr">
+      <c r="B3" s="13" t="inlineStr">
         <is>
           <t>#01 MERCEARIA - #01 CEREAIS E GRÃOS</t>
         </is>
       </c>
-      <c r="C3" s="21" t="inlineStr">
+      <c r="C3" s="13" t="inlineStr">
         <is>
           <t>ARROZ BREJEIRO 5KG BRANCO TIPO 1</t>
         </is>
       </c>
-      <c r="D3" s="21" t="inlineStr">
+      <c r="D3" s="13" t="inlineStr">
         <is>
           <t>ARROZ BREJEIRO PCT 5KG TIPO 1 BRANCO</t>
         </is>
@@ -731,20 +735,20 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="21" t="n">
+      <c r="A10" s="13" t="n">
         <v>325990</v>
       </c>
-      <c r="B10" s="21" t="inlineStr">
+      <c r="B10" s="13" t="inlineStr">
         <is>
           <t>#01 MERCEARIA - #01 CEREAIS E GRÃOS</t>
         </is>
       </c>
-      <c r="C10" s="21" t="inlineStr">
+      <c r="C10" s="13" t="inlineStr">
         <is>
           <t>ARROZ BRANCO FLORA 5KG TIPO 1</t>
         </is>
       </c>
-      <c r="D10" s="21" t="inlineStr">
+      <c r="D10" s="13" t="inlineStr">
         <is>
           <t>ARROZ FLORA PCT 5KG TIPO 1 BRANCO</t>
         </is>
@@ -771,20 +775,20 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="13" t="n">
+      <c r="A12" s="9" t="n">
         <v>229173</v>
       </c>
-      <c r="B12" s="13" t="inlineStr">
+      <c r="B12" s="9" t="inlineStr">
         <is>
           <t>#01 MERCEARIA - #01 CEREAIS E GRÃOS</t>
         </is>
       </c>
-      <c r="C12" s="13" t="inlineStr">
+      <c r="C12" s="9" t="inlineStr">
         <is>
           <t>ARROZ TIPO 1 KIDELICIA BRANCO 5KG</t>
         </is>
       </c>
-      <c r="D12" s="13" t="inlineStr">
+      <c r="D12" s="9" t="inlineStr">
         <is>
           <t>ARROZ KIDELICIA PCT 5KG TIPO 1 BRANCO</t>
         </is>
@@ -911,20 +915,20 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="21" t="n">
+      <c r="A19" s="13" t="n">
         <v>225003</v>
       </c>
-      <c r="B19" s="21" t="inlineStr">
+      <c r="B19" s="13" t="inlineStr">
         <is>
           <t>#01 MERCEARIA - #01 CEREAIS E GRÃOS</t>
         </is>
       </c>
-      <c r="C19" s="21" t="inlineStr">
+      <c r="C19" s="13" t="inlineStr">
         <is>
           <t>ARROZ RAMPINELLI 5KG TIPO1</t>
         </is>
       </c>
-      <c r="D19" s="21" t="inlineStr">
+      <c r="D19" s="13" t="inlineStr">
         <is>
           <t>ARROZ RAMPINELLI PCT 5KG TIPO 1 BRANCO</t>
         </is>
@@ -1251,20 +1255,20 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="13" t="n">
+      <c r="A36" s="9" t="n">
         <v>279573</v>
       </c>
-      <c r="B36" s="13" t="inlineStr">
+      <c r="B36" s="9" t="inlineStr">
         <is>
           <t>#01 MERCEARIA - #02 FEIJÕES E LEGUMINOSAS</t>
         </is>
       </c>
-      <c r="C36" s="13" t="inlineStr">
+      <c r="C36" s="9" t="inlineStr">
         <is>
           <t>FEIJÃO DONA MARIA 1KG CARIOCA</t>
         </is>
       </c>
-      <c r="D36" s="13" t="inlineStr">
+      <c r="D36" s="9" t="inlineStr">
         <is>
           <t>FEIJÃO CARIOCA DONA MARIA 1KG</t>
         </is>
@@ -1291,20 +1295,20 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="21" t="n">
+      <c r="A38" s="13" t="n">
         <v>327443</v>
       </c>
-      <c r="B38" s="21" t="inlineStr">
+      <c r="B38" s="13" t="inlineStr">
         <is>
           <t>#01 MERCEARIA - #02 FEIJÕES E LEGUMINOSAS</t>
         </is>
       </c>
-      <c r="C38" s="21" t="inlineStr">
+      <c r="C38" s="13" t="inlineStr">
         <is>
           <t>FEIJAO KALDINHO 1KG CARIOCA</t>
         </is>
       </c>
-      <c r="D38" s="21" t="inlineStr">
+      <c r="D38" s="13" t="inlineStr">
         <is>
           <t>FEIJÃO CARIOCA KALDINHO 1KG</t>
         </is>
@@ -1791,20 +1795,20 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="21" t="n">
+      <c r="A63" s="13" t="n">
         <v>167128</v>
       </c>
-      <c r="B63" s="21" t="inlineStr">
+      <c r="B63" s="13" t="inlineStr">
         <is>
           <t>#01 MERCEARIA - #03 ÓLEOS E GORDURAS</t>
         </is>
       </c>
-      <c r="C63" s="21" t="inlineStr">
+      <c r="C63" s="13" t="inlineStr">
         <is>
           <t>ÓLEO SOJA REFINADO CONCORDIA 900ML</t>
         </is>
       </c>
-      <c r="D63" s="21" t="inlineStr">
+      <c r="D63" s="13" t="inlineStr">
         <is>
           <t>ÓLEO DE SOJA CONCORDIA 900ML</t>
         </is>
@@ -1991,20 +1995,20 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="21" t="n">
+      <c r="A73" s="13" t="n">
         <v>345404</v>
       </c>
-      <c r="B73" s="21" t="inlineStr">
+      <c r="B73" s="13" t="inlineStr">
         <is>
           <t>#01 MERCEARIA - #04 AÇÚCAR E ADOÇANTES</t>
         </is>
       </c>
-      <c r="C73" s="21" t="inlineStr">
+      <c r="C73" s="13" t="inlineStr">
         <is>
           <t>ACUCAR ECO ACUCAR 2KG CRISTAL</t>
         </is>
       </c>
-      <c r="D73" s="21" t="inlineStr">
+      <c r="D73" s="13" t="inlineStr">
         <is>
           <t>AÇUCAR ECOÇUCAR 2KG CRISTAL</t>
         </is>
@@ -2391,20 +2395,20 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="21" t="n">
+      <c r="A93" s="13" t="n">
         <v>255232</v>
       </c>
-      <c r="B93" s="21" t="inlineStr">
+      <c r="B93" s="13" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - ACHOCOLATADOS E CAFÉ</t>
         </is>
       </c>
-      <c r="C93" s="21" t="inlineStr">
+      <c r="C93" s="13" t="inlineStr">
         <is>
           <t>ACHOCOLATADO EM PÓ TODDY 750G</t>
         </is>
       </c>
-      <c r="D93" s="21" t="inlineStr">
+      <c r="D93" s="13" t="inlineStr">
         <is>
           <t>ACHOCOLATADO EM PÓ TODDY 750G</t>
         </is>
@@ -2571,20 +2575,20 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="21" t="n">
+      <c r="A102" s="13" t="n">
         <v>101137</v>
       </c>
-      <c r="B102" s="21" t="inlineStr">
+      <c r="B102" s="13" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - ACHOCOLATADOS E CAFÉ</t>
         </is>
       </c>
-      <c r="C102" s="21" t="inlineStr">
+      <c r="C102" s="13" t="inlineStr">
         <is>
           <t>CAFÉ MARATA 250GR A VACUO TRADIC</t>
         </is>
       </c>
-      <c r="D102" s="21" t="inlineStr">
+      <c r="D102" s="13" t="inlineStr">
         <is>
           <t>CAFÉ MARATA 250G TRADICIONAL</t>
         </is>
@@ -2651,40 +2655,40 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="13" t="n">
+      <c r="A106" s="9" t="n">
         <v>174298</v>
       </c>
-      <c r="B106" s="13" t="inlineStr">
+      <c r="B106" s="9" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - ACHOCOLATADOS E CAFÉ</t>
         </is>
       </c>
-      <c r="C106" s="13" t="inlineStr">
+      <c r="C106" s="9" t="inlineStr">
         <is>
           <t>CAFE MOIDO RANCHEIRO 250GR TRAD</t>
         </is>
       </c>
-      <c r="D106" s="13" t="inlineStr">
+      <c r="D106" s="9" t="inlineStr">
         <is>
           <t>CAFÉ RANCHEIRO 250G TRADICIONAL</t>
         </is>
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="21" t="n">
+      <c r="A107" s="13" t="n">
         <v>114037</v>
       </c>
-      <c r="B107" s="21" t="inlineStr">
+      <c r="B107" s="13" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - ACHOCOLATADOS E CAFÉ</t>
         </is>
       </c>
-      <c r="C107" s="21" t="inlineStr">
+      <c r="C107" s="13" t="inlineStr">
         <is>
           <t>CAFÉ SANTA CLARA 250GR CLASSICO</t>
         </is>
       </c>
-      <c r="D107" s="21" t="inlineStr">
+      <c r="D107" s="13" t="inlineStr">
         <is>
           <t>CAFÉ SANTA CLARA 250G CLASSICO</t>
         </is>
@@ -3071,20 +3075,20 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="13" t="n">
+      <c r="A127" s="9" t="n">
         <v>261728</v>
       </c>
-      <c r="B127" s="13" t="inlineStr">
+      <c r="B127" s="9" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - BISCOITOS E SALGADINHOS</t>
         </is>
       </c>
-      <c r="C127" s="13" t="inlineStr">
+      <c r="C127" s="9" t="inlineStr">
         <is>
           <t>BISCOITO FORTALEZA 350GR CREAM CRACKER</t>
         </is>
       </c>
-      <c r="D127" s="13" t="inlineStr">
+      <c r="D127" s="9" t="inlineStr">
         <is>
           <t>BISCOITO CREAM CRACKER FORTALEZA 350G</t>
         </is>
@@ -3111,20 +3115,20 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="21" t="n">
+      <c r="A129" s="13" t="n">
         <v>186826</v>
       </c>
-      <c r="B129" s="21" t="inlineStr">
+      <c r="B129" s="13" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - BISCOITOS E SALGADINHOS</t>
         </is>
       </c>
-      <c r="C129" s="21" t="inlineStr">
+      <c r="C129" s="13" t="inlineStr">
         <is>
           <t>BISCOITO CREAM CRACKER GALLO 360GR</t>
         </is>
       </c>
-      <c r="D129" s="21" t="inlineStr">
+      <c r="D129" s="13" t="inlineStr">
         <is>
           <t>BISCOITO CREAM CRACKER GALLO 360G</t>
         </is>
@@ -3711,20 +3715,20 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="13" t="n">
+      <c r="A159" s="9" t="n">
         <v>263612</v>
       </c>
-      <c r="B159" s="13" t="inlineStr">
+      <c r="B159" s="9" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - BISCOITOS E SALGADINHOS</t>
         </is>
       </c>
-      <c r="C159" s="13" t="inlineStr">
+      <c r="C159" s="9" t="inlineStr">
         <is>
           <t>BISCOITO VITARELLA 350GR MAIZENA CHOCOLATE</t>
         </is>
       </c>
-      <c r="D159" s="13" t="inlineStr">
+      <c r="D159" s="9" t="inlineStr">
         <is>
           <t>BISCOITO MAISENA VITARELLA 350G CHOCOLATE</t>
         </is>
@@ -4351,20 +4355,20 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="13" t="n">
+      <c r="A191" s="9" t="n">
         <v>286197</v>
       </c>
-      <c r="B191" s="13" t="inlineStr">
+      <c r="B191" s="9" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - BISCOITOS E SALGADINHOS</t>
         </is>
       </c>
-      <c r="C191" s="13" t="inlineStr">
+      <c r="C191" s="9" t="inlineStr">
         <is>
           <t>BISCOITO MABEL 600GR ROSCA COCO</t>
         </is>
       </c>
-      <c r="D191" s="13" t="inlineStr">
+      <c r="D191" s="9" t="inlineStr">
         <is>
           <t>BISCOITO ROSQUINHA MABEL 600G COCO</t>
         </is>
@@ -4411,20 +4415,20 @@
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="21" t="n">
+      <c r="A194" s="13" t="n">
         <v>257157</v>
       </c>
-      <c r="B194" s="21" t="inlineStr">
+      <c r="B194" s="13" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - BISCOITOS E SALGADINHOS</t>
         </is>
       </c>
-      <c r="C194" s="21" t="inlineStr">
+      <c r="C194" s="13" t="inlineStr">
         <is>
           <t>ROSCA MICOS DE COCO 600G</t>
         </is>
       </c>
-      <c r="D194" s="21" t="inlineStr">
+      <c r="D194" s="13" t="inlineStr">
         <is>
           <t>BISCOITO ROSQUINHA MICOS 600G COCO</t>
         </is>
@@ -5631,20 +5635,20 @@
       </c>
     </row>
     <row r="255">
-      <c r="A255" s="21" t="n">
+      <c r="A255" s="13" t="n">
         <v>341362</v>
       </c>
-      <c r="B255" s="21" t="inlineStr">
+      <c r="B255" s="13" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - CHOCOLATES E DOCES</t>
         </is>
       </c>
-      <c r="C255" s="21" t="inlineStr">
+      <c r="C255" s="13" t="inlineStr">
         <is>
           <t>BOMBONS GAROTO 220G SORTIDOS CAIXA</t>
         </is>
       </c>
-      <c r="D255" s="21" t="inlineStr">
+      <c r="D255" s="13" t="inlineStr">
         <is>
           <t>BOMBOM GAROTO CAIXA 220G SORTIDOS</t>
         </is>
@@ -6911,20 +6915,20 @@
       </c>
     </row>
     <row r="319">
-      <c r="A319" s="21" t="n">
+      <c r="A319" s="13" t="n">
         <v>132657</v>
       </c>
-      <c r="B319" s="21" t="inlineStr">
+      <c r="B319" s="13" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - CONDIMENTOS E TEMPEROS</t>
         </is>
       </c>
-      <c r="C319" s="21" t="inlineStr">
+      <c r="C319" s="13" t="inlineStr">
         <is>
           <t>AZEITE GALLO 500ML EXTRA VIRGEM</t>
         </is>
       </c>
-      <c r="D319" s="21" t="inlineStr">
+      <c r="D319" s="13" t="inlineStr">
         <is>
           <t>AZEITE DE OLIVA GALLO VIDRO 500ML EXTRA VIRGEM</t>
         </is>
@@ -7391,20 +7395,20 @@
       </c>
     </row>
     <row r="343">
-      <c r="A343" s="13" t="n">
+      <c r="A343" s="9" t="n">
         <v>190801</v>
       </c>
-      <c r="B343" s="13" t="inlineStr">
+      <c r="B343" s="9" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - CONDIMENTOS E TEMPEROS</t>
         </is>
       </c>
-      <c r="C343" s="13" t="inlineStr">
+      <c r="C343" s="9" t="inlineStr">
         <is>
           <t>AZEITONAS VERDES INTEIRAS MARATA SACHET</t>
         </is>
       </c>
-      <c r="D343" s="13" t="inlineStr">
+      <c r="D343" s="9" t="inlineStr">
         <is>
           <t>AZEITONAS VERDES MARATA SACHE 210G INTEIRAS</t>
         </is>
@@ -8171,20 +8175,20 @@
       </c>
     </row>
     <row r="382">
-      <c r="A382" s="21" t="n">
+      <c r="A382" s="13" t="n">
         <v>273714</v>
       </c>
-      <c r="B382" s="21" t="inlineStr">
+      <c r="B382" s="13" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - CONDIMENTOS E TEMPEROS</t>
         </is>
       </c>
-      <c r="C382" s="21" t="inlineStr">
+      <c r="C382" s="13" t="inlineStr">
         <is>
           <t>EXTRATO TOMATE ELEFANTE 300G POTE</t>
         </is>
       </c>
-      <c r="D382" s="21" t="inlineStr">
+      <c r="D382" s="13" t="inlineStr">
         <is>
           <t>EXTRATO DE TOMATE ELEFANTE POTE 300G</t>
         </is>
@@ -8831,20 +8835,20 @@
       </c>
     </row>
     <row r="415">
-      <c r="A415" s="21" t="n">
+      <c r="A415" s="13" t="n">
         <v>101728</v>
       </c>
-      <c r="B415" s="21" t="inlineStr">
+      <c r="B415" s="13" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - CONDIMENTOS E TEMPEROS</t>
         </is>
       </c>
-      <c r="C415" s="21" t="inlineStr">
+      <c r="C415" s="13" t="inlineStr">
         <is>
           <t>MAIONESE HELLMANNS 500GR TRADICIONAL</t>
         </is>
       </c>
-      <c r="D415" s="21" t="inlineStr">
+      <c r="D415" s="13" t="inlineStr">
         <is>
           <t>MAIONESE HELLMANNS 500G TRADICIONAL</t>
         </is>
@@ -9671,20 +9675,20 @@
       </c>
     </row>
     <row r="457">
-      <c r="A457" s="21" t="n">
+      <c r="A457" s="13" t="n">
         <v>321107</v>
       </c>
-      <c r="B457" s="21" t="inlineStr">
+      <c r="B457" s="13" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - CONDIMENTOS E TEMPEROS</t>
         </is>
       </c>
-      <c r="C457" s="21" t="inlineStr">
+      <c r="C457" s="13" t="inlineStr">
         <is>
           <t>MOLHO PRONTO QUERO 240GR TRADICIONAL SCH</t>
         </is>
       </c>
-      <c r="D457" s="21" t="inlineStr">
+      <c r="D457" s="13" t="inlineStr">
         <is>
           <t>MOLHO QUERO PRONTO SACHÊ 240G TRADICIONAL</t>
         </is>
@@ -10151,20 +10155,20 @@
       </c>
     </row>
     <row r="481">
-      <c r="A481" s="21" t="n">
+      <c r="A481" s="13" t="n">
         <v>100876</v>
       </c>
-      <c r="B481" s="21" t="inlineStr">
+      <c r="B481" s="13" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - CONDIMENTOS E TEMPEROS</t>
         </is>
       </c>
-      <c r="C481" s="21" t="inlineStr">
+      <c r="C481" s="13" t="inlineStr">
         <is>
           <t>TEMPERO ARISCO 1KG COMPLETO C/ PIMENTA</t>
         </is>
       </c>
-      <c r="D481" s="21" t="inlineStr">
+      <c r="D481" s="13" t="inlineStr">
         <is>
           <t>TEMPERO COMPLETO ARISCO 1KG COM PIMENTA</t>
         </is>
@@ -11111,20 +11115,20 @@
       </c>
     </row>
     <row r="529">
-      <c r="A529" s="21" t="n">
+      <c r="A529" s="13" t="n">
         <v>141367</v>
       </c>
-      <c r="B529" s="21" t="inlineStr">
+      <c r="B529" s="13" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - CONDIMENTOS E TEMPEROS</t>
         </is>
       </c>
-      <c r="C529" s="21" t="inlineStr">
+      <c r="C529" s="13" t="inlineStr">
         <is>
           <t>VINAGRE ALCOOL MARATA 750ML COLORIDO</t>
         </is>
       </c>
-      <c r="D529" s="21" t="inlineStr">
+      <c r="D529" s="13" t="inlineStr">
         <is>
           <t>VINAGRE MARATÁ 750ML ALCOOL COLORIDO</t>
         </is>
@@ -11271,20 +11275,20 @@
       </c>
     </row>
     <row r="537">
-      <c r="A537" s="18" t="n">
+      <c r="A537" s="17" t="n">
         <v>230387</v>
       </c>
-      <c r="B537" s="18" t="inlineStr">
+      <c r="B537" s="17" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - CONGELADOS - BATATAS</t>
         </is>
       </c>
-      <c r="C537" s="18" t="inlineStr">
+      <c r="C537" s="17" t="inlineStr">
         <is>
           <t>BATATAS PRE-FRITAS CONG BOUA 1,05 KG</t>
         </is>
       </c>
-      <c r="D537" s="18" t="inlineStr">
+      <c r="D537" s="17" t="inlineStr">
         <is>
           <t>BATATAS CONGELADAS BOUA PCT 1,05KG PRE-FRITAS</t>
         </is>
@@ -11491,20 +11495,20 @@
       </c>
     </row>
     <row r="548">
-      <c r="A548" s="13" t="n">
+      <c r="A548" s="9" t="n">
         <v>227503</v>
       </c>
-      <c r="B548" s="13" t="inlineStr">
+      <c r="B548" s="9" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - CONGELADOS - BATATAS</t>
         </is>
       </c>
-      <c r="C548" s="13" t="inlineStr">
+      <c r="C548" s="9" t="inlineStr">
         <is>
           <t>BATATA PALITO PRE-FRITA CONG. SADIA PT 4</t>
         </is>
       </c>
-      <c r="D548" s="13" t="inlineStr">
+      <c r="D548" s="9" t="inlineStr">
         <is>
           <t>BATATAS CONGELADAS SADIA PCT 400G PALITO PRE-FRITA</t>
         </is>
@@ -12371,20 +12375,20 @@
       </c>
     </row>
     <row r="592">
-      <c r="A592" s="21" t="n">
+      <c r="A592" s="13" t="n">
         <v>130920</v>
       </c>
-      <c r="B592" s="21" t="inlineStr">
+      <c r="B592" s="13" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - CONSERVAS - HORTIFRUTI</t>
         </is>
       </c>
-      <c r="C592" s="21" t="inlineStr">
+      <c r="C592" s="13" t="inlineStr">
         <is>
           <t>MILHO VERDE FUGINI VAPOR LT 200GR</t>
         </is>
       </c>
-      <c r="D592" s="21" t="inlineStr">
+      <c r="D592" s="13" t="inlineStr">
         <is>
           <t>MILHO VERDE FUGINI LATA 200G VAPOR</t>
         </is>
@@ -12991,20 +12995,20 @@
       </c>
     </row>
     <row r="623">
-      <c r="A623" s="21" t="n">
+      <c r="A623" s="13" t="n">
         <v>100706</v>
       </c>
-      <c r="B623" s="21" t="inlineStr">
+      <c r="B623" s="13" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - CONSERVAS - SARDINHAS</t>
         </is>
       </c>
-      <c r="C623" s="21" t="inlineStr">
+      <c r="C623" s="13" t="inlineStr">
         <is>
           <t>SARDINHA COQUEIRO 125GR MOLHO DE TOMATE</t>
         </is>
       </c>
-      <c r="D623" s="21" t="inlineStr">
+      <c r="D623" s="13" t="inlineStr">
         <is>
           <t>SARDINHA COQUEIRO 125G MOLHO DE TOMATE</t>
         </is>
@@ -13031,20 +13035,20 @@
       </c>
     </row>
     <row r="625">
-      <c r="A625" s="21" t="n">
+      <c r="A625" s="13" t="n">
         <v>221089</v>
       </c>
-      <c r="B625" s="21" t="inlineStr">
+      <c r="B625" s="13" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - CONSERVAS - SARDINHAS</t>
         </is>
       </c>
-      <c r="C625" s="21" t="inlineStr">
+      <c r="C625" s="13" t="inlineStr">
         <is>
           <t>SARDINHA COQUEIRO ÓLEO 125G</t>
         </is>
       </c>
-      <c r="D625" s="21" t="inlineStr">
+      <c r="D625" s="13" t="inlineStr">
         <is>
           <t>SARDINHA COQUEIRO 125G ÓLEO</t>
         </is>
@@ -14291,20 +14295,20 @@
       </c>
     </row>
     <row r="688">
-      <c r="A688" s="21" t="n">
+      <c r="A688" s="13" t="n">
         <v>100027</v>
       </c>
-      <c r="B688" s="21" t="inlineStr">
+      <c r="B688" s="13" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - FARINHAS E DERIVADOS</t>
         </is>
       </c>
-      <c r="C688" s="21" t="inlineStr">
+      <c r="C688" s="13" t="inlineStr">
         <is>
           <t>FARINHA TRIGO ORQUIDEA 1KG SEM FERMENTO</t>
         </is>
       </c>
-      <c r="D688" s="21" t="inlineStr">
+      <c r="D688" s="13" t="inlineStr">
         <is>
           <t>FARINHA DE TRIGO ORQUIDEA 1KG SEM FERMENTO</t>
         </is>
@@ -14911,20 +14915,20 @@
       </c>
     </row>
     <row r="719">
-      <c r="A719" s="21" t="n">
+      <c r="A719" s="13" t="n">
         <v>100120</v>
       </c>
-      <c r="B719" s="21" t="inlineStr">
+      <c r="B719" s="13" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - FARINHAS E DERIVADOS</t>
         </is>
       </c>
-      <c r="C719" s="21" t="inlineStr">
+      <c r="C719" s="13" t="inlineStr">
         <is>
           <t>FLOCÃO DE MILHO BONOMILHO 500G</t>
         </is>
       </c>
-      <c r="D719" s="21" t="inlineStr">
+      <c r="D719" s="13" t="inlineStr">
         <is>
           <t>FLOCÃO DE MILHO BONOMILHO 500G</t>
         </is>
@@ -15331,20 +15335,20 @@
       </c>
     </row>
     <row r="740">
-      <c r="A740" s="21" t="n">
+      <c r="A740" s="13" t="n">
         <v>149121</v>
       </c>
-      <c r="B740" s="21" t="inlineStr">
+      <c r="B740" s="13" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - FARINHAS E DERIVADOS</t>
         </is>
       </c>
-      <c r="C740" s="21" t="inlineStr">
+      <c r="C740" s="13" t="inlineStr">
         <is>
           <t>MASSA P/ TAPIOCA AMAFIL 500G</t>
         </is>
       </c>
-      <c r="D740" s="21" t="inlineStr">
+      <c r="D740" s="13" t="inlineStr">
         <is>
           <t>MASSA PARA TAPIOCA AMAFIL 500G</t>
         </is>
@@ -16391,20 +16395,20 @@
       </c>
     </row>
     <row r="793">
-      <c r="A793" s="21" t="n">
+      <c r="A793" s="13" t="n">
         <v>128920</v>
       </c>
-      <c r="B793" s="21" t="inlineStr">
+      <c r="B793" s="13" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - FARINHAS E DERIVADOS</t>
         </is>
       </c>
-      <c r="C793" s="21" t="inlineStr">
+      <c r="C793" s="13" t="inlineStr">
         <is>
           <t>POLVILHO MATUTO 1KG DOCE</t>
         </is>
       </c>
-      <c r="D793" s="21" t="inlineStr">
+      <c r="D793" s="13" t="inlineStr">
         <is>
           <t>POLVILHO MATUTO 1KG DOCE</t>
         </is>
@@ -16631,20 +16635,20 @@
       </c>
     </row>
     <row r="805">
-      <c r="A805" s="13" t="n">
+      <c r="A805" s="9" t="n">
         <v>284048</v>
       </c>
-      <c r="B805" s="13" t="inlineStr">
+      <c r="B805" s="9" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - GORDURAS E MARGARINAS</t>
         </is>
       </c>
-      <c r="C805" s="13" t="inlineStr">
+      <c r="C805" s="9" t="inlineStr">
         <is>
           <t>MANTEIGA DE COCO PUROCOCO OHANA 200G</t>
         </is>
       </c>
-      <c r="D805" s="13" t="inlineStr">
+      <c r="D805" s="9" t="inlineStr">
         <is>
           <t>MANTEIGA DE COCO PUROCOCO OHANA 200G</t>
         </is>
@@ -16791,20 +16795,20 @@
       </c>
     </row>
     <row r="813">
-      <c r="A813" s="18" t="n">
+      <c r="A813" s="17" t="n">
         <v>336816</v>
       </c>
-      <c r="B813" s="18" t="inlineStr">
+      <c r="B813" s="17" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - GORDURAS E MARGARINAS</t>
         </is>
       </c>
-      <c r="C813" s="18" t="inlineStr">
+      <c r="C813" s="17" t="inlineStr">
         <is>
           <t>MANTEIGA QUEIJOLEITE 200GR DE PRIMEIRA Q</t>
         </is>
       </c>
-      <c r="D813" s="18" t="inlineStr">
+      <c r="D813" s="17" t="inlineStr">
         <is>
           <t>MANTEIGA QUEIJOLEITE 200G PRIMEIRA QUALIDADE</t>
         </is>
@@ -16911,20 +16915,20 @@
       </c>
     </row>
     <row r="819">
-      <c r="A819" s="18" t="n">
+      <c r="A819" s="17" t="n">
         <v>276943</v>
       </c>
-      <c r="B819" s="18" t="inlineStr">
+      <c r="B819" s="17" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - GORDURAS E MARGARINAS</t>
         </is>
       </c>
-      <c r="C819" s="18" t="inlineStr">
+      <c r="C819" s="17" t="inlineStr">
         <is>
           <t>MARGARINA DELICIA 1KG C CREME DE LEITE</t>
         </is>
       </c>
-      <c r="D819" s="18" t="inlineStr">
+      <c r="D819" s="17" t="inlineStr">
         <is>
           <t>MARGARINA DELICIA 1KG COM CREME DE LEITE</t>
         </is>
@@ -17031,20 +17035,20 @@
       </c>
     </row>
     <row r="825">
-      <c r="A825" s="13" t="n">
+      <c r="A825" s="9" t="n">
         <v>104651</v>
       </c>
-      <c r="B825" s="13" t="inlineStr">
+      <c r="B825" s="9" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - GORDURAS E MARGARINAS</t>
         </is>
       </c>
-      <c r="C825" s="13" t="inlineStr">
+      <c r="C825" s="9" t="inlineStr">
         <is>
           <t>MARGARINA DELINE C/SAL 500G</t>
         </is>
       </c>
-      <c r="D825" s="13" t="inlineStr">
+      <c r="D825" s="9" t="inlineStr">
         <is>
           <t>MARGARINA DELINE 500G COM SAL</t>
         </is>
@@ -17271,20 +17275,20 @@
       </c>
     </row>
     <row r="837">
-      <c r="A837" s="13" t="n">
+      <c r="A837" s="19" t="n">
         <v>182503</v>
       </c>
-      <c r="B837" s="13" t="inlineStr">
+      <c r="B837" s="19" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - GORDURAS E MARGARINAS</t>
         </is>
       </c>
-      <c r="C837" s="13" t="inlineStr">
+      <c r="C837" s="19" t="inlineStr">
         <is>
           <t>MARGARINA 77% C/ SAL VIGOR 250G SABOR MA</t>
         </is>
       </c>
-      <c r="D837" s="13" t="inlineStr">
+      <c r="D837" s="19" t="inlineStr">
         <is>
           <t>MARGARINA VIGOR 77% 250G COM SAL SABOR MANTEIGA</t>
         </is>
@@ -17631,40 +17635,40 @@
       </c>
     </row>
     <row r="855">
-      <c r="A855" s="18" t="n">
+      <c r="A855" s="20" t="n">
         <v>173935</v>
       </c>
-      <c r="B855" s="18" t="inlineStr">
+      <c r="B855" s="20" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - LATICÍNIOS - BEBIDAS LACTEAS</t>
         </is>
       </c>
-      <c r="C855" s="18" t="inlineStr">
+      <c r="C855" s="20" t="inlineStr">
         <is>
           <t>DANONINHO 320G MORANGO</t>
         </is>
       </c>
-      <c r="D855" s="18" t="inlineStr">
+      <c r="D855" s="20" t="inlineStr">
         <is>
           <t>DANONINHO 320G MORANGO</t>
         </is>
       </c>
     </row>
     <row r="856">
-      <c r="A856" s="18" t="n">
+      <c r="A856" s="20" t="n">
         <v>173606</v>
       </c>
-      <c r="B856" s="18" t="inlineStr">
+      <c r="B856" s="20" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - LATICÍNIOS - BEBIDAS LACTEAS</t>
         </is>
       </c>
-      <c r="C856" s="18" t="inlineStr">
+      <c r="C856" s="20" t="inlineStr">
         <is>
           <t>DANONINHO 320G MULTIFRUTAS</t>
         </is>
       </c>
-      <c r="D856" s="18" t="inlineStr">
+      <c r="D856" s="20" t="inlineStr">
         <is>
           <t>DANONINHO 320G MULTIFRUTAS</t>
         </is>
@@ -18251,40 +18255,40 @@
       </c>
     </row>
     <row r="886">
-      <c r="A886" s="13" t="n">
+      <c r="A886" s="9" t="n">
         <v>101063</v>
       </c>
-      <c r="B886" s="13" t="inlineStr">
+      <c r="B886" s="9" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - LATICÍNIOS - DERIVADOS LACTEOS</t>
         </is>
       </c>
-      <c r="C886" s="13" t="inlineStr">
+      <c r="C886" s="9" t="inlineStr">
         <is>
           <t>CREME LEITE PIRACANJUBA 200GR UHT</t>
         </is>
       </c>
-      <c r="D886" s="13" t="inlineStr">
+      <c r="D886" s="9" t="inlineStr">
         <is>
           <t>CREME DE LEITE PIRACANJUBA 200G</t>
         </is>
       </c>
     </row>
     <row r="887">
-      <c r="A887" s="21" t="n">
+      <c r="A887" s="13" t="n">
         <v>193295</v>
       </c>
-      <c r="B887" s="21" t="inlineStr">
+      <c r="B887" s="13" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - LATICÍNIOS - DERIVADOS LACTEOS</t>
         </is>
       </c>
-      <c r="C887" s="21" t="inlineStr">
+      <c r="C887" s="13" t="inlineStr">
         <is>
           <t>CREME DE LEITE TRIANGULO 200GR 17%GORDUR</t>
         </is>
       </c>
-      <c r="D887" s="21" t="inlineStr">
+      <c r="D887" s="13" t="inlineStr">
         <is>
           <t>CREME DE LEITE TRIANGULO 200G 17% GORDURA</t>
         </is>
@@ -18511,40 +18515,40 @@
       </c>
     </row>
     <row r="899">
-      <c r="A899" s="13" t="n">
+      <c r="A899" s="9" t="n">
         <v>101083</v>
       </c>
-      <c r="B899" s="13" t="inlineStr">
+      <c r="B899" s="9" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - LATICÍNIOS - DERIVADOS LACTEOS</t>
         </is>
       </c>
-      <c r="C899" s="13" t="inlineStr">
+      <c r="C899" s="9" t="inlineStr">
         <is>
           <t>LEITE CONDENSADO PIRACANJUBA 395GR TP</t>
         </is>
       </c>
-      <c r="D899" s="13" t="inlineStr">
+      <c r="D899" s="9" t="inlineStr">
         <is>
           <t>LEITE CONDENSADO PIRACANJUBA 395G</t>
         </is>
       </c>
     </row>
     <row r="900">
-      <c r="A900" s="21" t="n">
+      <c r="A900" s="13" t="n">
         <v>220451</v>
       </c>
-      <c r="B900" s="21" t="inlineStr">
+      <c r="B900" s="13" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - LATICÍNIOS - DERIVADOS LACTEOS</t>
         </is>
       </c>
-      <c r="C900" s="21" t="inlineStr">
+      <c r="C900" s="13" t="inlineStr">
         <is>
           <t>LEITE COND. TRIANGULO 395G TP SEMI</t>
         </is>
       </c>
-      <c r="D900" s="21" t="inlineStr">
+      <c r="D900" s="13" t="inlineStr">
         <is>
           <t>LEITE CONDENSADO TRIANGULO 395G SEMIDESNATADO</t>
         </is>
@@ -18911,40 +18915,40 @@
       </c>
     </row>
     <row r="919">
-      <c r="A919" s="13" t="n">
+      <c r="A919" s="9" t="n">
         <v>108252</v>
       </c>
-      <c r="B919" s="13" t="inlineStr">
+      <c r="B919" s="9" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - LATICÍNIOS - LEITE</t>
         </is>
       </c>
-      <c r="C919" s="13" t="inlineStr">
+      <c r="C919" s="9" t="inlineStr">
         <is>
           <t>LEITE PIRACANJUBA TP 1L EDGE DESNATADO</t>
         </is>
       </c>
-      <c r="D919" s="13" t="inlineStr">
+      <c r="D919" s="9" t="inlineStr">
         <is>
           <t>LEITE LONGA VIDA PIRACANJUBA 1L EDGE DESNATADO</t>
         </is>
       </c>
     </row>
     <row r="920">
-      <c r="A920" s="5" t="n">
+      <c r="A920" s="13" t="n">
         <v>101113</v>
       </c>
-      <c r="B920" s="5" t="inlineStr">
+      <c r="B920" s="13" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - LATICÍNIOS - LEITE</t>
         </is>
       </c>
-      <c r="C920" s="5" t="inlineStr">
+      <c r="C920" s="13" t="inlineStr">
         <is>
           <t>LEITE PIRACANJUBA UHT 1L EDGE INTEGRAL</t>
         </is>
       </c>
-      <c r="D920" s="5" t="inlineStr">
+      <c r="D920" s="13" t="inlineStr">
         <is>
           <t>LEITE LONGA VIDA PIRACANJUBA 1L INTEGRAL</t>
         </is>
@@ -19031,20 +19035,20 @@
       </c>
     </row>
     <row r="925">
-      <c r="A925" s="21" t="n">
+      <c r="A925" s="13" t="n">
         <v>106922</v>
       </c>
-      <c r="B925" s="21" t="inlineStr">
+      <c r="B925" s="13" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - LATICÍNIOS - LEITE EM PÓ</t>
         </is>
       </c>
-      <c r="C925" s="21" t="inlineStr">
+      <c r="C925" s="13" t="inlineStr">
         <is>
           <t>LEITE EM PÓ CCGL INTEGRAL 1KG</t>
         </is>
       </c>
-      <c r="D925" s="21" t="inlineStr">
+      <c r="D925" s="13" t="inlineStr">
         <is>
           <t>LEITE EM PÓ CCGL 1KG INTEGRAL</t>
         </is>
@@ -19151,20 +19155,20 @@
       </c>
     </row>
     <row r="931">
-      <c r="A931" s="21" t="n">
+      <c r="A931" s="13" t="n">
         <v>307145</v>
       </c>
-      <c r="B931" s="21" t="inlineStr">
+      <c r="B931" s="13" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - LATICÍNIOS - LEITE EM PÓ</t>
         </is>
       </c>
-      <c r="C931" s="21" t="inlineStr">
+      <c r="C931" s="13" t="inlineStr">
         <is>
           <t>LEITE EM PÓ NINHO 380GR INTEGRAL INSTANTANE</t>
         </is>
       </c>
-      <c r="D931" s="21" t="inlineStr">
+      <c r="D931" s="13" t="inlineStr">
         <is>
           <t>LEITE EM PÓ NINHO LATA 380G INTEGRAL INSTANTANEO</t>
         </is>
@@ -19511,20 +19515,20 @@
       </c>
     </row>
     <row r="949">
-      <c r="A949" s="18" t="n">
+      <c r="A949" s="17" t="n">
         <v>158733</v>
       </c>
-      <c r="B949" s="18" t="inlineStr">
+      <c r="B949" s="17" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - LATICÍNIOS - QUEIJO</t>
         </is>
       </c>
-      <c r="C949" s="18" t="inlineStr">
+      <c r="C949" s="17" t="inlineStr">
         <is>
           <t>QUEIJO MUSSARELA PIRAC FATIADO 150GR</t>
         </is>
       </c>
-      <c r="D949" s="18" t="inlineStr">
+      <c r="D949" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">QUEIJO MUSSARELA PIRACANJUBA 150G FATIADO </t>
         </is>
@@ -19971,40 +19975,40 @@
       </c>
     </row>
     <row r="972">
-      <c r="A972" s="18" t="n">
+      <c r="A972" s="17" t="n">
         <v>104770</v>
       </c>
-      <c r="B972" s="18" t="inlineStr">
+      <c r="B972" s="17" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - LATICÍNIOS - QUEIJO</t>
         </is>
       </c>
-      <c r="C972" s="18" t="inlineStr">
+      <c r="C972" s="17" t="inlineStr">
         <is>
           <t>REQUEIJAO CREM TIROLEZ 200GR</t>
         </is>
       </c>
-      <c r="D972" s="18" t="inlineStr">
+      <c r="D972" s="17" t="inlineStr">
         <is>
           <t>REQUEIJAO CREMOSO TIROLEZ 200G</t>
         </is>
       </c>
     </row>
     <row r="973">
-      <c r="A973" s="18" t="n">
+      <c r="A973" s="20" t="n">
         <v>133484</v>
       </c>
-      <c r="B973" s="18" t="inlineStr">
+      <c r="B973" s="20" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - LATICÍNIOS - QUEIJO</t>
         </is>
       </c>
-      <c r="C973" s="18" t="inlineStr">
+      <c r="C973" s="20" t="inlineStr">
         <is>
           <t>REQUEIJAO CREMOSO TIROLEZ LIGHT 200GR</t>
         </is>
       </c>
-      <c r="D973" s="18" t="inlineStr">
+      <c r="D973" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">REQUEIJÃO CREMOSO TIROLEZ 200G LIGHT </t>
         </is>
@@ -20091,20 +20095,20 @@
       </c>
     </row>
     <row r="978">
-      <c r="A978" s="13" t="n">
+      <c r="A978" s="9" t="n">
         <v>222973</v>
       </c>
-      <c r="B978" s="13" t="inlineStr">
+      <c r="B978" s="9" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - LATICÍNIOS - QUEIJO</t>
         </is>
       </c>
-      <c r="C978" s="13" t="inlineStr">
+      <c r="C978" s="9" t="inlineStr">
         <is>
           <t>QUEIJO MUSSARELA BOUA 150GR FATIADA</t>
         </is>
       </c>
-      <c r="D978" s="13" t="inlineStr">
+      <c r="D978" s="9" t="inlineStr">
         <is>
           <t>QUEIJO MUSSARELA BOUA 150G FATIADA</t>
         </is>
@@ -20251,20 +20255,20 @@
       </c>
     </row>
     <row r="986">
-      <c r="A986" s="21" t="n">
+      <c r="A986" s="13" t="n">
         <v>290255</v>
       </c>
-      <c r="B986" s="21" t="inlineStr">
+      <c r="B986" s="13" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - MASSAS</t>
         </is>
       </c>
-      <c r="C986" s="21" t="inlineStr">
+      <c r="C986" s="13" t="inlineStr">
         <is>
           <t>MACARRÃO CRISTAL 500GR SEMOLA ESPAGUETE</t>
         </is>
       </c>
-      <c r="D986" s="21" t="inlineStr">
+      <c r="D986" s="13" t="inlineStr">
         <is>
           <t>MACARRÃO CRISTAL SEMOLA ESPAGUETE 500G</t>
         </is>
@@ -20691,20 +20695,20 @@
       </c>
     </row>
     <row r="1008">
-      <c r="A1008" s="13" t="n">
+      <c r="A1008" s="9" t="n">
         <v>100642</v>
       </c>
-      <c r="B1008" s="13" t="inlineStr">
+      <c r="B1008" s="9" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - MASSAS</t>
         </is>
       </c>
-      <c r="C1008" s="13" t="inlineStr">
+      <c r="C1008" s="9" t="inlineStr">
         <is>
           <t>MAC PAULISTA ESPAGUETE 500GR SEMOLA</t>
         </is>
       </c>
-      <c r="D1008" s="13" t="inlineStr">
+      <c r="D1008" s="9" t="inlineStr">
         <is>
           <t>MACARRÃO PAULISTA ESPAGUETE SEMOLA 500G</t>
         </is>
@@ -20911,20 +20915,20 @@
       </c>
     </row>
     <row r="1019">
-      <c r="A1019" s="21" t="n">
+      <c r="A1019" s="13" t="n">
         <v>106791</v>
       </c>
-      <c r="B1019" s="21" t="inlineStr">
+      <c r="B1019" s="13" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - MASSAS</t>
         </is>
       </c>
-      <c r="C1019" s="21" t="inlineStr">
+      <c r="C1019" s="13" t="inlineStr">
         <is>
           <t>MAC PAULISTA PADRE NOSSO SEMOLA 500GR</t>
         </is>
       </c>
-      <c r="D1019" s="21" t="inlineStr">
+      <c r="D1019" s="13" t="inlineStr">
         <is>
           <t>MACARRÃO PAULISTA SEMOLA PADRE NOSSO 500G</t>
         </is>
@@ -23071,20 +23075,20 @@
       </c>
     </row>
     <row r="1127">
-      <c r="A1127" s="13" t="n">
+      <c r="A1127" s="19" t="n">
         <v>220822</v>
       </c>
-      <c r="B1127" s="13" t="inlineStr">
+      <c r="B1127" s="19" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - PÃES E BOLOS</t>
         </is>
       </c>
-      <c r="C1127" s="13" t="inlineStr">
+      <c r="C1127" s="19" t="inlineStr">
         <is>
           <t>PAO DE ALHO DI NAPOLI 350GR C/ QJO ERVAS</t>
         </is>
       </c>
-      <c r="D1127" s="13" t="inlineStr">
+      <c r="D1127" s="19" t="inlineStr">
         <is>
           <t>PÃO DE ALHO DI NAPOLI 350G QUEIJO E ERVAS</t>
         </is>
@@ -24251,20 +24255,20 @@
       </c>
     </row>
     <row r="1186">
-      <c r="A1186" s="21" t="n">
+      <c r="A1186" s="13" t="n">
         <v>105842</v>
       </c>
-      <c r="B1186" s="21" t="inlineStr">
+      <c r="B1186" s="13" t="inlineStr">
         <is>
           <t>#03 AÇOUGUE - #01 AVES</t>
         </is>
       </c>
-      <c r="C1186" s="21" t="inlineStr">
+      <c r="C1186" s="13" t="inlineStr">
         <is>
           <t>ASA FRANGO KG</t>
         </is>
       </c>
-      <c r="D1186" s="21" t="inlineStr">
+      <c r="D1186" s="13" t="inlineStr">
         <is>
           <t>ASA DE FRANGO KG</t>
         </is>
@@ -24311,20 +24315,20 @@
       </c>
     </row>
     <row r="1189">
-      <c r="A1189" s="18" t="n">
+      <c r="A1189" s="20" t="n">
         <v>224719</v>
       </c>
-      <c r="B1189" s="18" t="inlineStr">
+      <c r="B1189" s="20" t="inlineStr">
         <is>
           <t>#03 AÇOUGUE - #01 AVES</t>
         </is>
       </c>
-      <c r="C1189" s="18" t="inlineStr">
+      <c r="C1189" s="20" t="inlineStr">
         <is>
           <t>CORACAO BAND CONG BONASA 1KG</t>
         </is>
       </c>
-      <c r="D1189" s="18" t="inlineStr">
+      <c r="D1189" s="20" t="inlineStr">
         <is>
           <t>CORAÇÃO DE FRANGO BONASA BDJ 1KG</t>
         </is>
@@ -24391,20 +24395,20 @@
       </c>
     </row>
     <row r="1193">
-      <c r="A1193" t="n">
+      <c r="A1193" s="18" t="n">
         <v>345608</v>
       </c>
-      <c r="B1193" t="inlineStr">
+      <c r="B1193" s="18" t="inlineStr">
         <is>
           <t>#03 AÇOUGUE - #01 AVES</t>
         </is>
       </c>
-      <c r="C1193" t="inlineStr">
+      <c r="C1193" s="18" t="inlineStr">
         <is>
           <t>CORACAO PERU PERDIGAO 1KG CONGELADO PCT</t>
         </is>
       </c>
-      <c r="D1193" t="inlineStr">
+      <c r="D1193" s="18" t="inlineStr">
         <is>
           <t>CORAÇÃO DE PERU PERDIGÃO PCT 1KG</t>
         </is>
@@ -24431,20 +24435,20 @@
       </c>
     </row>
     <row r="1195">
-      <c r="A1195" s="21" t="n">
+      <c r="A1195" s="13" t="n">
         <v>105838</v>
       </c>
-      <c r="B1195" s="21" t="inlineStr">
+      <c r="B1195" s="13" t="inlineStr">
         <is>
           <t>#03 AÇOUGUE - #01 AVES</t>
         </is>
       </c>
-      <c r="C1195" s="21" t="inlineStr">
+      <c r="C1195" s="13" t="inlineStr">
         <is>
           <t>COXA/SOBRECOXA FRANGO KG</t>
         </is>
       </c>
-      <c r="D1195" s="21" t="inlineStr">
+      <c r="D1195" s="13" t="inlineStr">
         <is>
           <t>COXA COM SOBRECOXA DE FRANGO KG</t>
         </is>
@@ -24691,20 +24695,20 @@
       </c>
     </row>
     <row r="1208">
-      <c r="A1208" s="21" t="n">
+      <c r="A1208" s="13" t="n">
         <v>105840</v>
       </c>
-      <c r="B1208" s="21" t="inlineStr">
+      <c r="B1208" s="13" t="inlineStr">
         <is>
           <t>#03 AÇOUGUE - #01 AVES</t>
         </is>
       </c>
-      <c r="C1208" s="21" t="inlineStr">
+      <c r="C1208" s="13" t="inlineStr">
         <is>
           <t>COXINHA DA ASA FRANGO KG</t>
         </is>
       </c>
-      <c r="D1208" s="21" t="inlineStr">
+      <c r="D1208" s="13" t="inlineStr">
         <is>
           <t>COXINHA DA ASA DE FRANGO KG</t>
         </is>
@@ -24851,20 +24855,20 @@
       </c>
     </row>
     <row r="1216">
-      <c r="A1216" s="18" t="n">
+      <c r="A1216" s="20" t="n">
         <v>306504</v>
       </c>
-      <c r="B1216" s="18" t="inlineStr">
+      <c r="B1216" s="20" t="inlineStr">
         <is>
           <t>#03 AÇOUGUE - #01 AVES</t>
         </is>
       </c>
-      <c r="C1216" s="18" t="inlineStr">
+      <c r="C1216" s="20" t="inlineStr">
         <is>
           <t>FIGADO FRANGO CONGELADO PERDIGAO 1KG</t>
         </is>
       </c>
-      <c r="D1216" s="18" t="inlineStr">
+      <c r="D1216" s="20" t="inlineStr">
         <is>
           <t>FIGADO DE FRANGO PERDIGAO KG</t>
         </is>
@@ -24931,60 +24935,60 @@
       </c>
     </row>
     <row r="1220">
-      <c r="A1220" s="21" t="n">
+      <c r="A1220" s="13" t="n">
         <v>109597</v>
       </c>
-      <c r="B1220" s="21" t="inlineStr">
+      <c r="B1220" s="13" t="inlineStr">
         <is>
           <t>#03 AÇOUGUE - #01 AVES</t>
         </is>
       </c>
-      <c r="C1220" s="21" t="inlineStr">
+      <c r="C1220" s="13" t="inlineStr">
         <is>
           <t>FILE PEITO FRANGO KG</t>
         </is>
       </c>
-      <c r="D1220" s="21" t="inlineStr">
+      <c r="D1220" s="13" t="inlineStr">
         <is>
           <t>FILÉ DE PEITO DE FRANGO KG</t>
         </is>
       </c>
     </row>
     <row r="1221">
-      <c r="A1221" t="n">
+      <c r="A1221" s="18" t="n">
         <v>299804</v>
       </c>
-      <c r="B1221" t="inlineStr">
+      <c r="B1221" s="18" t="inlineStr">
         <is>
           <t>#03 AÇOUGUE - #01 AVES</t>
         </is>
       </c>
-      <c r="C1221" t="inlineStr">
+      <c r="C1221" s="18" t="inlineStr">
         <is>
           <t>FILE DE PEITO SADIA 1KG BANDEJA</t>
         </is>
       </c>
-      <c r="D1221" t="inlineStr">
+      <c r="D1221" s="18" t="inlineStr">
         <is>
           <t>FILE DE PEITO DE FRANGO SADIA BDJ 1KG</t>
         </is>
       </c>
     </row>
     <row r="1222">
-      <c r="A1222" s="13" t="n">
+      <c r="A1222" s="9" t="n">
         <v>108770</v>
       </c>
-      <c r="B1222" s="13" t="inlineStr">
+      <c r="B1222" s="9" t="inlineStr">
         <is>
           <t>#03 AÇOUGUE - #01 AVES</t>
         </is>
       </c>
-      <c r="C1222" s="13" t="inlineStr">
+      <c r="C1222" s="9" t="inlineStr">
         <is>
           <t>FILE PEITO S/OP FGO CONG BDJ SADIA 1KG</t>
         </is>
       </c>
-      <c r="D1222" s="13" t="inlineStr">
+      <c r="D1222" s="9" t="inlineStr">
         <is>
           <t>FILÉ DE PEITO DE FRANGO SADIA BDJ 1KG</t>
         </is>
@@ -25051,20 +25055,20 @@
       </c>
     </row>
     <row r="1226">
-      <c r="A1226" s="18" t="n">
+      <c r="A1226" s="17" t="n">
         <v>298784</v>
       </c>
-      <c r="B1226" s="18" t="inlineStr">
+      <c r="B1226" s="17" t="inlineStr">
         <is>
           <t>#03 AÇOUGUE - #01 AVES</t>
         </is>
       </c>
-      <c r="C1226" s="19" t="inlineStr">
+      <c r="C1226" s="16" t="inlineStr">
         <is>
           <t>FILE DE PEITO FRANGO SEARA 1KG BANDEJA</t>
         </is>
       </c>
-      <c r="D1226" s="18" t="inlineStr">
+      <c r="D1226" s="17" t="inlineStr">
         <is>
           <t>FILE DE PEITO DE FRANGO SEARA PCT 1KG</t>
         </is>
@@ -25091,20 +25095,20 @@
       </c>
     </row>
     <row r="1228">
-      <c r="A1228" s="13" t="n">
+      <c r="A1228" s="9" t="n">
         <v>108856</v>
       </c>
-      <c r="B1228" s="13" t="inlineStr">
+      <c r="B1228" s="9" t="inlineStr">
         <is>
           <t>#03 AÇOUGUE - #01 AVES</t>
         </is>
       </c>
-      <c r="C1228" s="13" t="inlineStr">
+      <c r="C1228" s="9" t="inlineStr">
         <is>
           <t>FILE PEITO SADIA PCT S/OPC 1KG PFFZP</t>
         </is>
       </c>
-      <c r="D1228" s="13" t="inlineStr">
+      <c r="D1228" s="9" t="inlineStr">
         <is>
           <t>FILE PEITO DE FRANGO SADIA PCT 1KG</t>
         </is>
@@ -25211,20 +25215,20 @@
       </c>
     </row>
     <row r="1234">
-      <c r="A1234" s="21" t="n">
+      <c r="A1234" s="13" t="n">
         <v>119927</v>
       </c>
-      <c r="B1234" s="21" t="inlineStr">
+      <c r="B1234" s="13" t="inlineStr">
         <is>
           <t>#03 AÇOUGUE - #01 AVES</t>
         </is>
       </c>
-      <c r="C1234" s="21" t="inlineStr">
+      <c r="C1234" s="13" t="inlineStr">
         <is>
           <t>FRANGO CONG AMERICANO KG</t>
         </is>
       </c>
-      <c r="D1234" s="21" t="inlineStr">
+      <c r="D1234" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">FRANGO AMERICANO KG CONGELADO </t>
         </is>
@@ -25331,40 +25335,40 @@
       </c>
     </row>
     <row r="1240">
-      <c r="A1240" t="n">
+      <c r="A1240" s="18" t="n">
         <v>105853</v>
       </c>
-      <c r="B1240" t="inlineStr">
+      <c r="B1240" s="18" t="inlineStr">
         <is>
           <t>#03 AÇOUGUE - #01 AVES</t>
         </is>
       </c>
-      <c r="C1240" t="inlineStr">
+      <c r="C1240" s="18" t="inlineStr">
         <is>
           <t>FRANGO CONG MARINGA KG</t>
         </is>
       </c>
-      <c r="D1240" t="inlineStr">
+      <c r="D1240" s="18" t="inlineStr">
         <is>
           <t>FRANGO MARINGA KG CONGELADO</t>
         </is>
       </c>
     </row>
     <row r="1241">
-      <c r="A1241" s="21" t="n">
+      <c r="A1241" s="13" t="n">
         <v>228289</v>
       </c>
-      <c r="B1241" s="21" t="inlineStr">
+      <c r="B1241" s="13" t="inlineStr">
         <is>
           <t>#03 AÇOUGUE - #01 AVES</t>
         </is>
       </c>
-      <c r="C1241" s="21" t="inlineStr">
+      <c r="C1241" s="13" t="inlineStr">
         <is>
           <t>FRANGO INTEIRO SADIA KG S/ MIUDOS TEMPER</t>
         </is>
       </c>
-      <c r="D1241" s="21" t="inlineStr">
+      <c r="D1241" s="13" t="inlineStr">
         <is>
           <t>FRANGO SADIA KG CONGELADO TEMPERADO SEM MIUDOS</t>
         </is>
@@ -25411,20 +25415,20 @@
       </c>
     </row>
     <row r="1244">
-      <c r="A1244" s="21" t="n">
+      <c r="A1244" s="13" t="n">
         <v>185934</v>
       </c>
-      <c r="B1244" s="21" t="inlineStr">
+      <c r="B1244" s="13" t="inlineStr">
         <is>
           <t>#03 AÇOUGUE - #01 AVES</t>
         </is>
       </c>
-      <c r="C1244" s="21" t="inlineStr">
+      <c r="C1244" s="13" t="inlineStr">
         <is>
           <t>GALINHA LEVE NOROESTE CONG KG</t>
         </is>
       </c>
-      <c r="D1244" s="21" t="inlineStr">
+      <c r="D1244" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">GALINHA NOROESTE KG CONGELADA </t>
         </is>
@@ -25491,20 +25495,20 @@
       </c>
     </row>
     <row r="1248">
-      <c r="A1248" s="18" t="n">
+      <c r="A1248" s="20" t="n">
         <v>289794</v>
       </c>
-      <c r="B1248" s="18" t="inlineStr">
+      <c r="B1248" s="20" t="inlineStr">
         <is>
           <t>#03 AÇOUGUE - #01 AVES</t>
         </is>
       </c>
-      <c r="C1248" s="19" t="inlineStr">
+      <c r="C1248" s="20" t="inlineStr">
         <is>
           <t>MEIO DA ASA SEARA1KG</t>
         </is>
       </c>
-      <c r="D1248" s="18" t="inlineStr">
+      <c r="D1248" s="20" t="inlineStr">
         <is>
           <t>MEIO DA ASA DE FRANGO SEARA 1KG</t>
         </is>
@@ -25551,20 +25555,20 @@
       </c>
     </row>
     <row r="1251">
-      <c r="A1251" s="18" t="n">
+      <c r="A1251" s="20" t="n">
         <v>195365</v>
       </c>
-      <c r="B1251" s="18" t="inlineStr">
+      <c r="B1251" s="20" t="inlineStr">
         <is>
           <t>#03 AÇOUGUE - #01 AVES</t>
         </is>
       </c>
-      <c r="C1251" s="19" t="inlineStr">
+      <c r="C1251" s="20" t="inlineStr">
         <is>
           <t>MIUDOS CONG FGO (MOELA) PCT 1KG PERDIGAO</t>
         </is>
       </c>
-      <c r="D1251" s="18" t="inlineStr">
+      <c r="D1251" s="20" t="inlineStr">
         <is>
           <t>MOELA DE FRANGO PERDIGÃO BDJ 1KG</t>
         </is>
@@ -25651,40 +25655,40 @@
       </c>
     </row>
     <row r="1256">
-      <c r="A1256" s="21" t="n">
+      <c r="A1256" s="13" t="n">
         <v>150768</v>
       </c>
-      <c r="B1256" s="21" t="inlineStr">
+      <c r="B1256" s="13" t="inlineStr">
         <is>
           <t>#03 AÇOUGUE - #01 AVES</t>
         </is>
       </c>
-      <c r="C1256" s="21" t="inlineStr">
+      <c r="C1256" s="13" t="inlineStr">
         <is>
           <t>PEITO DE FRANGO INTEIRO KG</t>
         </is>
       </c>
-      <c r="D1256" s="21" t="inlineStr">
+      <c r="D1256" s="13" t="inlineStr">
         <is>
           <t>PEITO DE FRANGO KG INTEIRO</t>
         </is>
       </c>
     </row>
     <row r="1257">
-      <c r="A1257" s="13" t="n">
+      <c r="A1257" s="9" t="n">
         <v>302029</v>
       </c>
-      <c r="B1257" s="13" t="inlineStr">
+      <c r="B1257" s="9" t="inlineStr">
         <is>
           <t>#03 AÇOUGUE - #01 AVES</t>
         </is>
       </c>
-      <c r="C1257" s="13" t="inlineStr">
+      <c r="C1257" s="9" t="inlineStr">
         <is>
           <t>PEITO FRANGO SADIA 1KG A PASSARINHO</t>
         </is>
       </c>
-      <c r="D1257" s="13" t="inlineStr">
+      <c r="D1257" s="9" t="inlineStr">
         <is>
           <t>PEITO DE FRANGO SADIA 1KG A PASSARINHO</t>
         </is>
@@ -25831,20 +25835,20 @@
       </c>
     </row>
     <row r="1265">
-      <c r="A1265" s="18" t="n">
+      <c r="A1265" s="17" t="n">
         <v>314513</v>
       </c>
-      <c r="B1265" s="18" t="inlineStr">
+      <c r="B1265" s="17" t="inlineStr">
         <is>
           <t>#03 AÇOUGUE - #01 AVES</t>
         </is>
       </c>
-      <c r="C1265" s="19" t="inlineStr">
+      <c r="C1265" s="16" t="inlineStr">
         <is>
           <t>FILEZINHO DE PEITO FRANGO SEARA 1KG CONG</t>
         </is>
       </c>
-      <c r="D1265" s="18" t="inlineStr">
+      <c r="D1265" s="17" t="inlineStr">
         <is>
           <t>FILEZINHO DE PEITO DE FRANGO SEARA 1KG</t>
         </is>
@@ -25871,20 +25875,20 @@
       </c>
     </row>
     <row r="1267">
-      <c r="A1267" s="8" t="n">
+      <c r="A1267" s="21" t="n">
         <v>105470</v>
       </c>
-      <c r="B1267" s="8" t="inlineStr">
+      <c r="B1267" s="21" t="inlineStr">
         <is>
           <t>#03 AÇOUGUE - #02 BOVINA</t>
         </is>
       </c>
-      <c r="C1267" s="8" t="inlineStr">
+      <c r="C1267" s="21" t="inlineStr">
         <is>
           <t>BOVINO - ACEM KG</t>
         </is>
       </c>
-      <c r="D1267" s="8" t="inlineStr">
+      <c r="D1267" s="21" t="inlineStr">
         <is>
           <t>ACEM BOVINO KG</t>
         </is>
@@ -25951,20 +25955,20 @@
       </c>
     </row>
     <row r="1271">
-      <c r="A1271" s="22" t="n">
+      <c r="A1271" s="20" t="n">
         <v>105460</v>
       </c>
-      <c r="B1271" s="22" t="inlineStr">
+      <c r="B1271" s="20" t="inlineStr">
         <is>
           <t>#03 AÇOUGUE - #02 BOVINA</t>
         </is>
       </c>
-      <c r="C1271" s="22" t="inlineStr">
+      <c r="C1271" s="20" t="inlineStr">
         <is>
           <t>BOVINA - BISTECA PALETA KG</t>
         </is>
       </c>
-      <c r="D1271" s="22" t="inlineStr">
+      <c r="D1271" s="20" t="inlineStr">
         <is>
           <t>BISTECA BOVINA DA PALETA KG</t>
         </is>
@@ -25991,20 +25995,20 @@
       </c>
     </row>
     <row r="1273">
-      <c r="A1273" s="21" t="n">
+      <c r="A1273" s="13" t="n">
         <v>105461</v>
       </c>
-      <c r="B1273" s="21" t="inlineStr">
+      <c r="B1273" s="13" t="inlineStr">
         <is>
           <t>#03 AÇOUGUE - #02 BOVINA</t>
         </is>
       </c>
-      <c r="C1273" s="21" t="inlineStr">
+      <c r="C1273" s="13" t="inlineStr">
         <is>
           <t>BOVINO - BISTECA CONTRA FILE KG</t>
         </is>
       </c>
-      <c r="D1273" s="21" t="inlineStr">
+      <c r="D1273" s="13" t="inlineStr">
         <is>
           <t>BISTECA BOVINA DO CONTRA FILE KG</t>
         </is>
@@ -26031,40 +26035,40 @@
       </c>
     </row>
     <row r="1275">
-      <c r="A1275" s="13" t="n">
+      <c r="A1275" s="9" t="n">
         <v>239334</v>
       </c>
-      <c r="B1275" s="13" t="inlineStr">
+      <c r="B1275" s="9" t="inlineStr">
         <is>
           <t>#03 AÇOUGUE - #02 BOVINA</t>
         </is>
       </c>
-      <c r="C1275" s="13" t="inlineStr">
+      <c r="C1275" s="9" t="inlineStr">
         <is>
           <t>BOVINO - CAPA DO CONTRA FILE KG</t>
         </is>
       </c>
-      <c r="D1275" s="13" t="inlineStr">
+      <c r="D1275" s="9" t="inlineStr">
         <is>
           <t>CAPA DO CONTRA FILE KG</t>
         </is>
       </c>
     </row>
     <row r="1276">
-      <c r="A1276" s="13" t="n">
+      <c r="A1276" s="9" t="n">
         <v>105457</v>
       </c>
-      <c r="B1276" s="13" t="inlineStr">
+      <c r="B1276" s="9" t="inlineStr">
         <is>
           <t>#03 AÇOUGUE - #02 BOVINA</t>
         </is>
       </c>
-      <c r="C1276" s="13" t="inlineStr">
+      <c r="C1276" s="9" t="inlineStr">
         <is>
           <t>BOVINO - CARNE SERENADA KG</t>
         </is>
       </c>
-      <c r="D1276" s="13" t="inlineStr">
+      <c r="D1276" s="9" t="inlineStr">
         <is>
           <t>CARNE BOVINA SERENADA KG</t>
         </is>
@@ -26099,7 +26103,7 @@
           <t>#03 AÇOUGUE - #02 BOVINA</t>
         </is>
       </c>
-      <c r="C1278" s="19" t="inlineStr">
+      <c r="C1278" s="20" t="inlineStr">
         <is>
           <t>BOVINO - CARNE DE SOL KG PRIMEIRA</t>
         </is>
@@ -26131,60 +26135,60 @@
       </c>
     </row>
     <row r="1280">
-      <c r="A1280" s="21" t="n">
+      <c r="A1280" s="15" t="n">
         <v>105468</v>
       </c>
-      <c r="B1280" s="21" t="inlineStr">
+      <c r="B1280" s="15" t="inlineStr">
         <is>
           <t>#03 AÇOUGUE - #02 BOVINA</t>
         </is>
       </c>
-      <c r="C1280" s="21" t="inlineStr">
+      <c r="C1280" s="15" t="inlineStr">
         <is>
           <t>BOVINO - CARNE MOIDA KG</t>
         </is>
       </c>
-      <c r="D1280" s="21" t="inlineStr">
+      <c r="D1280" s="15" t="inlineStr">
         <is>
           <t>CARNE MOIDA KG</t>
         </is>
       </c>
     </row>
     <row r="1281">
-      <c r="A1281" s="23" t="n">
+      <c r="A1281" s="20" t="n">
         <v>105458</v>
       </c>
-      <c r="B1281" s="23" t="inlineStr">
+      <c r="B1281" s="20" t="inlineStr">
         <is>
           <t>#03 AÇOUGUE - #02 BOVINA</t>
         </is>
       </c>
-      <c r="C1281" s="23" t="inlineStr">
+      <c r="C1281" s="20" t="inlineStr">
         <is>
           <t>BOVINO - CHAMBARI KG</t>
         </is>
       </c>
-      <c r="D1281" s="23" t="inlineStr">
+      <c r="D1281" s="20" t="inlineStr">
         <is>
           <t>CHAMBARI KG</t>
         </is>
       </c>
     </row>
     <row r="1282">
-      <c r="A1282" s="13" t="n">
+      <c r="A1282" s="19" t="n">
         <v>105451</v>
       </c>
-      <c r="B1282" s="13" t="inlineStr">
+      <c r="B1282" s="19" t="inlineStr">
         <is>
           <t>#03 AÇOUGUE - #02 BOVINA</t>
         </is>
       </c>
-      <c r="C1282" s="13" t="inlineStr">
+      <c r="C1282" s="19" t="inlineStr">
         <is>
           <t>BOVINO - CONTRA FILE KG</t>
         </is>
       </c>
-      <c r="D1282" s="13" t="inlineStr">
+      <c r="D1282" s="19" t="inlineStr">
         <is>
           <t>CONTRA FILÉ KG</t>
         </is>
@@ -26291,40 +26295,40 @@
       </c>
     </row>
     <row r="1288">
-      <c r="A1288" s="24" t="n">
+      <c r="A1288" s="20" t="n">
         <v>105449</v>
       </c>
-      <c r="B1288" s="24" t="inlineStr">
+      <c r="B1288" s="20" t="inlineStr">
         <is>
           <t>#03 AÇOUGUE - #02 BOVINA</t>
         </is>
       </c>
-      <c r="C1288" s="24" t="inlineStr">
+      <c r="C1288" s="20" t="inlineStr">
         <is>
           <t>BOVINO - COXAO DURO KG</t>
         </is>
       </c>
-      <c r="D1288" s="24" t="inlineStr">
+      <c r="D1288" s="20" t="inlineStr">
         <is>
           <t>COXÃO DURO KG</t>
         </is>
       </c>
     </row>
     <row r="1289">
-      <c r="A1289" s="21" t="n">
+      <c r="A1289" s="15" t="n">
         <v>105435</v>
       </c>
-      <c r="B1289" s="21" t="inlineStr">
+      <c r="B1289" s="15" t="inlineStr">
         <is>
           <t>#03 AÇOUGUE - #02 BOVINA</t>
         </is>
       </c>
-      <c r="C1289" s="21" t="inlineStr">
+      <c r="C1289" s="15" t="inlineStr">
         <is>
           <t>BOVINO - COXAO MOLE KG</t>
         </is>
       </c>
-      <c r="D1289" s="21" t="inlineStr">
+      <c r="D1289" s="15" t="inlineStr">
         <is>
           <t>COXÃO MOLE KG</t>
         </is>
@@ -26431,20 +26435,20 @@
       </c>
     </row>
     <row r="1295">
-      <c r="A1295" t="n">
+      <c r="A1295" s="18" t="n">
         <v>105474</v>
       </c>
-      <c r="B1295" t="inlineStr">
+      <c r="B1295" s="18" t="inlineStr">
         <is>
           <t>#03 AÇOUGUE - #02 BOVINA</t>
         </is>
       </c>
-      <c r="C1295" t="inlineStr">
+      <c r="C1295" s="18" t="inlineStr">
         <is>
           <t>BOVINO - FRALDINHA KG</t>
         </is>
       </c>
-      <c r="D1295" t="inlineStr">
+      <c r="D1295" s="18" t="inlineStr">
         <is>
           <t>FRALDINHA BOVINA KG</t>
         </is>
@@ -26491,20 +26495,20 @@
       </c>
     </row>
     <row r="1298">
-      <c r="A1298" s="13" t="n">
+      <c r="A1298" s="9" t="n">
         <v>107260</v>
       </c>
-      <c r="B1298" s="13" t="inlineStr">
+      <c r="B1298" s="9" t="inlineStr">
         <is>
           <t>#03 AÇOUGUE - #02 BOVINA</t>
         </is>
       </c>
-      <c r="C1298" s="13" t="inlineStr">
+      <c r="C1298" s="9" t="inlineStr">
         <is>
           <t>BOVINO - MACA DO PEITO KG</t>
         </is>
       </c>
-      <c r="D1298" s="13" t="inlineStr">
+      <c r="D1298" s="9" t="inlineStr">
         <is>
           <t>MAÇÃ DO PEITO KG</t>
         </is>
@@ -26651,20 +26655,20 @@
       </c>
     </row>
     <row r="1306">
-      <c r="A1306" s="21" t="n">
+      <c r="A1306" s="13" t="n">
         <v>105452</v>
       </c>
-      <c r="B1306" s="21" t="inlineStr">
+      <c r="B1306" s="13" t="inlineStr">
         <is>
           <t>#03 AÇOUGUE - #02 BOVINA</t>
         </is>
       </c>
-      <c r="C1306" s="21" t="inlineStr">
+      <c r="C1306" s="13" t="inlineStr">
         <is>
           <t>BOVINO - PATINHO KG</t>
         </is>
       </c>
-      <c r="D1306" s="21" t="inlineStr">
+      <c r="D1306" s="13" t="inlineStr">
         <is>
           <t>PATINHO BOVINO KG</t>
         </is>
@@ -26771,40 +26775,40 @@
       </c>
     </row>
     <row r="1312">
-      <c r="A1312" s="13" t="n">
+      <c r="A1312" s="9" t="n">
         <v>106053</v>
       </c>
-      <c r="B1312" s="13" t="inlineStr">
+      <c r="B1312" s="9" t="inlineStr">
         <is>
           <t>#03 AÇOUGUE - #03 SUÍNA</t>
         </is>
       </c>
-      <c r="C1312" s="13" t="inlineStr">
+      <c r="C1312" s="9" t="inlineStr">
         <is>
           <t>SUINO - BISTECA CARRE FRESCA KG</t>
         </is>
       </c>
-      <c r="D1312" s="13" t="inlineStr">
+      <c r="D1312" s="9" t="inlineStr">
         <is>
           <t>BISTECA SUINA CARRE KG</t>
         </is>
       </c>
     </row>
     <row r="1313">
-      <c r="A1313" s="18" t="n">
+      <c r="A1313" s="20" t="n">
         <v>105062</v>
       </c>
-      <c r="B1313" s="18" t="inlineStr">
+      <c r="B1313" s="20" t="inlineStr">
         <is>
           <t>#03 AÇOUGUE - #03 SUÍNA</t>
         </is>
       </c>
-      <c r="C1313" s="18" t="inlineStr">
+      <c r="C1313" s="20" t="inlineStr">
         <is>
           <t>SUINO - BISTECA PERNIL FRESCA KG</t>
         </is>
       </c>
-      <c r="D1313" s="18" t="inlineStr">
+      <c r="D1313" s="20" t="inlineStr">
         <is>
           <t>BISTECA SUINA DO PERNIL KG</t>
         </is>
@@ -26831,20 +26835,20 @@
       </c>
     </row>
     <row r="1315">
-      <c r="A1315" s="8" t="n">
+      <c r="A1315" s="21" t="n">
         <v>105433</v>
       </c>
-      <c r="B1315" s="8" t="inlineStr">
+      <c r="B1315" s="21" t="inlineStr">
         <is>
           <t>#03 AÇOUGUE - #03 SUÍNA</t>
         </is>
       </c>
-      <c r="C1315" s="8" t="inlineStr">
+      <c r="C1315" s="21" t="inlineStr">
         <is>
           <t>SUINO - COSTELA SUINA KG</t>
         </is>
       </c>
-      <c r="D1315" s="8" t="inlineStr">
+      <c r="D1315" s="21" t="inlineStr">
         <is>
           <t>COSTELA SUINA KG</t>
         </is>
@@ -26911,20 +26915,20 @@
       </c>
     </row>
     <row r="1319">
-      <c r="A1319" s="13" t="n">
+      <c r="A1319" s="9" t="n">
         <v>106008</v>
       </c>
-      <c r="B1319" s="13" t="inlineStr">
+      <c r="B1319" s="9" t="inlineStr">
         <is>
           <t>#03 AÇOUGUE - #03 SUÍNA</t>
         </is>
       </c>
-      <c r="C1319" s="13" t="inlineStr">
+      <c r="C1319" s="9" t="inlineStr">
         <is>
           <t>INGREDIENTES P/ FEIJOADA KG</t>
         </is>
       </c>
-      <c r="D1319" s="13" t="inlineStr">
+      <c r="D1319" s="9" t="inlineStr">
         <is>
           <t>INGREDIENTES PARA FEIJOADA KG</t>
         </is>
@@ -27011,20 +27015,20 @@
       </c>
     </row>
     <row r="1324">
-      <c r="A1324" s="13" t="n">
+      <c r="A1324" s="9" t="n">
         <v>258810</v>
       </c>
-      <c r="B1324" s="13" t="inlineStr">
+      <c r="B1324" s="9" t="inlineStr">
         <is>
           <t>#03 AÇOUGUE - #03 SUÍNA</t>
         </is>
       </c>
-      <c r="C1324" s="13" t="inlineStr">
+      <c r="C1324" s="9" t="inlineStr">
         <is>
           <t>SUINO - PANCETA KG</t>
         </is>
       </c>
-      <c r="D1324" s="13" t="inlineStr">
+      <c r="D1324" s="9" t="inlineStr">
         <is>
           <t>PANCETA SUINA KG</t>
         </is>
@@ -27051,20 +27055,20 @@
       </c>
     </row>
     <row r="1326">
-      <c r="A1326" s="7" t="n">
+      <c r="A1326" s="22" t="n">
         <v>106052</v>
       </c>
-      <c r="B1326" s="7" t="inlineStr">
+      <c r="B1326" s="22" t="inlineStr">
         <is>
           <t>#03 AÇOUGUE - #03 SUÍNA</t>
         </is>
       </c>
-      <c r="C1326" s="7" t="inlineStr">
+      <c r="C1326" s="22" t="inlineStr">
         <is>
           <t>SUINO - PELE SUINA FRESCA KG</t>
         </is>
       </c>
-      <c r="D1326" s="7" t="inlineStr">
+      <c r="D1326" s="22" t="inlineStr">
         <is>
           <t>PELE SUINA KG</t>
         </is>
@@ -27171,20 +27175,20 @@
       </c>
     </row>
     <row r="1332">
-      <c r="A1332" s="21" t="n">
+      <c r="A1332" s="13" t="n">
         <v>106034</v>
       </c>
-      <c r="B1332" s="21" t="inlineStr">
+      <c r="B1332" s="13" t="inlineStr">
         <is>
           <t>#03 AÇOUGUE - #03 SUÍNA</t>
         </is>
       </c>
-      <c r="C1332" s="21" t="inlineStr">
+      <c r="C1332" s="13" t="inlineStr">
         <is>
           <t>SUINO - SUAN FRESCA KG</t>
         </is>
       </c>
-      <c r="D1332" s="21" t="inlineStr">
+      <c r="D1332" s="13" t="inlineStr">
         <is>
           <t>SUAN SUINA KG</t>
         </is>
@@ -28051,20 +28055,20 @@
       </c>
     </row>
     <row r="1376">
-      <c r="A1376" t="n">
+      <c r="A1376" s="18" t="n">
         <v>343440</v>
       </c>
-      <c r="B1376" t="inlineStr">
+      <c r="B1376" s="18" t="inlineStr">
         <is>
           <t>#03 AÇOUGUE - #06 EMBUTIDOS E FRIOS</t>
         </is>
       </c>
-      <c r="C1376" t="inlineStr">
+      <c r="C1376" s="18" t="inlineStr">
         <is>
           <t>EMPAN FRANGO SEARA 275G ORIENTAL NETFLIX</t>
         </is>
       </c>
-      <c r="D1376" t="inlineStr">
+      <c r="D1376" s="18" t="inlineStr">
         <is>
           <t>EMPANADO DE FRANGO SEARA 275G ORIENTAL NETFLIX</t>
         </is>
@@ -28451,20 +28455,20 @@
       </c>
     </row>
     <row r="1396">
-      <c r="A1396" s="18" t="n">
+      <c r="A1396" s="20" t="n">
         <v>305039</v>
       </c>
-      <c r="B1396" s="18" t="inlineStr">
+      <c r="B1396" s="20" t="inlineStr">
         <is>
           <t>#03 AÇOUGUE - #06 EMBUTIDOS E FRIOS</t>
         </is>
       </c>
-      <c r="C1396" s="18" t="inlineStr">
+      <c r="C1396" s="20" t="inlineStr">
         <is>
           <t>LINGUIÇA BOVINA KG CASEIRA</t>
         </is>
       </c>
-      <c r="D1396" s="18" t="inlineStr">
+      <c r="D1396" s="20" t="inlineStr">
         <is>
           <t>LINGUIÇA CASEIRA BOVINA KG</t>
         </is>
@@ -28551,40 +28555,40 @@
       </c>
     </row>
     <row r="1401">
-      <c r="A1401" t="n">
+      <c r="A1401" s="18" t="n">
         <v>227259</v>
       </c>
-      <c r="B1401" t="inlineStr">
+      <c r="B1401" s="18" t="inlineStr">
         <is>
           <t>#03 AÇOUGUE - #06 EMBUTIDOS E FRIOS</t>
         </is>
       </c>
-      <c r="C1401" t="inlineStr">
+      <c r="C1401" s="18" t="inlineStr">
         <is>
           <t>LINGUICA FININHA DEFUMADA SEARA 215G</t>
         </is>
       </c>
-      <c r="D1401" t="inlineStr">
+      <c r="D1401" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">LINGUIÇA DEFUMADA SEARA 215G FININHA </t>
         </is>
       </c>
     </row>
     <row r="1402">
-      <c r="A1402" s="21" t="n">
+      <c r="A1402" s="13" t="n">
         <v>228422</v>
       </c>
-      <c r="B1402" s="21" t="inlineStr">
+      <c r="B1402" s="13" t="inlineStr">
         <is>
           <t>#03 AÇOUGUE - #06 EMBUTIDOS E FRIOS</t>
         </is>
       </c>
-      <c r="C1402" s="21" t="inlineStr">
+      <c r="C1402" s="13" t="inlineStr">
         <is>
           <t>LINGUIÇA SUPER FRANGO KG FRANGO GROSSA</t>
         </is>
       </c>
-      <c r="D1402" s="21" t="inlineStr">
+      <c r="D1402" s="13" t="inlineStr">
         <is>
           <t>LINGUIÇA GROSSA SUPER FRANGO KG</t>
         </is>
@@ -28831,20 +28835,20 @@
       </c>
     </row>
     <row r="1415">
-      <c r="A1415" s="13" t="n">
+      <c r="A1415" s="9" t="n">
         <v>301962</v>
       </c>
-      <c r="B1415" s="13" t="inlineStr">
+      <c r="B1415" s="9" t="inlineStr">
         <is>
           <t>#03 AÇOUGUE - #06 EMBUTIDOS E FRIOS</t>
         </is>
       </c>
-      <c r="C1415" s="13" t="inlineStr">
+      <c r="C1415" s="9" t="inlineStr">
         <is>
           <t>LINGUICA BONFRIGO SUINA KG</t>
         </is>
       </c>
-      <c r="D1415" s="13" t="inlineStr">
+      <c r="D1415" s="9" t="inlineStr">
         <is>
           <t>LINGUIÇA SUÍNA BONFRIGO KG</t>
         </is>
@@ -28951,20 +28955,20 @@
       </c>
     </row>
     <row r="1421">
-      <c r="A1421" s="18" t="n">
+      <c r="A1421" s="17" t="n">
         <v>292399</v>
       </c>
-      <c r="B1421" s="18" t="inlineStr">
+      <c r="B1421" s="17" t="inlineStr">
         <is>
           <t>#03 AÇOUGUE - #06 EMBUTIDOS E FRIOS</t>
         </is>
       </c>
-      <c r="C1421" s="18" t="inlineStr">
+      <c r="C1421" s="17" t="inlineStr">
         <is>
           <t>LINGUICA SUPER FRANGO 400GR DEFUMADA FRA</t>
         </is>
       </c>
-      <c r="D1421" s="18" t="inlineStr">
+      <c r="D1421" s="17" t="inlineStr">
         <is>
           <t>LINGUIÇA SUPER FRANGO 400G DEFUMADA</t>
         </is>
@@ -29071,20 +29075,20 @@
       </c>
     </row>
     <row r="1427">
-      <c r="A1427" t="n">
+      <c r="A1427" s="18" t="n">
         <v>330686</v>
       </c>
-      <c r="B1427" t="inlineStr">
+      <c r="B1427" s="18" t="inlineStr">
         <is>
           <t>#03 AÇOUGUE - #06 EMBUTIDOS E FRIOS</t>
         </is>
       </c>
-      <c r="C1427" t="inlineStr">
+      <c r="C1427" s="18" t="inlineStr">
         <is>
           <t>LINGUICA TOSCANA FRIELLA KG</t>
         </is>
       </c>
-      <c r="D1427" t="inlineStr">
+      <c r="D1427" s="18" t="inlineStr">
         <is>
           <t>LINGUICA TOSCANA FRIELLA KG</t>
         </is>
@@ -29511,20 +29515,20 @@
       </c>
     </row>
     <row r="1449">
-      <c r="A1449" s="13" t="n">
+      <c r="A1449" s="9" t="n">
         <v>170705</v>
       </c>
-      <c r="B1449" s="13" t="inlineStr">
+      <c r="B1449" s="9" t="inlineStr">
         <is>
           <t>#03 AÇOUGUE - #06 EMBUTIDOS E FRIOS</t>
         </is>
       </c>
-      <c r="C1449" s="13" t="inlineStr">
+      <c r="C1449" s="9" t="inlineStr">
         <is>
           <t>MORTADELA MISTA  SADIA 400GR</t>
         </is>
       </c>
-      <c r="D1449" s="13" t="inlineStr">
+      <c r="D1449" s="9" t="inlineStr">
         <is>
           <t>MORTADELA MISTA SADIA 400G</t>
         </is>
@@ -29571,20 +29575,20 @@
       </c>
     </row>
     <row r="1452">
-      <c r="A1452" s="21" t="n">
+      <c r="A1452" s="13" t="n">
         <v>105765</v>
       </c>
-      <c r="B1452" s="21" t="inlineStr">
+      <c r="B1452" s="13" t="inlineStr">
         <is>
           <t>#03 AÇOUGUE - #06 EMBUTIDOS E FRIOS</t>
         </is>
       </c>
-      <c r="C1452" s="21" t="inlineStr">
+      <c r="C1452" s="13" t="inlineStr">
         <is>
           <t>MORTADELA MISTA PERDIGAO KG</t>
         </is>
       </c>
-      <c r="D1452" s="21" t="inlineStr">
+      <c r="D1452" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">MORTADELA PERDIGÃO KG MISTA </t>
         </is>
@@ -29651,20 +29655,20 @@
       </c>
     </row>
     <row r="1456">
-      <c r="A1456" s="18" t="n">
+      <c r="A1456" s="17" t="n">
         <v>108558</v>
       </c>
-      <c r="B1456" s="18" t="inlineStr">
+      <c r="B1456" s="17" t="inlineStr">
         <is>
           <t>#03 AÇOUGUE - #06 EMBUTIDOS E FRIOS</t>
         </is>
       </c>
-      <c r="C1456" s="18" t="inlineStr">
+      <c r="C1456" s="17" t="inlineStr">
         <is>
           <t>MORTADELA SADIA  1KG SUINA</t>
         </is>
       </c>
-      <c r="D1456" s="18" t="inlineStr">
+      <c r="D1456" s="17" t="inlineStr">
         <is>
           <t>MORTADELA SUÍNA SADIA 1KG</t>
         </is>
@@ -29851,20 +29855,20 @@
       </c>
     </row>
     <row r="1466">
-      <c r="A1466" s="18" t="n">
+      <c r="A1466" s="17" t="n">
         <v>184045</v>
       </c>
-      <c r="B1466" s="18" t="inlineStr">
+      <c r="B1466" s="17" t="inlineStr">
         <is>
           <t>#03 AÇOUGUE - #06 EMBUTIDOS E FRIOS</t>
         </is>
       </c>
-      <c r="C1466" s="18" t="inlineStr">
+      <c r="C1466" s="17" t="inlineStr">
         <is>
           <t>SALAME PERDIGAO FATIADO 100GR SALF10</t>
         </is>
       </c>
-      <c r="D1466" s="18" t="inlineStr">
+      <c r="D1466" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">SALAME PERDIGÃO 100GR FATIADO </t>
         </is>
@@ -29971,20 +29975,20 @@
       </c>
     </row>
     <row r="1472">
-      <c r="A1472" s="21" t="n">
+      <c r="A1472" s="13" t="n">
         <v>227341</v>
       </c>
-      <c r="B1472" s="21" t="inlineStr">
+      <c r="B1472" s="13" t="inlineStr">
         <is>
           <t>#03 AÇOUGUE - #06 EMBUTIDOS E FRIOS</t>
         </is>
       </c>
-      <c r="C1472" s="21" t="inlineStr">
+      <c r="C1472" s="13" t="inlineStr">
         <is>
           <t>SALSICHA HOT DOG AMERICANO KG</t>
         </is>
       </c>
-      <c r="D1472" s="21" t="inlineStr">
+      <c r="D1472" s="13" t="inlineStr">
         <is>
           <t>SALSICHA AMERICANO KG PARA HOT DOG</t>
         </is>
@@ -30151,20 +30155,20 @@
       </c>
     </row>
     <row r="1481">
-      <c r="A1481" s="13" t="n">
+      <c r="A1481" s="9" t="n">
         <v>158192</v>
       </c>
-      <c r="B1481" s="13" t="inlineStr">
+      <c r="B1481" s="9" t="inlineStr">
         <is>
           <t>#03 AÇOUGUE - #06 EMBUTIDOS E FRIOS</t>
         </is>
       </c>
-      <c r="C1481" s="13" t="inlineStr">
+      <c r="C1481" s="9" t="inlineStr">
         <is>
           <t>MORTADELA FRICO 400GR MINI MISTA</t>
         </is>
       </c>
-      <c r="D1481" s="13" t="inlineStr">
+      <c r="D1481" s="9" t="inlineStr">
         <is>
           <t>MORTADELA MISTA FRICO 400G MINI</t>
         </is>
@@ -30211,20 +30215,20 @@
       </c>
     </row>
     <row r="1484">
-      <c r="A1484" s="13" t="n">
+      <c r="A1484" s="9" t="n">
         <v>345268</v>
       </c>
-      <c r="B1484" s="13" t="inlineStr">
+      <c r="B1484" s="9" t="inlineStr">
         <is>
           <t>#03 AÇOUGUE - #07 EMPANADOS E PRATOS PRONTOS</t>
         </is>
       </c>
-      <c r="C1484" s="13" t="inlineStr">
+      <c r="C1484" s="9" t="inlineStr">
         <is>
           <t>MINI HAMBURGUER SEARA 300G BOV/SUI CHURR</t>
         </is>
       </c>
-      <c r="D1484" s="13" t="inlineStr">
+      <c r="D1484" s="9" t="inlineStr">
         <is>
           <t>MINI HAMBURGUER SEARA 300G CHURRASCO BOVINO E SUINO</t>
         </is>
@@ -30311,40 +30315,40 @@
       </c>
     </row>
     <row r="1489">
-      <c r="A1489" s="18" t="n">
+      <c r="A1489" s="20" t="n">
         <v>138538</v>
       </c>
-      <c r="B1489" s="18" t="inlineStr">
+      <c r="B1489" s="20" t="inlineStr">
         <is>
           <t>#03 AÇOUGUE - #07 EMPANADOS E PRATOS PRONTOS</t>
         </is>
       </c>
-      <c r="C1489" s="18" t="inlineStr">
+      <c r="C1489" s="20" t="inlineStr">
         <is>
           <t>TEKITOS SEARA FRANGO 300G</t>
         </is>
       </c>
-      <c r="D1489" s="18" t="inlineStr">
+      <c r="D1489" s="20" t="inlineStr">
         <is>
           <t>TEKITOS SEARA 300G FRANGO</t>
         </is>
       </c>
     </row>
     <row r="1490">
-      <c r="A1490" s="18" t="n">
+      <c r="A1490" s="20" t="n">
         <v>127328</v>
       </c>
-      <c r="B1490" s="18" t="inlineStr">
+      <c r="B1490" s="20" t="inlineStr">
         <is>
           <t>#03 AÇOUGUE - #07 EMPANADOS E PRATOS PRONTOS</t>
         </is>
       </c>
-      <c r="C1490" s="18" t="inlineStr">
+      <c r="C1490" s="20" t="inlineStr">
         <is>
           <t>TEKITOS SEARA QUEIJO OREGANO 300GR</t>
         </is>
       </c>
-      <c r="D1490" s="18" t="inlineStr">
+      <c r="D1490" s="20" t="inlineStr">
         <is>
           <t>TEKITOS SEARA 300G QUEIJO COM OREGANO</t>
         </is>
@@ -30371,140 +30375,140 @@
       </c>
     </row>
     <row r="1492">
-      <c r="A1492" s="13" t="n">
+      <c r="A1492" s="9" t="n">
         <v>328607</v>
       </c>
-      <c r="B1492" s="13" t="inlineStr">
+      <c r="B1492" s="9" t="inlineStr">
         <is>
           <t>#03 AÇOUGUE - #07 EMPANADOS E PRATOS PRONTOS</t>
         </is>
       </c>
-      <c r="C1492" s="13" t="inlineStr">
+      <c r="C1492" s="9" t="inlineStr">
         <is>
           <t>BOLINHO DE CARNE SUINA SEARA 270GR COM</t>
         </is>
       </c>
-      <c r="D1492" s="13" t="inlineStr">
+      <c r="D1492" s="9" t="inlineStr">
         <is>
           <t>BOLINHO DE CARNE SUINA SEARA 270G MOLHO BARBECUE</t>
         </is>
       </c>
     </row>
     <row r="1493">
-      <c r="A1493" s="13" t="n">
+      <c r="A1493" s="9" t="n">
         <v>116233</v>
       </c>
-      <c r="B1493" s="13" t="inlineStr">
+      <c r="B1493" s="9" t="inlineStr">
         <is>
           <t>#03 AÇOUGUE - #07 EMPANADOS E PRATOS PRONTOS</t>
         </is>
       </c>
-      <c r="C1493" s="13" t="inlineStr">
+      <c r="C1493" s="9" t="inlineStr">
         <is>
           <t>HOT POCKET SADIA 145GR X FRANGO</t>
         </is>
       </c>
-      <c r="D1493" s="13" t="inlineStr">
+      <c r="D1493" s="9" t="inlineStr">
         <is>
           <t>HOT POCKET SADIA 145G X-FRANGO</t>
         </is>
       </c>
     </row>
     <row r="1494">
-      <c r="A1494" s="8" t="n">
+      <c r="A1494" s="21" t="n">
         <v>104931</v>
       </c>
-      <c r="B1494" s="8" t="inlineStr">
+      <c r="B1494" s="21" t="inlineStr">
         <is>
           <t>#04 HORTIFRUTI - #01 FRUTAS</t>
         </is>
       </c>
-      <c r="C1494" s="8" t="inlineStr">
+      <c r="C1494" s="21" t="inlineStr">
         <is>
           <t>LARANJA KG</t>
         </is>
       </c>
-      <c r="D1494" s="8" t="inlineStr">
+      <c r="D1494" s="21" t="inlineStr">
         <is>
           <t>LARANJA KG</t>
         </is>
       </c>
     </row>
     <row r="1495">
-      <c r="A1495" s="23" t="n">
+      <c r="A1495" s="17" t="n">
         <v>105010</v>
       </c>
-      <c r="B1495" s="23" t="inlineStr">
+      <c r="B1495" s="17" t="inlineStr">
         <is>
           <t>#04 HORTIFRUTI - #01 LEGUMES E TUBÉRCULOS</t>
         </is>
       </c>
-      <c r="C1495" s="23" t="inlineStr">
+      <c r="C1495" s="17" t="inlineStr">
         <is>
           <t>BATATA MONALISA KG</t>
         </is>
       </c>
-      <c r="D1495" s="23" t="inlineStr">
+      <c r="D1495" s="17" t="inlineStr">
         <is>
           <t>BATATA MONALISA KG</t>
         </is>
       </c>
     </row>
     <row r="1496">
-      <c r="A1496" s="8" t="n">
+      <c r="A1496" s="21" t="n">
         <v>104961</v>
       </c>
-      <c r="B1496" s="8" t="inlineStr">
+      <c r="B1496" s="21" t="inlineStr">
         <is>
           <t>#04 HORTIFRUTI - #01 LEGUMES E TUBÉRCULOS</t>
         </is>
       </c>
-      <c r="C1496" s="8" t="inlineStr">
+      <c r="C1496" s="21" t="inlineStr">
         <is>
           <t>TOMATE CARMEM KG</t>
         </is>
       </c>
-      <c r="D1496" s="8" t="inlineStr">
+      <c r="D1496" s="21" t="inlineStr">
         <is>
           <t>TOMATE CARMEM KG</t>
         </is>
       </c>
     </row>
     <row r="1497">
-      <c r="A1497" s="8" t="n">
+      <c r="A1497" s="21" t="n">
         <v>104919</v>
       </c>
-      <c r="B1497" s="8" t="inlineStr">
+      <c r="B1497" s="21" t="inlineStr">
         <is>
           <t>#04 HORTIFRUTI - #01 TEMPEROS FRESCOS</t>
         </is>
       </c>
-      <c r="C1497" s="8" t="inlineStr">
+      <c r="C1497" s="21" t="inlineStr">
         <is>
           <t>CEBOLA NACIONAL KG</t>
         </is>
       </c>
-      <c r="D1497" s="8" t="inlineStr">
+      <c r="D1497" s="21" t="inlineStr">
         <is>
           <t>CEBOLA NACIONAL KG</t>
         </is>
       </c>
     </row>
     <row r="1498">
-      <c r="A1498" s="8" t="n">
+      <c r="A1498" s="21" t="n">
         <v>104864</v>
       </c>
-      <c r="B1498" s="8" t="inlineStr">
+      <c r="B1498" s="21" t="inlineStr">
         <is>
           <t>#04 HORTIFRUTI - FRUTAS</t>
         </is>
       </c>
-      <c r="C1498" s="8" t="inlineStr">
+      <c r="C1498" s="21" t="inlineStr">
         <is>
           <t>ABACATE KG</t>
         </is>
       </c>
-      <c r="D1498" s="8" t="inlineStr">
+      <c r="D1498" s="21" t="inlineStr">
         <is>
           <t>ABACATE KG</t>
         </is>
@@ -30571,60 +30575,60 @@
       </c>
     </row>
     <row r="1502">
-      <c r="A1502" s="3" t="n">
+      <c r="A1502" s="23" t="n">
         <v>104998</v>
       </c>
-      <c r="B1502" s="3" t="inlineStr">
+      <c r="B1502" s="23" t="inlineStr">
         <is>
           <t>#04 HORTIFRUTI - FRUTAS</t>
         </is>
       </c>
-      <c r="C1502" s="3" t="inlineStr">
+      <c r="C1502" s="23" t="inlineStr">
         <is>
           <t>BANANA TERRA KG</t>
         </is>
       </c>
-      <c r="D1502" s="3" t="inlineStr">
+      <c r="D1502" s="23" t="inlineStr">
         <is>
           <t>BANANA DA TERRA KG</t>
         </is>
       </c>
     </row>
     <row r="1503">
-      <c r="A1503" s="3" t="n">
+      <c r="A1503" s="23" t="n">
         <v>104905</v>
       </c>
-      <c r="B1503" s="3" t="inlineStr">
+      <c r="B1503" s="23" t="inlineStr">
         <is>
           <t>#04 HORTIFRUTI - FRUTAS</t>
         </is>
       </c>
-      <c r="C1503" s="3" t="inlineStr">
+      <c r="C1503" s="23" t="inlineStr">
         <is>
           <t>BANANA NANICA KG</t>
         </is>
       </c>
-      <c r="D1503" s="3" t="inlineStr">
+      <c r="D1503" s="23" t="inlineStr">
         <is>
           <t>BANANA NANICA KG</t>
         </is>
       </c>
     </row>
     <row r="1504">
-      <c r="A1504" s="3" t="n">
+      <c r="A1504" s="23" t="n">
         <v>105023</v>
       </c>
-      <c r="B1504" s="3" t="inlineStr">
+      <c r="B1504" s="23" t="inlineStr">
         <is>
           <t>#04 HORTIFRUTI - FRUTAS</t>
         </is>
       </c>
-      <c r="C1504" s="3" t="inlineStr">
+      <c r="C1504" s="23" t="inlineStr">
         <is>
           <t>BANANA PRATA KG</t>
         </is>
       </c>
-      <c r="D1504" s="3" t="inlineStr">
+      <c r="D1504" s="23" t="inlineStr">
         <is>
           <t>BANANA PRATA KG</t>
         </is>
@@ -30691,100 +30695,100 @@
       </c>
     </row>
     <row r="1508">
-      <c r="A1508" s="23" t="n">
+      <c r="A1508" s="17" t="n">
         <v>104855</v>
       </c>
-      <c r="B1508" s="23" t="inlineStr">
+      <c r="B1508" s="17" t="inlineStr">
         <is>
           <t>#04 HORTIFRUTI - FRUTAS</t>
         </is>
       </c>
-      <c r="C1508" s="23" t="inlineStr">
+      <c r="C1508" s="17" t="inlineStr">
         <is>
           <t>LIMAO TAITI KG</t>
         </is>
       </c>
-      <c r="D1508" s="23" t="inlineStr">
+      <c r="D1508" s="17" t="inlineStr">
         <is>
           <t>LIMÃO TAITI KG</t>
         </is>
       </c>
     </row>
     <row r="1509">
-      <c r="A1509" s="3" t="n">
+      <c r="A1509" s="23" t="n">
         <v>104944</v>
       </c>
-      <c r="B1509" s="3" t="inlineStr">
+      <c r="B1509" s="23" t="inlineStr">
         <is>
           <t>#04 HORTIFRUTI - FRUTAS</t>
         </is>
       </c>
-      <c r="C1509" s="3" t="inlineStr">
+      <c r="C1509" s="23" t="inlineStr">
         <is>
           <t>MACA NACIONAL KG</t>
         </is>
       </c>
-      <c r="D1509" s="3" t="inlineStr">
+      <c r="D1509" s="23" t="inlineStr">
         <is>
           <t>MAÇÃ NACIONAL KG</t>
         </is>
       </c>
     </row>
     <row r="1510">
-      <c r="A1510" s="23" t="n">
+      <c r="A1510" s="17" t="n">
         <v>104881</v>
       </c>
-      <c r="B1510" s="23" t="inlineStr">
+      <c r="B1510" s="17" t="inlineStr">
         <is>
           <t>#04 HORTIFRUTI - FRUTAS</t>
         </is>
       </c>
-      <c r="C1510" s="23" t="inlineStr">
+      <c r="C1510" s="17" t="inlineStr">
         <is>
           <t>MAMAO FORMOSA KG</t>
         </is>
       </c>
-      <c r="D1510" s="23" t="inlineStr">
+      <c r="D1510" s="17" t="inlineStr">
         <is>
           <t>MAMÃO FORMOSA KG</t>
         </is>
       </c>
     </row>
     <row r="1511">
-      <c r="A1511" s="8" t="n">
+      <c r="A1511" s="21" t="n">
         <v>104928</v>
       </c>
-      <c r="B1511" s="8" t="inlineStr">
+      <c r="B1511" s="21" t="inlineStr">
         <is>
           <t>#04 HORTIFRUTI - FRUTAS</t>
         </is>
       </c>
-      <c r="C1511" s="8" t="inlineStr">
+      <c r="C1511" s="21" t="inlineStr">
         <is>
           <t>MANGA PALMER KG</t>
         </is>
       </c>
-      <c r="D1511" s="8" t="inlineStr">
+      <c r="D1511" s="21" t="inlineStr">
         <is>
           <t>MANGA KG PALMER</t>
         </is>
       </c>
     </row>
     <row r="1512">
-      <c r="A1512" s="23" t="n">
+      <c r="A1512" s="17" t="n">
         <v>104883</v>
       </c>
-      <c r="B1512" s="23" t="inlineStr">
+      <c r="B1512" s="17" t="inlineStr">
         <is>
           <t>#04 HORTIFRUTI - FRUTAS</t>
         </is>
       </c>
-      <c r="C1512" s="23" t="inlineStr">
+      <c r="C1512" s="17" t="inlineStr">
         <is>
           <t>MANGA TOMY KG</t>
         </is>
       </c>
-      <c r="D1512" s="23" t="inlineStr">
+      <c r="D1512" s="17" t="inlineStr">
         <is>
           <t>MANGA KG TOMY</t>
         </is>
@@ -30831,20 +30835,20 @@
       </c>
     </row>
     <row r="1515">
-      <c r="A1515" s="8" t="n">
+      <c r="A1515" s="21" t="n">
         <v>104947</v>
       </c>
-      <c r="B1515" s="8" t="inlineStr">
+      <c r="B1515" s="21" t="inlineStr">
         <is>
           <t>#04 HORTIFRUTI - FRUTAS</t>
         </is>
       </c>
-      <c r="C1515" s="8" t="inlineStr">
+      <c r="C1515" s="21" t="inlineStr">
         <is>
           <t>MELANCIA INTEIRA KG</t>
         </is>
       </c>
-      <c r="D1515" s="8" t="inlineStr">
+      <c r="D1515" s="21" t="inlineStr">
         <is>
           <t>MELANCIA INTEIRA KG</t>
         </is>
@@ -31291,40 +31295,40 @@
       </c>
     </row>
     <row r="1538">
-      <c r="A1538" s="8" t="n">
+      <c r="A1538" s="21" t="n">
         <v>104903</v>
       </c>
-      <c r="B1538" s="8" t="inlineStr">
+      <c r="B1538" s="21" t="inlineStr">
         <is>
           <t>#04 HORTIFRUTI - LEGUMES E TUBÉRCULOS</t>
         </is>
       </c>
-      <c r="C1538" s="8" t="inlineStr">
+      <c r="C1538" s="21" t="inlineStr">
         <is>
           <t>BATATA DOCE ROSA KG</t>
         </is>
       </c>
-      <c r="D1538" s="8" t="inlineStr">
+      <c r="D1538" s="21" t="inlineStr">
         <is>
           <t>BATATA DOCE KG ROSA</t>
         </is>
       </c>
     </row>
     <row r="1539">
-      <c r="A1539" s="3" t="n">
+      <c r="A1539" s="23" t="n">
         <v>105001</v>
       </c>
-      <c r="B1539" s="3" t="inlineStr">
+      <c r="B1539" s="23" t="inlineStr">
         <is>
           <t>#04 HORTIFRUTI - LEGUMES E TUBÉRCULOS</t>
         </is>
       </c>
-      <c r="C1539" s="3" t="inlineStr">
+      <c r="C1539" s="23" t="inlineStr">
         <is>
           <t>BETERRABA KG</t>
         </is>
       </c>
-      <c r="D1539" s="3" t="inlineStr">
+      <c r="D1539" s="23" t="inlineStr">
         <is>
           <t>BETERRABA KG</t>
         </is>
@@ -31351,40 +31355,40 @@
       </c>
     </row>
     <row r="1541">
-      <c r="A1541" s="8" t="n">
+      <c r="A1541" s="21" t="n">
         <v>104862</v>
       </c>
-      <c r="B1541" s="8" t="inlineStr">
+      <c r="B1541" s="21" t="inlineStr">
         <is>
           <t>#04 HORTIFRUTI - LEGUMES E TUBÉRCULOS</t>
         </is>
       </c>
-      <c r="C1541" s="8" t="inlineStr">
+      <c r="C1541" s="21" t="inlineStr">
         <is>
           <t>CENOURA KG</t>
         </is>
       </c>
-      <c r="D1541" s="8" t="inlineStr">
+      <c r="D1541" s="21" t="inlineStr">
         <is>
           <t>CENOURA KG</t>
         </is>
       </c>
     </row>
     <row r="1542">
-      <c r="A1542" s="8" t="n">
+      <c r="A1542" s="21" t="n">
         <v>111131</v>
       </c>
-      <c r="B1542" s="8" t="inlineStr">
+      <c r="B1542" s="21" t="inlineStr">
         <is>
           <t>#04 HORTIFRUTI - LEGUMES E TUBÉRCULOS</t>
         </is>
       </c>
-      <c r="C1542" s="8" t="inlineStr">
+      <c r="C1542" s="21" t="inlineStr">
         <is>
           <t>CHUCHU VERDE KG</t>
         </is>
       </c>
-      <c r="D1542" s="8" t="inlineStr">
+      <c r="D1542" s="21" t="inlineStr">
         <is>
           <t>CHUCHU VERDE KG</t>
         </is>
@@ -31491,40 +31495,40 @@
       </c>
     </row>
     <row r="1548">
-      <c r="A1548" s="3" t="n">
+      <c r="A1548" s="23" t="n">
         <v>104937</v>
       </c>
-      <c r="B1548" s="3" t="inlineStr">
+      <c r="B1548" s="23" t="inlineStr">
         <is>
           <t>#04 HORTIFRUTI - TEMPEROS FRESCOS</t>
         </is>
       </c>
-      <c r="C1548" s="3" t="inlineStr">
+      <c r="C1548" s="23" t="inlineStr">
         <is>
           <t>ALHO A GRANEL KG</t>
         </is>
       </c>
-      <c r="D1548" s="3" t="inlineStr">
+      <c r="D1548" s="23" t="inlineStr">
         <is>
           <t>ALHO A GRANEL KG</t>
         </is>
       </c>
     </row>
     <row r="1549">
-      <c r="A1549" s="3" t="n">
+      <c r="A1549" s="23" t="n">
         <v>104992</v>
       </c>
-      <c r="B1549" s="3" t="inlineStr">
+      <c r="B1549" s="23" t="inlineStr">
         <is>
           <t>#04 HORTIFRUTI - VERDURAS E FOLHAGENS</t>
         </is>
       </c>
-      <c r="C1549" s="3" t="inlineStr">
+      <c r="C1549" s="23" t="inlineStr">
         <is>
           <t>REPOLHO VERDE KG</t>
         </is>
       </c>
-      <c r="D1549" s="3" t="inlineStr">
+      <c r="D1549" s="23" t="inlineStr">
         <is>
           <t>REPOLHO VERDE KG</t>
         </is>
@@ -32351,20 +32355,20 @@
       </c>
     </row>
     <row r="1591">
-      <c r="A1591" s="21" t="n">
+      <c r="A1591" s="13" t="n">
         <v>104406</v>
       </c>
-      <c r="B1591" s="21" t="inlineStr">
+      <c r="B1591" s="13" t="inlineStr">
         <is>
           <t>#05 BEBIDA - #00 BEBIDAS GASEIFICADAS</t>
         </is>
       </c>
-      <c r="C1591" s="21" t="inlineStr">
+      <c r="C1591" s="13" t="inlineStr">
         <is>
           <t>REFRIGERANTE COCA COLA 2L</t>
         </is>
       </c>
-      <c r="D1591" s="21" t="inlineStr">
+      <c r="D1591" s="13" t="inlineStr">
         <is>
           <t>REFRIGERANTE COCA COLA 2L</t>
         </is>
@@ -32471,40 +32475,40 @@
       </c>
     </row>
     <row r="1597">
-      <c r="A1597" s="21" t="n">
+      <c r="A1597" s="13" t="n">
         <v>104404</v>
       </c>
-      <c r="B1597" s="21" t="inlineStr">
+      <c r="B1597" s="13" t="inlineStr">
         <is>
           <t>#05 BEBIDA - #00 BEBIDAS GASEIFICADAS</t>
         </is>
       </c>
-      <c r="C1597" s="21" t="inlineStr">
+      <c r="C1597" s="13" t="inlineStr">
         <is>
           <t>REFRIG FANTA LARANJA 2L</t>
         </is>
       </c>
-      <c r="D1597" s="21" t="inlineStr">
+      <c r="D1597" s="13" t="inlineStr">
         <is>
           <t>REFRIGERANTE FANTA 2L LARANJA</t>
         </is>
       </c>
     </row>
     <row r="1598">
-      <c r="A1598" s="13" t="n">
+      <c r="A1598" s="9" t="n">
         <v>104403</v>
       </c>
-      <c r="B1598" s="13" t="inlineStr">
+      <c r="B1598" s="9" t="inlineStr">
         <is>
           <t>#05 BEBIDA - #00 BEBIDAS GASEIFICADAS</t>
         </is>
       </c>
-      <c r="C1598" s="13" t="inlineStr">
+      <c r="C1598" s="9" t="inlineStr">
         <is>
           <t>REFRIG FANTA UVA 2L</t>
         </is>
       </c>
-      <c r="D1598" s="13" t="inlineStr">
+      <c r="D1598" s="9" t="inlineStr">
         <is>
           <t>REFRIGERANTE FANTA 2L UVA</t>
         </is>
@@ -32531,20 +32535,20 @@
       </c>
     </row>
     <row r="1600">
-      <c r="A1600" s="21" t="n">
+      <c r="A1600" s="13" t="n">
         <v>104410</v>
       </c>
-      <c r="B1600" s="21" t="inlineStr">
+      <c r="B1600" s="13" t="inlineStr">
         <is>
           <t>#05 BEBIDA - #00 BEBIDAS GASEIFICADAS</t>
         </is>
       </c>
-      <c r="C1600" s="21" t="inlineStr">
+      <c r="C1600" s="13" t="inlineStr">
         <is>
           <t>REFRIG GUARANA ANTARCTICA 2L PET ORIG</t>
         </is>
       </c>
-      <c r="D1600" s="21" t="inlineStr">
+      <c r="D1600" s="13" t="inlineStr">
         <is>
           <t>REFRIGERANTE GUARANA ANTARCTICA 2L</t>
         </is>
@@ -33631,40 +33635,40 @@
       </c>
     </row>
     <row r="1655">
-      <c r="A1655" s="13" t="n">
+      <c r="A1655" s="9" t="n">
         <v>156763</v>
       </c>
-      <c r="B1655" s="13" t="inlineStr">
+      <c r="B1655" s="9" t="inlineStr">
         <is>
           <t>#05 BEBIDA - #00 ENERGÉTICOS</t>
         </is>
       </c>
-      <c r="C1655" s="13" t="inlineStr">
+      <c r="C1655" s="9" t="inlineStr">
         <is>
           <t>ENERGETICO EXTRA POWER 1LT 250 ML GRATIS</t>
         </is>
       </c>
-      <c r="D1655" s="13" t="inlineStr">
+      <c r="D1655" s="9" t="inlineStr">
         <is>
           <t>ENERGETICO EXTRA POWER 1L PROMOCIONAL</t>
         </is>
       </c>
     </row>
     <row r="1656">
-      <c r="A1656" s="13" t="n">
+      <c r="A1656" s="9" t="n">
         <v>102287</v>
       </c>
-      <c r="B1656" s="13" t="inlineStr">
+      <c r="B1656" s="9" t="inlineStr">
         <is>
           <t>#05 BEBIDA - #00 ENERGÉTICOS</t>
         </is>
       </c>
-      <c r="C1656" s="13" t="inlineStr">
+      <c r="C1656" s="9" t="inlineStr">
         <is>
           <t>ENERGETICO EXTRA POWER 270ML UNID</t>
         </is>
       </c>
-      <c r="D1656" s="13" t="inlineStr">
+      <c r="D1656" s="9" t="inlineStr">
         <is>
           <t>ENERGETICO EXTRA POWER 270ML</t>
         </is>
@@ -34051,40 +34055,40 @@
       </c>
     </row>
     <row r="1676">
-      <c r="A1676" s="13" t="n">
+      <c r="A1676" s="9" t="n">
         <v>286325</v>
       </c>
-      <c r="B1676" s="13" t="inlineStr">
+      <c r="B1676" s="9" t="inlineStr">
         <is>
           <t>#05 BEBIDA - #01 SUCOS PRONTOS</t>
         </is>
       </c>
-      <c r="C1676" s="13" t="inlineStr">
+      <c r="C1676" s="9" t="inlineStr">
         <is>
           <t>SUCO DE UVA AURORA 1,5LT TINTO TP</t>
         </is>
       </c>
-      <c r="D1676" s="13" t="inlineStr">
+      <c r="D1676" s="9" t="inlineStr">
         <is>
           <t>SUCO AURORA TP 1,5L UVA TINTO</t>
         </is>
       </c>
     </row>
     <row r="1677">
-      <c r="A1677" s="21" t="n">
+      <c r="A1677" s="13" t="n">
         <v>102237</v>
       </c>
-      <c r="B1677" s="21" t="inlineStr">
+      <c r="B1677" s="13" t="inlineStr">
         <is>
           <t>#05 BEBIDA - #01 SUCOS PRONTOS</t>
         </is>
       </c>
-      <c r="C1677" s="21" t="inlineStr">
+      <c r="C1677" s="13" t="inlineStr">
         <is>
           <t>SUCO UVA INTEGRAL TINTO AURORA 1,5L VD</t>
         </is>
       </c>
-      <c r="D1677" s="21" t="inlineStr">
+      <c r="D1677" s="13" t="inlineStr">
         <is>
           <t>SUCO AURORA VIDRO 1,5L UVA INTEGRAL TINTO</t>
         </is>
@@ -34631,20 +34635,20 @@
       </c>
     </row>
     <row r="1705">
-      <c r="A1705" s="21" t="n">
+      <c r="A1705" s="13" t="n">
         <v>102149</v>
       </c>
-      <c r="B1705" s="21" t="inlineStr">
+      <c r="B1705" s="13" t="inlineStr">
         <is>
           <t>#05 BEBIDA - #01 SUCOS PRONTOS</t>
         </is>
       </c>
-      <c r="C1705" s="21" t="inlineStr">
+      <c r="C1705" s="13" t="inlineStr">
         <is>
           <t>SUCO PRONTO DAFRUTA 1L CAJU</t>
         </is>
       </c>
-      <c r="D1705" s="21" t="inlineStr">
+      <c r="D1705" s="13" t="inlineStr">
         <is>
           <t>SUCO PRONTO DAFRUTA 1L CAJU</t>
         </is>
@@ -34711,20 +34715,20 @@
       </c>
     </row>
     <row r="1709">
-      <c r="A1709" s="13" t="n">
+      <c r="A1709" s="9" t="n">
         <v>264452</v>
       </c>
-      <c r="B1709" s="13" t="inlineStr">
+      <c r="B1709" s="9" t="inlineStr">
         <is>
           <t>#05 BEBIDA - #01 SUCOS PRONTOS</t>
         </is>
       </c>
-      <c r="C1709" s="13" t="inlineStr">
+      <c r="C1709" s="9" t="inlineStr">
         <is>
           <t>SUCO PRONTO DAFRUTA 1L NECTAR UVA</t>
         </is>
       </c>
-      <c r="D1709" s="13" t="inlineStr">
+      <c r="D1709" s="9" t="inlineStr">
         <is>
           <t>SUCO PRONTO DAFRUTA 1L NECTAR UVA</t>
         </is>
@@ -35291,20 +35295,20 @@
       </c>
     </row>
     <row r="1738">
-      <c r="A1738" s="21" t="n">
+      <c r="A1738" s="13" t="n">
         <v>247799</v>
       </c>
-      <c r="B1738" s="21" t="inlineStr">
+      <c r="B1738" s="13" t="inlineStr">
         <is>
           <t>#05 BEBIDA - CERVEJAS</t>
         </is>
       </c>
-      <c r="C1738" s="21" t="inlineStr">
+      <c r="C1738" s="13" t="inlineStr">
         <is>
           <t>CERV BUDWEISER 330ML LAGER LN C/ 6 UNID</t>
         </is>
       </c>
-      <c r="D1738" s="21" t="inlineStr">
+      <c r="D1738" s="13" t="inlineStr">
         <is>
           <t>CERVEJA BUDWEISER LAGER LONG NECK 330ML</t>
         </is>
@@ -35411,20 +35415,20 @@
       </c>
     </row>
     <row r="1744">
-      <c r="A1744" s="13" t="n">
+      <c r="A1744" s="9" t="n">
         <v>220499</v>
       </c>
-      <c r="B1744" s="13" t="inlineStr">
+      <c r="B1744" s="9" t="inlineStr">
         <is>
           <t>#05 BEBIDA - CERVEJAS</t>
         </is>
       </c>
-      <c r="C1744" s="13" t="inlineStr">
+      <c r="C1744" s="9" t="inlineStr">
         <is>
           <t>CORONA EXTRA N LONG NECK 330ML</t>
         </is>
       </c>
-      <c r="D1744" s="13" t="inlineStr">
+      <c r="D1744" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">CERVEJA CORONA EXTRA LONG NECK 330ML </t>
         </is>
@@ -35531,20 +35535,20 @@
       </c>
     </row>
     <row r="1750">
-      <c r="A1750" t="n">
+      <c r="A1750" s="18" t="n">
         <v>265726</v>
       </c>
-      <c r="B1750" t="inlineStr">
+      <c r="B1750" s="18" t="inlineStr">
         <is>
           <t>#05 BEBIDA - CERVEJAS</t>
         </is>
       </c>
-      <c r="C1750" t="inlineStr">
+      <c r="C1750" s="18" t="inlineStr">
         <is>
           <t>CERVEJA HEINEKEN 269ML LATA UNID</t>
         </is>
       </c>
-      <c r="D1750" t="inlineStr">
+      <c r="D1750" s="18" t="inlineStr">
         <is>
           <t>CERVEJA HEINEKEN 269ML</t>
         </is>
@@ -35771,20 +35775,20 @@
       </c>
     </row>
     <row r="1762">
-      <c r="A1762" t="n">
+      <c r="A1762" s="18" t="n">
         <v>302401</v>
       </c>
-      <c r="B1762" t="inlineStr">
+      <c r="B1762" s="18" t="inlineStr">
         <is>
           <t>#05 BEBIDA - CERVEJAS</t>
         </is>
       </c>
-      <c r="C1762" t="inlineStr">
+      <c r="C1762" s="18" t="inlineStr">
         <is>
           <t>CERVEJA IMPERIO ULTRA 275ML LN</t>
         </is>
       </c>
-      <c r="D1762" t="inlineStr">
+      <c r="D1762" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">CERVEJA IMPERIO ULTRA LONG NECK 275ML </t>
         </is>
@@ -36011,40 +36015,40 @@
       </c>
     </row>
     <row r="1774">
-      <c r="A1774" s="13" t="n">
+      <c r="A1774" s="19" t="n">
         <v>259589</v>
       </c>
-      <c r="B1774" s="13" t="inlineStr">
+      <c r="B1774" s="19" t="inlineStr">
         <is>
           <t>#05 BEBIDA - CERVEJAS</t>
         </is>
       </c>
-      <c r="C1774" s="13" t="inlineStr">
+      <c r="C1774" s="19" t="inlineStr">
         <is>
           <t>STELLA ARTOIS ONE WAY 600ML</t>
         </is>
       </c>
-      <c r="D1774" s="13" t="inlineStr">
+      <c r="D1774" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">CERVEJA STELLA ARTOIS ONE WAY 600ML </t>
         </is>
       </c>
     </row>
     <row r="1775">
-      <c r="A1775" s="13" t="n">
+      <c r="A1775" s="9" t="n">
         <v>288739</v>
       </c>
-      <c r="B1775" s="13" t="inlineStr">
+      <c r="B1775" s="9" t="inlineStr">
         <is>
           <t>#05 BEBIDA - CERVEJAS</t>
         </is>
       </c>
-      <c r="C1775" s="13" t="inlineStr">
+      <c r="C1775" s="9" t="inlineStr">
         <is>
           <t>CERV STELLA ARTOIS 330ML PURE GOLD UNID</t>
         </is>
       </c>
-      <c r="D1775" s="13" t="inlineStr">
+      <c r="D1775" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">CERVEJA STELLA ARTOIS PURE GOLD LONG NECK 330ML </t>
         </is>
@@ -36191,20 +36195,20 @@
       </c>
     </row>
     <row r="1783">
-      <c r="A1783" s="13" t="n">
+      <c r="A1783" s="9" t="n">
         <v>258893</v>
       </c>
-      <c r="B1783" s="13" t="inlineStr">
+      <c r="B1783" s="9" t="inlineStr">
         <is>
           <t>#05 BEBIDA - CERVEJAS CX</t>
         </is>
       </c>
-      <c r="C1783" s="13" t="inlineStr">
+      <c r="C1783" s="9" t="inlineStr">
         <is>
           <t>CERV ANTARCTICA ORIGINAL LT 269ML C/8</t>
         </is>
       </c>
-      <c r="D1783" s="13" t="inlineStr">
+      <c r="D1783" s="9" t="inlineStr">
         <is>
           <t>CERVEJA ANTARCTICA ORIGINAL 15 X 269ML</t>
         </is>
@@ -36271,20 +36275,20 @@
       </c>
     </row>
     <row r="1787">
-      <c r="A1787" s="21" t="n">
+      <c r="A1787" s="13" t="n">
         <v>168712</v>
       </c>
-      <c r="B1787" s="21" t="inlineStr">
+      <c r="B1787" s="13" t="inlineStr">
         <is>
           <t>#05 BEBIDA - CERVEJAS CX</t>
         </is>
       </c>
-      <c r="C1787" s="21" t="inlineStr">
+      <c r="C1787" s="13" t="inlineStr">
         <is>
           <t>CERV ANTARCTICA 269ML C/ 15UND</t>
         </is>
       </c>
-      <c r="D1787" s="21" t="inlineStr">
+      <c r="D1787" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">CERVEJA ANTARCTICA PILSEN 15 X 269ML </t>
         </is>
@@ -36331,20 +36335,20 @@
       </c>
     </row>
     <row r="1790">
-      <c r="A1790" s="13" t="n">
+      <c r="A1790" s="9" t="n">
         <v>170451</v>
       </c>
-      <c r="B1790" s="13" t="inlineStr">
+      <c r="B1790" s="9" t="inlineStr">
         <is>
           <t>#05 BEBIDA - CERVEJAS CX</t>
         </is>
       </c>
-      <c r="C1790" s="13" t="inlineStr">
+      <c r="C1790" s="9" t="inlineStr">
         <is>
           <t>CERV BRAHMA CHOPP LATA 269ML C/ 15 UNID</t>
         </is>
       </c>
-      <c r="D1790" s="13" t="inlineStr">
+      <c r="D1790" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">CERVEJA BRAHMA CHOPP 15 X 269ML </t>
         </is>
@@ -36591,20 +36595,20 @@
       </c>
     </row>
     <row r="1803">
-      <c r="A1803" s="13" t="n">
+      <c r="A1803" s="9" t="n">
         <v>271001</v>
       </c>
-      <c r="B1803" s="13" t="inlineStr">
+      <c r="B1803" s="9" t="inlineStr">
         <is>
           <t>#05 BEBIDA - CERVEJAS CX</t>
         </is>
       </c>
-      <c r="C1803" s="13" t="inlineStr">
+      <c r="C1803" s="9" t="inlineStr">
         <is>
           <t>CERVEJA IMPERIO 15X269ML PURO MALTE</t>
         </is>
       </c>
-      <c r="D1803" s="13" t="inlineStr">
+      <c r="D1803" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">CERVEJA IMPERIO PURO MALTE 12 X 269ML </t>
         </is>
@@ -36711,20 +36715,20 @@
       </c>
     </row>
     <row r="1809">
-      <c r="A1809" s="21" t="n">
+      <c r="A1809" s="13" t="n">
         <v>324556</v>
       </c>
-      <c r="B1809" s="21" t="inlineStr">
+      <c r="B1809" s="13" t="inlineStr">
         <is>
           <t>#05 BEBIDA - CERVEJAS CX</t>
         </is>
       </c>
-      <c r="C1809" s="21" t="inlineStr">
+      <c r="C1809" s="13" t="inlineStr">
         <is>
           <t>CERVEJA SKOL PILSEN 269ML CAIXA C/15 MUL</t>
         </is>
       </c>
-      <c r="D1809" s="21" t="inlineStr">
+      <c r="D1809" s="13" t="inlineStr">
         <is>
           <t>CERVEJA SKOL PILSEN 15 X 269ML</t>
         </is>
@@ -37011,20 +37015,20 @@
       </c>
     </row>
     <row r="1824">
-      <c r="A1824" s="13" t="n">
+      <c r="A1824" s="9" t="n">
         <v>236673</v>
       </c>
-      <c r="B1824" s="13" t="inlineStr">
+      <c r="B1824" s="9" t="inlineStr">
         <is>
           <t>#05 BEBIDA - DESTILADOS</t>
         </is>
       </c>
-      <c r="C1824" s="13" t="inlineStr">
+      <c r="C1824" s="9" t="inlineStr">
         <is>
           <t>BEB FIU FIU TANGERINA ACEROLA 750ML</t>
         </is>
       </c>
-      <c r="D1824" s="13" t="inlineStr">
+      <c r="D1824" s="9" t="inlineStr">
         <is>
           <t>BEBIDA ALCOOLICA FIU FIU 750ML TANGERINA ACEROLA</t>
         </is>
@@ -37111,20 +37115,20 @@
       </c>
     </row>
     <row r="1829">
-      <c r="A1829" s="21" t="n">
+      <c r="A1829" s="13" t="n">
         <v>102085</v>
       </c>
-      <c r="B1829" s="21" t="inlineStr">
+      <c r="B1829" s="13" t="inlineStr">
         <is>
           <t>#05 BEBIDA - DESTILADOS</t>
         </is>
       </c>
-      <c r="C1829" s="21" t="inlineStr">
+      <c r="C1829" s="13" t="inlineStr">
         <is>
           <t>CACHACA 51 PIRASSUNUNGA 965ML TRAD</t>
         </is>
       </c>
-      <c r="D1829" s="21" t="inlineStr">
+      <c r="D1829" s="13" t="inlineStr">
         <is>
           <t>CACHAÇA 51 965ML</t>
         </is>
@@ -37191,20 +37195,20 @@
       </c>
     </row>
     <row r="1833">
-      <c r="A1833" s="13" t="n">
+      <c r="A1833" s="9" t="n">
         <v>265045</v>
       </c>
-      <c r="B1833" s="13" t="inlineStr">
+      <c r="B1833" s="9" t="inlineStr">
         <is>
           <t>#05 BEBIDA - DESTILADOS</t>
         </is>
       </c>
-      <c r="C1833" s="13" t="inlineStr">
+      <c r="C1833" s="9" t="inlineStr">
         <is>
           <t>CACHACA INDIAZINHA 750ML BANANINHA MISTA</t>
         </is>
       </c>
-      <c r="D1833" s="13" t="inlineStr">
+      <c r="D1833" s="9" t="inlineStr">
         <is>
           <t>CACHAÇA INDIAZINHA 750ML BANANINHA MISTA</t>
         </is>
@@ -37511,20 +37515,20 @@
       </c>
     </row>
     <row r="1849">
-      <c r="A1849" s="13" t="n">
+      <c r="A1849" s="9" t="n">
         <v>301843</v>
       </c>
-      <c r="B1849" s="13" t="inlineStr">
+      <c r="B1849" s="9" t="inlineStr">
         <is>
           <t>#05 BEBIDA - DESTILADOS</t>
         </is>
       </c>
-      <c r="C1849" s="13" t="inlineStr">
+      <c r="C1849" s="9" t="inlineStr">
         <is>
           <t>APERITIVO BITER CAMPARI 998ML</t>
         </is>
       </c>
-      <c r="D1849" s="13" t="inlineStr">
+      <c r="D1849" s="9" t="inlineStr">
         <is>
           <t>CAMPARI 998ML</t>
         </is>
@@ -37571,20 +37575,20 @@
       </c>
     </row>
     <row r="1852">
-      <c r="A1852" s="13" t="n">
+      <c r="A1852" s="9" t="n">
         <v>284865</v>
       </c>
-      <c r="B1852" s="13" t="inlineStr">
+      <c r="B1852" s="9" t="inlineStr">
         <is>
           <t>#05 BEBIDA - DESTILADOS</t>
         </is>
       </c>
-      <c r="C1852" s="13" t="inlineStr">
+      <c r="C1852" s="9" t="inlineStr">
         <is>
           <t>CONHAQUE DREHER 900ML ORIGINAL</t>
         </is>
       </c>
-      <c r="D1852" s="13" t="inlineStr">
+      <c r="D1852" s="9" t="inlineStr">
         <is>
           <t>CONHAQUE DREHER 900ML ORIGINAL</t>
         </is>
@@ -37611,20 +37615,20 @@
       </c>
     </row>
     <row r="1854">
-      <c r="A1854" s="13" t="n">
+      <c r="A1854" s="9" t="n">
         <v>102243</v>
       </c>
-      <c r="B1854" s="13" t="inlineStr">
+      <c r="B1854" s="9" t="inlineStr">
         <is>
           <t>#05 BEBIDA - DESTILADOS</t>
         </is>
       </c>
-      <c r="C1854" s="13" t="inlineStr">
+      <c r="C1854" s="9" t="inlineStr">
         <is>
           <t>CONHAQUE SAO JOAO DA BARRA 900ML TRAD</t>
         </is>
       </c>
-      <c r="D1854" s="13" t="inlineStr">
+      <c r="D1854" s="9" t="inlineStr">
         <is>
           <t>CONHAQUE SÃO JOÃO DA BARRA 900ML TRADICIONAL</t>
         </is>
@@ -37791,20 +37795,20 @@
       </c>
     </row>
     <row r="1863">
-      <c r="A1863" s="13" t="n">
+      <c r="A1863" s="9" t="n">
         <v>230698</v>
       </c>
-      <c r="B1863" s="13" t="inlineStr">
+      <c r="B1863" s="9" t="inlineStr">
         <is>
           <t>#05 BEBIDA - DESTILADOS</t>
         </is>
       </c>
-      <c r="C1863" s="13" t="inlineStr">
+      <c r="C1863" s="9" t="inlineStr">
         <is>
           <t>BE GIN TANQUERAI TEN 750 ML 750 ML</t>
         </is>
       </c>
-      <c r="D1863" s="13" t="inlineStr">
+      <c r="D1863" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">GIN TANQUERAI 750ML TEN </t>
         </is>
@@ -38111,20 +38115,20 @@
       </c>
     </row>
     <row r="1879">
-      <c r="A1879" s="13" t="n">
+      <c r="A1879" s="9" t="n">
         <v>134156</v>
       </c>
-      <c r="B1879" s="13" t="inlineStr">
+      <c r="B1879" s="9" t="inlineStr">
         <is>
           <t>#05 BEBIDA - DESTILADOS</t>
         </is>
       </c>
-      <c r="C1879" s="13" t="inlineStr">
+      <c r="C1879" s="9" t="inlineStr">
         <is>
           <t>VODKA SKYY 980ML</t>
         </is>
       </c>
-      <c r="D1879" s="13" t="inlineStr">
+      <c r="D1879" s="9" t="inlineStr">
         <is>
           <t>VODKA SKYY 980ML</t>
         </is>
@@ -38351,40 +38355,40 @@
       </c>
     </row>
     <row r="1891">
-      <c r="A1891" s="13" t="n">
+      <c r="A1891" s="9" t="n">
         <v>262730</v>
       </c>
-      <c r="B1891" s="13" t="inlineStr">
+      <c r="B1891" s="9" t="inlineStr">
         <is>
           <t>#05 BEBIDA - DESTILADOS</t>
         </is>
       </c>
-      <c r="C1891" s="13" t="inlineStr">
+      <c r="C1891" s="9" t="inlineStr">
         <is>
           <t>WHISKY BUCHANANS 750ML DELUXE 12 ANOS</t>
         </is>
       </c>
-      <c r="D1891" s="13" t="inlineStr">
+      <c r="D1891" s="9" t="inlineStr">
         <is>
           <t>WHISKY BUCHANANS 750ML DELUXE 12 ANOS</t>
         </is>
       </c>
     </row>
     <row r="1892">
-      <c r="A1892" s="13" t="n">
+      <c r="A1892" s="9" t="n">
         <v>109727</v>
       </c>
-      <c r="B1892" s="13" t="inlineStr">
+      <c r="B1892" s="9" t="inlineStr">
         <is>
           <t>#05 BEBIDA - DESTILADOS</t>
         </is>
       </c>
-      <c r="C1892" s="13" t="inlineStr">
+      <c r="C1892" s="9" t="inlineStr">
         <is>
           <t>WHISKY CHIVAS REGAL 12ANOS 1LT</t>
         </is>
       </c>
-      <c r="D1892" s="13" t="inlineStr">
+      <c r="D1892" s="9" t="inlineStr">
         <is>
           <t>WHISKY CHIVAS REGAL 1L 12 ANOS</t>
         </is>
@@ -38551,20 +38555,20 @@
       </c>
     </row>
     <row r="1901">
-      <c r="A1901" s="13" t="n">
+      <c r="A1901" s="9" t="n">
         <v>102077</v>
       </c>
-      <c r="B1901" s="13" t="inlineStr">
+      <c r="B1901" s="9" t="inlineStr">
         <is>
           <t>#05 BEBIDA - DESTILADOS</t>
         </is>
       </c>
-      <c r="C1901" s="13" t="inlineStr">
+      <c r="C1901" s="9" t="inlineStr">
         <is>
           <t>WHISKY OLD PARR 12 ANOS 1L</t>
         </is>
       </c>
-      <c r="D1901" s="13" t="inlineStr">
+      <c r="D1901" s="9" t="inlineStr">
         <is>
           <t>WHISKY OLD PARR 1L 12 ANOS</t>
         </is>
@@ -38751,20 +38755,20 @@
       </c>
     </row>
     <row r="1911">
-      <c r="A1911" s="21" t="n">
+      <c r="A1911" s="13" t="n">
         <v>295198</v>
       </c>
-      <c r="B1911" s="21" t="inlineStr">
+      <c r="B1911" s="13" t="inlineStr">
         <is>
           <t>#05 BEBIDA - FERMENTADOS</t>
         </is>
       </c>
-      <c r="C1911" s="21" t="inlineStr">
+      <c r="C1911" s="13" t="inlineStr">
         <is>
           <t>CHOPP DE VINHO STEMPEL 600ML RED</t>
         </is>
       </c>
-      <c r="D1911" s="21" t="inlineStr">
+      <c r="D1911" s="13" t="inlineStr">
         <is>
           <t>CHOPP DE VINHO STEMPEL 600ML RED</t>
         </is>
@@ -39191,20 +39195,20 @@
       </c>
     </row>
     <row r="1933">
-      <c r="A1933" s="13" t="n">
+      <c r="A1933" s="9" t="n">
         <v>147495</v>
       </c>
-      <c r="B1933" s="13" t="inlineStr">
+      <c r="B1933" s="9" t="inlineStr">
         <is>
           <t>#05 BEBIDA - FERMENTADOS</t>
         </is>
       </c>
-      <c r="C1933" s="13" t="inlineStr">
+      <c r="C1933" s="9" t="inlineStr">
         <is>
           <t>VINHO PERGOLA 2LT TINTO SUAVE</t>
         </is>
       </c>
-      <c r="D1933" s="13" t="inlineStr">
+      <c r="D1933" s="9" t="inlineStr">
         <is>
           <t>VINHO PERGOLA 2L TINTO SUAVE</t>
         </is>
@@ -39431,20 +39435,20 @@
       </c>
     </row>
     <row r="1945">
-      <c r="A1945" s="3" t="n">
+      <c r="A1945" s="23" t="n">
         <v>328966</v>
       </c>
-      <c r="B1945" s="3" t="inlineStr">
+      <c r="B1945" s="23" t="inlineStr">
         <is>
           <t>#05 OVOS</t>
         </is>
       </c>
-      <c r="C1945" s="3" t="inlineStr">
+      <c r="C1945" s="16" t="inlineStr">
         <is>
           <t>OVOS BRANCOS IANA C/30UN</t>
         </is>
       </c>
-      <c r="D1945" s="3" t="inlineStr">
+      <c r="D1945" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">OVOS DE GRANJA IANA BDJ 30UN BRANCOS </t>
         </is>
@@ -39651,20 +39655,20 @@
       </c>
     </row>
     <row r="1956">
-      <c r="A1956" s="21" t="n">
+      <c r="A1956" s="13" t="n">
         <v>207640</v>
       </c>
-      <c r="B1956" s="21" t="inlineStr">
+      <c r="B1956" s="13" t="inlineStr">
         <is>
           <t>#06 LIMPEZA - ALVEJANTES E ÁGUA SANITÁRIA</t>
         </is>
       </c>
-      <c r="C1956" s="21" t="inlineStr">
+      <c r="C1956" s="13" t="inlineStr">
         <is>
           <t>ÁGUA SANITÁRIA LAVABEM 2L</t>
         </is>
       </c>
-      <c r="D1956" s="21" t="inlineStr">
+      <c r="D1956" s="13" t="inlineStr">
         <is>
           <t>ÁGUA SANITÁRIA LAVABEM 2L</t>
         </is>
@@ -39731,20 +39735,20 @@
       </c>
     </row>
     <row r="1960">
-      <c r="A1960" s="13" t="n">
+      <c r="A1960" s="9" t="n">
         <v>257145</v>
       </c>
-      <c r="B1960" s="13" t="inlineStr">
+      <c r="B1960" s="9" t="inlineStr">
         <is>
           <t>#06 LIMPEZA - ALVEJANTES E ÁGUA SANITÁRIA</t>
         </is>
       </c>
-      <c r="C1960" s="13" t="inlineStr">
+      <c r="C1960" s="9" t="inlineStr">
         <is>
           <t>AGUA SANITARIA TUBARAO 1L</t>
         </is>
       </c>
-      <c r="D1960" s="13" t="inlineStr">
+      <c r="D1960" s="9" t="inlineStr">
         <is>
           <t>ÁGUA SANITARIA TUBARÃO 1L</t>
         </is>
@@ -41111,20 +41115,20 @@
       </c>
     </row>
     <row r="2029">
-      <c r="A2029" s="21" t="n">
+      <c r="A2029" s="13" t="n">
         <v>330053</v>
       </c>
-      <c r="B2029" s="21" t="inlineStr">
+      <c r="B2029" s="13" t="inlineStr">
         <is>
           <t>#06 LIMPEZA - AMACIANTES</t>
         </is>
       </c>
-      <c r="C2029" s="21" t="inlineStr">
+      <c r="C2029" s="13" t="inlineStr">
         <is>
           <t>AMACIANTE ROU YPÊ 1,6L ACONCHEGO</t>
         </is>
       </c>
-      <c r="D2029" s="21" t="inlineStr">
+      <c r="D2029" s="13" t="inlineStr">
         <is>
           <t>AMACIANTE DE ROUPAS YPÊ 1,6L ACONCHEGO</t>
         </is>
@@ -42651,40 +42655,40 @@
       </c>
     </row>
     <row r="2106">
-      <c r="A2106" s="21" t="n">
+      <c r="A2106" s="13" t="n">
         <v>148554</v>
       </c>
-      <c r="B2106" s="21" t="inlineStr">
+      <c r="B2106" s="13" t="inlineStr">
         <is>
           <t>#06 LIMPEZA - DESINFETANTES</t>
         </is>
       </c>
-      <c r="C2106" s="21" t="inlineStr">
+      <c r="C2106" s="13" t="inlineStr">
         <is>
           <t>DESINFETANTE BAK YPÊ EUCALIPTO 2LTS</t>
         </is>
       </c>
-      <c r="D2106" s="21" t="inlineStr">
+      <c r="D2106" s="13" t="inlineStr">
         <is>
           <t>DESINFETANTE YPÊ BAK 2L EUCALIPTO</t>
         </is>
       </c>
     </row>
     <row r="2107">
-      <c r="A2107" s="21" t="n">
+      <c r="A2107" s="13" t="n">
         <v>134193</v>
       </c>
-      <c r="B2107" s="21" t="inlineStr">
+      <c r="B2107" s="13" t="inlineStr">
         <is>
           <t>#06 LIMPEZA - DESINFETANTES</t>
         </is>
       </c>
-      <c r="C2107" s="21" t="inlineStr">
+      <c r="C2107" s="13" t="inlineStr">
         <is>
           <t>DESINFETANTE BAK YPÊ FLORAL 2LTS</t>
         </is>
       </c>
-      <c r="D2107" s="21" t="inlineStr">
+      <c r="D2107" s="13" t="inlineStr">
         <is>
           <t>DESINFETANTE YPÊ BAK 2L FLORAL</t>
         </is>
@@ -43191,100 +43195,100 @@
       </c>
     </row>
     <row r="2133">
-      <c r="A2133" s="21" t="n">
+      <c r="A2133" s="13" t="n">
         <v>100391</v>
       </c>
-      <c r="B2133" s="21" t="inlineStr">
+      <c r="B2133" s="13" t="inlineStr">
         <is>
           <t>#06 LIMPEZA - DETERGENTES</t>
         </is>
       </c>
-      <c r="C2133" s="21" t="inlineStr">
+      <c r="C2133" s="13" t="inlineStr">
         <is>
           <t>DETERGENTE LIQUIDO YPÊ 500ML CAPIM LIMAO</t>
         </is>
       </c>
-      <c r="D2133" s="21" t="inlineStr">
+      <c r="D2133" s="13" t="inlineStr">
         <is>
           <t>DETERGENTE LIQUIDO YPÊ 500ML CAPIM LIMÃO</t>
         </is>
       </c>
     </row>
     <row r="2134">
-      <c r="A2134" s="21" t="n">
+      <c r="A2134" s="13" t="n">
         <v>100394</v>
       </c>
-      <c r="B2134" s="21" t="inlineStr">
+      <c r="B2134" s="13" t="inlineStr">
         <is>
           <t>#06 LIMPEZA - DETERGENTES</t>
         </is>
       </c>
-      <c r="C2134" s="21" t="inlineStr">
+      <c r="C2134" s="13" t="inlineStr">
         <is>
           <t>DETERGENTE LIQUIDO YPÊ 500ML CLEAR</t>
         </is>
       </c>
-      <c r="D2134" s="21" t="inlineStr">
+      <c r="D2134" s="13" t="inlineStr">
         <is>
           <t>DETERGENTE LIQUIDO YPÊ 500ML CLEAR</t>
         </is>
       </c>
     </row>
     <row r="2135">
-      <c r="A2135" s="21" t="n">
+      <c r="A2135" s="13" t="n">
         <v>100392</v>
       </c>
-      <c r="B2135" s="21" t="inlineStr">
+      <c r="B2135" s="13" t="inlineStr">
         <is>
           <t>#06 LIMPEZA - DETERGENTES</t>
         </is>
       </c>
-      <c r="C2135" s="21" t="inlineStr">
+      <c r="C2135" s="13" t="inlineStr">
         <is>
           <t>DETERGENTE LIQUIDO YPÊ 500ML CLEAR CARE</t>
         </is>
       </c>
-      <c r="D2135" s="21" t="inlineStr">
+      <c r="D2135" s="13" t="inlineStr">
         <is>
           <t>DETERGENTE LIQUIDO YPÊ 500ML CLEAR CARE</t>
         </is>
       </c>
     </row>
     <row r="2136">
-      <c r="A2136" s="21" t="n">
+      <c r="A2136" s="13" t="n">
         <v>100402</v>
       </c>
-      <c r="B2136" s="21" t="inlineStr">
+      <c r="B2136" s="13" t="inlineStr">
         <is>
           <t>#06 LIMPEZA - DETERGENTES</t>
         </is>
       </c>
-      <c r="C2136" s="21" t="inlineStr">
+      <c r="C2136" s="13" t="inlineStr">
         <is>
           <t>DETERGENTE LIQUIDO YPÊ 500ML COCO</t>
         </is>
       </c>
-      <c r="D2136" s="21" t="inlineStr">
+      <c r="D2136" s="13" t="inlineStr">
         <is>
           <t>DETERGENTE LIQUIDO YPÊ 500ML COCO</t>
         </is>
       </c>
     </row>
     <row r="2137">
-      <c r="A2137" s="21" t="n">
+      <c r="A2137" s="13" t="n">
         <v>100403</v>
       </c>
-      <c r="B2137" s="21" t="inlineStr">
+      <c r="B2137" s="13" t="inlineStr">
         <is>
           <t>#06 LIMPEZA - DETERGENTES</t>
         </is>
       </c>
-      <c r="C2137" s="21" t="inlineStr">
+      <c r="C2137" s="13" t="inlineStr">
         <is>
           <t>DETERGENTE LIQUIDO YPÊ 500ML LIMAO</t>
         </is>
       </c>
-      <c r="D2137" s="21" t="inlineStr">
+      <c r="D2137" s="13" t="inlineStr">
         <is>
           <t>DETERGENTE LIQUIDO YPÊ 500ML LIMAO</t>
         </is>
@@ -43311,40 +43315,40 @@
       </c>
     </row>
     <row r="2139">
-      <c r="A2139" s="21" t="n">
+      <c r="A2139" s="13" t="n">
         <v>100393</v>
       </c>
-      <c r="B2139" s="21" t="inlineStr">
+      <c r="B2139" s="13" t="inlineStr">
         <is>
           <t>#06 LIMPEZA - DETERGENTES</t>
         </is>
       </c>
-      <c r="C2139" s="21" t="inlineStr">
+      <c r="C2139" s="13" t="inlineStr">
         <is>
           <t>DETERGENTE LIQUIDO YPÊ 500ML MACA</t>
         </is>
       </c>
-      <c r="D2139" s="21" t="inlineStr">
+      <c r="D2139" s="13" t="inlineStr">
         <is>
           <t>DETERGENTE LIQUIDO YPÊ 500ML MACA</t>
         </is>
       </c>
     </row>
     <row r="2140">
-      <c r="A2140" s="21" t="n">
+      <c r="A2140" s="13" t="n">
         <v>100390</v>
       </c>
-      <c r="B2140" s="21" t="inlineStr">
+      <c r="B2140" s="13" t="inlineStr">
         <is>
           <t>#06 LIMPEZA - DETERGENTES</t>
         </is>
       </c>
-      <c r="C2140" s="21" t="inlineStr">
+      <c r="C2140" s="13" t="inlineStr">
         <is>
           <t>DETERGENTE LIQUIDO YPÊ 500ML NEUTRO</t>
         </is>
       </c>
-      <c r="D2140" s="21" t="inlineStr">
+      <c r="D2140" s="13" t="inlineStr">
         <is>
           <t>DETERGENTE LIQUIDO YPÊ 500ML NEUTRO</t>
         </is>
@@ -43731,40 +43735,40 @@
       </c>
     </row>
     <row r="2160">
-      <c r="A2160" s="21" t="n">
+      <c r="A2160" s="13" t="n">
         <v>100511</v>
       </c>
-      <c r="B2160" s="21" t="inlineStr">
+      <c r="B2160" s="13" t="inlineStr">
         <is>
           <t>#06 LIMPEZA - LIMPA ALUMINIO</t>
         </is>
       </c>
-      <c r="C2160" s="21" t="inlineStr">
+      <c r="C2160" s="13" t="inlineStr">
         <is>
           <t>LIMPA ALUMINIO POLITRIZ 500ML LIMAO</t>
         </is>
       </c>
-      <c r="D2160" s="21" t="inlineStr">
+      <c r="D2160" s="13" t="inlineStr">
         <is>
           <t>LIMPA ALUMINIO POLITRIZ 500ML LIMÃO</t>
         </is>
       </c>
     </row>
     <row r="2161">
-      <c r="A2161" s="21" t="n">
+      <c r="A2161" s="13" t="n">
         <v>122716</v>
       </c>
-      <c r="B2161" s="21" t="inlineStr">
+      <c r="B2161" s="13" t="inlineStr">
         <is>
           <t>#06 LIMPEZA - LIMPA ALUMINIO</t>
         </is>
       </c>
-      <c r="C2161" s="21" t="inlineStr">
+      <c r="C2161" s="13" t="inlineStr">
         <is>
           <t>LIMPA ALUMINIO POLITRIZ 500ML TRADICIONA</t>
         </is>
       </c>
-      <c r="D2161" s="21" t="inlineStr">
+      <c r="D2161" s="13" t="inlineStr">
         <is>
           <t>LIMPA ALUMINIO POLITRIZ 500ML TRADICIONAL</t>
         </is>
@@ -45231,20 +45235,20 @@
       </c>
     </row>
     <row r="2235">
-      <c r="A2235" s="21" t="n">
+      <c r="A2235" s="13" t="n">
         <v>261980</v>
       </c>
-      <c r="B2235" s="21" t="inlineStr">
+      <c r="B2235" s="13" t="inlineStr">
         <is>
           <t>#06 LIMPEZA - SABÃO</t>
         </is>
       </c>
-      <c r="C2235" s="21" t="inlineStr">
+      <c r="C2235" s="13" t="inlineStr">
         <is>
           <t>SABÃO EM PÓ BRILHANTE 1,6KG LIMPEZA TOTA</t>
         </is>
       </c>
-      <c r="D2235" s="21" t="inlineStr">
+      <c r="D2235" s="13" t="inlineStr">
         <is>
           <t>SABÃO EM PÓ BRILHANTE CAIXA 1,6KG LIMPEZA TOTAL</t>
         </is>
@@ -49151,20 +49155,20 @@
       </c>
     </row>
     <row r="2431">
-      <c r="A2431" t="n">
+      <c r="A2431" s="20" t="n">
         <v>293779</v>
       </c>
-      <c r="B2431" t="inlineStr">
+      <c r="B2431" s="20" t="inlineStr">
         <is>
           <t>#07 HIGIENE PESSOAL - CABELOS</t>
         </is>
       </c>
-      <c r="C2431" t="inlineStr">
+      <c r="C2431" s="20" t="inlineStr">
         <is>
           <t>KIT HASKELL SHAMPOO 500ML+ CONDICIONADOR</t>
         </is>
       </c>
-      <c r="D2431" t="inlineStr">
+      <c r="D2431" s="20" t="inlineStr">
         <is>
           <t>KIT SHAMPOO E CONDICIONADOR HASKELL 500ML MURUMURU</t>
         </is>
@@ -49411,40 +49415,40 @@
       </c>
     </row>
     <row r="2444">
-      <c r="A2444" t="n">
+      <c r="A2444" s="20" t="n">
         <v>297599</v>
       </c>
-      <c r="B2444" t="inlineStr">
+      <c r="B2444" s="20" t="inlineStr">
         <is>
           <t>#07 HIGIENE PESSOAL - CABELOS</t>
         </is>
       </c>
-      <c r="C2444" t="inlineStr">
+      <c r="C2444" s="20" t="inlineStr">
         <is>
           <t>SHAMPOO+COND INF TURMA XUXINHA 400+210ML</t>
         </is>
       </c>
-      <c r="D2444" t="inlineStr">
+      <c r="D2444" s="20" t="inlineStr">
         <is>
           <t>KIT SHAMPOO E CONDICIONADOR TURMA DA XUXINHA BARUEL 1KIT INFANTIL</t>
         </is>
       </c>
     </row>
     <row r="2445">
-      <c r="A2445" t="n">
+      <c r="A2445" s="20" t="n">
         <v>297570</v>
       </c>
-      <c r="B2445" t="inlineStr">
+      <c r="B2445" s="20" t="inlineStr">
         <is>
           <t>#07 HIGIENE PESSOAL - CABELOS</t>
         </is>
       </c>
-      <c r="C2445" t="inlineStr">
+      <c r="C2445" s="20" t="inlineStr">
         <is>
           <t>KIT SHAMPOO 400ML+COND 210ML BARUEL TURM</t>
         </is>
       </c>
-      <c r="D2445" t="inlineStr">
+      <c r="D2445" s="20" t="inlineStr">
         <is>
           <t>KIT SHAMPOO E CONDICIONADOR TURMA DA XUXINHA BARUEL 1KIT ORIGINAL</t>
         </is>
@@ -51131,20 +51135,20 @@
       </c>
     </row>
     <row r="2530">
-      <c r="A2530" t="n">
+      <c r="A2530" s="20" t="n">
         <v>182034</v>
       </c>
-      <c r="B2530" t="inlineStr">
+      <c r="B2530" s="20" t="inlineStr">
         <is>
           <t>#07 HIGIENE PESSOAL - DESODORANTE</t>
         </is>
       </c>
-      <c r="C2530" t="inlineStr">
+      <c r="C2530" s="20" t="inlineStr">
         <is>
           <t>DESODORANTE DOVE AEROSOL ORIGINAL 150ML</t>
         </is>
       </c>
-      <c r="D2530" t="inlineStr">
+      <c r="D2530" s="20" t="inlineStr">
         <is>
           <t>DESODORANTE DOVE AEROSOL 150ML ORIGINAL</t>
         </is>
@@ -55451,20 +55455,20 @@
       </c>
     </row>
     <row r="2746">
-      <c r="A2746" t="n">
+      <c r="A2746" s="20" t="n">
         <v>144267</v>
       </c>
-      <c r="B2746" t="inlineStr">
+      <c r="B2746" s="20" t="inlineStr">
         <is>
           <t>#07 HIGIENE PESSOAL - HIGIENE</t>
         </is>
       </c>
-      <c r="C2746" t="inlineStr">
+      <c r="C2746" s="20" t="inlineStr">
         <is>
           <t>COTONETES TOPZ POTE - 150X1</t>
         </is>
       </c>
-      <c r="D2746" t="inlineStr">
+      <c r="D2746" s="20" t="inlineStr">
         <is>
           <t>HASTES FLEXIVEIS TOPZ POTE 150UN</t>
         </is>
@@ -56111,20 +56115,20 @@
       </c>
     </row>
     <row r="2779">
-      <c r="A2779" t="n">
+      <c r="A2779" s="20" t="n">
         <v>135954</v>
       </c>
-      <c r="B2779" t="inlineStr">
+      <c r="B2779" s="20" t="inlineStr">
         <is>
           <t>#07 HIGIENE PESSOAL - INTIMA</t>
         </is>
       </c>
-      <c r="C2779" t="inlineStr">
+      <c r="C2779" s="20" t="inlineStr">
         <is>
           <t>ABS INTIMUS GEL NOTURNO SUAVE C/ABAS 8UN</t>
         </is>
       </c>
-      <c r="D2779" t="inlineStr">
+      <c r="D2779" s="20" t="inlineStr">
         <is>
           <t>ABSORVENTE INTIMUS GEL 8 X 1 1PCT NOTURNO SUAVE COM ABAS</t>
         </is>
@@ -57471,20 +57475,20 @@
       </c>
     </row>
     <row r="2847">
-      <c r="A2847" s="13" t="n">
+      <c r="A2847" s="9" t="n">
         <v>219705</v>
       </c>
-      <c r="B2847" s="13" t="inlineStr">
+      <c r="B2847" s="9" t="inlineStr">
         <is>
           <t>#07 HIGIENE PESSOAL - PAPEL HIGIENICO</t>
         </is>
       </c>
-      <c r="C2847" s="13" t="inlineStr">
+      <c r="C2847" s="9" t="inlineStr">
         <is>
           <t>PAPEL HIG MIMMO 30MTS LEV12 PAG11</t>
         </is>
       </c>
-      <c r="D2847" s="13" t="inlineStr">
+      <c r="D2847" s="9" t="inlineStr">
         <is>
           <t>PAPEL HIGIENICO MIMMO 12 X 30M PROMOCIONAL NEUTRO</t>
         </is>
@@ -57591,20 +57595,20 @@
       </c>
     </row>
     <row r="2853">
-      <c r="A2853" s="21" t="n">
+      <c r="A2853" s="13" t="n">
         <v>346964</v>
       </c>
-      <c r="B2853" s="21" t="inlineStr">
+      <c r="B2853" s="13" t="inlineStr">
         <is>
           <t>#07 HIGIENE PESSOAL - PAPEL HIGIENICO</t>
         </is>
       </c>
-      <c r="C2853" s="21" t="inlineStr">
+      <c r="C2853" s="13" t="inlineStr">
         <is>
           <t>PAPEL HIG NOBLE FD 20M</t>
         </is>
       </c>
-      <c r="D2853" s="21" t="inlineStr">
+      <c r="D2853" s="13" t="inlineStr">
         <is>
           <t>PAPEL HIGIENICO NOBLE 12 X 20M FOLHA DUPLA</t>
         </is>
@@ -62191,107 +62195,367 @@
       </c>
     </row>
     <row r="3083">
-      <c r="A3083" s="13" t="n">
+      <c r="A3083" s="9" t="n">
         <v>343857</v>
       </c>
-      <c r="B3083" s="13" t="inlineStr">
+      <c r="B3083" s="9" t="inlineStr">
         <is>
           <t>#05 BEBIDA - DESTILADOS</t>
         </is>
       </c>
-      <c r="C3083" s="13" t="inlineStr">
+      <c r="C3083" s="9" t="inlineStr">
         <is>
           <t>RUM BACARDI 700ML C ORO</t>
         </is>
       </c>
-      <c r="D3083" s="13" t="inlineStr">
+      <c r="D3083" s="9" t="inlineStr">
         <is>
           <t>RUM BACARDI 700ML CARTA ORO</t>
         </is>
       </c>
     </row>
     <row r="3084">
-      <c r="A3084" s="18" t="n">
+      <c r="A3084" s="20" t="n">
         <v>231729</v>
       </c>
-      <c r="B3084" s="18" t="inlineStr">
+      <c r="B3084" s="20" t="inlineStr">
         <is>
           <t>#03 AÇOUGUE - #06 EMBUTIDOS E FRIOS</t>
         </is>
       </c>
-      <c r="C3084" s="18" t="inlineStr">
+      <c r="C3084" s="20" t="inlineStr">
         <is>
           <t>HAMBURGUER  56GR SADIA AVES E BOVINO</t>
         </is>
       </c>
-      <c r="D3084" s="18" t="inlineStr">
+      <c r="D3084" s="20" t="inlineStr">
         <is>
           <t>HAMBURGUER SADIA 56G AVES E BOVINO</t>
         </is>
       </c>
     </row>
     <row r="3085">
-      <c r="A3085" s="21" t="n">
+      <c r="A3085" s="13" t="n">
         <v>337322</v>
       </c>
-      <c r="B3085" s="21" t="inlineStr">
+      <c r="B3085" s="13" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - CONDIMENTOS E TEMPEROS</t>
         </is>
       </c>
-      <c r="C3085" s="21" t="inlineStr">
+      <c r="C3085" s="13" t="inlineStr">
         <is>
           <t>AZEITONA VERDE GUNE 200GR S/ CAROCO</t>
         </is>
       </c>
-      <c r="D3085" s="21" t="inlineStr">
+      <c r="D3085" s="13" t="inlineStr">
         <is>
           <t>AZEITONAS VERDES GUNE 200G SEM CAROÇO</t>
         </is>
       </c>
     </row>
     <row r="3086">
-      <c r="A3086" s="21" t="n">
+      <c r="A3086" s="13" t="n">
         <v>135408</v>
       </c>
-      <c r="B3086" s="21" t="inlineStr">
+      <c r="B3086" s="13" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - CONDIMENTOS E TEMPEROS</t>
         </is>
       </c>
-      <c r="C3086" s="21" t="inlineStr">
+      <c r="C3086" s="13" t="inlineStr">
         <is>
           <t>KETCHUP TRAD. QUERO 1,150KG</t>
         </is>
       </c>
-      <c r="D3086" s="21" t="inlineStr">
+      <c r="D3086" s="13" t="inlineStr">
         <is>
           <t>KETCHUP QUERO QUERO 1,150KG TRADICIONAL</t>
         </is>
       </c>
     </row>
     <row r="3087">
-      <c r="A3087" s="21" t="n">
+      <c r="A3087" s="13" t="n">
         <v>111530</v>
       </c>
-      <c r="B3087" s="21" t="inlineStr">
+      <c r="B3087" s="13" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - LATICÍNIOS - LEITE</t>
         </is>
       </c>
-      <c r="C3087" s="21" t="inlineStr">
+      <c r="C3087" s="13" t="inlineStr">
         <is>
           <t>LEITE TP TRIANGULO 1 LT INTEGRAL</t>
         </is>
       </c>
-      <c r="D3087" s="21" t="inlineStr">
+      <c r="D3087" s="13" t="inlineStr">
         <is>
           <t>LEITE LONGA VIDA TRIANGULO 1L INTEGRAL</t>
         </is>
       </c>
     </row>
+    <row r="3088">
+      <c r="A3088" s="20" t="n">
+        <v>254748</v>
+      </c>
+      <c r="B3088" s="20" t="inlineStr">
+        <is>
+          <t>#07 HIGIENE PESSOAL - CABELOS</t>
+        </is>
+      </c>
+      <c r="C3088" s="20" t="inlineStr">
+        <is>
+          <t>COND SEDA  JUNTIN 300ML BRILHO ENCANTADO</t>
+        </is>
+      </c>
+      <c r="D3088" s="20" t="inlineStr">
+        <is>
+          <t>CONDICIONADOR SEDA 300ML JUNTIN BRILHO ENCANTADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="3089">
+      <c r="A3089" s="20" t="n">
+        <v>156773</v>
+      </c>
+      <c r="B3089" s="20" t="inlineStr">
+        <is>
+          <t>#07 HIGIENE PESSOAL - CABELOS</t>
+        </is>
+      </c>
+      <c r="C3089" s="20" t="inlineStr">
+        <is>
+          <t>COND SEDA CERAMIDAS 325ML</t>
+        </is>
+      </c>
+      <c r="D3089" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CONDICIONADOR SEDA 325ML CERAMIDAS </t>
+        </is>
+      </c>
+    </row>
+    <row r="3090">
+      <c r="A3090" s="20" t="n">
+        <v>304974</v>
+      </c>
+      <c r="B3090" s="20" t="inlineStr">
+        <is>
+          <t>#07 HIGIENE PESSOAL - CABELOS</t>
+        </is>
+      </c>
+      <c r="C3090" s="20" t="inlineStr">
+        <is>
+          <t>CONDICIONADOR OH MY 300ML CACHINHO PERFE</t>
+        </is>
+      </c>
+      <c r="D3090" s="20" t="inlineStr">
+        <is>
+          <t>CONDICIONADOR OH MY 300ML CACHINHO PERFEITO</t>
+        </is>
+      </c>
+    </row>
+    <row r="3091">
+      <c r="A3091" s="20" t="n">
+        <v>253527</v>
+      </c>
+      <c r="B3091" s="20" t="inlineStr">
+        <is>
+          <t>#07 HIGIENE PESSOAL - HIGIENE BUCAL</t>
+        </is>
+      </c>
+      <c r="C3091" s="20" t="inlineStr">
+        <is>
+          <t>CR D SORRISO CARVAO ATIVADO 60G</t>
+        </is>
+      </c>
+      <c r="D3091" s="20" t="inlineStr">
+        <is>
+          <t>CREME DENTAL SORRISO 60G CARVÃO ATIVADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="3092">
+      <c r="A3092" s="20" t="n">
+        <v>266081</v>
+      </c>
+      <c r="B3092" s="20" t="inlineStr">
+        <is>
+          <t>#07 HIGIENE PESSOAL - HIGIENE BUCAL</t>
+        </is>
+      </c>
+      <c r="C3092" s="20" t="inlineStr">
+        <is>
+          <t>CREME DENTAL COLGATE 90GR TOTAL 12 ANTIT</t>
+        </is>
+      </c>
+      <c r="D3092" s="20" t="inlineStr">
+        <is>
+          <t>CREME DENTAL COLGATE 90G TOTAL 12 ANTITARTARO</t>
+        </is>
+      </c>
+    </row>
+    <row r="3093">
+      <c r="A3093" s="20" t="n">
+        <v>304971</v>
+      </c>
+      <c r="B3093" s="20" t="inlineStr">
+        <is>
+          <t>#07 HIGIENE PESSOAL - CABELOS</t>
+        </is>
+      </c>
+      <c r="C3093" s="20" t="inlineStr">
+        <is>
+          <t>CREME P/PENTEAR OH MY COSMETICS 300ML CA</t>
+        </is>
+      </c>
+      <c r="D3093" s="20" t="inlineStr">
+        <is>
+          <t>CREME PARA PENTEAR OH MY 300ML CACHINHO PERFEITO</t>
+        </is>
+      </c>
+    </row>
+    <row r="3094">
+      <c r="A3094" s="20" t="n">
+        <v>307886</v>
+      </c>
+      <c r="B3094" s="20" t="inlineStr">
+        <is>
+          <t>#07 HIGIENE PESSOAL - HIGIENE BUCAL</t>
+        </is>
+      </c>
+      <c r="C3094" s="20" t="inlineStr">
+        <is>
+          <t>ESC DENTAL COLGATE 1X6 ZIG ZAG ANTIBAC</t>
+        </is>
+      </c>
+      <c r="D3094" s="20" t="inlineStr">
+        <is>
+          <t>ESCOVA DENTAL COLGATE 1X6 ZIG ZAG ANTIBACTERICIDA</t>
+        </is>
+      </c>
+    </row>
+    <row r="3095">
+      <c r="A3095" s="20" t="n">
+        <v>141345</v>
+      </c>
+      <c r="B3095" s="20" t="inlineStr">
+        <is>
+          <t>#07 HIGIENE PESSOAL - SABONETE</t>
+        </is>
+      </c>
+      <c r="C3095" s="20" t="inlineStr">
+        <is>
+          <t>SAB DOVE 90GR LEITE DE COCO</t>
+        </is>
+      </c>
+      <c r="D3095" s="20" t="inlineStr">
+        <is>
+          <t>SABONETE DOVE 90G LEITE DE COCO</t>
+        </is>
+      </c>
+    </row>
+    <row r="3096">
+      <c r="A3096" s="20" t="n">
+        <v>286028</v>
+      </c>
+      <c r="B3096" s="20" t="inlineStr">
+        <is>
+          <t>#07 HIGIENE PESSOAL - SABONETE</t>
+        </is>
+      </c>
+      <c r="C3096" s="20" t="inlineStr">
+        <is>
+          <t>SABONETE LIQUIDO MONANGE 200ML DETOX REF</t>
+        </is>
+      </c>
+      <c r="D3096" s="20" t="inlineStr">
+        <is>
+          <t>SABONETE LIQUIDO MONANGE 200ML DETOX REFIL</t>
+        </is>
+      </c>
+    </row>
+    <row r="3097">
+      <c r="A3097" s="20" t="n">
+        <v>254752</v>
+      </c>
+      <c r="B3097" s="20" t="inlineStr">
+        <is>
+          <t>#07 HIGIENE PESSOAL - CABELOS</t>
+        </is>
+      </c>
+      <c r="C3097" s="20" t="inlineStr">
+        <is>
+          <t>SH SEDA JUNTI 300ML BRILHO ENCANTADO</t>
+        </is>
+      </c>
+      <c r="D3097" s="20" t="inlineStr">
+        <is>
+          <t>SHAMPOO SEDA 300ML FOZEN BRILHO ENCANTADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="3098">
+      <c r="A3098" s="20" t="n">
+        <v>156783</v>
+      </c>
+      <c r="B3098" s="20" t="inlineStr">
+        <is>
+          <t>#07 HIGIENE PESSOAL - CABELOS</t>
+        </is>
+      </c>
+      <c r="C3098" s="20" t="inlineStr">
+        <is>
+          <t>SH.SEDA CERAMIDAS 325ML</t>
+        </is>
+      </c>
+      <c r="D3098" s="20" t="inlineStr">
+        <is>
+          <t>SHAMPOO SEDA 325ML CERAMIDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="3099">
+      <c r="A3099" s="20" t="n">
+        <v>304970</v>
+      </c>
+      <c r="B3099" s="20" t="inlineStr">
+        <is>
+          <t>#07 HIGIENE PESSOAL - CABELOS</t>
+        </is>
+      </c>
+      <c r="C3099" s="20" t="inlineStr">
+        <is>
+          <t>SHAMPOO OH MY COSMETICS 300ML CACHINHO P</t>
+        </is>
+      </c>
+      <c r="D3099" s="20" t="inlineStr">
+        <is>
+          <t>SHAMPOO OH MY 300ML CACHINHO PERFEITO</t>
+        </is>
+      </c>
+    </row>
+    <row r="3100">
+      <c r="A3100" s="17" t="n">
+        <v>341363</v>
+      </c>
+      <c r="B3100" s="17" t="inlineStr">
+        <is>
+          <t>SEÇÃO NÃO ESPECIFICADA</t>
+        </is>
+      </c>
+      <c r="C3100" s="17" t="inlineStr">
+        <is>
+          <t>LINGUICA PERNIL PERDIGAO 700GR NA BRASA</t>
+        </is>
+      </c>
+      <c r="D3100" s="17" t="inlineStr">
+        <is>
+          <t>LINGUICA PERNIL PERDIGAO 700GR NA BRASA</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:D3087">
+  <autoFilter ref="A1:D3100">
     <sortState ref="A2:D3082">
       <sortCondition ref="B1:B3082"/>
     </sortState>

--- a/produtos_cadastrados.xlsx
+++ b/produtos_cadastrados.xlsx
@@ -9,7 +9,7 @@
     <sheet name="Produtos" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Produtos'!$A$1:$E$3164</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Produtos'!$A$1:$E$3180</definedName>
   </definedNames>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
@@ -199,7 +199,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
@@ -226,22 +226,16 @@
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="23" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="24" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="24" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="25" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="21" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="20" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="24" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -607,7 +601,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3164"/>
+  <dimension ref="A1:E3180"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7.42578125" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -665,25 +659,25 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="23" t="n">
+      <c r="A3" s="26" t="n">
         <v>100038</v>
       </c>
-      <c r="B3" s="23" t="inlineStr">
+      <c r="B3" s="26" t="inlineStr">
         <is>
           <t>#01 MERCEARIA - #01 CEREAIS E GRÃOS</t>
         </is>
       </c>
-      <c r="C3" s="23" t="inlineStr">
+      <c r="C3" s="26" t="inlineStr">
         <is>
           <t>ARROZ BRANCO BREJEIRO 5KG TIPO 1</t>
         </is>
       </c>
-      <c r="D3" s="23" t="inlineStr">
+      <c r="D3" s="26" t="inlineStr">
         <is>
           <t>ARROZ BREJEIRO PCT 5KG TIPO 1 BRANCO</t>
         </is>
       </c>
-      <c r="E3" s="23" t="inlineStr"/>
+      <c r="E3" s="26" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -806,25 +800,25 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="23" t="n">
+      <c r="A10" s="26" t="n">
         <v>325990</v>
       </c>
-      <c r="B10" s="23" t="inlineStr">
+      <c r="B10" s="26" t="inlineStr">
         <is>
           <t>#01 MERCEARIA - #01 CEREAIS E GRÃOS</t>
         </is>
       </c>
-      <c r="C10" s="23" t="inlineStr">
+      <c r="C10" s="26" t="inlineStr">
         <is>
           <t>ARROZ BRANCO FLORA 5KG TIPO 1</t>
         </is>
       </c>
-      <c r="D10" s="23" t="inlineStr">
+      <c r="D10" s="26" t="inlineStr">
         <is>
           <t>ARROZ FLORA PCT 5KG TIPO 1 BRANCO</t>
         </is>
       </c>
-      <c r="E10" s="23" t="inlineStr"/>
+      <c r="E10" s="26" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -968,109 +962,109 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="25" t="n">
+      <c r="A18" s="23" t="n">
         <v>199439</v>
       </c>
-      <c r="B18" s="25" t="inlineStr">
+      <c r="B18" s="23" t="inlineStr">
         <is>
           <t>#01 MERCEARIA - #01 CEREAIS E GRÃOS</t>
         </is>
       </c>
-      <c r="C18" s="25" t="inlineStr">
+      <c r="C18" s="23" t="inlineStr">
         <is>
           <t>ARROZ RACHA PANELA 5 KG TP 1</t>
         </is>
       </c>
-      <c r="D18" s="25" t="inlineStr">
+      <c r="D18" s="23" t="inlineStr">
         <is>
           <t>ARROZ RACHA PANELA PCT 5KG TIPO 1 BRANCO</t>
         </is>
       </c>
-      <c r="E18" s="25" t="inlineStr"/>
+      <c r="E18" s="23" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="25" t="n">
+      <c r="A19" s="23" t="n">
         <v>225003</v>
       </c>
-      <c r="B19" s="25" t="inlineStr">
+      <c r="B19" s="23" t="inlineStr">
         <is>
           <t>#01 MERCEARIA - #01 CEREAIS E GRÃOS</t>
         </is>
       </c>
-      <c r="C19" s="25" t="inlineStr">
+      <c r="C19" s="23" t="inlineStr">
         <is>
           <t>ARROZ RAMPINELLI 5KG TIPO1</t>
         </is>
       </c>
-      <c r="D19" s="25" t="inlineStr">
+      <c r="D19" s="23" t="inlineStr">
         <is>
           <t>ARROZ RAMPINELLI PCT 5KG TIPO 1 BRANCO</t>
         </is>
       </c>
-      <c r="E19" s="25" t="inlineStr"/>
+      <c r="E19" s="23" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="25" t="n">
+      <c r="A20" s="23" t="n">
         <v>343313</v>
       </c>
-      <c r="B20" s="25" t="inlineStr">
+      <c r="B20" s="23" t="inlineStr">
         <is>
           <t>#01 MERCEARIA - #01 CEREAIS E GRÃOS</t>
         </is>
       </c>
-      <c r="C20" s="25" t="inlineStr">
+      <c r="C20" s="23" t="inlineStr">
         <is>
           <t>ARROZ BRANCO RAMPINELLI 5KG TIPO 1 PREMI</t>
         </is>
       </c>
-      <c r="D20" s="25" t="inlineStr">
+      <c r="D20" s="23" t="inlineStr">
         <is>
           <t>ARROZ RAMPINELLI PREMIUM PCT 5KG TIPO 1 BRANCO</t>
         </is>
       </c>
-      <c r="E20" s="25" t="inlineStr"/>
+      <c r="E20" s="23" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="23" t="n">
+      <c r="A21" s="26" t="n">
         <v>100020</v>
       </c>
-      <c r="B21" s="23" t="inlineStr">
+      <c r="B21" s="26" t="inlineStr">
         <is>
           <t>#01 MERCEARIA - #01 CEREAIS E GRÃOS</t>
         </is>
       </c>
-      <c r="C21" s="23" t="inlineStr">
+      <c r="C21" s="26" t="inlineStr">
         <is>
           <t>ARROZ REALENGO 5KG BCO. TIPO 1</t>
         </is>
       </c>
-      <c r="D21" s="23" t="inlineStr">
+      <c r="D21" s="26" t="inlineStr">
         <is>
           <t>ARROZ REALENGO PCT 5KG TIPO 1 BRANCO</t>
         </is>
       </c>
-      <c r="E21" s="23" t="inlineStr"/>
+      <c r="E21" s="26" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="25" t="n">
+      <c r="A22" s="23" t="n">
         <v>100031</v>
       </c>
-      <c r="B22" s="25" t="inlineStr">
+      <c r="B22" s="23" t="inlineStr">
         <is>
           <t>#01 MERCEARIA - #01 CEREAIS E GRÃOS</t>
         </is>
       </c>
-      <c r="C22" s="25" t="inlineStr">
+      <c r="C22" s="23" t="inlineStr">
         <is>
           <t>ARROZ REI ARTHUR 5 KG BRANCO TIPO 1</t>
         </is>
       </c>
-      <c r="D22" s="25" t="inlineStr">
+      <c r="D22" s="23" t="inlineStr">
         <is>
           <t>ARROZ REI ARTHUR PCT 5KG TIPO 1 BRANCO</t>
         </is>
       </c>
-      <c r="E22" s="25" t="inlineStr"/>
+      <c r="E22" s="23" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -1294,25 +1288,25 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="23" t="n">
+      <c r="A34" s="26" t="n">
         <v>116507</v>
       </c>
-      <c r="B34" s="23" t="inlineStr">
+      <c r="B34" s="26" t="inlineStr">
         <is>
           <t>#01 MERCEARIA - #02 FEIJÕES E LEGUMINOSAS</t>
         </is>
       </c>
-      <c r="C34" s="23" t="inlineStr">
+      <c r="C34" s="26" t="inlineStr">
         <is>
           <t>FEIJÃO DA CASA 1KG CARIOCA</t>
         </is>
       </c>
-      <c r="D34" s="23" t="inlineStr">
+      <c r="D34" s="26" t="inlineStr">
         <is>
           <t>FEIJÃO CARIOCA DA CASA 1KG</t>
         </is>
       </c>
-      <c r="E34" s="23" t="inlineStr"/>
+      <c r="E34" s="26" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -1416,25 +1410,25 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="25" t="n">
+      <c r="A40" s="26" t="n">
         <v>163918</v>
       </c>
-      <c r="B40" s="25" t="inlineStr">
+      <c r="B40" s="26" t="inlineStr">
         <is>
           <t>#01 MERCEARIA - #02 FEIJÕES E LEGUMINOSAS</t>
         </is>
       </c>
-      <c r="C40" s="25" t="inlineStr">
+      <c r="C40" s="26" t="inlineStr">
         <is>
           <t>FEIJÃO KICALDO 1KG CARIOCA</t>
         </is>
       </c>
-      <c r="D40" s="25" t="inlineStr">
+      <c r="D40" s="26" t="inlineStr">
         <is>
           <t>FEIJÃO CARIOCA KICALDO 1KG</t>
         </is>
       </c>
-      <c r="E40" s="25" t="inlineStr"/>
+      <c r="E40" s="26" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -1617,25 +1611,25 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="23" t="n">
+      <c r="A50" s="26" t="n">
         <v>165928</v>
       </c>
-      <c r="B50" s="23" t="inlineStr">
+      <c r="B50" s="26" t="inlineStr">
         <is>
           <t>#01 MERCEARIA - #02 FEIJÕES E LEGUMINOSAS</t>
         </is>
       </c>
-      <c r="C50" s="23" t="inlineStr">
+      <c r="C50" s="26" t="inlineStr">
         <is>
           <t>FEIJAO PRETO JOAOZINHO 1KG</t>
         </is>
       </c>
-      <c r="D50" s="23" t="inlineStr">
+      <c r="D50" s="26" t="inlineStr">
         <is>
           <t>FEIJÃO PRETO JOÃOZINHO 1KG</t>
         </is>
       </c>
-      <c r="E50" s="23" t="inlineStr"/>
+      <c r="E50" s="26" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -1859,46 +1853,46 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="25" t="n">
+      <c r="A62" s="23" t="n">
         <v>100054</v>
       </c>
-      <c r="B62" s="25" t="inlineStr">
+      <c r="B62" s="23" t="inlineStr">
         <is>
           <t>#01 MERCEARIA - #03 ÓLEOS E GORDURAS</t>
         </is>
       </c>
-      <c r="C62" s="25" t="inlineStr">
+      <c r="C62" s="23" t="inlineStr">
         <is>
           <t>ÓLEO SOJA BREJEIRO 900 ML</t>
         </is>
       </c>
-      <c r="D62" s="25" t="inlineStr">
+      <c r="D62" s="23" t="inlineStr">
         <is>
           <t>ÓLEO DE SOJA BREJEIRO 900ML</t>
         </is>
       </c>
-      <c r="E62" s="25" t="inlineStr"/>
+      <c r="E62" s="23" t="inlineStr"/>
     </row>
     <row r="63">
-      <c r="A63" s="23" t="n">
+      <c r="A63" s="26" t="n">
         <v>167128</v>
       </c>
-      <c r="B63" s="23" t="inlineStr">
+      <c r="B63" s="26" t="inlineStr">
         <is>
           <t>#01 MERCEARIA - #03 ÓLEOS E GORDURAS</t>
         </is>
       </c>
-      <c r="C63" s="23" t="inlineStr">
+      <c r="C63" s="26" t="inlineStr">
         <is>
           <t>ÓLEO SOJA REFINADO CONCORDIA 900ML</t>
         </is>
       </c>
-      <c r="D63" s="23" t="inlineStr">
+      <c r="D63" s="26" t="inlineStr">
         <is>
           <t>ÓLEO DE SOJA CONCORDIA 900ML</t>
         </is>
       </c>
-      <c r="E63" s="23" t="inlineStr"/>
+      <c r="E63" s="26" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="5" t="n">
@@ -2021,25 +2015,25 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="25" t="n">
+      <c r="A70" s="23" t="n">
         <v>343925</v>
       </c>
-      <c r="B70" s="25" t="inlineStr">
+      <c r="B70" s="23" t="inlineStr">
         <is>
           <t>#01 MERCEARIA - #04 AÇÚCAR E ADOÇANTES</t>
         </is>
       </c>
-      <c r="C70" s="25" t="inlineStr">
+      <c r="C70" s="23" t="inlineStr">
         <is>
           <t>ACUCAR CRISTAL SAFIA 2KG</t>
         </is>
       </c>
-      <c r="D70" s="25" t="inlineStr">
+      <c r="D70" s="23" t="inlineStr">
         <is>
           <t>AÇUCAR CRISTAL SAFIA 2KG</t>
         </is>
       </c>
-      <c r="E70" s="25" t="inlineStr"/>
+      <c r="E70" s="23" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -2082,25 +2076,25 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="23" t="n">
+      <c r="A73" s="26" t="n">
         <v>345404</v>
       </c>
-      <c r="B73" s="23" t="inlineStr">
+      <c r="B73" s="26" t="inlineStr">
         <is>
           <t>#01 MERCEARIA - #04 AÇÚCAR E ADOÇANTES</t>
         </is>
       </c>
-      <c r="C73" s="23" t="inlineStr">
+      <c r="C73" s="26" t="inlineStr">
         <is>
           <t>ACUCAR ECO ACUCAR 2KG CRISTAL</t>
         </is>
       </c>
-      <c r="D73" s="23" t="inlineStr">
+      <c r="D73" s="26" t="inlineStr">
         <is>
           <t>AÇUCAR ECOÇUCAR 2KG CRISTAL</t>
         </is>
       </c>
-      <c r="E73" s="23" t="inlineStr"/>
+      <c r="E73" s="26" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -2483,25 +2477,25 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="25" t="n">
+      <c r="A93" s="26" t="n">
         <v>255232</v>
       </c>
-      <c r="B93" s="25" t="inlineStr">
+      <c r="B93" s="26" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - ACHOCOLATADOS E CAFÉ</t>
         </is>
       </c>
-      <c r="C93" s="25" t="inlineStr">
+      <c r="C93" s="26" t="inlineStr">
         <is>
           <t>ACHOC PO TODDY 750G</t>
         </is>
       </c>
-      <c r="D93" s="25" t="inlineStr">
+      <c r="D93" s="26" t="inlineStr">
         <is>
           <t>ACHOCOLATADO EM PÓ TODDY 750G</t>
         </is>
       </c>
-      <c r="E93" s="25" t="inlineStr"/>
+      <c r="E93" s="26" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -2644,46 +2638,46 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="25" t="n">
+      <c r="A101" s="26" t="n">
         <v>344310</v>
       </c>
-      <c r="B101" s="25" t="inlineStr">
+      <c r="B101" s="26" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - ACHOCOLATADOS E CAFÉ</t>
         </is>
       </c>
-      <c r="C101" s="25" t="inlineStr">
+      <c r="C101" s="26" t="inlineStr">
         <is>
           <t>CAFE MAMORE 250G TRAD TORRADO E MOIDO</t>
         </is>
       </c>
-      <c r="D101" s="25" t="inlineStr">
+      <c r="D101" s="26" t="inlineStr">
         <is>
           <t>CAFE MAMORE 250G TRADICIONAL TORRADO E MOIDO</t>
         </is>
       </c>
-      <c r="E101" s="25" t="inlineStr"/>
+      <c r="E101" s="26" t="inlineStr"/>
     </row>
     <row r="102">
-      <c r="A102" s="25" t="n">
+      <c r="A102" s="26" t="n">
         <v>101137</v>
       </c>
-      <c r="B102" s="25" t="inlineStr">
+      <c r="B102" s="26" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - ACHOCOLATADOS E CAFÉ</t>
         </is>
       </c>
-      <c r="C102" s="25" t="inlineStr">
+      <c r="C102" s="26" t="inlineStr">
         <is>
           <t>CAFÉ MARATA 250GR A VACUO TRADIC</t>
         </is>
       </c>
-      <c r="D102" s="25" t="inlineStr">
+      <c r="D102" s="26" t="inlineStr">
         <is>
           <t>CAFÉ MARATA 250G TRADICIONAL</t>
         </is>
       </c>
-      <c r="E102" s="25" t="inlineStr"/>
+      <c r="E102" s="26" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -2786,24 +2780,25 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" t="n">
+      <c r="A108" s="30" t="n">
         <v>271661</v>
       </c>
-      <c r="B108" t="inlineStr">
+      <c r="B108" s="30" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - ACHOCOLATADOS E CAFÉ</t>
         </is>
       </c>
-      <c r="C108" t="inlineStr">
+      <c r="C108" s="30" t="inlineStr">
         <is>
           <t>CAFÉ SANTA CLARA 250GR VACUO EXTRA FORTE</t>
         </is>
       </c>
-      <c r="D108" t="inlineStr">
+      <c r="D108" s="30" t="inlineStr">
         <is>
           <t>CAFÉ SANTA CLARA 250G EXTRA FORTE</t>
         </is>
       </c>
+      <c r="E108" s="30" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -3126,25 +3121,25 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="23" t="n">
+      <c r="A125" s="26" t="n">
         <v>110372</v>
       </c>
-      <c r="B125" s="23" t="inlineStr">
+      <c r="B125" s="26" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - BISCOITOS E SALGADINHOS</t>
         </is>
       </c>
-      <c r="C125" s="23" t="inlineStr">
+      <c r="C125" s="26" t="inlineStr">
         <is>
           <t>BISC CLUB SOCIAL 144GR ORIGINAL</t>
         </is>
       </c>
-      <c r="D125" s="23" t="inlineStr">
+      <c r="D125" s="26" t="inlineStr">
         <is>
           <t>BISCOITO CLUB SOCIAL 144G ORIGINAL</t>
         </is>
       </c>
-      <c r="E125" s="23" t="inlineStr"/>
+      <c r="E125" s="26" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -3247,25 +3242,25 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="23" t="n">
+      <c r="A131" s="26" t="n">
         <v>250013</v>
       </c>
-      <c r="B131" s="23" t="inlineStr">
+      <c r="B131" s="26" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - BISCOITOS E SALGADINHOS</t>
         </is>
       </c>
-      <c r="C131" s="23" t="inlineStr">
+      <c r="C131" s="26" t="inlineStr">
         <is>
           <t>BISC MARILAN CRACKER ESPECIAL 350GR</t>
         </is>
       </c>
-      <c r="D131" s="23" t="inlineStr">
+      <c r="D131" s="26" t="inlineStr">
         <is>
           <t>BISCOITO CREAM CRACKER MARILAN 350G ESPECIAL</t>
         </is>
       </c>
-      <c r="E131" s="23" t="inlineStr"/>
+      <c r="E131" s="26" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -4448,25 +4443,25 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="25" t="n">
+      <c r="A191" s="26" t="n">
         <v>286197</v>
       </c>
-      <c r="B191" s="25" t="inlineStr">
+      <c r="B191" s="26" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - BISCOITOS E SALGADINHOS</t>
         </is>
       </c>
-      <c r="C191" s="25" t="inlineStr">
+      <c r="C191" s="26" t="inlineStr">
         <is>
           <t>BISCOITO MABEL 600GR ROSCA COCO</t>
         </is>
       </c>
-      <c r="D191" s="25" t="inlineStr">
+      <c r="D191" s="26" t="inlineStr">
         <is>
           <t>BISCOITO ROSQUINHA MABEL 600G COCO</t>
         </is>
       </c>
-      <c r="E191" s="25" t="inlineStr"/>
+      <c r="E191" s="26" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" t="n">
@@ -5730,25 +5725,25 @@
       </c>
     </row>
     <row r="255">
-      <c r="A255" s="25" t="n">
+      <c r="A255" s="26" t="n">
         <v>341362</v>
       </c>
-      <c r="B255" s="25" t="inlineStr">
+      <c r="B255" s="26" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - CHOCOLATES E DOCES</t>
         </is>
       </c>
-      <c r="C255" s="25" t="inlineStr">
+      <c r="C255" s="26" t="inlineStr">
         <is>
           <t>BOMBONS GAROTO 220G SORTIDOS CAIXA</t>
         </is>
       </c>
-      <c r="D255" s="25" t="inlineStr">
+      <c r="D255" s="26" t="inlineStr">
         <is>
           <t>BOMBOM GAROTO CAIXA 220G SORTIDOS</t>
         </is>
       </c>
-      <c r="E255" s="25" t="inlineStr"/>
+      <c r="E255" s="26" t="inlineStr"/>
     </row>
     <row r="256">
       <c r="A256" t="n">
@@ -6911,25 +6906,25 @@
       </c>
     </row>
     <row r="314">
-      <c r="A314" s="25" t="n">
+      <c r="A314" s="23" t="n">
         <v>346331</v>
       </c>
-      <c r="B314" s="25" t="inlineStr">
+      <c r="B314" s="23" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - COMIDAS TIPICAS</t>
         </is>
       </c>
-      <c r="C314" s="25" t="inlineStr">
+      <c r="C314" s="23" t="inlineStr">
         <is>
           <t>JAMBU PAVAO 500GR</t>
         </is>
       </c>
-      <c r="D314" s="25" t="inlineStr">
+      <c r="D314" s="23" t="inlineStr">
         <is>
           <t>JAMBU PAVÃO 500G</t>
         </is>
       </c>
-      <c r="E314" s="25" t="inlineStr"/>
+      <c r="E314" s="23" t="inlineStr"/>
     </row>
     <row r="315">
       <c r="A315" t="n">
@@ -7372,25 +7367,25 @@
       </c>
     </row>
     <row r="337">
-      <c r="A337" s="25" t="n">
+      <c r="A337" s="23" t="n">
         <v>174071</v>
       </c>
-      <c r="B337" s="25" t="inlineStr">
+      <c r="B337" s="23" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - CONDIMENTOS E TEMPEROS</t>
         </is>
       </c>
-      <c r="C337" s="25" t="inlineStr">
+      <c r="C337" s="23" t="inlineStr">
         <is>
           <t>AZEITONA VERDE LA VIOLETERA 100GR SACHE</t>
         </is>
       </c>
-      <c r="D337" s="25" t="inlineStr">
+      <c r="D337" s="23" t="inlineStr">
         <is>
           <t>AZEITONAS VERDES LA VIOLETERA SACHÊ 100G</t>
         </is>
       </c>
-      <c r="E337" s="25" t="inlineStr"/>
+      <c r="E337" s="23" t="inlineStr"/>
     </row>
     <row r="338">
       <c r="A338" t="n">
@@ -7493,25 +7488,25 @@
       </c>
     </row>
     <row r="343">
-      <c r="A343" s="23" t="n">
+      <c r="A343" s="26" t="n">
         <v>190801</v>
       </c>
-      <c r="B343" s="23" t="inlineStr">
+      <c r="B343" s="26" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - CONDIMENTOS E TEMPEROS</t>
         </is>
       </c>
-      <c r="C343" s="23" t="inlineStr">
+      <c r="C343" s="26" t="inlineStr">
         <is>
           <t>AZEITONAS VERDES INTEIRAS MARATA SACHET</t>
         </is>
       </c>
-      <c r="D343" s="23" t="inlineStr">
+      <c r="D343" s="26" t="inlineStr">
         <is>
           <t>AZEITONAS VERDES MARATA SACHE 210G INTEIRAS</t>
         </is>
       </c>
-      <c r="E343" s="23" t="inlineStr"/>
+      <c r="E343" s="26" t="inlineStr"/>
     </row>
     <row r="344">
       <c r="A344" t="n">
@@ -7974,25 +7969,25 @@
       </c>
     </row>
     <row r="367">
-      <c r="A367" s="23" t="n">
+      <c r="A367" s="26" t="n">
         <v>242311</v>
       </c>
-      <c r="B367" s="23" t="inlineStr">
+      <c r="B367" s="26" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - CONDIMENTOS E TEMPEROS</t>
         </is>
       </c>
-      <c r="C367" s="23" t="inlineStr">
+      <c r="C367" s="26" t="inlineStr">
         <is>
           <t>CATCHUP ARISCO TRADICIONAL 370G</t>
         </is>
       </c>
-      <c r="D367" s="23" t="inlineStr">
+      <c r="D367" s="26" t="inlineStr">
         <is>
           <t>CATCHUP ARISCO 370G TRADICIONAL</t>
         </is>
       </c>
-      <c r="E367" s="23" t="inlineStr"/>
+      <c r="E367" s="26" t="inlineStr"/>
     </row>
     <row r="368">
       <c r="A368" t="n">
@@ -8275,25 +8270,25 @@
       </c>
     </row>
     <row r="382">
-      <c r="A382" s="25" t="n">
+      <c r="A382" s="23" t="n">
         <v>273714</v>
       </c>
-      <c r="B382" s="25" t="inlineStr">
+      <c r="B382" s="23" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - CONDIMENTOS E TEMPEROS</t>
         </is>
       </c>
-      <c r="C382" s="25" t="inlineStr">
+      <c r="C382" s="23" t="inlineStr">
         <is>
           <t>EXTRATO TOMATE ELEFANTE 300G POTE</t>
         </is>
       </c>
-      <c r="D382" s="25" t="inlineStr">
+      <c r="D382" s="23" t="inlineStr">
         <is>
           <t>EXTRATO DE TOMATE ELEFANTE POTE 300G</t>
         </is>
       </c>
-      <c r="E382" s="25" t="inlineStr"/>
+      <c r="E382" s="23" t="inlineStr"/>
     </row>
     <row r="383">
       <c r="A383" t="n">
@@ -8376,25 +8371,25 @@
       </c>
     </row>
     <row r="387">
-      <c r="A387" s="23" t="n">
+      <c r="A387" s="26" t="n">
         <v>100780</v>
       </c>
-      <c r="B387" s="23" t="inlineStr">
+      <c r="B387" s="26" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - CONDIMENTOS E TEMPEROS</t>
         </is>
       </c>
-      <c r="C387" s="23" t="inlineStr">
+      <c r="C387" s="26" t="inlineStr">
         <is>
           <t>EXT TOMATE OLE 190GR CP</t>
         </is>
       </c>
-      <c r="D387" s="23" t="inlineStr">
+      <c r="D387" s="26" t="inlineStr">
         <is>
           <t>EXTRATO DE TOMATE OLE COPO 190G</t>
         </is>
       </c>
-      <c r="E387" s="23" t="inlineStr"/>
+      <c r="E387" s="26" t="inlineStr"/>
     </row>
     <row r="388">
       <c r="A388" t="n">
@@ -8937,25 +8932,25 @@
       </c>
     </row>
     <row r="415">
-      <c r="A415" s="25" t="n">
+      <c r="A415" s="26" t="n">
         <v>101728</v>
       </c>
-      <c r="B415" s="25" t="inlineStr">
+      <c r="B415" s="26" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - CONDIMENTOS E TEMPEROS</t>
         </is>
       </c>
-      <c r="C415" s="25" t="inlineStr">
+      <c r="C415" s="26" t="inlineStr">
         <is>
           <t>MAIONESE HELLMANNS 500GR TRADICIONAL</t>
         </is>
       </c>
-      <c r="D415" s="25" t="inlineStr">
+      <c r="D415" s="26" t="inlineStr">
         <is>
           <t>MAIONESE HELLMANNS 500G TRADICIONAL</t>
         </is>
       </c>
-      <c r="E415" s="25" t="inlineStr"/>
+      <c r="E415" s="26" t="inlineStr"/>
     </row>
     <row r="416">
       <c r="A416" t="n">
@@ -9079,25 +9074,25 @@
       </c>
     </row>
     <row r="422">
-      <c r="A422" s="25" t="n">
+      <c r="A422" s="23" t="n">
         <v>133147</v>
       </c>
-      <c r="B422" s="25" t="inlineStr">
+      <c r="B422" s="23" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - CONDIMENTOS E TEMPEROS</t>
         </is>
       </c>
-      <c r="C422" s="25" t="inlineStr">
+      <c r="C422" s="23" t="inlineStr">
         <is>
           <t>MAIONESE SABORELLE PICANTE 200G</t>
         </is>
       </c>
-      <c r="D422" s="25" t="inlineStr">
+      <c r="D422" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">MAIONESE SABORELLE 200G PICANTE </t>
         </is>
       </c>
-      <c r="E422" s="25" t="inlineStr"/>
+      <c r="E422" s="23" t="inlineStr"/>
     </row>
     <row r="423">
       <c r="A423" t="n">
@@ -9300,25 +9295,25 @@
       </c>
     </row>
     <row r="433">
-      <c r="A433" s="23" t="n">
+      <c r="A433" s="26" t="n">
         <v>100851</v>
       </c>
-      <c r="B433" s="23" t="inlineStr">
+      <c r="B433" s="26" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - CONDIMENTOS E TEMPEROS</t>
         </is>
       </c>
-      <c r="C433" s="23" t="inlineStr">
+      <c r="C433" s="26" t="inlineStr">
         <is>
           <t>MOLHO PIMENTA MARATA GOTA 150ML</t>
         </is>
       </c>
-      <c r="D433" s="23" t="inlineStr">
+      <c r="D433" s="26" t="inlineStr">
         <is>
           <t>MOLHO DE PIMENTA MARATA GOTA 150ML</t>
         </is>
       </c>
-      <c r="E433" s="23" t="inlineStr"/>
+      <c r="E433" s="26" t="inlineStr"/>
     </row>
     <row r="434">
       <c r="A434" t="n">
@@ -9782,25 +9777,25 @@
       </c>
     </row>
     <row r="457">
-      <c r="A457" s="25" t="n">
+      <c r="A457" s="23" t="n">
         <v>321107</v>
       </c>
-      <c r="B457" s="25" t="inlineStr">
+      <c r="B457" s="23" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - CONDIMENTOS E TEMPEROS</t>
         </is>
       </c>
-      <c r="C457" s="25" t="inlineStr">
+      <c r="C457" s="23" t="inlineStr">
         <is>
           <t>MOLHO PRONTO QUERO 240GR TRADICIONAL SCH</t>
         </is>
       </c>
-      <c r="D457" s="25" t="inlineStr">
+      <c r="D457" s="23" t="inlineStr">
         <is>
           <t>MOLHO QUERO PRONTO SACHÊ 240G TRADICIONAL</t>
         </is>
       </c>
-      <c r="E457" s="25" t="inlineStr"/>
+      <c r="E457" s="23" t="inlineStr"/>
     </row>
     <row r="458">
       <c r="A458" t="n">
@@ -10083,25 +10078,25 @@
       </c>
     </row>
     <row r="472">
-      <c r="A472" s="23" t="n">
+      <c r="A472" s="26" t="n">
         <v>127461</v>
       </c>
-      <c r="B472" s="23" t="inlineStr">
+      <c r="B472" s="26" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - CONDIMENTOS E TEMPEROS</t>
         </is>
       </c>
-      <c r="C472" s="23" t="inlineStr">
+      <c r="C472" s="26" t="inlineStr">
         <is>
           <t>SAL P/ CHURRASCO ITA 1KG</t>
         </is>
       </c>
-      <c r="D472" s="23" t="inlineStr">
+      <c r="D472" s="26" t="inlineStr">
         <is>
           <t>SAL PARA CHURRASCO ITA 1KG</t>
         </is>
       </c>
-      <c r="E472" s="23" t="inlineStr"/>
+      <c r="E472" s="26" t="inlineStr"/>
     </row>
     <row r="473">
       <c r="A473" t="n">
@@ -10264,46 +10259,46 @@
       </c>
     </row>
     <row r="481">
-      <c r="A481" s="25" t="n">
+      <c r="A481" s="23" t="n">
         <v>100876</v>
       </c>
-      <c r="B481" s="25" t="inlineStr">
+      <c r="B481" s="23" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - CONDIMENTOS E TEMPEROS</t>
         </is>
       </c>
-      <c r="C481" s="25" t="inlineStr">
+      <c r="C481" s="23" t="inlineStr">
         <is>
           <t>TEMPERO ARISCO 1KG COMPLETO C/ PIMENTA</t>
         </is>
       </c>
-      <c r="D481" s="25" t="inlineStr">
+      <c r="D481" s="23" t="inlineStr">
         <is>
           <t>TEMPERO COMPLETO ARISCO 1KG COM PIMENTA</t>
         </is>
       </c>
-      <c r="E481" s="25" t="inlineStr"/>
+      <c r="E481" s="23" t="inlineStr"/>
     </row>
     <row r="482">
-      <c r="A482" s="23" t="n">
+      <c r="A482" s="26" t="n">
         <v>108518</v>
       </c>
-      <c r="B482" s="23" t="inlineStr">
+      <c r="B482" s="26" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - CONDIMENTOS E TEMPEROS</t>
         </is>
       </c>
-      <c r="C482" s="23" t="inlineStr">
+      <c r="C482" s="26" t="inlineStr">
         <is>
           <t>TEMPERO ARISCO 1KG COMPLETO S/ PIMENTA</t>
         </is>
       </c>
-      <c r="D482" s="23" t="inlineStr">
+      <c r="D482" s="26" t="inlineStr">
         <is>
           <t>TEMPERO COMPLETO ARISCO COMPLETO 1KG SEM PIMENTA</t>
         </is>
       </c>
-      <c r="E482" s="23" t="inlineStr"/>
+      <c r="E482" s="26" t="inlineStr"/>
     </row>
     <row r="483">
       <c r="A483" t="n">
@@ -10646,25 +10641,25 @@
       </c>
     </row>
     <row r="500">
-      <c r="A500" s="23" t="n">
+      <c r="A500" s="26" t="n">
         <v>100884</v>
       </c>
-      <c r="B500" s="23" t="inlineStr">
+      <c r="B500" s="26" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - CONDIMENTOS E TEMPEROS</t>
         </is>
       </c>
-      <c r="C500" s="23" t="inlineStr">
+      <c r="C500" s="26" t="inlineStr">
         <is>
           <t>TEMPERO SAZON 60GR SCH CARNES/VERMELHO</t>
         </is>
       </c>
-      <c r="D500" s="23" t="inlineStr">
+      <c r="D500" s="26" t="inlineStr">
         <is>
           <t>TEMPERO EM PÓ SAZON SACHÊ 60G CARNES/VERMELHO</t>
         </is>
       </c>
-      <c r="E500" s="23" t="inlineStr"/>
+      <c r="E500" s="26" t="inlineStr"/>
     </row>
     <row r="501">
       <c r="A501" t="n">
@@ -11107,25 +11102,25 @@
       </c>
     </row>
     <row r="523">
-      <c r="A523" s="23" t="n">
+      <c r="A523" s="26" t="n">
         <v>106961</v>
       </c>
-      <c r="B523" s="23" t="inlineStr">
+      <c r="B523" s="26" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - CONDIMENTOS E TEMPEROS</t>
         </is>
       </c>
-      <c r="C523" s="23" t="inlineStr">
+      <c r="C523" s="26" t="inlineStr">
         <is>
           <t>VINAGRE CASTELO 750ML ALCOOL</t>
         </is>
       </c>
-      <c r="D523" s="23" t="inlineStr">
+      <c r="D523" s="26" t="inlineStr">
         <is>
           <t>VINAGRE CASTELO 750ML ALCOOL</t>
         </is>
       </c>
-      <c r="E523" s="23" t="inlineStr"/>
+      <c r="E523" s="26" t="inlineStr"/>
     </row>
     <row r="524">
       <c r="A524" t="n">
@@ -11389,25 +11384,25 @@
       </c>
     </row>
     <row r="537">
-      <c r="A537" s="25" t="n">
+      <c r="A537" s="23" t="n">
         <v>230387</v>
       </c>
-      <c r="B537" s="25" t="inlineStr">
+      <c r="B537" s="23" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - CONGELADOS - BATATAS</t>
         </is>
       </c>
-      <c r="C537" s="25" t="inlineStr">
+      <c r="C537" s="23" t="inlineStr">
         <is>
           <t>BATATAS PRE-FRITAS CONG BOUA 1,05 KG</t>
         </is>
       </c>
-      <c r="D537" s="25" t="inlineStr">
+      <c r="D537" s="23" t="inlineStr">
         <is>
           <t>BATATAS CONGELADAS BOUA PCT 1,05KG PRE-FRITAS</t>
         </is>
       </c>
-      <c r="E537" s="25" t="inlineStr"/>
+      <c r="E537" s="23" t="inlineStr"/>
     </row>
     <row r="538">
       <c r="A538" t="n">
@@ -11430,25 +11425,25 @@
       </c>
     </row>
     <row r="539">
-      <c r="A539" s="35" t="n">
+      <c r="A539" s="26" t="n">
         <v>193650</v>
       </c>
-      <c r="B539" s="35" t="inlineStr">
+      <c r="B539" s="26" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - CONGELADOS - BATATAS</t>
         </is>
       </c>
-      <c r="C539" s="35" t="inlineStr">
+      <c r="C539" s="26" t="inlineStr">
         <is>
           <t>BATATAS PRE-FRITAS CONG BOUA 400GR</t>
         </is>
       </c>
-      <c r="D539" s="35" t="inlineStr">
+      <c r="D539" s="26" t="inlineStr">
         <is>
           <t>BATATAS CONGELADAS BOUA PCT 400G PRE-FRITAS</t>
         </is>
       </c>
-      <c r="E539" s="35" t="inlineStr"/>
+      <c r="E539" s="26" t="inlineStr"/>
     </row>
     <row r="540">
       <c r="A540" t="n">
@@ -12551,25 +12546,25 @@
       </c>
     </row>
     <row r="595">
-      <c r="A595" s="25" t="n">
+      <c r="A595" s="26" t="n">
         <v>221945</v>
       </c>
-      <c r="B595" s="25" t="inlineStr">
+      <c r="B595" s="26" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - CONSERVAS - HORTIFRUTI</t>
         </is>
       </c>
-      <c r="C595" s="25" t="inlineStr">
+      <c r="C595" s="26" t="inlineStr">
         <is>
           <t>MILHO VERDE LATA 170G PREDILECTA</t>
         </is>
       </c>
-      <c r="D595" s="25" t="inlineStr">
+      <c r="D595" s="26" t="inlineStr">
         <is>
           <t>MILHO VERDE PREDILECTA LATA 170G</t>
         </is>
       </c>
-      <c r="E595" s="25" t="inlineStr"/>
+      <c r="E595" s="26" t="inlineStr"/>
     </row>
     <row r="596">
       <c r="A596" t="n">
@@ -13292,25 +13287,25 @@
       </c>
     </row>
     <row r="632">
-      <c r="A632" s="23" t="n">
+      <c r="A632" s="26" t="n">
         <v>100705</v>
       </c>
-      <c r="B632" s="23" t="inlineStr">
+      <c r="B632" s="26" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - CONSERVAS - SARDINHAS</t>
         </is>
       </c>
-      <c r="C632" s="23" t="inlineStr">
+      <c r="C632" s="26" t="inlineStr">
         <is>
           <t>SARDINHA GOMES DA COSTA 125GR TOMATE</t>
         </is>
       </c>
-      <c r="D632" s="23" t="inlineStr">
+      <c r="D632" s="26" t="inlineStr">
         <is>
           <t>SARDINHA GOMES DA COSTA 125G TOMATE</t>
         </is>
       </c>
-      <c r="E632" s="23" t="inlineStr"/>
+      <c r="E632" s="26" t="inlineStr"/>
     </row>
     <row r="633">
       <c r="A633" t="n">
@@ -13714,25 +13709,25 @@
       <c r="E652" s="17" t="inlineStr"/>
     </row>
     <row r="653">
-      <c r="A653" s="25" t="n">
+      <c r="A653" s="26" t="n">
         <v>112978</v>
       </c>
-      <c r="B653" s="25" t="inlineStr">
+      <c r="B653" s="26" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - FARINHAS E DERIVADOS</t>
         </is>
       </c>
-      <c r="C653" s="25" t="inlineStr">
+      <c r="C653" s="26" t="inlineStr">
         <is>
           <t>CUSCUZ DE MILHO SINHA 500GR</t>
         </is>
       </c>
-      <c r="D653" s="25" t="inlineStr">
+      <c r="D653" s="26" t="inlineStr">
         <is>
           <t>CUSCUZ DE MILHO SINHA 500G</t>
         </is>
       </c>
-      <c r="E653" s="25" t="inlineStr"/>
+      <c r="E653" s="26" t="inlineStr"/>
     </row>
     <row r="654">
       <c r="A654" t="n">
@@ -13755,25 +13750,25 @@
       </c>
     </row>
     <row r="655">
-      <c r="A655" s="23" t="n">
+      <c r="A655" s="26" t="n">
         <v>128930</v>
       </c>
-      <c r="B655" s="23" t="inlineStr">
+      <c r="B655" s="26" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - FARINHAS E DERIVADOS</t>
         </is>
       </c>
-      <c r="C655" s="23" t="inlineStr">
+      <c r="C655" s="26" t="inlineStr">
         <is>
           <t>FARINHA MANDIOCA AMAFIL AMARELA OURO 1KG</t>
         </is>
       </c>
-      <c r="D655" s="23" t="inlineStr">
+      <c r="D655" s="26" t="inlineStr">
         <is>
           <t>FARINHA DE MANDIOCA AMAFIL 1KG AMARELA OURO</t>
         </is>
       </c>
-      <c r="E655" s="23" t="inlineStr"/>
+      <c r="E655" s="26" t="inlineStr"/>
     </row>
     <row r="656">
       <c r="A656" s="17" t="n">
@@ -13797,25 +13792,25 @@
       <c r="E656" s="17" t="inlineStr"/>
     </row>
     <row r="657">
-      <c r="A657" s="23" t="n">
+      <c r="A657" s="26" t="n">
         <v>118874</v>
       </c>
-      <c r="B657" s="23" t="inlineStr">
+      <c r="B657" s="26" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - FARINHAS E DERIVADOS</t>
         </is>
       </c>
-      <c r="C657" s="23" t="inlineStr">
+      <c r="C657" s="26" t="inlineStr">
         <is>
           <t>FARINHA MANDIOCA BIJU AMAFIL 500GR TORRA</t>
         </is>
       </c>
-      <c r="D657" s="23" t="inlineStr">
+      <c r="D657" s="26" t="inlineStr">
         <is>
           <t>FARINHA DE MANDIOCA BIJU AMAFIL 500G TORRADA</t>
         </is>
       </c>
-      <c r="E657" s="23" t="inlineStr"/>
+      <c r="E657" s="26" t="inlineStr"/>
     </row>
     <row r="658">
       <c r="A658" t="n">
@@ -14278,25 +14273,25 @@
       </c>
     </row>
     <row r="681">
-      <c r="A681" s="23" t="n">
+      <c r="A681" s="26" t="n">
         <v>100024</v>
       </c>
-      <c r="B681" s="23" t="inlineStr">
+      <c r="B681" s="26" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - FARINHAS E DERIVADOS</t>
         </is>
       </c>
-      <c r="C681" s="23" t="inlineStr">
+      <c r="C681" s="26" t="inlineStr">
         <is>
           <t>FARINHA TRIGO DONA BENTA 1KG SEM FERMENT</t>
         </is>
       </c>
-      <c r="D681" s="23" t="inlineStr">
+      <c r="D681" s="26" t="inlineStr">
         <is>
           <t>FARINHA DE TRIGO DONA BENTA 1KG SEM FERMENTO</t>
         </is>
       </c>
-      <c r="E681" s="23" t="inlineStr"/>
+      <c r="E681" s="26" t="inlineStr"/>
     </row>
     <row r="682">
       <c r="A682" t="n">
@@ -14420,25 +14415,25 @@
       </c>
     </row>
     <row r="688">
-      <c r="A688" s="25" t="n">
+      <c r="A688" s="26" t="n">
         <v>100027</v>
       </c>
-      <c r="B688" s="25" t="inlineStr">
+      <c r="B688" s="26" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - FARINHAS E DERIVADOS</t>
         </is>
       </c>
-      <c r="C688" s="25" t="inlineStr">
+      <c r="C688" s="26" t="inlineStr">
         <is>
           <t>FARINHA TRIGO ORQUIDEA 1KG SEM FERMENTO</t>
         </is>
       </c>
-      <c r="D688" s="25" t="inlineStr">
+      <c r="D688" s="26" t="inlineStr">
         <is>
           <t>FARINHA DE TRIGO ORQUIDEA 1KG SEM FERMENTO</t>
         </is>
       </c>
-      <c r="E688" s="25" t="inlineStr"/>
+      <c r="E688" s="26" t="inlineStr"/>
     </row>
     <row r="689">
       <c r="A689" s="14" t="n">
@@ -14522,25 +14517,25 @@
       </c>
     </row>
     <row r="693">
-      <c r="A693" s="25" t="n">
+      <c r="A693" s="23" t="n">
         <v>213696</v>
       </c>
-      <c r="B693" s="25" t="inlineStr">
+      <c r="B693" s="23" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - FARINHAS E DERIVADOS</t>
         </is>
       </c>
-      <c r="C693" s="25" t="inlineStr">
+      <c r="C693" s="23" t="inlineStr">
         <is>
           <t>FARINHA TRIGO TRES COROAS 1KG</t>
         </is>
       </c>
-      <c r="D693" s="25" t="inlineStr">
+      <c r="D693" s="23" t="inlineStr">
         <is>
           <t>FARINHA DE TRIGO TRES COROAS 1KG</t>
         </is>
       </c>
-      <c r="E693" s="25" t="inlineStr"/>
+      <c r="E693" s="23" t="inlineStr"/>
     </row>
     <row r="694">
       <c r="A694" t="n">
@@ -14983,25 +14978,25 @@
       </c>
     </row>
     <row r="716">
-      <c r="A716" s="23" t="n">
+      <c r="A716" s="26" t="n">
         <v>320648</v>
       </c>
-      <c r="B716" s="23" t="inlineStr">
+      <c r="B716" s="26" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - FARINHAS E DERIVADOS</t>
         </is>
       </c>
-      <c r="C716" s="23" t="inlineStr">
+      <c r="C716" s="26" t="inlineStr">
         <is>
           <t>FLOCAO DE ARROZ 500GR URBANO</t>
         </is>
       </c>
-      <c r="D716" s="23" t="inlineStr">
+      <c r="D716" s="26" t="inlineStr">
         <is>
           <t>FLOCÃO DE ARROZ URBANO 500G</t>
         </is>
       </c>
-      <c r="E716" s="23" t="inlineStr"/>
+      <c r="E716" s="26" t="inlineStr"/>
     </row>
     <row r="717">
       <c r="A717" t="n">
@@ -15205,25 +15200,25 @@
       </c>
     </row>
     <row r="727">
-      <c r="A727" s="25" t="n">
+      <c r="A727" s="26" t="n">
         <v>294706</v>
       </c>
-      <c r="B727" s="25" t="inlineStr">
+      <c r="B727" s="26" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - FARINHAS E DERIVADOS</t>
         </is>
       </c>
-      <c r="C727" s="25" t="inlineStr">
+      <c r="C727" s="26" t="inlineStr">
         <is>
           <t>FLOCAO DE MILHO JALAPAO 400G</t>
         </is>
       </c>
-      <c r="D727" s="25" t="inlineStr">
+      <c r="D727" s="26" t="inlineStr">
         <is>
           <t>FLOCÃO DE MILHO JALAPÃO 400G</t>
         </is>
       </c>
-      <c r="E727" s="25" t="inlineStr"/>
+      <c r="E727" s="26" t="inlineStr"/>
     </row>
     <row r="728">
       <c r="A728" t="n">
@@ -15446,25 +15441,25 @@
       </c>
     </row>
     <row r="739">
-      <c r="A739" s="23" t="n">
+      <c r="A739" s="30" t="n">
         <v>149122</v>
       </c>
-      <c r="B739" s="23" t="inlineStr">
+      <c r="B739" s="30" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - FARINHAS E DERIVADOS</t>
         </is>
       </c>
-      <c r="C739" s="23" t="inlineStr">
+      <c r="C739" s="30" t="inlineStr">
         <is>
           <t>MASSA P/ TAPIOCA AMAFIL 1KG</t>
         </is>
       </c>
-      <c r="D739" s="23" t="inlineStr">
+      <c r="D739" s="30" t="inlineStr">
         <is>
           <t>MASSA PARA TAPIOCA AMAFIL 1KG</t>
         </is>
       </c>
-      <c r="E739" s="23" t="inlineStr"/>
+      <c r="E739" s="30" t="inlineStr"/>
     </row>
     <row r="740">
       <c r="A740" s="10" t="n">
@@ -15548,25 +15543,25 @@
       </c>
     </row>
     <row r="744">
-      <c r="A744" s="25" t="n">
+      <c r="A744" s="23" t="n">
         <v>313827</v>
       </c>
-      <c r="B744" s="25" t="inlineStr">
+      <c r="B744" s="23" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - FARINHAS E DERIVADOS</t>
         </is>
       </c>
-      <c r="C744" s="25" t="inlineStr">
+      <c r="C744" s="23" t="inlineStr">
         <is>
           <t>MASSA TAPIOCA AMAFIL MATUTO 1KG SEMI PRO</t>
         </is>
       </c>
-      <c r="D744" s="25" t="inlineStr">
+      <c r="D744" s="23" t="inlineStr">
         <is>
           <t>MASSA PARA TAPIOCA MATUTO 1KG SEMI PRONTO</t>
         </is>
       </c>
-      <c r="E744" s="25" t="inlineStr"/>
+      <c r="E744" s="23" t="inlineStr"/>
     </row>
     <row r="745">
       <c r="A745" t="n">
@@ -15910,25 +15905,25 @@
       </c>
     </row>
     <row r="762">
-      <c r="A762" s="23" t="n">
+      <c r="A762" s="26" t="n">
         <v>225440</v>
       </c>
-      <c r="B762" s="23" t="inlineStr">
+      <c r="B762" s="26" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - FARINHAS E DERIVADOS</t>
         </is>
       </c>
-      <c r="C762" s="23" t="inlineStr">
+      <c r="C762" s="26" t="inlineStr">
         <is>
           <t>MIST BOLO FLEISCHMANN CHOCOLATE 390G</t>
         </is>
       </c>
-      <c r="D762" s="23" t="inlineStr">
+      <c r="D762" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">MISTURA PARA BOLOS FLEISCHMANN 390G CHOCOLATE </t>
         </is>
       </c>
-      <c r="E762" s="23" t="inlineStr"/>
+      <c r="E762" s="26" t="inlineStr"/>
     </row>
     <row r="763">
       <c r="A763" t="n">
@@ -16651,25 +16646,25 @@
       </c>
     </row>
     <row r="799">
-      <c r="A799" s="25" t="n">
+      <c r="A799" s="23" t="n">
         <v>228421</v>
       </c>
-      <c r="B799" s="25" t="inlineStr">
+      <c r="B799" s="23" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - GORDURAS E MARGARINAS</t>
         </is>
       </c>
-      <c r="C799" s="25" t="inlineStr">
+      <c r="C799" s="23" t="inlineStr">
         <is>
           <t>AZEITE EXTRA VIRGEM 500ML</t>
         </is>
       </c>
-      <c r="D799" s="25" t="inlineStr">
+      <c r="D799" s="23" t="inlineStr">
         <is>
           <t>AZEITE DE OLIVA GOMES DA GOSTA 500ML EXTRA VIRGEM</t>
         </is>
       </c>
-      <c r="E799" s="25" t="inlineStr"/>
+      <c r="E799" s="23" t="inlineStr"/>
     </row>
     <row r="800">
       <c r="A800" t="n">
@@ -17054,25 +17049,25 @@
       </c>
     </row>
     <row r="819">
-      <c r="A819" s="35" t="n">
+      <c r="A819" s="26" t="n">
         <v>276943</v>
       </c>
-      <c r="B819" s="35" t="inlineStr">
+      <c r="B819" s="26" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - GORDURAS E MARGARINAS</t>
         </is>
       </c>
-      <c r="C819" s="35" t="inlineStr">
+      <c r="C819" s="26" t="inlineStr">
         <is>
           <t>MARGARINA DELICIA 1KG C CREME DE LEITE</t>
         </is>
       </c>
-      <c r="D819" s="35" t="inlineStr">
+      <c r="D819" s="26" t="inlineStr">
         <is>
           <t>MARGARINA DELICIA 1KG COM CREME DE LEITE</t>
         </is>
       </c>
-      <c r="E819" s="35" t="inlineStr"/>
+      <c r="E819" s="26" t="inlineStr"/>
     </row>
     <row r="820">
       <c r="A820" t="n">
@@ -17235,25 +17230,25 @@
       </c>
     </row>
     <row r="828">
-      <c r="A828" s="25" t="n">
+      <c r="A828" s="23" t="n">
         <v>146752</v>
       </c>
-      <c r="B828" s="25" t="inlineStr">
+      <c r="B828" s="23" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - GORDURAS E MARGARINAS</t>
         </is>
       </c>
-      <c r="C828" s="25" t="inlineStr">
+      <c r="C828" s="23" t="inlineStr">
         <is>
           <t>MARGARINA DORIANA CR 500 GR</t>
         </is>
       </c>
-      <c r="D828" s="25" t="inlineStr">
+      <c r="D828" s="23" t="inlineStr">
         <is>
           <t>MARGARINA DORIANA 500G CREMOSA</t>
         </is>
       </c>
-      <c r="E828" s="25" t="inlineStr"/>
+      <c r="E828" s="23" t="inlineStr"/>
     </row>
     <row r="829">
       <c r="A829" t="n">
@@ -18217,25 +18212,25 @@
       </c>
     </row>
     <row r="877">
-      <c r="A877" s="23" t="n">
+      <c r="A877" s="26" t="n">
         <v>101874</v>
       </c>
-      <c r="B877" s="23" t="inlineStr">
+      <c r="B877" s="26" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - LATICÍNIOS - BEBIDAS LACTEAS</t>
         </is>
       </c>
-      <c r="C877" s="23" t="inlineStr">
+      <c r="C877" s="26" t="inlineStr">
         <is>
           <t>ACHOC LIQ TODDYNHO 200ML CHOCOLATE</t>
         </is>
       </c>
-      <c r="D877" s="23" t="inlineStr">
+      <c r="D877" s="26" t="inlineStr">
         <is>
           <t>TODDYNHO 200ML CHOCOLATE</t>
         </is>
       </c>
-      <c r="E877" s="23" t="inlineStr"/>
+      <c r="E877" s="26" t="inlineStr"/>
     </row>
     <row r="878">
       <c r="A878" t="n">
@@ -18419,25 +18414,25 @@
       </c>
     </row>
     <row r="887">
-      <c r="A887" s="23" t="n">
+      <c r="A887" s="26" t="n">
         <v>193295</v>
       </c>
-      <c r="B887" s="23" t="inlineStr">
+      <c r="B887" s="26" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - LATICÍNIOS - DERIVADOS LACTEOS</t>
         </is>
       </c>
-      <c r="C887" s="23" t="inlineStr">
+      <c r="C887" s="26" t="inlineStr">
         <is>
           <t>CREME DE LEITE TRIANGULO 200GR 10%GORDUR</t>
         </is>
       </c>
-      <c r="D887" s="23" t="inlineStr">
+      <c r="D887" s="26" t="inlineStr">
         <is>
           <t>CREME DE LEITE TRIANGULO 200G 10% GORDURA</t>
         </is>
       </c>
-      <c r="E887" s="23" t="inlineStr"/>
+      <c r="E887" s="26" t="inlineStr"/>
     </row>
     <row r="888">
       <c r="A888" t="n">
@@ -18661,25 +18656,25 @@
       </c>
     </row>
     <row r="899">
-      <c r="A899" s="25" t="n">
+      <c r="A899" s="26" t="n">
         <v>101083</v>
       </c>
-      <c r="B899" s="25" t="inlineStr">
+      <c r="B899" s="26" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - LATICÍNIOS - DERIVADOS LACTEOS</t>
         </is>
       </c>
-      <c r="C899" s="25" t="inlineStr">
+      <c r="C899" s="26" t="inlineStr">
         <is>
           <t>LEITE CONDENSADO PIRACANJUBA 395GR TP</t>
         </is>
       </c>
-      <c r="D899" s="25" t="inlineStr">
+      <c r="D899" s="26" t="inlineStr">
         <is>
           <t>LEITE CONDENSADO PIRACANJUBA 395G</t>
         </is>
       </c>
-      <c r="E899" s="25" t="inlineStr"/>
+      <c r="E899" s="26" t="inlineStr"/>
     </row>
     <row r="900">
       <c r="A900" s="10" t="n">
@@ -19083,25 +19078,25 @@
       </c>
     </row>
     <row r="920">
-      <c r="A920" s="25" t="n">
+      <c r="A920" s="26" t="n">
         <v>101113</v>
       </c>
-      <c r="B920" s="25" t="inlineStr">
+      <c r="B920" s="26" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - LATICÍNIOS - LEITE</t>
         </is>
       </c>
-      <c r="C920" s="25" t="inlineStr">
+      <c r="C920" s="26" t="inlineStr">
         <is>
           <t>LEITE PIRACANJUBA UHT 1L INTEGRAL</t>
         </is>
       </c>
-      <c r="D920" s="25" t="inlineStr">
+      <c r="D920" s="26" t="inlineStr">
         <is>
           <t>LEITE LONGA VIDA PIRACANJUBA 1L INTEGRAL</t>
         </is>
       </c>
-      <c r="E920" s="25" t="inlineStr"/>
+      <c r="E920" s="26" t="inlineStr"/>
     </row>
     <row r="921">
       <c r="A921" s="14" t="n">
@@ -19185,25 +19180,25 @@
       </c>
     </row>
     <row r="925">
-      <c r="A925" s="25" t="n">
+      <c r="A925" s="26" t="n">
         <v>106922</v>
       </c>
-      <c r="B925" s="25" t="inlineStr">
+      <c r="B925" s="26" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - LATICÍNIOS - LEITE EM PÓ</t>
         </is>
       </c>
-      <c r="C925" s="25" t="inlineStr">
+      <c r="C925" s="26" t="inlineStr">
         <is>
           <t>LEITE EM PO CCGL 1KG INTEGRAL</t>
         </is>
       </c>
-      <c r="D925" s="25" t="inlineStr">
+      <c r="D925" s="26" t="inlineStr">
         <is>
           <t>LEITE EM PÓ CCGL 1KG INTEGRAL</t>
         </is>
       </c>
-      <c r="E925" s="25" t="inlineStr"/>
+      <c r="E925" s="26" t="inlineStr"/>
     </row>
     <row r="926">
       <c r="A926" t="n">
@@ -19666,25 +19661,25 @@
       </c>
     </row>
     <row r="949">
-      <c r="A949" s="35" t="n">
+      <c r="A949" s="26" t="n">
         <v>158733</v>
       </c>
-      <c r="B949" s="35" t="inlineStr">
+      <c r="B949" s="26" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - LATICÍNIOS - QUEIJO</t>
         </is>
       </c>
-      <c r="C949" s="35" t="inlineStr">
+      <c r="C949" s="26" t="inlineStr">
         <is>
           <t>QUEIJO MUSSARELA PIRAC FATIADO 150GR</t>
         </is>
       </c>
-      <c r="D949" s="35" t="inlineStr">
+      <c r="D949" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">QUEIJO MUSSARELA PIRACANJUBA 150G FATIADO </t>
         </is>
       </c>
-      <c r="E949" s="35" t="inlineStr"/>
+      <c r="E949" s="26" t="inlineStr"/>
     </row>
     <row r="950">
       <c r="A950" t="n">
@@ -20127,25 +20122,25 @@
       </c>
     </row>
     <row r="972">
-      <c r="A972" s="35" t="n">
+      <c r="A972" s="26" t="n">
         <v>104770</v>
       </c>
-      <c r="B972" s="35" t="inlineStr">
+      <c r="B972" s="26" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - LATICÍNIOS - QUEIJO</t>
         </is>
       </c>
-      <c r="C972" s="35" t="inlineStr">
+      <c r="C972" s="26" t="inlineStr">
         <is>
           <t>REQUEIJAO CREM TIROLEZ 200GR</t>
         </is>
       </c>
-      <c r="D972" s="35" t="inlineStr">
+      <c r="D972" s="26" t="inlineStr">
         <is>
           <t>REQUEIJAO CREMOSO TIROLEZ 200G</t>
         </is>
       </c>
-      <c r="E972" s="35" t="inlineStr"/>
+      <c r="E972" s="26" t="inlineStr"/>
     </row>
     <row r="973">
       <c r="A973" s="11" t="n">
@@ -20408,25 +20403,25 @@
       </c>
     </row>
     <row r="986">
-      <c r="A986" s="23" t="n">
+      <c r="A986" s="26" t="n">
         <v>290255</v>
       </c>
-      <c r="B986" s="23" t="inlineStr">
+      <c r="B986" s="26" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - MASSAS</t>
         </is>
       </c>
-      <c r="C986" s="23" t="inlineStr">
+      <c r="C986" s="26" t="inlineStr">
         <is>
           <t>MACARRÃO CRISTAL 500GR SEMOLA ESPAGUETE</t>
         </is>
       </c>
-      <c r="D986" s="23" t="inlineStr">
+      <c r="D986" s="26" t="inlineStr">
         <is>
           <t>MACARRÃO CRISTAL SEMOLA ESPAGUETE 500G</t>
         </is>
       </c>
-      <c r="E986" s="23" t="inlineStr"/>
+      <c r="E986" s="26" t="inlineStr"/>
     </row>
     <row r="987">
       <c r="A987" t="n">
@@ -20469,25 +20464,25 @@
       </c>
     </row>
     <row r="989">
-      <c r="A989" s="23" t="n">
+      <c r="A989" s="26" t="n">
         <v>108415</v>
       </c>
-      <c r="B989" s="23" t="inlineStr">
+      <c r="B989" s="26" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - MASSAS</t>
         </is>
       </c>
-      <c r="C989" s="23" t="inlineStr">
+      <c r="C989" s="26" t="inlineStr">
         <is>
           <t>MAC CRISTAL 500G SEMOLA PARAFUSO</t>
         </is>
       </c>
-      <c r="D989" s="23" t="inlineStr">
+      <c r="D989" s="26" t="inlineStr">
         <is>
           <t>MACARRÃO CRISTAL SEMOLA PARAFUSO 500G</t>
         </is>
       </c>
-      <c r="E989" s="23" t="inlineStr"/>
+      <c r="E989" s="26" t="inlineStr"/>
     </row>
     <row r="990">
       <c r="A990" t="n">
@@ -20651,25 +20646,25 @@
       </c>
     </row>
     <row r="998">
-      <c r="A998" s="23" t="n">
+      <c r="A998" s="26" t="n">
         <v>163423</v>
       </c>
-      <c r="B998" s="23" t="inlineStr">
+      <c r="B998" s="26" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - MASSAS</t>
         </is>
       </c>
-      <c r="C998" s="23" t="inlineStr">
+      <c r="C998" s="26" t="inlineStr">
         <is>
           <t>MAC. GALO INTEGRAL 500GR PARAFUSO 2</t>
         </is>
       </c>
-      <c r="D998" s="23" t="inlineStr">
+      <c r="D998" s="26" t="inlineStr">
         <is>
           <t>MACARRÃO GALO INTEGRAL 500G PARAFUSO</t>
         </is>
       </c>
-      <c r="E998" s="23" t="inlineStr"/>
+      <c r="E998" s="26" t="inlineStr"/>
     </row>
     <row r="999">
       <c r="A999" t="n">
@@ -20852,25 +20847,25 @@
       </c>
     </row>
     <row r="1008">
-      <c r="A1008" s="25" t="n">
+      <c r="A1008" s="23" t="n">
         <v>100642</v>
       </c>
-      <c r="B1008" s="25" t="inlineStr">
+      <c r="B1008" s="23" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - MASSAS</t>
         </is>
       </c>
-      <c r="C1008" s="25" t="inlineStr">
+      <c r="C1008" s="23" t="inlineStr">
         <is>
           <t>MAC PAULISTA ESPAGUETE 500GR SEMOLA</t>
         </is>
       </c>
-      <c r="D1008" s="25" t="inlineStr">
+      <c r="D1008" s="23" t="inlineStr">
         <is>
           <t>MACARRÃO PAULISTA ESPAGUETE SEMOLA 500G</t>
         </is>
       </c>
-      <c r="E1008" s="25" t="inlineStr"/>
+      <c r="E1008" s="23" t="inlineStr"/>
     </row>
     <row r="1009">
       <c r="A1009" t="n">
@@ -21393,25 +21388,25 @@
       </c>
     </row>
     <row r="1035">
-      <c r="A1035" s="23" t="n">
+      <c r="A1035" s="26" t="n">
         <v>100632</v>
       </c>
-      <c r="B1035" s="23" t="inlineStr">
+      <c r="B1035" s="26" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - MASSAS</t>
         </is>
       </c>
-      <c r="C1035" s="23" t="inlineStr">
+      <c r="C1035" s="26" t="inlineStr">
         <is>
           <t>MASSA LASANHA FORTALEZA SEMOLA 500G</t>
         </is>
       </c>
-      <c r="D1035" s="23" t="inlineStr">
+      <c r="D1035" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">MASSA PARA LASANHA FORTALEZA 500G SEMOLA </t>
         </is>
       </c>
-      <c r="E1035" s="23" t="inlineStr"/>
+      <c r="E1035" s="26" t="inlineStr"/>
     </row>
     <row r="1036">
       <c r="A1036" t="n">
@@ -23375,25 +23370,25 @@
       </c>
     </row>
     <row r="1134">
-      <c r="A1134" s="25" t="n">
+      <c r="A1134" s="23" t="n">
         <v>286928</v>
       </c>
-      <c r="B1134" s="25" t="inlineStr">
+      <c r="B1134" s="23" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - PÃES E BOLOS</t>
         </is>
       </c>
-      <c r="C1134" s="25" t="inlineStr">
+      <c r="C1134" s="23" t="inlineStr">
         <is>
           <t>PAO DE ALHO NUMERO 1 330GR APIMENTADO</t>
         </is>
       </c>
-      <c r="D1134" s="25" t="inlineStr">
+      <c r="D1134" s="23" t="inlineStr">
         <is>
           <t>PÃO DE ALHO NUMERO 1 330G APIMENTADO</t>
         </is>
       </c>
-      <c r="E1134" s="25" t="inlineStr"/>
+      <c r="E1134" s="23" t="inlineStr"/>
     </row>
     <row r="1135">
       <c r="A1135" t="n">
@@ -23436,25 +23431,25 @@
       </c>
     </row>
     <row r="1137">
-      <c r="A1137" s="25" t="n">
+      <c r="A1137" s="23" t="n">
         <v>313190</v>
       </c>
-      <c r="B1137" s="25" t="inlineStr">
+      <c r="B1137" s="23" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - PÃES E BOLOS</t>
         </is>
       </c>
-      <c r="C1137" s="25" t="inlineStr">
+      <c r="C1137" s="23" t="inlineStr">
         <is>
           <t>PAO DE ALHO NUMERO 1 330GR TRADICIONAL</t>
         </is>
       </c>
-      <c r="D1137" s="25" t="inlineStr">
+      <c r="D1137" s="23" t="inlineStr">
         <is>
           <t>PÃO DE ALHO NUMERO 1 330G TRADICIONAL</t>
         </is>
       </c>
-      <c r="E1137" s="25" t="inlineStr"/>
+      <c r="E1137" s="23" t="inlineStr"/>
     </row>
     <row r="1138">
       <c r="A1138" t="n">
@@ -23517,25 +23512,25 @@
       </c>
     </row>
     <row r="1141">
-      <c r="A1141" s="25" t="n">
+      <c r="A1141" s="23" t="n">
         <v>110095</v>
       </c>
-      <c r="B1141" s="25" t="inlineStr">
+      <c r="B1141" s="23" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - PÃES E BOLOS</t>
         </is>
       </c>
-      <c r="C1141" s="25" t="inlineStr">
+      <c r="C1141" s="23" t="inlineStr">
         <is>
           <t>PAO FORMA PULLMAN 480GR TRADICIONAL</t>
         </is>
       </c>
-      <c r="D1141" s="25" t="inlineStr">
+      <c r="D1141" s="23" t="inlineStr">
         <is>
           <t>PÃO DE FORMA PULLMAN 480G TRADICIONAL</t>
         </is>
       </c>
-      <c r="E1141" s="25" t="inlineStr"/>
+      <c r="E1141" s="23" t="inlineStr"/>
     </row>
     <row r="1142">
       <c r="A1142" t="n">
@@ -24418,25 +24413,25 @@
       </c>
     </row>
     <row r="1186">
-      <c r="A1186" s="35" t="n">
+      <c r="A1186" s="26" t="n">
         <v>105842</v>
       </c>
-      <c r="B1186" s="35" t="inlineStr">
+      <c r="B1186" s="26" t="inlineStr">
         <is>
           <t>#03 AÇOUGUE - #01 AVES</t>
         </is>
       </c>
-      <c r="C1186" s="35" t="inlineStr">
+      <c r="C1186" s="26" t="inlineStr">
         <is>
           <t>ASA FRANGO KG</t>
         </is>
       </c>
-      <c r="D1186" s="35" t="inlineStr">
+      <c r="D1186" s="26" t="inlineStr">
         <is>
           <t>ASA DE FRANGO KG</t>
         </is>
       </c>
-      <c r="E1186" s="35" t="inlineStr"/>
+      <c r="E1186" s="26" t="inlineStr"/>
     </row>
     <row r="1187">
       <c r="A1187" t="n">
@@ -24601,25 +24596,25 @@
       </c>
     </row>
     <row r="1195">
-      <c r="A1195" s="35" t="n">
+      <c r="A1195" s="26" t="n">
         <v>105838</v>
       </c>
-      <c r="B1195" s="35" t="inlineStr">
+      <c r="B1195" s="26" t="inlineStr">
         <is>
           <t>#03 AÇOUGUE - #01 AVES</t>
         </is>
       </c>
-      <c r="C1195" s="35" t="inlineStr">
+      <c r="C1195" s="26" t="inlineStr">
         <is>
           <t>COXA/SOBRECOXA FRANGO KG</t>
         </is>
       </c>
-      <c r="D1195" s="35" t="inlineStr">
+      <c r="D1195" s="26" t="inlineStr">
         <is>
           <t>COXA COM SOBRECOXA DE FRANGO KG</t>
         </is>
       </c>
-      <c r="E1195" s="35" t="inlineStr"/>
+      <c r="E1195" s="26" t="inlineStr"/>
     </row>
     <row r="1196">
       <c r="A1196" t="n">
@@ -24862,25 +24857,25 @@
       </c>
     </row>
     <row r="1208">
-      <c r="A1208" s="35" t="n">
+      <c r="A1208" s="26" t="n">
         <v>105840</v>
       </c>
-      <c r="B1208" s="35" t="inlineStr">
+      <c r="B1208" s="26" t="inlineStr">
         <is>
           <t>#03 AÇOUGUE - #01 AVES</t>
         </is>
       </c>
-      <c r="C1208" s="35" t="inlineStr">
+      <c r="C1208" s="26" t="inlineStr">
         <is>
           <t>COXINHA DA ASA FRANGO KG</t>
         </is>
       </c>
-      <c r="D1208" s="35" t="inlineStr">
+      <c r="D1208" s="26" t="inlineStr">
         <is>
           <t>COXINHA DA ASA DE FRANGO KG</t>
         </is>
       </c>
-      <c r="E1208" s="35" t="inlineStr"/>
+      <c r="E1208" s="26" t="inlineStr"/>
     </row>
     <row r="1209">
       <c r="A1209" s="20" t="n">
@@ -24904,25 +24899,25 @@
       <c r="E1209" s="20" t="inlineStr"/>
     </row>
     <row r="1210">
-      <c r="A1210" s="35" t="n">
+      <c r="A1210" s="26" t="n">
         <v>108785</v>
       </c>
-      <c r="B1210" s="35" t="inlineStr">
+      <c r="B1210" s="26" t="inlineStr">
         <is>
           <t>#03 AÇOUGUE - #01 AVES</t>
         </is>
       </c>
-      <c r="C1210" s="35" t="inlineStr">
+      <c r="C1210" s="26" t="inlineStr">
         <is>
           <t>COXINHA DA ASA SADIA 1KG PACOTE DRUMETTE</t>
         </is>
       </c>
-      <c r="D1210" s="35" t="inlineStr">
+      <c r="D1210" s="26" t="inlineStr">
         <is>
           <t>COXINHA DA ASA DE FRANGO SADIA PCT 1KG DRUMETE</t>
         </is>
       </c>
-      <c r="E1210" s="35" t="inlineStr"/>
+      <c r="E1210" s="26" t="inlineStr"/>
     </row>
     <row r="1211">
       <c r="A1211" t="n">
@@ -25105,25 +25100,25 @@
       </c>
     </row>
     <row r="1220">
-      <c r="A1220" s="35" t="n">
+      <c r="A1220" s="26" t="n">
         <v>109597</v>
       </c>
-      <c r="B1220" s="35" t="inlineStr">
+      <c r="B1220" s="26" t="inlineStr">
         <is>
           <t>#03 AÇOUGUE - #01 AVES</t>
         </is>
       </c>
-      <c r="C1220" s="35" t="inlineStr">
+      <c r="C1220" s="26" t="inlineStr">
         <is>
           <t>FILE PEITO FRANGO KG</t>
         </is>
       </c>
-      <c r="D1220" s="35" t="inlineStr">
+      <c r="D1220" s="26" t="inlineStr">
         <is>
           <t>FILÉ DE PEITO DE FRANGO KG</t>
         </is>
       </c>
-      <c r="E1220" s="35" t="inlineStr"/>
+      <c r="E1220" s="26" t="inlineStr"/>
     </row>
     <row r="1221">
       <c r="A1221" s="13" t="n">
@@ -25267,25 +25262,25 @@
       </c>
     </row>
     <row r="1228">
-      <c r="A1228" s="35" t="n">
+      <c r="A1228" s="26" t="n">
         <v>108856</v>
       </c>
-      <c r="B1228" s="35" t="inlineStr">
+      <c r="B1228" s="26" t="inlineStr">
         <is>
           <t>#03 AÇOUGUE - #01 AVES</t>
         </is>
       </c>
-      <c r="C1228" s="35" t="inlineStr">
+      <c r="C1228" s="26" t="inlineStr">
         <is>
           <t>FILE PEITO SADIA PCT S/OPC 1KG PFFZP</t>
         </is>
       </c>
-      <c r="D1228" s="35" t="inlineStr">
+      <c r="D1228" s="26" t="inlineStr">
         <is>
           <t>FILE PEITO DE FRANGO SADIA PCT 1KG</t>
         </is>
       </c>
-      <c r="E1228" s="35" t="inlineStr"/>
+      <c r="E1228" s="26" t="inlineStr"/>
     </row>
     <row r="1229">
       <c r="A1229" t="n">
@@ -25388,25 +25383,25 @@
       </c>
     </row>
     <row r="1234">
-      <c r="A1234" s="35" t="n">
+      <c r="A1234" s="26" t="n">
         <v>119927</v>
       </c>
-      <c r="B1234" s="35" t="inlineStr">
+      <c r="B1234" s="26" t="inlineStr">
         <is>
           <t>#03 AÇOUGUE - #01 AVES</t>
         </is>
       </c>
-      <c r="C1234" s="35" t="inlineStr">
+      <c r="C1234" s="26" t="inlineStr">
         <is>
           <t>FRANGO CONG AMERICANO KG</t>
         </is>
       </c>
-      <c r="D1234" s="35" t="inlineStr">
+      <c r="D1234" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">FRANGO AMERICANO KG CONGELADO </t>
         </is>
       </c>
-      <c r="E1234" s="35" t="inlineStr"/>
+      <c r="E1234" s="26" t="inlineStr"/>
     </row>
     <row r="1235">
       <c r="A1235" t="n">
@@ -25469,25 +25464,25 @@
       </c>
     </row>
     <row r="1238">
-      <c r="A1238" s="35" t="n">
+      <c r="A1238" s="26" t="n">
         <v>298984</v>
       </c>
-      <c r="B1238" s="35" t="inlineStr">
+      <c r="B1238" s="26" t="inlineStr">
         <is>
           <t>#03 AÇOUGUE - #01 AVES</t>
         </is>
       </c>
-      <c r="C1238" s="35" t="inlineStr">
+      <c r="C1238" s="26" t="inlineStr">
         <is>
           <t>FRANGO DE PADARIA SEARA 1KG A PASSARINHO</t>
         </is>
       </c>
-      <c r="D1238" s="35" t="inlineStr">
+      <c r="D1238" s="26" t="inlineStr">
         <is>
           <t>FRANGO DE PADARIA SEARA 1KG A PASSARINHO</t>
         </is>
       </c>
-      <c r="E1238" s="35" t="inlineStr"/>
+      <c r="E1238" s="26" t="inlineStr"/>
     </row>
     <row r="1239">
       <c r="A1239" t="n">
@@ -25510,25 +25505,25 @@
       </c>
     </row>
     <row r="1240">
-      <c r="A1240" s="25" t="n">
+      <c r="A1240" s="23" t="n">
         <v>105853</v>
       </c>
-      <c r="B1240" s="25" t="inlineStr">
+      <c r="B1240" s="23" t="inlineStr">
         <is>
           <t>#03 AÇOUGUE - #01 AVES</t>
         </is>
       </c>
-      <c r="C1240" s="25" t="inlineStr">
+      <c r="C1240" s="23" t="inlineStr">
         <is>
           <t>FRANGO CONG MARINGA KG</t>
         </is>
       </c>
-      <c r="D1240" s="25" t="inlineStr">
+      <c r="D1240" s="23" t="inlineStr">
         <is>
           <t>FRANGO MARINGA KG CONGELADO</t>
         </is>
       </c>
-      <c r="E1240" s="25" t="inlineStr"/>
+      <c r="E1240" s="23" t="inlineStr"/>
     </row>
     <row r="1241">
       <c r="A1241" s="10" t="n">
@@ -26035,46 +26030,46 @@
       <c r="E1265" s="20" t="inlineStr"/>
     </row>
     <row r="1266">
-      <c r="A1266" s="35" t="n">
+      <c r="A1266" s="31" t="n">
         <v>157014</v>
       </c>
-      <c r="B1266" s="35" t="inlineStr">
+      <c r="B1266" s="31" t="inlineStr">
         <is>
           <t>#03 AÇOUGUE - #02 BOVINA</t>
         </is>
       </c>
-      <c r="C1266" s="35" t="inlineStr">
+      <c r="C1266" s="31" t="inlineStr">
         <is>
           <t>BOVINO - ACEM C/ OSSO KG</t>
         </is>
       </c>
-      <c r="D1266" s="35" t="inlineStr">
+      <c r="D1266" s="31" t="inlineStr">
         <is>
           <t>ACEM BOVINO COM OSSO KG</t>
         </is>
       </c>
-      <c r="E1266" s="35" t="inlineStr"/>
+      <c r="E1266" s="31" t="inlineStr"/>
     </row>
     <row r="1267">
-      <c r="A1267" s="14" t="n">
+      <c r="A1267" s="32" t="n">
         <v>105470</v>
       </c>
-      <c r="B1267" s="14" t="inlineStr">
+      <c r="B1267" s="32" t="inlineStr">
         <is>
           <t>#03 AÇOUGUE - #02 BOVINA</t>
         </is>
       </c>
-      <c r="C1267" s="14" t="inlineStr">
+      <c r="C1267" s="32" t="inlineStr">
         <is>
           <t>BOVINO - ACEM KG</t>
         </is>
       </c>
-      <c r="D1267" s="14" t="inlineStr">
+      <c r="D1267" s="32" t="inlineStr">
         <is>
           <t>ACEM BOVINO KG</t>
         </is>
       </c>
-      <c r="E1267" s="14" t="inlineStr"/>
+      <c r="E1267" s="32" t="inlineStr"/>
     </row>
     <row r="1268">
       <c r="A1268" t="n">
@@ -26117,25 +26112,25 @@
       </c>
     </row>
     <row r="1270">
-      <c r="A1270" s="35" t="n">
+      <c r="A1270" s="26" t="n">
         <v>105459</v>
       </c>
-      <c r="B1270" s="35" t="inlineStr">
+      <c r="B1270" s="26" t="inlineStr">
         <is>
           <t>#03 AÇOUGUE - #02 BOVINA</t>
         </is>
       </c>
-      <c r="C1270" s="35" t="inlineStr">
+      <c r="C1270" s="26" t="inlineStr">
         <is>
           <t>BOVINO - BISTECA MACA PEITO KG</t>
         </is>
       </c>
-      <c r="D1270" s="35" t="inlineStr">
+      <c r="D1270" s="26" t="inlineStr">
         <is>
           <t>BISTECA BOVINA DA MAÇÃ DO PEITO KG</t>
         </is>
       </c>
-      <c r="E1270" s="35" t="inlineStr"/>
+      <c r="E1270" s="26" t="inlineStr"/>
     </row>
     <row r="1271">
       <c r="A1271" s="11" t="n">
@@ -26178,25 +26173,25 @@
       </c>
     </row>
     <row r="1273">
-      <c r="A1273" s="25" t="n">
+      <c r="A1273" s="23" t="n">
         <v>105461</v>
       </c>
-      <c r="B1273" s="25" t="inlineStr">
+      <c r="B1273" s="23" t="inlineStr">
         <is>
           <t>#03 AÇOUGUE - #02 BOVINA</t>
         </is>
       </c>
-      <c r="C1273" s="25" t="inlineStr">
+      <c r="C1273" s="23" t="inlineStr">
         <is>
           <t>BOVINO - BISTECA CONTRA FILE KG</t>
         </is>
       </c>
-      <c r="D1273" s="25" t="inlineStr">
+      <c r="D1273" s="23" t="inlineStr">
         <is>
           <t>BISTECA BOVINA DO CONTRA FILE KG</t>
         </is>
       </c>
-      <c r="E1273" s="25" t="inlineStr"/>
+      <c r="E1273" s="23" t="inlineStr"/>
     </row>
     <row r="1274">
       <c r="A1274" t="n">
@@ -26219,25 +26214,25 @@
       </c>
     </row>
     <row r="1275">
-      <c r="A1275" s="33" t="n">
+      <c r="A1275" s="26" t="n">
         <v>239334</v>
       </c>
-      <c r="B1275" s="33" t="inlineStr">
+      <c r="B1275" s="26" t="inlineStr">
         <is>
           <t>#03 AÇOUGUE - #02 BOVINA</t>
         </is>
       </c>
-      <c r="C1275" s="33" t="inlineStr">
+      <c r="C1275" s="26" t="inlineStr">
         <is>
           <t>BOVINO - CAPA DO CONTRA FILE KG</t>
         </is>
       </c>
-      <c r="D1275" s="33" t="inlineStr">
+      <c r="D1275" s="26" t="inlineStr">
         <is>
           <t>CAPA DO CONTRA FILE KG</t>
         </is>
       </c>
-      <c r="E1275" s="33" t="inlineStr"/>
+      <c r="E1275" s="26" t="inlineStr"/>
     </row>
     <row r="1276">
       <c r="A1276" s="18" t="n">
@@ -26281,25 +26276,25 @@
       </c>
     </row>
     <row r="1278">
-      <c r="A1278" s="17" t="n">
+      <c r="A1278" s="33" t="n">
         <v>322584</v>
       </c>
-      <c r="B1278" s="17" t="inlineStr">
+      <c r="B1278" s="33" t="inlineStr">
         <is>
           <t>#03 AÇOUGUE - #02 BOVINA</t>
         </is>
       </c>
-      <c r="C1278" s="17" t="inlineStr">
+      <c r="C1278" s="33" t="inlineStr">
         <is>
           <t>CARNE DE SOL KG PRIMEIRA</t>
         </is>
       </c>
-      <c r="D1278" s="17" t="inlineStr">
+      <c r="D1278" s="33" t="inlineStr">
         <is>
           <t>CARNE DE SOL KG PRIMEIRA</t>
         </is>
       </c>
-      <c r="E1278" s="17" t="inlineStr"/>
+      <c r="E1278" s="33" t="inlineStr"/>
     </row>
     <row r="1279">
       <c r="A1279" t="n">
@@ -26322,25 +26317,25 @@
       </c>
     </row>
     <row r="1280">
-      <c r="A1280" s="35" t="n">
+      <c r="A1280" s="26" t="n">
         <v>105468</v>
       </c>
-      <c r="B1280" s="35" t="inlineStr">
+      <c r="B1280" s="26" t="inlineStr">
         <is>
           <t>#03 AÇOUGUE - #02 BOVINA</t>
         </is>
       </c>
-      <c r="C1280" s="35" t="inlineStr">
+      <c r="C1280" s="26" t="inlineStr">
         <is>
           <t>BOVINO - CARNE MOIDA KG</t>
         </is>
       </c>
-      <c r="D1280" s="35" t="inlineStr">
+      <c r="D1280" s="26" t="inlineStr">
         <is>
           <t>CARNE MOIDA KG</t>
         </is>
       </c>
-      <c r="E1280" s="35" t="inlineStr"/>
+      <c r="E1280" s="26" t="inlineStr"/>
     </row>
     <row r="1281">
       <c r="A1281" s="17" t="n">
@@ -26364,46 +26359,46 @@
       <c r="E1281" s="17" t="inlineStr"/>
     </row>
     <row r="1282">
-      <c r="A1282" s="25" t="n">
+      <c r="A1282" s="23" t="n">
         <v>105451</v>
       </c>
-      <c r="B1282" s="25" t="inlineStr">
+      <c r="B1282" s="23" t="inlineStr">
         <is>
           <t>#03 AÇOUGUE - #02 BOVINA</t>
         </is>
       </c>
-      <c r="C1282" s="25" t="inlineStr">
+      <c r="C1282" s="23" t="inlineStr">
         <is>
           <t>BOVINO - CONTRA FILE KG</t>
         </is>
       </c>
-      <c r="D1282" s="25" t="inlineStr">
+      <c r="D1282" s="23" t="inlineStr">
         <is>
           <t>CONTRA FILÉ KG</t>
         </is>
       </c>
-      <c r="E1282" s="25" t="inlineStr"/>
+      <c r="E1282" s="23" t="inlineStr"/>
     </row>
     <row r="1283">
-      <c r="A1283" s="33" t="n">
+      <c r="A1283" s="26" t="n">
         <v>105463</v>
       </c>
-      <c r="B1283" s="33" t="inlineStr">
+      <c r="B1283" s="26" t="inlineStr">
         <is>
           <t>#03 AÇOUGUE - #02 BOVINA</t>
         </is>
       </c>
-      <c r="C1283" s="33" t="inlineStr">
+      <c r="C1283" s="26" t="inlineStr">
         <is>
           <t>BOVINO - CORACAO KG</t>
         </is>
       </c>
-      <c r="D1283" s="33" t="inlineStr">
+      <c r="D1283" s="26" t="inlineStr">
         <is>
           <t>CORAÇÃO BOVINO KG</t>
         </is>
       </c>
-      <c r="E1283" s="33" t="inlineStr"/>
+      <c r="E1283" s="26" t="inlineStr"/>
     </row>
     <row r="1284">
       <c r="A1284" t="n">
@@ -26447,25 +26442,25 @@
       <c r="E1285" s="16" t="inlineStr"/>
     </row>
     <row r="1286">
-      <c r="A1286" s="25" t="n">
+      <c r="A1286" s="23" t="n">
         <v>105471</v>
       </c>
-      <c r="B1286" s="25" t="inlineStr">
+      <c r="B1286" s="23" t="inlineStr">
         <is>
           <t>#03 AÇOUGUE - #02 BOVINA</t>
         </is>
       </c>
-      <c r="C1286" s="25" t="inlineStr">
+      <c r="C1286" s="23" t="inlineStr">
         <is>
           <t>BOVINO - COSTELA KG</t>
         </is>
       </c>
-      <c r="D1286" s="25" t="inlineStr">
+      <c r="D1286" s="23" t="inlineStr">
         <is>
           <t>COSTELA BOVINA KG</t>
         </is>
       </c>
-      <c r="E1286" s="25" t="inlineStr"/>
+      <c r="E1286" s="23" t="inlineStr"/>
     </row>
     <row r="1287">
       <c r="A1287" t="n">
@@ -26488,46 +26483,46 @@
       </c>
     </row>
     <row r="1288">
-      <c r="A1288" s="33" t="n">
+      <c r="A1288" s="26" t="n">
         <v>105449</v>
       </c>
-      <c r="B1288" s="33" t="inlineStr">
+      <c r="B1288" s="26" t="inlineStr">
         <is>
           <t>#03 AÇOUGUE - #02 BOVINA</t>
         </is>
       </c>
-      <c r="C1288" s="33" t="inlineStr">
+      <c r="C1288" s="26" t="inlineStr">
         <is>
           <t>BOVINO - COXAO DURO KG</t>
         </is>
       </c>
-      <c r="D1288" s="33" t="inlineStr">
+      <c r="D1288" s="26" t="inlineStr">
         <is>
           <t>COXÃO DURO KG</t>
         </is>
       </c>
-      <c r="E1288" s="33" t="inlineStr"/>
+      <c r="E1288" s="26" t="inlineStr"/>
     </row>
     <row r="1289">
-      <c r="A1289" s="33" t="n">
+      <c r="A1289" s="31" t="n">
         <v>105435</v>
       </c>
-      <c r="B1289" s="33" t="inlineStr">
+      <c r="B1289" s="31" t="inlineStr">
         <is>
           <t>#03 AÇOUGUE - #02 BOVINA</t>
         </is>
       </c>
-      <c r="C1289" s="33" t="inlineStr">
+      <c r="C1289" s="31" t="inlineStr">
         <is>
           <t>BOVINO - COXAO MOLE KG</t>
         </is>
       </c>
-      <c r="D1289" s="33" t="inlineStr">
+      <c r="D1289" s="31" t="inlineStr">
         <is>
           <t>COXÃO MOLE KG</t>
         </is>
       </c>
-      <c r="E1289" s="33" t="inlineStr"/>
+      <c r="E1289" s="31" t="inlineStr"/>
     </row>
     <row r="1290">
       <c r="A1290" t="n">
@@ -26590,24 +26585,25 @@
       </c>
     </row>
     <row r="1293">
-      <c r="A1293" t="n">
+      <c r="A1293" s="29" t="n">
         <v>106065</v>
       </c>
-      <c r="B1293" t="inlineStr">
+      <c r="B1293" s="29" t="inlineStr">
         <is>
           <t>#03 AÇOUGUE - #02 BOVINA</t>
         </is>
       </c>
-      <c r="C1293" t="inlineStr">
+      <c r="C1293" s="29" t="inlineStr">
         <is>
           <t>BOVINO - FIGADO KG.</t>
         </is>
       </c>
-      <c r="D1293" t="inlineStr">
+      <c r="D1293" s="29" t="inlineStr">
         <is>
           <t>FIGADO BOVINO KG</t>
         </is>
       </c>
+      <c r="E1293" s="29" t="inlineStr"/>
     </row>
     <row r="1294">
       <c r="A1294" t="n">
@@ -26630,25 +26626,25 @@
       </c>
     </row>
     <row r="1295">
-      <c r="A1295" s="25" t="n">
+      <c r="A1295" s="23" t="n">
         <v>105474</v>
       </c>
-      <c r="B1295" s="25" t="inlineStr">
+      <c r="B1295" s="23" t="inlineStr">
         <is>
           <t>#03 AÇOUGUE - #02 BOVINA</t>
         </is>
       </c>
-      <c r="C1295" s="25" t="inlineStr">
+      <c r="C1295" s="23" t="inlineStr">
         <is>
           <t>BOVINO - FRALDINHA KG</t>
         </is>
       </c>
-      <c r="D1295" s="25" t="inlineStr">
+      <c r="D1295" s="23" t="inlineStr">
         <is>
           <t>FRALDINHA BOVINA KG</t>
         </is>
       </c>
-      <c r="E1295" s="25" t="inlineStr"/>
+      <c r="E1295" s="23" t="inlineStr"/>
     </row>
     <row r="1296">
       <c r="A1296" t="n">
@@ -26692,25 +26688,25 @@
       <c r="E1297" s="21" t="inlineStr"/>
     </row>
     <row r="1298">
-      <c r="A1298" s="33" t="n">
+      <c r="A1298" s="31" t="n">
         <v>107260</v>
       </c>
-      <c r="B1298" s="33" t="inlineStr">
+      <c r="B1298" s="31" t="inlineStr">
         <is>
           <t>#03 AÇOUGUE - #02 BOVINA</t>
         </is>
       </c>
-      <c r="C1298" s="33" t="inlineStr">
+      <c r="C1298" s="31" t="inlineStr">
         <is>
           <t>BOVINO - MACA DO PEITO KG</t>
         </is>
       </c>
-      <c r="D1298" s="33" t="inlineStr">
+      <c r="D1298" s="31" t="inlineStr">
         <is>
           <t>MAÇÃ DO PEITO KG</t>
         </is>
       </c>
-      <c r="E1298" s="33" t="inlineStr"/>
+      <c r="E1298" s="31" t="inlineStr"/>
     </row>
     <row r="1299">
       <c r="A1299" t="n">
@@ -26793,25 +26789,25 @@
       </c>
     </row>
     <row r="1303">
-      <c r="A1303" s="35" t="n">
+      <c r="A1303" s="26" t="n">
         <v>105475</v>
       </c>
-      <c r="B1303" s="35" t="inlineStr">
+      <c r="B1303" s="26" t="inlineStr">
         <is>
           <t>#03 AÇOUGUE - #02 BOVINA</t>
         </is>
       </c>
-      <c r="C1303" s="35" t="inlineStr">
+      <c r="C1303" s="26" t="inlineStr">
         <is>
           <t>BOVINO - MUSCULO KG</t>
         </is>
       </c>
-      <c r="D1303" s="35" t="inlineStr">
+      <c r="D1303" s="26" t="inlineStr">
         <is>
           <t>MUSCULO BOVINO KG</t>
         </is>
       </c>
-      <c r="E1303" s="35" t="inlineStr"/>
+      <c r="E1303" s="26" t="inlineStr"/>
     </row>
     <row r="1304">
       <c r="A1304" t="n">
@@ -26935,24 +26931,25 @@
       </c>
     </row>
     <row r="1310">
-      <c r="A1310" t="n">
+      <c r="A1310" s="29" t="n">
         <v>298422</v>
       </c>
-      <c r="B1310" t="inlineStr">
+      <c r="B1310" s="29" t="inlineStr">
         <is>
           <t>#03 AÇOUGUE - #03 SUÍNA</t>
         </is>
       </c>
-      <c r="C1310" t="inlineStr">
+      <c r="C1310" s="29" t="inlineStr">
         <is>
           <t>SUINO - CAIPIRA KG</t>
         </is>
       </c>
-      <c r="D1310" t="inlineStr">
+      <c r="D1310" s="29" t="inlineStr">
         <is>
           <t>SUINO CAIPIRA KG</t>
         </is>
       </c>
+      <c r="E1310" s="29" t="inlineStr"/>
     </row>
     <row r="1311">
       <c r="A1311" t="n">
@@ -26996,25 +26993,25 @@
       <c r="E1312" s="21" t="inlineStr"/>
     </row>
     <row r="1313">
-      <c r="A1313" s="35" t="n">
+      <c r="A1313" s="31" t="n">
         <v>105062</v>
       </c>
-      <c r="B1313" s="35" t="inlineStr">
+      <c r="B1313" s="31" t="inlineStr">
         <is>
           <t>#03 AÇOUGUE - #03 SUÍNA</t>
         </is>
       </c>
-      <c r="C1313" s="35" t="inlineStr">
+      <c r="C1313" s="31" t="inlineStr">
         <is>
           <t>SUINO - BISTECA PERNIL FRESCA KG</t>
         </is>
       </c>
-      <c r="D1313" s="35" t="inlineStr">
+      <c r="D1313" s="31" t="inlineStr">
         <is>
           <t>BISTECA SUINA DO PERNIL KG</t>
         </is>
       </c>
-      <c r="E1313" s="35" t="inlineStr"/>
+      <c r="E1313" s="31" t="inlineStr"/>
     </row>
     <row r="1314">
       <c r="A1314" t="n">
@@ -27037,25 +27034,25 @@
       </c>
     </row>
     <row r="1315">
-      <c r="A1315" s="35" t="n">
+      <c r="A1315" s="26" t="n">
         <v>105433</v>
       </c>
-      <c r="B1315" s="35" t="inlineStr">
+      <c r="B1315" s="26" t="inlineStr">
         <is>
           <t>#03 AÇOUGUE - #03 SUÍNA</t>
         </is>
       </c>
-      <c r="C1315" s="35" t="inlineStr">
+      <c r="C1315" s="26" t="inlineStr">
         <is>
           <t>SUINO - COSTELA SUINA KG</t>
         </is>
       </c>
-      <c r="D1315" s="35" t="inlineStr">
+      <c r="D1315" s="26" t="inlineStr">
         <is>
           <t>COSTELA SUINA KG</t>
         </is>
       </c>
-      <c r="E1315" s="35" t="inlineStr"/>
+      <c r="E1315" s="26" t="inlineStr"/>
     </row>
     <row r="1316">
       <c r="A1316" t="n">
@@ -27382,25 +27379,25 @@
       </c>
     </row>
     <row r="1332">
-      <c r="A1332" s="35" t="n">
+      <c r="A1332" s="26" t="n">
         <v>106034</v>
       </c>
-      <c r="B1332" s="35" t="inlineStr">
+      <c r="B1332" s="26" t="inlineStr">
         <is>
           <t>#03 AÇOUGUE - #03 SUÍNA</t>
         </is>
       </c>
-      <c r="C1332" s="35" t="inlineStr">
+      <c r="C1332" s="26" t="inlineStr">
         <is>
           <t>SUINO - SUAN KG</t>
         </is>
       </c>
-      <c r="D1332" s="35" t="inlineStr">
+      <c r="D1332" s="26" t="inlineStr">
         <is>
           <t>SUAN SUINA KG</t>
         </is>
       </c>
-      <c r="E1332" s="35" t="inlineStr"/>
+      <c r="E1332" s="26" t="inlineStr"/>
     </row>
     <row r="1333">
       <c r="A1333" s="17" t="n">
@@ -27664,46 +27661,46 @@
       </c>
     </row>
     <row r="1346">
-      <c r="A1346" s="25" t="n">
+      <c r="A1346" s="23" t="n">
         <v>114836</v>
       </c>
-      <c r="B1346" s="25" t="inlineStr">
+      <c r="B1346" s="23" t="inlineStr">
         <is>
           <t>#03 AÇOUGUE - #04 PEIXES</t>
         </is>
       </c>
-      <c r="C1346" s="25" t="inlineStr">
+      <c r="C1346" s="23" t="inlineStr">
         <is>
           <t>FILE DE SALMAO COSTA SUL C/PELE(PEDACOS</t>
         </is>
       </c>
-      <c r="D1346" s="25" t="inlineStr">
+      <c r="D1346" s="23" t="inlineStr">
         <is>
           <t>FILÉ DE SALMÃO COSTA SUL 500G COM PELE</t>
         </is>
       </c>
-      <c r="E1346" s="25" t="inlineStr"/>
+      <c r="E1346" s="23" t="inlineStr"/>
     </row>
     <row r="1347">
-      <c r="A1347" s="25" t="n">
+      <c r="A1347" s="23" t="n">
         <v>204452</v>
       </c>
-      <c r="B1347" s="25" t="inlineStr">
+      <c r="B1347" s="23" t="inlineStr">
         <is>
           <t>#03 AÇOUGUE - #04 PEIXES</t>
         </is>
       </c>
-      <c r="C1347" s="25" t="inlineStr">
+      <c r="C1347" s="23" t="inlineStr">
         <is>
           <t>FILE TILAPIA IQF BOUA 400G</t>
         </is>
       </c>
-      <c r="D1347" s="25" t="inlineStr">
+      <c r="D1347" s="23" t="inlineStr">
         <is>
           <t>FILÉ DE TILAPIA BOUA 400G</t>
         </is>
       </c>
-      <c r="E1347" s="25" t="inlineStr"/>
+      <c r="E1347" s="23" t="inlineStr"/>
     </row>
     <row r="1348">
       <c r="A1348" t="n">
@@ -27986,25 +27983,25 @@
       </c>
     </row>
     <row r="1362">
-      <c r="A1362" s="25" t="n">
+      <c r="A1362" s="23" t="n">
         <v>323487</v>
       </c>
-      <c r="B1362" s="25" t="inlineStr">
+      <c r="B1362" s="23" t="inlineStr">
         <is>
           <t>#03 AÇOUGUE - #05 FRUTOS DO MAR</t>
         </is>
       </c>
-      <c r="C1362" s="25" t="inlineStr">
+      <c r="C1362" s="23" t="inlineStr">
         <is>
           <t>CAMARAO VAN S/C COZ IQF-M 45/80 40X300G</t>
         </is>
       </c>
-      <c r="D1362" s="25" t="inlineStr">
+      <c r="D1362" s="23" t="inlineStr">
         <is>
           <t>CAMARAO COSTA SUL 300G VAN SEM CABEÇA COZIDO</t>
         </is>
       </c>
-      <c r="E1362" s="25" t="inlineStr"/>
+      <c r="E1362" s="23" t="inlineStr"/>
     </row>
     <row r="1363">
       <c r="A1363" t="n">
@@ -28127,25 +28124,25 @@
       </c>
     </row>
     <row r="1369">
-      <c r="A1369" s="35" t="n">
+      <c r="A1369" s="26" t="n">
         <v>272009</v>
       </c>
-      <c r="B1369" s="35" t="inlineStr">
+      <c r="B1369" s="26" t="inlineStr">
         <is>
           <t>#03 AÇOUGUE - #06 EMBUTIDOS E FRIOS</t>
         </is>
       </c>
-      <c r="C1369" s="35" t="inlineStr">
+      <c r="C1369" s="26" t="inlineStr">
         <is>
           <t>APRESUNTADO PERDIGAO 200GR FATIADO</t>
         </is>
       </c>
-      <c r="D1369" s="35" t="inlineStr">
+      <c r="D1369" s="26" t="inlineStr">
         <is>
           <t>APRESUNTADO PERDIGÃO 200G FATIADO</t>
         </is>
       </c>
-      <c r="E1369" s="35" t="inlineStr"/>
+      <c r="E1369" s="26" t="inlineStr"/>
     </row>
     <row r="1370">
       <c r="A1370" t="n">
@@ -28168,25 +28165,25 @@
       </c>
     </row>
     <row r="1371">
-      <c r="A1371" s="25" t="n">
+      <c r="A1371" s="23" t="n">
         <v>231513</v>
       </c>
-      <c r="B1371" s="25" t="inlineStr">
+      <c r="B1371" s="23" t="inlineStr">
         <is>
           <t>#03 AÇOUGUE - #06 EMBUTIDOS E FRIOS</t>
         </is>
       </c>
-      <c r="C1371" s="25" t="inlineStr">
+      <c r="C1371" s="23" t="inlineStr">
         <is>
           <t>BACON DEFUMADO FATIADO 250 G</t>
         </is>
       </c>
-      <c r="D1371" s="25" t="inlineStr">
+      <c r="D1371" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">BACON PERDIGÃO 250G DEFUMADO FATIADO </t>
         </is>
       </c>
-      <c r="E1371" s="25" t="inlineStr"/>
+      <c r="E1371" s="23" t="inlineStr"/>
     </row>
     <row r="1372">
       <c r="A1372" t="n">
@@ -28669,25 +28666,25 @@
       </c>
     </row>
     <row r="1396">
-      <c r="A1396" s="35" t="n">
+      <c r="A1396" s="26" t="n">
         <v>305039</v>
       </c>
-      <c r="B1396" s="35" t="inlineStr">
+      <c r="B1396" s="26" t="inlineStr">
         <is>
           <t>#03 AÇOUGUE - #06 EMBUTIDOS E FRIOS</t>
         </is>
       </c>
-      <c r="C1396" s="35" t="inlineStr">
+      <c r="C1396" s="26" t="inlineStr">
         <is>
           <t>LINGUIÇA BOVINA KG CASEIRA</t>
         </is>
       </c>
-      <c r="D1396" s="35" t="inlineStr">
+      <c r="D1396" s="26" t="inlineStr">
         <is>
           <t>LINGUIÇA CASEIRA BOVINA KG</t>
         </is>
       </c>
-      <c r="E1396" s="35" t="inlineStr"/>
+      <c r="E1396" s="26" t="inlineStr"/>
     </row>
     <row r="1397">
       <c r="A1397" t="n">
@@ -28770,67 +28767,67 @@
       </c>
     </row>
     <row r="1401">
-      <c r="A1401" s="25" t="n">
+      <c r="A1401" s="23" t="n">
         <v>227259</v>
       </c>
-      <c r="B1401" s="25" t="inlineStr">
+      <c r="B1401" s="23" t="inlineStr">
         <is>
           <t>#03 AÇOUGUE - #06 EMBUTIDOS E FRIOS</t>
         </is>
       </c>
-      <c r="C1401" s="25" t="inlineStr">
+      <c r="C1401" s="23" t="inlineStr">
         <is>
           <t>LINGUICA FININHA DEFUMADA SEARA 215G</t>
         </is>
       </c>
-      <c r="D1401" s="25" t="inlineStr">
+      <c r="D1401" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">LINGUIÇA DEFUMADA SEARA 215G FININHA </t>
         </is>
       </c>
-      <c r="E1401" s="25" t="inlineStr"/>
+      <c r="E1401" s="23" t="inlineStr"/>
     </row>
     <row r="1402">
-      <c r="A1402" s="35" t="n">
+      <c r="A1402" s="26" t="n">
         <v>228422</v>
       </c>
-      <c r="B1402" s="35" t="inlineStr">
+      <c r="B1402" s="26" t="inlineStr">
         <is>
           <t>#03 AÇOUGUE - #06 EMBUTIDOS E FRIOS</t>
         </is>
       </c>
-      <c r="C1402" s="35" t="inlineStr">
+      <c r="C1402" s="26" t="inlineStr">
         <is>
           <t>LING SUPER FRANGO KG GROSSA</t>
         </is>
       </c>
-      <c r="D1402" s="35" t="inlineStr">
+      <c r="D1402" s="26" t="inlineStr">
         <is>
           <t>LINGUIÇA GROSSA SUPER FRANGO KG</t>
         </is>
       </c>
-      <c r="E1402" s="35" t="inlineStr"/>
+      <c r="E1402" s="26" t="inlineStr"/>
     </row>
     <row r="1403">
-      <c r="A1403" s="35" t="n">
+      <c r="A1403" s="26" t="n">
         <v>289127</v>
       </c>
-      <c r="B1403" s="35" t="inlineStr">
+      <c r="B1403" s="26" t="inlineStr">
         <is>
           <t>#03 AÇOUGUE - #06 EMBUTIDOS E FRIOS</t>
         </is>
       </c>
-      <c r="C1403" s="35" t="inlineStr">
+      <c r="C1403" s="26" t="inlineStr">
         <is>
           <t>LINGUIÇA MISTA SADIA 215GR FININHA DEFUM</t>
         </is>
       </c>
-      <c r="D1403" s="35" t="inlineStr">
+      <c r="D1403" s="26" t="inlineStr">
         <is>
           <t>LINGUIÇA MISTA FININHA DEFUMADA SADIA 215G</t>
         </is>
       </c>
-      <c r="E1403" s="35" t="inlineStr"/>
+      <c r="E1403" s="26" t="inlineStr"/>
     </row>
     <row r="1404">
       <c r="A1404" s="20" t="n">
@@ -29054,25 +29051,25 @@
       </c>
     </row>
     <row r="1415">
-      <c r="A1415" s="25" t="n">
+      <c r="A1415" s="23" t="n">
         <v>301962</v>
       </c>
-      <c r="B1415" s="25" t="inlineStr">
+      <c r="B1415" s="23" t="inlineStr">
         <is>
           <t>#03 AÇOUGUE - #06 EMBUTIDOS E FRIOS</t>
         </is>
       </c>
-      <c r="C1415" s="25" t="inlineStr">
+      <c r="C1415" s="23" t="inlineStr">
         <is>
           <t>LINGUICA BONFRIGO SUINA KG</t>
         </is>
       </c>
-      <c r="D1415" s="25" t="inlineStr">
+      <c r="D1415" s="23" t="inlineStr">
         <is>
           <t>LINGUIÇA SUÍNA BONFRIGO KG</t>
         </is>
       </c>
-      <c r="E1415" s="25" t="inlineStr"/>
+      <c r="E1415" s="23" t="inlineStr"/>
     </row>
     <row r="1416">
       <c r="A1416" t="n">
@@ -29175,25 +29172,25 @@
       </c>
     </row>
     <row r="1421">
-      <c r="A1421" s="35" t="n">
+      <c r="A1421" s="26" t="n">
         <v>292399</v>
       </c>
-      <c r="B1421" s="35" t="inlineStr">
+      <c r="B1421" s="26" t="inlineStr">
         <is>
           <t>#03 AÇOUGUE - #06 EMBUTIDOS E FRIOS</t>
         </is>
       </c>
-      <c r="C1421" s="35" t="inlineStr">
+      <c r="C1421" s="26" t="inlineStr">
         <is>
           <t>LINGUICA SUPER FRANGO 400GR DEFUMADA FRA</t>
         </is>
       </c>
-      <c r="D1421" s="35" t="inlineStr">
+      <c r="D1421" s="26" t="inlineStr">
         <is>
           <t>LINGUIÇA SUPER FRANGO 400G DEFUMADA</t>
         </is>
       </c>
-      <c r="E1421" s="35" t="inlineStr"/>
+      <c r="E1421" s="26" t="inlineStr"/>
     </row>
     <row r="1422">
       <c r="A1422" t="n">
@@ -29777,25 +29774,25 @@
       </c>
     </row>
     <row r="1451">
-      <c r="A1451" s="35" t="n">
+      <c r="A1451" s="26" t="n">
         <v>105770</v>
       </c>
-      <c r="B1451" s="35" t="inlineStr">
+      <c r="B1451" s="26" t="inlineStr">
         <is>
           <t>#03 AÇOUGUE - #06 EMBUTIDOS E FRIOS</t>
         </is>
       </c>
-      <c r="C1451" s="35" t="inlineStr">
+      <c r="C1451" s="26" t="inlineStr">
         <is>
           <t>MORT PERDIGAO KG FRANGO</t>
         </is>
       </c>
-      <c r="D1451" s="35" t="inlineStr">
+      <c r="D1451" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">MORTADELA DE FRANGO PERDIGÃO KG FRANGO </t>
         </is>
       </c>
-      <c r="E1451" s="35" t="inlineStr"/>
+      <c r="E1451" s="26" t="inlineStr"/>
     </row>
     <row r="1452">
       <c r="A1452" s="10" t="n">
@@ -29878,25 +29875,25 @@
       </c>
     </row>
     <row r="1456">
-      <c r="A1456" s="35" t="n">
+      <c r="A1456" s="26" t="n">
         <v>108558</v>
       </c>
-      <c r="B1456" s="35" t="inlineStr">
+      <c r="B1456" s="26" t="inlineStr">
         <is>
           <t>#03 AÇOUGUE - #06 EMBUTIDOS E FRIOS</t>
         </is>
       </c>
-      <c r="C1456" s="35" t="inlineStr">
+      <c r="C1456" s="26" t="inlineStr">
         <is>
           <t>MORTADELA SADIA  1KG SUINA</t>
         </is>
       </c>
-      <c r="D1456" s="35" t="inlineStr">
+      <c r="D1456" s="26" t="inlineStr">
         <is>
           <t>MORTADELA SUÍNA SADIA 1KG</t>
         </is>
       </c>
-      <c r="E1456" s="35" t="inlineStr"/>
+      <c r="E1456" s="26" t="inlineStr"/>
     </row>
     <row r="1457">
       <c r="A1457" t="n">
@@ -29939,25 +29936,25 @@
       </c>
     </row>
     <row r="1459">
-      <c r="A1459" s="25" t="n">
+      <c r="A1459" s="23" t="n">
         <v>175253</v>
       </c>
-      <c r="B1459" s="25" t="inlineStr">
+      <c r="B1459" s="23" t="inlineStr">
         <is>
           <t>#03 AÇOUGUE - #06 EMBUTIDOS E FRIOS</t>
         </is>
       </c>
-      <c r="C1459" s="25" t="inlineStr">
+      <c r="C1459" s="23" t="inlineStr">
         <is>
           <t>PRESUNTO PARMA FATIADO SADIA ATM 100GR</t>
         </is>
       </c>
-      <c r="D1459" s="25" t="inlineStr">
+      <c r="D1459" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">PRESUNTO PARMA SADIA 100G FATIADO </t>
         </is>
       </c>
-      <c r="E1459" s="25" t="inlineStr"/>
+      <c r="E1459" s="23" t="inlineStr"/>
     </row>
     <row r="1460">
       <c r="A1460" t="n">
@@ -30080,25 +30077,25 @@
       </c>
     </row>
     <row r="1466">
-      <c r="A1466" s="35" t="n">
+      <c r="A1466" s="26" t="n">
         <v>184045</v>
       </c>
-      <c r="B1466" s="35" t="inlineStr">
+      <c r="B1466" s="26" t="inlineStr">
         <is>
           <t>#03 AÇOUGUE - #06 EMBUTIDOS E FRIOS</t>
         </is>
       </c>
-      <c r="C1466" s="35" t="inlineStr">
+      <c r="C1466" s="26" t="inlineStr">
         <is>
           <t>SALAME PERDIGAO FATIADO 100GR SALF10</t>
         </is>
       </c>
-      <c r="D1466" s="35" t="inlineStr">
+      <c r="D1466" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">SALAME PERDIGÃO 100GR FATIADO </t>
         </is>
       </c>
-      <c r="E1466" s="35" t="inlineStr"/>
+      <c r="E1466" s="26" t="inlineStr"/>
     </row>
     <row r="1467">
       <c r="A1467" t="n">
@@ -30201,25 +30198,25 @@
       </c>
     </row>
     <row r="1472">
-      <c r="A1472" s="35" t="n">
+      <c r="A1472" s="26" t="n">
         <v>227341</v>
       </c>
-      <c r="B1472" s="35" t="inlineStr">
+      <c r="B1472" s="26" t="inlineStr">
         <is>
           <t>#03 AÇOUGUE - #06 EMBUTIDOS E FRIOS</t>
         </is>
       </c>
-      <c r="C1472" s="35" t="inlineStr">
+      <c r="C1472" s="26" t="inlineStr">
         <is>
           <t>SALSICHA HOT DOG AMERICANO KG</t>
         </is>
       </c>
-      <c r="D1472" s="35" t="inlineStr">
+      <c r="D1472" s="26" t="inlineStr">
         <is>
           <t>SALSICHA AMERICANO KG PARA HOT DOG</t>
         </is>
       </c>
-      <c r="E1472" s="35" t="inlineStr"/>
+      <c r="E1472" s="26" t="inlineStr"/>
     </row>
     <row r="1473">
       <c r="A1473" t="n">
@@ -30522,25 +30519,25 @@
       </c>
     </row>
     <row r="1488">
-      <c r="A1488" s="35" t="n">
+      <c r="A1488" s="26" t="n">
         <v>170464</v>
       </c>
-      <c r="B1488" s="35" t="inlineStr">
+      <c r="B1488" s="26" t="inlineStr">
         <is>
           <t>#03 AÇOUGUE - #07 EMPANADOS E PRATOS PRONTOS</t>
         </is>
       </c>
-      <c r="C1488" s="35" t="inlineStr">
+      <c r="C1488" s="26" t="inlineStr">
         <is>
           <t>STEAK FRANGO EMPANADO SADIA 100G STCE</t>
         </is>
       </c>
-      <c r="D1488" s="35" t="inlineStr">
+      <c r="D1488" s="26" t="inlineStr">
         <is>
           <t>STEAK EMPANADO SADIA 100G FRANGO</t>
         </is>
       </c>
-      <c r="E1488" s="35" t="inlineStr"/>
+      <c r="E1488" s="26" t="inlineStr"/>
     </row>
     <row r="1489">
       <c r="A1489" s="20" t="n">
@@ -30564,25 +30561,25 @@
       <c r="E1489" s="20" t="inlineStr"/>
     </row>
     <row r="1490">
-      <c r="A1490" s="35" t="n">
+      <c r="A1490" s="26" t="n">
         <v>127328</v>
       </c>
-      <c r="B1490" s="35" t="inlineStr">
+      <c r="B1490" s="26" t="inlineStr">
         <is>
           <t>#03 AÇOUGUE - #07 EMPANADOS E PRATOS PRONTOS</t>
         </is>
       </c>
-      <c r="C1490" s="35" t="inlineStr">
+      <c r="C1490" s="26" t="inlineStr">
         <is>
           <t>TEKITOS SEARA QUEIJO OREGANO 300GR</t>
         </is>
       </c>
-      <c r="D1490" s="35" t="inlineStr">
+      <c r="D1490" s="26" t="inlineStr">
         <is>
           <t>TEKITOS SEARA 300G QUEIJO COM OREGANO</t>
         </is>
       </c>
-      <c r="E1490" s="35" t="inlineStr"/>
+      <c r="E1490" s="26" t="inlineStr"/>
     </row>
     <row r="1491">
       <c r="A1491" t="n">
@@ -32051,151 +32048,151 @@
       </c>
     </row>
     <row r="1563">
-      <c r="A1563" s="23" t="n">
+      <c r="A1563" s="26" t="n">
         <v>247972</v>
       </c>
-      <c r="B1563" s="23" t="inlineStr">
+      <c r="B1563" s="26" t="inlineStr">
         <is>
           <t>#05 BEBIDA - #00 BEBIDAS GASEIFICADAS</t>
         </is>
       </c>
-      <c r="C1563" s="23" t="inlineStr">
+      <c r="C1563" s="26" t="inlineStr">
         <is>
           <t>BEBIDA ICE 51 275ML BALADA</t>
         </is>
       </c>
-      <c r="D1563" s="23" t="inlineStr">
+      <c r="D1563" s="26" t="inlineStr">
         <is>
           <t>BEBIDA ICE 51 275ML BALADA</t>
         </is>
       </c>
-      <c r="E1563" s="23" t="inlineStr"/>
+      <c r="E1563" s="26" t="inlineStr"/>
     </row>
     <row r="1564">
-      <c r="A1564" s="23" t="n">
+      <c r="A1564" s="26" t="n">
         <v>247970</v>
       </c>
-      <c r="B1564" s="23" t="inlineStr">
+      <c r="B1564" s="26" t="inlineStr">
         <is>
           <t>#05 BEBIDA - #00 BEBIDAS GASEIFICADAS</t>
         </is>
       </c>
-      <c r="C1564" s="23" t="inlineStr">
+      <c r="C1564" s="26" t="inlineStr">
         <is>
           <t>BEBIDA ICE 51 275ML BALADA</t>
         </is>
       </c>
-      <c r="D1564" s="23" t="inlineStr">
+      <c r="D1564" s="26" t="inlineStr">
         <is>
           <t>BEBIDA ICE 51 275ML BALADA</t>
         </is>
       </c>
-      <c r="E1564" s="23" t="inlineStr"/>
+      <c r="E1564" s="26" t="inlineStr"/>
     </row>
     <row r="1565">
-      <c r="A1565" s="23" t="n">
+      <c r="A1565" s="26" t="n">
         <v>247993</v>
       </c>
-      <c r="B1565" s="23" t="inlineStr">
+      <c r="B1565" s="26" t="inlineStr">
         <is>
           <t>#05 BEBIDA - #00 BEBIDAS GASEIFICADAS</t>
         </is>
       </c>
-      <c r="C1565" s="23" t="inlineStr">
+      <c r="C1565" s="26" t="inlineStr">
         <is>
           <t>BEB ICE 51 275ML KIWI</t>
         </is>
       </c>
-      <c r="D1565" s="23" t="inlineStr">
+      <c r="D1565" s="26" t="inlineStr">
         <is>
           <t>BEBIDA ICE 51 275ML KIWI</t>
         </is>
       </c>
-      <c r="E1565" s="23" t="inlineStr"/>
+      <c r="E1565" s="26" t="inlineStr"/>
     </row>
     <row r="1566">
-      <c r="A1566" s="23" t="n">
+      <c r="A1566" s="26" t="n">
         <v>247995</v>
       </c>
-      <c r="B1566" s="23" t="inlineStr">
+      <c r="B1566" s="26" t="inlineStr">
         <is>
           <t>#05 BEBIDA - #00 BEBIDAS GASEIFICADAS</t>
         </is>
       </c>
-      <c r="C1566" s="23" t="inlineStr">
+      <c r="C1566" s="26" t="inlineStr">
         <is>
           <t>BEB ICE 51 275ML LIMAO</t>
         </is>
       </c>
-      <c r="D1566" s="23" t="inlineStr">
+      <c r="D1566" s="26" t="inlineStr">
         <is>
           <t>BEBIDA ICE 51 275ML LIMÃO</t>
         </is>
       </c>
-      <c r="E1566" s="23" t="inlineStr"/>
+      <c r="E1566" s="26" t="inlineStr"/>
     </row>
     <row r="1567">
-      <c r="A1567" s="23" t="n">
+      <c r="A1567" s="26" t="n">
         <v>286357</v>
       </c>
-      <c r="B1567" s="23" t="inlineStr">
+      <c r="B1567" s="26" t="inlineStr">
         <is>
           <t>#05 BEBIDA - #00 BEBIDAS GASEIFICADAS</t>
         </is>
       </c>
-      <c r="C1567" s="23" t="inlineStr">
+      <c r="C1567" s="26" t="inlineStr">
         <is>
           <t>BEBIDA CABARE ICE 275ML MACA VERDE</t>
         </is>
       </c>
-      <c r="D1567" s="23" t="inlineStr">
+      <c r="D1567" s="26" t="inlineStr">
         <is>
           <t>BEBIDA ICE 51 275ML MAÇÃ VERDE</t>
         </is>
       </c>
-      <c r="E1567" s="23" t="inlineStr"/>
+      <c r="E1567" s="26" t="inlineStr"/>
     </row>
     <row r="1568">
-      <c r="A1568" s="23" t="n">
+      <c r="A1568" s="26" t="n">
         <v>248003</v>
       </c>
-      <c r="B1568" s="23" t="inlineStr">
+      <c r="B1568" s="26" t="inlineStr">
         <is>
           <t>#05 BEBIDA - #00 BEBIDAS GASEIFICADAS</t>
         </is>
       </c>
-      <c r="C1568" s="23" t="inlineStr">
+      <c r="C1568" s="26" t="inlineStr">
         <is>
           <t>BEB ICE 51 275ML MARACUJA</t>
         </is>
       </c>
-      <c r="D1568" s="23" t="inlineStr">
+      <c r="D1568" s="26" t="inlineStr">
         <is>
           <t>BEBIDA ICE 51 275ML MARACUJA</t>
         </is>
       </c>
-      <c r="E1568" s="23" t="inlineStr"/>
+      <c r="E1568" s="26" t="inlineStr"/>
     </row>
     <row r="1569">
-      <c r="A1569" s="23" t="n">
+      <c r="A1569" s="26" t="n">
         <v>247998</v>
       </c>
-      <c r="B1569" s="23" t="inlineStr">
+      <c r="B1569" s="26" t="inlineStr">
         <is>
           <t>#05 BEBIDA - #00 BEBIDAS GASEIFICADAS</t>
         </is>
       </c>
-      <c r="C1569" s="23" t="inlineStr">
+      <c r="C1569" s="26" t="inlineStr">
         <is>
           <t>BEB ICE 51 275ML MORANGO LARANJA</t>
         </is>
       </c>
-      <c r="D1569" s="23" t="inlineStr">
+      <c r="D1569" s="26" t="inlineStr">
         <is>
           <t>BEBIDA ICE 51 275ML MORANGO COM LARANJA</t>
         </is>
       </c>
-      <c r="E1569" s="23" t="inlineStr"/>
+      <c r="E1569" s="26" t="inlineStr"/>
     </row>
     <row r="1570">
       <c r="A1570" t="n">
@@ -32238,109 +32235,109 @@
       </c>
     </row>
     <row r="1572">
-      <c r="A1572" s="23" t="n">
+      <c r="A1572" s="26" t="n">
         <v>247992</v>
       </c>
-      <c r="B1572" s="23" t="inlineStr">
+      <c r="B1572" s="26" t="inlineStr">
         <is>
           <t>#05 BEBIDA - #00 BEBIDAS GASEIFICADAS</t>
         </is>
       </c>
-      <c r="C1572" s="23" t="inlineStr">
+      <c r="C1572" s="26" t="inlineStr">
         <is>
           <t>BEB ICE 51 275ML KIWI</t>
         </is>
       </c>
-      <c r="D1572" s="23" t="inlineStr">
+      <c r="D1572" s="26" t="inlineStr">
         <is>
           <t>BEBIDA ICE 51 275ML KIWI</t>
         </is>
       </c>
-      <c r="E1572" s="23" t="inlineStr"/>
+      <c r="E1572" s="26" t="inlineStr"/>
     </row>
     <row r="1573">
-      <c r="A1573" s="23" t="n">
+      <c r="A1573" s="26" t="n">
         <v>247994</v>
       </c>
-      <c r="B1573" s="23" t="inlineStr">
+      <c r="B1573" s="26" t="inlineStr">
         <is>
           <t>#05 BEBIDA - #00 BEBIDAS GASEIFICADAS</t>
         </is>
       </c>
-      <c r="C1573" s="23" t="inlineStr">
+      <c r="C1573" s="26" t="inlineStr">
         <is>
           <t>BEB ICE 51 275ML LIMAO</t>
         </is>
       </c>
-      <c r="D1573" s="23" t="inlineStr">
+      <c r="D1573" s="26" t="inlineStr">
         <is>
           <t>BEBIDA ICE 51 275ML LIMÃO</t>
         </is>
       </c>
-      <c r="E1573" s="23" t="inlineStr"/>
+      <c r="E1573" s="26" t="inlineStr"/>
     </row>
     <row r="1574">
-      <c r="A1574" s="23" t="n">
+      <c r="A1574" s="26" t="n">
         <v>248002</v>
       </c>
-      <c r="B1574" s="23" t="inlineStr">
+      <c r="B1574" s="26" t="inlineStr">
         <is>
           <t>#05 BEBIDA - #00 BEBIDAS GASEIFICADAS</t>
         </is>
       </c>
-      <c r="C1574" s="23" t="inlineStr">
+      <c r="C1574" s="26" t="inlineStr">
         <is>
           <t>BEB ICE 51 275ML MARACUJA</t>
         </is>
       </c>
-      <c r="D1574" s="23" t="inlineStr">
+      <c r="D1574" s="26" t="inlineStr">
         <is>
           <t>BEBIDA ICE 51 275ML MARACUJA</t>
         </is>
       </c>
-      <c r="E1574" s="23" t="inlineStr"/>
+      <c r="E1574" s="26" t="inlineStr"/>
     </row>
     <row r="1575">
-      <c r="A1575" s="23" t="n">
+      <c r="A1575" s="26" t="n">
         <v>247996</v>
       </c>
-      <c r="B1575" s="23" t="inlineStr">
+      <c r="B1575" s="26" t="inlineStr">
         <is>
           <t>#05 BEBIDA - #00 BEBIDAS GASEIFICADAS</t>
         </is>
       </c>
-      <c r="C1575" s="23" t="inlineStr">
+      <c r="C1575" s="26" t="inlineStr">
         <is>
           <t>BEB ICE 51 275ML MORANGO LARANJA</t>
         </is>
       </c>
-      <c r="D1575" s="23" t="inlineStr">
+      <c r="D1575" s="26" t="inlineStr">
         <is>
           <t>BEBIDA ICE 51 275ML MORANGO COM LARANJA</t>
         </is>
       </c>
-      <c r="E1575" s="23" t="inlineStr"/>
+      <c r="E1575" s="26" t="inlineStr"/>
     </row>
     <row r="1576">
-      <c r="A1576" s="23" t="n">
+      <c r="A1576" s="26" t="n">
         <v>248000</v>
       </c>
-      <c r="B1576" s="23" t="inlineStr">
+      <c r="B1576" s="26" t="inlineStr">
         <is>
           <t>#05 BEBIDA - #00 BEBIDAS GASEIFICADAS</t>
         </is>
       </c>
-      <c r="C1576" s="23" t="inlineStr">
+      <c r="C1576" s="26" t="inlineStr">
         <is>
           <t>BEB ICE 51 275ML TANGERINA UN</t>
         </is>
       </c>
-      <c r="D1576" s="23" t="inlineStr">
+      <c r="D1576" s="26" t="inlineStr">
         <is>
           <t>BEBIDA ICE 51 275ML TANGERINA</t>
         </is>
       </c>
-      <c r="E1576" s="23" t="inlineStr"/>
+      <c r="E1576" s="26" t="inlineStr"/>
     </row>
     <row r="1577">
       <c r="A1577" t="n">
@@ -32523,25 +32520,25 @@
       </c>
     </row>
     <row r="1586">
-      <c r="A1586" s="23" t="n">
+      <c r="A1586" s="26" t="n">
         <v>161871</v>
       </c>
-      <c r="B1586" s="23" t="inlineStr">
+      <c r="B1586" s="26" t="inlineStr">
         <is>
           <t>#05 BEBIDA - #00 BEBIDAS GASEIFICADAS</t>
         </is>
       </c>
-      <c r="C1586" s="23" t="inlineStr">
+      <c r="C1586" s="26" t="inlineStr">
         <is>
           <t>REFRIG GUARANA TUCHAUA 2LT</t>
         </is>
       </c>
-      <c r="D1586" s="23" t="inlineStr">
+      <c r="D1586" s="26" t="inlineStr">
         <is>
           <t>REFRIGANTE TUCHAUA 2L GUARANA</t>
         </is>
       </c>
-      <c r="E1586" s="23" t="inlineStr"/>
+      <c r="E1586" s="26" t="inlineStr"/>
     </row>
     <row r="1587">
       <c r="A1587" t="n">
@@ -32604,46 +32601,46 @@
       </c>
     </row>
     <row r="1590">
-      <c r="A1590" s="23" t="n">
+      <c r="A1590" s="26" t="n">
         <v>288761</v>
       </c>
-      <c r="B1590" s="23" t="inlineStr">
+      <c r="B1590" s="26" t="inlineStr">
         <is>
           <t>#05 BEBIDA - #00 BEBIDAS GASEIFICADAS</t>
         </is>
       </c>
-      <c r="C1590" s="23" t="inlineStr">
+      <c r="C1590" s="26" t="inlineStr">
         <is>
           <t>REFRIGERANTE COCA COLA 1L SEM ACUCAR PET</t>
         </is>
       </c>
-      <c r="D1590" s="23" t="inlineStr">
+      <c r="D1590" s="26" t="inlineStr">
         <is>
           <t>REFRIGERANTE COCA COLA 1L  SEM AÇUCAR</t>
         </is>
       </c>
-      <c r="E1590" s="23" t="inlineStr"/>
+      <c r="E1590" s="26" t="inlineStr"/>
     </row>
     <row r="1591">
-      <c r="A1591" s="25" t="n">
+      <c r="A1591" s="26" t="n">
         <v>104406</v>
       </c>
-      <c r="B1591" s="25" t="inlineStr">
+      <c r="B1591" s="26" t="inlineStr">
         <is>
           <t>#05 BEBIDA - #00 BEBIDAS GASEIFICADAS</t>
         </is>
       </c>
-      <c r="C1591" s="25" t="inlineStr">
+      <c r="C1591" s="26" t="inlineStr">
         <is>
           <t>REFRIGERANTE COCA COLA 2L ORIGINAL</t>
         </is>
       </c>
-      <c r="D1591" s="25" t="inlineStr">
+      <c r="D1591" s="26" t="inlineStr">
         <is>
           <t>REFRIGERANTE COCA COLA 2L</t>
         </is>
       </c>
-      <c r="E1591" s="25" t="inlineStr"/>
+      <c r="E1591" s="26" t="inlineStr"/>
     </row>
     <row r="1592">
       <c r="A1592" t="n">
@@ -32746,25 +32743,25 @@
       </c>
     </row>
     <row r="1597">
-      <c r="A1597" s="23" t="n">
+      <c r="A1597" s="26" t="n">
         <v>104404</v>
       </c>
-      <c r="B1597" s="23" t="inlineStr">
+      <c r="B1597" s="26" t="inlineStr">
         <is>
           <t>#05 BEBIDA - #00 BEBIDAS GASEIFICADAS</t>
         </is>
       </c>
-      <c r="C1597" s="23" t="inlineStr">
+      <c r="C1597" s="26" t="inlineStr">
         <is>
           <t>REFRIG FANTA LARANJA 2L</t>
         </is>
       </c>
-      <c r="D1597" s="23" t="inlineStr">
+      <c r="D1597" s="26" t="inlineStr">
         <is>
           <t>REFRIGERANTE FANTA 2L LARANJA</t>
         </is>
       </c>
-      <c r="E1597" s="23" t="inlineStr"/>
+      <c r="E1597" s="26" t="inlineStr"/>
     </row>
     <row r="1598">
       <c r="A1598" s="9" t="n">
@@ -32807,25 +32804,25 @@
       </c>
     </row>
     <row r="1600">
-      <c r="A1600" s="25" t="n">
+      <c r="A1600" s="23" t="n">
         <v>104410</v>
       </c>
-      <c r="B1600" s="25" t="inlineStr">
+      <c r="B1600" s="23" t="inlineStr">
         <is>
           <t>#05 BEBIDA - #00 BEBIDAS GASEIFICADAS</t>
         </is>
       </c>
-      <c r="C1600" s="25" t="inlineStr">
+      <c r="C1600" s="23" t="inlineStr">
         <is>
           <t>REFRIG GUARANA ANTARCTICA 2L PET ORIG</t>
         </is>
       </c>
-      <c r="D1600" s="25" t="inlineStr">
+      <c r="D1600" s="23" t="inlineStr">
         <is>
           <t>REFRIGERANTE GUARANA ANTARCTICA 2L</t>
         </is>
       </c>
-      <c r="E1600" s="25" t="inlineStr"/>
+      <c r="E1600" s="23" t="inlineStr"/>
     </row>
     <row r="1601">
       <c r="A1601" s="12" t="n">
@@ -32908,25 +32905,25 @@
       </c>
     </row>
     <row r="1605">
-      <c r="A1605" s="23" t="n">
+      <c r="A1605" s="26" t="n">
         <v>325127</v>
       </c>
-      <c r="B1605" s="23" t="inlineStr">
+      <c r="B1605" s="26" t="inlineStr">
         <is>
           <t>#05 BEBIDA - #00 BEBIDAS GASEIFICADAS</t>
         </is>
       </c>
-      <c r="C1605" s="23" t="inlineStr">
+      <c r="C1605" s="26" t="inlineStr">
         <is>
           <t>REFRIGERANTE H2OH LIMONETO 1,5L PET</t>
         </is>
       </c>
-      <c r="D1605" s="23" t="inlineStr">
+      <c r="D1605" s="26" t="inlineStr">
         <is>
           <t>REFRIGERANTE H2OH 1,5L LIMONETO</t>
         </is>
       </c>
-      <c r="E1605" s="23" t="inlineStr"/>
+      <c r="E1605" s="26" t="inlineStr"/>
     </row>
     <row r="1606">
       <c r="A1606" t="n">
@@ -34090,25 +34087,25 @@
       </c>
     </row>
     <row r="1664">
-      <c r="A1664" s="25" t="n">
+      <c r="A1664" s="23" t="n">
         <v>102282</v>
       </c>
-      <c r="B1664" s="25" t="inlineStr">
+      <c r="B1664" s="23" t="inlineStr">
         <is>
           <t>#05 BEBIDA - #00 ENERGÉTICOS</t>
         </is>
       </c>
-      <c r="C1664" s="25" t="inlineStr">
+      <c r="C1664" s="23" t="inlineStr">
         <is>
           <t>ENERG RED BULL 250ML TRAD</t>
         </is>
       </c>
-      <c r="D1664" s="25" t="inlineStr">
+      <c r="D1664" s="23" t="inlineStr">
         <is>
           <t>ENERGETICO RED BULL 250ML TRADICIONAL</t>
         </is>
       </c>
-      <c r="E1664" s="25" t="inlineStr"/>
+      <c r="E1664" s="23" t="inlineStr"/>
     </row>
     <row r="1665">
       <c r="A1665" t="n">
@@ -34331,25 +34328,25 @@
       </c>
     </row>
     <row r="1676">
-      <c r="A1676" s="23" t="n">
+      <c r="A1676" s="26" t="n">
         <v>286325</v>
       </c>
-      <c r="B1676" s="23" t="inlineStr">
+      <c r="B1676" s="26" t="inlineStr">
         <is>
           <t>#05 BEBIDA - #01 SUCOS PRONTOS</t>
         </is>
       </c>
-      <c r="C1676" s="23" t="inlineStr">
+      <c r="C1676" s="26" t="inlineStr">
         <is>
           <t>SUCO DE UVA AURORA 1,5LT TINTO TP</t>
         </is>
       </c>
-      <c r="D1676" s="23" t="inlineStr">
+      <c r="D1676" s="26" t="inlineStr">
         <is>
           <t>SUCO AURORA TP 1,5L UVA TINTO</t>
         </is>
       </c>
-      <c r="E1676" s="23" t="inlineStr"/>
+      <c r="E1676" s="26" t="inlineStr"/>
     </row>
     <row r="1677">
       <c r="A1677" s="10" t="n">
@@ -34412,25 +34409,25 @@
       </c>
     </row>
     <row r="1680">
-      <c r="A1680" s="23" t="n">
+      <c r="A1680" s="26" t="n">
         <v>108631</v>
       </c>
-      <c r="B1680" s="23" t="inlineStr">
+      <c r="B1680" s="26" t="inlineStr">
         <is>
           <t>#05 BEBIDA - #01 SUCOS PRONTOS</t>
         </is>
       </c>
-      <c r="C1680" s="23" t="inlineStr">
+      <c r="C1680" s="26" t="inlineStr">
         <is>
           <t>SUCO DAFRUTA CONCENTRADO PET 500ML  CAJU</t>
         </is>
       </c>
-      <c r="D1680" s="23" t="inlineStr">
+      <c r="D1680" s="26" t="inlineStr">
         <is>
           <t>SUCO CONCENTRADO DAFRUTA 500ML CAJU</t>
         </is>
       </c>
-      <c r="E1680" s="23" t="inlineStr"/>
+      <c r="E1680" s="26" t="inlineStr"/>
     </row>
     <row r="1681">
       <c r="A1681" t="n">
@@ -34653,25 +34650,25 @@
       </c>
     </row>
     <row r="1692">
-      <c r="A1692" s="23" t="n">
+      <c r="A1692" s="26" t="n">
         <v>338379</v>
       </c>
-      <c r="B1692" s="23" t="inlineStr">
+      <c r="B1692" s="26" t="inlineStr">
         <is>
           <t>#05 BEBIDA - #01 SUCOS PRONTOS</t>
         </is>
       </c>
-      <c r="C1692" s="23" t="inlineStr">
+      <c r="C1692" s="26" t="inlineStr">
         <is>
           <t>SUCO NATURAL ONE 1,3L UVA</t>
         </is>
       </c>
-      <c r="D1692" s="23" t="inlineStr">
+      <c r="D1692" s="26" t="inlineStr">
         <is>
           <t>SUCO NATURAL ONE 1,3L UVA</t>
         </is>
       </c>
-      <c r="E1692" s="23" t="inlineStr"/>
+      <c r="E1692" s="26" t="inlineStr"/>
     </row>
     <row r="1693">
       <c r="A1693" t="n">
@@ -34914,25 +34911,25 @@
       </c>
     </row>
     <row r="1705">
-      <c r="A1705" s="25" t="n">
+      <c r="A1705" s="23" t="n">
         <v>102149</v>
       </c>
-      <c r="B1705" s="25" t="inlineStr">
+      <c r="B1705" s="23" t="inlineStr">
         <is>
           <t>#05 BEBIDA - #01 SUCOS PRONTOS</t>
         </is>
       </c>
-      <c r="C1705" s="25" t="inlineStr">
+      <c r="C1705" s="23" t="inlineStr">
         <is>
           <t>SUCO DAFRUTA 1L CAJU</t>
         </is>
       </c>
-      <c r="D1705" s="25" t="inlineStr">
+      <c r="D1705" s="23" t="inlineStr">
         <is>
           <t>SUCO PRONTO DAFRUTA 1L CAJU</t>
         </is>
       </c>
-      <c r="E1705" s="25" t="inlineStr"/>
+      <c r="E1705" s="23" t="inlineStr"/>
     </row>
     <row r="1706">
       <c r="A1706" t="n">
@@ -35636,25 +35633,25 @@
       </c>
     </row>
     <row r="1741">
-      <c r="A1741" s="23" t="n">
+      <c r="A1741" s="26" t="n">
         <v>267604</v>
       </c>
-      <c r="B1741" s="23" t="inlineStr">
+      <c r="B1741" s="26" t="inlineStr">
         <is>
           <t>#05 BEBIDA - CERVEJAS</t>
         </is>
       </c>
-      <c r="C1741" s="23" t="inlineStr">
+      <c r="C1741" s="26" t="inlineStr">
         <is>
           <t>CERVEJA BUDWEISER 330ML ZERO ALCOOL LN U</t>
         </is>
       </c>
-      <c r="D1741" s="23" t="inlineStr">
+      <c r="D1741" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">CERVEJA BUDWEISER ZERO ALCOOL LONG NECK 330ML </t>
         </is>
       </c>
-      <c r="E1741" s="23" t="inlineStr"/>
+      <c r="E1741" s="26" t="inlineStr"/>
     </row>
     <row r="1742">
       <c r="A1742" t="n">
@@ -35817,25 +35814,25 @@
       </c>
     </row>
     <row r="1750">
-      <c r="A1750" s="23" t="n">
+      <c r="A1750" s="26" t="n">
         <v>265726</v>
       </c>
-      <c r="B1750" s="23" t="inlineStr">
+      <c r="B1750" s="26" t="inlineStr">
         <is>
           <t>#05 BEBIDA - CERVEJAS</t>
         </is>
       </c>
-      <c r="C1750" s="23" t="inlineStr">
+      <c r="C1750" s="26" t="inlineStr">
         <is>
           <t>CERVEJA HEINEKEN 269ML LATA UNID</t>
         </is>
       </c>
-      <c r="D1750" s="23" t="inlineStr">
+      <c r="D1750" s="26" t="inlineStr">
         <is>
           <t>CERVEJA HEINEKEN 269ML</t>
         </is>
       </c>
-      <c r="E1750" s="23" t="inlineStr"/>
+      <c r="E1750" s="26" t="inlineStr"/>
     </row>
     <row r="1751">
       <c r="A1751" t="n">
@@ -35878,25 +35875,25 @@
       </c>
     </row>
     <row r="1753">
-      <c r="A1753" s="25" t="n">
+      <c r="A1753" s="23" t="n">
         <v>157496</v>
       </c>
-      <c r="B1753" s="25" t="inlineStr">
+      <c r="B1753" s="23" t="inlineStr">
         <is>
           <t>#05 BEBIDA - CERVEJAS</t>
         </is>
       </c>
-      <c r="C1753" s="25" t="inlineStr">
+      <c r="C1753" s="23" t="inlineStr">
         <is>
           <t>CERVEJA HEINEKEN GARRAFA 600ML</t>
         </is>
       </c>
-      <c r="D1753" s="25" t="inlineStr">
+      <c r="D1753" s="23" t="inlineStr">
         <is>
           <t>CERVEJA HEINEKEN 600ML</t>
         </is>
       </c>
-      <c r="E1753" s="25" t="inlineStr"/>
+      <c r="E1753" s="23" t="inlineStr"/>
     </row>
     <row r="1754">
       <c r="A1754" t="n">
@@ -36059,25 +36056,25 @@
       </c>
     </row>
     <row r="1762">
-      <c r="A1762" s="23" t="n">
+      <c r="A1762" s="26" t="n">
         <v>302401</v>
       </c>
-      <c r="B1762" s="23" t="inlineStr">
+      <c r="B1762" s="26" t="inlineStr">
         <is>
           <t>#05 BEBIDA - CERVEJAS</t>
         </is>
       </c>
-      <c r="C1762" s="23" t="inlineStr">
+      <c r="C1762" s="26" t="inlineStr">
         <is>
           <t>CERVEJA IMPERIO ULTRA 275ML LN</t>
         </is>
       </c>
-      <c r="D1762" s="23" t="inlineStr">
+      <c r="D1762" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">CERVEJA IMPERIO ULTRA LONG NECK 275ML </t>
         </is>
       </c>
-      <c r="E1762" s="23" t="inlineStr"/>
+      <c r="E1762" s="26" t="inlineStr"/>
     </row>
     <row r="1763">
       <c r="A1763" s="12" t="n">
@@ -36180,25 +36177,25 @@
       </c>
     </row>
     <row r="1768">
-      <c r="A1768" s="25" t="n">
+      <c r="A1768" s="23" t="n">
         <v>183095</v>
       </c>
-      <c r="B1768" s="25" t="inlineStr">
+      <c r="B1768" s="23" t="inlineStr">
         <is>
           <t>#05 BEBIDA - CERVEJAS</t>
         </is>
       </c>
-      <c r="C1768" s="25" t="inlineStr">
+      <c r="C1768" s="23" t="inlineStr">
         <is>
           <t>CERVEJA SOL 330ML PREMIUM LN</t>
         </is>
       </c>
-      <c r="D1768" s="25" t="inlineStr">
+      <c r="D1768" s="23" t="inlineStr">
         <is>
           <t>CERVEJA SOL PREMIUM LONG NECK 330ML</t>
         </is>
       </c>
-      <c r="E1768" s="25" t="inlineStr"/>
+      <c r="E1768" s="23" t="inlineStr"/>
     </row>
     <row r="1769">
       <c r="A1769" t="n">
@@ -36321,25 +36318,25 @@
       </c>
     </row>
     <row r="1775">
-      <c r="A1775" s="25" t="n">
+      <c r="A1775" s="23" t="n">
         <v>288739</v>
       </c>
-      <c r="B1775" s="25" t="inlineStr">
+      <c r="B1775" s="23" t="inlineStr">
         <is>
           <t>#05 BEBIDA - CERVEJAS</t>
         </is>
       </c>
-      <c r="C1775" s="25" t="inlineStr">
+      <c r="C1775" s="23" t="inlineStr">
         <is>
           <t>CERV STELLA ARTOIS 330ML PURE GOLD UNID</t>
         </is>
       </c>
-      <c r="D1775" s="25" t="inlineStr">
+      <c r="D1775" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">CERVEJA STELLA ARTOIS PURE GOLD LONG NECK 330ML </t>
         </is>
       </c>
-      <c r="E1775" s="25" t="inlineStr"/>
+      <c r="E1775" s="23" t="inlineStr"/>
     </row>
     <row r="1776">
       <c r="A1776" t="n">
@@ -36442,25 +36439,25 @@
       </c>
     </row>
     <row r="1781">
-      <c r="A1781" s="23" t="n">
+      <c r="A1781" s="30" t="n">
         <v>341231</v>
       </c>
-      <c r="B1781" s="23" t="inlineStr">
+      <c r="B1781" s="30" t="inlineStr">
         <is>
           <t>#05 BEBIDA - CERVEJAS CX</t>
         </is>
       </c>
-      <c r="C1781" s="23" t="inlineStr">
+      <c r="C1781" s="30" t="inlineStr">
         <is>
           <t>CERVEJA ANTARCTICA 269ML MULTIPACK</t>
         </is>
       </c>
-      <c r="D1781" s="23" t="inlineStr">
+      <c r="D1781" s="30" t="inlineStr">
         <is>
           <t>CERVEJA ANTARCTICA 15 X 269ML MULTIPACK</t>
         </is>
       </c>
-      <c r="E1781" s="23" t="inlineStr"/>
+      <c r="E1781" s="30" t="inlineStr"/>
     </row>
     <row r="1782">
       <c r="A1782" t="n">
@@ -36483,25 +36480,25 @@
       </c>
     </row>
     <row r="1783">
-      <c r="A1783" s="25" t="n">
+      <c r="A1783" s="23" t="n">
         <v>258893</v>
       </c>
-      <c r="B1783" s="25" t="inlineStr">
+      <c r="B1783" s="23" t="inlineStr">
         <is>
           <t>#05 BEBIDA - CERVEJAS CX</t>
         </is>
       </c>
-      <c r="C1783" s="25" t="inlineStr">
+      <c r="C1783" s="23" t="inlineStr">
         <is>
           <t>CERV ANTARCTICA ORIGINAL LT 269ML</t>
         </is>
       </c>
-      <c r="D1783" s="25" t="inlineStr">
+      <c r="D1783" s="23" t="inlineStr">
         <is>
           <t>CERVEJA ANTARCTICA ORIGINAL 15 X 269ML</t>
         </is>
       </c>
-      <c r="E1783" s="25" t="inlineStr"/>
+      <c r="E1783" s="23" t="inlineStr"/>
     </row>
     <row r="1784">
       <c r="A1784" t="n">
@@ -36564,25 +36561,25 @@
       </c>
     </row>
     <row r="1787">
-      <c r="A1787" s="25" t="n">
+      <c r="A1787" s="23" t="n">
         <v>168712</v>
       </c>
-      <c r="B1787" s="25" t="inlineStr">
+      <c r="B1787" s="23" t="inlineStr">
         <is>
           <t>#05 BEBIDA - CERVEJAS CX</t>
         </is>
       </c>
-      <c r="C1787" s="25" t="inlineStr">
+      <c r="C1787" s="23" t="inlineStr">
         <is>
           <t>CERVEJA ANTARCTICA 269ML PILSEN</t>
         </is>
       </c>
-      <c r="D1787" s="25" t="inlineStr">
+      <c r="D1787" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">CERVEJA ANTARCTICA PILSEN 15 X 269ML </t>
         </is>
       </c>
-      <c r="E1787" s="25" t="inlineStr"/>
+      <c r="E1787" s="23" t="inlineStr"/>
     </row>
     <row r="1788">
       <c r="A1788" t="n">
@@ -36885,25 +36882,25 @@
       </c>
     </row>
     <row r="1803">
-      <c r="A1803" s="25" t="n">
+      <c r="A1803" s="26" t="n">
         <v>271001</v>
       </c>
-      <c r="B1803" s="25" t="inlineStr">
+      <c r="B1803" s="26" t="inlineStr">
         <is>
           <t>#05 BEBIDA - CERVEJAS CX</t>
         </is>
       </c>
-      <c r="C1803" s="25" t="inlineStr">
+      <c r="C1803" s="26" t="inlineStr">
         <is>
           <t>CERVEJA IMPERIO  PURO MALTE 269ML PACK C</t>
         </is>
       </c>
-      <c r="D1803" s="25" t="inlineStr">
+      <c r="D1803" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">CERVEJA IMPERIO PURO MALTE 15 X 269ML </t>
         </is>
       </c>
-      <c r="E1803" s="25" t="inlineStr"/>
+      <c r="E1803" s="26" t="inlineStr"/>
     </row>
     <row r="1804">
       <c r="A1804" t="n">
@@ -37006,25 +37003,25 @@
       </c>
     </row>
     <row r="1809">
-      <c r="A1809" s="25" t="n">
+      <c r="A1809" s="26" t="n">
         <v>324556</v>
       </c>
-      <c r="B1809" s="25" t="inlineStr">
+      <c r="B1809" s="26" t="inlineStr">
         <is>
           <t>#05 BEBIDA - CERVEJAS CX</t>
         </is>
       </c>
-      <c r="C1809" s="25" t="inlineStr">
+      <c r="C1809" s="26" t="inlineStr">
         <is>
           <t>CERVEJA SKOL PILSEN 269ML ECO</t>
         </is>
       </c>
-      <c r="D1809" s="25" t="inlineStr">
+      <c r="D1809" s="26" t="inlineStr">
         <is>
           <t>CERVEJA SKOL PILSEN 15 X 269ML</t>
         </is>
       </c>
-      <c r="E1809" s="25" t="inlineStr"/>
+      <c r="E1809" s="26" t="inlineStr"/>
     </row>
     <row r="1810">
       <c r="A1810" t="n">
@@ -37067,25 +37064,25 @@
       </c>
     </row>
     <row r="1812">
-      <c r="A1812" s="23" t="n">
+      <c r="A1812" s="26" t="n">
         <v>149113</v>
       </c>
-      <c r="B1812" s="23" t="inlineStr">
+      <c r="B1812" s="26" t="inlineStr">
         <is>
           <t>#05 BEBIDA - DESTILADOS</t>
         </is>
       </c>
-      <c r="C1812" s="23" t="inlineStr">
+      <c r="C1812" s="26" t="inlineStr">
         <is>
           <t>AGUARD 29 GARRAFA  600ML</t>
         </is>
       </c>
-      <c r="D1812" s="23" t="inlineStr">
+      <c r="D1812" s="26" t="inlineStr">
         <is>
           <t>AGUARDENTE 29 600ML</t>
         </is>
       </c>
-      <c r="E1812" s="23" t="inlineStr"/>
+      <c r="E1812" s="26" t="inlineStr"/>
     </row>
     <row r="1813">
       <c r="A1813" t="n">
@@ -37309,25 +37306,25 @@
       </c>
     </row>
     <row r="1824">
-      <c r="A1824" s="25" t="n">
+      <c r="A1824" s="23" t="n">
         <v>236673</v>
       </c>
-      <c r="B1824" s="25" t="inlineStr">
+      <c r="B1824" s="23" t="inlineStr">
         <is>
           <t>#05 BEBIDA - DESTILADOS</t>
         </is>
       </c>
-      <c r="C1824" s="25" t="inlineStr">
+      <c r="C1824" s="23" t="inlineStr">
         <is>
           <t>BEB FIU FIU TANGERINA ACEROLA 750ML</t>
         </is>
       </c>
-      <c r="D1824" s="25" t="inlineStr">
+      <c r="D1824" s="23" t="inlineStr">
         <is>
           <t>BEBIDA ALCOOLICA FIU FIU 750ML TANGERINA ACEROLA</t>
         </is>
       </c>
-      <c r="E1824" s="25" t="inlineStr"/>
+      <c r="E1824" s="23" t="inlineStr"/>
     </row>
     <row r="1825">
       <c r="A1825" t="n">
@@ -37410,25 +37407,25 @@
       </c>
     </row>
     <row r="1829">
-      <c r="A1829" s="25" t="n">
+      <c r="A1829" s="26" t="n">
         <v>102085</v>
       </c>
-      <c r="B1829" s="25" t="inlineStr">
+      <c r="B1829" s="26" t="inlineStr">
         <is>
           <t>#05 BEBIDA - DESTILADOS</t>
         </is>
       </c>
-      <c r="C1829" s="25" t="inlineStr">
+      <c r="C1829" s="26" t="inlineStr">
         <is>
           <t>CACHACA 51 PIRASSUNUNGA 965ML</t>
         </is>
       </c>
-      <c r="D1829" s="25" t="inlineStr">
+      <c r="D1829" s="26" t="inlineStr">
         <is>
           <t>CACHAÇA 51 965ML</t>
         </is>
       </c>
-      <c r="E1829" s="25" t="inlineStr"/>
+      <c r="E1829" s="26" t="inlineStr"/>
     </row>
     <row r="1830">
       <c r="A1830" s="15" t="n">
@@ -37632,25 +37629,25 @@
       </c>
     </row>
     <row r="1840">
-      <c r="A1840" s="23" t="n">
+      <c r="A1840" s="26" t="n">
         <v>145655</v>
       </c>
-      <c r="B1840" s="23" t="inlineStr">
+      <c r="B1840" s="26" t="inlineStr">
         <is>
           <t>#05 BEBIDA - DESTILADOS</t>
         </is>
       </c>
-      <c r="C1840" s="23" t="inlineStr">
+      <c r="C1840" s="26" t="inlineStr">
         <is>
           <t>CACHACA SELETA 1LT</t>
         </is>
       </c>
-      <c r="D1840" s="23" t="inlineStr">
+      <c r="D1840" s="26" t="inlineStr">
         <is>
           <t>CACHAÇA SELETA 1L</t>
         </is>
       </c>
-      <c r="E1840" s="23" t="inlineStr"/>
+      <c r="E1840" s="26" t="inlineStr"/>
     </row>
     <row r="1841">
       <c r="A1841" t="n">
@@ -37813,25 +37810,25 @@
       </c>
     </row>
     <row r="1849">
-      <c r="A1849" s="25" t="n">
+      <c r="A1849" s="23" t="n">
         <v>301843</v>
       </c>
-      <c r="B1849" s="25" t="inlineStr">
+      <c r="B1849" s="23" t="inlineStr">
         <is>
           <t>#05 BEBIDA - DESTILADOS</t>
         </is>
       </c>
-      <c r="C1849" s="25" t="inlineStr">
+      <c r="C1849" s="23" t="inlineStr">
         <is>
           <t>APERITIVO BITER CAMPARI 998ML</t>
         </is>
       </c>
-      <c r="D1849" s="25" t="inlineStr">
+      <c r="D1849" s="23" t="inlineStr">
         <is>
           <t>CAMPARI 998ML</t>
         </is>
       </c>
-      <c r="E1849" s="25" t="inlineStr"/>
+      <c r="E1849" s="23" t="inlineStr"/>
     </row>
     <row r="1850">
       <c r="A1850" t="n">
@@ -37914,25 +37911,25 @@
       </c>
     </row>
     <row r="1854">
-      <c r="A1854" s="23" t="n">
+      <c r="A1854" s="26" t="n">
         <v>102243</v>
       </c>
-      <c r="B1854" s="23" t="inlineStr">
+      <c r="B1854" s="26" t="inlineStr">
         <is>
           <t>#05 BEBIDA - DESTILADOS</t>
         </is>
       </c>
-      <c r="C1854" s="23" t="inlineStr">
+      <c r="C1854" s="26" t="inlineStr">
         <is>
           <t>CONHAQUE SAO JOAO DA BARRA 900ML TRAD</t>
         </is>
       </c>
-      <c r="D1854" s="23" t="inlineStr">
+      <c r="D1854" s="26" t="inlineStr">
         <is>
           <t>CONHAQUE SÃO JOÃO DA BARRA 900ML TRADICIONAL</t>
         </is>
       </c>
-      <c r="E1854" s="23" t="inlineStr"/>
+      <c r="E1854" s="26" t="inlineStr"/>
     </row>
     <row r="1855">
       <c r="A1855" t="n">
@@ -38677,25 +38674,25 @@
       </c>
     </row>
     <row r="1892">
-      <c r="A1892" s="25" t="n">
+      <c r="A1892" s="23" t="n">
         <v>109727</v>
       </c>
-      <c r="B1892" s="25" t="inlineStr">
+      <c r="B1892" s="23" t="inlineStr">
         <is>
           <t>#05 BEBIDA - DESTILADOS</t>
         </is>
       </c>
-      <c r="C1892" s="25" t="inlineStr">
+      <c r="C1892" s="23" t="inlineStr">
         <is>
           <t>WHISKY CHIVAS REGAL 12ANOS 1LT</t>
         </is>
       </c>
-      <c r="D1892" s="25" t="inlineStr">
+      <c r="D1892" s="23" t="inlineStr">
         <is>
           <t>WHISKY CHIVAS REGAL 1L 12 ANOS</t>
         </is>
       </c>
-      <c r="E1892" s="25" t="inlineStr"/>
+      <c r="E1892" s="23" t="inlineStr"/>
     </row>
     <row r="1893">
       <c r="A1893" t="n">
@@ -38919,25 +38916,25 @@
       </c>
     </row>
     <row r="1904">
-      <c r="A1904" s="23" t="n">
+      <c r="A1904" s="26" t="n">
         <v>109729</v>
       </c>
-      <c r="B1904" s="23" t="inlineStr">
+      <c r="B1904" s="26" t="inlineStr">
         <is>
           <t>#05 BEBIDA - DESTILADOS</t>
         </is>
       </c>
-      <c r="C1904" s="23" t="inlineStr">
+      <c r="C1904" s="26" t="inlineStr">
         <is>
           <t>WHISKY WHITE HORSE 1LT</t>
         </is>
       </c>
-      <c r="D1904" s="23" t="inlineStr">
+      <c r="D1904" s="26" t="inlineStr">
         <is>
           <t>WHISKY WHITE HORSE 1L</t>
         </is>
       </c>
-      <c r="E1904" s="23" t="inlineStr"/>
+      <c r="E1904" s="26" t="inlineStr"/>
     </row>
     <row r="1905">
       <c r="A1905" t="n">
@@ -39402,25 +39399,25 @@
       </c>
     </row>
     <row r="1928">
-      <c r="A1928" s="23" t="n">
+      <c r="A1928" s="26" t="n">
         <v>102035</v>
       </c>
-      <c r="B1928" s="23" t="inlineStr">
+      <c r="B1928" s="26" t="inlineStr">
         <is>
           <t>#05 BEBIDA - FERMENTADOS</t>
         </is>
       </c>
-      <c r="C1928" s="23" t="inlineStr">
+      <c r="C1928" s="26" t="inlineStr">
         <is>
           <t>VINHO GALIOTTO 750ML TINTO SUAVE</t>
         </is>
       </c>
-      <c r="D1928" s="23" t="inlineStr">
+      <c r="D1928" s="26" t="inlineStr">
         <is>
           <t>VINHO GALIOTTO 750ML TINTO SUAVE</t>
         </is>
       </c>
-      <c r="E1928" s="23" t="inlineStr"/>
+      <c r="E1928" s="26" t="inlineStr"/>
     </row>
     <row r="1929">
       <c r="A1929" t="n">
@@ -39984,25 +39981,25 @@
       </c>
     </row>
     <row r="1957">
-      <c r="A1957" s="25" t="n">
+      <c r="A1957" s="26" t="n">
         <v>100426</v>
       </c>
-      <c r="B1957" s="25" t="inlineStr">
+      <c r="B1957" s="26" t="inlineStr">
         <is>
           <t>#06 LIMPEZA - ALVEJANTES E ÁGUA SANITÁRIA</t>
         </is>
       </c>
-      <c r="C1957" s="25" t="inlineStr">
+      <c r="C1957" s="26" t="inlineStr">
         <is>
           <t>ÁGUA SANIT QBOA 1L MULTIPLO USO</t>
         </is>
       </c>
-      <c r="D1957" s="25" t="inlineStr">
+      <c r="D1957" s="26" t="inlineStr">
         <is>
           <t>ÁGUA SANITÁRIA QBOA 1L</t>
         </is>
       </c>
-      <c r="E1957" s="25" t="inlineStr"/>
+      <c r="E1957" s="26" t="inlineStr"/>
     </row>
     <row r="1958">
       <c r="A1958" s="14" t="n">
@@ -40107,25 +40104,25 @@
       </c>
     </row>
     <row r="1963">
-      <c r="A1963" s="23" t="n">
+      <c r="A1963" s="26" t="n">
         <v>132145</v>
       </c>
-      <c r="B1963" s="23" t="inlineStr">
+      <c r="B1963" s="26" t="inlineStr">
         <is>
           <t>#06 LIMPEZA - ALVEJANTES E ÁGUA SANITÁRIA</t>
         </is>
       </c>
-      <c r="C1963" s="23" t="inlineStr">
+      <c r="C1963" s="26" t="inlineStr">
         <is>
           <t>AGUA SANITARIA YPE BOMBONA 5 LT</t>
         </is>
       </c>
-      <c r="D1963" s="23" t="inlineStr">
+      <c r="D1963" s="26" t="inlineStr">
         <is>
           <t>ÁGUA SANITARIA YPE BOMBONA 5L</t>
         </is>
       </c>
-      <c r="E1963" s="23" t="inlineStr"/>
+      <c r="E1963" s="26" t="inlineStr"/>
     </row>
     <row r="1964">
       <c r="A1964" t="n">
@@ -40148,25 +40145,25 @@
       </c>
     </row>
     <row r="1965">
-      <c r="A1965" s="23" t="n">
+      <c r="A1965" s="26" t="n">
         <v>336903</v>
       </c>
-      <c r="B1965" s="23" t="inlineStr">
+      <c r="B1965" s="26" t="inlineStr">
         <is>
           <t>#06 LIMPEZA - ALVEJANTES E ÁGUA SANITÁRIA</t>
         </is>
       </c>
-      <c r="C1965" s="23" t="inlineStr">
+      <c r="C1965" s="26" t="inlineStr">
         <is>
           <t>PERCARBONATO DE SODIO TUFF 1KG</t>
         </is>
       </c>
-      <c r="D1965" s="23" t="inlineStr">
+      <c r="D1965" s="26" t="inlineStr">
         <is>
           <t>PERCARBONATO DE SODIO TUFF 1KG</t>
         </is>
       </c>
-      <c r="E1965" s="23" t="inlineStr"/>
+      <c r="E1965" s="26" t="inlineStr"/>
     </row>
     <row r="1966">
       <c r="A1966" t="n">
@@ -40209,25 +40206,25 @@
       </c>
     </row>
     <row r="1968">
-      <c r="A1968" s="23" t="n">
+      <c r="A1968" s="26" t="n">
         <v>133368</v>
       </c>
-      <c r="B1968" s="23" t="inlineStr">
+      <c r="B1968" s="26" t="inlineStr">
         <is>
           <t>#06 LIMPEZA - AMACIANTES</t>
         </is>
       </c>
-      <c r="C1968" s="23" t="inlineStr">
+      <c r="C1968" s="26" t="inlineStr">
         <is>
           <t>AMACIANTE +FAMILIA 5L FLORIST ORIGINAL</t>
         </is>
       </c>
-      <c r="D1968" s="23" t="inlineStr">
+      <c r="D1968" s="26" t="inlineStr">
         <is>
           <t>AMACIANTE DE ROUPAS +FAMILIA 5L ORIGINAL</t>
         </is>
       </c>
-      <c r="E1968" s="23" t="inlineStr"/>
+      <c r="E1968" s="26" t="inlineStr"/>
     </row>
     <row r="1969">
       <c r="A1969" t="n">
@@ -40430,25 +40427,25 @@
       </c>
     </row>
     <row r="1979">
-      <c r="A1979" s="23" t="n">
+      <c r="A1979" s="26" t="n">
         <v>339330</v>
       </c>
-      <c r="B1979" s="23" t="inlineStr">
+      <c r="B1979" s="26" t="inlineStr">
         <is>
           <t>#06 LIMPEZA - AMACIANTES</t>
         </is>
       </c>
-      <c r="C1979" s="23" t="inlineStr">
+      <c r="C1979" s="26" t="inlineStr">
         <is>
           <t>AMAC COMFORT CONC 1,5LT BRIDGERTON</t>
         </is>
       </c>
-      <c r="D1979" s="23" t="inlineStr">
+      <c r="D1979" s="26" t="inlineStr">
         <is>
           <t>AMACIANTE DE ROUPAS CONCENTRADO COMFORT 1,5L BRIDGERTON</t>
         </is>
       </c>
-      <c r="E1979" s="23" t="inlineStr"/>
+      <c r="E1979" s="26" t="inlineStr"/>
     </row>
     <row r="1980">
       <c r="A1980" t="n">
@@ -40651,25 +40648,25 @@
       </c>
     </row>
     <row r="1990">
-      <c r="A1990" s="23" t="n">
+      <c r="A1990" s="26" t="n">
         <v>100568</v>
       </c>
-      <c r="B1990" s="23" t="inlineStr">
+      <c r="B1990" s="26" t="inlineStr">
         <is>
           <t>#06 LIMPEZA - AMACIANTES</t>
         </is>
       </c>
-      <c r="C1990" s="23" t="inlineStr">
+      <c r="C1990" s="26" t="inlineStr">
         <is>
           <t>AMAC CONC DOWNY 500ML FRESCOR PRIMAVERA</t>
         </is>
       </c>
-      <c r="D1990" s="23" t="inlineStr">
+      <c r="D1990" s="26" t="inlineStr">
         <is>
           <t>AMACIANTE DE ROUPAS CONCENTRADO DOWNY 500ML FRESCOR PRIMAVERA</t>
         </is>
       </c>
-      <c r="E1990" s="23" t="inlineStr"/>
+      <c r="E1990" s="26" t="inlineStr"/>
     </row>
     <row r="1991">
       <c r="A1991" t="n">
@@ -41474,25 +41471,25 @@
       <c r="E2030" s="14" t="inlineStr"/>
     </row>
     <row r="2031">
-      <c r="A2031" s="25" t="n">
+      <c r="A2031" s="23" t="n">
         <v>106711</v>
       </c>
-      <c r="B2031" s="25" t="inlineStr">
+      <c r="B2031" s="23" t="inlineStr">
         <is>
           <t>#06 LIMPEZA - AMACIANTES</t>
         </is>
       </c>
-      <c r="C2031" s="25" t="inlineStr">
+      <c r="C2031" s="23" t="inlineStr">
         <is>
           <t>AMAC ROUPAS YPÊ 2LT ACONCHEGO</t>
         </is>
       </c>
-      <c r="D2031" s="25" t="inlineStr">
+      <c r="D2031" s="23" t="inlineStr">
         <is>
           <t>AMACIANTE DE ROUPAS YPÊ 2L ACONCHEGO</t>
         </is>
       </c>
-      <c r="E2031" s="25" t="inlineStr"/>
+      <c r="E2031" s="23" t="inlineStr"/>
     </row>
     <row r="2032">
       <c r="A2032" t="n">
@@ -41515,46 +41512,46 @@
       </c>
     </row>
     <row r="2033">
-      <c r="A2033" s="25" t="n">
+      <c r="A2033" s="23" t="n">
         <v>107394</v>
       </c>
-      <c r="B2033" s="25" t="inlineStr">
+      <c r="B2033" s="23" t="inlineStr">
         <is>
           <t>#06 LIMPEZA - AMACIANTES</t>
         </is>
       </c>
-      <c r="C2033" s="25" t="inlineStr">
+      <c r="C2033" s="23" t="inlineStr">
         <is>
           <t>AMAC ROUPAS YPÊ 2L CARINHO</t>
         </is>
       </c>
-      <c r="D2033" s="25" t="inlineStr">
+      <c r="D2033" s="23" t="inlineStr">
         <is>
           <t>AMACIANTE DE ROUPAS YPÊ 2L CARINHO</t>
         </is>
       </c>
-      <c r="E2033" s="25" t="inlineStr"/>
+      <c r="E2033" s="23" t="inlineStr"/>
     </row>
     <row r="2034">
-      <c r="A2034" s="25" t="n">
+      <c r="A2034" s="23" t="n">
         <v>107413</v>
       </c>
-      <c r="B2034" s="25" t="inlineStr">
+      <c r="B2034" s="23" t="inlineStr">
         <is>
           <t>#06 LIMPEZA - AMACIANTES</t>
         </is>
       </c>
-      <c r="C2034" s="25" t="inlineStr">
+      <c r="C2034" s="23" t="inlineStr">
         <is>
           <t>AMACIANTE YPÊ 2L DELICADO BRANCO</t>
         </is>
       </c>
-      <c r="D2034" s="25" t="inlineStr">
+      <c r="D2034" s="23" t="inlineStr">
         <is>
           <t>AMACIANTE DE ROUPAS YPÊ 2L DELICADO BRANCO</t>
         </is>
       </c>
-      <c r="E2034" s="25" t="inlineStr"/>
+      <c r="E2034" s="23" t="inlineStr"/>
     </row>
     <row r="2035">
       <c r="A2035" t="n">
@@ -41617,25 +41614,25 @@
       </c>
     </row>
     <row r="2038">
-      <c r="A2038" s="25" t="n">
+      <c r="A2038" s="23" t="n">
         <v>106712</v>
       </c>
-      <c r="B2038" s="25" t="inlineStr">
+      <c r="B2038" s="23" t="inlineStr">
         <is>
           <t>#06 LIMPEZA - AMACIANTES</t>
         </is>
       </c>
-      <c r="C2038" s="25" t="inlineStr">
+      <c r="C2038" s="23" t="inlineStr">
         <is>
           <t>AMAC ROUPAS YPÊ 2LT TERNURA</t>
         </is>
       </c>
-      <c r="D2038" s="25" t="inlineStr">
+      <c r="D2038" s="23" t="inlineStr">
         <is>
           <t>AMACIANTE DE ROUPAS YPÊ 2L TERNURA</t>
         </is>
       </c>
-      <c r="E2038" s="25" t="inlineStr"/>
+      <c r="E2038" s="23" t="inlineStr"/>
     </row>
     <row r="2039">
       <c r="A2039" t="n">
@@ -42921,25 +42918,25 @@
       </c>
     </row>
     <row r="2103">
-      <c r="A2103" s="25" t="n">
+      <c r="A2103" s="26" t="n">
         <v>204823</v>
       </c>
-      <c r="B2103" s="25" t="inlineStr">
+      <c r="B2103" s="26" t="inlineStr">
         <is>
           <t>#06 LIMPEZA - DESINFETANTES</t>
         </is>
       </c>
-      <c r="C2103" s="25" t="inlineStr">
+      <c r="C2103" s="26" t="inlineStr">
         <is>
           <t>DESINFETANTE BAK YPÊ 1LT EUCALIPTO</t>
         </is>
       </c>
-      <c r="D2103" s="25" t="inlineStr">
+      <c r="D2103" s="26" t="inlineStr">
         <is>
           <t>DESINFETANTE YPÊ BAK 1L EUCALIPTO</t>
         </is>
       </c>
-      <c r="E2103" s="25" t="inlineStr"/>
+      <c r="E2103" s="26" t="inlineStr"/>
     </row>
     <row r="2104">
       <c r="A2104" t="n">
@@ -43529,109 +43526,109 @@
       </c>
     </row>
     <row r="2133">
-      <c r="A2133" s="25" t="n">
+      <c r="A2133" s="26" t="n">
         <v>100391</v>
       </c>
-      <c r="B2133" s="25" t="inlineStr">
+      <c r="B2133" s="26" t="inlineStr">
         <is>
           <t>#06 LIMPEZA - DETERGENTES</t>
         </is>
       </c>
-      <c r="C2133" s="25" t="inlineStr">
+      <c r="C2133" s="26" t="inlineStr">
         <is>
           <t>DETERGENTE LIQ YPE 500ML CAPIM LIMAO</t>
         </is>
       </c>
-      <c r="D2133" s="25" t="inlineStr">
+      <c r="D2133" s="26" t="inlineStr">
         <is>
           <t>DETERGENTE LIQUIDO YPÊ 500ML CAPIM LIMÃO</t>
         </is>
       </c>
-      <c r="E2133" s="25" t="inlineStr"/>
+      <c r="E2133" s="26" t="inlineStr"/>
     </row>
     <row r="2134">
-      <c r="A2134" s="25" t="n">
+      <c r="A2134" s="26" t="n">
         <v>100394</v>
       </c>
-      <c r="B2134" s="25" t="inlineStr">
+      <c r="B2134" s="26" t="inlineStr">
         <is>
           <t>#06 LIMPEZA - DETERGENTES</t>
         </is>
       </c>
-      <c r="C2134" s="25" t="inlineStr">
+      <c r="C2134" s="26" t="inlineStr">
         <is>
           <t>DETERGENTE LIQ YPE 500ML CLEAR</t>
         </is>
       </c>
-      <c r="D2134" s="25" t="inlineStr">
+      <c r="D2134" s="26" t="inlineStr">
         <is>
           <t>DETERGENTE LIQUIDO YPÊ 500ML CLEAR</t>
         </is>
       </c>
-      <c r="E2134" s="25" t="inlineStr"/>
+      <c r="E2134" s="26" t="inlineStr"/>
     </row>
     <row r="2135">
-      <c r="A2135" s="25" t="n">
+      <c r="A2135" s="26" t="n">
         <v>100392</v>
       </c>
-      <c r="B2135" s="25" t="inlineStr">
+      <c r="B2135" s="26" t="inlineStr">
         <is>
           <t>#06 LIMPEZA - DETERGENTES</t>
         </is>
       </c>
-      <c r="C2135" s="25" t="inlineStr">
+      <c r="C2135" s="26" t="inlineStr">
         <is>
           <t>DETERGENTE LIQ YPE 500ML CLEAR CARE</t>
         </is>
       </c>
-      <c r="D2135" s="25" t="inlineStr">
+      <c r="D2135" s="26" t="inlineStr">
         <is>
           <t>DETERGENTE LIQUIDO YPÊ 500ML CLEAR CARE</t>
         </is>
       </c>
-      <c r="E2135" s="25" t="inlineStr"/>
+      <c r="E2135" s="26" t="inlineStr"/>
     </row>
     <row r="2136">
-      <c r="A2136" s="25" t="n">
+      <c r="A2136" s="26" t="n">
         <v>100402</v>
       </c>
-      <c r="B2136" s="25" t="inlineStr">
+      <c r="B2136" s="26" t="inlineStr">
         <is>
           <t>#06 LIMPEZA - DETERGENTES</t>
         </is>
       </c>
-      <c r="C2136" s="25" t="inlineStr">
+      <c r="C2136" s="26" t="inlineStr">
         <is>
           <t>DETERGENTE LIQ YPE 500ML COCO</t>
         </is>
       </c>
-      <c r="D2136" s="25" t="inlineStr">
+      <c r="D2136" s="26" t="inlineStr">
         <is>
           <t>DETERGENTE LIQUIDO YPÊ 500ML COCO</t>
         </is>
       </c>
-      <c r="E2136" s="25" t="inlineStr"/>
+      <c r="E2136" s="26" t="inlineStr"/>
     </row>
     <row r="2137">
-      <c r="A2137" s="25" t="n">
+      <c r="A2137" s="26" t="n">
         <v>100403</v>
       </c>
-      <c r="B2137" s="25" t="inlineStr">
+      <c r="B2137" s="26" t="inlineStr">
         <is>
           <t>#06 LIMPEZA - DETERGENTES</t>
         </is>
       </c>
-      <c r="C2137" s="25" t="inlineStr">
+      <c r="C2137" s="26" t="inlineStr">
         <is>
           <t>DETERGENTE LIQ YPE 500ML LIMAO</t>
         </is>
       </c>
-      <c r="D2137" s="25" t="inlineStr">
+      <c r="D2137" s="26" t="inlineStr">
         <is>
           <t>DETERGENTE LIQUIDO YPÊ 500ML LIMAO</t>
         </is>
       </c>
-      <c r="E2137" s="25" t="inlineStr"/>
+      <c r="E2137" s="26" t="inlineStr"/>
     </row>
     <row r="2138">
       <c r="A2138" t="n">
@@ -43654,46 +43651,46 @@
       </c>
     </row>
     <row r="2139">
-      <c r="A2139" s="25" t="n">
+      <c r="A2139" s="26" t="n">
         <v>100393</v>
       </c>
-      <c r="B2139" s="25" t="inlineStr">
+      <c r="B2139" s="26" t="inlineStr">
         <is>
           <t>#06 LIMPEZA - DETERGENTES</t>
         </is>
       </c>
-      <c r="C2139" s="25" t="inlineStr">
+      <c r="C2139" s="26" t="inlineStr">
         <is>
           <t>DETERGENTE LIQ YPE 500ML MACA</t>
         </is>
       </c>
-      <c r="D2139" s="25" t="inlineStr">
+      <c r="D2139" s="26" t="inlineStr">
         <is>
           <t>DETERGENTE LIQUIDO YPÊ 500ML MACA</t>
         </is>
       </c>
-      <c r="E2139" s="25" t="inlineStr"/>
+      <c r="E2139" s="26" t="inlineStr"/>
     </row>
     <row r="2140">
-      <c r="A2140" s="25" t="n">
+      <c r="A2140" s="26" t="n">
         <v>100390</v>
       </c>
-      <c r="B2140" s="25" t="inlineStr">
+      <c r="B2140" s="26" t="inlineStr">
         <is>
           <t>#06 LIMPEZA - DETERGENTES</t>
         </is>
       </c>
-      <c r="C2140" s="25" t="inlineStr">
+      <c r="C2140" s="26" t="inlineStr">
         <is>
           <t>DETERGENTE LIQ YPE 500ML NEUTRO</t>
         </is>
       </c>
-      <c r="D2140" s="25" t="inlineStr">
+      <c r="D2140" s="26" t="inlineStr">
         <is>
           <t>DETERGENTE LIQUIDO YPÊ 500ML NEUTRO</t>
         </is>
       </c>
-      <c r="E2140" s="25" t="inlineStr"/>
+      <c r="E2140" s="26" t="inlineStr"/>
     </row>
     <row r="2141">
       <c r="A2141" t="n">
@@ -44278,25 +44275,25 @@
       </c>
     </row>
     <row r="2170">
-      <c r="A2170" s="23" t="n">
+      <c r="A2170" s="26" t="n">
         <v>113220</v>
       </c>
-      <c r="B2170" s="23" t="inlineStr">
+      <c r="B2170" s="26" t="inlineStr">
         <is>
           <t>#06 LIMPEZA - LIMPADORES</t>
         </is>
       </c>
-      <c r="C2170" s="23" t="inlineStr">
+      <c r="C2170" s="26" t="inlineStr">
         <is>
           <t>LIMPADOR START AZULIM M USO ORIGINAL 500</t>
         </is>
       </c>
-      <c r="D2170" s="23" t="inlineStr">
+      <c r="D2170" s="26" t="inlineStr">
         <is>
           <t>LIMPADOR MULTIUSO AZULIN 500ML ORIGINAL</t>
         </is>
       </c>
-      <c r="E2170" s="23" t="inlineStr"/>
+      <c r="E2170" s="26" t="inlineStr"/>
     </row>
     <row r="2171">
       <c r="A2171" t="n">
@@ -45020,25 +45017,25 @@
       </c>
     </row>
     <row r="2207">
-      <c r="A2207" s="23" t="n">
+      <c r="A2207" s="26" t="n">
         <v>318739</v>
       </c>
-      <c r="B2207" s="23" t="inlineStr">
+      <c r="B2207" s="26" t="inlineStr">
         <is>
           <t>#06 LIMPEZA - LIMPADORES</t>
         </is>
       </c>
-      <c r="C2207" s="23" t="inlineStr">
+      <c r="C2207" s="26" t="inlineStr">
         <is>
           <t>LIMPADOR EM PO CIF 2,4KG LIMPEZA PESADA</t>
         </is>
       </c>
-      <c r="D2207" s="23" t="inlineStr">
+      <c r="D2207" s="26" t="inlineStr">
         <is>
           <t>LIMPADOR EM PÓ CIF 2,4KG LIMPEZA PESADA</t>
         </is>
       </c>
-      <c r="E2207" s="23" t="inlineStr"/>
+      <c r="E2207" s="26" t="inlineStr"/>
     </row>
     <row r="2208">
       <c r="A2208" t="n">
@@ -45502,25 +45499,25 @@
       </c>
     </row>
     <row r="2231">
-      <c r="A2231" s="25" t="n">
+      <c r="A2231" s="26" t="n">
         <v>257710</v>
       </c>
-      <c r="B2231" s="25" t="inlineStr">
+      <c r="B2231" s="26" t="inlineStr">
         <is>
           <t>#06 LIMPEZA - SABÃO</t>
         </is>
       </c>
-      <c r="C2231" s="25" t="inlineStr">
+      <c r="C2231" s="26" t="inlineStr">
         <is>
           <t>SABAO BARRA YPE 5X160GR NEUTRO GLICERINA</t>
         </is>
       </c>
-      <c r="D2231" s="25" t="inlineStr">
+      <c r="D2231" s="26" t="inlineStr">
         <is>
           <t>SABÃO EM BARRA YPÊ 900G NEUTRO</t>
         </is>
       </c>
-      <c r="E2231" s="25" t="inlineStr"/>
+      <c r="E2231" s="26" t="inlineStr"/>
     </row>
     <row r="2232">
       <c r="A2232" t="n">
@@ -45583,25 +45580,25 @@
       </c>
     </row>
     <row r="2235">
-      <c r="A2235" s="25" t="n">
+      <c r="A2235" s="23" t="n">
         <v>261980</v>
       </c>
-      <c r="B2235" s="25" t="inlineStr">
+      <c r="B2235" s="23" t="inlineStr">
         <is>
           <t>#06 LIMPEZA - SABÃO</t>
         </is>
       </c>
-      <c r="C2235" s="25" t="inlineStr">
+      <c r="C2235" s="23" t="inlineStr">
         <is>
           <t>SABAO PO BRILHANTE 1,6KG CX LIMPEZA TOTA</t>
         </is>
       </c>
-      <c r="D2235" s="25" t="inlineStr">
+      <c r="D2235" s="23" t="inlineStr">
         <is>
           <t>SABÃO EM PÓ BRILHANTE CAIXA 1,6KG LIMPEZA TOTAL</t>
         </is>
       </c>
-      <c r="E2235" s="25" t="inlineStr"/>
+      <c r="E2235" s="23" t="inlineStr"/>
     </row>
     <row r="2236">
       <c r="A2236" t="n">
@@ -46004,46 +46001,46 @@
       </c>
     </row>
     <row r="2256">
-      <c r="A2256" s="23" t="n">
+      <c r="A2256" s="26" t="n">
         <v>286199</v>
       </c>
-      <c r="B2256" s="23" t="inlineStr">
+      <c r="B2256" s="26" t="inlineStr">
         <is>
           <t>#06 LIMPEZA - SABÃO</t>
         </is>
       </c>
-      <c r="C2256" s="23" t="inlineStr">
+      <c r="C2256" s="26" t="inlineStr">
         <is>
           <t>SABAO PO TIXAN YPE 800GR MACIEZ CAIXA</t>
         </is>
       </c>
-      <c r="D2256" s="23" t="inlineStr">
+      <c r="D2256" s="26" t="inlineStr">
         <is>
           <t>SABÃO EM PÓ TIXAN YPÊ CAIXA 800G MACIEZ</t>
         </is>
       </c>
-      <c r="E2256" s="23" t="inlineStr"/>
+      <c r="E2256" s="26" t="inlineStr"/>
     </row>
     <row r="2257">
-      <c r="A2257" s="23" t="n">
+      <c r="A2257" s="26" t="n">
         <v>261083</v>
       </c>
-      <c r="B2257" s="23" t="inlineStr">
+      <c r="B2257" s="26" t="inlineStr">
         <is>
           <t>#06 LIMPEZA - SABÃO</t>
         </is>
       </c>
-      <c r="C2257" s="23" t="inlineStr">
+      <c r="C2257" s="26" t="inlineStr">
         <is>
           <t>SABAO PO TIXAN YPE 800GR PRIMAVERA CAIXA</t>
         </is>
       </c>
-      <c r="D2257" s="23" t="inlineStr">
+      <c r="D2257" s="26" t="inlineStr">
         <is>
           <t>SABÃO EM PÓ TIXAN YPÊ CAIXA 800G PRIMAVERA</t>
         </is>
       </c>
-      <c r="E2257" s="23" t="inlineStr"/>
+      <c r="E2257" s="26" t="inlineStr"/>
     </row>
     <row r="2258">
       <c r="A2258" t="n">
@@ -46266,46 +46263,46 @@
       </c>
     </row>
     <row r="2269">
-      <c r="A2269" s="23" t="n">
+      <c r="A2269" s="26" t="n">
         <v>100373</v>
       </c>
-      <c r="B2269" s="23" t="inlineStr">
+      <c r="B2269" s="26" t="inlineStr">
         <is>
           <t>#06 LIMPEZA - SODAS CAUSTICAS</t>
         </is>
       </c>
-      <c r="C2269" s="23" t="inlineStr">
+      <c r="C2269" s="26" t="inlineStr">
         <is>
           <t>SODA CAUSTICA SOL 1KG</t>
         </is>
       </c>
-      <c r="D2269" s="23" t="inlineStr">
+      <c r="D2269" s="26" t="inlineStr">
         <is>
           <t>SODA CAUSTICA SOL 1KG</t>
         </is>
       </c>
-      <c r="E2269" s="23" t="inlineStr"/>
+      <c r="E2269" s="26" t="inlineStr"/>
     </row>
     <row r="2270">
-      <c r="A2270" s="25" t="n">
+      <c r="A2270" s="23" t="n">
         <v>135352</v>
       </c>
-      <c r="B2270" s="25" t="inlineStr">
+      <c r="B2270" s="23" t="inlineStr">
         <is>
           <t>#06 LIMPEZA - SODAS CAUSTICAS</t>
         </is>
       </c>
-      <c r="C2270" s="25" t="inlineStr">
+      <c r="C2270" s="23" t="inlineStr">
         <is>
           <t>SODA CAUSTICA TROVAO 1KG</t>
         </is>
       </c>
-      <c r="D2270" s="25" t="inlineStr">
+      <c r="D2270" s="23" t="inlineStr">
         <is>
           <t>SODA CAUSTICA TROVÃO 1KG</t>
         </is>
       </c>
-      <c r="E2270" s="25" t="inlineStr"/>
+      <c r="E2270" s="23" t="inlineStr"/>
     </row>
     <row r="2271">
       <c r="A2271" t="n">
@@ -55811,25 +55808,25 @@
       </c>
     </row>
     <row r="2746">
-      <c r="A2746" s="23" t="n">
+      <c r="A2746" s="26" t="n">
         <v>144267</v>
       </c>
-      <c r="B2746" s="23" t="inlineStr">
+      <c r="B2746" s="26" t="inlineStr">
         <is>
           <t>#07 HIGIENE PESSOAL - HIGIENE</t>
         </is>
       </c>
-      <c r="C2746" s="23" t="inlineStr">
+      <c r="C2746" s="26" t="inlineStr">
         <is>
           <t>COTONETES TOPZ POTE - 150X1</t>
         </is>
       </c>
-      <c r="D2746" s="23" t="inlineStr">
+      <c r="D2746" s="26" t="inlineStr">
         <is>
           <t>HASTES FLEXIVEIS TOPZ POTE 150UN</t>
         </is>
       </c>
-      <c r="E2746" s="23" t="inlineStr"/>
+      <c r="E2746" s="26" t="inlineStr"/>
     </row>
     <row r="2747">
       <c r="A2747" t="n">
@@ -55972,25 +55969,25 @@
       </c>
     </row>
     <row r="2754">
-      <c r="A2754" s="25" t="n">
+      <c r="A2754" s="23" t="n">
         <v>107928</v>
       </c>
-      <c r="B2754" s="25" t="inlineStr">
+      <c r="B2754" s="23" t="inlineStr">
         <is>
           <t>#07 HIGIENE PESSOAL - HIGIENE BUCAL</t>
         </is>
       </c>
-      <c r="C2754" s="25" t="inlineStr">
+      <c r="C2754" s="23" t="inlineStr">
         <is>
           <t>CR DENTAL COLGATE MPA 180G</t>
         </is>
       </c>
-      <c r="D2754" s="25" t="inlineStr">
+      <c r="D2754" s="23" t="inlineStr">
         <is>
           <t>CREME DENTAL COLGATE 180G MPA</t>
         </is>
       </c>
-      <c r="E2754" s="25" t="inlineStr"/>
+      <c r="E2754" s="23" t="inlineStr"/>
     </row>
     <row r="2755">
       <c r="A2755" t="n">
@@ -56535,25 +56532,25 @@
       </c>
     </row>
     <row r="2782">
-      <c r="A2782" s="23" t="n">
+      <c r="A2782" s="26" t="n">
         <v>108140</v>
       </c>
-      <c r="B2782" s="23" t="inlineStr">
+      <c r="B2782" s="26" t="inlineStr">
         <is>
           <t>#07 HIGIENE PESSOAL - INTIMA</t>
         </is>
       </c>
-      <c r="C2782" s="23" t="inlineStr">
+      <c r="C2782" s="26" t="inlineStr">
         <is>
           <t>ABS INT GEL TRIPLA PROT C/ABA 8X1 TRIP P</t>
         </is>
       </c>
-      <c r="D2782" s="23" t="inlineStr">
+      <c r="D2782" s="26" t="inlineStr">
         <is>
           <t>ABSORVENTE INTIMUS GEL 8 X 1 1PTC TRIPLA PROTEÇÃO COM ABAS SECA</t>
         </is>
       </c>
-      <c r="E2782" s="23" t="inlineStr"/>
+      <c r="E2782" s="26" t="inlineStr"/>
     </row>
     <row r="2783">
       <c r="A2783" t="n">
@@ -57957,25 +57954,25 @@
       </c>
     </row>
     <row r="2853">
-      <c r="A2853" s="25" t="n">
+      <c r="A2853" s="26" t="n">
         <v>346964</v>
       </c>
-      <c r="B2853" s="25" t="inlineStr">
+      <c r="B2853" s="26" t="inlineStr">
         <is>
           <t>#07 HIGIENE PESSOAL - PAPEL HIGIENICO</t>
         </is>
       </c>
-      <c r="C2853" s="25" t="inlineStr">
+      <c r="C2853" s="26" t="inlineStr">
         <is>
           <t>PAPEL HIG NOBLE FD 20M</t>
         </is>
       </c>
-      <c r="D2853" s="25" t="inlineStr">
+      <c r="D2853" s="26" t="inlineStr">
         <is>
           <t>PAPEL HIGIENICO NOBLE 12 X 20M FOLHA DUPLA</t>
         </is>
       </c>
-      <c r="E2853" s="25" t="inlineStr"/>
+      <c r="E2853" s="26" t="inlineStr"/>
     </row>
     <row r="2854">
       <c r="A2854" t="n">
@@ -59398,25 +59395,25 @@
       </c>
     </row>
     <row r="2925">
-      <c r="A2925" s="23" t="n">
+      <c r="A2925" s="26" t="n">
         <v>200683</v>
       </c>
-      <c r="B2925" s="23" t="inlineStr">
+      <c r="B2925" s="26" t="inlineStr">
         <is>
           <t>#07 HIGIENE PESSOAL - SABONETE</t>
         </is>
       </c>
-      <c r="C2925" s="23" t="inlineStr">
+      <c r="C2925" s="26" t="inlineStr">
         <is>
           <t>SAB LUX SUAVE LIRIO AZUL 85G</t>
         </is>
       </c>
-      <c r="D2925" s="23" t="inlineStr">
+      <c r="D2925" s="26" t="inlineStr">
         <is>
           <t>SABONETE LUX 85G SUAVE LIRIO AZUL</t>
         </is>
       </c>
-      <c r="E2925" s="23" t="inlineStr"/>
+      <c r="E2925" s="26" t="inlineStr"/>
     </row>
     <row r="2926">
       <c r="A2926" t="n">
@@ -60774,25 +60771,25 @@
       </c>
     </row>
     <row r="2993">
-      <c r="A2993" s="23" t="n">
+      <c r="A2993" s="26" t="n">
         <v>114809</v>
       </c>
-      <c r="B2993" s="23" t="inlineStr">
+      <c r="B2993" s="26" t="inlineStr">
         <is>
           <t>#08 BAZAR - DESCARTÁVEIS</t>
         </is>
       </c>
-      <c r="C2993" s="23" t="inlineStr">
+      <c r="C2993" s="26" t="inlineStr">
         <is>
           <t>COPO DESC MARATA 200ML 100X1</t>
         </is>
       </c>
-      <c r="D2993" s="23" t="inlineStr">
+      <c r="D2993" s="26" t="inlineStr">
         <is>
           <t>COPO DESCARTAVEL MARATA 200ML X 100UN</t>
         </is>
       </c>
-      <c r="E2993" s="23" t="inlineStr"/>
+      <c r="E2993" s="26" t="inlineStr"/>
     </row>
     <row r="2994">
       <c r="A2994" t="n">
@@ -61055,25 +61052,25 @@
       </c>
     </row>
     <row r="3007">
-      <c r="A3007" s="23" t="n">
+      <c r="A3007" s="26" t="n">
         <v>295630</v>
       </c>
-      <c r="B3007" s="23" t="inlineStr">
+      <c r="B3007" s="26" t="inlineStr">
         <is>
           <t>#08 BAZAR - DESCARTÁVEIS</t>
         </is>
       </c>
-      <c r="C3007" s="23" t="inlineStr">
+      <c r="C3007" s="26" t="inlineStr">
         <is>
           <t>SACO PLASTICO PARANA 7KG ROLO C/50UN</t>
         </is>
       </c>
-      <c r="D3007" s="23" t="inlineStr">
+      <c r="D3007" s="26" t="inlineStr">
         <is>
           <t>SACO PLASTICO PARANA 7KG ROLO 50UN</t>
         </is>
       </c>
-      <c r="E3007" s="23" t="inlineStr"/>
+      <c r="E3007" s="26" t="inlineStr"/>
     </row>
     <row r="3008">
       <c r="A3008" t="n">
@@ -61397,46 +61394,46 @@
       </c>
     </row>
     <row r="3024">
-      <c r="A3024" s="25" t="n">
+      <c r="A3024" s="23" t="n">
         <v>111807</v>
       </c>
-      <c r="B3024" s="25" t="inlineStr">
+      <c r="B3024" s="23" t="inlineStr">
         <is>
           <t>#08 BAZAR - LIMPEZA</t>
         </is>
       </c>
-      <c r="C3024" s="25" t="inlineStr">
+      <c r="C3024" s="23" t="inlineStr">
         <is>
           <t>VASSOURA BETTANIN VARRY 1000</t>
         </is>
       </c>
-      <c r="D3024" s="25" t="inlineStr">
+      <c r="D3024" s="23" t="inlineStr">
         <is>
           <t>VASSOURA BETTANIN VARRY 1000</t>
         </is>
       </c>
-      <c r="E3024" s="25" t="inlineStr"/>
+      <c r="E3024" s="23" t="inlineStr"/>
     </row>
     <row r="3025">
-      <c r="A3025" s="23" t="n">
+      <c r="A3025" s="26" t="n">
         <v>101818</v>
       </c>
-      <c r="B3025" s="23" t="inlineStr">
+      <c r="B3025" s="26" t="inlineStr">
         <is>
           <t>#08 BAZAR - LIMPEZA</t>
         </is>
       </c>
-      <c r="C3025" s="23" t="inlineStr">
+      <c r="C3025" s="26" t="inlineStr">
         <is>
           <t>VASSOURA SANTA MARIA PHENIX 956</t>
         </is>
       </c>
-      <c r="D3025" s="23" t="inlineStr">
+      <c r="D3025" s="26" t="inlineStr">
         <is>
           <t>VASSOURA SANTA MARIA PHENIX 956</t>
         </is>
       </c>
-      <c r="E3025" s="23" t="inlineStr"/>
+      <c r="E3025" s="26" t="inlineStr"/>
     </row>
     <row r="3026">
       <c r="A3026" t="n">
@@ -61639,25 +61636,25 @@
       </c>
     </row>
     <row r="3036">
-      <c r="A3036" s="23" t="n">
+      <c r="A3036" s="26" t="n">
         <v>234144</v>
       </c>
-      <c r="B3036" s="23" t="inlineStr">
+      <c r="B3036" s="26" t="inlineStr">
         <is>
           <t>#08 BAZAR - PANELAS E UTENSÍLIOS DE COZINHA</t>
         </is>
       </c>
-      <c r="C3036" s="23" t="inlineStr">
+      <c r="C3036" s="26" t="inlineStr">
         <is>
           <t>COPO VDO CRISTAR CHOPP 296ML/CM3 PILSENE</t>
         </is>
       </c>
-      <c r="D3036" s="23" t="inlineStr">
+      <c r="D3036" s="26" t="inlineStr">
         <is>
           <t>COPO DE VIDRO CRISTAR 269ML PILSENE CHOPP</t>
         </is>
       </c>
-      <c r="E3036" s="23" t="inlineStr"/>
+      <c r="E3036" s="26" t="inlineStr"/>
     </row>
     <row r="3037">
       <c r="A3037" t="n">
@@ -61680,25 +61677,25 @@
       </c>
     </row>
     <row r="3038">
-      <c r="A3038" s="23" t="n">
+      <c r="A3038" s="26" t="n">
         <v>290165</v>
       </c>
-      <c r="B3038" s="23" t="inlineStr">
+      <c r="B3038" s="26" t="inlineStr">
         <is>
           <t>#08 BAZAR - PANELAS E UTENSÍLIOS DE COZINHA</t>
         </is>
       </c>
-      <c r="C3038" s="23" t="inlineStr">
+      <c r="C3038" s="26" t="inlineStr">
         <is>
           <t>COPO DE VIDRO DARA G4U 300ML BAIXO 52276</t>
         </is>
       </c>
-      <c r="D3038" s="23" t="inlineStr">
+      <c r="D3038" s="26" t="inlineStr">
         <is>
           <t>COPO DE VIDRO DARA G4U 300ML BAIXO</t>
         </is>
       </c>
-      <c r="E3038" s="23" t="inlineStr"/>
+      <c r="E3038" s="26" t="inlineStr"/>
     </row>
     <row r="3039">
       <c r="A3039" t="n">
@@ -61741,25 +61738,25 @@
       </c>
     </row>
     <row r="3041">
-      <c r="A3041" s="23" t="n">
+      <c r="A3041" s="26" t="n">
         <v>112924</v>
       </c>
-      <c r="B3041" s="23" t="inlineStr">
+      <c r="B3041" s="26" t="inlineStr">
         <is>
           <t>#08 BAZAR - PANELAS E UTENSÍLIOS DE COZINHA</t>
         </is>
       </c>
-      <c r="C3041" s="23" t="inlineStr">
+      <c r="C3041" s="26" t="inlineStr">
         <is>
           <t>COPO NADIR AMERICANO DUPLO 300ML</t>
         </is>
       </c>
-      <c r="D3041" s="23" t="inlineStr">
+      <c r="D3041" s="26" t="inlineStr">
         <is>
           <t>COPO DE VIDRO NADIR AMERICANO DUPLO 300ML</t>
         </is>
       </c>
-      <c r="E3041" s="23" t="inlineStr"/>
+      <c r="E3041" s="26" t="inlineStr"/>
     </row>
     <row r="3042">
       <c r="A3042" t="n">
@@ -61782,25 +61779,25 @@
       </c>
     </row>
     <row r="3043">
-      <c r="A3043" s="23" t="n">
+      <c r="A3043" s="26" t="n">
         <v>113856</v>
       </c>
-      <c r="B3043" s="23" t="inlineStr">
+      <c r="B3043" s="26" t="inlineStr">
         <is>
           <t>#08 BAZAR - PANELAS E UTENSÍLIOS DE COZINHA</t>
         </is>
       </c>
-      <c r="C3043" s="23" t="inlineStr">
+      <c r="C3043" s="26" t="inlineStr">
         <is>
           <t>COPO DOSE NADIR 60ML OLE</t>
         </is>
       </c>
-      <c r="D3043" s="23" t="inlineStr">
+      <c r="D3043" s="26" t="inlineStr">
         <is>
           <t>COPO DOSE NADIR OLÉ VIDRO 60ML</t>
         </is>
       </c>
-      <c r="E3043" s="23" t="inlineStr"/>
+      <c r="E3043" s="26" t="inlineStr"/>
     </row>
     <row r="3044">
       <c r="A3044" t="n">
@@ -62143,25 +62140,25 @@
       </c>
     </row>
     <row r="3061">
-      <c r="A3061" s="23" t="n">
+      <c r="A3061" s="26" t="n">
         <v>321965</v>
       </c>
-      <c r="B3061" s="23" t="inlineStr">
+      <c r="B3061" s="26" t="inlineStr">
         <is>
           <t>#08 BAZAR - PAPÉIS DE USO DOMÉSTICO</t>
         </is>
       </c>
-      <c r="C3061" s="23" t="inlineStr">
+      <c r="C3061" s="26" t="inlineStr">
         <is>
           <t>PAPEL TOALHA SANTEPEL 2 ROLOS 120UN SUPE</t>
         </is>
       </c>
-      <c r="D3061" s="23" t="inlineStr">
+      <c r="D3061" s="26" t="inlineStr">
         <is>
           <t>PAPEL TOALHA SANTEPEL 2 X 120UN SUPER ABSORÇÃO</t>
         </is>
       </c>
-      <c r="E3061" s="23" t="inlineStr"/>
+      <c r="E3061" s="26" t="inlineStr"/>
     </row>
     <row r="3062">
       <c r="A3062" t="n">
@@ -62747,25 +62744,25 @@
       </c>
     </row>
     <row r="3091">
-      <c r="A3091" s="25" t="n">
+      <c r="A3091" s="23" t="n">
         <v>253527</v>
       </c>
-      <c r="B3091" s="25" t="inlineStr">
+      <c r="B3091" s="23" t="inlineStr">
         <is>
           <t>#07 HIGIENE PESSOAL - HIGIENE BUCAL</t>
         </is>
       </c>
-      <c r="C3091" s="25" t="inlineStr">
+      <c r="C3091" s="23" t="inlineStr">
         <is>
           <t>CR D SORRISO CARVAO ATIVADO 60G</t>
         </is>
       </c>
-      <c r="D3091" s="25" t="inlineStr">
+      <c r="D3091" s="23" t="inlineStr">
         <is>
           <t>CREME DENTAL SORRISO 60G CARVÃO ATIVADO</t>
         </is>
       </c>
-      <c r="E3091" s="25" t="inlineStr"/>
+      <c r="E3091" s="23" t="inlineStr"/>
     </row>
     <row r="3092">
       <c r="A3092" s="11" t="n">
@@ -62930,25 +62927,25 @@
       </c>
     </row>
     <row r="3100">
-      <c r="A3100" s="35" t="n">
+      <c r="A3100" s="26" t="n">
         <v>341363</v>
       </c>
-      <c r="B3100" s="35" t="inlineStr">
+      <c r="B3100" s="26" t="inlineStr">
         <is>
           <t>#03 AÇOUGUE - #06 EMBUTIDOS E FRIOS</t>
         </is>
       </c>
-      <c r="C3100" s="35" t="inlineStr">
+      <c r="C3100" s="26" t="inlineStr">
         <is>
           <t>LINGUICA PERNIL PERDIGAO 700GR NA BRASA</t>
         </is>
       </c>
-      <c r="D3100" s="35" t="inlineStr">
+      <c r="D3100" s="26" t="inlineStr">
         <is>
           <t>LINGUIÇA DE PERNIL PERDIGÃO 700G NA BRASA</t>
         </is>
       </c>
-      <c r="E3100" s="35" t="inlineStr"/>
+      <c r="E3100" s="26" t="inlineStr"/>
     </row>
     <row r="3101">
       <c r="A3101" s="14" t="n">
@@ -62972,25 +62969,25 @@
       <c r="E3101" s="14" t="inlineStr"/>
     </row>
     <row r="3102">
-      <c r="A3102" s="25" t="n">
+      <c r="A3102" s="23" t="n">
         <v>321525</v>
       </c>
-      <c r="B3102" s="25" t="inlineStr">
+      <c r="B3102" s="23" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - BISCOITOS E SALGADINHOS</t>
         </is>
       </c>
-      <c r="C3102" s="25" t="inlineStr">
+      <c r="C3102" s="23" t="inlineStr">
         <is>
           <t>BISCOITO DOCE MABEL 300GR LEITE</t>
         </is>
       </c>
-      <c r="D3102" s="25" t="inlineStr">
+      <c r="D3102" s="23" t="inlineStr">
         <is>
           <t>BISCOITO DOCE MABEL 300G LEITE</t>
         </is>
       </c>
-      <c r="E3102" s="25" t="inlineStr"/>
+      <c r="E3102" s="23" t="inlineStr"/>
     </row>
     <row r="3103">
       <c r="A3103" s="14" t="n">
@@ -63035,25 +63032,25 @@
       <c r="E3104" s="14" t="inlineStr"/>
     </row>
     <row r="3105">
-      <c r="A3105" s="25" t="n">
+      <c r="A3105" s="23" t="n">
         <v>128900</v>
       </c>
-      <c r="B3105" s="25" t="inlineStr">
+      <c r="B3105" s="23" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - FARINHAS E DERIVADOS</t>
         </is>
       </c>
-      <c r="C3105" s="25" t="inlineStr">
+      <c r="C3105" s="23" t="inlineStr">
         <is>
           <t>FARINHA MAND AMAFIL AMARELA FINA 1KG</t>
         </is>
       </c>
-      <c r="D3105" s="25" t="inlineStr">
+      <c r="D3105" s="23" t="inlineStr">
         <is>
           <t>FARINHA DE MANDIOCA AMAFIL 1KG AMARELA FINA</t>
         </is>
       </c>
-      <c r="E3105" s="25" t="inlineStr"/>
+      <c r="E3105" s="23" t="inlineStr"/>
     </row>
     <row r="3106">
       <c r="A3106" s="14" t="n">
@@ -63644,214 +63641,214 @@
       <c r="E3133" s="20" t="inlineStr"/>
     </row>
     <row r="3134">
-      <c r="A3134" s="25" t="n">
+      <c r="A3134" s="23" t="n">
         <v>299200</v>
       </c>
-      <c r="B3134" s="25" t="inlineStr">
+      <c r="B3134" s="23" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - BISCOITOS E SALGADINHOS</t>
         </is>
       </c>
-      <c r="C3134" s="25" t="inlineStr">
+      <c r="C3134" s="23" t="inlineStr">
         <is>
           <t>BISCOITO MABEL 300GR AGUA E SAL</t>
         </is>
       </c>
-      <c r="D3134" s="25" t="inlineStr">
+      <c r="D3134" s="23" t="inlineStr">
         <is>
           <t>BISCOITO AGUA E SAL MABEL 300G</t>
         </is>
       </c>
-      <c r="E3134" s="25" t="inlineStr"/>
+      <c r="E3134" s="23" t="inlineStr"/>
     </row>
     <row r="3135">
-      <c r="A3135" s="25" t="n">
+      <c r="A3135" s="23" t="n">
         <v>308023</v>
       </c>
-      <c r="B3135" s="25" t="inlineStr">
+      <c r="B3135" s="23" t="inlineStr">
         <is>
           <t>#05 BEBIDA - #01 SUCOS PRONTOS</t>
         </is>
       </c>
-      <c r="C3135" s="25" t="inlineStr">
+      <c r="C3135" s="23" t="inlineStr">
         <is>
           <t>SUCO NUTRI 200ML ABACAXI</t>
         </is>
       </c>
-      <c r="D3135" s="25" t="inlineStr">
+      <c r="D3135" s="23" t="inlineStr">
         <is>
           <t>SUCO NUTRI 200ML ABACAXI</t>
         </is>
       </c>
-      <c r="E3135" s="25" t="inlineStr"/>
+      <c r="E3135" s="23" t="inlineStr"/>
     </row>
     <row r="3136">
-      <c r="A3136" s="25" t="n">
+      <c r="A3136" s="23" t="n">
         <v>308026</v>
       </c>
-      <c r="B3136" s="25" t="inlineStr">
+      <c r="B3136" s="23" t="inlineStr">
         <is>
           <t>#05 BEBIDA - #01 SUCOS PRONTOS</t>
         </is>
       </c>
-      <c r="C3136" s="25" t="inlineStr">
+      <c r="C3136" s="23" t="inlineStr">
         <is>
           <t>SUCO NUTRI 200ML CAJU</t>
         </is>
       </c>
-      <c r="D3136" s="25" t="inlineStr">
+      <c r="D3136" s="23" t="inlineStr">
         <is>
           <t>SUCO NUTRI 200ML CAJU</t>
         </is>
       </c>
-      <c r="E3136" s="25" t="inlineStr"/>
+      <c r="E3136" s="23" t="inlineStr"/>
     </row>
     <row r="3137">
-      <c r="A3137" s="25" t="n">
+      <c r="A3137" s="23" t="n">
         <v>308030</v>
       </c>
-      <c r="B3137" s="25" t="inlineStr">
+      <c r="B3137" s="23" t="inlineStr">
         <is>
           <t>#05 BEBIDA - #01 SUCOS PRONTOS</t>
         </is>
       </c>
-      <c r="C3137" s="25" t="inlineStr">
+      <c r="C3137" s="23" t="inlineStr">
         <is>
           <t>SUCO NUTRI 200ML GOIABA</t>
         </is>
       </c>
-      <c r="D3137" s="25" t="inlineStr">
+      <c r="D3137" s="23" t="inlineStr">
         <is>
           <t>SUCO NUTRI 200ML GOIABA</t>
         </is>
       </c>
-      <c r="E3137" s="25" t="inlineStr"/>
+      <c r="E3137" s="23" t="inlineStr"/>
     </row>
     <row r="3138">
-      <c r="A3138" s="25" t="n">
+      <c r="A3138" s="23" t="n">
         <v>308022</v>
       </c>
-      <c r="B3138" s="25" t="inlineStr">
+      <c r="B3138" s="23" t="inlineStr">
         <is>
           <t>#05 BEBIDA - #01 SUCOS PRONTOS</t>
         </is>
       </c>
-      <c r="C3138" s="25" t="inlineStr">
+      <c r="C3138" s="23" t="inlineStr">
         <is>
           <t>SUCO NUTRI 200ML MANGA</t>
         </is>
       </c>
-      <c r="D3138" s="25" t="inlineStr">
+      <c r="D3138" s="23" t="inlineStr">
         <is>
           <t>SUCO NUTRI 200ML MANGA</t>
         </is>
       </c>
-      <c r="E3138" s="25" t="inlineStr"/>
+      <c r="E3138" s="23" t="inlineStr"/>
     </row>
     <row r="3139">
-      <c r="A3139" s="25" t="n">
+      <c r="A3139" s="23" t="n">
         <v>308028</v>
       </c>
-      <c r="B3139" s="25" t="inlineStr">
+      <c r="B3139" s="23" t="inlineStr">
         <is>
           <t>#05 BEBIDA - #01 SUCOS PRONTOS</t>
         </is>
       </c>
-      <c r="C3139" s="25" t="inlineStr">
+      <c r="C3139" s="23" t="inlineStr">
         <is>
           <t>SUCO NUTRI 200ML MORANGO</t>
         </is>
       </c>
-      <c r="D3139" s="25" t="inlineStr">
+      <c r="D3139" s="23" t="inlineStr">
         <is>
           <t>SUCO NUTRI 200ML MORANGO</t>
         </is>
       </c>
-      <c r="E3139" s="25" t="inlineStr"/>
+      <c r="E3139" s="23" t="inlineStr"/>
     </row>
     <row r="3140">
-      <c r="A3140" s="25" t="n">
+      <c r="A3140" s="23" t="n">
         <v>308029</v>
       </c>
-      <c r="B3140" s="25" t="inlineStr">
+      <c r="B3140" s="23" t="inlineStr">
         <is>
           <t>#05 BEBIDA - #01 SUCOS PRONTOS</t>
         </is>
       </c>
-      <c r="C3140" s="25" t="inlineStr">
+      <c r="C3140" s="23" t="inlineStr">
         <is>
           <t>SUCO NUTRI 200ML UVA</t>
         </is>
       </c>
-      <c r="D3140" s="25" t="inlineStr">
+      <c r="D3140" s="23" t="inlineStr">
         <is>
           <t>SUCO NUTRI 200ML UVA</t>
         </is>
       </c>
-      <c r="E3140" s="25" t="inlineStr"/>
+      <c r="E3140" s="23" t="inlineStr"/>
     </row>
     <row r="3141">
-      <c r="A3141" s="25" t="n">
+      <c r="A3141" s="23" t="n">
         <v>192637</v>
       </c>
-      <c r="B3141" s="25" t="inlineStr">
+      <c r="B3141" s="23" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - FARINHAS E DERIVADOS</t>
         </is>
       </c>
-      <c r="C3141" s="25" t="inlineStr">
+      <c r="C3141" s="23" t="inlineStr">
         <is>
           <t>AMIDO DE MILHO AMAFIL 400GR</t>
         </is>
       </c>
-      <c r="D3141" s="25" t="inlineStr">
+      <c r="D3141" s="23" t="inlineStr">
         <is>
           <t>AMIDO DE MILHO AMAFIL 400G</t>
         </is>
       </c>
-      <c r="E3141" s="25" t="inlineStr"/>
+      <c r="E3141" s="23" t="inlineStr"/>
     </row>
     <row r="3142">
-      <c r="A3142" s="25" t="n">
+      <c r="A3142" s="26" t="n">
         <v>118011</v>
       </c>
-      <c r="B3142" s="25" t="inlineStr">
+      <c r="B3142" s="26" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - CONDIMENTOS E TEMPEROS</t>
         </is>
       </c>
-      <c r="C3142" s="25" t="inlineStr">
+      <c r="C3142" s="26" t="inlineStr">
         <is>
           <t>COLORIFICO SINHA 500GR</t>
         </is>
       </c>
-      <c r="D3142" s="25" t="inlineStr">
+      <c r="D3142" s="26" t="inlineStr">
         <is>
           <t>COLORIFICO SINHA 500G</t>
         </is>
       </c>
-      <c r="E3142" s="25" t="inlineStr"/>
+      <c r="E3142" s="26" t="inlineStr"/>
     </row>
     <row r="3143">
-      <c r="A3143" s="25" t="n">
+      <c r="A3143" s="23" t="n">
         <v>315282</v>
       </c>
-      <c r="B3143" s="25" t="inlineStr">
+      <c r="B3143" s="23" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - MASSAS</t>
         </is>
       </c>
-      <c r="C3143" s="25" t="inlineStr">
+      <c r="C3143" s="23" t="inlineStr">
         <is>
           <t>MASSA PASTEL MASSAS DA MAMMA 1KG RETANG</t>
         </is>
       </c>
-      <c r="D3143" s="25" t="inlineStr">
+      <c r="D3143" s="23" t="inlineStr">
         <is>
           <t>MASSA DE PASTEL MASSAS DA MAMMA 1KG RETANGULAR</t>
         </is>
       </c>
-      <c r="E3143" s="25" t="inlineStr"/>
+      <c r="E3143" s="23" t="inlineStr"/>
     </row>
     <row r="3144">
       <c r="A3144" s="22" t="n">
@@ -63917,385 +63914,721 @@
       <c r="E3146" s="22" t="inlineStr"/>
     </row>
     <row r="3147">
-      <c r="A3147" s="23" t="n">
+      <c r="A3147" s="26" t="n">
         <v>222380</v>
       </c>
-      <c r="B3147" s="23" t="inlineStr">
+      <c r="B3147" s="26" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - CONDIMENTOS E TEMPEROS</t>
         </is>
       </c>
-      <c r="C3147" s="23" t="inlineStr">
+      <c r="C3147" s="26" t="inlineStr">
         <is>
           <t>AZEITONAS MARATA FAT P240G D100G</t>
         </is>
       </c>
-      <c r="D3147" s="23" t="inlineStr">
+      <c r="D3147" s="26" t="inlineStr">
         <is>
           <t>AZEITONAS VERDES MARATA 240G FATIADAS</t>
         </is>
       </c>
-      <c r="E3147" s="23" t="inlineStr"/>
+      <c r="E3147" s="26" t="inlineStr"/>
     </row>
     <row r="3148">
-      <c r="A3148" s="23" t="n">
+      <c r="A3148" s="26" t="n">
         <v>321526</v>
       </c>
-      <c r="B3148" s="23" t="inlineStr">
+      <c r="B3148" s="26" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - BISCOITOS E SALGADINHOS</t>
         </is>
       </c>
-      <c r="C3148" s="23" t="inlineStr">
+      <c r="C3148" s="26" t="inlineStr">
         <is>
           <t>BISCOITO LAMINADO MABEL 300GR CHOCOLATE</t>
         </is>
       </c>
-      <c r="D3148" s="23" t="inlineStr">
+      <c r="D3148" s="26" t="inlineStr">
         <is>
           <t>BISCOITO LAMINADO MABEL 300G CHOCOLATE</t>
         </is>
       </c>
-      <c r="E3148" s="23" t="inlineStr"/>
+      <c r="E3148" s="26" t="inlineStr"/>
     </row>
     <row r="3149">
-      <c r="A3149" s="23" t="n">
+      <c r="A3149" s="26" t="n">
         <v>260315</v>
       </c>
-      <c r="B3149" s="23" t="inlineStr">
+      <c r="B3149" s="26" t="inlineStr">
         <is>
           <t>#08 BAZAR - DESCARTÁVEIS</t>
         </is>
       </c>
-      <c r="C3149" s="23" t="inlineStr">
+      <c r="C3149" s="26" t="inlineStr">
         <is>
           <t>COPO DESC 180ML PS TRANSP PURACASA</t>
         </is>
       </c>
-      <c r="D3149" s="23" t="inlineStr">
+      <c r="D3149" s="26" t="inlineStr">
         <is>
           <t>COPO DESCARTAVEL PURACASA 180ML TRANSPARENTES</t>
         </is>
       </c>
-      <c r="E3149" s="23" t="inlineStr"/>
+      <c r="E3149" s="26" t="inlineStr"/>
     </row>
     <row r="3150">
-      <c r="A3150" s="23" t="n">
+      <c r="A3150" s="26" t="n">
         <v>107946</v>
       </c>
-      <c r="B3150" s="23" t="inlineStr">
+      <c r="B3150" s="26" t="inlineStr">
         <is>
           <t>#07 HIGIENE PESSOAL - HIGIENE BUCAL</t>
         </is>
       </c>
-      <c r="C3150" s="23" t="inlineStr">
+      <c r="C3150" s="26" t="inlineStr">
         <is>
           <t>CR DENTAL COLGATE MPA/MFP 90GR</t>
         </is>
       </c>
-      <c r="D3150" s="23" t="inlineStr">
+      <c r="D3150" s="26" t="inlineStr">
         <is>
           <t>CREME DENTAL COLGATE 90G MENTA REFRESCANTE</t>
         </is>
       </c>
-      <c r="E3150" s="23" t="inlineStr"/>
+      <c r="E3150" s="26" t="inlineStr"/>
     </row>
     <row r="3151">
-      <c r="A3151" s="23" t="n">
+      <c r="A3151" s="26" t="n">
         <v>143493</v>
       </c>
-      <c r="B3151" s="23" t="inlineStr">
+      <c r="B3151" s="26" t="inlineStr">
         <is>
           <t>#08 BAZAR - DESCARTÁVEIS</t>
         </is>
       </c>
-      <c r="C3151" s="23" t="inlineStr">
+      <c r="C3151" s="26" t="inlineStr">
         <is>
           <t>FOLHA DE ALUMINIO WIDA 7,5M X 45CM</t>
         </is>
       </c>
-      <c r="D3151" s="23" t="inlineStr">
+      <c r="D3151" s="26" t="inlineStr">
         <is>
           <t>FOLHA DE ALUMINIO WIDA 7,5M X 45CM</t>
         </is>
       </c>
-      <c r="E3151" s="23" t="inlineStr"/>
+      <c r="E3151" s="26" t="inlineStr"/>
     </row>
     <row r="3152">
-      <c r="A3152" s="23" t="n">
+      <c r="A3152" s="26" t="n">
         <v>228961</v>
       </c>
-      <c r="B3152" s="23" t="inlineStr">
+      <c r="B3152" s="26" t="inlineStr">
         <is>
           <t>#06 LIMPEZA - LIMPADORES</t>
         </is>
       </c>
-      <c r="C3152" s="23" t="inlineStr">
+      <c r="C3152" s="26" t="inlineStr">
         <is>
           <t>GLADE AERO F AGUAS FLORAIS 360ML</t>
         </is>
       </c>
-      <c r="D3152" s="23" t="inlineStr">
+      <c r="D3152" s="26" t="inlineStr">
         <is>
           <t>ODORIZADOR AEROSOL GLADE 360ML AGUAS FLORAIS</t>
         </is>
       </c>
-      <c r="E3152" s="23" t="inlineStr"/>
+      <c r="E3152" s="26" t="inlineStr"/>
     </row>
     <row r="3153">
-      <c r="A3153" s="23" t="n">
+      <c r="A3153" s="26" t="n">
         <v>220933</v>
       </c>
-      <c r="B3153" s="23" t="inlineStr">
+      <c r="B3153" s="26" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - CONDIMENTOS E TEMPEROS</t>
         </is>
       </c>
-      <c r="C3153" s="23" t="inlineStr">
+      <c r="C3153" s="26" t="inlineStr">
         <is>
           <t>KETCHUP HEINZ 1,033KG FR</t>
         </is>
       </c>
-      <c r="D3153" s="23" t="inlineStr">
+      <c r="D3153" s="26" t="inlineStr">
         <is>
           <t>KETCHUP HEINZ 1,033KG</t>
         </is>
       </c>
-      <c r="E3153" s="23" t="inlineStr"/>
+      <c r="E3153" s="26" t="inlineStr"/>
     </row>
     <row r="3154">
-      <c r="A3154" s="23" t="n">
+      <c r="A3154" s="26" t="n">
         <v>148607</v>
       </c>
-      <c r="B3154" s="23" t="inlineStr">
+      <c r="B3154" s="26" t="inlineStr">
         <is>
           <t>#06 LIMPEZA - LIMPADORES</t>
         </is>
       </c>
-      <c r="C3154" s="23" t="inlineStr">
+      <c r="C3154" s="26" t="inlineStr">
         <is>
           <t>LIMP PERF CASA E PERFUME 500ML PASSIONE</t>
         </is>
       </c>
-      <c r="D3154" s="23" t="inlineStr">
+      <c r="D3154" s="26" t="inlineStr">
         <is>
           <t>LIMPADOR PERFUMADO CASA E PERFUME 500ML PASSIONE</t>
         </is>
       </c>
-      <c r="E3154" s="23" t="inlineStr"/>
+      <c r="E3154" s="26" t="inlineStr"/>
     </row>
     <row r="3155">
-      <c r="A3155" s="23" t="n">
+      <c r="A3155" s="26" t="n">
         <v>156417</v>
       </c>
-      <c r="B3155" s="23" t="inlineStr">
+      <c r="B3155" s="26" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - BISCOITOS E SALGADINHOS</t>
         </is>
       </c>
-      <c r="C3155" s="23" t="inlineStr">
+      <c r="C3155" s="26" t="inlineStr">
         <is>
           <t>MILHO DE PIPOCA BONOMILHO 500GR</t>
         </is>
       </c>
-      <c r="D3155" s="23" t="inlineStr">
+      <c r="D3155" s="26" t="inlineStr">
         <is>
           <t>MILHO DE PIPOCA BONOMILHO 500G</t>
         </is>
       </c>
-      <c r="E3155" s="23" t="inlineStr"/>
+      <c r="E3155" s="26" t="inlineStr"/>
     </row>
     <row r="3156">
-      <c r="A3156" s="23" t="n">
+      <c r="A3156" s="26" t="n">
         <v>183229</v>
       </c>
-      <c r="B3156" s="23" t="inlineStr">
+      <c r="B3156" s="26" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - CONDIMENTOS E TEMPEROS</t>
         </is>
       </c>
-      <c r="C3156" s="23" t="inlineStr">
+      <c r="C3156" s="26" t="inlineStr">
         <is>
           <t>MOLHO TOMATE DEZ 300GR ERVAS FINAS</t>
         </is>
       </c>
-      <c r="D3156" s="23" t="inlineStr">
+      <c r="D3156" s="26" t="inlineStr">
         <is>
           <t>MOLHO DE TOMATE DEZ 300G ERVAS FINAS</t>
         </is>
       </c>
-      <c r="E3156" s="23" t="inlineStr"/>
+      <c r="E3156" s="26" t="inlineStr"/>
     </row>
     <row r="3157">
-      <c r="A3157" s="23" t="n">
+      <c r="A3157" s="26" t="n">
         <v>104418</v>
       </c>
-      <c r="B3157" s="23" t="inlineStr">
+      <c r="B3157" s="26" t="inlineStr">
         <is>
           <t>#05 BEBIDA - #00 BEBIDAS GASEIFICADAS</t>
         </is>
       </c>
-      <c r="C3157" s="23" t="inlineStr">
+      <c r="C3157" s="26" t="inlineStr">
         <is>
           <t>REFRIG COCA COLA ZERO 2L</t>
         </is>
       </c>
-      <c r="D3157" s="23" t="inlineStr">
+      <c r="D3157" s="26" t="inlineStr">
         <is>
           <t>REFRIGERANTE COCA COLA ZERO 2L</t>
         </is>
       </c>
-      <c r="E3157" s="23" t="inlineStr"/>
+      <c r="E3157" s="26" t="inlineStr"/>
     </row>
     <row r="3158">
-      <c r="A3158" s="23" t="n">
+      <c r="A3158" s="26" t="n">
         <v>200680</v>
       </c>
-      <c r="B3158" s="23" t="inlineStr">
+      <c r="B3158" s="26" t="inlineStr">
         <is>
           <t>#07 HIGIENE PESSOAL - SABONETE</t>
         </is>
       </c>
-      <c r="C3158" s="23" t="inlineStr">
+      <c r="C3158" s="26" t="inlineStr">
         <is>
           <t>SAB LUX SUAVE BUQUE JASMIM 85G</t>
         </is>
       </c>
-      <c r="D3158" s="23" t="inlineStr">
+      <c r="D3158" s="26" t="inlineStr">
         <is>
           <t>SABONETE LUX 85G SUAVE BUQUE DE JASMIM</t>
         </is>
       </c>
-      <c r="E3158" s="23" t="inlineStr"/>
+      <c r="E3158" s="26" t="inlineStr"/>
     </row>
     <row r="3159">
-      <c r="A3159" s="23" t="n">
+      <c r="A3159" s="26" t="n">
         <v>200684</v>
       </c>
-      <c r="B3159" s="23" t="inlineStr">
+      <c r="B3159" s="26" t="inlineStr">
         <is>
           <t>#07 HIGIENE PESSOAL - SABONETE</t>
         </is>
       </c>
-      <c r="C3159" s="23" t="inlineStr">
+      <c r="C3159" s="26" t="inlineStr">
         <is>
           <t>SAB LUX SUAVE ORQUIDEA NEGRA 85G</t>
         </is>
       </c>
-      <c r="D3159" s="23" t="inlineStr">
+      <c r="D3159" s="26" t="inlineStr">
         <is>
           <t>SABONETE LUX 85G SUAVE ORQUIDEA NEGRA</t>
         </is>
       </c>
-      <c r="E3159" s="23" t="inlineStr"/>
+      <c r="E3159" s="26" t="inlineStr"/>
     </row>
     <row r="3160">
-      <c r="A3160" s="23" t="n">
+      <c r="A3160" s="26" t="n">
         <v>199374</v>
       </c>
-      <c r="B3160" s="23" t="inlineStr">
+      <c r="B3160" s="26" t="inlineStr">
         <is>
           <t>#07 HIGIENE PESSOAL - SABONETE</t>
         </is>
       </c>
-      <c r="C3160" s="23" t="inlineStr">
+      <c r="C3160" s="26" t="inlineStr">
         <is>
           <t>SAB.LUX BOTANICALS 85GR FLOR DE LOTUS</t>
         </is>
       </c>
-      <c r="D3160" s="23" t="inlineStr">
+      <c r="D3160" s="26" t="inlineStr">
         <is>
           <t>SABONETE LUX 85G BOTANICALS FLOR DE LOTUS</t>
         </is>
       </c>
-      <c r="E3160" s="23" t="inlineStr"/>
+      <c r="E3160" s="26" t="inlineStr"/>
     </row>
     <row r="3161">
-      <c r="A3161" s="23" t="n">
+      <c r="A3161" s="26" t="n">
         <v>200697</v>
       </c>
-      <c r="B3161" s="23" t="inlineStr">
+      <c r="B3161" s="26" t="inlineStr">
         <is>
           <t>#07 HIGIENE PESSOAL - SABONETE</t>
         </is>
       </c>
-      <c r="C3161" s="23" t="inlineStr">
+      <c r="C3161" s="26" t="inlineStr">
         <is>
           <t>SAB.LUX BOTANICALS 85GR ROSAS FRANCESAS</t>
         </is>
       </c>
-      <c r="D3161" s="23" t="inlineStr">
+      <c r="D3161" s="26" t="inlineStr">
         <is>
           <t>SABONETE LUX 85G ROSAS FRANCESAS</t>
         </is>
       </c>
-      <c r="E3161" s="23" t="inlineStr"/>
+      <c r="E3161" s="26" t="inlineStr"/>
     </row>
     <row r="3162">
-      <c r="A3162" s="23" t="n">
+      <c r="A3162" s="26" t="n">
         <v>314809</v>
       </c>
-      <c r="B3162" s="23" t="inlineStr">
+      <c r="B3162" s="26" t="inlineStr">
         <is>
           <t>#07 HIGIENE PESSOAL - SABONETE</t>
         </is>
       </c>
-      <c r="C3162" s="23" t="inlineStr">
+      <c r="C3162" s="26" t="inlineStr">
         <is>
           <t>SABONETE LUX 85GR BOTANICALS</t>
         </is>
       </c>
-      <c r="D3162" s="23" t="inlineStr">
+      <c r="D3162" s="26" t="inlineStr">
         <is>
           <t>SABONETE LUX 85G BOTANICALS</t>
         </is>
       </c>
-      <c r="E3162" s="23" t="inlineStr"/>
+      <c r="E3162" s="26" t="inlineStr"/>
     </row>
     <row r="3163">
-      <c r="A3163" s="35" t="n">
+      <c r="A3163" s="26" t="n">
         <v>332652</v>
       </c>
-      <c r="B3163" s="35" t="inlineStr">
+      <c r="B3163" s="26" t="inlineStr">
         <is>
           <t>#03 AÇOUGUE - #06 EMBUTIDOS E FRIOS</t>
         </is>
       </c>
-      <c r="C3163" s="35" t="inlineStr">
+      <c r="C3163" s="26" t="inlineStr">
         <is>
           <t>LINGUICA BACON SEARA 600G TERMO</t>
         </is>
       </c>
-      <c r="D3163" s="35" t="inlineStr">
+      <c r="D3163" s="26" t="inlineStr">
         <is>
           <t>LINGUIÇA DE BACON SEARA 600G TERMO</t>
         </is>
       </c>
-      <c r="E3163" s="35" t="inlineStr"/>
+      <c r="E3163" s="26" t="inlineStr"/>
     </row>
     <row r="3164">
-      <c r="A3164" s="35" t="n">
+      <c r="A3164" s="26" t="n">
         <v>289484</v>
       </c>
-      <c r="B3164" s="35" t="inlineStr">
+      <c r="B3164" s="26" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - GORDURAS E MARGARINAS</t>
         </is>
       </c>
-      <c r="C3164" s="35" t="inlineStr">
+      <c r="C3164" s="26" t="inlineStr">
         <is>
           <t>MANTEIGA COMUM GRANSELETTO 200G  COM SAL</t>
         </is>
       </c>
-      <c r="D3164" s="35" t="inlineStr">
+      <c r="D3164" s="26" t="inlineStr">
         <is>
           <t>MANTEIGA COMUM GRANSELETTO 200G COM SAL</t>
         </is>
       </c>
-      <c r="E3164" s="35" t="inlineStr"/>
+      <c r="E3164" s="26" t="inlineStr"/>
+    </row>
+    <row r="3165">
+      <c r="A3165" s="30" t="n">
+        <v>247767</v>
+      </c>
+      <c r="B3165" s="30" t="inlineStr">
+        <is>
+          <t>#02 MERCEARIA - CHOCOLATES E DOCES</t>
+        </is>
+      </c>
+      <c r="C3165" s="30" t="inlineStr">
+        <is>
+          <t>CHOCOLATE LACTA BIS 100,8GR BRANCO</t>
+        </is>
+      </c>
+      <c r="D3165" s="30" t="inlineStr">
+        <is>
+          <t>CHOCOLATE BIS 100,8G BRANCO</t>
+        </is>
+      </c>
+      <c r="E3165" s="30" t="inlineStr"/>
+    </row>
+    <row r="3166">
+      <c r="A3166" s="30" t="n">
+        <v>247770</v>
+      </c>
+      <c r="B3166" s="30" t="inlineStr">
+        <is>
+          <t>#02 MERCEARIA - CHOCOLATES E DOCES</t>
+        </is>
+      </c>
+      <c r="C3166" s="30" t="inlineStr">
+        <is>
+          <t>CHOCOLATE WAFER BIS 100,8GR  AO LEITE</t>
+        </is>
+      </c>
+      <c r="D3166" s="30" t="inlineStr">
+        <is>
+          <t>CHOCOLATE BIS 100,8G AO LEITE</t>
+        </is>
+      </c>
+      <c r="E3166" s="30" t="inlineStr"/>
+    </row>
+    <row r="3167">
+      <c r="A3167" s="30" t="n">
+        <v>297222</v>
+      </c>
+      <c r="B3167" s="30" t="inlineStr">
+        <is>
+          <t>#02 MERCEARIA - REFRESCOS EM PÓ</t>
+        </is>
+      </c>
+      <c r="C3167" s="30" t="inlineStr">
+        <is>
+          <t>REFRESCO PO FRISCO 18GR LARANJA C/ACEROL</t>
+        </is>
+      </c>
+      <c r="D3167" s="30" t="inlineStr">
+        <is>
+          <t>REFRESCO EM PÓ FRISCO 18G LARANJA COM ACEROLA</t>
+        </is>
+      </c>
+      <c r="E3167" s="30" t="inlineStr"/>
+    </row>
+    <row r="3168">
+      <c r="A3168" s="30" t="n">
+        <v>293872</v>
+      </c>
+      <c r="B3168" s="30" t="inlineStr">
+        <is>
+          <t>#02 MERCEARIA - REFRESCOS EM PÓ</t>
+        </is>
+      </c>
+      <c r="C3168" s="30" t="inlineStr">
+        <is>
+          <t>REFRESCO PO FRISCO 18GR MARACUJA</t>
+        </is>
+      </c>
+      <c r="D3168" s="30" t="inlineStr">
+        <is>
+          <t>REFRESCO EM PÓ FRISCO 18G MARACUJA</t>
+        </is>
+      </c>
+      <c r="E3168" s="30" t="inlineStr"/>
+    </row>
+    <row r="3169">
+      <c r="A3169" s="30" t="n">
+        <v>295228</v>
+      </c>
+      <c r="B3169" s="30" t="inlineStr">
+        <is>
+          <t>#02 MERCEARIA - REFRESCOS EM PÓ</t>
+        </is>
+      </c>
+      <c r="C3169" s="30" t="inlineStr">
+        <is>
+          <t>REFRESCO PO FRISCO 18GR SACHE CAJA</t>
+        </is>
+      </c>
+      <c r="D3169" s="30" t="inlineStr">
+        <is>
+          <t>REFRESCO EM PÓ FRISCO 18G CAJA</t>
+        </is>
+      </c>
+      <c r="E3169" s="30" t="inlineStr"/>
+    </row>
+    <row r="3170">
+      <c r="A3170" s="30" t="n">
+        <v>309635</v>
+      </c>
+      <c r="B3170" s="30" t="inlineStr">
+        <is>
+          <t>#02 MERCEARIA - REFRESCOS EM PÓ</t>
+        </is>
+      </c>
+      <c r="C3170" s="30" t="inlineStr">
+        <is>
+          <t>REFRESCO PO FRISCO 18GR SACHE CAJU</t>
+        </is>
+      </c>
+      <c r="D3170" s="30" t="inlineStr">
+        <is>
+          <t>REFRESCO EM PÓ FRISCO 18G CAJU</t>
+        </is>
+      </c>
+      <c r="E3170" s="30" t="inlineStr"/>
+    </row>
+    <row r="3171">
+      <c r="A3171" s="30" t="n">
+        <v>295223</v>
+      </c>
+      <c r="B3171" s="30" t="inlineStr">
+        <is>
+          <t>#02 MERCEARIA - REFRESCOS EM PÓ</t>
+        </is>
+      </c>
+      <c r="C3171" s="30" t="inlineStr">
+        <is>
+          <t>REFRESCO PO FRISCO 18GR SACHE GOIABA JON</t>
+        </is>
+      </c>
+      <c r="D3171" s="30" t="inlineStr">
+        <is>
+          <t>REFRESCO EM PÓ FRISCO 18G GOIABA</t>
+        </is>
+      </c>
+      <c r="E3171" s="30" t="inlineStr"/>
+    </row>
+    <row r="3172">
+      <c r="A3172" s="30" t="n">
+        <v>309636</v>
+      </c>
+      <c r="B3172" s="30" t="inlineStr">
+        <is>
+          <t>#02 MERCEARIA - REFRESCOS EM PÓ</t>
+        </is>
+      </c>
+      <c r="C3172" s="30" t="inlineStr">
+        <is>
+          <t>REFRESCO PO FRISCO 18GR SACHE GRAVIOLA</t>
+        </is>
+      </c>
+      <c r="D3172" s="30" t="inlineStr">
+        <is>
+          <t>REFRESCO EM PÓ FRISCO 18G GRAVIOLA</t>
+        </is>
+      </c>
+      <c r="E3172" s="30" t="inlineStr"/>
+    </row>
+    <row r="3173">
+      <c r="A3173" s="30" t="n">
+        <v>309637</v>
+      </c>
+      <c r="B3173" s="30" t="inlineStr">
+        <is>
+          <t>#02 MERCEARIA - REFRESCOS EM PÓ</t>
+        </is>
+      </c>
+      <c r="C3173" s="30" t="inlineStr">
+        <is>
+          <t>REFRESCO PO FRISCO 18GR SACHE GUARANA</t>
+        </is>
+      </c>
+      <c r="D3173" s="30" t="inlineStr">
+        <is>
+          <t>REFRESCO EM PÓ FRISCO 18G GUARANA</t>
+        </is>
+      </c>
+      <c r="E3173" s="30" t="inlineStr"/>
+    </row>
+    <row r="3174">
+      <c r="A3174" s="30" t="n">
+        <v>295222</v>
+      </c>
+      <c r="B3174" s="30" t="inlineStr">
+        <is>
+          <t>#02 MERCEARIA - REFRESCOS EM PÓ</t>
+        </is>
+      </c>
+      <c r="C3174" s="30" t="inlineStr">
+        <is>
+          <t>REFRESCO PO FRISCO 18GR SACHE LARANJA JO</t>
+        </is>
+      </c>
+      <c r="D3174" s="30" t="inlineStr">
+        <is>
+          <t>REFRESCO EM PÓ FRISCO 18G LARANJA</t>
+        </is>
+      </c>
+      <c r="E3174" s="30" t="inlineStr"/>
+    </row>
+    <row r="3175">
+      <c r="A3175" s="30" t="n">
+        <v>295225</v>
+      </c>
+      <c r="B3175" s="30" t="inlineStr">
+        <is>
+          <t>#02 MERCEARIA - REFRESCOS EM PÓ</t>
+        </is>
+      </c>
+      <c r="C3175" s="30" t="inlineStr">
+        <is>
+          <t>REFRESCO PO FRISCO 18GR SACHE MANGA JONE</t>
+        </is>
+      </c>
+      <c r="D3175" s="30" t="inlineStr">
+        <is>
+          <t>REFRESCO EM PÓ FRISCO 18G MANGA</t>
+        </is>
+      </c>
+      <c r="E3175" s="30" t="inlineStr"/>
+    </row>
+    <row r="3176">
+      <c r="A3176" s="30" t="n">
+        <v>295221</v>
+      </c>
+      <c r="B3176" s="30" t="inlineStr">
+        <is>
+          <t>#02 MERCEARIA - REFRESCOS EM PÓ</t>
+        </is>
+      </c>
+      <c r="C3176" s="30" t="inlineStr">
+        <is>
+          <t>REFRESCO PO FRISCO 18GR SACHE MORANGO JO</t>
+        </is>
+      </c>
+      <c r="D3176" s="30" t="inlineStr">
+        <is>
+          <t>REFRESCO EM PÓ FRISCO 18G MORANGO</t>
+        </is>
+      </c>
+      <c r="E3176" s="30" t="inlineStr"/>
+    </row>
+    <row r="3177">
+      <c r="A3177" s="30" t="n">
+        <v>309638</v>
+      </c>
+      <c r="B3177" s="30" t="inlineStr">
+        <is>
+          <t>#02 MERCEARIA - REFRESCOS EM PÓ</t>
+        </is>
+      </c>
+      <c r="C3177" s="30" t="inlineStr">
+        <is>
+          <t>REFRESCO PO FRISCO 18GR SACHE SALADA DE</t>
+        </is>
+      </c>
+      <c r="D3177" s="30" t="inlineStr">
+        <is>
+          <t>REFRESCO EM PÓ FRISCO 18G SALADA</t>
+        </is>
+      </c>
+      <c r="E3177" s="30" t="inlineStr"/>
+    </row>
+    <row r="3178">
+      <c r="A3178" s="30" t="n">
+        <v>297220</v>
+      </c>
+      <c r="B3178" s="30" t="inlineStr">
+        <is>
+          <t>#02 MERCEARIA - REFRESCOS EM PÓ</t>
+        </is>
+      </c>
+      <c r="C3178" s="30" t="inlineStr">
+        <is>
+          <t>REFRESCO PO FRISCO 18GR TANGERINA SACHE</t>
+        </is>
+      </c>
+      <c r="D3178" s="30" t="inlineStr">
+        <is>
+          <t>REFRESCO EM PÓ FRISCO 18G TANGERINA</t>
+        </is>
+      </c>
+      <c r="E3178" s="30" t="inlineStr"/>
+    </row>
+    <row r="3179">
+      <c r="A3179" s="30" t="n">
+        <v>295226</v>
+      </c>
+      <c r="B3179" s="30" t="inlineStr">
+        <is>
+          <t>#02 MERCEARIA - REFRESCOS EM PÓ</t>
+        </is>
+      </c>
+      <c r="C3179" s="30" t="inlineStr">
+        <is>
+          <t>REFRESCO PO FRISCO LIMAO JONES SACHE 18G</t>
+        </is>
+      </c>
+      <c r="D3179" s="30" t="inlineStr">
+        <is>
+          <t>REFRESCO EM PÓ FRISCO 18G LIMÃO</t>
+        </is>
+      </c>
+      <c r="E3179" s="30" t="inlineStr"/>
+    </row>
+    <row r="3180">
+      <c r="A3180" s="30" t="n">
+        <v>295224</v>
+      </c>
+      <c r="B3180" s="30" t="inlineStr">
+        <is>
+          <t>#02 MERCEARIA - REFRESCOS EM PÓ</t>
+        </is>
+      </c>
+      <c r="C3180" s="30" t="inlineStr">
+        <is>
+          <t>REFRESCO PO FRISCO UVA JONES SACHE 18GR</t>
+        </is>
+      </c>
+      <c r="D3180" s="30" t="inlineStr">
+        <is>
+          <t>REFRESCO EM PÓ FRISCO 18G UVA</t>
+        </is>
+      </c>
+      <c r="E3180" s="30" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E3164">
+  <autoFilter ref="A1:E3180">
     <sortState ref="A1226:E1265">
       <sortCondition ref="E1:E3113"/>
     </sortState>

--- a/produtos_cadastrados.xlsx
+++ b/produtos_cadastrados.xlsx
@@ -659,25 +659,25 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="26" t="n">
+      <c r="A3" s="31" t="n">
         <v>100038</v>
       </c>
-      <c r="B3" s="26" t="inlineStr">
+      <c r="B3" s="31" t="inlineStr">
         <is>
           <t>#01 MERCEARIA - #01 CEREAIS E GRÃOS</t>
         </is>
       </c>
-      <c r="C3" s="26" t="inlineStr">
+      <c r="C3" s="31" t="inlineStr">
         <is>
           <t>ARROZ BRANCO BREJEIRO 5KG TIPO 1</t>
         </is>
       </c>
-      <c r="D3" s="26" t="inlineStr">
+      <c r="D3" s="31" t="inlineStr">
         <is>
           <t>ARROZ BREJEIRO PCT 5KG TIPO 1 BRANCO</t>
         </is>
       </c>
-      <c r="E3" s="26" t="inlineStr"/>
+      <c r="E3" s="31" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -800,25 +800,25 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="26" t="n">
+      <c r="A10" s="31" t="n">
         <v>325990</v>
       </c>
-      <c r="B10" s="26" t="inlineStr">
+      <c r="B10" s="31" t="inlineStr">
         <is>
           <t>#01 MERCEARIA - #01 CEREAIS E GRÃOS</t>
         </is>
       </c>
-      <c r="C10" s="26" t="inlineStr">
+      <c r="C10" s="31" t="inlineStr">
         <is>
           <t>ARROZ BRANCO FLORA 5KG TIPO 1</t>
         </is>
       </c>
-      <c r="D10" s="26" t="inlineStr">
+      <c r="D10" s="31" t="inlineStr">
         <is>
           <t>ARROZ FLORA PCT 5KG TIPO 1 BRANCO</t>
         </is>
       </c>
-      <c r="E10" s="26" t="inlineStr"/>
+      <c r="E10" s="31" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1025,25 +1025,25 @@
       <c r="E20" s="23" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="26" t="n">
+      <c r="A21" s="31" t="n">
         <v>100020</v>
       </c>
-      <c r="B21" s="26" t="inlineStr">
+      <c r="B21" s="31" t="inlineStr">
         <is>
           <t>#01 MERCEARIA - #01 CEREAIS E GRÃOS</t>
         </is>
       </c>
-      <c r="C21" s="26" t="inlineStr">
+      <c r="C21" s="31" t="inlineStr">
         <is>
           <t>ARROZ REALENGO 5KG BCO. TIPO 1</t>
         </is>
       </c>
-      <c r="D21" s="26" t="inlineStr">
+      <c r="D21" s="31" t="inlineStr">
         <is>
           <t>ARROZ REALENGO PCT 5KG TIPO 1 BRANCO</t>
         </is>
       </c>
-      <c r="E21" s="26" t="inlineStr"/>
+      <c r="E21" s="31" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="23" t="n">
@@ -1288,25 +1288,25 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="26" t="n">
+      <c r="A34" s="31" t="n">
         <v>116507</v>
       </c>
-      <c r="B34" s="26" t="inlineStr">
+      <c r="B34" s="31" t="inlineStr">
         <is>
           <t>#01 MERCEARIA - #02 FEIJÕES E LEGUMINOSAS</t>
         </is>
       </c>
-      <c r="C34" s="26" t="inlineStr">
+      <c r="C34" s="31" t="inlineStr">
         <is>
           <t>FEIJÃO DA CASA 1KG CARIOCA</t>
         </is>
       </c>
-      <c r="D34" s="26" t="inlineStr">
+      <c r="D34" s="31" t="inlineStr">
         <is>
           <t>FEIJÃO CARIOCA DA CASA 1KG</t>
         </is>
       </c>
-      <c r="E34" s="26" t="inlineStr"/>
+      <c r="E34" s="31" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -1410,25 +1410,25 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="26" t="n">
+      <c r="A40" s="31" t="n">
         <v>163918</v>
       </c>
-      <c r="B40" s="26" t="inlineStr">
+      <c r="B40" s="31" t="inlineStr">
         <is>
           <t>#01 MERCEARIA - #02 FEIJÕES E LEGUMINOSAS</t>
         </is>
       </c>
-      <c r="C40" s="26" t="inlineStr">
+      <c r="C40" s="31" t="inlineStr">
         <is>
           <t>FEIJÃO KICALDO 1KG CARIOCA</t>
         </is>
       </c>
-      <c r="D40" s="26" t="inlineStr">
+      <c r="D40" s="31" t="inlineStr">
         <is>
           <t>FEIJÃO CARIOCA KICALDO 1KG</t>
         </is>
       </c>
-      <c r="E40" s="26" t="inlineStr"/>
+      <c r="E40" s="31" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -1611,25 +1611,25 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="26" t="n">
+      <c r="A50" s="31" t="n">
         <v>165928</v>
       </c>
-      <c r="B50" s="26" t="inlineStr">
+      <c r="B50" s="31" t="inlineStr">
         <is>
           <t>#01 MERCEARIA - #02 FEIJÕES E LEGUMINOSAS</t>
         </is>
       </c>
-      <c r="C50" s="26" t="inlineStr">
+      <c r="C50" s="31" t="inlineStr">
         <is>
           <t>FEIJAO PRETO JOAOZINHO 1KG</t>
         </is>
       </c>
-      <c r="D50" s="26" t="inlineStr">
+      <c r="D50" s="31" t="inlineStr">
         <is>
           <t>FEIJÃO PRETO JOÃOZINHO 1KG</t>
         </is>
       </c>
-      <c r="E50" s="26" t="inlineStr"/>
+      <c r="E50" s="31" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -1874,25 +1874,25 @@
       <c r="E62" s="23" t="inlineStr"/>
     </row>
     <row r="63">
-      <c r="A63" s="26" t="n">
+      <c r="A63" s="31" t="n">
         <v>167128</v>
       </c>
-      <c r="B63" s="26" t="inlineStr">
+      <c r="B63" s="31" t="inlineStr">
         <is>
           <t>#01 MERCEARIA - #03 ÓLEOS E GORDURAS</t>
         </is>
       </c>
-      <c r="C63" s="26" t="inlineStr">
+      <c r="C63" s="31" t="inlineStr">
         <is>
           <t>ÓLEO SOJA REFINADO CONCORDIA 900ML</t>
         </is>
       </c>
-      <c r="D63" s="26" t="inlineStr">
+      <c r="D63" s="31" t="inlineStr">
         <is>
           <t>ÓLEO DE SOJA CONCORDIA 900ML</t>
         </is>
       </c>
-      <c r="E63" s="26" t="inlineStr"/>
+      <c r="E63" s="31" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="5" t="n">
@@ -2076,25 +2076,25 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="26" t="n">
+      <c r="A73" s="31" t="n">
         <v>345404</v>
       </c>
-      <c r="B73" s="26" t="inlineStr">
+      <c r="B73" s="31" t="inlineStr">
         <is>
           <t>#01 MERCEARIA - #04 AÇÚCAR E ADOÇANTES</t>
         </is>
       </c>
-      <c r="C73" s="26" t="inlineStr">
+      <c r="C73" s="31" t="inlineStr">
         <is>
           <t>ACUCAR ECO ACUCAR 2KG CRISTAL</t>
         </is>
       </c>
-      <c r="D73" s="26" t="inlineStr">
+      <c r="D73" s="31" t="inlineStr">
         <is>
           <t>AÇUCAR ECOÇUCAR 2KG CRISTAL</t>
         </is>
       </c>
-      <c r="E73" s="26" t="inlineStr"/>
+      <c r="E73" s="31" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -2477,25 +2477,25 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="26" t="n">
+      <c r="A93" s="31" t="n">
         <v>255232</v>
       </c>
-      <c r="B93" s="26" t="inlineStr">
+      <c r="B93" s="31" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - ACHOCOLATADOS E CAFÉ</t>
         </is>
       </c>
-      <c r="C93" s="26" t="inlineStr">
+      <c r="C93" s="31" t="inlineStr">
         <is>
           <t>ACHOC PO TODDY 750G</t>
         </is>
       </c>
-      <c r="D93" s="26" t="inlineStr">
+      <c r="D93" s="31" t="inlineStr">
         <is>
           <t>ACHOCOLATADO EM PÓ TODDY 750G</t>
         </is>
       </c>
-      <c r="E93" s="26" t="inlineStr"/>
+      <c r="E93" s="31" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -2638,46 +2638,46 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="26" t="n">
+      <c r="A101" s="31" t="n">
         <v>344310</v>
       </c>
-      <c r="B101" s="26" t="inlineStr">
+      <c r="B101" s="31" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - ACHOCOLATADOS E CAFÉ</t>
         </is>
       </c>
-      <c r="C101" s="26" t="inlineStr">
+      <c r="C101" s="31" t="inlineStr">
         <is>
           <t>CAFE MAMORE 250G TRAD TORRADO E MOIDO</t>
         </is>
       </c>
-      <c r="D101" s="26" t="inlineStr">
+      <c r="D101" s="31" t="inlineStr">
         <is>
           <t>CAFE MAMORE 250G TRADICIONAL TORRADO E MOIDO</t>
         </is>
       </c>
-      <c r="E101" s="26" t="inlineStr"/>
+      <c r="E101" s="31" t="inlineStr"/>
     </row>
     <row r="102">
-      <c r="A102" s="26" t="n">
+      <c r="A102" s="31" t="n">
         <v>101137</v>
       </c>
-      <c r="B102" s="26" t="inlineStr">
+      <c r="B102" s="31" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - ACHOCOLATADOS E CAFÉ</t>
         </is>
       </c>
-      <c r="C102" s="26" t="inlineStr">
+      <c r="C102" s="31" t="inlineStr">
         <is>
           <t>CAFÉ MARATA 250GR A VACUO TRADIC</t>
         </is>
       </c>
-      <c r="D102" s="26" t="inlineStr">
+      <c r="D102" s="31" t="inlineStr">
         <is>
           <t>CAFÉ MARATA 250G TRADICIONAL</t>
         </is>
       </c>
-      <c r="E102" s="26" t="inlineStr"/>
+      <c r="E102" s="31" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -3121,25 +3121,25 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="26" t="n">
+      <c r="A125" s="31" t="n">
         <v>110372</v>
       </c>
-      <c r="B125" s="26" t="inlineStr">
+      <c r="B125" s="31" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - BISCOITOS E SALGADINHOS</t>
         </is>
       </c>
-      <c r="C125" s="26" t="inlineStr">
+      <c r="C125" s="31" t="inlineStr">
         <is>
           <t>BISC CLUB SOCIAL 144GR ORIGINAL</t>
         </is>
       </c>
-      <c r="D125" s="26" t="inlineStr">
+      <c r="D125" s="31" t="inlineStr">
         <is>
           <t>BISCOITO CLUB SOCIAL 144G ORIGINAL</t>
         </is>
       </c>
-      <c r="E125" s="26" t="inlineStr"/>
+      <c r="E125" s="31" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -3242,25 +3242,25 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="26" t="n">
+      <c r="A131" s="31" t="n">
         <v>250013</v>
       </c>
-      <c r="B131" s="26" t="inlineStr">
+      <c r="B131" s="31" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - BISCOITOS E SALGADINHOS</t>
         </is>
       </c>
-      <c r="C131" s="26" t="inlineStr">
+      <c r="C131" s="31" t="inlineStr">
         <is>
           <t>BISC MARILAN CRACKER ESPECIAL 350GR</t>
         </is>
       </c>
-      <c r="D131" s="26" t="inlineStr">
+      <c r="D131" s="31" t="inlineStr">
         <is>
           <t>BISCOITO CREAM CRACKER MARILAN 350G ESPECIAL</t>
         </is>
       </c>
-      <c r="E131" s="26" t="inlineStr"/>
+      <c r="E131" s="31" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -4443,25 +4443,25 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="26" t="n">
+      <c r="A191" s="31" t="n">
         <v>286197</v>
       </c>
-      <c r="B191" s="26" t="inlineStr">
+      <c r="B191" s="31" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - BISCOITOS E SALGADINHOS</t>
         </is>
       </c>
-      <c r="C191" s="26" t="inlineStr">
+      <c r="C191" s="31" t="inlineStr">
         <is>
           <t>BISCOITO MABEL 600GR ROSCA COCO</t>
         </is>
       </c>
-      <c r="D191" s="26" t="inlineStr">
+      <c r="D191" s="31" t="inlineStr">
         <is>
           <t>BISCOITO ROSQUINHA MABEL 600G COCO</t>
         </is>
       </c>
-      <c r="E191" s="26" t="inlineStr"/>
+      <c r="E191" s="31" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" t="n">
@@ -5725,25 +5725,25 @@
       </c>
     </row>
     <row r="255">
-      <c r="A255" s="26" t="n">
+      <c r="A255" s="31" t="n">
         <v>341362</v>
       </c>
-      <c r="B255" s="26" t="inlineStr">
+      <c r="B255" s="31" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - CHOCOLATES E DOCES</t>
         </is>
       </c>
-      <c r="C255" s="26" t="inlineStr">
+      <c r="C255" s="31" t="inlineStr">
         <is>
           <t>BOMBONS GAROTO 220G SORTIDOS CAIXA</t>
         </is>
       </c>
-      <c r="D255" s="26" t="inlineStr">
+      <c r="D255" s="31" t="inlineStr">
         <is>
           <t>BOMBOM GAROTO CAIXA 220G SORTIDOS</t>
         </is>
       </c>
-      <c r="E255" s="26" t="inlineStr"/>
+      <c r="E255" s="31" t="inlineStr"/>
     </row>
     <row r="256">
       <c r="A256" t="n">
@@ -7488,25 +7488,25 @@
       </c>
     </row>
     <row r="343">
-      <c r="A343" s="26" t="n">
+      <c r="A343" s="31" t="n">
         <v>190801</v>
       </c>
-      <c r="B343" s="26" t="inlineStr">
+      <c r="B343" s="31" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - CONDIMENTOS E TEMPEROS</t>
         </is>
       </c>
-      <c r="C343" s="26" t="inlineStr">
+      <c r="C343" s="31" t="inlineStr">
         <is>
           <t>AZEITONAS VERDES INTEIRAS MARATA SACHET</t>
         </is>
       </c>
-      <c r="D343" s="26" t="inlineStr">
+      <c r="D343" s="31" t="inlineStr">
         <is>
           <t>AZEITONAS VERDES MARATA SACHE 210G INTEIRAS</t>
         </is>
       </c>
-      <c r="E343" s="26" t="inlineStr"/>
+      <c r="E343" s="31" t="inlineStr"/>
     </row>
     <row r="344">
       <c r="A344" t="n">
@@ -7969,25 +7969,25 @@
       </c>
     </row>
     <row r="367">
-      <c r="A367" s="26" t="n">
+      <c r="A367" s="31" t="n">
         <v>242311</v>
       </c>
-      <c r="B367" s="26" t="inlineStr">
+      <c r="B367" s="31" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - CONDIMENTOS E TEMPEROS</t>
         </is>
       </c>
-      <c r="C367" s="26" t="inlineStr">
+      <c r="C367" s="31" t="inlineStr">
         <is>
           <t>CATCHUP ARISCO TRADICIONAL 370G</t>
         </is>
       </c>
-      <c r="D367" s="26" t="inlineStr">
+      <c r="D367" s="31" t="inlineStr">
         <is>
           <t>CATCHUP ARISCO 370G TRADICIONAL</t>
         </is>
       </c>
-      <c r="E367" s="26" t="inlineStr"/>
+      <c r="E367" s="31" t="inlineStr"/>
     </row>
     <row r="368">
       <c r="A368" t="n">
@@ -8371,25 +8371,25 @@
       </c>
     </row>
     <row r="387">
-      <c r="A387" s="26" t="n">
+      <c r="A387" s="31" t="n">
         <v>100780</v>
       </c>
-      <c r="B387" s="26" t="inlineStr">
+      <c r="B387" s="31" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - CONDIMENTOS E TEMPEROS</t>
         </is>
       </c>
-      <c r="C387" s="26" t="inlineStr">
+      <c r="C387" s="31" t="inlineStr">
         <is>
           <t>EXT TOMATE OLE 190GR CP</t>
         </is>
       </c>
-      <c r="D387" s="26" t="inlineStr">
+      <c r="D387" s="31" t="inlineStr">
         <is>
           <t>EXTRATO DE TOMATE OLE COPO 190G</t>
         </is>
       </c>
-      <c r="E387" s="26" t="inlineStr"/>
+      <c r="E387" s="31" t="inlineStr"/>
     </row>
     <row r="388">
       <c r="A388" t="n">
@@ -8932,25 +8932,25 @@
       </c>
     </row>
     <row r="415">
-      <c r="A415" s="26" t="n">
+      <c r="A415" s="31" t="n">
         <v>101728</v>
       </c>
-      <c r="B415" s="26" t="inlineStr">
+      <c r="B415" s="31" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - CONDIMENTOS E TEMPEROS</t>
         </is>
       </c>
-      <c r="C415" s="26" t="inlineStr">
+      <c r="C415" s="31" t="inlineStr">
         <is>
           <t>MAIONESE HELLMANNS 500GR TRADICIONAL</t>
         </is>
       </c>
-      <c r="D415" s="26" t="inlineStr">
+      <c r="D415" s="31" t="inlineStr">
         <is>
           <t>MAIONESE HELLMANNS 500G TRADICIONAL</t>
         </is>
       </c>
-      <c r="E415" s="26" t="inlineStr"/>
+      <c r="E415" s="31" t="inlineStr"/>
     </row>
     <row r="416">
       <c r="A416" t="n">
@@ -9295,25 +9295,25 @@
       </c>
     </row>
     <row r="433">
-      <c r="A433" s="26" t="n">
+      <c r="A433" s="31" t="n">
         <v>100851</v>
       </c>
-      <c r="B433" s="26" t="inlineStr">
+      <c r="B433" s="31" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - CONDIMENTOS E TEMPEROS</t>
         </is>
       </c>
-      <c r="C433" s="26" t="inlineStr">
+      <c r="C433" s="31" t="inlineStr">
         <is>
           <t>MOLHO PIMENTA MARATA GOTA 150ML</t>
         </is>
       </c>
-      <c r="D433" s="26" t="inlineStr">
+      <c r="D433" s="31" t="inlineStr">
         <is>
           <t>MOLHO DE PIMENTA MARATA GOTA 150ML</t>
         </is>
       </c>
-      <c r="E433" s="26" t="inlineStr"/>
+      <c r="E433" s="31" t="inlineStr"/>
     </row>
     <row r="434">
       <c r="A434" t="n">
@@ -10078,25 +10078,25 @@
       </c>
     </row>
     <row r="472">
-      <c r="A472" s="26" t="n">
+      <c r="A472" s="31" t="n">
         <v>127461</v>
       </c>
-      <c r="B472" s="26" t="inlineStr">
+      <c r="B472" s="31" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - CONDIMENTOS E TEMPEROS</t>
         </is>
       </c>
-      <c r="C472" s="26" t="inlineStr">
+      <c r="C472" s="31" t="inlineStr">
         <is>
           <t>SAL P/ CHURRASCO ITA 1KG</t>
         </is>
       </c>
-      <c r="D472" s="26" t="inlineStr">
+      <c r="D472" s="31" t="inlineStr">
         <is>
           <t>SAL PARA CHURRASCO ITA 1KG</t>
         </is>
       </c>
-      <c r="E472" s="26" t="inlineStr"/>
+      <c r="E472" s="31" t="inlineStr"/>
     </row>
     <row r="473">
       <c r="A473" t="n">
@@ -10280,25 +10280,25 @@
       <c r="E481" s="23" t="inlineStr"/>
     </row>
     <row r="482">
-      <c r="A482" s="26" t="n">
+      <c r="A482" s="31" t="n">
         <v>108518</v>
       </c>
-      <c r="B482" s="26" t="inlineStr">
+      <c r="B482" s="31" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - CONDIMENTOS E TEMPEROS</t>
         </is>
       </c>
-      <c r="C482" s="26" t="inlineStr">
+      <c r="C482" s="31" t="inlineStr">
         <is>
           <t>TEMPERO ARISCO 1KG COMPLETO S/ PIMENTA</t>
         </is>
       </c>
-      <c r="D482" s="26" t="inlineStr">
+      <c r="D482" s="31" t="inlineStr">
         <is>
           <t>TEMPERO COMPLETO ARISCO COMPLETO 1KG SEM PIMENTA</t>
         </is>
       </c>
-      <c r="E482" s="26" t="inlineStr"/>
+      <c r="E482" s="31" t="inlineStr"/>
     </row>
     <row r="483">
       <c r="A483" t="n">
@@ -10641,25 +10641,25 @@
       </c>
     </row>
     <row r="500">
-      <c r="A500" s="26" t="n">
+      <c r="A500" s="31" t="n">
         <v>100884</v>
       </c>
-      <c r="B500" s="26" t="inlineStr">
+      <c r="B500" s="31" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - CONDIMENTOS E TEMPEROS</t>
         </is>
       </c>
-      <c r="C500" s="26" t="inlineStr">
+      <c r="C500" s="31" t="inlineStr">
         <is>
           <t>TEMPERO SAZON 60GR SCH CARNES/VERMELHO</t>
         </is>
       </c>
-      <c r="D500" s="26" t="inlineStr">
+      <c r="D500" s="31" t="inlineStr">
         <is>
           <t>TEMPERO EM PÓ SAZON SACHÊ 60G CARNES/VERMELHO</t>
         </is>
       </c>
-      <c r="E500" s="26" t="inlineStr"/>
+      <c r="E500" s="31" t="inlineStr"/>
     </row>
     <row r="501">
       <c r="A501" t="n">
@@ -11102,25 +11102,25 @@
       </c>
     </row>
     <row r="523">
-      <c r="A523" s="26" t="n">
+      <c r="A523" s="31" t="n">
         <v>106961</v>
       </c>
-      <c r="B523" s="26" t="inlineStr">
+      <c r="B523" s="31" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - CONDIMENTOS E TEMPEROS</t>
         </is>
       </c>
-      <c r="C523" s="26" t="inlineStr">
+      <c r="C523" s="31" t="inlineStr">
         <is>
           <t>VINAGRE CASTELO 750ML ALCOOL</t>
         </is>
       </c>
-      <c r="D523" s="26" t="inlineStr">
+      <c r="D523" s="31" t="inlineStr">
         <is>
           <t>VINAGRE CASTELO 750ML ALCOOL</t>
         </is>
       </c>
-      <c r="E523" s="26" t="inlineStr"/>
+      <c r="E523" s="31" t="inlineStr"/>
     </row>
     <row r="524">
       <c r="A524" t="n">
@@ -11425,25 +11425,25 @@
       </c>
     </row>
     <row r="539">
-      <c r="A539" s="26" t="n">
+      <c r="A539" s="30" t="n">
         <v>193650</v>
       </c>
-      <c r="B539" s="26" t="inlineStr">
+      <c r="B539" s="30" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - CONGELADOS - BATATAS</t>
         </is>
       </c>
-      <c r="C539" s="26" t="inlineStr">
+      <c r="C539" s="30" t="inlineStr">
         <is>
           <t>BATATAS PRE-FRITAS CONG BOUA 400GR</t>
         </is>
       </c>
-      <c r="D539" s="26" t="inlineStr">
+      <c r="D539" s="30" t="inlineStr">
         <is>
           <t>BATATAS CONGELADAS BOUA PCT 400G PRE-FRITAS</t>
         </is>
       </c>
-      <c r="E539" s="26" t="inlineStr"/>
+      <c r="E539" s="30" t="inlineStr"/>
     </row>
     <row r="540">
       <c r="A540" t="n">
@@ -12546,25 +12546,25 @@
       </c>
     </row>
     <row r="595">
-      <c r="A595" s="26" t="n">
+      <c r="A595" s="31" t="n">
         <v>221945</v>
       </c>
-      <c r="B595" s="26" t="inlineStr">
+      <c r="B595" s="31" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - CONSERVAS - HORTIFRUTI</t>
         </is>
       </c>
-      <c r="C595" s="26" t="inlineStr">
+      <c r="C595" s="31" t="inlineStr">
         <is>
           <t>MILHO VERDE LATA 170G PREDILECTA</t>
         </is>
       </c>
-      <c r="D595" s="26" t="inlineStr">
+      <c r="D595" s="31" t="inlineStr">
         <is>
           <t>MILHO VERDE PREDILECTA LATA 170G</t>
         </is>
       </c>
-      <c r="E595" s="26" t="inlineStr"/>
+      <c r="E595" s="31" t="inlineStr"/>
     </row>
     <row r="596">
       <c r="A596" t="n">
@@ -13287,25 +13287,25 @@
       </c>
     </row>
     <row r="632">
-      <c r="A632" s="26" t="n">
+      <c r="A632" s="31" t="n">
         <v>100705</v>
       </c>
-      <c r="B632" s="26" t="inlineStr">
+      <c r="B632" s="31" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - CONSERVAS - SARDINHAS</t>
         </is>
       </c>
-      <c r="C632" s="26" t="inlineStr">
+      <c r="C632" s="31" t="inlineStr">
         <is>
           <t>SARDINHA GOMES DA COSTA 125GR TOMATE</t>
         </is>
       </c>
-      <c r="D632" s="26" t="inlineStr">
+      <c r="D632" s="31" t="inlineStr">
         <is>
           <t>SARDINHA GOMES DA COSTA 125G TOMATE</t>
         </is>
       </c>
-      <c r="E632" s="26" t="inlineStr"/>
+      <c r="E632" s="31" t="inlineStr"/>
     </row>
     <row r="633">
       <c r="A633" t="n">
@@ -13709,25 +13709,25 @@
       <c r="E652" s="17" t="inlineStr"/>
     </row>
     <row r="653">
-      <c r="A653" s="26" t="n">
+      <c r="A653" s="31" t="n">
         <v>112978</v>
       </c>
-      <c r="B653" s="26" t="inlineStr">
+      <c r="B653" s="31" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - FARINHAS E DERIVADOS</t>
         </is>
       </c>
-      <c r="C653" s="26" t="inlineStr">
+      <c r="C653" s="31" t="inlineStr">
         <is>
           <t>CUSCUZ DE MILHO SINHA 500GR</t>
         </is>
       </c>
-      <c r="D653" s="26" t="inlineStr">
+      <c r="D653" s="31" t="inlineStr">
         <is>
           <t>CUSCUZ DE MILHO SINHA 500G</t>
         </is>
       </c>
-      <c r="E653" s="26" t="inlineStr"/>
+      <c r="E653" s="31" t="inlineStr"/>
     </row>
     <row r="654">
       <c r="A654" t="n">
@@ -13750,25 +13750,25 @@
       </c>
     </row>
     <row r="655">
-      <c r="A655" s="26" t="n">
+      <c r="A655" s="31" t="n">
         <v>128930</v>
       </c>
-      <c r="B655" s="26" t="inlineStr">
+      <c r="B655" s="31" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - FARINHAS E DERIVADOS</t>
         </is>
       </c>
-      <c r="C655" s="26" t="inlineStr">
+      <c r="C655" s="31" t="inlineStr">
         <is>
           <t>FARINHA MANDIOCA AMAFIL AMARELA OURO 1KG</t>
         </is>
       </c>
-      <c r="D655" s="26" t="inlineStr">
+      <c r="D655" s="31" t="inlineStr">
         <is>
           <t>FARINHA DE MANDIOCA AMAFIL 1KG AMARELA OURO</t>
         </is>
       </c>
-      <c r="E655" s="26" t="inlineStr"/>
+      <c r="E655" s="31" t="inlineStr"/>
     </row>
     <row r="656">
       <c r="A656" s="17" t="n">
@@ -13792,25 +13792,25 @@
       <c r="E656" s="17" t="inlineStr"/>
     </row>
     <row r="657">
-      <c r="A657" s="26" t="n">
+      <c r="A657" s="31" t="n">
         <v>118874</v>
       </c>
-      <c r="B657" s="26" t="inlineStr">
+      <c r="B657" s="31" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - FARINHAS E DERIVADOS</t>
         </is>
       </c>
-      <c r="C657" s="26" t="inlineStr">
+      <c r="C657" s="31" t="inlineStr">
         <is>
           <t>FARINHA MANDIOCA BIJU AMAFIL 500GR TORRA</t>
         </is>
       </c>
-      <c r="D657" s="26" t="inlineStr">
+      <c r="D657" s="31" t="inlineStr">
         <is>
           <t>FARINHA DE MANDIOCA BIJU AMAFIL 500G TORRADA</t>
         </is>
       </c>
-      <c r="E657" s="26" t="inlineStr"/>
+      <c r="E657" s="31" t="inlineStr"/>
     </row>
     <row r="658">
       <c r="A658" t="n">
@@ -14273,25 +14273,25 @@
       </c>
     </row>
     <row r="681">
-      <c r="A681" s="26" t="n">
+      <c r="A681" s="31" t="n">
         <v>100024</v>
       </c>
-      <c r="B681" s="26" t="inlineStr">
+      <c r="B681" s="31" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - FARINHAS E DERIVADOS</t>
         </is>
       </c>
-      <c r="C681" s="26" t="inlineStr">
+      <c r="C681" s="31" t="inlineStr">
         <is>
           <t>FARINHA TRIGO DONA BENTA 1KG SEM FERMENT</t>
         </is>
       </c>
-      <c r="D681" s="26" t="inlineStr">
+      <c r="D681" s="31" t="inlineStr">
         <is>
           <t>FARINHA DE TRIGO DONA BENTA 1KG SEM FERMENTO</t>
         </is>
       </c>
-      <c r="E681" s="26" t="inlineStr"/>
+      <c r="E681" s="31" t="inlineStr"/>
     </row>
     <row r="682">
       <c r="A682" t="n">
@@ -14415,25 +14415,25 @@
       </c>
     </row>
     <row r="688">
-      <c r="A688" s="26" t="n">
+      <c r="A688" s="31" t="n">
         <v>100027</v>
       </c>
-      <c r="B688" s="26" t="inlineStr">
+      <c r="B688" s="31" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - FARINHAS E DERIVADOS</t>
         </is>
       </c>
-      <c r="C688" s="26" t="inlineStr">
+      <c r="C688" s="31" t="inlineStr">
         <is>
           <t>FARINHA TRIGO ORQUIDEA 1KG SEM FERMENTO</t>
         </is>
       </c>
-      <c r="D688" s="26" t="inlineStr">
+      <c r="D688" s="31" t="inlineStr">
         <is>
           <t>FARINHA DE TRIGO ORQUIDEA 1KG SEM FERMENTO</t>
         </is>
       </c>
-      <c r="E688" s="26" t="inlineStr"/>
+      <c r="E688" s="31" t="inlineStr"/>
     </row>
     <row r="689">
       <c r="A689" s="14" t="n">
@@ -14978,25 +14978,25 @@
       </c>
     </row>
     <row r="716">
-      <c r="A716" s="26" t="n">
+      <c r="A716" s="31" t="n">
         <v>320648</v>
       </c>
-      <c r="B716" s="26" t="inlineStr">
+      <c r="B716" s="31" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - FARINHAS E DERIVADOS</t>
         </is>
       </c>
-      <c r="C716" s="26" t="inlineStr">
+      <c r="C716" s="31" t="inlineStr">
         <is>
           <t>FLOCAO DE ARROZ 500GR URBANO</t>
         </is>
       </c>
-      <c r="D716" s="26" t="inlineStr">
+      <c r="D716" s="31" t="inlineStr">
         <is>
           <t>FLOCÃO DE ARROZ URBANO 500G</t>
         </is>
       </c>
-      <c r="E716" s="26" t="inlineStr"/>
+      <c r="E716" s="31" t="inlineStr"/>
     </row>
     <row r="717">
       <c r="A717" t="n">
@@ -15200,25 +15200,25 @@
       </c>
     </row>
     <row r="727">
-      <c r="A727" s="26" t="n">
+      <c r="A727" s="31" t="n">
         <v>294706</v>
       </c>
-      <c r="B727" s="26" t="inlineStr">
+      <c r="B727" s="31" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - FARINHAS E DERIVADOS</t>
         </is>
       </c>
-      <c r="C727" s="26" t="inlineStr">
+      <c r="C727" s="31" t="inlineStr">
         <is>
           <t>FLOCAO DE MILHO JALAPAO 400G</t>
         </is>
       </c>
-      <c r="D727" s="26" t="inlineStr">
+      <c r="D727" s="31" t="inlineStr">
         <is>
           <t>FLOCÃO DE MILHO JALAPÃO 400G</t>
         </is>
       </c>
-      <c r="E727" s="26" t="inlineStr"/>
+      <c r="E727" s="31" t="inlineStr"/>
     </row>
     <row r="728">
       <c r="A728" t="n">
@@ -15441,25 +15441,25 @@
       </c>
     </row>
     <row r="739">
-      <c r="A739" s="30" t="n">
+      <c r="A739" s="28" t="n">
         <v>149122</v>
       </c>
-      <c r="B739" s="30" t="inlineStr">
+      <c r="B739" s="28" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - FARINHAS E DERIVADOS</t>
         </is>
       </c>
-      <c r="C739" s="30" t="inlineStr">
+      <c r="C739" s="28" t="inlineStr">
         <is>
           <t>MASSA P/ TAPIOCA AMAFIL 1KG</t>
         </is>
       </c>
-      <c r="D739" s="30" t="inlineStr">
+      <c r="D739" s="28" t="inlineStr">
         <is>
           <t>MASSA PARA TAPIOCA AMAFIL 1KG</t>
         </is>
       </c>
-      <c r="E739" s="30" t="inlineStr"/>
+      <c r="E739" s="28" t="inlineStr"/>
     </row>
     <row r="740">
       <c r="A740" s="10" t="n">
@@ -15905,25 +15905,25 @@
       </c>
     </row>
     <row r="762">
-      <c r="A762" s="26" t="n">
+      <c r="A762" s="31" t="n">
         <v>225440</v>
       </c>
-      <c r="B762" s="26" t="inlineStr">
+      <c r="B762" s="31" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - FARINHAS E DERIVADOS</t>
         </is>
       </c>
-      <c r="C762" s="26" t="inlineStr">
+      <c r="C762" s="31" t="inlineStr">
         <is>
           <t>MIST BOLO FLEISCHMANN CHOCOLATE 390G</t>
         </is>
       </c>
-      <c r="D762" s="26" t="inlineStr">
+      <c r="D762" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">MISTURA PARA BOLOS FLEISCHMANN 390G CHOCOLATE </t>
         </is>
       </c>
-      <c r="E762" s="26" t="inlineStr"/>
+      <c r="E762" s="31" t="inlineStr"/>
     </row>
     <row r="763">
       <c r="A763" t="n">
@@ -17049,25 +17049,25 @@
       </c>
     </row>
     <row r="819">
-      <c r="A819" s="26" t="n">
+      <c r="A819" s="30" t="n">
         <v>276943</v>
       </c>
-      <c r="B819" s="26" t="inlineStr">
+      <c r="B819" s="30" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - GORDURAS E MARGARINAS</t>
         </is>
       </c>
-      <c r="C819" s="26" t="inlineStr">
+      <c r="C819" s="30" t="inlineStr">
         <is>
           <t>MARGARINA DELICIA 1KG C CREME DE LEITE</t>
         </is>
       </c>
-      <c r="D819" s="26" t="inlineStr">
+      <c r="D819" s="30" t="inlineStr">
         <is>
           <t>MARGARINA DELICIA 1KG COM CREME DE LEITE</t>
         </is>
       </c>
-      <c r="E819" s="26" t="inlineStr"/>
+      <c r="E819" s="30" t="inlineStr"/>
     </row>
     <row r="820">
       <c r="A820" t="n">
@@ -18212,25 +18212,25 @@
       </c>
     </row>
     <row r="877">
-      <c r="A877" s="26" t="n">
+      <c r="A877" s="31" t="n">
         <v>101874</v>
       </c>
-      <c r="B877" s="26" t="inlineStr">
+      <c r="B877" s="31" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - LATICÍNIOS - BEBIDAS LACTEAS</t>
         </is>
       </c>
-      <c r="C877" s="26" t="inlineStr">
+      <c r="C877" s="31" t="inlineStr">
         <is>
           <t>ACHOC LIQ TODDYNHO 200ML CHOCOLATE</t>
         </is>
       </c>
-      <c r="D877" s="26" t="inlineStr">
+      <c r="D877" s="31" t="inlineStr">
         <is>
           <t>TODDYNHO 200ML CHOCOLATE</t>
         </is>
       </c>
-      <c r="E877" s="26" t="inlineStr"/>
+      <c r="E877" s="31" t="inlineStr"/>
     </row>
     <row r="878">
       <c r="A878" t="n">
@@ -18414,25 +18414,25 @@
       </c>
     </row>
     <row r="887">
-      <c r="A887" s="26" t="n">
+      <c r="A887" s="31" t="n">
         <v>193295</v>
       </c>
-      <c r="B887" s="26" t="inlineStr">
+      <c r="B887" s="31" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - LATICÍNIOS - DERIVADOS LACTEOS</t>
         </is>
       </c>
-      <c r="C887" s="26" t="inlineStr">
+      <c r="C887" s="31" t="inlineStr">
         <is>
           <t>CREME DE LEITE TRIANGULO 200GR 10%GORDUR</t>
         </is>
       </c>
-      <c r="D887" s="26" t="inlineStr">
+      <c r="D887" s="31" t="inlineStr">
         <is>
           <t>CREME DE LEITE TRIANGULO 200G 10% GORDURA</t>
         </is>
       </c>
-      <c r="E887" s="26" t="inlineStr"/>
+      <c r="E887" s="31" t="inlineStr"/>
     </row>
     <row r="888">
       <c r="A888" t="n">
@@ -18656,25 +18656,25 @@
       </c>
     </row>
     <row r="899">
-      <c r="A899" s="26" t="n">
+      <c r="A899" s="31" t="n">
         <v>101083</v>
       </c>
-      <c r="B899" s="26" t="inlineStr">
+      <c r="B899" s="31" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - LATICÍNIOS - DERIVADOS LACTEOS</t>
         </is>
       </c>
-      <c r="C899" s="26" t="inlineStr">
+      <c r="C899" s="31" t="inlineStr">
         <is>
           <t>LEITE CONDENSADO PIRACANJUBA 395GR TP</t>
         </is>
       </c>
-      <c r="D899" s="26" t="inlineStr">
+      <c r="D899" s="31" t="inlineStr">
         <is>
           <t>LEITE CONDENSADO PIRACANJUBA 395G</t>
         </is>
       </c>
-      <c r="E899" s="26" t="inlineStr"/>
+      <c r="E899" s="31" t="inlineStr"/>
     </row>
     <row r="900">
       <c r="A900" s="10" t="n">
@@ -19078,25 +19078,25 @@
       </c>
     </row>
     <row r="920">
-      <c r="A920" s="26" t="n">
+      <c r="A920" s="31" t="n">
         <v>101113</v>
       </c>
-      <c r="B920" s="26" t="inlineStr">
+      <c r="B920" s="31" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - LATICÍNIOS - LEITE</t>
         </is>
       </c>
-      <c r="C920" s="26" t="inlineStr">
+      <c r="C920" s="31" t="inlineStr">
         <is>
           <t>LEITE PIRACANJUBA UHT 1L INTEGRAL</t>
         </is>
       </c>
-      <c r="D920" s="26" t="inlineStr">
+      <c r="D920" s="31" t="inlineStr">
         <is>
           <t>LEITE LONGA VIDA PIRACANJUBA 1L INTEGRAL</t>
         </is>
       </c>
-      <c r="E920" s="26" t="inlineStr"/>
+      <c r="E920" s="31" t="inlineStr"/>
     </row>
     <row r="921">
       <c r="A921" s="14" t="n">
@@ -19180,25 +19180,25 @@
       </c>
     </row>
     <row r="925">
-      <c r="A925" s="26" t="n">
+      <c r="A925" s="31" t="n">
         <v>106922</v>
       </c>
-      <c r="B925" s="26" t="inlineStr">
+      <c r="B925" s="31" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - LATICÍNIOS - LEITE EM PÓ</t>
         </is>
       </c>
-      <c r="C925" s="26" t="inlineStr">
+      <c r="C925" s="31" t="inlineStr">
         <is>
           <t>LEITE EM PO CCGL 1KG INTEGRAL</t>
         </is>
       </c>
-      <c r="D925" s="26" t="inlineStr">
+      <c r="D925" s="31" t="inlineStr">
         <is>
           <t>LEITE EM PÓ CCGL 1KG INTEGRAL</t>
         </is>
       </c>
-      <c r="E925" s="26" t="inlineStr"/>
+      <c r="E925" s="31" t="inlineStr"/>
     </row>
     <row r="926">
       <c r="A926" t="n">
@@ -19661,25 +19661,25 @@
       </c>
     </row>
     <row r="949">
-      <c r="A949" s="26" t="n">
+      <c r="A949" s="30" t="n">
         <v>158733</v>
       </c>
-      <c r="B949" s="26" t="inlineStr">
+      <c r="B949" s="30" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - LATICÍNIOS - QUEIJO</t>
         </is>
       </c>
-      <c r="C949" s="26" t="inlineStr">
+      <c r="C949" s="30" t="inlineStr">
         <is>
           <t>QUEIJO MUSSARELA PIRAC FATIADO 150GR</t>
         </is>
       </c>
-      <c r="D949" s="26" t="inlineStr">
+      <c r="D949" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">QUEIJO MUSSARELA PIRACANJUBA 150G FATIADO </t>
         </is>
       </c>
-      <c r="E949" s="26" t="inlineStr"/>
+      <c r="E949" s="30" t="inlineStr"/>
     </row>
     <row r="950">
       <c r="A950" t="n">
@@ -20122,25 +20122,25 @@
       </c>
     </row>
     <row r="972">
-      <c r="A972" s="26" t="n">
+      <c r="A972" s="30" t="n">
         <v>104770</v>
       </c>
-      <c r="B972" s="26" t="inlineStr">
+      <c r="B972" s="30" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - LATICÍNIOS - QUEIJO</t>
         </is>
       </c>
-      <c r="C972" s="26" t="inlineStr">
+      <c r="C972" s="30" t="inlineStr">
         <is>
           <t>REQUEIJAO CREM TIROLEZ 200GR</t>
         </is>
       </c>
-      <c r="D972" s="26" t="inlineStr">
+      <c r="D972" s="30" t="inlineStr">
         <is>
           <t>REQUEIJAO CREMOSO TIROLEZ 200G</t>
         </is>
       </c>
-      <c r="E972" s="26" t="inlineStr"/>
+      <c r="E972" s="30" t="inlineStr"/>
     </row>
     <row r="973">
       <c r="A973" s="11" t="n">
@@ -20403,25 +20403,25 @@
       </c>
     </row>
     <row r="986">
-      <c r="A986" s="26" t="n">
+      <c r="A986" s="31" t="n">
         <v>290255</v>
       </c>
-      <c r="B986" s="26" t="inlineStr">
+      <c r="B986" s="31" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - MASSAS</t>
         </is>
       </c>
-      <c r="C986" s="26" t="inlineStr">
+      <c r="C986" s="31" t="inlineStr">
         <is>
           <t>MACARRÃO CRISTAL 500GR SEMOLA ESPAGUETE</t>
         </is>
       </c>
-      <c r="D986" s="26" t="inlineStr">
+      <c r="D986" s="31" t="inlineStr">
         <is>
           <t>MACARRÃO CRISTAL SEMOLA ESPAGUETE 500G</t>
         </is>
       </c>
-      <c r="E986" s="26" t="inlineStr"/>
+      <c r="E986" s="31" t="inlineStr"/>
     </row>
     <row r="987">
       <c r="A987" t="n">
@@ -20464,25 +20464,25 @@
       </c>
     </row>
     <row r="989">
-      <c r="A989" s="26" t="n">
+      <c r="A989" s="31" t="n">
         <v>108415</v>
       </c>
-      <c r="B989" s="26" t="inlineStr">
+      <c r="B989" s="31" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - MASSAS</t>
         </is>
       </c>
-      <c r="C989" s="26" t="inlineStr">
+      <c r="C989" s="31" t="inlineStr">
         <is>
           <t>MAC CRISTAL 500G SEMOLA PARAFUSO</t>
         </is>
       </c>
-      <c r="D989" s="26" t="inlineStr">
+      <c r="D989" s="31" t="inlineStr">
         <is>
           <t>MACARRÃO CRISTAL SEMOLA PARAFUSO 500G</t>
         </is>
       </c>
-      <c r="E989" s="26" t="inlineStr"/>
+      <c r="E989" s="31" t="inlineStr"/>
     </row>
     <row r="990">
       <c r="A990" t="n">
@@ -20646,25 +20646,25 @@
       </c>
     </row>
     <row r="998">
-      <c r="A998" s="26" t="n">
+      <c r="A998" s="31" t="n">
         <v>163423</v>
       </c>
-      <c r="B998" s="26" t="inlineStr">
+      <c r="B998" s="31" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - MASSAS</t>
         </is>
       </c>
-      <c r="C998" s="26" t="inlineStr">
+      <c r="C998" s="31" t="inlineStr">
         <is>
           <t>MAC. GALO INTEGRAL 500GR PARAFUSO 2</t>
         </is>
       </c>
-      <c r="D998" s="26" t="inlineStr">
+      <c r="D998" s="31" t="inlineStr">
         <is>
           <t>MACARRÃO GALO INTEGRAL 500G PARAFUSO</t>
         </is>
       </c>
-      <c r="E998" s="26" t="inlineStr"/>
+      <c r="E998" s="31" t="inlineStr"/>
     </row>
     <row r="999">
       <c r="A999" t="n">
@@ -21388,25 +21388,25 @@
       </c>
     </row>
     <row r="1035">
-      <c r="A1035" s="26" t="n">
+      <c r="A1035" s="31" t="n">
         <v>100632</v>
       </c>
-      <c r="B1035" s="26" t="inlineStr">
+      <c r="B1035" s="31" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - MASSAS</t>
         </is>
       </c>
-      <c r="C1035" s="26" t="inlineStr">
+      <c r="C1035" s="31" t="inlineStr">
         <is>
           <t>MASSA LASANHA FORTALEZA SEMOLA 500G</t>
         </is>
       </c>
-      <c r="D1035" s="26" t="inlineStr">
+      <c r="D1035" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">MASSA PARA LASANHA FORTALEZA 500G SEMOLA </t>
         </is>
       </c>
-      <c r="E1035" s="26" t="inlineStr"/>
+      <c r="E1035" s="31" t="inlineStr"/>
     </row>
     <row r="1036">
       <c r="A1036" t="n">
@@ -24899,25 +24899,25 @@
       <c r="E1209" s="20" t="inlineStr"/>
     </row>
     <row r="1210">
-      <c r="A1210" s="26" t="n">
+      <c r="A1210" s="30" t="n">
         <v>108785</v>
       </c>
-      <c r="B1210" s="26" t="inlineStr">
+      <c r="B1210" s="30" t="inlineStr">
         <is>
           <t>#03 AÇOUGUE - #01 AVES</t>
         </is>
       </c>
-      <c r="C1210" s="26" t="inlineStr">
+      <c r="C1210" s="30" t="inlineStr">
         <is>
           <t>COXINHA DA ASA SADIA 1KG PACOTE DRUMETTE</t>
         </is>
       </c>
-      <c r="D1210" s="26" t="inlineStr">
+      <c r="D1210" s="30" t="inlineStr">
         <is>
           <t>COXINHA DA ASA DE FRANGO SADIA PCT 1KG DRUMETE</t>
         </is>
       </c>
-      <c r="E1210" s="26" t="inlineStr"/>
+      <c r="E1210" s="30" t="inlineStr"/>
     </row>
     <row r="1211">
       <c r="A1211" t="n">
@@ -25262,25 +25262,25 @@
       </c>
     </row>
     <row r="1228">
-      <c r="A1228" s="26" t="n">
+      <c r="A1228" s="30" t="n">
         <v>108856</v>
       </c>
-      <c r="B1228" s="26" t="inlineStr">
+      <c r="B1228" s="30" t="inlineStr">
         <is>
           <t>#03 AÇOUGUE - #01 AVES</t>
         </is>
       </c>
-      <c r="C1228" s="26" t="inlineStr">
+      <c r="C1228" s="30" t="inlineStr">
         <is>
           <t>FILE PEITO SADIA PCT S/OPC 1KG PFFZP</t>
         </is>
       </c>
-      <c r="D1228" s="26" t="inlineStr">
+      <c r="D1228" s="30" t="inlineStr">
         <is>
           <t>FILE PEITO DE FRANGO SADIA PCT 1KG</t>
         </is>
       </c>
-      <c r="E1228" s="26" t="inlineStr"/>
+      <c r="E1228" s="30" t="inlineStr"/>
     </row>
     <row r="1229">
       <c r="A1229" t="n">
@@ -25464,25 +25464,25 @@
       </c>
     </row>
     <row r="1238">
-      <c r="A1238" s="26" t="n">
+      <c r="A1238" s="30" t="n">
         <v>298984</v>
       </c>
-      <c r="B1238" s="26" t="inlineStr">
+      <c r="B1238" s="30" t="inlineStr">
         <is>
           <t>#03 AÇOUGUE - #01 AVES</t>
         </is>
       </c>
-      <c r="C1238" s="26" t="inlineStr">
+      <c r="C1238" s="30" t="inlineStr">
         <is>
           <t>FRANGO DE PADARIA SEARA 1KG A PASSARINHO</t>
         </is>
       </c>
-      <c r="D1238" s="26" t="inlineStr">
+      <c r="D1238" s="30" t="inlineStr">
         <is>
           <t>FRANGO DE PADARIA SEARA 1KG A PASSARINHO</t>
         </is>
       </c>
-      <c r="E1238" s="26" t="inlineStr"/>
+      <c r="E1238" s="30" t="inlineStr"/>
     </row>
     <row r="1239">
       <c r="A1239" t="n">
@@ -26030,46 +26030,46 @@
       <c r="E1265" s="20" t="inlineStr"/>
     </row>
     <row r="1266">
-      <c r="A1266" s="31" t="n">
+      <c r="A1266" s="30" t="n">
         <v>157014</v>
       </c>
-      <c r="B1266" s="31" t="inlineStr">
+      <c r="B1266" s="30" t="inlineStr">
         <is>
           <t>#03 AÇOUGUE - #02 BOVINA</t>
         </is>
       </c>
-      <c r="C1266" s="31" t="inlineStr">
+      <c r="C1266" s="30" t="inlineStr">
         <is>
           <t>BOVINO - ACEM C/ OSSO KG</t>
         </is>
       </c>
-      <c r="D1266" s="31" t="inlineStr">
+      <c r="D1266" s="30" t="inlineStr">
         <is>
           <t>ACEM BOVINO COM OSSO KG</t>
         </is>
       </c>
-      <c r="E1266" s="31" t="inlineStr"/>
+      <c r="E1266" s="30" t="inlineStr"/>
     </row>
     <row r="1267">
-      <c r="A1267" s="32" t="n">
+      <c r="A1267" s="30" t="n">
         <v>105470</v>
       </c>
-      <c r="B1267" s="32" t="inlineStr">
+      <c r="B1267" s="30" t="inlineStr">
         <is>
           <t>#03 AÇOUGUE - #02 BOVINA</t>
         </is>
       </c>
-      <c r="C1267" s="32" t="inlineStr">
+      <c r="C1267" s="30" t="inlineStr">
         <is>
           <t>BOVINO - ACEM KG</t>
         </is>
       </c>
-      <c r="D1267" s="32" t="inlineStr">
+      <c r="D1267" s="30" t="inlineStr">
         <is>
           <t>ACEM BOVINO KG</t>
         </is>
       </c>
-      <c r="E1267" s="32" t="inlineStr"/>
+      <c r="E1267" s="30" t="inlineStr"/>
     </row>
     <row r="1268">
       <c r="A1268" t="n">
@@ -26276,25 +26276,25 @@
       </c>
     </row>
     <row r="1278">
-      <c r="A1278" s="33" t="n">
+      <c r="A1278" s="30" t="n">
         <v>322584</v>
       </c>
-      <c r="B1278" s="33" t="inlineStr">
+      <c r="B1278" s="30" t="inlineStr">
         <is>
           <t>#03 AÇOUGUE - #02 BOVINA</t>
         </is>
       </c>
-      <c r="C1278" s="33" t="inlineStr">
+      <c r="C1278" s="30" t="inlineStr">
         <is>
           <t>CARNE DE SOL KG PRIMEIRA</t>
         </is>
       </c>
-      <c r="D1278" s="33" t="inlineStr">
+      <c r="D1278" s="30" t="inlineStr">
         <is>
           <t>CARNE DE SOL KG PRIMEIRA</t>
         </is>
       </c>
-      <c r="E1278" s="33" t="inlineStr"/>
+      <c r="E1278" s="30" t="inlineStr"/>
     </row>
     <row r="1279">
       <c r="A1279" t="n">
@@ -26504,25 +26504,25 @@
       <c r="E1288" s="26" t="inlineStr"/>
     </row>
     <row r="1289">
-      <c r="A1289" s="31" t="n">
+      <c r="A1289" s="30" t="n">
         <v>105435</v>
       </c>
-      <c r="B1289" s="31" t="inlineStr">
+      <c r="B1289" s="30" t="inlineStr">
         <is>
           <t>#03 AÇOUGUE - #02 BOVINA</t>
         </is>
       </c>
-      <c r="C1289" s="31" t="inlineStr">
+      <c r="C1289" s="30" t="inlineStr">
         <is>
           <t>BOVINO - COXAO MOLE KG</t>
         </is>
       </c>
-      <c r="D1289" s="31" t="inlineStr">
+      <c r="D1289" s="30" t="inlineStr">
         <is>
           <t>COXÃO MOLE KG</t>
         </is>
       </c>
-      <c r="E1289" s="31" t="inlineStr"/>
+      <c r="E1289" s="30" t="inlineStr"/>
     </row>
     <row r="1290">
       <c r="A1290" t="n">
@@ -26585,25 +26585,25 @@
       </c>
     </row>
     <row r="1293">
-      <c r="A1293" s="29" t="n">
+      <c r="A1293" s="30" t="n">
         <v>106065</v>
       </c>
-      <c r="B1293" s="29" t="inlineStr">
+      <c r="B1293" s="30" t="inlineStr">
         <is>
           <t>#03 AÇOUGUE - #02 BOVINA</t>
         </is>
       </c>
-      <c r="C1293" s="29" t="inlineStr">
+      <c r="C1293" s="30" t="inlineStr">
         <is>
           <t>BOVINO - FIGADO KG.</t>
         </is>
       </c>
-      <c r="D1293" s="29" t="inlineStr">
+      <c r="D1293" s="30" t="inlineStr">
         <is>
           <t>FIGADO BOVINO KG</t>
         </is>
       </c>
-      <c r="E1293" s="29" t="inlineStr"/>
+      <c r="E1293" s="30" t="inlineStr"/>
     </row>
     <row r="1294">
       <c r="A1294" t="n">
@@ -26688,25 +26688,25 @@
       <c r="E1297" s="21" t="inlineStr"/>
     </row>
     <row r="1298">
-      <c r="A1298" s="31" t="n">
+      <c r="A1298" s="30" t="n">
         <v>107260</v>
       </c>
-      <c r="B1298" s="31" t="inlineStr">
+      <c r="B1298" s="30" t="inlineStr">
         <is>
           <t>#03 AÇOUGUE - #02 BOVINA</t>
         </is>
       </c>
-      <c r="C1298" s="31" t="inlineStr">
+      <c r="C1298" s="30" t="inlineStr">
         <is>
           <t>BOVINO - MACA DO PEITO KG</t>
         </is>
       </c>
-      <c r="D1298" s="31" t="inlineStr">
+      <c r="D1298" s="30" t="inlineStr">
         <is>
           <t>MAÇÃ DO PEITO KG</t>
         </is>
       </c>
-      <c r="E1298" s="31" t="inlineStr"/>
+      <c r="E1298" s="30" t="inlineStr"/>
     </row>
     <row r="1299">
       <c r="A1299" t="n">
@@ -26931,25 +26931,25 @@
       </c>
     </row>
     <row r="1310">
-      <c r="A1310" s="29" t="n">
+      <c r="A1310" s="30" t="n">
         <v>298422</v>
       </c>
-      <c r="B1310" s="29" t="inlineStr">
+      <c r="B1310" s="30" t="inlineStr">
         <is>
           <t>#03 AÇOUGUE - #03 SUÍNA</t>
         </is>
       </c>
-      <c r="C1310" s="29" t="inlineStr">
+      <c r="C1310" s="30" t="inlineStr">
         <is>
           <t>SUINO - CAIPIRA KG</t>
         </is>
       </c>
-      <c r="D1310" s="29" t="inlineStr">
+      <c r="D1310" s="30" t="inlineStr">
         <is>
           <t>SUINO CAIPIRA KG</t>
         </is>
       </c>
-      <c r="E1310" s="29" t="inlineStr"/>
+      <c r="E1310" s="30" t="inlineStr"/>
     </row>
     <row r="1311">
       <c r="A1311" t="n">
@@ -26993,25 +26993,25 @@
       <c r="E1312" s="21" t="inlineStr"/>
     </row>
     <row r="1313">
-      <c r="A1313" s="31" t="n">
+      <c r="A1313" s="30" t="n">
         <v>105062</v>
       </c>
-      <c r="B1313" s="31" t="inlineStr">
+      <c r="B1313" s="30" t="inlineStr">
         <is>
           <t>#03 AÇOUGUE - #03 SUÍNA</t>
         </is>
       </c>
-      <c r="C1313" s="31" t="inlineStr">
+      <c r="C1313" s="30" t="inlineStr">
         <is>
           <t>SUINO - BISTECA PERNIL FRESCA KG</t>
         </is>
       </c>
-      <c r="D1313" s="31" t="inlineStr">
+      <c r="D1313" s="30" t="inlineStr">
         <is>
           <t>BISTECA SUINA DO PERNIL KG</t>
         </is>
       </c>
-      <c r="E1313" s="31" t="inlineStr"/>
+      <c r="E1313" s="30" t="inlineStr"/>
     </row>
     <row r="1314">
       <c r="A1314" t="n">
@@ -28124,25 +28124,25 @@
       </c>
     </row>
     <row r="1369">
-      <c r="A1369" s="26" t="n">
+      <c r="A1369" s="30" t="n">
         <v>272009</v>
       </c>
-      <c r="B1369" s="26" t="inlineStr">
+      <c r="B1369" s="30" t="inlineStr">
         <is>
           <t>#03 AÇOUGUE - #06 EMBUTIDOS E FRIOS</t>
         </is>
       </c>
-      <c r="C1369" s="26" t="inlineStr">
+      <c r="C1369" s="30" t="inlineStr">
         <is>
           <t>APRESUNTADO PERDIGAO 200GR FATIADO</t>
         </is>
       </c>
-      <c r="D1369" s="26" t="inlineStr">
+      <c r="D1369" s="30" t="inlineStr">
         <is>
           <t>APRESUNTADO PERDIGÃO 200G FATIADO</t>
         </is>
       </c>
-      <c r="E1369" s="26" t="inlineStr"/>
+      <c r="E1369" s="30" t="inlineStr"/>
     </row>
     <row r="1370">
       <c r="A1370" t="n">
@@ -28809,25 +28809,25 @@
       <c r="E1402" s="26" t="inlineStr"/>
     </row>
     <row r="1403">
-      <c r="A1403" s="26" t="n">
+      <c r="A1403" s="30" t="n">
         <v>289127</v>
       </c>
-      <c r="B1403" s="26" t="inlineStr">
+      <c r="B1403" s="30" t="inlineStr">
         <is>
           <t>#03 AÇOUGUE - #06 EMBUTIDOS E FRIOS</t>
         </is>
       </c>
-      <c r="C1403" s="26" t="inlineStr">
+      <c r="C1403" s="30" t="inlineStr">
         <is>
           <t>LINGUIÇA MISTA SADIA 215GR FININHA DEFUM</t>
         </is>
       </c>
-      <c r="D1403" s="26" t="inlineStr">
+      <c r="D1403" s="30" t="inlineStr">
         <is>
           <t>LINGUIÇA MISTA FININHA DEFUMADA SADIA 215G</t>
         </is>
       </c>
-      <c r="E1403" s="26" t="inlineStr"/>
+      <c r="E1403" s="30" t="inlineStr"/>
     </row>
     <row r="1404">
       <c r="A1404" s="20" t="n">
@@ -29172,25 +29172,25 @@
       </c>
     </row>
     <row r="1421">
-      <c r="A1421" s="26" t="n">
+      <c r="A1421" s="30" t="n">
         <v>292399</v>
       </c>
-      <c r="B1421" s="26" t="inlineStr">
+      <c r="B1421" s="30" t="inlineStr">
         <is>
           <t>#03 AÇOUGUE - #06 EMBUTIDOS E FRIOS</t>
         </is>
       </c>
-      <c r="C1421" s="26" t="inlineStr">
+      <c r="C1421" s="30" t="inlineStr">
         <is>
           <t>LINGUICA SUPER FRANGO 400GR DEFUMADA FRA</t>
         </is>
       </c>
-      <c r="D1421" s="26" t="inlineStr">
+      <c r="D1421" s="30" t="inlineStr">
         <is>
           <t>LINGUIÇA SUPER FRANGO 400G DEFUMADA</t>
         </is>
       </c>
-      <c r="E1421" s="26" t="inlineStr"/>
+      <c r="E1421" s="30" t="inlineStr"/>
     </row>
     <row r="1422">
       <c r="A1422" t="n">
@@ -29875,25 +29875,25 @@
       </c>
     </row>
     <row r="1456">
-      <c r="A1456" s="26" t="n">
+      <c r="A1456" s="30" t="n">
         <v>108558</v>
       </c>
-      <c r="B1456" s="26" t="inlineStr">
+      <c r="B1456" s="30" t="inlineStr">
         <is>
           <t>#03 AÇOUGUE - #06 EMBUTIDOS E FRIOS</t>
         </is>
       </c>
-      <c r="C1456" s="26" t="inlineStr">
+      <c r="C1456" s="30" t="inlineStr">
         <is>
           <t>MORTADELA SADIA  1KG SUINA</t>
         </is>
       </c>
-      <c r="D1456" s="26" t="inlineStr">
+      <c r="D1456" s="30" t="inlineStr">
         <is>
           <t>MORTADELA SUÍNA SADIA 1KG</t>
         </is>
       </c>
-      <c r="E1456" s="26" t="inlineStr"/>
+      <c r="E1456" s="30" t="inlineStr"/>
     </row>
     <row r="1457">
       <c r="A1457" t="n">
@@ -30077,25 +30077,25 @@
       </c>
     </row>
     <row r="1466">
-      <c r="A1466" s="26" t="n">
+      <c r="A1466" s="30" t="n">
         <v>184045</v>
       </c>
-      <c r="B1466" s="26" t="inlineStr">
+      <c r="B1466" s="30" t="inlineStr">
         <is>
           <t>#03 AÇOUGUE - #06 EMBUTIDOS E FRIOS</t>
         </is>
       </c>
-      <c r="C1466" s="26" t="inlineStr">
+      <c r="C1466" s="30" t="inlineStr">
         <is>
           <t>SALAME PERDIGAO FATIADO 100GR SALF10</t>
         </is>
       </c>
-      <c r="D1466" s="26" t="inlineStr">
+      <c r="D1466" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">SALAME PERDIGÃO 100GR FATIADO </t>
         </is>
       </c>
-      <c r="E1466" s="26" t="inlineStr"/>
+      <c r="E1466" s="30" t="inlineStr"/>
     </row>
     <row r="1467">
       <c r="A1467" t="n">
@@ -30519,25 +30519,25 @@
       </c>
     </row>
     <row r="1488">
-      <c r="A1488" s="26" t="n">
+      <c r="A1488" s="30" t="n">
         <v>170464</v>
       </c>
-      <c r="B1488" s="26" t="inlineStr">
+      <c r="B1488" s="30" t="inlineStr">
         <is>
           <t>#03 AÇOUGUE - #07 EMPANADOS E PRATOS PRONTOS</t>
         </is>
       </c>
-      <c r="C1488" s="26" t="inlineStr">
+      <c r="C1488" s="30" t="inlineStr">
         <is>
           <t>STEAK FRANGO EMPANADO SADIA 100G STCE</t>
         </is>
       </c>
-      <c r="D1488" s="26" t="inlineStr">
+      <c r="D1488" s="30" t="inlineStr">
         <is>
           <t>STEAK EMPANADO SADIA 100G FRANGO</t>
         </is>
       </c>
-      <c r="E1488" s="26" t="inlineStr"/>
+      <c r="E1488" s="30" t="inlineStr"/>
     </row>
     <row r="1489">
       <c r="A1489" s="20" t="n">
@@ -30561,25 +30561,25 @@
       <c r="E1489" s="20" t="inlineStr"/>
     </row>
     <row r="1490">
-      <c r="A1490" s="26" t="n">
+      <c r="A1490" s="30" t="n">
         <v>127328</v>
       </c>
-      <c r="B1490" s="26" t="inlineStr">
+      <c r="B1490" s="30" t="inlineStr">
         <is>
           <t>#03 AÇOUGUE - #07 EMPANADOS E PRATOS PRONTOS</t>
         </is>
       </c>
-      <c r="C1490" s="26" t="inlineStr">
+      <c r="C1490" s="30" t="inlineStr">
         <is>
           <t>TEKITOS SEARA QUEIJO OREGANO 300GR</t>
         </is>
       </c>
-      <c r="D1490" s="26" t="inlineStr">
+      <c r="D1490" s="30" t="inlineStr">
         <is>
           <t>TEKITOS SEARA 300G QUEIJO COM OREGANO</t>
         </is>
       </c>
-      <c r="E1490" s="26" t="inlineStr"/>
+      <c r="E1490" s="30" t="inlineStr"/>
     </row>
     <row r="1491">
       <c r="A1491" t="n">
@@ -32048,151 +32048,151 @@
       </c>
     </row>
     <row r="1563">
-      <c r="A1563" s="26" t="n">
+      <c r="A1563" s="31" t="n">
         <v>247972</v>
       </c>
-      <c r="B1563" s="26" t="inlineStr">
+      <c r="B1563" s="31" t="inlineStr">
         <is>
           <t>#05 BEBIDA - #00 BEBIDAS GASEIFICADAS</t>
         </is>
       </c>
-      <c r="C1563" s="26" t="inlineStr">
+      <c r="C1563" s="31" t="inlineStr">
         <is>
           <t>BEBIDA ICE 51 275ML BALADA</t>
         </is>
       </c>
-      <c r="D1563" s="26" t="inlineStr">
+      <c r="D1563" s="31" t="inlineStr">
         <is>
           <t>BEBIDA ICE 51 275ML BALADA</t>
         </is>
       </c>
-      <c r="E1563" s="26" t="inlineStr"/>
+      <c r="E1563" s="31" t="inlineStr"/>
     </row>
     <row r="1564">
-      <c r="A1564" s="26" t="n">
+      <c r="A1564" s="31" t="n">
         <v>247970</v>
       </c>
-      <c r="B1564" s="26" t="inlineStr">
+      <c r="B1564" s="31" t="inlineStr">
         <is>
           <t>#05 BEBIDA - #00 BEBIDAS GASEIFICADAS</t>
         </is>
       </c>
-      <c r="C1564" s="26" t="inlineStr">
+      <c r="C1564" s="31" t="inlineStr">
         <is>
           <t>BEBIDA ICE 51 275ML BALADA</t>
         </is>
       </c>
-      <c r="D1564" s="26" t="inlineStr">
+      <c r="D1564" s="31" t="inlineStr">
         <is>
           <t>BEBIDA ICE 51 275ML BALADA</t>
         </is>
       </c>
-      <c r="E1564" s="26" t="inlineStr"/>
+      <c r="E1564" s="31" t="inlineStr"/>
     </row>
     <row r="1565">
-      <c r="A1565" s="26" t="n">
+      <c r="A1565" s="31" t="n">
         <v>247993</v>
       </c>
-      <c r="B1565" s="26" t="inlineStr">
+      <c r="B1565" s="31" t="inlineStr">
         <is>
           <t>#05 BEBIDA - #00 BEBIDAS GASEIFICADAS</t>
         </is>
       </c>
-      <c r="C1565" s="26" t="inlineStr">
+      <c r="C1565" s="31" t="inlineStr">
         <is>
           <t>BEB ICE 51 275ML KIWI</t>
         </is>
       </c>
-      <c r="D1565" s="26" t="inlineStr">
+      <c r="D1565" s="31" t="inlineStr">
         <is>
           <t>BEBIDA ICE 51 275ML KIWI</t>
         </is>
       </c>
-      <c r="E1565" s="26" t="inlineStr"/>
+      <c r="E1565" s="31" t="inlineStr"/>
     </row>
     <row r="1566">
-      <c r="A1566" s="26" t="n">
+      <c r="A1566" s="31" t="n">
         <v>247995</v>
       </c>
-      <c r="B1566" s="26" t="inlineStr">
+      <c r="B1566" s="31" t="inlineStr">
         <is>
           <t>#05 BEBIDA - #00 BEBIDAS GASEIFICADAS</t>
         </is>
       </c>
-      <c r="C1566" s="26" t="inlineStr">
+      <c r="C1566" s="31" t="inlineStr">
         <is>
           <t>BEB ICE 51 275ML LIMAO</t>
         </is>
       </c>
-      <c r="D1566" s="26" t="inlineStr">
+      <c r="D1566" s="31" t="inlineStr">
         <is>
           <t>BEBIDA ICE 51 275ML LIMÃO</t>
         </is>
       </c>
-      <c r="E1566" s="26" t="inlineStr"/>
+      <c r="E1566" s="31" t="inlineStr"/>
     </row>
     <row r="1567">
-      <c r="A1567" s="26" t="n">
+      <c r="A1567" s="31" t="n">
         <v>286357</v>
       </c>
-      <c r="B1567" s="26" t="inlineStr">
+      <c r="B1567" s="31" t="inlineStr">
         <is>
           <t>#05 BEBIDA - #00 BEBIDAS GASEIFICADAS</t>
         </is>
       </c>
-      <c r="C1567" s="26" t="inlineStr">
+      <c r="C1567" s="31" t="inlineStr">
         <is>
           <t>BEBIDA CABARE ICE 275ML MACA VERDE</t>
         </is>
       </c>
-      <c r="D1567" s="26" t="inlineStr">
+      <c r="D1567" s="31" t="inlineStr">
         <is>
           <t>BEBIDA ICE 51 275ML MAÇÃ VERDE</t>
         </is>
       </c>
-      <c r="E1567" s="26" t="inlineStr"/>
+      <c r="E1567" s="31" t="inlineStr"/>
     </row>
     <row r="1568">
-      <c r="A1568" s="26" t="n">
+      <c r="A1568" s="31" t="n">
         <v>248003</v>
       </c>
-      <c r="B1568" s="26" t="inlineStr">
+      <c r="B1568" s="31" t="inlineStr">
         <is>
           <t>#05 BEBIDA - #00 BEBIDAS GASEIFICADAS</t>
         </is>
       </c>
-      <c r="C1568" s="26" t="inlineStr">
+      <c r="C1568" s="31" t="inlineStr">
         <is>
           <t>BEB ICE 51 275ML MARACUJA</t>
         </is>
       </c>
-      <c r="D1568" s="26" t="inlineStr">
+      <c r="D1568" s="31" t="inlineStr">
         <is>
           <t>BEBIDA ICE 51 275ML MARACUJA</t>
         </is>
       </c>
-      <c r="E1568" s="26" t="inlineStr"/>
+      <c r="E1568" s="31" t="inlineStr"/>
     </row>
     <row r="1569">
-      <c r="A1569" s="26" t="n">
+      <c r="A1569" s="31" t="n">
         <v>247998</v>
       </c>
-      <c r="B1569" s="26" t="inlineStr">
+      <c r="B1569" s="31" t="inlineStr">
         <is>
           <t>#05 BEBIDA - #00 BEBIDAS GASEIFICADAS</t>
         </is>
       </c>
-      <c r="C1569" s="26" t="inlineStr">
+      <c r="C1569" s="31" t="inlineStr">
         <is>
           <t>BEB ICE 51 275ML MORANGO LARANJA</t>
         </is>
       </c>
-      <c r="D1569" s="26" t="inlineStr">
+      <c r="D1569" s="31" t="inlineStr">
         <is>
           <t>BEBIDA ICE 51 275ML MORANGO COM LARANJA</t>
         </is>
       </c>
-      <c r="E1569" s="26" t="inlineStr"/>
+      <c r="E1569" s="31" t="inlineStr"/>
     </row>
     <row r="1570">
       <c r="A1570" t="n">
@@ -32235,109 +32235,109 @@
       </c>
     </row>
     <row r="1572">
-      <c r="A1572" s="26" t="n">
+      <c r="A1572" s="31" t="n">
         <v>247992</v>
       </c>
-      <c r="B1572" s="26" t="inlineStr">
+      <c r="B1572" s="31" t="inlineStr">
         <is>
           <t>#05 BEBIDA - #00 BEBIDAS GASEIFICADAS</t>
         </is>
       </c>
-      <c r="C1572" s="26" t="inlineStr">
+      <c r="C1572" s="31" t="inlineStr">
         <is>
           <t>BEB ICE 51 275ML KIWI</t>
         </is>
       </c>
-      <c r="D1572" s="26" t="inlineStr">
+      <c r="D1572" s="31" t="inlineStr">
         <is>
           <t>BEBIDA ICE 51 275ML KIWI</t>
         </is>
       </c>
-      <c r="E1572" s="26" t="inlineStr"/>
+      <c r="E1572" s="31" t="inlineStr"/>
     </row>
     <row r="1573">
-      <c r="A1573" s="26" t="n">
+      <c r="A1573" s="31" t="n">
         <v>247994</v>
       </c>
-      <c r="B1573" s="26" t="inlineStr">
+      <c r="B1573" s="31" t="inlineStr">
         <is>
           <t>#05 BEBIDA - #00 BEBIDAS GASEIFICADAS</t>
         </is>
       </c>
-      <c r="C1573" s="26" t="inlineStr">
+      <c r="C1573" s="31" t="inlineStr">
         <is>
           <t>BEB ICE 51 275ML LIMAO</t>
         </is>
       </c>
-      <c r="D1573" s="26" t="inlineStr">
+      <c r="D1573" s="31" t="inlineStr">
         <is>
           <t>BEBIDA ICE 51 275ML LIMÃO</t>
         </is>
       </c>
-      <c r="E1573" s="26" t="inlineStr"/>
+      <c r="E1573" s="31" t="inlineStr"/>
     </row>
     <row r="1574">
-      <c r="A1574" s="26" t="n">
+      <c r="A1574" s="31" t="n">
         <v>248002</v>
       </c>
-      <c r="B1574" s="26" t="inlineStr">
+      <c r="B1574" s="31" t="inlineStr">
         <is>
           <t>#05 BEBIDA - #00 BEBIDAS GASEIFICADAS</t>
         </is>
       </c>
-      <c r="C1574" s="26" t="inlineStr">
+      <c r="C1574" s="31" t="inlineStr">
         <is>
           <t>BEB ICE 51 275ML MARACUJA</t>
         </is>
       </c>
-      <c r="D1574" s="26" t="inlineStr">
+      <c r="D1574" s="31" t="inlineStr">
         <is>
           <t>BEBIDA ICE 51 275ML MARACUJA</t>
         </is>
       </c>
-      <c r="E1574" s="26" t="inlineStr"/>
+      <c r="E1574" s="31" t="inlineStr"/>
     </row>
     <row r="1575">
-      <c r="A1575" s="26" t="n">
+      <c r="A1575" s="31" t="n">
         <v>247996</v>
       </c>
-      <c r="B1575" s="26" t="inlineStr">
+      <c r="B1575" s="31" t="inlineStr">
         <is>
           <t>#05 BEBIDA - #00 BEBIDAS GASEIFICADAS</t>
         </is>
       </c>
-      <c r="C1575" s="26" t="inlineStr">
+      <c r="C1575" s="31" t="inlineStr">
         <is>
           <t>BEB ICE 51 275ML MORANGO LARANJA</t>
         </is>
       </c>
-      <c r="D1575" s="26" t="inlineStr">
+      <c r="D1575" s="31" t="inlineStr">
         <is>
           <t>BEBIDA ICE 51 275ML MORANGO COM LARANJA</t>
         </is>
       </c>
-      <c r="E1575" s="26" t="inlineStr"/>
+      <c r="E1575" s="31" t="inlineStr"/>
     </row>
     <row r="1576">
-      <c r="A1576" s="26" t="n">
+      <c r="A1576" s="31" t="n">
         <v>248000</v>
       </c>
-      <c r="B1576" s="26" t="inlineStr">
+      <c r="B1576" s="31" t="inlineStr">
         <is>
           <t>#05 BEBIDA - #00 BEBIDAS GASEIFICADAS</t>
         </is>
       </c>
-      <c r="C1576" s="26" t="inlineStr">
+      <c r="C1576" s="31" t="inlineStr">
         <is>
           <t>BEB ICE 51 275ML TANGERINA UN</t>
         </is>
       </c>
-      <c r="D1576" s="26" t="inlineStr">
+      <c r="D1576" s="31" t="inlineStr">
         <is>
           <t>BEBIDA ICE 51 275ML TANGERINA</t>
         </is>
       </c>
-      <c r="E1576" s="26" t="inlineStr"/>
+      <c r="E1576" s="31" t="inlineStr"/>
     </row>
     <row r="1577">
       <c r="A1577" t="n">
@@ -32520,25 +32520,25 @@
       </c>
     </row>
     <row r="1586">
-      <c r="A1586" s="26" t="n">
+      <c r="A1586" s="31" t="n">
         <v>161871</v>
       </c>
-      <c r="B1586" s="26" t="inlineStr">
+      <c r="B1586" s="31" t="inlineStr">
         <is>
           <t>#05 BEBIDA - #00 BEBIDAS GASEIFICADAS</t>
         </is>
       </c>
-      <c r="C1586" s="26" t="inlineStr">
+      <c r="C1586" s="31" t="inlineStr">
         <is>
           <t>REFRIG GUARANA TUCHAUA 2LT</t>
         </is>
       </c>
-      <c r="D1586" s="26" t="inlineStr">
+      <c r="D1586" s="31" t="inlineStr">
         <is>
           <t>REFRIGANTE TUCHAUA 2L GUARANA</t>
         </is>
       </c>
-      <c r="E1586" s="26" t="inlineStr"/>
+      <c r="E1586" s="31" t="inlineStr"/>
     </row>
     <row r="1587">
       <c r="A1587" t="n">
@@ -32601,46 +32601,46 @@
       </c>
     </row>
     <row r="1590">
-      <c r="A1590" s="26" t="n">
+      <c r="A1590" s="31" t="n">
         <v>288761</v>
       </c>
-      <c r="B1590" s="26" t="inlineStr">
+      <c r="B1590" s="31" t="inlineStr">
         <is>
           <t>#05 BEBIDA - #00 BEBIDAS GASEIFICADAS</t>
         </is>
       </c>
-      <c r="C1590" s="26" t="inlineStr">
+      <c r="C1590" s="31" t="inlineStr">
         <is>
           <t>REFRIGERANTE COCA COLA 1L SEM ACUCAR PET</t>
         </is>
       </c>
-      <c r="D1590" s="26" t="inlineStr">
+      <c r="D1590" s="31" t="inlineStr">
         <is>
           <t>REFRIGERANTE COCA COLA 1L  SEM AÇUCAR</t>
         </is>
       </c>
-      <c r="E1590" s="26" t="inlineStr"/>
+      <c r="E1590" s="31" t="inlineStr"/>
     </row>
     <row r="1591">
-      <c r="A1591" s="26" t="n">
+      <c r="A1591" s="31" t="n">
         <v>104406</v>
       </c>
-      <c r="B1591" s="26" t="inlineStr">
+      <c r="B1591" s="31" t="inlineStr">
         <is>
           <t>#05 BEBIDA - #00 BEBIDAS GASEIFICADAS</t>
         </is>
       </c>
-      <c r="C1591" s="26" t="inlineStr">
+      <c r="C1591" s="31" t="inlineStr">
         <is>
           <t>REFRIGERANTE COCA COLA 2L ORIGINAL</t>
         </is>
       </c>
-      <c r="D1591" s="26" t="inlineStr">
+      <c r="D1591" s="31" t="inlineStr">
         <is>
           <t>REFRIGERANTE COCA COLA 2L</t>
         </is>
       </c>
-      <c r="E1591" s="26" t="inlineStr"/>
+      <c r="E1591" s="31" t="inlineStr"/>
     </row>
     <row r="1592">
       <c r="A1592" t="n">
@@ -32743,25 +32743,25 @@
       </c>
     </row>
     <row r="1597">
-      <c r="A1597" s="26" t="n">
+      <c r="A1597" s="31" t="n">
         <v>104404</v>
       </c>
-      <c r="B1597" s="26" t="inlineStr">
+      <c r="B1597" s="31" t="inlineStr">
         <is>
           <t>#05 BEBIDA - #00 BEBIDAS GASEIFICADAS</t>
         </is>
       </c>
-      <c r="C1597" s="26" t="inlineStr">
+      <c r="C1597" s="31" t="inlineStr">
         <is>
           <t>REFRIG FANTA LARANJA 2L</t>
         </is>
       </c>
-      <c r="D1597" s="26" t="inlineStr">
+      <c r="D1597" s="31" t="inlineStr">
         <is>
           <t>REFRIGERANTE FANTA 2L LARANJA</t>
         </is>
       </c>
-      <c r="E1597" s="26" t="inlineStr"/>
+      <c r="E1597" s="31" t="inlineStr"/>
     </row>
     <row r="1598">
       <c r="A1598" s="9" t="n">
@@ -32905,25 +32905,25 @@
       </c>
     </row>
     <row r="1605">
-      <c r="A1605" s="26" t="n">
+      <c r="A1605" s="31" t="n">
         <v>325127</v>
       </c>
-      <c r="B1605" s="26" t="inlineStr">
+      <c r="B1605" s="31" t="inlineStr">
         <is>
           <t>#05 BEBIDA - #00 BEBIDAS GASEIFICADAS</t>
         </is>
       </c>
-      <c r="C1605" s="26" t="inlineStr">
+      <c r="C1605" s="31" t="inlineStr">
         <is>
           <t>REFRIGERANTE H2OH LIMONETO 1,5L PET</t>
         </is>
       </c>
-      <c r="D1605" s="26" t="inlineStr">
+      <c r="D1605" s="31" t="inlineStr">
         <is>
           <t>REFRIGERANTE H2OH 1,5L LIMONETO</t>
         </is>
       </c>
-      <c r="E1605" s="26" t="inlineStr"/>
+      <c r="E1605" s="31" t="inlineStr"/>
     </row>
     <row r="1606">
       <c r="A1606" t="n">
@@ -34328,25 +34328,25 @@
       </c>
     </row>
     <row r="1676">
-      <c r="A1676" s="26" t="n">
+      <c r="A1676" s="31" t="n">
         <v>286325</v>
       </c>
-      <c r="B1676" s="26" t="inlineStr">
+      <c r="B1676" s="31" t="inlineStr">
         <is>
           <t>#05 BEBIDA - #01 SUCOS PRONTOS</t>
         </is>
       </c>
-      <c r="C1676" s="26" t="inlineStr">
+      <c r="C1676" s="31" t="inlineStr">
         <is>
           <t>SUCO DE UVA AURORA 1,5LT TINTO TP</t>
         </is>
       </c>
-      <c r="D1676" s="26" t="inlineStr">
+      <c r="D1676" s="31" t="inlineStr">
         <is>
           <t>SUCO AURORA TP 1,5L UVA TINTO</t>
         </is>
       </c>
-      <c r="E1676" s="26" t="inlineStr"/>
+      <c r="E1676" s="31" t="inlineStr"/>
     </row>
     <row r="1677">
       <c r="A1677" s="10" t="n">
@@ -34409,25 +34409,25 @@
       </c>
     </row>
     <row r="1680">
-      <c r="A1680" s="26" t="n">
+      <c r="A1680" s="31" t="n">
         <v>108631</v>
       </c>
-      <c r="B1680" s="26" t="inlineStr">
+      <c r="B1680" s="31" t="inlineStr">
         <is>
           <t>#05 BEBIDA - #01 SUCOS PRONTOS</t>
         </is>
       </c>
-      <c r="C1680" s="26" t="inlineStr">
+      <c r="C1680" s="31" t="inlineStr">
         <is>
           <t>SUCO DAFRUTA CONCENTRADO PET 500ML  CAJU</t>
         </is>
       </c>
-      <c r="D1680" s="26" t="inlineStr">
+      <c r="D1680" s="31" t="inlineStr">
         <is>
           <t>SUCO CONCENTRADO DAFRUTA 500ML CAJU</t>
         </is>
       </c>
-      <c r="E1680" s="26" t="inlineStr"/>
+      <c r="E1680" s="31" t="inlineStr"/>
     </row>
     <row r="1681">
       <c r="A1681" t="n">
@@ -34650,25 +34650,25 @@
       </c>
     </row>
     <row r="1692">
-      <c r="A1692" s="26" t="n">
+      <c r="A1692" s="31" t="n">
         <v>338379</v>
       </c>
-      <c r="B1692" s="26" t="inlineStr">
+      <c r="B1692" s="31" t="inlineStr">
         <is>
           <t>#05 BEBIDA - #01 SUCOS PRONTOS</t>
         </is>
       </c>
-      <c r="C1692" s="26" t="inlineStr">
+      <c r="C1692" s="31" t="inlineStr">
         <is>
           <t>SUCO NATURAL ONE 1,3L UVA</t>
         </is>
       </c>
-      <c r="D1692" s="26" t="inlineStr">
+      <c r="D1692" s="31" t="inlineStr">
         <is>
           <t>SUCO NATURAL ONE 1,3L UVA</t>
         </is>
       </c>
-      <c r="E1692" s="26" t="inlineStr"/>
+      <c r="E1692" s="31" t="inlineStr"/>
     </row>
     <row r="1693">
       <c r="A1693" t="n">
@@ -35633,25 +35633,25 @@
       </c>
     </row>
     <row r="1741">
-      <c r="A1741" s="26" t="n">
+      <c r="A1741" s="31" t="n">
         <v>267604</v>
       </c>
-      <c r="B1741" s="26" t="inlineStr">
+      <c r="B1741" s="31" t="inlineStr">
         <is>
           <t>#05 BEBIDA - CERVEJAS</t>
         </is>
       </c>
-      <c r="C1741" s="26" t="inlineStr">
+      <c r="C1741" s="31" t="inlineStr">
         <is>
           <t>CERVEJA BUDWEISER 330ML ZERO ALCOOL LN U</t>
         </is>
       </c>
-      <c r="D1741" s="26" t="inlineStr">
+      <c r="D1741" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">CERVEJA BUDWEISER ZERO ALCOOL LONG NECK 330ML </t>
         </is>
       </c>
-      <c r="E1741" s="26" t="inlineStr"/>
+      <c r="E1741" s="31" t="inlineStr"/>
     </row>
     <row r="1742">
       <c r="A1742" t="n">
@@ -35814,25 +35814,25 @@
       </c>
     </row>
     <row r="1750">
-      <c r="A1750" s="26" t="n">
+      <c r="A1750" s="31" t="n">
         <v>265726</v>
       </c>
-      <c r="B1750" s="26" t="inlineStr">
+      <c r="B1750" s="31" t="inlineStr">
         <is>
           <t>#05 BEBIDA - CERVEJAS</t>
         </is>
       </c>
-      <c r="C1750" s="26" t="inlineStr">
+      <c r="C1750" s="31" t="inlineStr">
         <is>
           <t>CERVEJA HEINEKEN 269ML LATA UNID</t>
         </is>
       </c>
-      <c r="D1750" s="26" t="inlineStr">
+      <c r="D1750" s="31" t="inlineStr">
         <is>
           <t>CERVEJA HEINEKEN 269ML</t>
         </is>
       </c>
-      <c r="E1750" s="26" t="inlineStr"/>
+      <c r="E1750" s="31" t="inlineStr"/>
     </row>
     <row r="1751">
       <c r="A1751" t="n">
@@ -36056,25 +36056,25 @@
       </c>
     </row>
     <row r="1762">
-      <c r="A1762" s="26" t="n">
+      <c r="A1762" s="31" t="n">
         <v>302401</v>
       </c>
-      <c r="B1762" s="26" t="inlineStr">
+      <c r="B1762" s="31" t="inlineStr">
         <is>
           <t>#05 BEBIDA - CERVEJAS</t>
         </is>
       </c>
-      <c r="C1762" s="26" t="inlineStr">
+      <c r="C1762" s="31" t="inlineStr">
         <is>
           <t>CERVEJA IMPERIO ULTRA 275ML LN</t>
         </is>
       </c>
-      <c r="D1762" s="26" t="inlineStr">
+      <c r="D1762" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">CERVEJA IMPERIO ULTRA LONG NECK 275ML </t>
         </is>
       </c>
-      <c r="E1762" s="26" t="inlineStr"/>
+      <c r="E1762" s="31" t="inlineStr"/>
     </row>
     <row r="1763">
       <c r="A1763" s="12" t="n">
@@ -36439,25 +36439,25 @@
       </c>
     </row>
     <row r="1781">
-      <c r="A1781" s="30" t="n">
+      <c r="A1781" s="28" t="n">
         <v>341231</v>
       </c>
-      <c r="B1781" s="30" t="inlineStr">
+      <c r="B1781" s="28" t="inlineStr">
         <is>
           <t>#05 BEBIDA - CERVEJAS CX</t>
         </is>
       </c>
-      <c r="C1781" s="30" t="inlineStr">
+      <c r="C1781" s="28" t="inlineStr">
         <is>
           <t>CERVEJA ANTARCTICA 269ML MULTIPACK</t>
         </is>
       </c>
-      <c r="D1781" s="30" t="inlineStr">
+      <c r="D1781" s="28" t="inlineStr">
         <is>
           <t>CERVEJA ANTARCTICA 15 X 269ML MULTIPACK</t>
         </is>
       </c>
-      <c r="E1781" s="30" t="inlineStr"/>
+      <c r="E1781" s="28" t="inlineStr"/>
     </row>
     <row r="1782">
       <c r="A1782" t="n">
@@ -36882,25 +36882,25 @@
       </c>
     </row>
     <row r="1803">
-      <c r="A1803" s="26" t="n">
+      <c r="A1803" s="31" t="n">
         <v>271001</v>
       </c>
-      <c r="B1803" s="26" t="inlineStr">
+      <c r="B1803" s="31" t="inlineStr">
         <is>
           <t>#05 BEBIDA - CERVEJAS CX</t>
         </is>
       </c>
-      <c r="C1803" s="26" t="inlineStr">
+      <c r="C1803" s="31" t="inlineStr">
         <is>
           <t>CERVEJA IMPERIO  PURO MALTE 269ML PACK C</t>
         </is>
       </c>
-      <c r="D1803" s="26" t="inlineStr">
+      <c r="D1803" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">CERVEJA IMPERIO PURO MALTE 15 X 269ML </t>
         </is>
       </c>
-      <c r="E1803" s="26" t="inlineStr"/>
+      <c r="E1803" s="31" t="inlineStr"/>
     </row>
     <row r="1804">
       <c r="A1804" t="n">
@@ -37003,25 +37003,25 @@
       </c>
     </row>
     <row r="1809">
-      <c r="A1809" s="26" t="n">
+      <c r="A1809" s="31" t="n">
         <v>324556</v>
       </c>
-      <c r="B1809" s="26" t="inlineStr">
+      <c r="B1809" s="31" t="inlineStr">
         <is>
           <t>#05 BEBIDA - CERVEJAS CX</t>
         </is>
       </c>
-      <c r="C1809" s="26" t="inlineStr">
+      <c r="C1809" s="31" t="inlineStr">
         <is>
           <t>CERVEJA SKOL PILSEN 269ML ECO</t>
         </is>
       </c>
-      <c r="D1809" s="26" t="inlineStr">
+      <c r="D1809" s="31" t="inlineStr">
         <is>
           <t>CERVEJA SKOL PILSEN 15 X 269ML</t>
         </is>
       </c>
-      <c r="E1809" s="26" t="inlineStr"/>
+      <c r="E1809" s="31" t="inlineStr"/>
     </row>
     <row r="1810">
       <c r="A1810" t="n">
@@ -37064,25 +37064,25 @@
       </c>
     </row>
     <row r="1812">
-      <c r="A1812" s="26" t="n">
+      <c r="A1812" s="31" t="n">
         <v>149113</v>
       </c>
-      <c r="B1812" s="26" t="inlineStr">
+      <c r="B1812" s="31" t="inlineStr">
         <is>
           <t>#05 BEBIDA - DESTILADOS</t>
         </is>
       </c>
-      <c r="C1812" s="26" t="inlineStr">
+      <c r="C1812" s="31" t="inlineStr">
         <is>
           <t>AGUARD 29 GARRAFA  600ML</t>
         </is>
       </c>
-      <c r="D1812" s="26" t="inlineStr">
+      <c r="D1812" s="31" t="inlineStr">
         <is>
           <t>AGUARDENTE 29 600ML</t>
         </is>
       </c>
-      <c r="E1812" s="26" t="inlineStr"/>
+      <c r="E1812" s="31" t="inlineStr"/>
     </row>
     <row r="1813">
       <c r="A1813" t="n">
@@ -37407,25 +37407,25 @@
       </c>
     </row>
     <row r="1829">
-      <c r="A1829" s="26" t="n">
+      <c r="A1829" s="31" t="n">
         <v>102085</v>
       </c>
-      <c r="B1829" s="26" t="inlineStr">
+      <c r="B1829" s="31" t="inlineStr">
         <is>
           <t>#05 BEBIDA - DESTILADOS</t>
         </is>
       </c>
-      <c r="C1829" s="26" t="inlineStr">
+      <c r="C1829" s="31" t="inlineStr">
         <is>
           <t>CACHACA 51 PIRASSUNUNGA 965ML</t>
         </is>
       </c>
-      <c r="D1829" s="26" t="inlineStr">
+      <c r="D1829" s="31" t="inlineStr">
         <is>
           <t>CACHAÇA 51 965ML</t>
         </is>
       </c>
-      <c r="E1829" s="26" t="inlineStr"/>
+      <c r="E1829" s="31" t="inlineStr"/>
     </row>
     <row r="1830">
       <c r="A1830" s="15" t="n">
@@ -37629,25 +37629,25 @@
       </c>
     </row>
     <row r="1840">
-      <c r="A1840" s="26" t="n">
+      <c r="A1840" s="31" t="n">
         <v>145655</v>
       </c>
-      <c r="B1840" s="26" t="inlineStr">
+      <c r="B1840" s="31" t="inlineStr">
         <is>
           <t>#05 BEBIDA - DESTILADOS</t>
         </is>
       </c>
-      <c r="C1840" s="26" t="inlineStr">
+      <c r="C1840" s="31" t="inlineStr">
         <is>
           <t>CACHACA SELETA 1LT</t>
         </is>
       </c>
-      <c r="D1840" s="26" t="inlineStr">
+      <c r="D1840" s="31" t="inlineStr">
         <is>
           <t>CACHAÇA SELETA 1L</t>
         </is>
       </c>
-      <c r="E1840" s="26" t="inlineStr"/>
+      <c r="E1840" s="31" t="inlineStr"/>
     </row>
     <row r="1841">
       <c r="A1841" t="n">
@@ -37911,25 +37911,25 @@
       </c>
     </row>
     <row r="1854">
-      <c r="A1854" s="26" t="n">
+      <c r="A1854" s="31" t="n">
         <v>102243</v>
       </c>
-      <c r="B1854" s="26" t="inlineStr">
+      <c r="B1854" s="31" t="inlineStr">
         <is>
           <t>#05 BEBIDA - DESTILADOS</t>
         </is>
       </c>
-      <c r="C1854" s="26" t="inlineStr">
+      <c r="C1854" s="31" t="inlineStr">
         <is>
           <t>CONHAQUE SAO JOAO DA BARRA 900ML TRAD</t>
         </is>
       </c>
-      <c r="D1854" s="26" t="inlineStr">
+      <c r="D1854" s="31" t="inlineStr">
         <is>
           <t>CONHAQUE SÃO JOÃO DA BARRA 900ML TRADICIONAL</t>
         </is>
       </c>
-      <c r="E1854" s="26" t="inlineStr"/>
+      <c r="E1854" s="31" t="inlineStr"/>
     </row>
     <row r="1855">
       <c r="A1855" t="n">
@@ -38916,25 +38916,25 @@
       </c>
     </row>
     <row r="1904">
-      <c r="A1904" s="26" t="n">
+      <c r="A1904" s="31" t="n">
         <v>109729</v>
       </c>
-      <c r="B1904" s="26" t="inlineStr">
+      <c r="B1904" s="31" t="inlineStr">
         <is>
           <t>#05 BEBIDA - DESTILADOS</t>
         </is>
       </c>
-      <c r="C1904" s="26" t="inlineStr">
+      <c r="C1904" s="31" t="inlineStr">
         <is>
           <t>WHISKY WHITE HORSE 1LT</t>
         </is>
       </c>
-      <c r="D1904" s="26" t="inlineStr">
+      <c r="D1904" s="31" t="inlineStr">
         <is>
           <t>WHISKY WHITE HORSE 1L</t>
         </is>
       </c>
-      <c r="E1904" s="26" t="inlineStr"/>
+      <c r="E1904" s="31" t="inlineStr"/>
     </row>
     <row r="1905">
       <c r="A1905" t="n">
@@ -39399,25 +39399,25 @@
       </c>
     </row>
     <row r="1928">
-      <c r="A1928" s="26" t="n">
+      <c r="A1928" s="31" t="n">
         <v>102035</v>
       </c>
-      <c r="B1928" s="26" t="inlineStr">
+      <c r="B1928" s="31" t="inlineStr">
         <is>
           <t>#05 BEBIDA - FERMENTADOS</t>
         </is>
       </c>
-      <c r="C1928" s="26" t="inlineStr">
+      <c r="C1928" s="31" t="inlineStr">
         <is>
           <t>VINHO GALIOTTO 750ML TINTO SUAVE</t>
         </is>
       </c>
-      <c r="D1928" s="26" t="inlineStr">
+      <c r="D1928" s="31" t="inlineStr">
         <is>
           <t>VINHO GALIOTTO 750ML TINTO SUAVE</t>
         </is>
       </c>
-      <c r="E1928" s="26" t="inlineStr"/>
+      <c r="E1928" s="31" t="inlineStr"/>
     </row>
     <row r="1929">
       <c r="A1929" t="n">
@@ -39981,25 +39981,25 @@
       </c>
     </row>
     <row r="1957">
-      <c r="A1957" s="26" t="n">
+      <c r="A1957" s="31" t="n">
         <v>100426</v>
       </c>
-      <c r="B1957" s="26" t="inlineStr">
+      <c r="B1957" s="31" t="inlineStr">
         <is>
           <t>#06 LIMPEZA - ALVEJANTES E ÁGUA SANITÁRIA</t>
         </is>
       </c>
-      <c r="C1957" s="26" t="inlineStr">
+      <c r="C1957" s="31" t="inlineStr">
         <is>
           <t>ÁGUA SANIT QBOA 1L MULTIPLO USO</t>
         </is>
       </c>
-      <c r="D1957" s="26" t="inlineStr">
+      <c r="D1957" s="31" t="inlineStr">
         <is>
           <t>ÁGUA SANITÁRIA QBOA 1L</t>
         </is>
       </c>
-      <c r="E1957" s="26" t="inlineStr"/>
+      <c r="E1957" s="31" t="inlineStr"/>
     </row>
     <row r="1958">
       <c r="A1958" s="14" t="n">
@@ -40104,25 +40104,25 @@
       </c>
     </row>
     <row r="1963">
-      <c r="A1963" s="26" t="n">
+      <c r="A1963" s="31" t="n">
         <v>132145</v>
       </c>
-      <c r="B1963" s="26" t="inlineStr">
+      <c r="B1963" s="31" t="inlineStr">
         <is>
           <t>#06 LIMPEZA - ALVEJANTES E ÁGUA SANITÁRIA</t>
         </is>
       </c>
-      <c r="C1963" s="26" t="inlineStr">
+      <c r="C1963" s="31" t="inlineStr">
         <is>
           <t>AGUA SANITARIA YPE BOMBONA 5 LT</t>
         </is>
       </c>
-      <c r="D1963" s="26" t="inlineStr">
+      <c r="D1963" s="31" t="inlineStr">
         <is>
           <t>ÁGUA SANITARIA YPE BOMBONA 5L</t>
         </is>
       </c>
-      <c r="E1963" s="26" t="inlineStr"/>
+      <c r="E1963" s="31" t="inlineStr"/>
     </row>
     <row r="1964">
       <c r="A1964" t="n">
@@ -40145,25 +40145,25 @@
       </c>
     </row>
     <row r="1965">
-      <c r="A1965" s="26" t="n">
+      <c r="A1965" s="31" t="n">
         <v>336903</v>
       </c>
-      <c r="B1965" s="26" t="inlineStr">
+      <c r="B1965" s="31" t="inlineStr">
         <is>
           <t>#06 LIMPEZA - ALVEJANTES E ÁGUA SANITÁRIA</t>
         </is>
       </c>
-      <c r="C1965" s="26" t="inlineStr">
+      <c r="C1965" s="31" t="inlineStr">
         <is>
           <t>PERCARBONATO DE SODIO TUFF 1KG</t>
         </is>
       </c>
-      <c r="D1965" s="26" t="inlineStr">
+      <c r="D1965" s="31" t="inlineStr">
         <is>
           <t>PERCARBONATO DE SODIO TUFF 1KG</t>
         </is>
       </c>
-      <c r="E1965" s="26" t="inlineStr"/>
+      <c r="E1965" s="31" t="inlineStr"/>
     </row>
     <row r="1966">
       <c r="A1966" t="n">
@@ -40206,25 +40206,25 @@
       </c>
     </row>
     <row r="1968">
-      <c r="A1968" s="26" t="n">
+      <c r="A1968" s="31" t="n">
         <v>133368</v>
       </c>
-      <c r="B1968" s="26" t="inlineStr">
+      <c r="B1968" s="31" t="inlineStr">
         <is>
           <t>#06 LIMPEZA - AMACIANTES</t>
         </is>
       </c>
-      <c r="C1968" s="26" t="inlineStr">
+      <c r="C1968" s="31" t="inlineStr">
         <is>
           <t>AMACIANTE +FAMILIA 5L FLORIST ORIGINAL</t>
         </is>
       </c>
-      <c r="D1968" s="26" t="inlineStr">
+      <c r="D1968" s="31" t="inlineStr">
         <is>
           <t>AMACIANTE DE ROUPAS +FAMILIA 5L ORIGINAL</t>
         </is>
       </c>
-      <c r="E1968" s="26" t="inlineStr"/>
+      <c r="E1968" s="31" t="inlineStr"/>
     </row>
     <row r="1969">
       <c r="A1969" t="n">
@@ -40427,25 +40427,25 @@
       </c>
     </row>
     <row r="1979">
-      <c r="A1979" s="26" t="n">
+      <c r="A1979" s="31" t="n">
         <v>339330</v>
       </c>
-      <c r="B1979" s="26" t="inlineStr">
+      <c r="B1979" s="31" t="inlineStr">
         <is>
           <t>#06 LIMPEZA - AMACIANTES</t>
         </is>
       </c>
-      <c r="C1979" s="26" t="inlineStr">
+      <c r="C1979" s="31" t="inlineStr">
         <is>
           <t>AMAC COMFORT CONC 1,5LT BRIDGERTON</t>
         </is>
       </c>
-      <c r="D1979" s="26" t="inlineStr">
+      <c r="D1979" s="31" t="inlineStr">
         <is>
           <t>AMACIANTE DE ROUPAS CONCENTRADO COMFORT 1,5L BRIDGERTON</t>
         </is>
       </c>
-      <c r="E1979" s="26" t="inlineStr"/>
+      <c r="E1979" s="31" t="inlineStr"/>
     </row>
     <row r="1980">
       <c r="A1980" t="n">
@@ -40648,25 +40648,25 @@
       </c>
     </row>
     <row r="1990">
-      <c r="A1990" s="26" t="n">
+      <c r="A1990" s="31" t="n">
         <v>100568</v>
       </c>
-      <c r="B1990" s="26" t="inlineStr">
+      <c r="B1990" s="31" t="inlineStr">
         <is>
           <t>#06 LIMPEZA - AMACIANTES</t>
         </is>
       </c>
-      <c r="C1990" s="26" t="inlineStr">
+      <c r="C1990" s="31" t="inlineStr">
         <is>
           <t>AMAC CONC DOWNY 500ML FRESCOR PRIMAVERA</t>
         </is>
       </c>
-      <c r="D1990" s="26" t="inlineStr">
+      <c r="D1990" s="31" t="inlineStr">
         <is>
           <t>AMACIANTE DE ROUPAS CONCENTRADO DOWNY 500ML FRESCOR PRIMAVERA</t>
         </is>
       </c>
-      <c r="E1990" s="26" t="inlineStr"/>
+      <c r="E1990" s="31" t="inlineStr"/>
     </row>
     <row r="1991">
       <c r="A1991" t="n">
@@ -42918,25 +42918,25 @@
       </c>
     </row>
     <row r="2103">
-      <c r="A2103" s="26" t="n">
+      <c r="A2103" s="31" t="n">
         <v>204823</v>
       </c>
-      <c r="B2103" s="26" t="inlineStr">
+      <c r="B2103" s="31" t="inlineStr">
         <is>
           <t>#06 LIMPEZA - DESINFETANTES</t>
         </is>
       </c>
-      <c r="C2103" s="26" t="inlineStr">
+      <c r="C2103" s="31" t="inlineStr">
         <is>
           <t>DESINFETANTE BAK YPÊ 1LT EUCALIPTO</t>
         </is>
       </c>
-      <c r="D2103" s="26" t="inlineStr">
+      <c r="D2103" s="31" t="inlineStr">
         <is>
           <t>DESINFETANTE YPÊ BAK 1L EUCALIPTO</t>
         </is>
       </c>
-      <c r="E2103" s="26" t="inlineStr"/>
+      <c r="E2103" s="31" t="inlineStr"/>
     </row>
     <row r="2104">
       <c r="A2104" t="n">
@@ -43526,109 +43526,109 @@
       </c>
     </row>
     <row r="2133">
-      <c r="A2133" s="26" t="n">
+      <c r="A2133" s="31" t="n">
         <v>100391</v>
       </c>
-      <c r="B2133" s="26" t="inlineStr">
+      <c r="B2133" s="31" t="inlineStr">
         <is>
           <t>#06 LIMPEZA - DETERGENTES</t>
         </is>
       </c>
-      <c r="C2133" s="26" t="inlineStr">
+      <c r="C2133" s="31" t="inlineStr">
         <is>
           <t>DETERGENTE LIQ YPE 500ML CAPIM LIMAO</t>
         </is>
       </c>
-      <c r="D2133" s="26" t="inlineStr">
+      <c r="D2133" s="31" t="inlineStr">
         <is>
           <t>DETERGENTE LIQUIDO YPÊ 500ML CAPIM LIMÃO</t>
         </is>
       </c>
-      <c r="E2133" s="26" t="inlineStr"/>
+      <c r="E2133" s="31" t="inlineStr"/>
     </row>
     <row r="2134">
-      <c r="A2134" s="26" t="n">
+      <c r="A2134" s="31" t="n">
         <v>100394</v>
       </c>
-      <c r="B2134" s="26" t="inlineStr">
+      <c r="B2134" s="31" t="inlineStr">
         <is>
           <t>#06 LIMPEZA - DETERGENTES</t>
         </is>
       </c>
-      <c r="C2134" s="26" t="inlineStr">
+      <c r="C2134" s="31" t="inlineStr">
         <is>
           <t>DETERGENTE LIQ YPE 500ML CLEAR</t>
         </is>
       </c>
-      <c r="D2134" s="26" t="inlineStr">
+      <c r="D2134" s="31" t="inlineStr">
         <is>
           <t>DETERGENTE LIQUIDO YPÊ 500ML CLEAR</t>
         </is>
       </c>
-      <c r="E2134" s="26" t="inlineStr"/>
+      <c r="E2134" s="31" t="inlineStr"/>
     </row>
     <row r="2135">
-      <c r="A2135" s="26" t="n">
+      <c r="A2135" s="31" t="n">
         <v>100392</v>
       </c>
-      <c r="B2135" s="26" t="inlineStr">
+      <c r="B2135" s="31" t="inlineStr">
         <is>
           <t>#06 LIMPEZA - DETERGENTES</t>
         </is>
       </c>
-      <c r="C2135" s="26" t="inlineStr">
+      <c r="C2135" s="31" t="inlineStr">
         <is>
           <t>DETERGENTE LIQ YPE 500ML CLEAR CARE</t>
         </is>
       </c>
-      <c r="D2135" s="26" t="inlineStr">
+      <c r="D2135" s="31" t="inlineStr">
         <is>
           <t>DETERGENTE LIQUIDO YPÊ 500ML CLEAR CARE</t>
         </is>
       </c>
-      <c r="E2135" s="26" t="inlineStr"/>
+      <c r="E2135" s="31" t="inlineStr"/>
     </row>
     <row r="2136">
-      <c r="A2136" s="26" t="n">
+      <c r="A2136" s="31" t="n">
         <v>100402</v>
       </c>
-      <c r="B2136" s="26" t="inlineStr">
+      <c r="B2136" s="31" t="inlineStr">
         <is>
           <t>#06 LIMPEZA - DETERGENTES</t>
         </is>
       </c>
-      <c r="C2136" s="26" t="inlineStr">
+      <c r="C2136" s="31" t="inlineStr">
         <is>
           <t>DETERGENTE LIQ YPE 500ML COCO</t>
         </is>
       </c>
-      <c r="D2136" s="26" t="inlineStr">
+      <c r="D2136" s="31" t="inlineStr">
         <is>
           <t>DETERGENTE LIQUIDO YPÊ 500ML COCO</t>
         </is>
       </c>
-      <c r="E2136" s="26" t="inlineStr"/>
+      <c r="E2136" s="31" t="inlineStr"/>
     </row>
     <row r="2137">
-      <c r="A2137" s="26" t="n">
+      <c r="A2137" s="31" t="n">
         <v>100403</v>
       </c>
-      <c r="B2137" s="26" t="inlineStr">
+      <c r="B2137" s="31" t="inlineStr">
         <is>
           <t>#06 LIMPEZA - DETERGENTES</t>
         </is>
       </c>
-      <c r="C2137" s="26" t="inlineStr">
+      <c r="C2137" s="31" t="inlineStr">
         <is>
           <t>DETERGENTE LIQ YPE 500ML LIMAO</t>
         </is>
       </c>
-      <c r="D2137" s="26" t="inlineStr">
+      <c r="D2137" s="31" t="inlineStr">
         <is>
           <t>DETERGENTE LIQUIDO YPÊ 500ML LIMAO</t>
         </is>
       </c>
-      <c r="E2137" s="26" t="inlineStr"/>
+      <c r="E2137" s="31" t="inlineStr"/>
     </row>
     <row r="2138">
       <c r="A2138" t="n">
@@ -43651,46 +43651,46 @@
       </c>
     </row>
     <row r="2139">
-      <c r="A2139" s="26" t="n">
+      <c r="A2139" s="31" t="n">
         <v>100393</v>
       </c>
-      <c r="B2139" s="26" t="inlineStr">
+      <c r="B2139" s="31" t="inlineStr">
         <is>
           <t>#06 LIMPEZA - DETERGENTES</t>
         </is>
       </c>
-      <c r="C2139" s="26" t="inlineStr">
+      <c r="C2139" s="31" t="inlineStr">
         <is>
           <t>DETERGENTE LIQ YPE 500ML MACA</t>
         </is>
       </c>
-      <c r="D2139" s="26" t="inlineStr">
+      <c r="D2139" s="31" t="inlineStr">
         <is>
           <t>DETERGENTE LIQUIDO YPÊ 500ML MACA</t>
         </is>
       </c>
-      <c r="E2139" s="26" t="inlineStr"/>
+      <c r="E2139" s="31" t="inlineStr"/>
     </row>
     <row r="2140">
-      <c r="A2140" s="26" t="n">
+      <c r="A2140" s="31" t="n">
         <v>100390</v>
       </c>
-      <c r="B2140" s="26" t="inlineStr">
+      <c r="B2140" s="31" t="inlineStr">
         <is>
           <t>#06 LIMPEZA - DETERGENTES</t>
         </is>
       </c>
-      <c r="C2140" s="26" t="inlineStr">
+      <c r="C2140" s="31" t="inlineStr">
         <is>
           <t>DETERGENTE LIQ YPE 500ML NEUTRO</t>
         </is>
       </c>
-      <c r="D2140" s="26" t="inlineStr">
+      <c r="D2140" s="31" t="inlineStr">
         <is>
           <t>DETERGENTE LIQUIDO YPÊ 500ML NEUTRO</t>
         </is>
       </c>
-      <c r="E2140" s="26" t="inlineStr"/>
+      <c r="E2140" s="31" t="inlineStr"/>
     </row>
     <row r="2141">
       <c r="A2141" t="n">
@@ -44275,25 +44275,25 @@
       </c>
     </row>
     <row r="2170">
-      <c r="A2170" s="26" t="n">
+      <c r="A2170" s="31" t="n">
         <v>113220</v>
       </c>
-      <c r="B2170" s="26" t="inlineStr">
+      <c r="B2170" s="31" t="inlineStr">
         <is>
           <t>#06 LIMPEZA - LIMPADORES</t>
         </is>
       </c>
-      <c r="C2170" s="26" t="inlineStr">
+      <c r="C2170" s="31" t="inlineStr">
         <is>
           <t>LIMPADOR START AZULIM M USO ORIGINAL 500</t>
         </is>
       </c>
-      <c r="D2170" s="26" t="inlineStr">
+      <c r="D2170" s="31" t="inlineStr">
         <is>
           <t>LIMPADOR MULTIUSO AZULIN 500ML ORIGINAL</t>
         </is>
       </c>
-      <c r="E2170" s="26" t="inlineStr"/>
+      <c r="E2170" s="31" t="inlineStr"/>
     </row>
     <row r="2171">
       <c r="A2171" t="n">
@@ -45017,25 +45017,25 @@
       </c>
     </row>
     <row r="2207">
-      <c r="A2207" s="26" t="n">
+      <c r="A2207" s="31" t="n">
         <v>318739</v>
       </c>
-      <c r="B2207" s="26" t="inlineStr">
+      <c r="B2207" s="31" t="inlineStr">
         <is>
           <t>#06 LIMPEZA - LIMPADORES</t>
         </is>
       </c>
-      <c r="C2207" s="26" t="inlineStr">
+      <c r="C2207" s="31" t="inlineStr">
         <is>
           <t>LIMPADOR EM PO CIF 2,4KG LIMPEZA PESADA</t>
         </is>
       </c>
-      <c r="D2207" s="26" t="inlineStr">
+      <c r="D2207" s="31" t="inlineStr">
         <is>
           <t>LIMPADOR EM PÓ CIF 2,4KG LIMPEZA PESADA</t>
         </is>
       </c>
-      <c r="E2207" s="26" t="inlineStr"/>
+      <c r="E2207" s="31" t="inlineStr"/>
     </row>
     <row r="2208">
       <c r="A2208" t="n">
@@ -45499,25 +45499,25 @@
       </c>
     </row>
     <row r="2231">
-      <c r="A2231" s="26" t="n">
+      <c r="A2231" s="31" t="n">
         <v>257710</v>
       </c>
-      <c r="B2231" s="26" t="inlineStr">
+      <c r="B2231" s="31" t="inlineStr">
         <is>
           <t>#06 LIMPEZA - SABÃO</t>
         </is>
       </c>
-      <c r="C2231" s="26" t="inlineStr">
+      <c r="C2231" s="31" t="inlineStr">
         <is>
           <t>SABAO BARRA YPE 5X160GR NEUTRO GLICERINA</t>
         </is>
       </c>
-      <c r="D2231" s="26" t="inlineStr">
+      <c r="D2231" s="31" t="inlineStr">
         <is>
           <t>SABÃO EM BARRA YPÊ 900G NEUTRO</t>
         </is>
       </c>
-      <c r="E2231" s="26" t="inlineStr"/>
+      <c r="E2231" s="31" t="inlineStr"/>
     </row>
     <row r="2232">
       <c r="A2232" t="n">
@@ -46001,46 +46001,46 @@
       </c>
     </row>
     <row r="2256">
-      <c r="A2256" s="26" t="n">
+      <c r="A2256" s="31" t="n">
         <v>286199</v>
       </c>
-      <c r="B2256" s="26" t="inlineStr">
+      <c r="B2256" s="31" t="inlineStr">
         <is>
           <t>#06 LIMPEZA - SABÃO</t>
         </is>
       </c>
-      <c r="C2256" s="26" t="inlineStr">
+      <c r="C2256" s="31" t="inlineStr">
         <is>
           <t>SABAO PO TIXAN YPE 800GR MACIEZ CAIXA</t>
         </is>
       </c>
-      <c r="D2256" s="26" t="inlineStr">
+      <c r="D2256" s="31" t="inlineStr">
         <is>
           <t>SABÃO EM PÓ TIXAN YPÊ CAIXA 800G MACIEZ</t>
         </is>
       </c>
-      <c r="E2256" s="26" t="inlineStr"/>
+      <c r="E2256" s="31" t="inlineStr"/>
     </row>
     <row r="2257">
-      <c r="A2257" s="26" t="n">
+      <c r="A2257" s="31" t="n">
         <v>261083</v>
       </c>
-      <c r="B2257" s="26" t="inlineStr">
+      <c r="B2257" s="31" t="inlineStr">
         <is>
           <t>#06 LIMPEZA - SABÃO</t>
         </is>
       </c>
-      <c r="C2257" s="26" t="inlineStr">
+      <c r="C2257" s="31" t="inlineStr">
         <is>
           <t>SABAO PO TIXAN YPE 800GR PRIMAVERA CAIXA</t>
         </is>
       </c>
-      <c r="D2257" s="26" t="inlineStr">
+      <c r="D2257" s="31" t="inlineStr">
         <is>
           <t>SABÃO EM PÓ TIXAN YPÊ CAIXA 800G PRIMAVERA</t>
         </is>
       </c>
-      <c r="E2257" s="26" t="inlineStr"/>
+      <c r="E2257" s="31" t="inlineStr"/>
     </row>
     <row r="2258">
       <c r="A2258" t="n">
@@ -46263,25 +46263,25 @@
       </c>
     </row>
     <row r="2269">
-      <c r="A2269" s="26" t="n">
+      <c r="A2269" s="31" t="n">
         <v>100373</v>
       </c>
-      <c r="B2269" s="26" t="inlineStr">
+      <c r="B2269" s="31" t="inlineStr">
         <is>
           <t>#06 LIMPEZA - SODAS CAUSTICAS</t>
         </is>
       </c>
-      <c r="C2269" s="26" t="inlineStr">
+      <c r="C2269" s="31" t="inlineStr">
         <is>
           <t>SODA CAUSTICA SOL 1KG</t>
         </is>
       </c>
-      <c r="D2269" s="26" t="inlineStr">
+      <c r="D2269" s="31" t="inlineStr">
         <is>
           <t>SODA CAUSTICA SOL 1KG</t>
         </is>
       </c>
-      <c r="E2269" s="26" t="inlineStr"/>
+      <c r="E2269" s="31" t="inlineStr"/>
     </row>
     <row r="2270">
       <c r="A2270" s="23" t="n">
@@ -55808,25 +55808,25 @@
       </c>
     </row>
     <row r="2746">
-      <c r="A2746" s="26" t="n">
+      <c r="A2746" s="31" t="n">
         <v>144267</v>
       </c>
-      <c r="B2746" s="26" t="inlineStr">
+      <c r="B2746" s="31" t="inlineStr">
         <is>
           <t>#07 HIGIENE PESSOAL - HIGIENE</t>
         </is>
       </c>
-      <c r="C2746" s="26" t="inlineStr">
+      <c r="C2746" s="31" t="inlineStr">
         <is>
           <t>COTONETES TOPZ POTE - 150X1</t>
         </is>
       </c>
-      <c r="D2746" s="26" t="inlineStr">
+      <c r="D2746" s="31" t="inlineStr">
         <is>
           <t>HASTES FLEXIVEIS TOPZ POTE 150UN</t>
         </is>
       </c>
-      <c r="E2746" s="26" t="inlineStr"/>
+      <c r="E2746" s="31" t="inlineStr"/>
     </row>
     <row r="2747">
       <c r="A2747" t="n">
@@ -56532,25 +56532,25 @@
       </c>
     </row>
     <row r="2782">
-      <c r="A2782" s="26" t="n">
+      <c r="A2782" s="31" t="n">
         <v>108140</v>
       </c>
-      <c r="B2782" s="26" t="inlineStr">
+      <c r="B2782" s="31" t="inlineStr">
         <is>
           <t>#07 HIGIENE PESSOAL - INTIMA</t>
         </is>
       </c>
-      <c r="C2782" s="26" t="inlineStr">
+      <c r="C2782" s="31" t="inlineStr">
         <is>
           <t>ABS INT GEL TRIPLA PROT C/ABA 8X1 TRIP P</t>
         </is>
       </c>
-      <c r="D2782" s="26" t="inlineStr">
+      <c r="D2782" s="31" t="inlineStr">
         <is>
           <t>ABSORVENTE INTIMUS GEL 8 X 1 1PTC TRIPLA PROTEÇÃO COM ABAS SECA</t>
         </is>
       </c>
-      <c r="E2782" s="26" t="inlineStr"/>
+      <c r="E2782" s="31" t="inlineStr"/>
     </row>
     <row r="2783">
       <c r="A2783" t="n">
@@ -57954,25 +57954,25 @@
       </c>
     </row>
     <row r="2853">
-      <c r="A2853" s="26" t="n">
+      <c r="A2853" s="31" t="n">
         <v>346964</v>
       </c>
-      <c r="B2853" s="26" t="inlineStr">
+      <c r="B2853" s="31" t="inlineStr">
         <is>
           <t>#07 HIGIENE PESSOAL - PAPEL HIGIENICO</t>
         </is>
       </c>
-      <c r="C2853" s="26" t="inlineStr">
+      <c r="C2853" s="31" t="inlineStr">
         <is>
           <t>PAPEL HIG NOBLE FD 20M</t>
         </is>
       </c>
-      <c r="D2853" s="26" t="inlineStr">
+      <c r="D2853" s="31" t="inlineStr">
         <is>
           <t>PAPEL HIGIENICO NOBLE 12 X 20M FOLHA DUPLA</t>
         </is>
       </c>
-      <c r="E2853" s="26" t="inlineStr"/>
+      <c r="E2853" s="31" t="inlineStr"/>
     </row>
     <row r="2854">
       <c r="A2854" t="n">
@@ -59395,25 +59395,25 @@
       </c>
     </row>
     <row r="2925">
-      <c r="A2925" s="26" t="n">
+      <c r="A2925" s="31" t="n">
         <v>200683</v>
       </c>
-      <c r="B2925" s="26" t="inlineStr">
+      <c r="B2925" s="31" t="inlineStr">
         <is>
           <t>#07 HIGIENE PESSOAL - SABONETE</t>
         </is>
       </c>
-      <c r="C2925" s="26" t="inlineStr">
+      <c r="C2925" s="31" t="inlineStr">
         <is>
           <t>SAB LUX SUAVE LIRIO AZUL 85G</t>
         </is>
       </c>
-      <c r="D2925" s="26" t="inlineStr">
+      <c r="D2925" s="31" t="inlineStr">
         <is>
           <t>SABONETE LUX 85G SUAVE LIRIO AZUL</t>
         </is>
       </c>
-      <c r="E2925" s="26" t="inlineStr"/>
+      <c r="E2925" s="31" t="inlineStr"/>
     </row>
     <row r="2926">
       <c r="A2926" t="n">
@@ -60771,25 +60771,25 @@
       </c>
     </row>
     <row r="2993">
-      <c r="A2993" s="26" t="n">
+      <c r="A2993" s="31" t="n">
         <v>114809</v>
       </c>
-      <c r="B2993" s="26" t="inlineStr">
+      <c r="B2993" s="31" t="inlineStr">
         <is>
           <t>#08 BAZAR - DESCARTÁVEIS</t>
         </is>
       </c>
-      <c r="C2993" s="26" t="inlineStr">
+      <c r="C2993" s="31" t="inlineStr">
         <is>
           <t>COPO DESC MARATA 200ML 100X1</t>
         </is>
       </c>
-      <c r="D2993" s="26" t="inlineStr">
+      <c r="D2993" s="31" t="inlineStr">
         <is>
           <t>COPO DESCARTAVEL MARATA 200ML X 100UN</t>
         </is>
       </c>
-      <c r="E2993" s="26" t="inlineStr"/>
+      <c r="E2993" s="31" t="inlineStr"/>
     </row>
     <row r="2994">
       <c r="A2994" t="n">
@@ -61052,25 +61052,25 @@
       </c>
     </row>
     <row r="3007">
-      <c r="A3007" s="26" t="n">
+      <c r="A3007" s="31" t="n">
         <v>295630</v>
       </c>
-      <c r="B3007" s="26" t="inlineStr">
+      <c r="B3007" s="31" t="inlineStr">
         <is>
           <t>#08 BAZAR - DESCARTÁVEIS</t>
         </is>
       </c>
-      <c r="C3007" s="26" t="inlineStr">
+      <c r="C3007" s="31" t="inlineStr">
         <is>
           <t>SACO PLASTICO PARANA 7KG ROLO C/50UN</t>
         </is>
       </c>
-      <c r="D3007" s="26" t="inlineStr">
+      <c r="D3007" s="31" t="inlineStr">
         <is>
           <t>SACO PLASTICO PARANA 7KG ROLO 50UN</t>
         </is>
       </c>
-      <c r="E3007" s="26" t="inlineStr"/>
+      <c r="E3007" s="31" t="inlineStr"/>
     </row>
     <row r="3008">
       <c r="A3008" t="n">
@@ -61415,25 +61415,25 @@
       <c r="E3024" s="23" t="inlineStr"/>
     </row>
     <row r="3025">
-      <c r="A3025" s="26" t="n">
+      <c r="A3025" s="31" t="n">
         <v>101818</v>
       </c>
-      <c r="B3025" s="26" t="inlineStr">
+      <c r="B3025" s="31" t="inlineStr">
         <is>
           <t>#08 BAZAR - LIMPEZA</t>
         </is>
       </c>
-      <c r="C3025" s="26" t="inlineStr">
+      <c r="C3025" s="31" t="inlineStr">
         <is>
           <t>VASSOURA SANTA MARIA PHENIX 956</t>
         </is>
       </c>
-      <c r="D3025" s="26" t="inlineStr">
+      <c r="D3025" s="31" t="inlineStr">
         <is>
           <t>VASSOURA SANTA MARIA PHENIX 956</t>
         </is>
       </c>
-      <c r="E3025" s="26" t="inlineStr"/>
+      <c r="E3025" s="31" t="inlineStr"/>
     </row>
     <row r="3026">
       <c r="A3026" t="n">
@@ -61636,25 +61636,25 @@
       </c>
     </row>
     <row r="3036">
-      <c r="A3036" s="26" t="n">
+      <c r="A3036" s="31" t="n">
         <v>234144</v>
       </c>
-      <c r="B3036" s="26" t="inlineStr">
+      <c r="B3036" s="31" t="inlineStr">
         <is>
           <t>#08 BAZAR - PANELAS E UTENSÍLIOS DE COZINHA</t>
         </is>
       </c>
-      <c r="C3036" s="26" t="inlineStr">
+      <c r="C3036" s="31" t="inlineStr">
         <is>
           <t>COPO VDO CRISTAR CHOPP 296ML/CM3 PILSENE</t>
         </is>
       </c>
-      <c r="D3036" s="26" t="inlineStr">
+      <c r="D3036" s="31" t="inlineStr">
         <is>
           <t>COPO DE VIDRO CRISTAR 269ML PILSENE CHOPP</t>
         </is>
       </c>
-      <c r="E3036" s="26" t="inlineStr"/>
+      <c r="E3036" s="31" t="inlineStr"/>
     </row>
     <row r="3037">
       <c r="A3037" t="n">
@@ -61677,25 +61677,25 @@
       </c>
     </row>
     <row r="3038">
-      <c r="A3038" s="26" t="n">
+      <c r="A3038" s="31" t="n">
         <v>290165</v>
       </c>
-      <c r="B3038" s="26" t="inlineStr">
+      <c r="B3038" s="31" t="inlineStr">
         <is>
           <t>#08 BAZAR - PANELAS E UTENSÍLIOS DE COZINHA</t>
         </is>
       </c>
-      <c r="C3038" s="26" t="inlineStr">
+      <c r="C3038" s="31" t="inlineStr">
         <is>
           <t>COPO DE VIDRO DARA G4U 300ML BAIXO 52276</t>
         </is>
       </c>
-      <c r="D3038" s="26" t="inlineStr">
+      <c r="D3038" s="31" t="inlineStr">
         <is>
           <t>COPO DE VIDRO DARA G4U 300ML BAIXO</t>
         </is>
       </c>
-      <c r="E3038" s="26" t="inlineStr"/>
+      <c r="E3038" s="31" t="inlineStr"/>
     </row>
     <row r="3039">
       <c r="A3039" t="n">
@@ -61738,25 +61738,25 @@
       </c>
     </row>
     <row r="3041">
-      <c r="A3041" s="26" t="n">
+      <c r="A3041" s="31" t="n">
         <v>112924</v>
       </c>
-      <c r="B3041" s="26" t="inlineStr">
+      <c r="B3041" s="31" t="inlineStr">
         <is>
           <t>#08 BAZAR - PANELAS E UTENSÍLIOS DE COZINHA</t>
         </is>
       </c>
-      <c r="C3041" s="26" t="inlineStr">
+      <c r="C3041" s="31" t="inlineStr">
         <is>
           <t>COPO NADIR AMERICANO DUPLO 300ML</t>
         </is>
       </c>
-      <c r="D3041" s="26" t="inlineStr">
+      <c r="D3041" s="31" t="inlineStr">
         <is>
           <t>COPO DE VIDRO NADIR AMERICANO DUPLO 300ML</t>
         </is>
       </c>
-      <c r="E3041" s="26" t="inlineStr"/>
+      <c r="E3041" s="31" t="inlineStr"/>
     </row>
     <row r="3042">
       <c r="A3042" t="n">
@@ -61779,25 +61779,25 @@
       </c>
     </row>
     <row r="3043">
-      <c r="A3043" s="26" t="n">
+      <c r="A3043" s="31" t="n">
         <v>113856</v>
       </c>
-      <c r="B3043" s="26" t="inlineStr">
+      <c r="B3043" s="31" t="inlineStr">
         <is>
           <t>#08 BAZAR - PANELAS E UTENSÍLIOS DE COZINHA</t>
         </is>
       </c>
-      <c r="C3043" s="26" t="inlineStr">
+      <c r="C3043" s="31" t="inlineStr">
         <is>
           <t>COPO DOSE NADIR 60ML OLE</t>
         </is>
       </c>
-      <c r="D3043" s="26" t="inlineStr">
+      <c r="D3043" s="31" t="inlineStr">
         <is>
           <t>COPO DOSE NADIR OLÉ VIDRO 60ML</t>
         </is>
       </c>
-      <c r="E3043" s="26" t="inlineStr"/>
+      <c r="E3043" s="31" t="inlineStr"/>
     </row>
     <row r="3044">
       <c r="A3044" t="n">
@@ -62140,25 +62140,25 @@
       </c>
     </row>
     <row r="3061">
-      <c r="A3061" s="26" t="n">
+      <c r="A3061" s="31" t="n">
         <v>321965</v>
       </c>
-      <c r="B3061" s="26" t="inlineStr">
+      <c r="B3061" s="31" t="inlineStr">
         <is>
           <t>#08 BAZAR - PAPÉIS DE USO DOMÉSTICO</t>
         </is>
       </c>
-      <c r="C3061" s="26" t="inlineStr">
+      <c r="C3061" s="31" t="inlineStr">
         <is>
           <t>PAPEL TOALHA SANTEPEL 2 ROLOS 120UN SUPE</t>
         </is>
       </c>
-      <c r="D3061" s="26" t="inlineStr">
+      <c r="D3061" s="31" t="inlineStr">
         <is>
           <t>PAPEL TOALHA SANTEPEL 2 X 120UN SUPER ABSORÇÃO</t>
         </is>
       </c>
-      <c r="E3061" s="26" t="inlineStr"/>
+      <c r="E3061" s="31" t="inlineStr"/>
     </row>
     <row r="3062">
       <c r="A3062" t="n">
@@ -62927,25 +62927,25 @@
       </c>
     </row>
     <row r="3100">
-      <c r="A3100" s="26" t="n">
+      <c r="A3100" s="30" t="n">
         <v>341363</v>
       </c>
-      <c r="B3100" s="26" t="inlineStr">
+      <c r="B3100" s="30" t="inlineStr">
         <is>
           <t>#03 AÇOUGUE - #06 EMBUTIDOS E FRIOS</t>
         </is>
       </c>
-      <c r="C3100" s="26" t="inlineStr">
+      <c r="C3100" s="30" t="inlineStr">
         <is>
           <t>LINGUICA PERNIL PERDIGAO 700GR NA BRASA</t>
         </is>
       </c>
-      <c r="D3100" s="26" t="inlineStr">
+      <c r="D3100" s="30" t="inlineStr">
         <is>
           <t>LINGUIÇA DE PERNIL PERDIGÃO 700G NA BRASA</t>
         </is>
       </c>
-      <c r="E3100" s="26" t="inlineStr"/>
+      <c r="E3100" s="30" t="inlineStr"/>
     </row>
     <row r="3101">
       <c r="A3101" s="14" t="n">
@@ -63809,25 +63809,25 @@
       <c r="E3141" s="23" t="inlineStr"/>
     </row>
     <row r="3142">
-      <c r="A3142" s="26" t="n">
+      <c r="A3142" s="31" t="n">
         <v>118011</v>
       </c>
-      <c r="B3142" s="26" t="inlineStr">
+      <c r="B3142" s="31" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - CONDIMENTOS E TEMPEROS</t>
         </is>
       </c>
-      <c r="C3142" s="26" t="inlineStr">
+      <c r="C3142" s="31" t="inlineStr">
         <is>
           <t>COLORIFICO SINHA 500GR</t>
         </is>
       </c>
-      <c r="D3142" s="26" t="inlineStr">
+      <c r="D3142" s="31" t="inlineStr">
         <is>
           <t>COLORIFICO SINHA 500G</t>
         </is>
       </c>
-      <c r="E3142" s="26" t="inlineStr"/>
+      <c r="E3142" s="31" t="inlineStr"/>
     </row>
     <row r="3143">
       <c r="A3143" s="23" t="n">
@@ -63914,382 +63914,382 @@
       <c r="E3146" s="22" t="inlineStr"/>
     </row>
     <row r="3147">
-      <c r="A3147" s="26" t="n">
+      <c r="A3147" s="31" t="n">
         <v>222380</v>
       </c>
-      <c r="B3147" s="26" t="inlineStr">
+      <c r="B3147" s="31" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - CONDIMENTOS E TEMPEROS</t>
         </is>
       </c>
-      <c r="C3147" s="26" t="inlineStr">
+      <c r="C3147" s="31" t="inlineStr">
         <is>
           <t>AZEITONAS MARATA FAT P240G D100G</t>
         </is>
       </c>
-      <c r="D3147" s="26" t="inlineStr">
+      <c r="D3147" s="31" t="inlineStr">
         <is>
           <t>AZEITONAS VERDES MARATA 240G FATIADAS</t>
         </is>
       </c>
-      <c r="E3147" s="26" t="inlineStr"/>
+      <c r="E3147" s="31" t="inlineStr"/>
     </row>
     <row r="3148">
-      <c r="A3148" s="26" t="n">
+      <c r="A3148" s="31" t="n">
         <v>321526</v>
       </c>
-      <c r="B3148" s="26" t="inlineStr">
+      <c r="B3148" s="31" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - BISCOITOS E SALGADINHOS</t>
         </is>
       </c>
-      <c r="C3148" s="26" t="inlineStr">
+      <c r="C3148" s="31" t="inlineStr">
         <is>
           <t>BISCOITO LAMINADO MABEL 300GR CHOCOLATE</t>
         </is>
       </c>
-      <c r="D3148" s="26" t="inlineStr">
+      <c r="D3148" s="31" t="inlineStr">
         <is>
           <t>BISCOITO LAMINADO MABEL 300G CHOCOLATE</t>
         </is>
       </c>
-      <c r="E3148" s="26" t="inlineStr"/>
+      <c r="E3148" s="31" t="inlineStr"/>
     </row>
     <row r="3149">
-      <c r="A3149" s="26" t="n">
+      <c r="A3149" s="31" t="n">
         <v>260315</v>
       </c>
-      <c r="B3149" s="26" t="inlineStr">
+      <c r="B3149" s="31" t="inlineStr">
         <is>
           <t>#08 BAZAR - DESCARTÁVEIS</t>
         </is>
       </c>
-      <c r="C3149" s="26" t="inlineStr">
+      <c r="C3149" s="31" t="inlineStr">
         <is>
           <t>COPO DESC 180ML PS TRANSP PURACASA</t>
         </is>
       </c>
-      <c r="D3149" s="26" t="inlineStr">
+      <c r="D3149" s="31" t="inlineStr">
         <is>
           <t>COPO DESCARTAVEL PURACASA 180ML TRANSPARENTES</t>
         </is>
       </c>
-      <c r="E3149" s="26" t="inlineStr"/>
+      <c r="E3149" s="31" t="inlineStr"/>
     </row>
     <row r="3150">
-      <c r="A3150" s="26" t="n">
+      <c r="A3150" s="31" t="n">
         <v>107946</v>
       </c>
-      <c r="B3150" s="26" t="inlineStr">
+      <c r="B3150" s="31" t="inlineStr">
         <is>
           <t>#07 HIGIENE PESSOAL - HIGIENE BUCAL</t>
         </is>
       </c>
-      <c r="C3150" s="26" t="inlineStr">
+      <c r="C3150" s="31" t="inlineStr">
         <is>
           <t>CR DENTAL COLGATE MPA/MFP 90GR</t>
         </is>
       </c>
-      <c r="D3150" s="26" t="inlineStr">
+      <c r="D3150" s="31" t="inlineStr">
         <is>
           <t>CREME DENTAL COLGATE 90G MENTA REFRESCANTE</t>
         </is>
       </c>
-      <c r="E3150" s="26" t="inlineStr"/>
+      <c r="E3150" s="31" t="inlineStr"/>
     </row>
     <row r="3151">
-      <c r="A3151" s="26" t="n">
+      <c r="A3151" s="31" t="n">
         <v>143493</v>
       </c>
-      <c r="B3151" s="26" t="inlineStr">
+      <c r="B3151" s="31" t="inlineStr">
         <is>
           <t>#08 BAZAR - DESCARTÁVEIS</t>
         </is>
       </c>
-      <c r="C3151" s="26" t="inlineStr">
+      <c r="C3151" s="31" t="inlineStr">
         <is>
           <t>FOLHA DE ALUMINIO WIDA 7,5M X 45CM</t>
         </is>
       </c>
-      <c r="D3151" s="26" t="inlineStr">
+      <c r="D3151" s="31" t="inlineStr">
         <is>
           <t>FOLHA DE ALUMINIO WIDA 7,5M X 45CM</t>
         </is>
       </c>
-      <c r="E3151" s="26" t="inlineStr"/>
+      <c r="E3151" s="31" t="inlineStr"/>
     </row>
     <row r="3152">
-      <c r="A3152" s="26" t="n">
+      <c r="A3152" s="31" t="n">
         <v>228961</v>
       </c>
-      <c r="B3152" s="26" t="inlineStr">
+      <c r="B3152" s="31" t="inlineStr">
         <is>
           <t>#06 LIMPEZA - LIMPADORES</t>
         </is>
       </c>
-      <c r="C3152" s="26" t="inlineStr">
+      <c r="C3152" s="31" t="inlineStr">
         <is>
           <t>GLADE AERO F AGUAS FLORAIS 360ML</t>
         </is>
       </c>
-      <c r="D3152" s="26" t="inlineStr">
+      <c r="D3152" s="31" t="inlineStr">
         <is>
           <t>ODORIZADOR AEROSOL GLADE 360ML AGUAS FLORAIS</t>
         </is>
       </c>
-      <c r="E3152" s="26" t="inlineStr"/>
+      <c r="E3152" s="31" t="inlineStr"/>
     </row>
     <row r="3153">
-      <c r="A3153" s="26" t="n">
+      <c r="A3153" s="31" t="n">
         <v>220933</v>
       </c>
-      <c r="B3153" s="26" t="inlineStr">
+      <c r="B3153" s="31" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - CONDIMENTOS E TEMPEROS</t>
         </is>
       </c>
-      <c r="C3153" s="26" t="inlineStr">
+      <c r="C3153" s="31" t="inlineStr">
         <is>
           <t>KETCHUP HEINZ 1,033KG FR</t>
         </is>
       </c>
-      <c r="D3153" s="26" t="inlineStr">
+      <c r="D3153" s="31" t="inlineStr">
         <is>
           <t>KETCHUP HEINZ 1,033KG</t>
         </is>
       </c>
-      <c r="E3153" s="26" t="inlineStr"/>
+      <c r="E3153" s="31" t="inlineStr"/>
     </row>
     <row r="3154">
-      <c r="A3154" s="26" t="n">
+      <c r="A3154" s="31" t="n">
         <v>148607</v>
       </c>
-      <c r="B3154" s="26" t="inlineStr">
+      <c r="B3154" s="31" t="inlineStr">
         <is>
           <t>#06 LIMPEZA - LIMPADORES</t>
         </is>
       </c>
-      <c r="C3154" s="26" t="inlineStr">
+      <c r="C3154" s="31" t="inlineStr">
         <is>
           <t>LIMP PERF CASA E PERFUME 500ML PASSIONE</t>
         </is>
       </c>
-      <c r="D3154" s="26" t="inlineStr">
+      <c r="D3154" s="31" t="inlineStr">
         <is>
           <t>LIMPADOR PERFUMADO CASA E PERFUME 500ML PASSIONE</t>
         </is>
       </c>
-      <c r="E3154" s="26" t="inlineStr"/>
+      <c r="E3154" s="31" t="inlineStr"/>
     </row>
     <row r="3155">
-      <c r="A3155" s="26" t="n">
+      <c r="A3155" s="31" t="n">
         <v>156417</v>
       </c>
-      <c r="B3155" s="26" t="inlineStr">
+      <c r="B3155" s="31" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - BISCOITOS E SALGADINHOS</t>
         </is>
       </c>
-      <c r="C3155" s="26" t="inlineStr">
+      <c r="C3155" s="31" t="inlineStr">
         <is>
           <t>MILHO DE PIPOCA BONOMILHO 500GR</t>
         </is>
       </c>
-      <c r="D3155" s="26" t="inlineStr">
+      <c r="D3155" s="31" t="inlineStr">
         <is>
           <t>MILHO DE PIPOCA BONOMILHO 500G</t>
         </is>
       </c>
-      <c r="E3155" s="26" t="inlineStr"/>
+      <c r="E3155" s="31" t="inlineStr"/>
     </row>
     <row r="3156">
-      <c r="A3156" s="26" t="n">
+      <c r="A3156" s="31" t="n">
         <v>183229</v>
       </c>
-      <c r="B3156" s="26" t="inlineStr">
+      <c r="B3156" s="31" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - CONDIMENTOS E TEMPEROS</t>
         </is>
       </c>
-      <c r="C3156" s="26" t="inlineStr">
+      <c r="C3156" s="31" t="inlineStr">
         <is>
           <t>MOLHO TOMATE DEZ 300GR ERVAS FINAS</t>
         </is>
       </c>
-      <c r="D3156" s="26" t="inlineStr">
+      <c r="D3156" s="31" t="inlineStr">
         <is>
           <t>MOLHO DE TOMATE DEZ 300G ERVAS FINAS</t>
         </is>
       </c>
-      <c r="E3156" s="26" t="inlineStr"/>
+      <c r="E3156" s="31" t="inlineStr"/>
     </row>
     <row r="3157">
-      <c r="A3157" s="26" t="n">
+      <c r="A3157" s="31" t="n">
         <v>104418</v>
       </c>
-      <c r="B3157" s="26" t="inlineStr">
+      <c r="B3157" s="31" t="inlineStr">
         <is>
           <t>#05 BEBIDA - #00 BEBIDAS GASEIFICADAS</t>
         </is>
       </c>
-      <c r="C3157" s="26" t="inlineStr">
+      <c r="C3157" s="31" t="inlineStr">
         <is>
           <t>REFRIG COCA COLA ZERO 2L</t>
         </is>
       </c>
-      <c r="D3157" s="26" t="inlineStr">
+      <c r="D3157" s="31" t="inlineStr">
         <is>
           <t>REFRIGERANTE COCA COLA ZERO 2L</t>
         </is>
       </c>
-      <c r="E3157" s="26" t="inlineStr"/>
+      <c r="E3157" s="31" t="inlineStr"/>
     </row>
     <row r="3158">
-      <c r="A3158" s="26" t="n">
+      <c r="A3158" s="31" t="n">
         <v>200680</v>
       </c>
-      <c r="B3158" s="26" t="inlineStr">
+      <c r="B3158" s="31" t="inlineStr">
         <is>
           <t>#07 HIGIENE PESSOAL - SABONETE</t>
         </is>
       </c>
-      <c r="C3158" s="26" t="inlineStr">
+      <c r="C3158" s="31" t="inlineStr">
         <is>
           <t>SAB LUX SUAVE BUQUE JASMIM 85G</t>
         </is>
       </c>
-      <c r="D3158" s="26" t="inlineStr">
+      <c r="D3158" s="31" t="inlineStr">
         <is>
           <t>SABONETE LUX 85G SUAVE BUQUE DE JASMIM</t>
         </is>
       </c>
-      <c r="E3158" s="26" t="inlineStr"/>
+      <c r="E3158" s="31" t="inlineStr"/>
     </row>
     <row r="3159">
-      <c r="A3159" s="26" t="n">
+      <c r="A3159" s="31" t="n">
         <v>200684</v>
       </c>
-      <c r="B3159" s="26" t="inlineStr">
+      <c r="B3159" s="31" t="inlineStr">
         <is>
           <t>#07 HIGIENE PESSOAL - SABONETE</t>
         </is>
       </c>
-      <c r="C3159" s="26" t="inlineStr">
+      <c r="C3159" s="31" t="inlineStr">
         <is>
           <t>SAB LUX SUAVE ORQUIDEA NEGRA 85G</t>
         </is>
       </c>
-      <c r="D3159" s="26" t="inlineStr">
+      <c r="D3159" s="31" t="inlineStr">
         <is>
           <t>SABONETE LUX 85G SUAVE ORQUIDEA NEGRA</t>
         </is>
       </c>
-      <c r="E3159" s="26" t="inlineStr"/>
+      <c r="E3159" s="31" t="inlineStr"/>
     </row>
     <row r="3160">
-      <c r="A3160" s="26" t="n">
+      <c r="A3160" s="31" t="n">
         <v>199374</v>
       </c>
-      <c r="B3160" s="26" t="inlineStr">
+      <c r="B3160" s="31" t="inlineStr">
         <is>
           <t>#07 HIGIENE PESSOAL - SABONETE</t>
         </is>
       </c>
-      <c r="C3160" s="26" t="inlineStr">
+      <c r="C3160" s="31" t="inlineStr">
         <is>
           <t>SAB.LUX BOTANICALS 85GR FLOR DE LOTUS</t>
         </is>
       </c>
-      <c r="D3160" s="26" t="inlineStr">
+      <c r="D3160" s="31" t="inlineStr">
         <is>
           <t>SABONETE LUX 85G BOTANICALS FLOR DE LOTUS</t>
         </is>
       </c>
-      <c r="E3160" s="26" t="inlineStr"/>
+      <c r="E3160" s="31" t="inlineStr"/>
     </row>
     <row r="3161">
-      <c r="A3161" s="26" t="n">
+      <c r="A3161" s="31" t="n">
         <v>200697</v>
       </c>
-      <c r="B3161" s="26" t="inlineStr">
+      <c r="B3161" s="31" t="inlineStr">
         <is>
           <t>#07 HIGIENE PESSOAL - SABONETE</t>
         </is>
       </c>
-      <c r="C3161" s="26" t="inlineStr">
+      <c r="C3161" s="31" t="inlineStr">
         <is>
           <t>SAB.LUX BOTANICALS 85GR ROSAS FRANCESAS</t>
         </is>
       </c>
-      <c r="D3161" s="26" t="inlineStr">
+      <c r="D3161" s="31" t="inlineStr">
         <is>
           <t>SABONETE LUX 85G ROSAS FRANCESAS</t>
         </is>
       </c>
-      <c r="E3161" s="26" t="inlineStr"/>
+      <c r="E3161" s="31" t="inlineStr"/>
     </row>
     <row r="3162">
-      <c r="A3162" s="26" t="n">
+      <c r="A3162" s="31" t="n">
         <v>314809</v>
       </c>
-      <c r="B3162" s="26" t="inlineStr">
+      <c r="B3162" s="31" t="inlineStr">
         <is>
           <t>#07 HIGIENE PESSOAL - SABONETE</t>
         </is>
       </c>
-      <c r="C3162" s="26" t="inlineStr">
+      <c r="C3162" s="31" t="inlineStr">
         <is>
           <t>SABONETE LUX 85GR BOTANICALS</t>
         </is>
       </c>
-      <c r="D3162" s="26" t="inlineStr">
+      <c r="D3162" s="31" t="inlineStr">
         <is>
           <t>SABONETE LUX 85G BOTANICALS</t>
         </is>
       </c>
-      <c r="E3162" s="26" t="inlineStr"/>
+      <c r="E3162" s="31" t="inlineStr"/>
     </row>
     <row r="3163">
-      <c r="A3163" s="26" t="n">
+      <c r="A3163" s="30" t="n">
         <v>332652</v>
       </c>
-      <c r="B3163" s="26" t="inlineStr">
+      <c r="B3163" s="30" t="inlineStr">
         <is>
           <t>#03 AÇOUGUE - #06 EMBUTIDOS E FRIOS</t>
         </is>
       </c>
-      <c r="C3163" s="26" t="inlineStr">
+      <c r="C3163" s="30" t="inlineStr">
         <is>
           <t>LINGUICA BACON SEARA 600G TERMO</t>
         </is>
       </c>
-      <c r="D3163" s="26" t="inlineStr">
+      <c r="D3163" s="30" t="inlineStr">
         <is>
           <t>LINGUIÇA DE BACON SEARA 600G TERMO</t>
         </is>
       </c>
-      <c r="E3163" s="26" t="inlineStr"/>
+      <c r="E3163" s="30" t="inlineStr"/>
     </row>
     <row r="3164">
-      <c r="A3164" s="26" t="n">
+      <c r="A3164" s="30" t="n">
         <v>289484</v>
       </c>
-      <c r="B3164" s="26" t="inlineStr">
+      <c r="B3164" s="30" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - GORDURAS E MARGARINAS</t>
         </is>
       </c>
-      <c r="C3164" s="26" t="inlineStr">
+      <c r="C3164" s="30" t="inlineStr">
         <is>
           <t>MANTEIGA COMUM GRANSELETTO 200G  COM SAL</t>
         </is>
       </c>
-      <c r="D3164" s="26" t="inlineStr">
+      <c r="D3164" s="30" t="inlineStr">
         <is>
           <t>MANTEIGA COMUM GRANSELETTO 200G COM SAL</t>
         </is>
       </c>
-      <c r="E3164" s="26" t="inlineStr"/>
+      <c r="E3164" s="30" t="inlineStr"/>
     </row>
     <row r="3165">
       <c r="A3165" s="30" t="n">

--- a/produtos_cadastrados.xlsx
+++ b/produtos_cadastrados.xlsx
@@ -9,7 +9,7 @@
     <sheet name="Produtos" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Produtos'!$A$1:$E$3200</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Produtos'!$A$1:$E$3207</definedName>
   </definedNames>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="31">
+  <fonts count="32">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -168,15 +168,21 @@
     </font>
     <font>
       <name val="Calibri"/>
+      <color rgb="FF000000"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="FF000000"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
       <color rgb="00000000"/>
       <sz val="11"/>
     </font>
-    <font>
-      <b val="1"/>
-      <color rgb="009C0006"/>
-    </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -193,12 +199,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="0045A045"/>
         <bgColor rgb="0045A045"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFC7CE"/>
-        <bgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
   </fills>
@@ -229,7 +229,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
@@ -260,19 +260,13 @@
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="27" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="28" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="30" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="29" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="25" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="26" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="23" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="31" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="30" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="20" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -638,14 +632,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3200"/>
+  <dimension ref="A1:E3207"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7.42578125" bestFit="1" customWidth="1" min="1" max="1"/>
     <col width="48.85546875" bestFit="1" customWidth="1" min="2" max="2"/>
     <col width="64.85546875" bestFit="1" customWidth="1" min="3" max="3"/>
     <col width="82" bestFit="1" customWidth="1" min="4" max="4"/>
-    <col width="44.140625" bestFit="1" customWidth="1" min="5" max="5"/>
+    <col width="40.28515625" bestFit="1" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -717,25 +711,25 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="27" t="n">
+      <c r="A4" s="28" t="n">
         <v>100031</v>
       </c>
-      <c r="B4" s="27" t="inlineStr">
+      <c r="B4" s="28" t="inlineStr">
         <is>
           <t>#01 MERCEARIA - #01 CEREAIS E GRÃOS</t>
         </is>
       </c>
-      <c r="C4" s="27" t="inlineStr">
+      <c r="C4" s="28" t="inlineStr">
         <is>
           <t>ARROZ REI ARTHUR 5 KG BRANCO TIPO 1</t>
         </is>
       </c>
-      <c r="D4" s="27" t="inlineStr">
+      <c r="D4" s="28" t="inlineStr">
         <is>
           <t>ARROZ REI ARTHUR PCT 5KG TIPO 1 BRANCO</t>
         </is>
       </c>
-      <c r="E4" s="27" t="inlineStr"/>
+      <c r="E4" s="28" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -758,25 +752,25 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="33" t="n">
+      <c r="A6" s="32" t="n">
         <v>100038</v>
       </c>
-      <c r="B6" s="33" t="inlineStr">
+      <c r="B6" s="32" t="inlineStr">
         <is>
           <t>#01 MERCEARIA - #01 CEREAIS E GRÃOS</t>
         </is>
       </c>
-      <c r="C6" s="33" t="inlineStr">
+      <c r="C6" s="32" t="inlineStr">
         <is>
           <t>ARROZ BRANCO BREJEIRO 5KG TIPO 1</t>
         </is>
       </c>
-      <c r="D6" s="33" t="inlineStr">
+      <c r="D6" s="32" t="inlineStr">
         <is>
           <t>ARROZ BREJEIRO PCT 5KG TIPO 1 BRANCO</t>
         </is>
       </c>
-      <c r="E6" s="33" t="inlineStr"/>
+      <c r="E6" s="32" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -920,25 +914,25 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="27" t="n">
+      <c r="A14" s="28" t="n">
         <v>225003</v>
       </c>
-      <c r="B14" s="27" t="inlineStr">
+      <c r="B14" s="28" t="inlineStr">
         <is>
           <t>#01 MERCEARIA - #01 CEREAIS E GRÃOS</t>
         </is>
       </c>
-      <c r="C14" s="27" t="inlineStr">
+      <c r="C14" s="28" t="inlineStr">
         <is>
           <t>ARROZ RAMPINELLI 5KG TIPO1</t>
         </is>
       </c>
-      <c r="D14" s="27" t="inlineStr">
+      <c r="D14" s="28" t="inlineStr">
         <is>
           <t>ARROZ RAMPINELLI PCT 5KG TIPO 1 BRANCO</t>
         </is>
       </c>
-      <c r="E14" s="27" t="inlineStr"/>
+      <c r="E14" s="28" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -961,25 +955,25 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="27" t="n">
+      <c r="A16" s="32" t="n">
         <v>229173</v>
       </c>
-      <c r="B16" s="27" t="inlineStr">
+      <c r="B16" s="32" t="inlineStr">
         <is>
           <t>#01 MERCEARIA - #01 CEREAIS E GRÃOS</t>
         </is>
       </c>
-      <c r="C16" s="27" t="inlineStr">
+      <c r="C16" s="32" t="inlineStr">
         <is>
           <t>ARROZ BRANCO KIDELICIA 5KG TIPO 1</t>
         </is>
       </c>
-      <c r="D16" s="27" t="inlineStr">
+      <c r="D16" s="32" t="inlineStr">
         <is>
           <t>ARROZ KIDELICIA PCT 5KG TIPO 1 BRANCO</t>
         </is>
       </c>
-      <c r="E16" s="27" t="inlineStr"/>
+      <c r="E16" s="32" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -1062,25 +1056,25 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="14" t="n">
+      <c r="A21" s="32" t="n">
         <v>301961</v>
       </c>
-      <c r="B21" s="14" t="inlineStr">
+      <c r="B21" s="32" t="inlineStr">
         <is>
           <t>#01 MERCEARIA - #01 CEREAIS E GRÃOS</t>
         </is>
       </c>
-      <c r="C21" s="14" t="inlineStr">
+      <c r="C21" s="32" t="inlineStr">
         <is>
           <t>ARROZ SELECAO 5KG BRANCO TIPO1</t>
         </is>
       </c>
-      <c r="D21" s="14" t="inlineStr">
+      <c r="D21" s="32" t="inlineStr">
         <is>
           <t>ARROZ SELEÇÃO PCT 5KG TIPO 1 BRANCO</t>
         </is>
       </c>
-      <c r="E21" s="14" t="inlineStr"/>
+      <c r="E21" s="32" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="25" t="n">
@@ -1204,25 +1198,25 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="27" t="n">
+      <c r="A28" s="28" t="n">
         <v>343313</v>
       </c>
-      <c r="B28" s="27" t="inlineStr">
+      <c r="B28" s="28" t="inlineStr">
         <is>
           <t>#01 MERCEARIA - #01 CEREAIS E GRÃOS</t>
         </is>
       </c>
-      <c r="C28" s="27" t="inlineStr">
+      <c r="C28" s="28" t="inlineStr">
         <is>
           <t>ARROZ BRANCO RAMPINELLI 5KG TIPO 1 PREMI</t>
         </is>
       </c>
-      <c r="D28" s="27" t="inlineStr">
+      <c r="D28" s="28" t="inlineStr">
         <is>
           <t>ARROZ RAMPINELLI PREMIUM PCT 5KG TIPO 1 BRANCO</t>
         </is>
       </c>
-      <c r="E28" s="27" t="inlineStr"/>
+      <c r="E28" s="28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -1305,25 +1299,25 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="27" t="n">
+      <c r="A33" s="28" t="n">
         <v>116507</v>
       </c>
-      <c r="B33" s="27" t="inlineStr">
+      <c r="B33" s="28" t="inlineStr">
         <is>
           <t>#01 MERCEARIA - #02 FEIJÕES E LEGUMINOSAS</t>
         </is>
       </c>
-      <c r="C33" s="27" t="inlineStr">
+      <c r="C33" s="28" t="inlineStr">
         <is>
           <t>FEIJÃO DA CASA 1KG CARIOCA</t>
         </is>
       </c>
-      <c r="D33" s="27" t="inlineStr">
+      <c r="D33" s="28" t="inlineStr">
         <is>
           <t>FEIJÃO CARIOCA DA CASA 1KG</t>
         </is>
       </c>
-      <c r="E33" s="27" t="inlineStr"/>
+      <c r="E33" s="28" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -1386,25 +1380,25 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="27" t="n">
+      <c r="A37" s="28" t="n">
         <v>132367</v>
       </c>
-      <c r="B37" s="27" t="inlineStr">
+      <c r="B37" s="28" t="inlineStr">
         <is>
           <t>#01 MERCEARIA - #02 FEIJÕES E LEGUMINOSAS</t>
         </is>
       </c>
-      <c r="C37" s="27" t="inlineStr">
+      <c r="C37" s="28" t="inlineStr">
         <is>
           <t>AMENDOIM PACHA TORRADO MOIDO 500GR</t>
         </is>
       </c>
-      <c r="D37" s="27" t="inlineStr">
+      <c r="D37" s="28" t="inlineStr">
         <is>
           <t>AMENDOIM PACHA 500G TORRADO E MOIDO</t>
         </is>
       </c>
-      <c r="E37" s="27" t="inlineStr"/>
+      <c r="E37" s="28" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -1529,24 +1523,25 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" t="n">
+      <c r="A44" s="32" t="n">
         <v>167687</v>
       </c>
-      <c r="B44" t="inlineStr">
+      <c r="B44" s="32" t="inlineStr">
         <is>
           <t>#01 MERCEARIA - #02 FEIJÕES E LEGUMINOSAS</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr">
+      <c r="C44" s="32" t="inlineStr">
         <is>
           <t>FEIJÃO CARIOCA JOAOZINHO PREMIUM 1KG</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr">
+      <c r="D44" s="32" t="inlineStr">
         <is>
           <t>FEIJÃO CARIOCA JOÃOZINHO 1KG PREMIUM</t>
         </is>
       </c>
+      <c r="E44" s="32" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -1952,25 +1947,25 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="27" t="n">
+      <c r="A65" s="32" t="n">
         <v>167128</v>
       </c>
-      <c r="B65" s="27" t="inlineStr">
+      <c r="B65" s="32" t="inlineStr">
         <is>
           <t>#01 MERCEARIA - #03 ÓLEOS E GORDURAS</t>
         </is>
       </c>
-      <c r="C65" s="27" t="inlineStr">
+      <c r="C65" s="32" t="inlineStr">
         <is>
           <t>ÓLEO SOJA REFINADO CONCORDIA 900ML</t>
         </is>
       </c>
-      <c r="D65" s="27" t="inlineStr">
+      <c r="D65" s="32" t="inlineStr">
         <is>
           <t>ÓLEO DE SOJA CONCORDIA 900ML</t>
         </is>
       </c>
-      <c r="E65" s="27" t="inlineStr"/>
+      <c r="E65" s="32" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -2274,25 +2269,25 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="27" t="n">
+      <c r="A81" s="32" t="n">
         <v>345404</v>
       </c>
-      <c r="B81" s="27" t="inlineStr">
+      <c r="B81" s="32" t="inlineStr">
         <is>
           <t>#01 MERCEARIA - #04 AÇÚCAR E ADOÇANTES</t>
         </is>
       </c>
-      <c r="C81" s="27" t="inlineStr">
+      <c r="C81" s="32" t="inlineStr">
         <is>
           <t>ACUCAR ECO ACUCAR 2KG CRISTAL</t>
         </is>
       </c>
-      <c r="D81" s="27" t="inlineStr">
+      <c r="D81" s="32" t="inlineStr">
         <is>
           <t>AÇUCAR ECOÇUCAR 2KG CRISTAL</t>
         </is>
       </c>
-      <c r="E81" s="27" t="inlineStr"/>
+      <c r="E81" s="32" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -2355,25 +2350,25 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="27" t="n">
+      <c r="A85" s="32" t="n">
         <v>101137</v>
       </c>
-      <c r="B85" s="27" t="inlineStr">
+      <c r="B85" s="32" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - ACHOCOLATADOS E CAFÉ</t>
         </is>
       </c>
-      <c r="C85" s="27" t="inlineStr">
+      <c r="C85" s="32" t="inlineStr">
         <is>
           <t>CAFÉ MARATA 250GR A VACUO TRADIC</t>
         </is>
       </c>
-      <c r="D85" s="27" t="inlineStr">
+      <c r="D85" s="32" t="inlineStr">
         <is>
           <t>CAFÉ MARATA 250G TRADICIONAL</t>
         </is>
       </c>
-      <c r="E85" s="27" t="inlineStr"/>
+      <c r="E85" s="32" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -2416,25 +2411,25 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="27" t="n">
+      <c r="A88" s="32" t="n">
         <v>104679</v>
       </c>
-      <c r="B88" s="27" t="inlineStr">
+      <c r="B88" s="32" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - ACHOCOLATADOS E CAFÉ</t>
         </is>
       </c>
-      <c r="C88" s="27" t="inlineStr">
+      <c r="C88" s="32" t="inlineStr">
         <is>
           <t>ACHOC UHT DANETTE LIQ 200ML CHOCOLATE</t>
         </is>
       </c>
-      <c r="D88" s="27" t="inlineStr">
+      <c r="D88" s="32" t="inlineStr">
         <is>
           <t>ACHOCOLATADO DANETTE 200ML</t>
         </is>
       </c>
-      <c r="E88" s="27" t="inlineStr"/>
+      <c r="E88" s="32" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -2657,24 +2652,25 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="9" t="n">
+      <c r="A100" s="32" t="n">
         <v>174298</v>
       </c>
-      <c r="B100" s="9" t="inlineStr">
+      <c r="B100" s="32" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - ACHOCOLATADOS E CAFÉ</t>
         </is>
       </c>
-      <c r="C100" s="9" t="inlineStr">
+      <c r="C100" s="32" t="inlineStr">
         <is>
           <t>CAFE MOIDO RANCHEIRO 250GR TRAD</t>
         </is>
       </c>
-      <c r="D100" s="9" t="inlineStr">
+      <c r="D100" s="32" t="inlineStr">
         <is>
           <t>CAFÉ RANCHEIRO 250G TRADICIONAL</t>
         </is>
       </c>
+      <c r="E100" s="32" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -2777,25 +2773,25 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="27" t="n">
+      <c r="A106" s="32" t="n">
         <v>255232</v>
       </c>
-      <c r="B106" s="27" t="inlineStr">
+      <c r="B106" s="32" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - ACHOCOLATADOS E CAFÉ</t>
         </is>
       </c>
-      <c r="C106" s="27" t="inlineStr">
+      <c r="C106" s="32" t="inlineStr">
         <is>
           <t>ACHOC PO TODDY 750G</t>
         </is>
       </c>
-      <c r="D106" s="27" t="inlineStr">
+      <c r="D106" s="32" t="inlineStr">
         <is>
           <t>ACHOCOLATADO EM PÓ TODDY 750G</t>
         </is>
       </c>
-      <c r="E106" s="27" t="inlineStr"/>
+      <c r="E106" s="32" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -2979,25 +2975,25 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="27" t="n">
+      <c r="A116" s="28" t="n">
         <v>344310</v>
       </c>
-      <c r="B116" s="27" t="inlineStr">
+      <c r="B116" s="28" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - ACHOCOLATADOS E CAFÉ</t>
         </is>
       </c>
-      <c r="C116" s="27" t="inlineStr">
+      <c r="C116" s="28" t="inlineStr">
         <is>
           <t>CAFE MAMORE 250G TRAD TORRADO E MOIDO</t>
         </is>
       </c>
-      <c r="D116" s="27" t="inlineStr">
+      <c r="D116" s="28" t="inlineStr">
         <is>
           <t>CAFE MAMORE 250G TRADICIONAL TORRADO E MOIDO</t>
         </is>
       </c>
-      <c r="E116" s="27" t="inlineStr"/>
+      <c r="E116" s="28" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -3201,25 +3197,25 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="25" t="n">
+      <c r="A127" s="32" t="n">
         <v>156417</v>
       </c>
-      <c r="B127" s="25" t="inlineStr">
+      <c r="B127" s="32" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - BISCOITOS E SALGADINHOS</t>
         </is>
       </c>
-      <c r="C127" s="25" t="inlineStr">
+      <c r="C127" s="32" t="inlineStr">
         <is>
           <t>MILHO DE PIPOCA BONOMILHO 500GR</t>
         </is>
       </c>
-      <c r="D127" s="25" t="inlineStr">
+      <c r="D127" s="32" t="inlineStr">
         <is>
           <t>MILHO DE PIPOCA BONOMILHO 500G</t>
         </is>
       </c>
-      <c r="E127" s="25" t="inlineStr"/>
+      <c r="E127" s="32" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -3763,25 +3759,25 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="27" t="n">
+      <c r="A155" s="32" t="n">
         <v>250013</v>
       </c>
-      <c r="B155" s="27" t="inlineStr">
+      <c r="B155" s="32" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - BISCOITOS E SALGADINHOS</t>
         </is>
       </c>
-      <c r="C155" s="27" t="inlineStr">
+      <c r="C155" s="32" t="inlineStr">
         <is>
           <t>BISC MARILAN CRACKER ESPECIAL 350GR</t>
         </is>
       </c>
-      <c r="D155" s="27" t="inlineStr">
+      <c r="D155" s="32" t="inlineStr">
         <is>
           <t>BISCOITO CREAM CRACKER MARILAN 350G ESPECIAL</t>
         </is>
       </c>
-      <c r="E155" s="27" t="inlineStr"/>
+      <c r="E155" s="32" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -3884,25 +3880,25 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="27" t="n">
+      <c r="A161" s="28" t="n">
         <v>253813</v>
       </c>
-      <c r="B161" s="27" t="inlineStr">
+      <c r="B161" s="28" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - BISCOITOS E SALGADINHOS</t>
         </is>
       </c>
-      <c r="C161" s="27" t="inlineStr">
+      <c r="C161" s="28" t="inlineStr">
         <is>
           <t>BISC MARILAN TORTINHA LIMAO 140G</t>
         </is>
       </c>
-      <c r="D161" s="27" t="inlineStr">
+      <c r="D161" s="28" t="inlineStr">
         <is>
           <t>BISCOITO TORTINHA MARILAN 140G LIMÃO</t>
         </is>
       </c>
-      <c r="E161" s="27" t="inlineStr"/>
+      <c r="E161" s="28" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="n">
@@ -4025,25 +4021,25 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="27" t="n">
+      <c r="A168" s="28" t="n">
         <v>262392</v>
       </c>
-      <c r="B168" s="27" t="inlineStr">
+      <c r="B168" s="28" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - BISCOITOS E SALGADINHOS</t>
         </is>
       </c>
-      <c r="C168" s="27" t="inlineStr">
+      <c r="C168" s="28" t="inlineStr">
         <is>
           <t>BISCOITO FORTALEZA 350GR MARIA TRADICION</t>
         </is>
       </c>
-      <c r="D168" s="27" t="inlineStr">
+      <c r="D168" s="28" t="inlineStr">
         <is>
           <t>BISCOITO MARIA FORTALEZA 350G TRADICIONAL</t>
         </is>
       </c>
-      <c r="E168" s="27" t="inlineStr"/>
+      <c r="E168" s="28" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="n">
@@ -4666,25 +4662,25 @@
       </c>
     </row>
     <row r="200">
-      <c r="A200" s="27" t="n">
+      <c r="A200" s="32" t="n">
         <v>286197</v>
       </c>
-      <c r="B200" s="27" t="inlineStr">
+      <c r="B200" s="32" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - BISCOITOS E SALGADINHOS</t>
         </is>
       </c>
-      <c r="C200" s="27" t="inlineStr">
+      <c r="C200" s="32" t="inlineStr">
         <is>
           <t>BISCOITO MABEL 600GR ROSCA COCO</t>
         </is>
       </c>
-      <c r="D200" s="27" t="inlineStr">
+      <c r="D200" s="32" t="inlineStr">
         <is>
           <t>BISCOITO ROSQUINHA MABEL 600G COCO</t>
         </is>
       </c>
-      <c r="E200" s="27" t="inlineStr"/>
+      <c r="E200" s="32" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" t="n">
@@ -4727,25 +4723,25 @@
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="27" t="n">
+      <c r="A203" s="28" t="n">
         <v>286380</v>
       </c>
-      <c r="B203" s="27" t="inlineStr">
+      <c r="B203" s="28" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - BISCOITOS E SALGADINHOS</t>
         </is>
       </c>
-      <c r="C203" s="27" t="inlineStr">
+      <c r="C203" s="28" t="inlineStr">
         <is>
           <t>BISCOITO MARIA FORTALEZA CHOCOLATE 350GR</t>
         </is>
       </c>
-      <c r="D203" s="27" t="inlineStr">
+      <c r="D203" s="28" t="inlineStr">
         <is>
           <t>BISCOITO MARIA FORTALEZA 350G CHOCOLATE</t>
         </is>
       </c>
-      <c r="E203" s="27" t="inlineStr"/>
+      <c r="E203" s="28" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" t="n">
@@ -5271,25 +5267,25 @@
       </c>
     </row>
     <row r="230">
-      <c r="A230" s="27" t="n">
+      <c r="A230" s="28" t="n">
         <v>334126</v>
       </c>
-      <c r="B230" s="27" t="inlineStr">
+      <c r="B230" s="28" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - BISCOITOS E SALGADINHOS</t>
         </is>
       </c>
-      <c r="C230" s="27" t="inlineStr">
+      <c r="C230" s="28" t="inlineStr">
         <is>
           <t>BOLACHA NANA E CIA 230GR  SABOR MANTEIGA</t>
         </is>
       </c>
-      <c r="D230" s="27" t="inlineStr">
+      <c r="D230" s="28" t="inlineStr">
         <is>
           <t>BOLACHA NANA E CIA 230G SABOR MANTEIGA</t>
         </is>
       </c>
-      <c r="E230" s="27" t="inlineStr"/>
+      <c r="E230" s="28" t="inlineStr"/>
     </row>
     <row r="231">
       <c r="A231" t="n">
@@ -5372,25 +5368,25 @@
       </c>
     </row>
     <row r="235">
-      <c r="A235" s="27" t="n">
+      <c r="A235" s="28" t="n">
         <v>338634</v>
       </c>
-      <c r="B235" s="27" t="inlineStr">
+      <c r="B235" s="28" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - BISCOITOS E SALGADINHOS</t>
         </is>
       </c>
-      <c r="C235" s="27" t="inlineStr">
+      <c r="C235" s="28" t="inlineStr">
         <is>
           <t>BISCOITO RECH AMORI 125GR MISTERIO A</t>
         </is>
       </c>
-      <c r="D235" s="27" t="inlineStr">
+      <c r="D235" s="28" t="inlineStr">
         <is>
           <t>BISCOITO RECHEADO AMORI 125G MISTÉRIO A</t>
         </is>
       </c>
-      <c r="E235" s="27" t="inlineStr"/>
+      <c r="E235" s="28" t="inlineStr"/>
     </row>
     <row r="236">
       <c r="A236" t="n">
@@ -5713,25 +5709,25 @@
       </c>
     </row>
     <row r="252">
-      <c r="A252" s="27" t="n">
+      <c r="A252" s="28" t="n">
         <v>348447</v>
       </c>
-      <c r="B252" s="27" t="inlineStr">
+      <c r="B252" s="28" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - BISCOITOS E SALGADINHOS</t>
         </is>
       </c>
-      <c r="C252" s="27" t="inlineStr">
+      <c r="C252" s="28" t="inlineStr">
         <is>
           <t>BISCOITO DE POLVILHO AZEDO NANA E CIA 10</t>
         </is>
       </c>
-      <c r="D252" s="27" t="inlineStr">
+      <c r="D252" s="28" t="inlineStr">
         <is>
           <t>BISCOITO DE POLVILHO AZEDO NANA E CIA 100G PARMESÃO</t>
         </is>
       </c>
-      <c r="E252" s="27" t="inlineStr"/>
+      <c r="E252" s="28" t="inlineStr"/>
     </row>
     <row r="253">
       <c r="A253" t="n">
@@ -7016,25 +7012,25 @@
       </c>
     </row>
     <row r="317">
-      <c r="A317" s="27" t="n">
+      <c r="A317" s="28" t="n">
         <v>341362</v>
       </c>
-      <c r="B317" s="27" t="inlineStr">
+      <c r="B317" s="28" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - CHOCOLATES E DOCES</t>
         </is>
       </c>
-      <c r="C317" s="27" t="inlineStr">
+      <c r="C317" s="28" t="inlineStr">
         <is>
           <t>BOMBONS GAROTO 220G SORTIDOS CAIXA</t>
         </is>
       </c>
-      <c r="D317" s="27" t="inlineStr">
+      <c r="D317" s="28" t="inlineStr">
         <is>
           <t>BOMBOM GAROTO CAIXA 220G SORTIDOS</t>
         </is>
       </c>
-      <c r="E317" s="27" t="inlineStr"/>
+      <c r="E317" s="28" t="inlineStr"/>
     </row>
     <row r="318">
       <c r="A318" s="8" t="n">
@@ -7277,25 +7273,25 @@
       </c>
     </row>
     <row r="330">
-      <c r="A330" s="34" t="n">
+      <c r="A330" s="29" t="n">
         <v>346331</v>
       </c>
-      <c r="B330" s="34" t="inlineStr">
+      <c r="B330" s="29" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - COMIDAS TIPICAS</t>
         </is>
       </c>
-      <c r="C330" s="34" t="inlineStr">
+      <c r="C330" s="29" t="inlineStr">
         <is>
           <t>JAMBU PAVAO 500GR</t>
         </is>
       </c>
-      <c r="D330" s="34" t="inlineStr">
+      <c r="D330" s="29" t="inlineStr">
         <is>
           <t>JAMBU PAVÃO 500G</t>
         </is>
       </c>
-      <c r="E330" s="34" t="inlineStr"/>
+      <c r="E330" s="29" t="inlineStr"/>
     </row>
     <row r="331">
       <c r="A331" t="n">
@@ -7418,25 +7414,25 @@
       </c>
     </row>
     <row r="337">
-      <c r="A337" s="27" t="n">
+      <c r="A337" s="28" t="n">
         <v>100780</v>
       </c>
-      <c r="B337" s="27" t="inlineStr">
+      <c r="B337" s="28" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - CONDIMENTOS E TEMPEROS</t>
         </is>
       </c>
-      <c r="C337" s="27" t="inlineStr">
+      <c r="C337" s="28" t="inlineStr">
         <is>
           <t>EXT TOMATE OLE 190GR CP</t>
         </is>
       </c>
-      <c r="D337" s="27" t="inlineStr">
+      <c r="D337" s="28" t="inlineStr">
         <is>
           <t>EXTRATO DE TOMATE OLE COPO 190G</t>
         </is>
       </c>
-      <c r="E337" s="27" t="inlineStr"/>
+      <c r="E337" s="28" t="inlineStr"/>
     </row>
     <row r="338">
       <c r="A338" t="n">
@@ -7560,25 +7556,25 @@
       </c>
     </row>
     <row r="344">
-      <c r="A344" s="27" t="n">
+      <c r="A344" s="28" t="n">
         <v>100876</v>
       </c>
-      <c r="B344" s="27" t="inlineStr">
+      <c r="B344" s="28" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - CONDIMENTOS E TEMPEROS</t>
         </is>
       </c>
-      <c r="C344" s="27" t="inlineStr">
+      <c r="C344" s="28" t="inlineStr">
         <is>
           <t>TEMPERO ARISCO 1KG COMPLETO C/ PIMENTA</t>
         </is>
       </c>
-      <c r="D344" s="27" t="inlineStr">
+      <c r="D344" s="28" t="inlineStr">
         <is>
           <t>TEMPERO COMPLETO ARISCO 1KG COM PIMENTA</t>
         </is>
       </c>
-      <c r="E344" s="27" t="inlineStr"/>
+      <c r="E344" s="28" t="inlineStr"/>
     </row>
     <row r="345">
       <c r="A345" t="n">
@@ -7641,25 +7637,25 @@
       </c>
     </row>
     <row r="348">
-      <c r="A348" s="27" t="n">
+      <c r="A348" s="32" t="n">
         <v>100884</v>
       </c>
-      <c r="B348" s="27" t="inlineStr">
+      <c r="B348" s="32" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - CONDIMENTOS E TEMPEROS</t>
         </is>
       </c>
-      <c r="C348" s="27" t="inlineStr">
+      <c r="C348" s="32" t="inlineStr">
         <is>
           <t>TEMPERO SAZON 60GR SCH CARNES/VERMELHO</t>
         </is>
       </c>
-      <c r="D348" s="27" t="inlineStr">
+      <c r="D348" s="32" t="inlineStr">
         <is>
           <t>TEMPERO EM PÓ SAZON SACHÊ 60G CARNES/VERMELHO</t>
         </is>
       </c>
-      <c r="E348" s="27" t="inlineStr"/>
+      <c r="E348" s="32" t="inlineStr"/>
     </row>
     <row r="349">
       <c r="A349" t="n">
@@ -7802,25 +7798,25 @@
       </c>
     </row>
     <row r="356">
-      <c r="A356" s="27" t="n">
+      <c r="A356" s="32" t="n">
         <v>101728</v>
       </c>
-      <c r="B356" s="27" t="inlineStr">
+      <c r="B356" s="32" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - CONDIMENTOS E TEMPEROS</t>
         </is>
       </c>
-      <c r="C356" s="27" t="inlineStr">
+      <c r="C356" s="32" t="inlineStr">
         <is>
           <t>MAIONESE HELLMANNS 500GR TRADICIONAL</t>
         </is>
       </c>
-      <c r="D356" s="27" t="inlineStr">
+      <c r="D356" s="32" t="inlineStr">
         <is>
           <t>MAIONESE HELLMANNS 500G TRADICIONAL</t>
         </is>
       </c>
-      <c r="E356" s="27" t="inlineStr"/>
+      <c r="E356" s="32" t="inlineStr"/>
     </row>
     <row r="357">
       <c r="A357" t="n">
@@ -8023,25 +8019,25 @@
       </c>
     </row>
     <row r="367">
-      <c r="A367" s="27" t="n">
+      <c r="A367" s="28" t="n">
         <v>106960</v>
       </c>
-      <c r="B367" s="27" t="inlineStr">
+      <c r="B367" s="28" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - CONDIMENTOS E TEMPEROS</t>
         </is>
       </c>
-      <c r="C367" s="27" t="inlineStr">
+      <c r="C367" s="28" t="inlineStr">
         <is>
           <t>VINAGRE CASTELO 750ML ALCOOL COLORIDO</t>
         </is>
       </c>
-      <c r="D367" s="27" t="inlineStr">
+      <c r="D367" s="28" t="inlineStr">
         <is>
           <t>VINAGRE CASTELO 750ML ALCOOL COLORIDO</t>
         </is>
       </c>
-      <c r="E367" s="27" t="inlineStr"/>
+      <c r="E367" s="28" t="inlineStr"/>
     </row>
     <row r="368">
       <c r="A368" s="25" t="n">
@@ -8125,25 +8121,25 @@
       </c>
     </row>
     <row r="372">
-      <c r="A372" s="25" t="n">
+      <c r="A372" s="32" t="n">
         <v>108518</v>
       </c>
-      <c r="B372" s="25" t="inlineStr">
+      <c r="B372" s="32" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - CONDIMENTOS E TEMPEROS</t>
         </is>
       </c>
-      <c r="C372" s="25" t="inlineStr">
+      <c r="C372" s="32" t="inlineStr">
         <is>
           <t>TEMPERO ARISCO 1KG COMPLETO S/ PIMENTA</t>
         </is>
       </c>
-      <c r="D372" s="25" t="inlineStr">
+      <c r="D372" s="32" t="inlineStr">
         <is>
           <t>TEMPERO COMPLETO ARISCO COMPLETO 1KG SEM PIMENTA</t>
         </is>
       </c>
-      <c r="E372" s="25" t="inlineStr"/>
+      <c r="E372" s="32" t="inlineStr"/>
     </row>
     <row r="373">
       <c r="A373" t="n">
@@ -8466,25 +8462,25 @@
       </c>
     </row>
     <row r="389">
-      <c r="A389" s="27" t="n">
+      <c r="A389" s="28" t="n">
         <v>115548</v>
       </c>
-      <c r="B389" s="27" t="inlineStr">
+      <c r="B389" s="28" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - CONDIMENTOS E TEMPEROS</t>
         </is>
       </c>
-      <c r="C389" s="27" t="inlineStr">
+      <c r="C389" s="28" t="inlineStr">
         <is>
           <t>TEMPERO COLORAU SINHA 100GR</t>
         </is>
       </c>
-      <c r="D389" s="27" t="inlineStr">
+      <c r="D389" s="28" t="inlineStr">
         <is>
           <t>TEMPERO COLORAU SINHA 100G</t>
         </is>
       </c>
-      <c r="E389" s="27" t="inlineStr"/>
+      <c r="E389" s="28" t="inlineStr"/>
     </row>
     <row r="390">
       <c r="A390" t="n">
@@ -8527,25 +8523,25 @@
       </c>
     </row>
     <row r="392">
-      <c r="A392" s="27" t="n">
+      <c r="A392" s="28" t="n">
         <v>115724</v>
       </c>
-      <c r="B392" s="27" t="inlineStr">
+      <c r="B392" s="28" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - CONDIMENTOS E TEMPEROS</t>
         </is>
       </c>
-      <c r="C392" s="27" t="inlineStr">
+      <c r="C392" s="28" t="inlineStr">
         <is>
           <t>MAIONESE QUERO SCHT 200GR</t>
         </is>
       </c>
-      <c r="D392" s="27" t="inlineStr">
+      <c r="D392" s="28" t="inlineStr">
         <is>
           <t>MAIONESE QUERO SACHÊ 200G</t>
         </is>
       </c>
-      <c r="E392" s="27" t="inlineStr"/>
+      <c r="E392" s="28" t="inlineStr"/>
     </row>
     <row r="393">
       <c r="A393" t="n">
@@ -8950,25 +8946,25 @@
       </c>
     </row>
     <row r="413">
-      <c r="A413" s="22" t="n">
+      <c r="A413" s="32" t="n">
         <v>133147</v>
       </c>
-      <c r="B413" s="22" t="inlineStr">
+      <c r="B413" s="32" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - CONDIMENTOS E TEMPEROS</t>
         </is>
       </c>
-      <c r="C413" s="22" t="inlineStr">
+      <c r="C413" s="32" t="inlineStr">
         <is>
           <t>MAIONESE SABORELLE PICANTE 200G</t>
         </is>
       </c>
-      <c r="D413" s="22" t="inlineStr">
+      <c r="D413" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">MAIONESE SABORELLE 200G PICANTE </t>
         </is>
       </c>
-      <c r="E413" s="22" t="inlineStr"/>
+      <c r="E413" s="32" t="inlineStr"/>
     </row>
     <row r="414">
       <c r="A414" t="n">
@@ -9071,25 +9067,25 @@
       </c>
     </row>
     <row r="419">
-      <c r="A419" s="14" t="n">
+      <c r="A419" s="32" t="n">
         <v>141367</v>
       </c>
-      <c r="B419" s="14" t="inlineStr">
+      <c r="B419" s="32" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - CONDIMENTOS E TEMPEROS</t>
         </is>
       </c>
-      <c r="C419" s="14" t="inlineStr">
+      <c r="C419" s="32" t="inlineStr">
         <is>
           <t>VINAGRE ALCOOL MARATA 750ML COLORIDO</t>
         </is>
       </c>
-      <c r="D419" s="14" t="inlineStr">
+      <c r="D419" s="32" t="inlineStr">
         <is>
           <t>VINAGRE MARATÁ 750ML ALCOOL COLORIDO</t>
         </is>
       </c>
-      <c r="E419" s="14" t="inlineStr"/>
+      <c r="E419" s="32" t="inlineStr"/>
     </row>
     <row r="420">
       <c r="A420" t="n">
@@ -9132,24 +9128,25 @@
       </c>
     </row>
     <row r="422">
-      <c r="A422" t="n">
+      <c r="A422" s="32" t="n">
         <v>147164</v>
       </c>
-      <c r="B422" t="inlineStr">
+      <c r="B422" s="32" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - CONDIMENTOS E TEMPEROS</t>
         </is>
       </c>
-      <c r="C422" t="inlineStr">
+      <c r="C422" s="32" t="inlineStr">
         <is>
           <t>MILHO VERDE OLE VD 120GR</t>
         </is>
       </c>
-      <c r="D422" t="inlineStr">
+      <c r="D422" s="32" t="inlineStr">
         <is>
           <t>MILHO VERDE OLE VIDRO 120G</t>
         </is>
       </c>
+      <c r="E422" s="32" t="inlineStr"/>
     </row>
     <row r="423">
       <c r="A423" t="n">
@@ -9493,25 +9490,25 @@
       <c r="E439" s="22" t="inlineStr"/>
     </row>
     <row r="440">
-      <c r="A440" s="27" t="n">
+      <c r="A440" s="28" t="n">
         <v>183229</v>
       </c>
-      <c r="B440" s="27" t="inlineStr">
+      <c r="B440" s="28" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - CONDIMENTOS E TEMPEROS</t>
         </is>
       </c>
-      <c r="C440" s="27" t="inlineStr">
+      <c r="C440" s="28" t="inlineStr">
         <is>
           <t>MOLHO TOMATE DEZ 300GR ERVAS FINAS</t>
         </is>
       </c>
-      <c r="D440" s="27" t="inlineStr">
+      <c r="D440" s="28" t="inlineStr">
         <is>
           <t>MOLHO DE TOMATE DEZ 300G ERVAS FINAS</t>
         </is>
       </c>
-      <c r="E440" s="27" t="inlineStr"/>
+      <c r="E440" s="28" t="inlineStr"/>
     </row>
     <row r="441">
       <c r="A441" t="n">
@@ -9818,25 +9815,25 @@
       </c>
     </row>
     <row r="456">
-      <c r="A456" s="27" t="n">
+      <c r="A456" s="28" t="n">
         <v>228310</v>
       </c>
-      <c r="B456" s="27" t="inlineStr">
+      <c r="B456" s="28" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - CONDIMENTOS E TEMPEROS</t>
         </is>
       </c>
-      <c r="C456" s="27" t="inlineStr">
+      <c r="C456" s="28" t="inlineStr">
         <is>
           <t>MILHO PREDILECTA VEG 170G SACHE</t>
         </is>
       </c>
-      <c r="D456" s="27" t="inlineStr">
+      <c r="D456" s="28" t="inlineStr">
         <is>
           <t>MILHO VERDE PREDILECTA SACHÊ 170G</t>
         </is>
       </c>
-      <c r="E456" s="27" t="inlineStr"/>
+      <c r="E456" s="28" t="inlineStr"/>
     </row>
     <row r="457">
       <c r="A457" t="n">
@@ -10500,25 +10497,25 @@
       </c>
     </row>
     <row r="490">
-      <c r="A490" s="22" t="n">
+      <c r="A490" s="32" t="n">
         <v>273714</v>
       </c>
-      <c r="B490" s="22" t="inlineStr">
+      <c r="B490" s="32" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - CONDIMENTOS E TEMPEROS</t>
         </is>
       </c>
-      <c r="C490" s="22" t="inlineStr">
+      <c r="C490" s="32" t="inlineStr">
         <is>
           <t>EXTRATO TOMATE ELEFANTE 300G POTE</t>
         </is>
       </c>
-      <c r="D490" s="22" t="inlineStr">
+      <c r="D490" s="32" t="inlineStr">
         <is>
           <t>EXTRATO DE TOMATE ELEFANTE POTE 300G</t>
         </is>
       </c>
-      <c r="E490" s="22" t="inlineStr"/>
+      <c r="E490" s="32" t="inlineStr"/>
     </row>
     <row r="491">
       <c r="A491" t="n">
@@ -10821,25 +10818,25 @@
       </c>
     </row>
     <row r="506">
-      <c r="A506" s="27" t="n">
+      <c r="A506" s="28" t="n">
         <v>287390</v>
       </c>
-      <c r="B506" s="27" t="inlineStr">
+      <c r="B506" s="28" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - CONDIMENTOS E TEMPEROS</t>
         </is>
       </c>
-      <c r="C506" s="27" t="inlineStr">
+      <c r="C506" s="28" t="inlineStr">
         <is>
           <t>MOLHO TOMATE MARATA 300G TRADICIONAL</t>
         </is>
       </c>
-      <c r="D506" s="27" t="inlineStr">
+      <c r="D506" s="28" t="inlineStr">
         <is>
           <t>MOLHO DE TOMATE MARATA 300G TRADICIONAL</t>
         </is>
       </c>
-      <c r="E506" s="27" t="inlineStr"/>
+      <c r="E506" s="28" t="inlineStr"/>
     </row>
     <row r="507">
       <c r="A507" t="n">
@@ -11222,25 +11219,25 @@
       </c>
     </row>
     <row r="526">
-      <c r="A526" s="22" t="n">
+      <c r="A526" s="32" t="n">
         <v>321107</v>
       </c>
-      <c r="B526" s="22" t="inlineStr">
+      <c r="B526" s="32" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - CONDIMENTOS E TEMPEROS</t>
         </is>
       </c>
-      <c r="C526" s="22" t="inlineStr">
+      <c r="C526" s="32" t="inlineStr">
         <is>
           <t>MOLHO PRONTO QUERO 240GR TRADICIONAL SCH</t>
         </is>
       </c>
-      <c r="D526" s="22" t="inlineStr">
+      <c r="D526" s="32" t="inlineStr">
         <is>
           <t>MOLHO QUERO PRONTO SACHÊ 240G TRADICIONAL</t>
         </is>
       </c>
-      <c r="E526" s="22" t="inlineStr"/>
+      <c r="E526" s="32" t="inlineStr"/>
     </row>
     <row r="527">
       <c r="A527" t="n">
@@ -11503,25 +11500,25 @@
       </c>
     </row>
     <row r="540">
-      <c r="A540" s="27" t="n">
+      <c r="A540" s="28" t="n">
         <v>336113</v>
       </c>
-      <c r="B540" s="27" t="inlineStr">
+      <c r="B540" s="28" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - CONDIMENTOS E TEMPEROS</t>
         </is>
       </c>
-      <c r="C540" s="27" t="inlineStr">
+      <c r="C540" s="28" t="inlineStr">
         <is>
           <t>AZEITONA VERDE GUNE 200GR C/ CAROCO</t>
         </is>
       </c>
-      <c r="D540" s="27" t="inlineStr">
+      <c r="D540" s="28" t="inlineStr">
         <is>
           <t>AZEITONAS VERDES GUNE 200G COM CAROÇO</t>
         </is>
       </c>
-      <c r="E540" s="27" t="inlineStr"/>
+      <c r="E540" s="28" t="inlineStr"/>
     </row>
     <row r="541">
       <c r="A541" t="n">
@@ -12827,24 +12824,25 @@
       </c>
     </row>
     <row r="606">
-      <c r="A606" t="n">
+      <c r="A606" s="32" t="n">
         <v>107640</v>
       </c>
-      <c r="B606" t="inlineStr">
+      <c r="B606" s="32" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - CONSERVAS - HORTIFRUTI</t>
         </is>
       </c>
-      <c r="C606" t="inlineStr">
+      <c r="C606" s="32" t="inlineStr">
         <is>
           <t>MILHO VERDE QUERO 170GR LATA</t>
         </is>
       </c>
-      <c r="D606" t="inlineStr">
+      <c r="D606" s="32" t="inlineStr">
         <is>
           <t>MILHO VERDE QUERO LATA 170G</t>
         </is>
       </c>
+      <c r="E606" s="32" t="inlineStr"/>
     </row>
     <row r="607">
       <c r="A607" t="n">
@@ -13107,25 +13105,25 @@
       </c>
     </row>
     <row r="620">
-      <c r="A620" s="27" t="n">
+      <c r="A620" s="28" t="n">
         <v>221945</v>
       </c>
-      <c r="B620" s="27" t="inlineStr">
+      <c r="B620" s="28" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - CONSERVAS - HORTIFRUTI</t>
         </is>
       </c>
-      <c r="C620" s="27" t="inlineStr">
+      <c r="C620" s="28" t="inlineStr">
         <is>
           <t>MILHO VERDE LATA 170G PREDILECTA</t>
         </is>
       </c>
-      <c r="D620" s="27" t="inlineStr">
+      <c r="D620" s="28" t="inlineStr">
         <is>
           <t>MILHO VERDE PREDILECTA LATA 170G</t>
         </is>
       </c>
-      <c r="E620" s="27" t="inlineStr"/>
+      <c r="E620" s="28" t="inlineStr"/>
     </row>
     <row r="621">
       <c r="A621" t="n">
@@ -13548,25 +13546,25 @@
       </c>
     </row>
     <row r="642">
-      <c r="A642" s="27" t="n">
+      <c r="A642" s="32" t="n">
         <v>100705</v>
       </c>
-      <c r="B642" s="27" t="inlineStr">
+      <c r="B642" s="32" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - CONSERVAS - SARDINHAS</t>
         </is>
       </c>
-      <c r="C642" s="27" t="inlineStr">
+      <c r="C642" s="32" t="inlineStr">
         <is>
           <t>SARDINHA GOMES DA COSTA 125GR TOMATE</t>
         </is>
       </c>
-      <c r="D642" s="27" t="inlineStr">
+      <c r="D642" s="32" t="inlineStr">
         <is>
           <t>SARDINHA GOMES DA COSTA 125G TOMATE</t>
         </is>
       </c>
-      <c r="E642" s="27" t="inlineStr"/>
+      <c r="E642" s="32" t="inlineStr"/>
     </row>
     <row r="643">
       <c r="A643" s="10" t="n">
@@ -13830,25 +13828,25 @@
       <c r="E655" s="25" t="inlineStr"/>
     </row>
     <row r="656">
-      <c r="A656" s="27" t="n">
+      <c r="A656" s="28" t="n">
         <v>100027</v>
       </c>
-      <c r="B656" s="27" t="inlineStr">
+      <c r="B656" s="28" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - FARINHAS E DERIVADOS</t>
         </is>
       </c>
-      <c r="C656" s="27" t="inlineStr">
+      <c r="C656" s="28" t="inlineStr">
         <is>
           <t>FARINHA TRIGO ORQUIDEA 1KG SEM FERMENTO</t>
         </is>
       </c>
-      <c r="D656" s="27" t="inlineStr">
+      <c r="D656" s="28" t="inlineStr">
         <is>
           <t>FARINHA DE TRIGO ORQUIDEA 1KG SEM FERMENTO</t>
         </is>
       </c>
-      <c r="E656" s="27" t="inlineStr"/>
+      <c r="E656" s="28" t="inlineStr"/>
     </row>
     <row r="657">
       <c r="A657" t="n">
@@ -14172,25 +14170,25 @@
       </c>
     </row>
     <row r="673">
-      <c r="A673" s="27" t="n">
+      <c r="A673" s="28" t="n">
         <v>101130</v>
       </c>
-      <c r="B673" s="27" t="inlineStr">
+      <c r="B673" s="28" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - FARINHAS E DERIVADOS</t>
         </is>
       </c>
-      <c r="C673" s="27" t="inlineStr">
+      <c r="C673" s="28" t="inlineStr">
         <is>
           <t>MIST BOLO DONA BENTA 450GR CHOCOLATE</t>
         </is>
       </c>
-      <c r="D673" s="27" t="inlineStr">
+      <c r="D673" s="28" t="inlineStr">
         <is>
           <t>MISTURA PARA BOLOS DONA BENTA 450G CHOCOLATE</t>
         </is>
       </c>
-      <c r="E673" s="27" t="inlineStr"/>
+      <c r="E673" s="28" t="inlineStr"/>
     </row>
     <row r="674">
       <c r="A674" t="n">
@@ -14493,25 +14491,25 @@
       </c>
     </row>
     <row r="689">
-      <c r="A689" s="27" t="n">
+      <c r="A689" s="32" t="n">
         <v>112978</v>
       </c>
-      <c r="B689" s="27" t="inlineStr">
+      <c r="B689" s="32" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - FARINHAS E DERIVADOS</t>
         </is>
       </c>
-      <c r="C689" s="27" t="inlineStr">
+      <c r="C689" s="32" t="inlineStr">
         <is>
           <t>CUSCUZ DE MILHO SINHA 500GR</t>
         </is>
       </c>
-      <c r="D689" s="27" t="inlineStr">
+      <c r="D689" s="32" t="inlineStr">
         <is>
           <t>CUSCUZ DE MILHO SINHA 500G</t>
         </is>
       </c>
-      <c r="E689" s="27" t="inlineStr"/>
+      <c r="E689" s="32" t="inlineStr"/>
     </row>
     <row r="690">
       <c r="A690" t="n">
@@ -14656,46 +14654,46 @@
       </c>
     </row>
     <row r="697">
-      <c r="A697" s="27" t="n">
+      <c r="A697" s="32" t="n">
         <v>128920</v>
       </c>
-      <c r="B697" s="27" t="inlineStr">
+      <c r="B697" s="32" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - FARINHAS E DERIVADOS</t>
         </is>
       </c>
-      <c r="C697" s="27" t="inlineStr">
+      <c r="C697" s="32" t="inlineStr">
         <is>
           <t>POLVILHO AMAFIL MATUTO 1KG DOCE</t>
         </is>
       </c>
-      <c r="D697" s="27" t="inlineStr">
+      <c r="D697" s="32" t="inlineStr">
         <is>
           <t>POLVILHO MATUTO 1KG DOCE</t>
         </is>
       </c>
-      <c r="E697" s="27" t="inlineStr"/>
+      <c r="E697" s="32" t="inlineStr"/>
     </row>
     <row r="698">
-      <c r="A698" s="27" t="n">
+      <c r="A698" s="28" t="n">
         <v>128930</v>
       </c>
-      <c r="B698" s="27" t="inlineStr">
+      <c r="B698" s="28" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - FARINHAS E DERIVADOS</t>
         </is>
       </c>
-      <c r="C698" s="27" t="inlineStr">
+      <c r="C698" s="28" t="inlineStr">
         <is>
           <t>FARINHA MANDIOCA AMAFIL AMARELA OURO 1KG</t>
         </is>
       </c>
-      <c r="D698" s="27" t="inlineStr">
+      <c r="D698" s="28" t="inlineStr">
         <is>
           <t>FARINHA DE MANDIOCA AMAFIL 1KG AMARELA OURO</t>
         </is>
       </c>
-      <c r="E698" s="27" t="inlineStr"/>
+      <c r="E698" s="28" t="inlineStr"/>
     </row>
     <row r="699">
       <c r="A699" t="n">
@@ -15703,25 +15701,25 @@
       </c>
     </row>
     <row r="749">
-      <c r="A749" s="27" t="n">
+      <c r="A749" s="32" t="n">
         <v>213696</v>
       </c>
-      <c r="B749" s="27" t="inlineStr">
+      <c r="B749" s="32" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - FARINHAS E DERIVADOS</t>
         </is>
       </c>
-      <c r="C749" s="27" t="inlineStr">
+      <c r="C749" s="32" t="inlineStr">
         <is>
           <t>FARINHA TRIGO TRES COROAS 1KG</t>
         </is>
       </c>
-      <c r="D749" s="27" t="inlineStr">
+      <c r="D749" s="32" t="inlineStr">
         <is>
           <t>FARINHA DE TRIGO TRES COROAS 1KG</t>
         </is>
       </c>
-      <c r="E749" s="27" t="inlineStr"/>
+      <c r="E749" s="32" t="inlineStr"/>
     </row>
     <row r="750">
       <c r="A750" t="n">
@@ -16550,25 +16548,25 @@
       </c>
     </row>
     <row r="791">
-      <c r="A791" s="27" t="n">
+      <c r="A791" s="32" t="n">
         <v>313827</v>
       </c>
-      <c r="B791" s="27" t="inlineStr">
+      <c r="B791" s="32" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - FARINHAS E DERIVADOS</t>
         </is>
       </c>
-      <c r="C791" s="27" t="inlineStr">
+      <c r="C791" s="32" t="inlineStr">
         <is>
           <t>MASSA TAPIOCA AMAFIL MATUTO 1KG SEMI PRO</t>
         </is>
       </c>
-      <c r="D791" s="27" t="inlineStr">
+      <c r="D791" s="32" t="inlineStr">
         <is>
           <t>MASSA PARA TAPIOCA MATUTO 1KG SEMI PRONTO</t>
         </is>
       </c>
-      <c r="E791" s="27" t="inlineStr"/>
+      <c r="E791" s="32" t="inlineStr"/>
     </row>
     <row r="792">
       <c r="A792" t="n">
@@ -16691,25 +16689,25 @@
       </c>
     </row>
     <row r="798">
-      <c r="A798" s="25" t="n">
+      <c r="A798" s="32" t="n">
         <v>320648</v>
       </c>
-      <c r="B798" s="25" t="inlineStr">
+      <c r="B798" s="32" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - FARINHAS E DERIVADOS</t>
         </is>
       </c>
-      <c r="C798" s="25" t="inlineStr">
+      <c r="C798" s="32" t="inlineStr">
         <is>
           <t>FLOCAO DE ARROZ 500GR URBANO</t>
         </is>
       </c>
-      <c r="D798" s="25" t="inlineStr">
+      <c r="D798" s="32" t="inlineStr">
         <is>
           <t>FLOCÃO DE ARROZ URBANO 500G</t>
         </is>
       </c>
-      <c r="E798" s="25" t="inlineStr"/>
+      <c r="E798" s="32" t="inlineStr"/>
     </row>
     <row r="799">
       <c r="A799" t="n">
@@ -18881,25 +18879,25 @@
       </c>
     </row>
     <row r="907">
-      <c r="A907" s="25" t="n">
+      <c r="A907" s="32" t="n">
         <v>101083</v>
       </c>
-      <c r="B907" s="25" t="inlineStr">
+      <c r="B907" s="32" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - LATICÍNIOS - DERIVADOS LACTEOS</t>
         </is>
       </c>
-      <c r="C907" s="25" t="inlineStr">
+      <c r="C907" s="32" t="inlineStr">
         <is>
           <t>LEITE CONDENSADO PIRACANJUBA 395GR TP</t>
         </is>
       </c>
-      <c r="D907" s="25" t="inlineStr">
+      <c r="D907" s="32" t="inlineStr">
         <is>
           <t>LEITE CONDENSADO PIRACANJUBA 395G</t>
         </is>
       </c>
-      <c r="E907" s="25" t="inlineStr"/>
+      <c r="E907" s="32" t="inlineStr"/>
     </row>
     <row r="908">
       <c r="A908" t="n">
@@ -19063,25 +19061,25 @@
       </c>
     </row>
     <row r="916">
-      <c r="A916" s="25" t="n">
+      <c r="A916" s="32" t="n">
         <v>193295</v>
       </c>
-      <c r="B916" s="25" t="inlineStr">
+      <c r="B916" s="32" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - LATICÍNIOS - DERIVADOS LACTEOS</t>
         </is>
       </c>
-      <c r="C916" s="25" t="inlineStr">
+      <c r="C916" s="32" t="inlineStr">
         <is>
           <t>CREME DE LEITE TRIANGULO 200GR 10%GORDUR</t>
         </is>
       </c>
-      <c r="D916" s="25" t="inlineStr">
+      <c r="D916" s="32" t="inlineStr">
         <is>
           <t>CREME DE LEITE TRIANGULO 200G 10% GORDURA</t>
         </is>
       </c>
-      <c r="E916" s="25" t="inlineStr"/>
+      <c r="E916" s="32" t="inlineStr"/>
     </row>
     <row r="917">
       <c r="A917" t="n">
@@ -19144,25 +19142,25 @@
       </c>
     </row>
     <row r="920">
-      <c r="A920" s="27" t="n">
+      <c r="A920" s="28" t="n">
         <v>220451</v>
       </c>
-      <c r="B920" s="27" t="inlineStr">
+      <c r="B920" s="28" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - LATICÍNIOS - DERIVADOS LACTEOS</t>
         </is>
       </c>
-      <c r="C920" s="27" t="inlineStr">
+      <c r="C920" s="28" t="inlineStr">
         <is>
           <t>LEITE COND. TRIANGULO 395G TP SEMI</t>
         </is>
       </c>
-      <c r="D920" s="27" t="inlineStr">
+      <c r="D920" s="28" t="inlineStr">
         <is>
           <t>LEITE CONDENSADO TRIANGULO 395G SEMIDESNATADO</t>
         </is>
       </c>
-      <c r="E920" s="27" t="inlineStr"/>
+      <c r="E920" s="28" t="inlineStr"/>
     </row>
     <row r="921">
       <c r="A921" t="n">
@@ -19306,46 +19304,46 @@
       </c>
     </row>
     <row r="928">
-      <c r="A928" s="25" t="n">
+      <c r="A928" s="32" t="n">
         <v>101113</v>
       </c>
-      <c r="B928" s="25" t="inlineStr">
+      <c r="B928" s="32" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - LATICÍNIOS - LEITE</t>
         </is>
       </c>
-      <c r="C928" s="25" t="inlineStr">
+      <c r="C928" s="32" t="inlineStr">
         <is>
           <t>LEITE PIRACANJUBA UHT 1L INTEGRAL</t>
         </is>
       </c>
-      <c r="D928" s="25" t="inlineStr">
+      <c r="D928" s="32" t="inlineStr">
         <is>
           <t>LEITE LONGA VIDA PIRACANJUBA 1L INTEGRAL</t>
         </is>
       </c>
-      <c r="E928" s="25" t="inlineStr"/>
+      <c r="E928" s="32" t="inlineStr"/>
     </row>
     <row r="929">
-      <c r="A929" s="27" t="n">
+      <c r="A929" s="32" t="n">
         <v>108252</v>
       </c>
-      <c r="B929" s="27" t="inlineStr">
+      <c r="B929" s="32" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - LATICÍNIOS - LEITE</t>
         </is>
       </c>
-      <c r="C929" s="27" t="inlineStr">
+      <c r="C929" s="32" t="inlineStr">
         <is>
           <t>LEITE LV PIRANCANJUBA 1LT DESNATADO</t>
         </is>
       </c>
-      <c r="D929" s="27" t="inlineStr">
+      <c r="D929" s="32" t="inlineStr">
         <is>
           <t>LEITE LONGA VIDA PIRACANJUBA 1L DESNATADO</t>
         </is>
       </c>
-      <c r="E929" s="27" t="inlineStr"/>
+      <c r="E929" s="32" t="inlineStr"/>
     </row>
     <row r="930">
       <c r="A930" s="10" t="n">
@@ -19368,25 +19366,25 @@
       </c>
     </row>
     <row r="931">
-      <c r="A931" s="27" t="n">
+      <c r="A931" s="32" t="n">
         <v>112296</v>
       </c>
-      <c r="B931" s="27" t="inlineStr">
+      <c r="B931" s="32" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - LATICÍNIOS - LEITE</t>
         </is>
       </c>
-      <c r="C931" s="27" t="inlineStr">
+      <c r="C931" s="32" t="inlineStr">
         <is>
           <t>LEITE PIRACANJUBA UHT 1L SEMIDESNATADO</t>
         </is>
       </c>
-      <c r="D931" s="27" t="inlineStr">
+      <c r="D931" s="32" t="inlineStr">
         <is>
           <t>LEITE LONGA VIDA PIRACANJUBA 1L SEMI DESNATADO</t>
         </is>
       </c>
-      <c r="E931" s="27" t="inlineStr"/>
+      <c r="E931" s="32" t="inlineStr"/>
     </row>
     <row r="932">
       <c r="A932" t="n">
@@ -19429,25 +19427,25 @@
       </c>
     </row>
     <row r="934">
-      <c r="A934" s="27" t="n">
+      <c r="A934" s="28" t="n">
         <v>170363</v>
       </c>
-      <c r="B934" s="27" t="inlineStr">
+      <c r="B934" s="28" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - LATICÍNIOS - LEITE</t>
         </is>
       </c>
-      <c r="C934" s="27" t="inlineStr">
+      <c r="C934" s="28" t="inlineStr">
         <is>
           <t>LEITE L.VIDA LEITBOM INTEGRAL</t>
         </is>
       </c>
-      <c r="D934" s="27" t="inlineStr">
+      <c r="D934" s="28" t="inlineStr">
         <is>
           <t>LEITE LONGA VIDA LEITBOM 1L INTEGRAL</t>
         </is>
       </c>
-      <c r="E934" s="27" t="inlineStr"/>
+      <c r="E934" s="28" t="inlineStr"/>
     </row>
     <row r="935">
       <c r="A935" t="n">
@@ -19710,25 +19708,25 @@
       </c>
     </row>
     <row r="948">
-      <c r="A948" s="27" t="n">
+      <c r="A948" s="32" t="n">
         <v>106922</v>
       </c>
-      <c r="B948" s="27" t="inlineStr">
+      <c r="B948" s="32" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - LATICÍNIOS - LEITE EM PÓ</t>
         </is>
       </c>
-      <c r="C948" s="27" t="inlineStr">
+      <c r="C948" s="32" t="inlineStr">
         <is>
           <t>LEITE EM PO CCGL 1KG INTEGRAL</t>
         </is>
       </c>
-      <c r="D948" s="27" t="inlineStr">
+      <c r="D948" s="32" t="inlineStr">
         <is>
           <t>LEITE EM PÓ CCGL 1KG INTEGRAL</t>
         </is>
       </c>
-      <c r="E948" s="27" t="inlineStr"/>
+      <c r="E948" s="32" t="inlineStr"/>
     </row>
     <row r="949">
       <c r="A949" t="n">
@@ -19911,25 +19909,25 @@
       </c>
     </row>
     <row r="958">
-      <c r="A958" s="27" t="n">
+      <c r="A958" s="32" t="n">
         <v>307145</v>
       </c>
-      <c r="B958" s="27" t="inlineStr">
+      <c r="B958" s="32" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - LATICÍNIOS - LEITE EM PÓ</t>
         </is>
       </c>
-      <c r="C958" s="27" t="inlineStr">
+      <c r="C958" s="32" t="inlineStr">
         <is>
           <t>LEITE PO NINHO 380GR INTEGRAL INSTANTANE</t>
         </is>
       </c>
-      <c r="D958" s="27" t="inlineStr">
+      <c r="D958" s="32" t="inlineStr">
         <is>
           <t>LEITE EM PÓ NINHO LATA 380G INTEGRAL INSTANTANEO</t>
         </is>
       </c>
-      <c r="E958" s="27" t="inlineStr"/>
+      <c r="E958" s="32" t="inlineStr"/>
     </row>
     <row r="959">
       <c r="A959" t="n">
@@ -20093,24 +20091,25 @@
       </c>
     </row>
     <row r="967">
-      <c r="A967" s="11" t="n">
+      <c r="A967" s="34" t="n">
         <v>133484</v>
       </c>
-      <c r="B967" s="11" t="inlineStr">
+      <c r="B967" s="34" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - LATICÍNIOS - QUEIJO</t>
         </is>
       </c>
-      <c r="C967" s="11" t="inlineStr">
+      <c r="C967" s="34" t="inlineStr">
         <is>
           <t>REQUEIJAO CREMOSO TIROLEZ LIGHT 200GR</t>
         </is>
       </c>
-      <c r="D967" s="11" t="inlineStr">
+      <c r="D967" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">REQUEIJÃO CREMOSO TIROLEZ 200G LIGHT </t>
         </is>
       </c>
+      <c r="E967" s="34" t="inlineStr"/>
     </row>
     <row r="968">
       <c r="A968" t="n">
@@ -20233,25 +20232,25 @@
       </c>
     </row>
     <row r="974">
-      <c r="A974" s="35" t="n">
+      <c r="A974" s="34" t="n">
         <v>158733</v>
       </c>
-      <c r="B974" s="35" t="inlineStr">
+      <c r="B974" s="34" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - LATICÍNIOS - QUEIJO</t>
         </is>
       </c>
-      <c r="C974" s="35" t="inlineStr">
+      <c r="C974" s="34" t="inlineStr">
         <is>
           <t>QUEIJO MUSSARELA PIRAC FATIADO 150GR</t>
         </is>
       </c>
-      <c r="D974" s="35" t="inlineStr">
+      <c r="D974" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">QUEIJO MUSSARELA PIRACANJUBA 150G FATIADO </t>
         </is>
       </c>
-      <c r="E974" s="35" t="inlineStr"/>
+      <c r="E974" s="34" t="inlineStr"/>
     </row>
     <row r="975">
       <c r="A975" s="34" t="n">
@@ -20876,25 +20875,25 @@
       <c r="E1005" s="25" t="inlineStr"/>
     </row>
     <row r="1006">
-      <c r="A1006" s="27" t="n">
+      <c r="A1006" s="28" t="n">
         <v>100642</v>
       </c>
-      <c r="B1006" s="27" t="inlineStr">
+      <c r="B1006" s="28" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - MASSAS</t>
         </is>
       </c>
-      <c r="C1006" s="27" t="inlineStr">
+      <c r="C1006" s="28" t="inlineStr">
         <is>
           <t>MAC PAULISTA ESPAGUETE 500GR SEMOLA</t>
         </is>
       </c>
-      <c r="D1006" s="27" t="inlineStr">
+      <c r="D1006" s="28" t="inlineStr">
         <is>
           <t>MACARRÃO PAULISTA ESPAGUETE SEMOLA 500G</t>
         </is>
       </c>
-      <c r="E1006" s="27" t="inlineStr"/>
+      <c r="E1006" s="28" t="inlineStr"/>
     </row>
     <row r="1007">
       <c r="A1007" s="12" t="n">
@@ -21599,25 +21598,25 @@
       </c>
     </row>
     <row r="1042">
-      <c r="A1042" s="27" t="n">
+      <c r="A1042" s="28" t="n">
         <v>190851</v>
       </c>
-      <c r="B1042" s="27" t="inlineStr">
+      <c r="B1042" s="28" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - MASSAS</t>
         </is>
       </c>
-      <c r="C1042" s="27" t="inlineStr">
+      <c r="C1042" s="28" t="inlineStr">
         <is>
           <t>MAC GALO INTEGRAL PENA 500G</t>
         </is>
       </c>
-      <c r="D1042" s="27" t="inlineStr">
+      <c r="D1042" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">MACARRÃO GALO PENA 500G INTEGRAL </t>
         </is>
       </c>
-      <c r="E1042" s="27" t="inlineStr"/>
+      <c r="E1042" s="28" t="inlineStr"/>
     </row>
     <row r="1043">
       <c r="A1043" t="n">
@@ -21901,25 +21900,25 @@
       <c r="E1056" s="25" t="inlineStr"/>
     </row>
     <row r="1057">
-      <c r="A1057" s="14" t="n">
+      <c r="A1057" s="32" t="n">
         <v>303196</v>
       </c>
-      <c r="B1057" s="14" t="inlineStr">
+      <c r="B1057" s="32" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - MASSAS</t>
         </is>
       </c>
-      <c r="C1057" s="14" t="inlineStr">
+      <c r="C1057" s="32" t="inlineStr">
         <is>
           <t>MACARRAO GALO 400GR ESPAGUETE AMARELO</t>
         </is>
       </c>
-      <c r="D1057" s="14" t="inlineStr">
+      <c r="D1057" s="32" t="inlineStr">
         <is>
           <t>MACARRÃO GALO ESPAGUETE AMARELO 400G</t>
         </is>
       </c>
-      <c r="E1057" s="14" t="inlineStr"/>
+      <c r="E1057" s="32" t="inlineStr"/>
     </row>
     <row r="1058">
       <c r="A1058" t="n">
@@ -23864,25 +23863,25 @@
       </c>
     </row>
     <row r="1155">
-      <c r="A1155" s="15" t="n">
+      <c r="A1155" s="34" t="n">
         <v>220822</v>
       </c>
-      <c r="B1155" s="15" t="inlineStr">
+      <c r="B1155" s="34" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - PÃES E BOLOS</t>
         </is>
       </c>
-      <c r="C1155" s="15" t="inlineStr">
+      <c r="C1155" s="34" t="inlineStr">
         <is>
           <t>PAO DE ALHO DI NAPOLI 350GR C/ QJO ERVAS</t>
         </is>
       </c>
-      <c r="D1155" s="15" t="inlineStr">
+      <c r="D1155" s="34" t="inlineStr">
         <is>
           <t>PÃO DE ALHO DI NAPOLI 350G QUEIJO E ERVAS</t>
         </is>
       </c>
-      <c r="E1155" s="15" t="inlineStr"/>
+      <c r="E1155" s="34" t="inlineStr"/>
     </row>
     <row r="1156">
       <c r="A1156" t="n">
@@ -24168,25 +24167,25 @@
       </c>
     </row>
     <row r="1170">
-      <c r="A1170" s="34" t="n">
+      <c r="A1170" s="29" t="n">
         <v>338924</v>
       </c>
-      <c r="B1170" s="34" t="inlineStr">
+      <c r="B1170" s="29" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - PÃES E BOLOS</t>
         </is>
       </c>
-      <c r="C1170" s="34" t="inlineStr">
+      <c r="C1170" s="29" t="inlineStr">
         <is>
           <t>PAO DE ALHO MAIS MIL 300GR SABOR PICANTE</t>
         </is>
       </c>
-      <c r="D1170" s="34" t="inlineStr">
+      <c r="D1170" s="29" t="inlineStr">
         <is>
           <t>PÃO DE ALHO MAIS MIL 300G PICANTE</t>
         </is>
       </c>
-      <c r="E1170" s="34" t="inlineStr"/>
+      <c r="E1170" s="29" t="inlineStr"/>
     </row>
     <row r="1171">
       <c r="A1171" t="n">
@@ -25344,87 +25343,88 @@
       </c>
     </row>
     <row r="1228">
-      <c r="A1228" t="n">
+      <c r="A1228" s="34" t="n">
         <v>104602</v>
       </c>
-      <c r="B1228" t="inlineStr">
+      <c r="B1228" s="34" t="inlineStr">
         <is>
           <t>#03 AÇOUGUE - #01 AVES</t>
         </is>
       </c>
-      <c r="C1228" t="inlineStr">
+      <c r="C1228" s="34" t="inlineStr">
         <is>
           <t>COXA SADIA FRANGO PACOTE 1KG</t>
         </is>
       </c>
-      <c r="D1228" t="inlineStr">
+      <c r="D1228" s="34" t="inlineStr">
         <is>
           <t>COXA DE FRANGO SADIA PCT 1KG</t>
         </is>
       </c>
+      <c r="E1228" s="34" t="inlineStr"/>
     </row>
     <row r="1229">
-      <c r="A1229" s="23" t="n">
+      <c r="A1229" s="34" t="n">
         <v>105838</v>
       </c>
-      <c r="B1229" s="23" t="inlineStr">
+      <c r="B1229" s="34" t="inlineStr">
         <is>
           <t>#03 AÇOUGUE - #01 AVES</t>
         </is>
       </c>
-      <c r="C1229" s="23" t="inlineStr">
+      <c r="C1229" s="34" t="inlineStr">
         <is>
           <t>COXA/SOBRECOXA FRANGO KG</t>
         </is>
       </c>
-      <c r="D1229" s="23" t="inlineStr">
+      <c r="D1229" s="34" t="inlineStr">
         <is>
           <t>COXA COM SOBRECOXA DE FRANGO KG</t>
         </is>
       </c>
-      <c r="E1229" s="23" t="inlineStr"/>
+      <c r="E1229" s="34" t="inlineStr"/>
     </row>
     <row r="1230">
-      <c r="A1230" s="23" t="n">
+      <c r="A1230" s="34" t="n">
         <v>105840</v>
       </c>
-      <c r="B1230" s="23" t="inlineStr">
+      <c r="B1230" s="34" t="inlineStr">
         <is>
           <t>#03 AÇOUGUE - #01 AVES</t>
         </is>
       </c>
-      <c r="C1230" s="23" t="inlineStr">
+      <c r="C1230" s="34" t="inlineStr">
         <is>
           <t>COXINHA DA ASA FRANGO KG</t>
         </is>
       </c>
-      <c r="D1230" s="23" t="inlineStr">
+      <c r="D1230" s="34" t="inlineStr">
         <is>
           <t>COXINHA DA ASA DE FRANGO KG</t>
         </is>
       </c>
-      <c r="E1230" s="23" t="inlineStr"/>
+      <c r="E1230" s="34" t="inlineStr"/>
     </row>
     <row r="1231">
-      <c r="A1231" s="23" t="n">
+      <c r="A1231" s="34" t="n">
         <v>105842</v>
       </c>
-      <c r="B1231" s="23" t="inlineStr">
+      <c r="B1231" s="34" t="inlineStr">
         <is>
           <t>#03 AÇOUGUE - #01 AVES</t>
         </is>
       </c>
-      <c r="C1231" s="23" t="inlineStr">
+      <c r="C1231" s="34" t="inlineStr">
         <is>
           <t>ASA FRANGO KG</t>
         </is>
       </c>
-      <c r="D1231" s="23" t="inlineStr">
+      <c r="D1231" s="34" t="inlineStr">
         <is>
           <t>ASA DE FRANGO KG</t>
         </is>
       </c>
-      <c r="E1231" s="23" t="inlineStr"/>
+      <c r="E1231" s="34" t="inlineStr"/>
     </row>
     <row r="1232">
       <c r="A1232" s="22" t="n">
@@ -25568,25 +25568,25 @@
       </c>
     </row>
     <row r="1239">
-      <c r="A1239" s="35" t="n">
+      <c r="A1239" s="34" t="n">
         <v>108785</v>
       </c>
-      <c r="B1239" s="35" t="inlineStr">
+      <c r="B1239" s="34" t="inlineStr">
         <is>
           <t>#03 AÇOUGUE - #01 AVES</t>
         </is>
       </c>
-      <c r="C1239" s="35" t="inlineStr">
+      <c r="C1239" s="34" t="inlineStr">
         <is>
           <t>COXINHA DA ASA SADIA 1KG PACOTE DRUMETTE</t>
         </is>
       </c>
-      <c r="D1239" s="35" t="inlineStr">
+      <c r="D1239" s="34" t="inlineStr">
         <is>
           <t>COXINHA DA ASA DE FRANGO SADIA PCT 1KG DRUMETE</t>
         </is>
       </c>
-      <c r="E1239" s="35" t="inlineStr"/>
+      <c r="E1239" s="34" t="inlineStr"/>
     </row>
     <row r="1240">
       <c r="A1240" t="n">
@@ -25629,25 +25629,25 @@
       </c>
     </row>
     <row r="1242">
-      <c r="A1242" s="35" t="n">
+      <c r="A1242" s="34" t="n">
         <v>108856</v>
       </c>
-      <c r="B1242" s="35" t="inlineStr">
+      <c r="B1242" s="34" t="inlineStr">
         <is>
           <t>#03 AÇOUGUE - #01 AVES</t>
         </is>
       </c>
-      <c r="C1242" s="35" t="inlineStr">
+      <c r="C1242" s="34" t="inlineStr">
         <is>
           <t>FILE PEITO SADIA PCT S/OPC 1KG PFFZP</t>
         </is>
       </c>
-      <c r="D1242" s="35" t="inlineStr">
+      <c r="D1242" s="34" t="inlineStr">
         <is>
           <t>FILE PEITO DE FRANGO SADIA PCT 1KG</t>
         </is>
       </c>
-      <c r="E1242" s="35" t="inlineStr"/>
+      <c r="E1242" s="34" t="inlineStr"/>
     </row>
     <row r="1243">
       <c r="A1243" t="n">
@@ -25670,25 +25670,25 @@
       </c>
     </row>
     <row r="1244">
-      <c r="A1244" s="23" t="n">
+      <c r="A1244" s="34" t="n">
         <v>109597</v>
       </c>
-      <c r="B1244" s="23" t="inlineStr">
+      <c r="B1244" s="34" t="inlineStr">
         <is>
           <t>#03 AÇOUGUE - #01 AVES</t>
         </is>
       </c>
-      <c r="C1244" s="23" t="inlineStr">
+      <c r="C1244" s="34" t="inlineStr">
         <is>
           <t>FILE PEITO FRANGO KG</t>
         </is>
       </c>
-      <c r="D1244" s="23" t="inlineStr">
+      <c r="D1244" s="34" t="inlineStr">
         <is>
           <t>FILÉ DE PEITO DE FRANGO KG</t>
         </is>
       </c>
-      <c r="E1244" s="23" t="inlineStr"/>
+      <c r="E1244" s="34" t="inlineStr"/>
     </row>
     <row r="1245">
       <c r="A1245" t="n">
@@ -25913,25 +25913,25 @@
       </c>
     </row>
     <row r="1256">
-      <c r="A1256" s="17" t="n">
+      <c r="A1256" s="34" t="n">
         <v>150768</v>
       </c>
-      <c r="B1256" s="17" t="inlineStr">
+      <c r="B1256" s="34" t="inlineStr">
         <is>
           <t>#03 AÇOUGUE - #01 AVES</t>
         </is>
       </c>
-      <c r="C1256" s="17" t="inlineStr">
+      <c r="C1256" s="34" t="inlineStr">
         <is>
           <t>PEITO DE FRANGO INTEIRO KG</t>
         </is>
       </c>
-      <c r="D1256" s="17" t="inlineStr">
+      <c r="D1256" s="34" t="inlineStr">
         <is>
           <t>PEITO DE FRANGO KG INTEIRO</t>
         </is>
       </c>
-      <c r="E1256" s="17" t="inlineStr"/>
+      <c r="E1256" s="34" t="inlineStr"/>
     </row>
     <row r="1257">
       <c r="A1257" t="n">
@@ -26055,25 +26055,25 @@
       </c>
     </row>
     <row r="1263">
-      <c r="A1263" s="18" t="n">
+      <c r="A1263" s="34" t="n">
         <v>195365</v>
       </c>
-      <c r="B1263" s="18" t="inlineStr">
+      <c r="B1263" s="34" t="inlineStr">
         <is>
           <t>#03 AÇOUGUE - #01 AVES</t>
         </is>
       </c>
-      <c r="C1263" s="18" t="inlineStr">
+      <c r="C1263" s="34" t="inlineStr">
         <is>
           <t>MOELA FRANGO PERDIGAO 1KG CONGELADA</t>
         </is>
       </c>
-      <c r="D1263" s="18" t="inlineStr">
+      <c r="D1263" s="34" t="inlineStr">
         <is>
           <t>MOELA DE FRANGO PERDIGÃO BDJ 1KG</t>
         </is>
       </c>
-      <c r="E1263" s="18" t="inlineStr"/>
+      <c r="E1263" s="34" t="inlineStr"/>
     </row>
     <row r="1264">
       <c r="A1264" t="n">
@@ -26679,24 +26679,25 @@
       </c>
     </row>
     <row r="1294">
-      <c r="A1294" s="11" t="n">
+      <c r="A1294" s="34" t="n">
         <v>306504</v>
       </c>
-      <c r="B1294" s="11" t="inlineStr">
+      <c r="B1294" s="34" t="inlineStr">
         <is>
           <t>#03 AÇOUGUE - #01 AVES</t>
         </is>
       </c>
-      <c r="C1294" s="11" t="inlineStr">
+      <c r="C1294" s="34" t="inlineStr">
         <is>
           <t>FIGADO FRANGO CONGELADO PERDIGAO 1KG</t>
         </is>
       </c>
-      <c r="D1294" s="11" t="inlineStr">
+      <c r="D1294" s="34" t="inlineStr">
         <is>
           <t>FIGADO DE FRANGO PERDIGAO KG</t>
         </is>
       </c>
+      <c r="E1294" s="34" t="inlineStr"/>
     </row>
     <row r="1295">
       <c r="A1295" t="n">
@@ -27001,25 +27002,25 @@
       </c>
     </row>
     <row r="1310">
-      <c r="A1310" s="26" t="n">
+      <c r="A1310" s="34" t="n">
         <v>105435</v>
       </c>
-      <c r="B1310" s="26" t="inlineStr">
+      <c r="B1310" s="34" t="inlineStr">
         <is>
           <t>#03 AÇOUGUE - #02 BOVINA</t>
         </is>
       </c>
-      <c r="C1310" s="26" t="inlineStr">
+      <c r="C1310" s="34" t="inlineStr">
         <is>
           <t>BOVINO - COXAO MOLE KG</t>
         </is>
       </c>
-      <c r="D1310" s="26" t="inlineStr">
+      <c r="D1310" s="34" t="inlineStr">
         <is>
           <t>COXÃO MOLE KG</t>
         </is>
       </c>
-      <c r="E1310" s="26" t="inlineStr"/>
+      <c r="E1310" s="34" t="inlineStr"/>
     </row>
     <row r="1311">
       <c r="A1311" t="n">
@@ -27042,25 +27043,25 @@
       </c>
     </row>
     <row r="1312">
-      <c r="A1312" s="25" t="n">
+      <c r="A1312" s="29" t="n">
         <v>105449</v>
       </c>
-      <c r="B1312" s="25" t="inlineStr">
+      <c r="B1312" s="29" t="inlineStr">
         <is>
           <t>#03 AÇOUGUE - #02 BOVINA</t>
         </is>
       </c>
-      <c r="C1312" s="25" t="inlineStr">
+      <c r="C1312" s="29" t="inlineStr">
         <is>
           <t>BOVINO - COXAO DURO KG</t>
         </is>
       </c>
-      <c r="D1312" s="25" t="inlineStr">
+      <c r="D1312" s="29" t="inlineStr">
         <is>
           <t>COXÃO DURO KG</t>
         </is>
       </c>
-      <c r="E1312" s="25" t="inlineStr"/>
+      <c r="E1312" s="29" t="inlineStr"/>
     </row>
     <row r="1313">
       <c r="A1313" t="n">
@@ -27083,25 +27084,25 @@
       </c>
     </row>
     <row r="1314">
-      <c r="A1314" s="36" t="n">
+      <c r="A1314" s="29" t="n">
         <v>105451</v>
       </c>
-      <c r="B1314" s="36" t="inlineStr">
+      <c r="B1314" s="29" t="inlineStr">
         <is>
           <t>#03 AÇOUGUE - #02 BOVINA</t>
         </is>
       </c>
-      <c r="C1314" s="36" t="inlineStr">
+      <c r="C1314" s="29" t="inlineStr">
         <is>
           <t>BOVINO - CONTRA FILE KG</t>
         </is>
       </c>
-      <c r="D1314" s="36" t="inlineStr">
+      <c r="D1314" s="29" t="inlineStr">
         <is>
           <t>CONTRA FILÉ KG</t>
         </is>
       </c>
-      <c r="E1314" s="36" t="inlineStr"/>
+      <c r="E1314" s="29" t="inlineStr"/>
     </row>
     <row r="1315">
       <c r="A1315" s="17" t="n">
@@ -27165,67 +27166,67 @@
       </c>
     </row>
     <row r="1318">
-      <c r="A1318" s="33" t="n">
+      <c r="A1318" s="28" t="n">
         <v>105457</v>
       </c>
-      <c r="B1318" s="33" t="inlineStr">
+      <c r="B1318" s="28" t="inlineStr">
         <is>
           <t>#03 AÇOUGUE - #02 BOVINA</t>
         </is>
       </c>
-      <c r="C1318" s="33" t="inlineStr">
+      <c r="C1318" s="28" t="inlineStr">
         <is>
           <t>BOVINO - CARNE SERENADA KG</t>
         </is>
       </c>
-      <c r="D1318" s="33" t="inlineStr">
+      <c r="D1318" s="28" t="inlineStr">
         <is>
           <t>CARNE BOVINA SERENADA KG</t>
         </is>
       </c>
-      <c r="E1318" s="33" t="inlineStr"/>
+      <c r="E1318" s="28" t="inlineStr"/>
     </row>
     <row r="1319">
-      <c r="A1319" s="26" t="n">
+      <c r="A1319" s="34" t="n">
         <v>105458</v>
       </c>
-      <c r="B1319" s="26" t="inlineStr">
+      <c r="B1319" s="34" t="inlineStr">
         <is>
           <t>#03 AÇOUGUE - #02 BOVINA</t>
         </is>
       </c>
-      <c r="C1319" s="26" t="inlineStr">
+      <c r="C1319" s="34" t="inlineStr">
         <is>
           <t>BOVINO - CHAMBARI KG</t>
         </is>
       </c>
-      <c r="D1319" s="26" t="inlineStr">
+      <c r="D1319" s="34" t="inlineStr">
         <is>
           <t>CHAMBARI KG</t>
         </is>
       </c>
-      <c r="E1319" s="26" t="inlineStr"/>
+      <c r="E1319" s="34" t="inlineStr"/>
     </row>
     <row r="1320">
-      <c r="A1320" s="37" t="n">
+      <c r="A1320" s="28" t="n">
         <v>105459</v>
       </c>
-      <c r="B1320" s="37" t="inlineStr">
+      <c r="B1320" s="28" t="inlineStr">
         <is>
           <t>#03 AÇOUGUE - #02 BOVINA</t>
         </is>
       </c>
-      <c r="C1320" s="37" t="inlineStr">
+      <c r="C1320" s="28" t="inlineStr">
         <is>
           <t>BOVINO - BISTECA MACA PEITO KG</t>
         </is>
       </c>
-      <c r="D1320" s="37" t="inlineStr">
+      <c r="D1320" s="28" t="inlineStr">
         <is>
           <t>BISTECA BOVINA DA MAÇÃ DO PEITO KG</t>
         </is>
       </c>
-      <c r="E1320" s="37" t="inlineStr"/>
+      <c r="E1320" s="28" t="inlineStr"/>
     </row>
     <row r="1321">
       <c r="A1321" s="11" t="n">
@@ -27248,25 +27249,25 @@
       </c>
     </row>
     <row r="1322">
-      <c r="A1322" s="36" t="n">
+      <c r="A1322" s="28" t="n">
         <v>105461</v>
       </c>
-      <c r="B1322" s="36" t="inlineStr">
+      <c r="B1322" s="28" t="inlineStr">
         <is>
           <t>#03 AÇOUGUE - #02 BOVINA</t>
         </is>
       </c>
-      <c r="C1322" s="36" t="inlineStr">
+      <c r="C1322" s="28" t="inlineStr">
         <is>
           <t>BOVINO - BISTECA CONTRA FILE KG</t>
         </is>
       </c>
-      <c r="D1322" s="36" t="inlineStr">
+      <c r="D1322" s="28" t="inlineStr">
         <is>
           <t>BISTECA BOVINA DO CONTRA FILE KG</t>
         </is>
       </c>
-      <c r="E1322" s="36" t="inlineStr"/>
+      <c r="E1322" s="28" t="inlineStr"/>
     </row>
     <row r="1323">
       <c r="A1323" s="23" t="n">
@@ -27311,25 +27312,25 @@
       <c r="E1324" s="26" t="inlineStr"/>
     </row>
     <row r="1325">
-      <c r="A1325" s="25" t="n">
+      <c r="A1325" s="34" t="n">
         <v>105468</v>
       </c>
-      <c r="B1325" s="25" t="inlineStr">
+      <c r="B1325" s="34" t="inlineStr">
         <is>
           <t>#03 AÇOUGUE - #02 BOVINA</t>
         </is>
       </c>
-      <c r="C1325" s="25" t="inlineStr">
+      <c r="C1325" s="34" t="inlineStr">
         <is>
           <t>BOVINO - CARNE MOIDA KG</t>
         </is>
       </c>
-      <c r="D1325" s="25" t="inlineStr">
+      <c r="D1325" s="34" t="inlineStr">
         <is>
           <t>CARNE MOIDA KG</t>
         </is>
       </c>
-      <c r="E1325" s="25" t="inlineStr"/>
+      <c r="E1325" s="34" t="inlineStr"/>
     </row>
     <row r="1326">
       <c r="A1326" t="n">
@@ -27352,88 +27353,88 @@
       </c>
     </row>
     <row r="1327">
-      <c r="A1327" s="24" t="n">
+      <c r="A1327" s="34" t="n">
         <v>105470</v>
       </c>
-      <c r="B1327" s="24" t="inlineStr">
+      <c r="B1327" s="34" t="inlineStr">
         <is>
           <t>#03 AÇOUGUE - #02 BOVINA</t>
         </is>
       </c>
-      <c r="C1327" s="24" t="inlineStr">
+      <c r="C1327" s="34" t="inlineStr">
         <is>
           <t>BOVINO - ACEM KG</t>
         </is>
       </c>
-      <c r="D1327" s="24" t="inlineStr">
+      <c r="D1327" s="34" t="inlineStr">
         <is>
           <t>ACEM BOVINO KG</t>
         </is>
       </c>
-      <c r="E1327" s="24" t="inlineStr"/>
+      <c r="E1327" s="34" t="inlineStr"/>
     </row>
     <row r="1328">
-      <c r="A1328" s="22" t="n">
+      <c r="A1328" s="29" t="n">
         <v>105471</v>
       </c>
-      <c r="B1328" s="22" t="inlineStr">
+      <c r="B1328" s="29" t="inlineStr">
         <is>
           <t>#03 AÇOUGUE - #02 BOVINA</t>
         </is>
       </c>
-      <c r="C1328" s="22" t="inlineStr">
+      <c r="C1328" s="29" t="inlineStr">
         <is>
           <t>BOVINO - COSTELA KG</t>
         </is>
       </c>
-      <c r="D1328" s="22" t="inlineStr">
+      <c r="D1328" s="29" t="inlineStr">
         <is>
           <t>COSTELA BOVINA KG</t>
         </is>
       </c>
-      <c r="E1328" s="22" t="inlineStr"/>
+      <c r="E1328" s="29" t="inlineStr"/>
     </row>
     <row r="1329">
-      <c r="A1329" s="22" t="n">
+      <c r="A1329" s="29" t="n">
         <v>105474</v>
       </c>
-      <c r="B1329" s="22" t="inlineStr">
+      <c r="B1329" s="29" t="inlineStr">
         <is>
           <t>#03 AÇOUGUE - #02 BOVINA</t>
         </is>
       </c>
-      <c r="C1329" s="22" t="inlineStr">
+      <c r="C1329" s="29" t="inlineStr">
         <is>
           <t>BOVINO - FRALDINHA KG</t>
         </is>
       </c>
-      <c r="D1329" s="22" t="inlineStr">
+      <c r="D1329" s="29" t="inlineStr">
         <is>
           <t>FRALDINHA BOVINA KG</t>
         </is>
       </c>
-      <c r="E1329" s="22" t="inlineStr"/>
+      <c r="E1329" s="29" t="inlineStr"/>
     </row>
     <row r="1330">
-      <c r="A1330" s="23" t="n">
+      <c r="A1330" s="34" t="n">
         <v>105475</v>
       </c>
-      <c r="B1330" s="23" t="inlineStr">
+      <c r="B1330" s="34" t="inlineStr">
         <is>
           <t>#03 AÇOUGUE - #02 BOVINA</t>
         </is>
       </c>
-      <c r="C1330" s="23" t="inlineStr">
+      <c r="C1330" s="34" t="inlineStr">
         <is>
           <t>BOVINO - MUSCULO KG</t>
         </is>
       </c>
-      <c r="D1330" s="23" t="inlineStr">
+      <c r="D1330" s="34" t="inlineStr">
         <is>
           <t>MUSCULO BOVINO KG</t>
         </is>
       </c>
-      <c r="E1330" s="23" t="inlineStr"/>
+      <c r="E1330" s="34" t="inlineStr"/>
     </row>
     <row r="1331">
       <c r="A1331" t="n">
@@ -27456,25 +27457,25 @@
       </c>
     </row>
     <row r="1332">
-      <c r="A1332" s="35" t="n">
+      <c r="A1332" s="28" t="n">
         <v>106065</v>
       </c>
-      <c r="B1332" s="35" t="inlineStr">
+      <c r="B1332" s="28" t="inlineStr">
         <is>
           <t>#03 AÇOUGUE - #02 BOVINA</t>
         </is>
       </c>
-      <c r="C1332" s="35" t="inlineStr">
+      <c r="C1332" s="28" t="inlineStr">
         <is>
           <t>BOVINO - FIGADO KG.</t>
         </is>
       </c>
-      <c r="D1332" s="35" t="inlineStr">
+      <c r="D1332" s="28" t="inlineStr">
         <is>
           <t>FIGADO BOVINO KG</t>
         </is>
       </c>
-      <c r="E1332" s="35" t="inlineStr"/>
+      <c r="E1332" s="28" t="inlineStr"/>
     </row>
     <row r="1333">
       <c r="A1333" t="n">
@@ -27538,50 +27539,46 @@
       </c>
     </row>
     <row r="1336">
-      <c r="A1336" s="34" t="n">
+      <c r="A1336" s="29" t="n">
         <v>107260</v>
       </c>
-      <c r="B1336" s="34" t="inlineStr">
+      <c r="B1336" s="29" t="inlineStr">
         <is>
           <t>#03 AÇOUGUE - #02 BOVINA</t>
         </is>
       </c>
-      <c r="C1336" s="34" t="inlineStr">
+      <c r="C1336" s="29" t="inlineStr">
         <is>
           <t>BOVINO - MACA DO PEITO KG</t>
         </is>
       </c>
-      <c r="D1336" s="34" t="inlineStr">
+      <c r="D1336" s="29" t="inlineStr">
         <is>
           <t>MAÇÃ DO PEITO KG</t>
         </is>
       </c>
-      <c r="E1336" s="34" t="inlineStr"/>
+      <c r="E1336" s="29" t="inlineStr"/>
     </row>
     <row r="1337">
-      <c r="A1337" s="38" t="n">
+      <c r="A1337" s="34" t="n">
         <v>110573</v>
       </c>
-      <c r="B1337" s="38" t="inlineStr">
+      <c r="B1337" s="34" t="inlineStr">
         <is>
           <t>#03 AÇOUGUE - #02 BOVINA</t>
         </is>
       </c>
-      <c r="C1337" s="39" t="inlineStr">
-        <is>
-          <t>BOVINO - CARNE DE SOL PICADA KG</t>
-        </is>
-      </c>
-      <c r="D1337" s="38" t="inlineStr">
+      <c r="C1337" s="34" t="inlineStr">
+        <is>
+          <t>CARNE DE SOL PICADA KG</t>
+        </is>
+      </c>
+      <c r="D1337" s="34" t="inlineStr">
         <is>
           <t>CARNE DE SOL BOVINA PICADA KG</t>
         </is>
       </c>
-      <c r="E1337" s="38" t="inlineStr">
-        <is>
-          <t>CARNE DE SOL PICADA KG</t>
-        </is>
-      </c>
+      <c r="E1337" s="34" t="inlineStr"/>
     </row>
     <row r="1338">
       <c r="A1338" t="n">
@@ -27644,25 +27641,25 @@
       </c>
     </row>
     <row r="1341">
-      <c r="A1341" s="26" t="n">
+      <c r="A1341" s="34" t="n">
         <v>157014</v>
       </c>
-      <c r="B1341" s="26" t="inlineStr">
+      <c r="B1341" s="34" t="inlineStr">
         <is>
           <t>#03 AÇOUGUE - #02 BOVINA</t>
         </is>
       </c>
-      <c r="C1341" s="26" t="inlineStr">
+      <c r="C1341" s="34" t="inlineStr">
         <is>
           <t>BOVINO - ACEM C/ OSSO KG</t>
         </is>
       </c>
-      <c r="D1341" s="26" t="inlineStr">
+      <c r="D1341" s="34" t="inlineStr">
         <is>
           <t>ACEM BOVINO COM OSSO KG</t>
         </is>
       </c>
-      <c r="E1341" s="26" t="inlineStr"/>
+      <c r="E1341" s="34" t="inlineStr"/>
     </row>
     <row r="1342">
       <c r="A1342" t="n">
@@ -27745,25 +27742,25 @@
       </c>
     </row>
     <row r="1346">
-      <c r="A1346" s="25" t="n">
+      <c r="A1346" s="29" t="n">
         <v>239334</v>
       </c>
-      <c r="B1346" s="25" t="inlineStr">
+      <c r="B1346" s="29" t="inlineStr">
         <is>
           <t>#03 AÇOUGUE - #02 BOVINA</t>
         </is>
       </c>
-      <c r="C1346" s="25" t="inlineStr">
+      <c r="C1346" s="29" t="inlineStr">
         <is>
           <t>BOVINO - CAPA DO CONTRA FILE KG</t>
         </is>
       </c>
-      <c r="D1346" s="25" t="inlineStr">
+      <c r="D1346" s="29" t="inlineStr">
         <is>
           <t>CAPA DO CONTRA FILE KG</t>
         </is>
       </c>
-      <c r="E1346" s="25" t="inlineStr"/>
+      <c r="E1346" s="29" t="inlineStr"/>
     </row>
     <row r="1347">
       <c r="A1347" t="n">
@@ -27867,46 +27864,46 @@
       </c>
     </row>
     <row r="1352">
-      <c r="A1352" s="24" t="n">
+      <c r="A1352" s="29" t="n">
         <v>105062</v>
       </c>
-      <c r="B1352" s="24" t="inlineStr">
+      <c r="B1352" s="29" t="inlineStr">
         <is>
           <t>#03 AÇOUGUE - #03 SUÍNA</t>
         </is>
       </c>
-      <c r="C1352" s="24" t="inlineStr">
+      <c r="C1352" s="29" t="inlineStr">
         <is>
           <t>SUINO - BISTECA PERNIL FRESCA KG</t>
         </is>
       </c>
-      <c r="D1352" s="24" t="inlineStr">
+      <c r="D1352" s="29" t="inlineStr">
         <is>
           <t>BISTECA SUINA DO PERNIL KG</t>
         </is>
       </c>
-      <c r="E1352" s="24" t="inlineStr"/>
+      <c r="E1352" s="29" t="inlineStr"/>
     </row>
     <row r="1353">
-      <c r="A1353" s="26" t="n">
+      <c r="A1353" s="29" t="n">
         <v>105433</v>
       </c>
-      <c r="B1353" s="26" t="inlineStr">
+      <c r="B1353" s="29" t="inlineStr">
         <is>
           <t>#03 AÇOUGUE - #03 SUÍNA</t>
         </is>
       </c>
-      <c r="C1353" s="26" t="inlineStr">
+      <c r="C1353" s="29" t="inlineStr">
         <is>
           <t>SUINO - COSTELA SUINA KG</t>
         </is>
       </c>
-      <c r="D1353" s="26" t="inlineStr">
+      <c r="D1353" s="29" t="inlineStr">
         <is>
           <t>COSTELA SUINA KG</t>
         </is>
       </c>
-      <c r="E1353" s="26" t="inlineStr"/>
+      <c r="E1353" s="29" t="inlineStr"/>
     </row>
     <row r="1354">
       <c r="A1354" t="n">
@@ -28256,25 +28253,25 @@
       </c>
     </row>
     <row r="1371">
-      <c r="A1371" s="34" t="n">
+      <c r="A1371" s="29" t="n">
         <v>298422</v>
       </c>
-      <c r="B1371" s="34" t="inlineStr">
+      <c r="B1371" s="29" t="inlineStr">
         <is>
           <t>#03 AÇOUGUE - #03 SUÍNA</t>
         </is>
       </c>
-      <c r="C1371" s="34" t="inlineStr">
+      <c r="C1371" s="29" t="inlineStr">
         <is>
           <t>SUINO - CAIPIRA KG</t>
         </is>
       </c>
-      <c r="D1371" s="34" t="inlineStr">
+      <c r="D1371" s="29" t="inlineStr">
         <is>
           <t>SUINO CAIPIRA KG</t>
         </is>
       </c>
-      <c r="E1371" s="34" t="inlineStr"/>
+      <c r="E1371" s="29" t="inlineStr"/>
     </row>
     <row r="1372">
       <c r="A1372" s="7" t="n">
@@ -28638,25 +28635,25 @@
       </c>
     </row>
     <row r="1390">
-      <c r="A1390" s="34" t="n">
+      <c r="A1390" s="29" t="n">
         <v>204452</v>
       </c>
-      <c r="B1390" s="34" t="inlineStr">
+      <c r="B1390" s="29" t="inlineStr">
         <is>
           <t>#03 AÇOUGUE - #04 PEIXES</t>
         </is>
       </c>
-      <c r="C1390" s="34" t="inlineStr">
+      <c r="C1390" s="29" t="inlineStr">
         <is>
           <t>FILE TILAPIA IQF BOUA 400G</t>
         </is>
       </c>
-      <c r="D1390" s="34" t="inlineStr">
+      <c r="D1390" s="29" t="inlineStr">
         <is>
           <t>FILÉ DE TILAPIA BOUA 400G</t>
         </is>
       </c>
-      <c r="E1390" s="34" t="inlineStr"/>
+      <c r="E1390" s="29" t="inlineStr"/>
     </row>
     <row r="1391">
       <c r="A1391" t="n">
@@ -28919,25 +28916,25 @@
       </c>
     </row>
     <row r="1404">
-      <c r="A1404" s="34" t="n">
+      <c r="A1404" s="29" t="n">
         <v>323487</v>
       </c>
-      <c r="B1404" s="34" t="inlineStr">
+      <c r="B1404" s="29" t="inlineStr">
         <is>
           <t>#03 AÇOUGUE - #05 FRUTOS DO MAR</t>
         </is>
       </c>
-      <c r="C1404" s="34" t="inlineStr">
+      <c r="C1404" s="29" t="inlineStr">
         <is>
           <t>CAMARAO VAN S/C COZ IQF-M 45/80 40X300G</t>
         </is>
       </c>
-      <c r="D1404" s="34" t="inlineStr">
+      <c r="D1404" s="29" t="inlineStr">
         <is>
           <t>CAMARAO COSTA SUL 300G VAN SEM CABEÇA COZIDO</t>
         </is>
       </c>
-      <c r="E1404" s="34" t="inlineStr"/>
+      <c r="E1404" s="29" t="inlineStr"/>
     </row>
     <row r="1405">
       <c r="A1405" t="n">
@@ -29020,25 +29017,25 @@
       </c>
     </row>
     <row r="1409">
-      <c r="A1409" s="34" t="n">
+      <c r="A1409" s="29" t="n">
         <v>335193</v>
       </c>
-      <c r="B1409" s="34" t="inlineStr">
+      <c r="B1409" s="29" t="inlineStr">
         <is>
           <t>#03 AÇOUGUE - #05 FRUTOS DO MAR</t>
         </is>
       </c>
-      <c r="C1409" s="34" t="inlineStr">
+      <c r="C1409" s="29" t="inlineStr">
         <is>
           <t>LULA EM ANEIS COSTA SUL 300G CONGELADO</t>
         </is>
       </c>
-      <c r="D1409" s="34" t="inlineStr">
+      <c r="D1409" s="29" t="inlineStr">
         <is>
           <t>LULA EM ANEIS COSTA SUL 300G CONGELADO</t>
         </is>
       </c>
-      <c r="E1409" s="34" t="inlineStr"/>
+      <c r="E1409" s="29" t="inlineStr"/>
     </row>
     <row r="1410">
       <c r="A1410" t="n">
@@ -29081,24 +29078,25 @@
       </c>
     </row>
     <row r="1412">
-      <c r="A1412" s="10" t="n">
+      <c r="A1412" s="34" t="n">
         <v>105765</v>
       </c>
-      <c r="B1412" s="10" t="inlineStr">
+      <c r="B1412" s="34" t="inlineStr">
         <is>
           <t>#03 AÇOUGUE - #06 EMBUTIDOS E FRIOS</t>
         </is>
       </c>
-      <c r="C1412" s="10" t="inlineStr">
-        <is>
-          <t>MORTADELA MISTA PERDIGAO KG</t>
-        </is>
-      </c>
-      <c r="D1412" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">MORTADELA PERDIGÃO KG MISTA </t>
-        </is>
-      </c>
+      <c r="C1412" s="34" t="inlineStr">
+        <is>
+          <t>MORT PERDIGAO KG MISTA</t>
+        </is>
+      </c>
+      <c r="D1412" s="34" t="inlineStr">
+        <is>
+          <t>MORTADELA MISTA PERDIGÃO KG</t>
+        </is>
+      </c>
+      <c r="E1412" s="34" t="inlineStr"/>
     </row>
     <row r="1413">
       <c r="A1413" s="23" t="n">
@@ -30046,25 +30044,25 @@
       <c r="E1459" s="20" t="inlineStr"/>
     </row>
     <row r="1460">
-      <c r="A1460" s="40" t="n">
+      <c r="A1460" s="29" t="n">
         <v>189031</v>
       </c>
-      <c r="B1460" s="40" t="inlineStr">
+      <c r="B1460" s="29" t="inlineStr">
         <is>
           <t>#03 AÇOUGUE - #06 EMBUTIDOS E FRIOS</t>
         </is>
       </c>
-      <c r="C1460" s="40" t="inlineStr">
+      <c r="C1460" s="29" t="inlineStr">
         <is>
           <t>LINGUIÇA MISTA FRICO KG</t>
         </is>
       </c>
-      <c r="D1460" s="40" t="inlineStr">
+      <c r="D1460" s="29" t="inlineStr">
         <is>
           <t>LINGUIÇA MISTA FRICÓ KG</t>
         </is>
       </c>
-      <c r="E1460" s="40" t="inlineStr"/>
+      <c r="E1460" s="29" t="inlineStr"/>
     </row>
     <row r="1461">
       <c r="A1461" t="n">
@@ -30127,25 +30125,25 @@
       </c>
     </row>
     <row r="1464">
-      <c r="A1464" s="34" t="n">
+      <c r="A1464" s="29" t="n">
         <v>197181</v>
       </c>
-      <c r="B1464" s="34" t="inlineStr">
+      <c r="B1464" s="29" t="inlineStr">
         <is>
           <t>#03 AÇOUGUE - #06 EMBUTIDOS E FRIOS</t>
         </is>
       </c>
-      <c r="C1464" s="34" t="inlineStr">
+      <c r="C1464" s="29" t="inlineStr">
         <is>
           <t>LINGUICA CALABRESA BOUA KG</t>
         </is>
       </c>
-      <c r="D1464" s="34" t="inlineStr">
+      <c r="D1464" s="29" t="inlineStr">
         <is>
           <t>LINGUIÇA CALABRESA BOUA KG</t>
         </is>
       </c>
-      <c r="E1464" s="34" t="inlineStr"/>
+      <c r="E1464" s="29" t="inlineStr"/>
     </row>
     <row r="1465">
       <c r="A1465" t="n">
@@ -30288,24 +30286,25 @@
       </c>
     </row>
     <row r="1472">
-      <c r="A1472" t="n">
+      <c r="A1472" s="34" t="n">
         <v>209710</v>
       </c>
-      <c r="B1472" t="inlineStr">
+      <c r="B1472" s="34" t="inlineStr">
         <is>
           <t>#03 AÇOUGUE - #06 EMBUTIDOS E FRIOS</t>
         </is>
       </c>
-      <c r="C1472" t="inlineStr">
+      <c r="C1472" s="34" t="inlineStr">
         <is>
           <t>LINGUICA CALABRESA FRESCAL FRIMESA PCT 1</t>
         </is>
       </c>
-      <c r="D1472" t="inlineStr">
+      <c r="D1472" s="34" t="inlineStr">
         <is>
           <t>LINGUIÇA CALABRESA FRESCAL FRIMESA PCT 1KG</t>
         </is>
       </c>
+      <c r="E1472" s="34" t="inlineStr"/>
     </row>
     <row r="1473">
       <c r="A1473" t="n">
@@ -30328,67 +30327,67 @@
       </c>
     </row>
     <row r="1474">
-      <c r="A1474" s="22" t="n">
+      <c r="A1474" s="34" t="n">
         <v>227259</v>
       </c>
-      <c r="B1474" s="22" t="inlineStr">
+      <c r="B1474" s="34" t="inlineStr">
         <is>
           <t>#03 AÇOUGUE - #06 EMBUTIDOS E FRIOS</t>
         </is>
       </c>
-      <c r="C1474" s="22" t="inlineStr">
+      <c r="C1474" s="34" t="inlineStr">
         <is>
           <t>LINGUICA FININHA DEFUMADA SEARA 215G</t>
         </is>
       </c>
-      <c r="D1474" s="22" t="inlineStr">
+      <c r="D1474" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">LINGUIÇA DEFUMADA SEARA 215G FININHA </t>
         </is>
       </c>
-      <c r="E1474" s="22" t="inlineStr"/>
+      <c r="E1474" s="34" t="inlineStr"/>
     </row>
     <row r="1475">
-      <c r="A1475" s="23" t="n">
+      <c r="A1475" s="34" t="n">
         <v>227341</v>
       </c>
-      <c r="B1475" s="23" t="inlineStr">
+      <c r="B1475" s="34" t="inlineStr">
         <is>
           <t>#03 AÇOUGUE - #06 EMBUTIDOS E FRIOS</t>
         </is>
       </c>
-      <c r="C1475" s="23" t="inlineStr">
+      <c r="C1475" s="34" t="inlineStr">
         <is>
           <t>SALSICHA HOT DOG AMERICANO KG</t>
         </is>
       </c>
-      <c r="D1475" s="23" t="inlineStr">
+      <c r="D1475" s="34" t="inlineStr">
         <is>
           <t>SALSICHA AMERICANO KG PARA HOT DOG</t>
         </is>
       </c>
-      <c r="E1475" s="23" t="inlineStr"/>
+      <c r="E1475" s="34" t="inlineStr"/>
     </row>
     <row r="1476">
-      <c r="A1476" s="23" t="n">
+      <c r="A1476" s="34" t="n">
         <v>228422</v>
       </c>
-      <c r="B1476" s="23" t="inlineStr">
+      <c r="B1476" s="34" t="inlineStr">
         <is>
           <t>#03 AÇOUGUE - #06 EMBUTIDOS E FRIOS</t>
         </is>
       </c>
-      <c r="C1476" s="23" t="inlineStr">
+      <c r="C1476" s="34" t="inlineStr">
         <is>
           <t>LING SUPER FRANGO KG GROSSA</t>
         </is>
       </c>
-      <c r="D1476" s="23" t="inlineStr">
+      <c r="D1476" s="34" t="inlineStr">
         <is>
           <t>LINGUIÇA GROSSA SUPER FRANGO KG</t>
         </is>
       </c>
-      <c r="E1476" s="23" t="inlineStr"/>
+      <c r="E1476" s="34" t="inlineStr"/>
     </row>
     <row r="1477">
       <c r="A1477" t="n">
@@ -30532,25 +30531,25 @@
       </c>
     </row>
     <row r="1484">
-      <c r="A1484" s="35" t="n">
+      <c r="A1484" s="29" t="n">
         <v>272009</v>
       </c>
-      <c r="B1484" s="35" t="inlineStr">
+      <c r="B1484" s="29" t="inlineStr">
         <is>
           <t>#03 AÇOUGUE - #06 EMBUTIDOS E FRIOS</t>
         </is>
       </c>
-      <c r="C1484" s="35" t="inlineStr">
+      <c r="C1484" s="29" t="inlineStr">
         <is>
           <t>APRESUNTADO PERDIGAO 200GR FATIADO</t>
         </is>
       </c>
-      <c r="D1484" s="35" t="inlineStr">
+      <c r="D1484" s="29" t="inlineStr">
         <is>
           <t>APRESUNTADO PERDIGÃO 200G FATIADO</t>
         </is>
       </c>
-      <c r="E1484" s="35" t="inlineStr"/>
+      <c r="E1484" s="29" t="inlineStr"/>
     </row>
     <row r="1485">
       <c r="A1485" t="n">
@@ -30734,46 +30733,46 @@
       </c>
     </row>
     <row r="1494">
-      <c r="A1494" s="24" t="n">
+      <c r="A1494" s="34" t="n">
         <v>292399</v>
       </c>
-      <c r="B1494" s="24" t="inlineStr">
+      <c r="B1494" s="34" t="inlineStr">
         <is>
           <t>#03 AÇOUGUE - #06 EMBUTIDOS E FRIOS</t>
         </is>
       </c>
-      <c r="C1494" s="24" t="inlineStr">
+      <c r="C1494" s="34" t="inlineStr">
         <is>
           <t>LINGUICA SUPER FRANGO 400GR DEFUMADA FRA</t>
         </is>
       </c>
-      <c r="D1494" s="24" t="inlineStr">
+      <c r="D1494" s="34" t="inlineStr">
         <is>
           <t>LINGUIÇA SUPER FRANGO 400G DEFUMADA</t>
         </is>
       </c>
-      <c r="E1494" s="24" t="inlineStr"/>
+      <c r="E1494" s="34" t="inlineStr"/>
     </row>
     <row r="1495">
-      <c r="A1495" s="38" t="n">
+      <c r="A1495" s="29" t="n">
         <v>292705</v>
       </c>
-      <c r="B1495" s="38" t="inlineStr">
+      <c r="B1495" s="29" t="inlineStr">
         <is>
           <t>#03 AÇOUGUE - #06 EMBUTIDOS E FRIOS</t>
         </is>
       </c>
-      <c r="C1495" s="38" t="inlineStr">
+      <c r="C1495" s="29" t="inlineStr">
         <is>
           <t>PRESUNTO SADIA 180GR COZIDO FATIADA</t>
         </is>
       </c>
-      <c r="D1495" s="38" t="inlineStr">
+      <c r="D1495" s="29" t="inlineStr">
         <is>
           <t>PRESUNTO SADIA 180G COZIDO FATIADO</t>
         </is>
       </c>
-      <c r="E1495" s="38" t="inlineStr"/>
+      <c r="E1495" s="29" t="inlineStr"/>
     </row>
     <row r="1496">
       <c r="A1496" t="n">
@@ -30938,25 +30937,25 @@
       </c>
     </row>
     <row r="1504">
-      <c r="A1504" s="34" t="n">
+      <c r="A1504" s="29" t="n">
         <v>320120</v>
       </c>
-      <c r="B1504" s="34" t="inlineStr">
+      <c r="B1504" s="29" t="inlineStr">
         <is>
           <t>#03 AÇOUGUE - #06 EMBUTIDOS E FRIOS</t>
         </is>
       </c>
-      <c r="C1504" s="34" t="inlineStr">
+      <c r="C1504" s="29" t="inlineStr">
         <is>
           <t>LING SUINA MIMOSA KG APIMENTADA</t>
         </is>
       </c>
-      <c r="D1504" s="34" t="inlineStr">
+      <c r="D1504" s="29" t="inlineStr">
         <is>
           <t>LINGUIÇA SUINA MIMOSA KG APIMENTADA</t>
         </is>
       </c>
-      <c r="E1504" s="34" t="inlineStr"/>
+      <c r="E1504" s="29" t="inlineStr"/>
     </row>
     <row r="1505">
       <c r="A1505" t="n">
@@ -31180,25 +31179,25 @@
       </c>
     </row>
     <row r="1516">
-      <c r="A1516" s="35" t="n">
+      <c r="A1516" s="29" t="n">
         <v>332652</v>
       </c>
-      <c r="B1516" s="35" t="inlineStr">
+      <c r="B1516" s="29" t="inlineStr">
         <is>
           <t>#03 AÇOUGUE - #06 EMBUTIDOS E FRIOS</t>
         </is>
       </c>
-      <c r="C1516" s="35" t="inlineStr">
+      <c r="C1516" s="29" t="inlineStr">
         <is>
           <t>LINGUICA BACON SEARA 600G TERMO</t>
         </is>
       </c>
-      <c r="D1516" s="35" t="inlineStr">
+      <c r="D1516" s="29" t="inlineStr">
         <is>
           <t>LINGUIÇA DE BACON SEARA 600G TERMO</t>
         </is>
       </c>
-      <c r="E1516" s="35" t="inlineStr"/>
+      <c r="E1516" s="29" t="inlineStr"/>
     </row>
     <row r="1517">
       <c r="A1517" t="n">
@@ -31301,25 +31300,25 @@
       </c>
     </row>
     <row r="1522">
-      <c r="A1522" s="34" t="n">
+      <c r="A1522" s="29" t="n">
         <v>341363</v>
       </c>
-      <c r="B1522" s="34" t="inlineStr">
+      <c r="B1522" s="29" t="inlineStr">
         <is>
           <t>#03 AÇOUGUE - #06 EMBUTIDOS E FRIOS</t>
         </is>
       </c>
-      <c r="C1522" s="34" t="inlineStr">
+      <c r="C1522" s="29" t="inlineStr">
         <is>
           <t>LINGUICA PERNIL PERDIGAO 700GR NA BRASA</t>
         </is>
       </c>
-      <c r="D1522" s="34" t="inlineStr">
+      <c r="D1522" s="29" t="inlineStr">
         <is>
           <t>LINGUIÇA DE PERNIL PERDIGÃO 700G NA BRASA</t>
         </is>
       </c>
-      <c r="E1522" s="34" t="inlineStr"/>
+      <c r="E1522" s="29" t="inlineStr"/>
     </row>
     <row r="1523">
       <c r="A1523" t="n">
@@ -31462,46 +31461,46 @@
       </c>
     </row>
     <row r="1530">
-      <c r="A1530" s="24" t="n">
+      <c r="A1530" s="34" t="n">
         <v>127328</v>
       </c>
-      <c r="B1530" s="24" t="inlineStr">
+      <c r="B1530" s="34" t="inlineStr">
         <is>
           <t>#03 AÇOUGUE - #07 EMPANADOS E PRATOS PRONTOS</t>
         </is>
       </c>
-      <c r="C1530" s="24" t="inlineStr">
+      <c r="C1530" s="34" t="inlineStr">
         <is>
           <t>TEKITOS SEARA QUEIJO OREGANO 300GR</t>
         </is>
       </c>
-      <c r="D1530" s="24" t="inlineStr">
+      <c r="D1530" s="34" t="inlineStr">
         <is>
           <t>TEKITOS SEARA 300G QUEIJO COM OREGANO</t>
         </is>
       </c>
-      <c r="E1530" s="24" t="inlineStr"/>
+      <c r="E1530" s="34" t="inlineStr"/>
     </row>
     <row r="1531">
-      <c r="A1531" s="20" t="n">
+      <c r="A1531" s="34" t="n">
         <v>138538</v>
       </c>
-      <c r="B1531" s="20" t="inlineStr">
+      <c r="B1531" s="34" t="inlineStr">
         <is>
           <t>#03 AÇOUGUE - #07 EMPANADOS E PRATOS PRONTOS</t>
         </is>
       </c>
-      <c r="C1531" s="20" t="inlineStr">
+      <c r="C1531" s="34" t="inlineStr">
         <is>
           <t>TEKITOS SEARA FRANGO 300G</t>
         </is>
       </c>
-      <c r="D1531" s="20" t="inlineStr">
+      <c r="D1531" s="34" t="inlineStr">
         <is>
           <t>TEKITOS SEARA 300G FRANGO</t>
         </is>
       </c>
-      <c r="E1531" s="20" t="inlineStr"/>
+      <c r="E1531" s="34" t="inlineStr"/>
     </row>
     <row r="1532">
       <c r="A1532" t="n">
@@ -31665,67 +31664,67 @@
       </c>
     </row>
     <row r="1540">
-      <c r="A1540" s="25" t="n">
+      <c r="A1540" s="29" t="n">
         <v>104931</v>
       </c>
-      <c r="B1540" s="25" t="inlineStr">
+      <c r="B1540" s="29" t="inlineStr">
         <is>
           <t>#04 HORTIFRUTI - #01 FRUTAS</t>
         </is>
       </c>
-      <c r="C1540" s="25" t="inlineStr">
+      <c r="C1540" s="29" t="inlineStr">
         <is>
           <t>LARANJA KG</t>
         </is>
       </c>
-      <c r="D1540" s="25" t="inlineStr">
+      <c r="D1540" s="29" t="inlineStr">
         <is>
           <t>LARANJA KG</t>
         </is>
       </c>
-      <c r="E1540" s="25" t="inlineStr"/>
+      <c r="E1540" s="29" t="inlineStr"/>
     </row>
     <row r="1541">
-      <c r="A1541" s="25" t="n">
+      <c r="A1541" s="29" t="n">
         <v>104961</v>
       </c>
-      <c r="B1541" s="25" t="inlineStr">
+      <c r="B1541" s="29" t="inlineStr">
         <is>
           <t>#04 HORTIFRUTI - #01 LEGUMES E TUBÉRCULOS</t>
         </is>
       </c>
-      <c r="C1541" s="25" t="inlineStr">
+      <c r="C1541" s="29" t="inlineStr">
         <is>
           <t>TOMATE CARMEM KG</t>
         </is>
       </c>
-      <c r="D1541" s="25" t="inlineStr">
+      <c r="D1541" s="29" t="inlineStr">
         <is>
           <t>TOMATE CARMEM KG</t>
         </is>
       </c>
-      <c r="E1541" s="25" t="inlineStr"/>
+      <c r="E1541" s="29" t="inlineStr"/>
     </row>
     <row r="1542">
-      <c r="A1542" s="25" t="n">
+      <c r="A1542" s="29" t="n">
         <v>105010</v>
       </c>
-      <c r="B1542" s="25" t="inlineStr">
+      <c r="B1542" s="29" t="inlineStr">
         <is>
           <t>#04 HORTIFRUTI - #01 LEGUMES E TUBÉRCULOS</t>
         </is>
       </c>
-      <c r="C1542" s="25" t="inlineStr">
+      <c r="C1542" s="29" t="inlineStr">
         <is>
           <t>BATATA MONALISA KG</t>
         </is>
       </c>
-      <c r="D1542" s="25" t="inlineStr">
+      <c r="D1542" s="29" t="inlineStr">
         <is>
           <t>BATATA MONALISA KG</t>
         </is>
       </c>
-      <c r="E1542" s="25" t="inlineStr"/>
+      <c r="E1542" s="29" t="inlineStr"/>
     </row>
     <row r="1543">
       <c r="A1543" s="25" t="n">
@@ -31770,46 +31769,46 @@
       <c r="E1544" s="19" t="inlineStr"/>
     </row>
     <row r="1545">
-      <c r="A1545" s="25" t="n">
+      <c r="A1545" s="29" t="n">
         <v>104855</v>
       </c>
-      <c r="B1545" s="25" t="inlineStr">
+      <c r="B1545" s="29" t="inlineStr">
         <is>
           <t>#04 HORTIFRUTI - FRUTAS</t>
         </is>
       </c>
-      <c r="C1545" s="25" t="inlineStr">
+      <c r="C1545" s="29" t="inlineStr">
         <is>
           <t>LIMAO TAITI KG</t>
         </is>
       </c>
-      <c r="D1545" s="25" t="inlineStr">
+      <c r="D1545" s="29" t="inlineStr">
         <is>
           <t>LIMÃO TAITI KG</t>
         </is>
       </c>
-      <c r="E1545" s="25" t="inlineStr"/>
+      <c r="E1545" s="29" t="inlineStr"/>
     </row>
     <row r="1546">
-      <c r="A1546" s="25" t="n">
+      <c r="A1546" s="29" t="n">
         <v>104864</v>
       </c>
-      <c r="B1546" s="25" t="inlineStr">
+      <c r="B1546" s="29" t="inlineStr">
         <is>
           <t>#04 HORTIFRUTI - FRUTAS</t>
         </is>
       </c>
-      <c r="C1546" s="25" t="inlineStr">
+      <c r="C1546" s="29" t="inlineStr">
         <is>
           <t>ABACATE KG</t>
         </is>
       </c>
-      <c r="D1546" s="25" t="inlineStr">
+      <c r="D1546" s="29" t="inlineStr">
         <is>
           <t>ABACATE KG</t>
         </is>
       </c>
-      <c r="E1546" s="25" t="inlineStr"/>
+      <c r="E1546" s="29" t="inlineStr"/>
     </row>
     <row r="1547">
       <c r="A1547" t="n">
@@ -31853,25 +31852,25 @@
       <c r="E1548" s="21" t="inlineStr"/>
     </row>
     <row r="1549">
-      <c r="A1549" s="25" t="n">
+      <c r="A1549" s="29" t="n">
         <v>104883</v>
       </c>
-      <c r="B1549" s="25" t="inlineStr">
+      <c r="B1549" s="29" t="inlineStr">
         <is>
           <t>#04 HORTIFRUTI - FRUTAS</t>
         </is>
       </c>
-      <c r="C1549" s="25" t="inlineStr">
+      <c r="C1549" s="29" t="inlineStr">
         <is>
           <t>MANGA TOMY KG</t>
         </is>
       </c>
-      <c r="D1549" s="25" t="inlineStr">
+      <c r="D1549" s="29" t="inlineStr">
         <is>
           <t>MANGA KG TOMY</t>
         </is>
       </c>
-      <c r="E1549" s="25" t="inlineStr"/>
+      <c r="E1549" s="29" t="inlineStr"/>
     </row>
     <row r="1550">
       <c r="A1550" t="n">
@@ -31934,25 +31933,25 @@
       </c>
     </row>
     <row r="1553">
-      <c r="A1553" s="25" t="n">
+      <c r="A1553" s="29" t="n">
         <v>104928</v>
       </c>
-      <c r="B1553" s="25" t="inlineStr">
+      <c r="B1553" s="29" t="inlineStr">
         <is>
           <t>#04 HORTIFRUTI - FRUTAS</t>
         </is>
       </c>
-      <c r="C1553" s="25" t="inlineStr">
+      <c r="C1553" s="29" t="inlineStr">
         <is>
           <t>MANGA PALMER KG</t>
         </is>
       </c>
-      <c r="D1553" s="25" t="inlineStr">
+      <c r="D1553" s="29" t="inlineStr">
         <is>
           <t>MANGA KG PALMER</t>
         </is>
       </c>
-      <c r="E1553" s="25" t="inlineStr"/>
+      <c r="E1553" s="29" t="inlineStr"/>
     </row>
     <row r="1554">
       <c r="A1554" s="3" t="n">
@@ -31975,46 +31974,46 @@
       </c>
     </row>
     <row r="1555">
-      <c r="A1555" s="25" t="n">
+      <c r="A1555" s="29" t="n">
         <v>104944</v>
       </c>
-      <c r="B1555" s="25" t="inlineStr">
+      <c r="B1555" s="29" t="inlineStr">
         <is>
           <t>#04 HORTIFRUTI - FRUTAS</t>
         </is>
       </c>
-      <c r="C1555" s="25" t="inlineStr">
+      <c r="C1555" s="29" t="inlineStr">
         <is>
           <t>MACA NACIONAL KG</t>
         </is>
       </c>
-      <c r="D1555" s="25" t="inlineStr">
+      <c r="D1555" s="29" t="inlineStr">
         <is>
           <t>MAÇÃ NACIONAL KG</t>
         </is>
       </c>
-      <c r="E1555" s="25" t="inlineStr"/>
+      <c r="E1555" s="29" t="inlineStr"/>
     </row>
     <row r="1556">
-      <c r="A1556" s="25" t="n">
+      <c r="A1556" s="29" t="n">
         <v>104947</v>
       </c>
-      <c r="B1556" s="25" t="inlineStr">
+      <c r="B1556" s="29" t="inlineStr">
         <is>
           <t>#04 HORTIFRUTI - FRUTAS</t>
         </is>
       </c>
-      <c r="C1556" s="25" t="inlineStr">
+      <c r="C1556" s="29" t="inlineStr">
         <is>
           <t>MELANCIA INTEIRA KG</t>
         </is>
       </c>
-      <c r="D1556" s="25" t="inlineStr">
+      <c r="D1556" s="29" t="inlineStr">
         <is>
           <t>MELANCIA INTEIRA KG</t>
         </is>
       </c>
-      <c r="E1556" s="25" t="inlineStr"/>
+      <c r="E1556" s="29" t="inlineStr"/>
     </row>
     <row r="1557">
       <c r="A1557" t="n">
@@ -32201,25 +32200,25 @@
       </c>
     </row>
     <row r="1566">
-      <c r="A1566" s="19" t="n">
+      <c r="A1566" s="29" t="n">
         <v>113290</v>
       </c>
-      <c r="B1566" s="19" t="inlineStr">
+      <c r="B1566" s="29" t="inlineStr">
         <is>
           <t>#04 HORTIFRUTI - FRUTAS</t>
         </is>
       </c>
-      <c r="C1566" s="19" t="inlineStr">
+      <c r="C1566" s="29" t="inlineStr">
         <is>
           <t>MELAO AMARELO REI / REDINHA KG</t>
         </is>
       </c>
-      <c r="D1566" s="19" t="inlineStr">
+      <c r="D1566" s="29" t="inlineStr">
         <is>
           <t>MELÃO AMARELO KG REI | REDINHA</t>
         </is>
       </c>
-      <c r="E1566" s="19" t="inlineStr"/>
+      <c r="E1566" s="29" t="inlineStr"/>
     </row>
     <row r="1567">
       <c r="A1567" s="25" t="n">
@@ -32585,25 +32584,25 @@
       </c>
     </row>
     <row r="1585">
-      <c r="A1585" s="25" t="n">
+      <c r="A1585" s="29" t="n">
         <v>104903</v>
       </c>
-      <c r="B1585" s="25" t="inlineStr">
+      <c r="B1585" s="29" t="inlineStr">
         <is>
           <t>#04 HORTIFRUTI - LEGUMES E TUBÉRCULOS</t>
         </is>
       </c>
-      <c r="C1585" s="25" t="inlineStr">
+      <c r="C1585" s="29" t="inlineStr">
         <is>
           <t>BATATA DOCE ROSA KG</t>
         </is>
       </c>
-      <c r="D1585" s="25" t="inlineStr">
+      <c r="D1585" s="29" t="inlineStr">
         <is>
           <t>BATATA DOCE KG ROSA</t>
         </is>
       </c>
-      <c r="E1585" s="25" t="inlineStr"/>
+      <c r="E1585" s="29" t="inlineStr"/>
     </row>
     <row r="1586">
       <c r="A1586" t="n">
@@ -32749,25 +32748,25 @@
       <c r="E1592" s="21" t="inlineStr"/>
     </row>
     <row r="1593">
-      <c r="A1593" s="25" t="n">
+      <c r="A1593" s="29" t="n">
         <v>108603</v>
       </c>
-      <c r="B1593" s="25" t="inlineStr">
+      <c r="B1593" s="29" t="inlineStr">
         <is>
           <t>#04 HORTIFRUTI - LEGUMES E TUBÉRCULOS</t>
         </is>
       </c>
-      <c r="C1593" s="25" t="inlineStr">
+      <c r="C1593" s="29" t="inlineStr">
         <is>
           <t>PIMENTAO VERDE KG</t>
         </is>
       </c>
-      <c r="D1593" s="25" t="inlineStr">
+      <c r="D1593" s="29" t="inlineStr">
         <is>
           <t>PIMENTÃO VERDE KG</t>
         </is>
       </c>
-      <c r="E1593" s="25" t="inlineStr"/>
+      <c r="E1593" s="29" t="inlineStr"/>
     </row>
     <row r="1594">
       <c r="A1594" s="25" t="n">
@@ -32791,25 +32790,25 @@
       <c r="E1594" s="25" t="inlineStr"/>
     </row>
     <row r="1595">
-      <c r="A1595" s="21" t="n">
+      <c r="A1595" s="29" t="n">
         <v>117983</v>
       </c>
-      <c r="B1595" s="21" t="inlineStr">
+      <c r="B1595" s="29" t="inlineStr">
         <is>
           <t>#04 HORTIFRUTI - LEGUMES E TUBÉRCULOS</t>
         </is>
       </c>
-      <c r="C1595" s="21" t="inlineStr">
+      <c r="C1595" s="29" t="inlineStr">
         <is>
           <t>ABOBORA ITALIA KG</t>
         </is>
       </c>
-      <c r="D1595" s="21" t="inlineStr">
+      <c r="D1595" s="29" t="inlineStr">
         <is>
           <t>ABOBORA ITALIA KG</t>
         </is>
       </c>
-      <c r="E1595" s="21" t="inlineStr"/>
+      <c r="E1595" s="29" t="inlineStr"/>
     </row>
     <row r="1596">
       <c r="A1596" s="21" t="n">
@@ -32833,25 +32832,25 @@
       <c r="E1596" s="21" t="inlineStr"/>
     </row>
     <row r="1597">
-      <c r="A1597" s="25" t="n">
+      <c r="A1597" s="29" t="n">
         <v>104937</v>
       </c>
-      <c r="B1597" s="25" t="inlineStr">
+      <c r="B1597" s="29" t="inlineStr">
         <is>
           <t>#04 HORTIFRUTI - TEMPEROS FRESCOS</t>
         </is>
       </c>
-      <c r="C1597" s="25" t="inlineStr">
+      <c r="C1597" s="29" t="inlineStr">
         <is>
           <t>ALHO A GRANEL KG</t>
         </is>
       </c>
-      <c r="D1597" s="25" t="inlineStr">
+      <c r="D1597" s="29" t="inlineStr">
         <is>
           <t>ALHO A GRANEL KG</t>
         </is>
       </c>
-      <c r="E1597" s="25" t="inlineStr"/>
+      <c r="E1597" s="29" t="inlineStr"/>
     </row>
     <row r="1598">
       <c r="A1598" s="3" t="n">
@@ -32874,25 +32873,25 @@
       </c>
     </row>
     <row r="1599">
-      <c r="A1599" s="25" t="n">
+      <c r="A1599" s="29" t="n">
         <v>104992</v>
       </c>
-      <c r="B1599" s="25" t="inlineStr">
+      <c r="B1599" s="29" t="inlineStr">
         <is>
           <t>#04 HORTIFRUTI - VERDURAS E FOLHAGENS</t>
         </is>
       </c>
-      <c r="C1599" s="25" t="inlineStr">
+      <c r="C1599" s="29" t="inlineStr">
         <is>
           <t>REPOLHO VERDE KG</t>
         </is>
       </c>
-      <c r="D1599" s="25" t="inlineStr">
+      <c r="D1599" s="29" t="inlineStr">
         <is>
           <t>REPOLHO VERDE KG</t>
         </is>
       </c>
-      <c r="E1599" s="25" t="inlineStr"/>
+      <c r="E1599" s="29" t="inlineStr"/>
     </row>
     <row r="1600">
       <c r="A1600" s="8" t="n">
@@ -33015,25 +33014,25 @@
       </c>
     </row>
     <row r="1606">
-      <c r="A1606" s="27" t="n">
+      <c r="A1606" s="32" t="n">
         <v>104404</v>
       </c>
-      <c r="B1606" s="27" t="inlineStr">
+      <c r="B1606" s="32" t="inlineStr">
         <is>
           <t>#05 BEBIDA - #00 BEBIDAS GASEIFICADAS</t>
         </is>
       </c>
-      <c r="C1606" s="27" t="inlineStr">
+      <c r="C1606" s="32" t="inlineStr">
         <is>
           <t>REFRIG FANTA LARANJA 2L</t>
         </is>
       </c>
-      <c r="D1606" s="27" t="inlineStr">
+      <c r="D1606" s="32" t="inlineStr">
         <is>
           <t>REFRIGERANTE FANTA 2L LARANJA</t>
         </is>
       </c>
-      <c r="E1606" s="27" t="inlineStr"/>
+      <c r="E1606" s="32" t="inlineStr"/>
     </row>
     <row r="1607">
       <c r="A1607" t="n">
@@ -33056,25 +33055,25 @@
       </c>
     </row>
     <row r="1608">
-      <c r="A1608" s="27" t="n">
+      <c r="A1608" s="32" t="n">
         <v>104406</v>
       </c>
-      <c r="B1608" s="27" t="inlineStr">
+      <c r="B1608" s="32" t="inlineStr">
         <is>
           <t>#05 BEBIDA - #00 BEBIDAS GASEIFICADAS</t>
         </is>
       </c>
-      <c r="C1608" s="27" t="inlineStr">
+      <c r="C1608" s="32" t="inlineStr">
         <is>
           <t>REFRIGERANTE COCA COLA 2L ORIGINAL</t>
         </is>
       </c>
-      <c r="D1608" s="27" t="inlineStr">
+      <c r="D1608" s="32" t="inlineStr">
         <is>
           <t>REFRIGERANTE COCA COLA 2L</t>
         </is>
       </c>
-      <c r="E1608" s="27" t="inlineStr"/>
+      <c r="E1608" s="32" t="inlineStr"/>
     </row>
     <row r="1609">
       <c r="A1609" s="22" t="n">
@@ -33158,25 +33157,25 @@
       </c>
     </row>
     <row r="1613">
-      <c r="A1613" s="27" t="n">
+      <c r="A1613" s="28" t="n">
         <v>104418</v>
       </c>
-      <c r="B1613" s="27" t="inlineStr">
+      <c r="B1613" s="28" t="inlineStr">
         <is>
           <t>#05 BEBIDA - #00 BEBIDAS GASEIFICADAS</t>
         </is>
       </c>
-      <c r="C1613" s="27" t="inlineStr">
+      <c r="C1613" s="28" t="inlineStr">
         <is>
           <t>REFRIG COCA COLA ZERO 2L</t>
         </is>
       </c>
-      <c r="D1613" s="27" t="inlineStr">
+      <c r="D1613" s="28" t="inlineStr">
         <is>
           <t>REFRIGERANTE COCA COLA ZERO 2L</t>
         </is>
       </c>
-      <c r="E1613" s="27" t="inlineStr"/>
+      <c r="E1613" s="28" t="inlineStr"/>
     </row>
     <row r="1614">
       <c r="A1614" t="n">
@@ -33319,25 +33318,25 @@
       </c>
     </row>
     <row r="1621">
-      <c r="A1621" s="25" t="n">
+      <c r="A1621" s="29" t="n">
         <v>161871</v>
       </c>
-      <c r="B1621" s="25" t="inlineStr">
+      <c r="B1621" s="29" t="inlineStr">
         <is>
           <t>#05 BEBIDA - #00 BEBIDAS GASEIFICADAS</t>
         </is>
       </c>
-      <c r="C1621" s="25" t="inlineStr">
+      <c r="C1621" s="29" t="inlineStr">
         <is>
           <t>REFRIG GUARANA TUCHAUA 2LT</t>
         </is>
       </c>
-      <c r="D1621" s="25" t="inlineStr">
+      <c r="D1621" s="29" t="inlineStr">
         <is>
           <t>REFRIGANTE TUCHAUA 2L GUARANA</t>
         </is>
       </c>
-      <c r="E1621" s="25" t="inlineStr"/>
+      <c r="E1621" s="29" t="inlineStr"/>
     </row>
     <row r="1622">
       <c r="A1622" t="n">
@@ -33420,25 +33419,25 @@
       </c>
     </row>
     <row r="1626">
-      <c r="A1626" s="25" t="n">
+      <c r="A1626" s="29" t="n">
         <v>247970</v>
       </c>
-      <c r="B1626" s="25" t="inlineStr">
+      <c r="B1626" s="29" t="inlineStr">
         <is>
           <t>#05 BEBIDA - #00 BEBIDAS GASEIFICADAS</t>
         </is>
       </c>
-      <c r="C1626" s="25" t="inlineStr">
+      <c r="C1626" s="29" t="inlineStr">
         <is>
           <t>BEBIDA ICE 51 275ML BALADA</t>
         </is>
       </c>
-      <c r="D1626" s="25" t="inlineStr">
+      <c r="D1626" s="29" t="inlineStr">
         <is>
           <t>BEBIDA ICE 51 275ML BALADA</t>
         </is>
       </c>
-      <c r="E1626" s="25" t="inlineStr"/>
+      <c r="E1626" s="29" t="inlineStr"/>
     </row>
     <row r="1627">
       <c r="A1627" s="25" t="n">
@@ -34154,25 +34153,25 @@
       </c>
     </row>
     <row r="1662">
-      <c r="A1662" s="27" t="n">
+      <c r="A1662" s="28" t="n">
         <v>325127</v>
       </c>
-      <c r="B1662" s="27" t="inlineStr">
+      <c r="B1662" s="28" t="inlineStr">
         <is>
           <t>#05 BEBIDA - #00 BEBIDAS GASEIFICADAS</t>
         </is>
       </c>
-      <c r="C1662" s="27" t="inlineStr">
+      <c r="C1662" s="28" t="inlineStr">
         <is>
           <t>REFRIGERANTE H2OH LIMONETO 1,5L PET</t>
         </is>
       </c>
-      <c r="D1662" s="27" t="inlineStr">
+      <c r="D1662" s="28" t="inlineStr">
         <is>
           <t>REFRIGERANTE H2OH 1,5L LIMONETO</t>
         </is>
       </c>
-      <c r="E1662" s="27" t="inlineStr"/>
+      <c r="E1662" s="28" t="inlineStr"/>
     </row>
     <row r="1663">
       <c r="A1663" t="n">
@@ -34436,45 +34435,46 @@
       <c r="E1675" s="22" t="inlineStr"/>
     </row>
     <row r="1676">
-      <c r="A1676" s="27" t="n">
+      <c r="A1676" s="28" t="n">
         <v>102285</v>
       </c>
-      <c r="B1676" s="27" t="inlineStr">
+      <c r="B1676" s="28" t="inlineStr">
         <is>
           <t>#05 BEBIDA - #00 ENERGÉTICOS</t>
         </is>
       </c>
-      <c r="C1676" s="27" t="inlineStr">
+      <c r="C1676" s="28" t="inlineStr">
         <is>
           <t>ENERGETICO EXTRA POWER 473ML TRAD</t>
         </is>
       </c>
-      <c r="D1676" s="27" t="inlineStr">
+      <c r="D1676" s="28" t="inlineStr">
         <is>
           <t>ENERGETICO EXTRA POWER 473ML TRADICIONAL</t>
         </is>
       </c>
-      <c r="E1676" s="27" t="inlineStr"/>
+      <c r="E1676" s="28" t="inlineStr"/>
     </row>
     <row r="1677">
-      <c r="A1677" s="9" t="n">
+      <c r="A1677" s="32" t="n">
         <v>102287</v>
       </c>
-      <c r="B1677" s="9" t="inlineStr">
+      <c r="B1677" s="32" t="inlineStr">
         <is>
           <t>#05 BEBIDA - #00 ENERGÉTICOS</t>
         </is>
       </c>
-      <c r="C1677" s="9" t="inlineStr">
-        <is>
-          <t>ENERGETICO EXTRA POWER 270ML UNID</t>
-        </is>
-      </c>
-      <c r="D1677" s="9" t="inlineStr">
-        <is>
-          <t>ENERGETICO EXTRA POWER 270ML</t>
-        </is>
-      </c>
+      <c r="C1677" s="32" t="inlineStr">
+        <is>
+          <t>ENERGETICO EXTRA POWER 270ML TRAD UN</t>
+        </is>
+      </c>
+      <c r="D1677" s="32" t="inlineStr">
+        <is>
+          <t>ENERGETICO EXTRA POWER 270ML TRADICIONAL</t>
+        </is>
+      </c>
+      <c r="E1677" s="32" t="inlineStr"/>
     </row>
     <row r="1678">
       <c r="A1678" t="n">
@@ -34497,24 +34497,25 @@
       </c>
     </row>
     <row r="1679">
-      <c r="A1679" t="n">
+      <c r="A1679" s="29" t="n">
         <v>117100</v>
       </c>
-      <c r="B1679" t="inlineStr">
+      <c r="B1679" s="29" t="inlineStr">
         <is>
           <t>#05 BEBIDA - #00 ENERGÉTICOS</t>
         </is>
       </c>
-      <c r="C1679" t="inlineStr">
+      <c r="C1679" s="29" t="inlineStr">
         <is>
           <t>ENERGETICO EXTRA POWER 2L</t>
         </is>
       </c>
-      <c r="D1679" t="inlineStr">
+      <c r="D1679" s="29" t="inlineStr">
         <is>
           <t>ENERGETICO EXTRA POWER 2L</t>
         </is>
       </c>
+      <c r="E1679" s="29" t="inlineStr"/>
     </row>
     <row r="1680">
       <c r="A1680" s="9" t="n">
@@ -35438,25 +35439,25 @@
       </c>
     </row>
     <row r="1726">
-      <c r="A1726" s="27" t="n">
+      <c r="A1726" s="28" t="n">
         <v>108631</v>
       </c>
-      <c r="B1726" s="27" t="inlineStr">
+      <c r="B1726" s="28" t="inlineStr">
         <is>
           <t>#05 BEBIDA - #01 SUCOS PRONTOS</t>
         </is>
       </c>
-      <c r="C1726" s="27" t="inlineStr">
+      <c r="C1726" s="28" t="inlineStr">
         <is>
           <t>SUCO DAFRUTA CONCENTRADO PET 500ML  CAJU</t>
         </is>
       </c>
-      <c r="D1726" s="27" t="inlineStr">
+      <c r="D1726" s="28" t="inlineStr">
         <is>
           <t>SUCO CONCENTRADO DAFRUTA 500ML CAJU</t>
         </is>
       </c>
-      <c r="E1726" s="27" t="inlineStr"/>
+      <c r="E1726" s="28" t="inlineStr"/>
     </row>
     <row r="1727">
       <c r="A1727" t="n">
@@ -35599,25 +35600,25 @@
       </c>
     </row>
     <row r="1734">
-      <c r="A1734" s="27" t="n">
+      <c r="A1734" s="28" t="n">
         <v>264452</v>
       </c>
-      <c r="B1734" s="27" t="inlineStr">
+      <c r="B1734" s="28" t="inlineStr">
         <is>
           <t>#05 BEBIDA - #01 SUCOS PRONTOS</t>
         </is>
       </c>
-      <c r="C1734" s="27" t="inlineStr">
+      <c r="C1734" s="28" t="inlineStr">
         <is>
           <t>SUCO PRONTO DAFRUTA 1L NECTAR UVA</t>
         </is>
       </c>
-      <c r="D1734" s="27" t="inlineStr">
+      <c r="D1734" s="28" t="inlineStr">
         <is>
           <t>SUCO PRONTO DAFRUTA 1L NECTAR UVA</t>
         </is>
       </c>
-      <c r="E1734" s="27" t="inlineStr"/>
+      <c r="E1734" s="28" t="inlineStr"/>
     </row>
     <row r="1735">
       <c r="A1735" t="n">
@@ -35680,25 +35681,25 @@
       </c>
     </row>
     <row r="1738">
-      <c r="A1738" s="27" t="n">
+      <c r="A1738" s="28" t="n">
         <v>286325</v>
       </c>
-      <c r="B1738" s="27" t="inlineStr">
+      <c r="B1738" s="28" t="inlineStr">
         <is>
           <t>#05 BEBIDA - #01 SUCOS PRONTOS</t>
         </is>
       </c>
-      <c r="C1738" s="27" t="inlineStr">
+      <c r="C1738" s="28" t="inlineStr">
         <is>
           <t>SUCO DE UVA AURORA 1,5LT TINTO TP</t>
         </is>
       </c>
-      <c r="D1738" s="27" t="inlineStr">
+      <c r="D1738" s="28" t="inlineStr">
         <is>
           <t>SUCO AURORA TP 1,5L UVA TINTO</t>
         </is>
       </c>
-      <c r="E1738" s="27" t="inlineStr"/>
+      <c r="E1738" s="28" t="inlineStr"/>
     </row>
     <row r="1739">
       <c r="A1739" t="n">
@@ -35721,25 +35722,25 @@
       </c>
     </row>
     <row r="1740">
-      <c r="A1740" s="27" t="n">
+      <c r="A1740" s="28" t="n">
         <v>288980</v>
       </c>
-      <c r="B1740" s="27" t="inlineStr">
+      <c r="B1740" s="28" t="inlineStr">
         <is>
           <t>#05 BEBIDA - #01 SUCOS PRONTOS</t>
         </is>
       </c>
-      <c r="C1740" s="27" t="inlineStr">
+      <c r="C1740" s="28" t="inlineStr">
         <is>
           <t>AGUA DE COCO COPRA 1L C/POLPA TP</t>
         </is>
       </c>
-      <c r="D1740" s="27" t="inlineStr">
+      <c r="D1740" s="28" t="inlineStr">
         <is>
           <t>ÁGUA DE COCO COPRA TP 1L COM POLPA</t>
         </is>
       </c>
-      <c r="E1740" s="27" t="inlineStr"/>
+      <c r="E1740" s="28" t="inlineStr"/>
     </row>
     <row r="1741">
       <c r="A1741" t="n">
@@ -36709,25 +36710,25 @@
       </c>
     </row>
     <row r="1789">
-      <c r="A1789" s="22" t="n">
+      <c r="A1789" s="29" t="n">
         <v>157496</v>
       </c>
-      <c r="B1789" s="22" t="inlineStr">
+      <c r="B1789" s="29" t="inlineStr">
         <is>
           <t>#05 BEBIDA - CERVEJAS</t>
         </is>
       </c>
-      <c r="C1789" s="22" t="inlineStr">
+      <c r="C1789" s="29" t="inlineStr">
         <is>
           <t>CERVEJA HEINEKEN GARRAFA 600ML</t>
         </is>
       </c>
-      <c r="D1789" s="22" t="inlineStr">
+      <c r="D1789" s="29" t="inlineStr">
         <is>
           <t>CERVEJA HEINEKEN 600ML</t>
         </is>
       </c>
-      <c r="E1789" s="22" t="inlineStr"/>
+      <c r="E1789" s="29" t="inlineStr"/>
     </row>
     <row r="1790">
       <c r="A1790" t="n">
@@ -36810,25 +36811,25 @@
       </c>
     </row>
     <row r="1794">
-      <c r="A1794" s="22" t="n">
+      <c r="A1794" s="29" t="n">
         <v>183095</v>
       </c>
-      <c r="B1794" s="22" t="inlineStr">
+      <c r="B1794" s="29" t="inlineStr">
         <is>
           <t>#05 BEBIDA - CERVEJAS</t>
         </is>
       </c>
-      <c r="C1794" s="22" t="inlineStr">
+      <c r="C1794" s="29" t="inlineStr">
         <is>
           <t>CERVEJA SOL 330ML PREMIUM LN</t>
         </is>
       </c>
-      <c r="D1794" s="22" t="inlineStr">
+      <c r="D1794" s="29" t="inlineStr">
         <is>
           <t>CERVEJA SOL PREMIUM LONG NECK 330ML</t>
         </is>
       </c>
-      <c r="E1794" s="22" t="inlineStr"/>
+      <c r="E1794" s="29" t="inlineStr"/>
     </row>
     <row r="1795">
       <c r="A1795" t="n">
@@ -37353,46 +37354,46 @@
       </c>
     </row>
     <row r="1821">
-      <c r="A1821" s="27" t="n">
+      <c r="A1821" s="28" t="n">
         <v>288739</v>
       </c>
-      <c r="B1821" s="27" t="inlineStr">
+      <c r="B1821" s="28" t="inlineStr">
         <is>
           <t>#05 BEBIDA - CERVEJAS</t>
         </is>
       </c>
-      <c r="C1821" s="27" t="inlineStr">
+      <c r="C1821" s="28" t="inlineStr">
         <is>
           <t>CERV STELLA ARTOIS 330ML PURE GOLD UNID</t>
         </is>
       </c>
-      <c r="D1821" s="27" t="inlineStr">
+      <c r="D1821" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">CERVEJA STELLA ARTOIS PURE GOLD LONG NECK 330ML </t>
         </is>
       </c>
-      <c r="E1821" s="27" t="inlineStr"/>
+      <c r="E1821" s="28" t="inlineStr"/>
     </row>
     <row r="1822">
-      <c r="A1822" s="27" t="n">
+      <c r="A1822" s="32" t="n">
         <v>302401</v>
       </c>
-      <c r="B1822" s="27" t="inlineStr">
+      <c r="B1822" s="32" t="inlineStr">
         <is>
           <t>#05 BEBIDA - CERVEJAS</t>
         </is>
       </c>
-      <c r="C1822" s="27" t="inlineStr">
+      <c r="C1822" s="32" t="inlineStr">
         <is>
           <t>CERVEJA IMPERIO ULTRA 275ML LN</t>
         </is>
       </c>
-      <c r="D1822" s="27" t="inlineStr">
+      <c r="D1822" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">CERVEJA IMPERIO ULTRA LONG NECK 275ML </t>
         </is>
       </c>
-      <c r="E1822" s="27" t="inlineStr"/>
+      <c r="E1822" s="32" t="inlineStr"/>
     </row>
     <row r="1823">
       <c r="A1823" t="n">
@@ -37475,24 +37476,25 @@
       </c>
     </row>
     <row r="1827">
-      <c r="A1827" t="n">
+      <c r="A1827" s="29" t="n">
         <v>325999</v>
       </c>
-      <c r="B1827" t="inlineStr">
+      <c r="B1827" s="29" t="inlineStr">
         <is>
           <t>#05 BEBIDA - CERVEJAS</t>
         </is>
       </c>
-      <c r="C1827" t="inlineStr">
+      <c r="C1827" s="29" t="inlineStr">
         <is>
           <t>CERVEJA IMPERIO 210ML LAGER PURO MALTE</t>
         </is>
       </c>
-      <c r="D1827" t="inlineStr">
+      <c r="D1827" s="29" t="inlineStr">
         <is>
           <t>CERVEJA IMPERIO PURO MALTE LAGER 210ML</t>
         </is>
       </c>
+      <c r="E1827" s="29" t="inlineStr"/>
     </row>
     <row r="1828">
       <c r="A1828" t="n">
@@ -37655,25 +37657,25 @@
       </c>
     </row>
     <row r="1836">
-      <c r="A1836" s="27" t="n">
+      <c r="A1836" s="28" t="n">
         <v>136330</v>
       </c>
-      <c r="B1836" s="27" t="inlineStr">
+      <c r="B1836" s="28" t="inlineStr">
         <is>
           <t>#05 BEBIDA - CERVEJAS CX</t>
         </is>
       </c>
-      <c r="C1836" s="27" t="inlineStr">
+      <c r="C1836" s="28" t="inlineStr">
         <is>
           <t>CERVEJA PETRA 269ML PURO MALTE LT</t>
         </is>
       </c>
-      <c r="D1836" s="27" t="inlineStr">
+      <c r="D1836" s="28" t="inlineStr">
         <is>
           <t>CERVEJA PETRA PURO MALTE 12 X 269ML</t>
         </is>
       </c>
-      <c r="E1836" s="27" t="inlineStr"/>
+      <c r="E1836" s="28" t="inlineStr"/>
     </row>
     <row r="1837">
       <c r="A1837" t="n">
@@ -37696,25 +37698,25 @@
       </c>
     </row>
     <row r="1838">
-      <c r="A1838" s="27" t="n">
+      <c r="A1838" s="28" t="n">
         <v>168712</v>
       </c>
-      <c r="B1838" s="27" t="inlineStr">
+      <c r="B1838" s="28" t="inlineStr">
         <is>
           <t>#05 BEBIDA - CERVEJAS CX</t>
         </is>
       </c>
-      <c r="C1838" s="27" t="inlineStr">
+      <c r="C1838" s="28" t="inlineStr">
         <is>
           <t>CERVEJA ANTARCTICA 269ML PILSEN</t>
         </is>
       </c>
-      <c r="D1838" s="27" t="inlineStr">
+      <c r="D1838" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">CERVEJA ANTARCTICA PILSEN 15 X 269ML </t>
         </is>
       </c>
-      <c r="E1838" s="27" t="inlineStr"/>
+      <c r="E1838" s="28" t="inlineStr"/>
     </row>
     <row r="1839">
       <c r="A1839" s="9" t="n">
@@ -37857,25 +37859,25 @@
       </c>
     </row>
     <row r="1846">
-      <c r="A1846" s="27" t="n">
+      <c r="A1846" s="28" t="n">
         <v>239446</v>
       </c>
-      <c r="B1846" s="27" t="inlineStr">
+      <c r="B1846" s="28" t="inlineStr">
         <is>
           <t>#05 BEBIDA - CERVEJAS CX</t>
         </is>
       </c>
-      <c r="C1846" s="27" t="inlineStr">
+      <c r="C1846" s="28" t="inlineStr">
         <is>
           <t>CERVEJA AMSTEL 269ML LAGER LT</t>
         </is>
       </c>
-      <c r="D1846" s="27" t="inlineStr">
+      <c r="D1846" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">CERVEJA AMSTEL LAGER 12 X 269ML </t>
         </is>
       </c>
-      <c r="E1846" s="27" t="inlineStr"/>
+      <c r="E1846" s="28" t="inlineStr"/>
     </row>
     <row r="1847">
       <c r="A1847" t="n">
@@ -37918,25 +37920,25 @@
       </c>
     </row>
     <row r="1849">
-      <c r="A1849" s="22" t="n">
+      <c r="A1849" s="32" t="n">
         <v>258893</v>
       </c>
-      <c r="B1849" s="22" t="inlineStr">
+      <c r="B1849" s="32" t="inlineStr">
         <is>
           <t>#05 BEBIDA - CERVEJAS CX</t>
         </is>
       </c>
-      <c r="C1849" s="22" t="inlineStr">
+      <c r="C1849" s="32" t="inlineStr">
         <is>
           <t>CERV ANTARCTICA ORIGINAL LT 269ML</t>
         </is>
       </c>
-      <c r="D1849" s="22" t="inlineStr">
+      <c r="D1849" s="32" t="inlineStr">
         <is>
           <t>CERVEJA ANTARCTICA ORIGINAL 15 X 269ML</t>
         </is>
       </c>
-      <c r="E1849" s="22" t="inlineStr"/>
+      <c r="E1849" s="32" t="inlineStr"/>
     </row>
     <row r="1850">
       <c r="A1850" t="n">
@@ -37999,25 +38001,25 @@
       </c>
     </row>
     <row r="1853">
-      <c r="A1853" s="25" t="n">
+      <c r="A1853" s="32" t="n">
         <v>271001</v>
       </c>
-      <c r="B1853" s="25" t="inlineStr">
+      <c r="B1853" s="32" t="inlineStr">
         <is>
           <t>#05 BEBIDA - CERVEJAS CX</t>
         </is>
       </c>
-      <c r="C1853" s="25" t="inlineStr">
+      <c r="C1853" s="32" t="inlineStr">
         <is>
           <t>CERVEJA IMPERIO  PURO MALTE 269ML PACK C</t>
         </is>
       </c>
-      <c r="D1853" s="25" t="inlineStr">
+      <c r="D1853" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">CERVEJA IMPERIO PURO MALTE 15 X 269ML </t>
         </is>
       </c>
-      <c r="E1853" s="25" t="inlineStr"/>
+      <c r="E1853" s="32" t="inlineStr"/>
     </row>
     <row r="1854">
       <c r="A1854" t="n">
@@ -38240,25 +38242,25 @@
       </c>
     </row>
     <row r="1865">
-      <c r="A1865" s="27" t="n">
+      <c r="A1865" s="28" t="n">
         <v>324556</v>
       </c>
-      <c r="B1865" s="27" t="inlineStr">
+      <c r="B1865" s="28" t="inlineStr">
         <is>
           <t>#05 BEBIDA - CERVEJAS CX</t>
         </is>
       </c>
-      <c r="C1865" s="27" t="inlineStr">
+      <c r="C1865" s="28" t="inlineStr">
         <is>
           <t>CERVEJA SKOL PILSEN 269ML ECO</t>
         </is>
       </c>
-      <c r="D1865" s="27" t="inlineStr">
+      <c r="D1865" s="28" t="inlineStr">
         <is>
           <t>CERVEJA SKOL PILSEN 15 X 269ML</t>
         </is>
       </c>
-      <c r="E1865" s="27" t="inlineStr"/>
+      <c r="E1865" s="28" t="inlineStr"/>
     </row>
     <row r="1866">
       <c r="A1866" t="n">
@@ -38281,25 +38283,25 @@
       </c>
     </row>
     <row r="1867">
-      <c r="A1867" s="25" t="n">
+      <c r="A1867" s="32" t="n">
         <v>341231</v>
       </c>
-      <c r="B1867" s="25" t="inlineStr">
+      <c r="B1867" s="32" t="inlineStr">
         <is>
           <t>#05 BEBIDA - CERVEJAS CX</t>
         </is>
       </c>
-      <c r="C1867" s="25" t="inlineStr">
+      <c r="C1867" s="32" t="inlineStr">
         <is>
           <t>CERVEJA ANTARCTICA 269ML MULTIPACK</t>
         </is>
       </c>
-      <c r="D1867" s="25" t="inlineStr">
+      <c r="D1867" s="32" t="inlineStr">
         <is>
           <t>CERVEJA ANTARCTICA 15 X 269ML MULTIPACK</t>
         </is>
       </c>
-      <c r="E1867" s="25" t="inlineStr"/>
+      <c r="E1867" s="32" t="inlineStr"/>
     </row>
     <row r="1868">
       <c r="A1868" s="15" t="n">
@@ -38443,25 +38445,25 @@
       </c>
     </row>
     <row r="1875">
-      <c r="A1875" s="27" t="n">
+      <c r="A1875" s="28" t="n">
         <v>102085</v>
       </c>
-      <c r="B1875" s="27" t="inlineStr">
+      <c r="B1875" s="28" t="inlineStr">
         <is>
           <t>#05 BEBIDA - DESTILADOS</t>
         </is>
       </c>
-      <c r="C1875" s="27" t="inlineStr">
+      <c r="C1875" s="28" t="inlineStr">
         <is>
           <t>CACHACA 51 PIRASSUNUNGA 965ML</t>
         </is>
       </c>
-      <c r="D1875" s="27" t="inlineStr">
+      <c r="D1875" s="28" t="inlineStr">
         <is>
           <t>CACHAÇA 51 965ML</t>
         </is>
       </c>
-      <c r="E1875" s="27" t="inlineStr"/>
+      <c r="E1875" s="28" t="inlineStr"/>
     </row>
     <row r="1876">
       <c r="A1876" t="n">
@@ -38625,25 +38627,25 @@
       <c r="E1883" s="17" t="inlineStr"/>
     </row>
     <row r="1884">
-      <c r="A1884" s="27" t="n">
+      <c r="A1884" s="28" t="n">
         <v>102243</v>
       </c>
-      <c r="B1884" s="27" t="inlineStr">
+      <c r="B1884" s="28" t="inlineStr">
         <is>
           <t>#05 BEBIDA - DESTILADOS</t>
         </is>
       </c>
-      <c r="C1884" s="27" t="inlineStr">
+      <c r="C1884" s="28" t="inlineStr">
         <is>
           <t>CONHAQUE SAO JOAO DA BARRA 900ML TRAD</t>
         </is>
       </c>
-      <c r="D1884" s="27" t="inlineStr">
+      <c r="D1884" s="28" t="inlineStr">
         <is>
           <t>CONHAQUE SÃO JOÃO DA BARRA 900ML TRADICIONAL</t>
         </is>
       </c>
-      <c r="E1884" s="27" t="inlineStr"/>
+      <c r="E1884" s="28" t="inlineStr"/>
     </row>
     <row r="1885">
       <c r="A1885" t="n">
@@ -38726,46 +38728,46 @@
       </c>
     </row>
     <row r="1889">
-      <c r="A1889" s="22" t="n">
+      <c r="A1889" s="29" t="n">
         <v>109727</v>
       </c>
-      <c r="B1889" s="22" t="inlineStr">
+      <c r="B1889" s="29" t="inlineStr">
         <is>
           <t>#05 BEBIDA - DESTILADOS</t>
         </is>
       </c>
-      <c r="C1889" s="22" t="inlineStr">
+      <c r="C1889" s="29" t="inlineStr">
         <is>
           <t>WHISKY CHIVAS REGAL 12ANOS 1LT</t>
         </is>
       </c>
-      <c r="D1889" s="22" t="inlineStr">
+      <c r="D1889" s="29" t="inlineStr">
         <is>
           <t>WHISKY CHIVAS REGAL 1L 12 ANOS</t>
         </is>
       </c>
-      <c r="E1889" s="22" t="inlineStr"/>
+      <c r="E1889" s="29" t="inlineStr"/>
     </row>
     <row r="1890">
-      <c r="A1890" s="27" t="n">
+      <c r="A1890" s="28" t="n">
         <v>109729</v>
       </c>
-      <c r="B1890" s="27" t="inlineStr">
+      <c r="B1890" s="28" t="inlineStr">
         <is>
           <t>#05 BEBIDA - DESTILADOS</t>
         </is>
       </c>
-      <c r="C1890" s="27" t="inlineStr">
+      <c r="C1890" s="28" t="inlineStr">
         <is>
           <t>WHISKY WHITE HORSE 1LT</t>
         </is>
       </c>
-      <c r="D1890" s="27" t="inlineStr">
+      <c r="D1890" s="28" t="inlineStr">
         <is>
           <t>WHISKY WHITE HORSE 1L</t>
         </is>
       </c>
-      <c r="E1890" s="27" t="inlineStr"/>
+      <c r="E1890" s="28" t="inlineStr"/>
     </row>
     <row r="1891">
       <c r="A1891" t="n">
@@ -38889,24 +38891,25 @@
       </c>
     </row>
     <row r="1897">
-      <c r="A1897" t="n">
+      <c r="A1897" s="29" t="n">
         <v>123548</v>
       </c>
-      <c r="B1897" t="inlineStr">
+      <c r="B1897" s="29" t="inlineStr">
         <is>
           <t>#05 BEBIDA - DESTILADOS</t>
         </is>
       </c>
-      <c r="C1897" t="inlineStr">
+      <c r="C1897" s="29" t="inlineStr">
         <is>
           <t>VODKA IMP ABSOLUT NAT 1L</t>
         </is>
       </c>
-      <c r="D1897" t="inlineStr">
+      <c r="D1897" s="29" t="inlineStr">
         <is>
           <t>VODKA ABSOLUT 1L</t>
         </is>
       </c>
+      <c r="E1897" s="29" t="inlineStr"/>
     </row>
     <row r="1898">
       <c r="A1898" s="15" t="n">
@@ -38991,25 +38994,25 @@
       </c>
     </row>
     <row r="1902">
-      <c r="A1902" s="25" t="n">
+      <c r="A1902" s="29" t="n">
         <v>149113</v>
       </c>
-      <c r="B1902" s="25" t="inlineStr">
+      <c r="B1902" s="29" t="inlineStr">
         <is>
           <t>#05 BEBIDA - DESTILADOS</t>
         </is>
       </c>
-      <c r="C1902" s="25" t="inlineStr">
+      <c r="C1902" s="29" t="inlineStr">
         <is>
           <t>AGUARD 29 GARRAFA  600ML</t>
         </is>
       </c>
-      <c r="D1902" s="25" t="inlineStr">
+      <c r="D1902" s="29" t="inlineStr">
         <is>
           <t>AGUARDENTE 29 600ML</t>
         </is>
       </c>
-      <c r="E1902" s="25" t="inlineStr"/>
+      <c r="E1902" s="29" t="inlineStr"/>
     </row>
     <row r="1903">
       <c r="A1903" t="n">
@@ -39575,24 +39578,25 @@
       </c>
     </row>
     <row r="1931">
-      <c r="A1931" s="9" t="n">
+      <c r="A1931" s="29" t="n">
         <v>230698</v>
       </c>
-      <c r="B1931" s="9" t="inlineStr">
+      <c r="B1931" s="29" t="inlineStr">
         <is>
           <t>#05 BEBIDA - DESTILADOS</t>
         </is>
       </c>
-      <c r="C1931" s="9" t="inlineStr">
+      <c r="C1931" s="29" t="inlineStr">
         <is>
           <t>BE GIN TANQUERAI TEN 750 ML 750 ML</t>
         </is>
       </c>
-      <c r="D1931" s="9" t="inlineStr">
+      <c r="D1931" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">GIN TANQUERAI 750ML TEN </t>
         </is>
       </c>
+      <c r="E1931" s="29" t="inlineStr"/>
     </row>
     <row r="1932">
       <c r="A1932" t="n">
@@ -39695,25 +39699,25 @@
       </c>
     </row>
     <row r="1937">
-      <c r="A1937" s="22" t="n">
+      <c r="A1937" s="29" t="n">
         <v>236673</v>
       </c>
-      <c r="B1937" s="22" t="inlineStr">
+      <c r="B1937" s="29" t="inlineStr">
         <is>
           <t>#05 BEBIDA - DESTILADOS</t>
         </is>
       </c>
-      <c r="C1937" s="22" t="inlineStr">
+      <c r="C1937" s="29" t="inlineStr">
         <is>
           <t>BEB FIU FIU TANGERINA ACEROLA 750ML</t>
         </is>
       </c>
-      <c r="D1937" s="22" t="inlineStr">
+      <c r="D1937" s="29" t="inlineStr">
         <is>
           <t>BEBIDA ALCOOLICA FIU FIU 750ML TANGERINA ACEROLA</t>
         </is>
       </c>
-      <c r="E1937" s="22" t="inlineStr"/>
+      <c r="E1937" s="29" t="inlineStr"/>
     </row>
     <row r="1938">
       <c r="A1938" t="n">
@@ -39996,24 +40000,25 @@
       </c>
     </row>
     <row r="1952">
-      <c r="A1952" s="9" t="n">
+      <c r="A1952" s="29" t="n">
         <v>284865</v>
       </c>
-      <c r="B1952" s="9" t="inlineStr">
+      <c r="B1952" s="29" t="inlineStr">
         <is>
           <t>#05 BEBIDA - DESTILADOS</t>
         </is>
       </c>
-      <c r="C1952" s="9" t="inlineStr">
+      <c r="C1952" s="29" t="inlineStr">
         <is>
           <t>CONHAQUE DREHER 900ML ORIGINAL</t>
         </is>
       </c>
-      <c r="D1952" s="9" t="inlineStr">
+      <c r="D1952" s="29" t="inlineStr">
         <is>
           <t>CONHAQUE DREHER 900ML ORIGINAL</t>
         </is>
       </c>
+      <c r="E1952" s="29" t="inlineStr"/>
     </row>
     <row r="1953">
       <c r="A1953" t="n">
@@ -40481,25 +40486,25 @@
       </c>
     </row>
     <row r="1976">
-      <c r="A1976" s="27" t="n">
+      <c r="A1976" s="28" t="n">
         <v>139964</v>
       </c>
-      <c r="B1976" s="27" t="inlineStr">
+      <c r="B1976" s="28" t="inlineStr">
         <is>
           <t>#05 BEBIDA - FERMENTADOS</t>
         </is>
       </c>
-      <c r="C1976" s="27" t="inlineStr">
+      <c r="C1976" s="28" t="inlineStr">
         <is>
           <t>VINHO PERGOLA 1LT TINTO SUAVE</t>
         </is>
       </c>
-      <c r="D1976" s="27" t="inlineStr">
+      <c r="D1976" s="28" t="inlineStr">
         <is>
           <t>VINHO PERGOLA 1L TINTO SUAVE</t>
         </is>
       </c>
-      <c r="E1976" s="27" t="inlineStr"/>
+      <c r="E1976" s="28" t="inlineStr"/>
     </row>
     <row r="1977">
       <c r="A1977" s="9" t="n">
@@ -40762,25 +40767,25 @@
       </c>
     </row>
     <row r="1990">
-      <c r="A1990" s="27" t="n">
+      <c r="A1990" s="28" t="n">
         <v>295198</v>
       </c>
-      <c r="B1990" s="27" t="inlineStr">
+      <c r="B1990" s="28" t="inlineStr">
         <is>
           <t>#05 BEBIDA - FERMENTADOS</t>
         </is>
       </c>
-      <c r="C1990" s="27" t="inlineStr">
+      <c r="C1990" s="28" t="inlineStr">
         <is>
           <t>CHOPP DE VINHO STEMPEL 600ML RED</t>
         </is>
       </c>
-      <c r="D1990" s="27" t="inlineStr">
+      <c r="D1990" s="28" t="inlineStr">
         <is>
           <t>CHOPP DE VINHO STEMPEL 600ML RED</t>
         </is>
       </c>
-      <c r="E1990" s="27" t="inlineStr"/>
+      <c r="E1990" s="28" t="inlineStr"/>
     </row>
     <row r="1991">
       <c r="A1991" t="n">
@@ -41264,25 +41269,25 @@
       </c>
     </row>
     <row r="2015">
-      <c r="A2015" s="27" t="n">
+      <c r="A2015" s="32" t="n">
         <v>100426</v>
       </c>
-      <c r="B2015" s="27" t="inlineStr">
+      <c r="B2015" s="32" t="inlineStr">
         <is>
           <t>#06 LIMPEZA - ALVEJANTES E ÁGUA SANITÁRIA</t>
         </is>
       </c>
-      <c r="C2015" s="27" t="inlineStr">
+      <c r="C2015" s="32" t="inlineStr">
         <is>
           <t>ÁGUA SANIT QBOA 1L MULTIPLO USO</t>
         </is>
       </c>
-      <c r="D2015" s="27" t="inlineStr">
+      <c r="D2015" s="32" t="inlineStr">
         <is>
           <t>ÁGUA SANITÁRIA QBOA 1L</t>
         </is>
       </c>
-      <c r="E2015" s="27" t="inlineStr"/>
+      <c r="E2015" s="32" t="inlineStr"/>
     </row>
     <row r="2016">
       <c r="A2016" t="n">
@@ -41305,67 +41310,67 @@
       </c>
     </row>
     <row r="2017">
-      <c r="A2017" s="27" t="n">
+      <c r="A2017" s="28" t="n">
         <v>100431</v>
       </c>
-      <c r="B2017" s="27" t="inlineStr">
+      <c r="B2017" s="28" t="inlineStr">
         <is>
           <t>#06 LIMPEZA - ALVEJANTES E ÁGUA SANITÁRIA</t>
         </is>
       </c>
-      <c r="C2017" s="27" t="inlineStr">
+      <c r="C2017" s="28" t="inlineStr">
         <is>
           <t>ÁGUA SANIT QBOA 2L MULTI USO</t>
         </is>
       </c>
-      <c r="D2017" s="27" t="inlineStr">
+      <c r="D2017" s="28" t="inlineStr">
         <is>
           <t>ÁGUA SANITÁRIA QBOA 2L</t>
         </is>
       </c>
-      <c r="E2017" s="27" t="inlineStr"/>
+      <c r="E2017" s="28" t="inlineStr"/>
     </row>
     <row r="2018">
-      <c r="A2018" s="27" t="n">
+      <c r="A2018" s="28" t="n">
         <v>100440</v>
       </c>
-      <c r="B2018" s="27" t="inlineStr">
+      <c r="B2018" s="28" t="inlineStr">
         <is>
           <t>#06 LIMPEZA - ALVEJANTES E ÁGUA SANITÁRIA</t>
         </is>
       </c>
-      <c r="C2018" s="27" t="inlineStr">
+      <c r="C2018" s="28" t="inlineStr">
         <is>
           <t>ALVEJANTE QBOA 1LT LAVANDA</t>
         </is>
       </c>
-      <c r="D2018" s="27" t="inlineStr">
+      <c r="D2018" s="28" t="inlineStr">
         <is>
           <t>ALVEJANTE QBOA 1L LAVANDA</t>
         </is>
       </c>
-      <c r="E2018" s="27" t="inlineStr"/>
+      <c r="E2018" s="28" t="inlineStr"/>
     </row>
     <row r="2019">
-      <c r="A2019" s="27" t="n">
+      <c r="A2019" s="28" t="n">
         <v>100441</v>
       </c>
-      <c r="B2019" s="27" t="inlineStr">
+      <c r="B2019" s="28" t="inlineStr">
         <is>
           <t>#06 LIMPEZA - ALVEJANTES E ÁGUA SANITÁRIA</t>
         </is>
       </c>
-      <c r="C2019" s="27" t="inlineStr">
+      <c r="C2019" s="28" t="inlineStr">
         <is>
           <t>ALVEJANTE QBOA 1LT FLORAL</t>
         </is>
       </c>
-      <c r="D2019" s="27" t="inlineStr">
+      <c r="D2019" s="28" t="inlineStr">
         <is>
           <t>ALVEJANTE QBOA 1L FLORAL</t>
         </is>
       </c>
-      <c r="E2019" s="27" t="inlineStr"/>
+      <c r="E2019" s="28" t="inlineStr"/>
     </row>
     <row r="2020">
       <c r="A2020" t="n">
@@ -41510,25 +41515,25 @@
       <c r="E2026" s="17" t="inlineStr"/>
     </row>
     <row r="2027">
-      <c r="A2027" s="27" t="n">
+      <c r="A2027" s="32" t="n">
         <v>336903</v>
       </c>
-      <c r="B2027" s="27" t="inlineStr">
+      <c r="B2027" s="32" t="inlineStr">
         <is>
           <t>#06 LIMPEZA - ALVEJANTES E ÁGUA SANITÁRIA</t>
         </is>
       </c>
-      <c r="C2027" s="27" t="inlineStr">
+      <c r="C2027" s="32" t="inlineStr">
         <is>
           <t>PERCARBONATO DE SODIO TUFF 1KG</t>
         </is>
       </c>
-      <c r="D2027" s="27" t="inlineStr">
+      <c r="D2027" s="32" t="inlineStr">
         <is>
           <t>PERCARBONATO DE SODIO TUFF 1KG</t>
         </is>
       </c>
-      <c r="E2027" s="27" t="inlineStr"/>
+      <c r="E2027" s="32" t="inlineStr"/>
     </row>
     <row r="2028">
       <c r="A2028" t="n">
@@ -41612,25 +41617,25 @@
       </c>
     </row>
     <row r="2032">
-      <c r="A2032" s="27" t="n">
+      <c r="A2032" s="28" t="n">
         <v>106711</v>
       </c>
-      <c r="B2032" s="27" t="inlineStr">
+      <c r="B2032" s="28" t="inlineStr">
         <is>
           <t>#06 LIMPEZA - AMACIANTES</t>
         </is>
       </c>
-      <c r="C2032" s="27" t="inlineStr">
+      <c r="C2032" s="28" t="inlineStr">
         <is>
           <t>AMAC ROUPAS YPÊ 2LT ACONCHEGO</t>
         </is>
       </c>
-      <c r="D2032" s="27" t="inlineStr">
+      <c r="D2032" s="28" t="inlineStr">
         <is>
           <t>AMACIANTE DE ROUPAS YPÊ 2L ACONCHEGO</t>
         </is>
       </c>
-      <c r="E2032" s="27" t="inlineStr"/>
+      <c r="E2032" s="28" t="inlineStr"/>
     </row>
     <row r="2033">
       <c r="A2033" s="22" t="n">
@@ -42157,24 +42162,25 @@
       </c>
     </row>
     <row r="2059">
-      <c r="A2059" t="n">
+      <c r="A2059" s="32" t="n">
         <v>226474</v>
       </c>
-      <c r="B2059" t="inlineStr">
+      <c r="B2059" s="32" t="inlineStr">
         <is>
           <t>#06 LIMPEZA - AMACIANTES</t>
         </is>
       </c>
-      <c r="C2059" t="inlineStr">
+      <c r="C2059" s="32" t="inlineStr">
         <is>
           <t>AMAC CONC DOWNY 1,5LTS FRESCOR PRIMAVERA</t>
         </is>
       </c>
-      <c r="D2059" t="inlineStr">
+      <c r="D2059" s="32" t="inlineStr">
         <is>
           <t>AMACIANTE DE ROUPAS CONCENTRADO DOWNY 1,5L FRESCOR PRIMAVERA</t>
         </is>
       </c>
+      <c r="E2059" s="32" t="inlineStr"/>
     </row>
     <row r="2060">
       <c r="A2060" t="n">
@@ -43361,24 +43367,25 @@
       </c>
     </row>
     <row r="2119">
-      <c r="A2119" t="n">
+      <c r="A2119" s="32" t="n">
         <v>106629</v>
       </c>
-      <c r="B2119" t="inlineStr">
+      <c r="B2119" s="32" t="inlineStr">
         <is>
           <t>#06 LIMPEZA - DESINFETANTES</t>
         </is>
       </c>
-      <c r="C2119" t="inlineStr">
+      <c r="C2119" s="32" t="inlineStr">
         <is>
           <t>DESINF PINHO BRIL 1LT PLUS</t>
         </is>
       </c>
-      <c r="D2119" t="inlineStr">
+      <c r="D2119" s="32" t="inlineStr">
         <is>
           <t>DESINFETANTE PINHO BRIL 1L PLUS</t>
         </is>
       </c>
+      <c r="E2119" s="32" t="inlineStr"/>
     </row>
     <row r="2120">
       <c r="A2120" t="n">
@@ -43441,25 +43448,25 @@
       </c>
     </row>
     <row r="2123">
-      <c r="A2123" s="27" t="n">
+      <c r="A2123" s="28" t="n">
         <v>109602</v>
       </c>
-      <c r="B2123" s="27" t="inlineStr">
+      <c r="B2123" s="28" t="inlineStr">
         <is>
           <t>#06 LIMPEZA - DESINFETANTES</t>
         </is>
       </c>
-      <c r="C2123" s="27" t="inlineStr">
+      <c r="C2123" s="28" t="inlineStr">
         <is>
           <t>DESINFETANTE +FAMILIA 2L LAVANDA</t>
         </is>
       </c>
-      <c r="D2123" s="27" t="inlineStr">
+      <c r="D2123" s="28" t="inlineStr">
         <is>
           <t>DESINFETANTE +FAMILIA 2L LAVANDA</t>
         </is>
       </c>
-      <c r="E2123" s="27" t="inlineStr"/>
+      <c r="E2123" s="28" t="inlineStr"/>
     </row>
     <row r="2124">
       <c r="A2124" t="n">
@@ -44265,25 +44272,25 @@
       </c>
     </row>
     <row r="2164">
-      <c r="A2164" s="27" t="n">
+      <c r="A2164" s="32" t="n">
         <v>306803</v>
       </c>
-      <c r="B2164" s="27" t="inlineStr">
+      <c r="B2164" s="32" t="inlineStr">
         <is>
           <t>#06 LIMPEZA - DESINFETANTES</t>
         </is>
       </c>
-      <c r="C2164" s="27" t="inlineStr">
+      <c r="C2164" s="32" t="inlineStr">
         <is>
           <t>DESINFETANTE UAU 500ML BANHEIRO 7 EM 1</t>
         </is>
       </c>
-      <c r="D2164" s="27" t="inlineStr">
+      <c r="D2164" s="32" t="inlineStr">
         <is>
           <t>DESINFETANTE UAU 500ML BANHEIRO 7 EM 1</t>
         </is>
       </c>
-      <c r="E2164" s="27" t="inlineStr"/>
+      <c r="E2164" s="32" t="inlineStr"/>
     </row>
     <row r="2165">
       <c r="A2165" t="n">
@@ -44508,151 +44515,151 @@
       </c>
     </row>
     <row r="2176">
-      <c r="A2176" s="27" t="n">
+      <c r="A2176" s="32" t="n">
         <v>100390</v>
       </c>
-      <c r="B2176" s="27" t="inlineStr">
+      <c r="B2176" s="32" t="inlineStr">
         <is>
           <t>#06 LIMPEZA - DETERGENTES</t>
         </is>
       </c>
-      <c r="C2176" s="27" t="inlineStr">
+      <c r="C2176" s="32" t="inlineStr">
         <is>
           <t>DETERGENTE LIQ YPE 500ML NEUTRO</t>
         </is>
       </c>
-      <c r="D2176" s="27" t="inlineStr">
+      <c r="D2176" s="32" t="inlineStr">
         <is>
           <t>DETERGENTE LIQUIDO YPÊ 500ML NEUTRO</t>
         </is>
       </c>
-      <c r="E2176" s="27" t="inlineStr"/>
+      <c r="E2176" s="32" t="inlineStr"/>
     </row>
     <row r="2177">
-      <c r="A2177" s="27" t="n">
+      <c r="A2177" s="32" t="n">
         <v>100391</v>
       </c>
-      <c r="B2177" s="27" t="inlineStr">
+      <c r="B2177" s="32" t="inlineStr">
         <is>
           <t>#06 LIMPEZA - DETERGENTES</t>
         </is>
       </c>
-      <c r="C2177" s="27" t="inlineStr">
+      <c r="C2177" s="32" t="inlineStr">
         <is>
           <t>DETERGENTE LIQ YPE 500ML CAPIM LIMAO</t>
         </is>
       </c>
-      <c r="D2177" s="27" t="inlineStr">
+      <c r="D2177" s="32" t="inlineStr">
         <is>
           <t>DETERGENTE LIQUIDO YPÊ 500ML CAPIM LIMÃO</t>
         </is>
       </c>
-      <c r="E2177" s="27" t="inlineStr"/>
+      <c r="E2177" s="32" t="inlineStr"/>
     </row>
     <row r="2178">
-      <c r="A2178" s="27" t="n">
+      <c r="A2178" s="32" t="n">
         <v>100392</v>
       </c>
-      <c r="B2178" s="27" t="inlineStr">
+      <c r="B2178" s="32" t="inlineStr">
         <is>
           <t>#06 LIMPEZA - DETERGENTES</t>
         </is>
       </c>
-      <c r="C2178" s="27" t="inlineStr">
+      <c r="C2178" s="32" t="inlineStr">
         <is>
           <t>DETERGENTE LIQ YPE 500ML CLEAR CARE</t>
         </is>
       </c>
-      <c r="D2178" s="27" t="inlineStr">
+      <c r="D2178" s="32" t="inlineStr">
         <is>
           <t>DETERGENTE LIQUIDO YPÊ 500ML CLEAR CARE</t>
         </is>
       </c>
-      <c r="E2178" s="27" t="inlineStr"/>
+      <c r="E2178" s="32" t="inlineStr"/>
     </row>
     <row r="2179">
-      <c r="A2179" s="27" t="n">
+      <c r="A2179" s="32" t="n">
         <v>100393</v>
       </c>
-      <c r="B2179" s="27" t="inlineStr">
+      <c r="B2179" s="32" t="inlineStr">
         <is>
           <t>#06 LIMPEZA - DETERGENTES</t>
         </is>
       </c>
-      <c r="C2179" s="27" t="inlineStr">
+      <c r="C2179" s="32" t="inlineStr">
         <is>
           <t>DETERGENTE LIQ YPE 500ML MACA</t>
         </is>
       </c>
-      <c r="D2179" s="27" t="inlineStr">
+      <c r="D2179" s="32" t="inlineStr">
         <is>
           <t>DETERGENTE LIQUIDO YPÊ 500ML MACA</t>
         </is>
       </c>
-      <c r="E2179" s="27" t="inlineStr"/>
+      <c r="E2179" s="32" t="inlineStr"/>
     </row>
     <row r="2180">
-      <c r="A2180" s="27" t="n">
+      <c r="A2180" s="32" t="n">
         <v>100394</v>
       </c>
-      <c r="B2180" s="27" t="inlineStr">
+      <c r="B2180" s="32" t="inlineStr">
         <is>
           <t>#06 LIMPEZA - DETERGENTES</t>
         </is>
       </c>
-      <c r="C2180" s="27" t="inlineStr">
+      <c r="C2180" s="32" t="inlineStr">
         <is>
           <t>DETERGENTE LIQ YPE 500ML CLEAR</t>
         </is>
       </c>
-      <c r="D2180" s="27" t="inlineStr">
+      <c r="D2180" s="32" t="inlineStr">
         <is>
           <t>DETERGENTE LIQUIDO YPÊ 500ML CLEAR</t>
         </is>
       </c>
-      <c r="E2180" s="27" t="inlineStr"/>
+      <c r="E2180" s="32" t="inlineStr"/>
     </row>
     <row r="2181">
-      <c r="A2181" s="27" t="n">
+      <c r="A2181" s="32" t="n">
         <v>100402</v>
       </c>
-      <c r="B2181" s="27" t="inlineStr">
+      <c r="B2181" s="32" t="inlineStr">
         <is>
           <t>#06 LIMPEZA - DETERGENTES</t>
         </is>
       </c>
-      <c r="C2181" s="27" t="inlineStr">
+      <c r="C2181" s="32" t="inlineStr">
         <is>
           <t>DETERGENTE LIQ YPE 500ML COCO</t>
         </is>
       </c>
-      <c r="D2181" s="27" t="inlineStr">
+      <c r="D2181" s="32" t="inlineStr">
         <is>
           <t>DETERGENTE LIQUIDO YPÊ 500ML COCO</t>
         </is>
       </c>
-      <c r="E2181" s="27" t="inlineStr"/>
+      <c r="E2181" s="32" t="inlineStr"/>
     </row>
     <row r="2182">
-      <c r="A2182" s="27" t="n">
+      <c r="A2182" s="32" t="n">
         <v>100403</v>
       </c>
-      <c r="B2182" s="27" t="inlineStr">
+      <c r="B2182" s="32" t="inlineStr">
         <is>
           <t>#06 LIMPEZA - DETERGENTES</t>
         </is>
       </c>
-      <c r="C2182" s="27" t="inlineStr">
+      <c r="C2182" s="32" t="inlineStr">
         <is>
           <t>DETERGENTE LIQ YPE 500ML LIMAO</t>
         </is>
       </c>
-      <c r="D2182" s="27" t="inlineStr">
+      <c r="D2182" s="32" t="inlineStr">
         <is>
           <t>DETERGENTE LIQUIDO YPÊ 500ML LIMAO</t>
         </is>
       </c>
-      <c r="E2182" s="27" t="inlineStr"/>
+      <c r="E2182" s="32" t="inlineStr"/>
     </row>
     <row r="2183">
       <c r="A2183" s="8" t="n">
@@ -45322,25 +45329,25 @@
       </c>
     </row>
     <row r="2216">
-      <c r="A2216" s="27" t="n">
+      <c r="A2216" s="28" t="n">
         <v>291602</v>
       </c>
-      <c r="B2216" s="27" t="inlineStr">
+      <c r="B2216" s="28" t="inlineStr">
         <is>
           <t>#06 LIMPEZA - LAVA ROUPAS</t>
         </is>
       </c>
-      <c r="C2216" s="27" t="inlineStr">
+      <c r="C2216" s="28" t="inlineStr">
         <is>
           <t>LAVA ROUPA LIQUIDO BRILHANTE 7L LAV PROF</t>
         </is>
       </c>
-      <c r="D2216" s="27" t="inlineStr">
+      <c r="D2216" s="28" t="inlineStr">
         <is>
           <t>LAVA ROUPAS LÍQUIDO BRILHANTE 7L LAVANDERIA PROFISSIONAL</t>
         </is>
       </c>
-      <c r="E2216" s="27" t="inlineStr"/>
+      <c r="E2216" s="28" t="inlineStr"/>
     </row>
     <row r="2217">
       <c r="A2217" t="n">
@@ -45483,25 +45490,25 @@
       </c>
     </row>
     <row r="2224">
-      <c r="A2224" s="27" t="n">
+      <c r="A2224" s="32" t="n">
         <v>100511</v>
       </c>
-      <c r="B2224" s="27" t="inlineStr">
+      <c r="B2224" s="32" t="inlineStr">
         <is>
           <t>#06 LIMPEZA - LIMPA ALUMINIO</t>
         </is>
       </c>
-      <c r="C2224" s="27" t="inlineStr">
+      <c r="C2224" s="32" t="inlineStr">
         <is>
           <t>LIMPA ALUMINIO POLITRIZ 500ML LIMAO</t>
         </is>
       </c>
-      <c r="D2224" s="27" t="inlineStr">
+      <c r="D2224" s="32" t="inlineStr">
         <is>
           <t>LIMPA ALUMINIO POLITRIZ 500ML LIMÃO</t>
         </is>
       </c>
-      <c r="E2224" s="27" t="inlineStr"/>
+      <c r="E2224" s="32" t="inlineStr"/>
     </row>
     <row r="2225">
       <c r="A2225" s="14" t="n">
@@ -45586,25 +45593,25 @@
       </c>
     </row>
     <row r="2229">
-      <c r="A2229" s="27" t="n">
+      <c r="A2229" s="32" t="n">
         <v>122716</v>
       </c>
-      <c r="B2229" s="27" t="inlineStr">
+      <c r="B2229" s="32" t="inlineStr">
         <is>
           <t>#06 LIMPEZA - LIMPA ALUMINIO</t>
         </is>
       </c>
-      <c r="C2229" s="27" t="inlineStr">
+      <c r="C2229" s="32" t="inlineStr">
         <is>
           <t>LIMPA ALUMINIO POLITRIZ 500ML TRADICIONA</t>
         </is>
       </c>
-      <c r="D2229" s="27" t="inlineStr">
+      <c r="D2229" s="32" t="inlineStr">
         <is>
           <t>LIMPA ALUMINIO POLITRIZ 500ML TRADICIONAL</t>
         </is>
       </c>
-      <c r="E2229" s="27" t="inlineStr"/>
+      <c r="E2229" s="32" t="inlineStr"/>
     </row>
     <row r="2230">
       <c r="A2230" t="n">
@@ -47212,25 +47219,25 @@
       </c>
     </row>
     <row r="2310">
-      <c r="A2310" s="25" t="n">
+      <c r="A2310" s="32" t="n">
         <v>257710</v>
       </c>
-      <c r="B2310" s="25" t="inlineStr">
+      <c r="B2310" s="32" t="inlineStr">
         <is>
           <t>#06 LIMPEZA - SABÃO</t>
         </is>
       </c>
-      <c r="C2310" s="25" t="inlineStr">
+      <c r="C2310" s="32" t="inlineStr">
         <is>
           <t>SABAO BARRA YPE 5X160GR NEUTRO GLICERINA</t>
         </is>
       </c>
-      <c r="D2310" s="25" t="inlineStr">
+      <c r="D2310" s="32" t="inlineStr">
         <is>
           <t>SABÃO EM BARRA YPÊ 900G NEUTRO</t>
         </is>
       </c>
-      <c r="E2310" s="25" t="inlineStr"/>
+      <c r="E2310" s="32" t="inlineStr"/>
     </row>
     <row r="2311">
       <c r="A2311" t="n">
@@ -47313,25 +47320,25 @@
       </c>
     </row>
     <row r="2315">
-      <c r="A2315" s="27" t="n">
+      <c r="A2315" s="28" t="n">
         <v>261083</v>
       </c>
-      <c r="B2315" s="27" t="inlineStr">
+      <c r="B2315" s="28" t="inlineStr">
         <is>
           <t>#06 LIMPEZA - SABÃO</t>
         </is>
       </c>
-      <c r="C2315" s="27" t="inlineStr">
+      <c r="C2315" s="28" t="inlineStr">
         <is>
           <t>SABAO PO TIXAN YPE 800GR PRIMAVERA CAIXA</t>
         </is>
       </c>
-      <c r="D2315" s="27" t="inlineStr">
+      <c r="D2315" s="28" t="inlineStr">
         <is>
           <t>SABÃO EM PÓ TIXAN YPÊ CAIXA 800G PRIMAVERA</t>
         </is>
       </c>
-      <c r="E2315" s="27" t="inlineStr"/>
+      <c r="E2315" s="28" t="inlineStr"/>
     </row>
     <row r="2316">
       <c r="A2316" t="n">
@@ -47374,25 +47381,25 @@
       </c>
     </row>
     <row r="2318">
-      <c r="A2318" s="27" t="n">
+      <c r="A2318" s="28" t="n">
         <v>261360</v>
       </c>
-      <c r="B2318" s="27" t="inlineStr">
+      <c r="B2318" s="28" t="inlineStr">
         <is>
           <t>#06 LIMPEZA - SABÃO</t>
         </is>
       </c>
-      <c r="C2318" s="27" t="inlineStr">
+      <c r="C2318" s="28" t="inlineStr">
         <is>
           <t>SABAO BARRA MINUANO 800G NEUTRO GLIC</t>
         </is>
       </c>
-      <c r="D2318" s="27" t="inlineStr">
+      <c r="D2318" s="28" t="inlineStr">
         <is>
           <t>SABÃO EM BARRA MINUANO 800G NEUTRO GLICERINADO</t>
         </is>
       </c>
-      <c r="E2318" s="27" t="inlineStr"/>
+      <c r="E2318" s="28" t="inlineStr"/>
     </row>
     <row r="2319">
       <c r="A2319" t="n">
@@ -47455,25 +47462,25 @@
       </c>
     </row>
     <row r="2322">
-      <c r="A2322" s="22" t="n">
+      <c r="A2322" s="32" t="n">
         <v>261980</v>
       </c>
-      <c r="B2322" s="22" t="inlineStr">
+      <c r="B2322" s="32" t="inlineStr">
         <is>
           <t>#06 LIMPEZA - SABÃO</t>
         </is>
       </c>
-      <c r="C2322" s="22" t="inlineStr">
+      <c r="C2322" s="32" t="inlineStr">
         <is>
           <t>SABAO PO BRILHANTE 1,6KG CX LIMPEZA TOTA</t>
         </is>
       </c>
-      <c r="D2322" s="22" t="inlineStr">
+      <c r="D2322" s="32" t="inlineStr">
         <is>
           <t>SABÃO EM PÓ BRILHANTE CAIXA 1,6KG LIMPEZA TOTAL</t>
         </is>
       </c>
-      <c r="E2322" s="22" t="inlineStr"/>
+      <c r="E2322" s="32" t="inlineStr"/>
     </row>
     <row r="2323">
       <c r="A2323" t="n">
@@ -47516,25 +47523,25 @@
       </c>
     </row>
     <row r="2325">
-      <c r="A2325" s="27" t="n">
+      <c r="A2325" s="28" t="n">
         <v>286199</v>
       </c>
-      <c r="B2325" s="27" t="inlineStr">
+      <c r="B2325" s="28" t="inlineStr">
         <is>
           <t>#06 LIMPEZA - SABÃO</t>
         </is>
       </c>
-      <c r="C2325" s="27" t="inlineStr">
+      <c r="C2325" s="28" t="inlineStr">
         <is>
           <t>SABAO PO TIXAN YPE 800GR MACIEZ CAIXA</t>
         </is>
       </c>
-      <c r="D2325" s="27" t="inlineStr">
+      <c r="D2325" s="28" t="inlineStr">
         <is>
           <t>SABÃO EM PÓ TIXAN YPÊ CAIXA 800G MACIEZ</t>
         </is>
       </c>
-      <c r="E2325" s="27" t="inlineStr"/>
+      <c r="E2325" s="28" t="inlineStr"/>
     </row>
     <row r="2326">
       <c r="A2326" t="n">
@@ -47797,25 +47804,25 @@
       </c>
     </row>
     <row r="2339">
-      <c r="A2339" s="27" t="n">
+      <c r="A2339" s="32" t="n">
         <v>100373</v>
       </c>
-      <c r="B2339" s="27" t="inlineStr">
+      <c r="B2339" s="32" t="inlineStr">
         <is>
           <t>#06 LIMPEZA - SODAS CAUSTICAS</t>
         </is>
       </c>
-      <c r="C2339" s="27" t="inlineStr">
+      <c r="C2339" s="32" t="inlineStr">
         <is>
           <t>SODA CAUSTICA SOL 1KG</t>
         </is>
       </c>
-      <c r="D2339" s="27" t="inlineStr">
+      <c r="D2339" s="32" t="inlineStr">
         <is>
           <t>SODA CAUSTICA SOL 1KG</t>
         </is>
       </c>
-      <c r="E2339" s="27" t="inlineStr"/>
+      <c r="E2339" s="32" t="inlineStr"/>
     </row>
     <row r="2340">
       <c r="A2340" s="22" t="n">
@@ -57778,29 +57785,25 @@
       <c r="E2836" s="18" t="inlineStr"/>
     </row>
     <row r="2837">
-      <c r="A2837" s="31" t="n">
+      <c r="A2837" s="28" t="n">
         <v>107928</v>
       </c>
-      <c r="B2837" s="31" t="inlineStr">
+      <c r="B2837" s="28" t="inlineStr">
         <is>
           <t>#07 HIGIENE PESSOAL - HIGIENE BUCAL</t>
         </is>
       </c>
-      <c r="C2837" s="39" t="inlineStr">
+      <c r="C2837" s="28" t="inlineStr">
         <is>
           <t>CR DENTAL COLGATE MPA 180G</t>
         </is>
       </c>
-      <c r="D2837" s="31" t="inlineStr">
+      <c r="D2837" s="28" t="inlineStr">
         <is>
           <t>CREME DENTAL COLGATE 180G MPA MENTA REFRESCANTE</t>
         </is>
       </c>
-      <c r="E2837" s="31" t="inlineStr">
-        <is>
-          <t>CREME DENTAL COLGATE 180GR MENTA RESFRES</t>
-        </is>
-      </c>
+      <c r="E2837" s="28" t="inlineStr"/>
     </row>
     <row r="2838">
       <c r="A2838" s="25" t="n">
@@ -57944,25 +57947,25 @@
       </c>
     </row>
     <row r="2845">
-      <c r="A2845" s="31" t="n">
+      <c r="A2845" s="28" t="n">
         <v>235809</v>
       </c>
-      <c r="B2845" s="31" t="inlineStr">
+      <c r="B2845" s="28" t="inlineStr">
         <is>
           <t>#07 HIGIENE PESSOAL - HIGIENE BUCAL</t>
         </is>
       </c>
-      <c r="C2845" s="31" t="inlineStr">
+      <c r="C2845" s="28" t="inlineStr">
         <is>
           <t>CR D SORRISO TR LIMP COMP PCO ESP 120G</t>
         </is>
       </c>
-      <c r="D2845" s="31" t="inlineStr">
+      <c r="D2845" s="28" t="inlineStr">
         <is>
           <t>CREME DENTAL SORRISO 120G TRIPLA LIMPEZA COMPLETA</t>
         </is>
       </c>
-      <c r="E2845" s="31" t="inlineStr"/>
+      <c r="E2845" s="28" t="inlineStr"/>
     </row>
     <row r="2846">
       <c r="A2846" t="n">
@@ -59955,25 +59958,25 @@
       </c>
     </row>
     <row r="2945">
-      <c r="A2945" s="17" t="n">
+      <c r="A2945" s="32" t="n">
         <v>219705</v>
       </c>
-      <c r="B2945" s="17" t="inlineStr">
+      <c r="B2945" s="32" t="inlineStr">
         <is>
           <t>#07 HIGIENE PESSOAL - PAPEL HIGIENICO</t>
         </is>
       </c>
-      <c r="C2945" s="17" t="inlineStr">
+      <c r="C2945" s="32" t="inlineStr">
         <is>
           <t>PAPEL HIG MIMMO 30MTS LEV12 PAG11</t>
         </is>
       </c>
-      <c r="D2945" s="17" t="inlineStr">
+      <c r="D2945" s="32" t="inlineStr">
         <is>
           <t>PAPEL HIGIENICO MIMMO 12 X 30M PROMOCIONAL NEUTRO</t>
         </is>
       </c>
-      <c r="E2945" s="17" t="inlineStr"/>
+      <c r="E2945" s="32" t="inlineStr"/>
     </row>
     <row r="2946">
       <c r="A2946" t="n">
@@ -60236,25 +60239,25 @@
       </c>
     </row>
     <row r="2959">
-      <c r="A2959" s="27" t="n">
+      <c r="A2959" s="28" t="n">
         <v>346964</v>
       </c>
-      <c r="B2959" s="27" t="inlineStr">
+      <c r="B2959" s="28" t="inlineStr">
         <is>
           <t>#07 HIGIENE PESSOAL - PAPEL HIGIENICO</t>
         </is>
       </c>
-      <c r="C2959" s="27" t="inlineStr">
+      <c r="C2959" s="28" t="inlineStr">
         <is>
           <t>PAPEL HIG NOBLE FD 20M</t>
         </is>
       </c>
-      <c r="D2959" s="27" t="inlineStr">
+      <c r="D2959" s="28" t="inlineStr">
         <is>
           <t>PAPEL HIGIENICO NOBLE 12 X 20M FOLHA DUPLA</t>
         </is>
       </c>
-      <c r="E2959" s="27" t="inlineStr"/>
+      <c r="E2959" s="28" t="inlineStr"/>
     </row>
     <row r="2960">
       <c r="A2960" t="n">
@@ -60317,25 +60320,25 @@
       </c>
     </row>
     <row r="2963">
-      <c r="A2963" s="31" t="n">
+      <c r="A2963" s="28" t="n">
         <v>107698</v>
       </c>
-      <c r="B2963" s="31" t="inlineStr">
+      <c r="B2963" s="28" t="inlineStr">
         <is>
           <t>#07 HIGIENE PESSOAL - SABONETE</t>
         </is>
       </c>
-      <c r="C2963" s="31" t="inlineStr">
+      <c r="C2963" s="28" t="inlineStr">
         <is>
           <t>SAB PALMOLIVE 150GR ALOE E OLIVA</t>
         </is>
       </c>
-      <c r="D2963" s="31" t="inlineStr">
+      <c r="D2963" s="28" t="inlineStr">
         <is>
           <t>SABONETE PALMOLIVE 150G ALOE E OLIVA</t>
         </is>
       </c>
-      <c r="E2963" s="31" t="inlineStr"/>
+      <c r="E2963" s="28" t="inlineStr"/>
     </row>
     <row r="2964">
       <c r="A2964" t="n">
@@ -60346,7 +60349,7 @@
           <t>#07 HIGIENE PESSOAL - SABONETE</t>
         </is>
       </c>
-      <c r="C2964" s="32" t="inlineStr">
+      <c r="C2964" s="27" t="inlineStr">
         <is>
           <t>SAB PALMOLIVE 150GR LEITE E PETALAS ROSA</t>
         </is>
@@ -60366,7 +60369,7 @@
           <t>#07 HIGIENE PESSOAL - SABONETE</t>
         </is>
       </c>
-      <c r="C2965" s="32" t="inlineStr">
+      <c r="C2965" s="27" t="inlineStr">
         <is>
           <t>SAB PALMOLIVE 150GR MANT CACAU E KARITE</t>
         </is>
@@ -60386,7 +60389,7 @@
           <t>#07 HIGIENE PESSOAL - SABONETE</t>
         </is>
       </c>
-      <c r="C2966" s="32" t="inlineStr">
+      <c r="C2966" s="27" t="inlineStr">
         <is>
           <t>SAB PALMOLIVE 150GR OLE ARGAN E OL COMPL</t>
         </is>
@@ -60406,7 +60409,7 @@
           <t>#07 HIGIENE PESSOAL - SABONETE</t>
         </is>
       </c>
-      <c r="C2967" s="32" t="inlineStr">
+      <c r="C2967" s="27" t="inlineStr">
         <is>
           <t>SAB PALM NATURALS T.SEGREDO SEDUTOR 150G</t>
         </is>
@@ -60426,7 +60429,7 @@
           <t>#07 HIGIENE PESSOAL - SABONETE</t>
         </is>
       </c>
-      <c r="C2968" s="32" t="inlineStr">
+      <c r="C2968" s="27" t="inlineStr">
         <is>
           <t>SAB PALMOLIVE 150GR GELEIA REAL E PROT</t>
         </is>
@@ -60438,46 +60441,46 @@
       </c>
     </row>
     <row r="2969">
-      <c r="A2969" s="31" t="n">
+      <c r="A2969" s="28" t="n">
         <v>108866</v>
       </c>
-      <c r="B2969" s="31" t="inlineStr">
+      <c r="B2969" s="28" t="inlineStr">
         <is>
           <t>#07 HIGIENE PESSOAL - SABONETE</t>
         </is>
       </c>
-      <c r="C2969" s="31" t="inlineStr">
+      <c r="C2969" s="28" t="inlineStr">
         <is>
           <t>SAB PALMOLIVE 150GR LEITE E PETALAS ROSA</t>
         </is>
       </c>
-      <c r="D2969" s="31" t="inlineStr">
+      <c r="D2969" s="28" t="inlineStr">
         <is>
           <t>SABONETE PALMOLIVE 150G LEITE E PETALAS ROSA</t>
         </is>
       </c>
-      <c r="E2969" s="31" t="inlineStr"/>
+      <c r="E2969" s="28" t="inlineStr"/>
     </row>
     <row r="2970">
-      <c r="A2970" s="31" t="n">
+      <c r="A2970" s="28" t="n">
         <v>108867</v>
       </c>
-      <c r="B2970" s="31" t="inlineStr">
+      <c r="B2970" s="28" t="inlineStr">
         <is>
           <t>#07 HIGIENE PESSOAL - SABONETE</t>
         </is>
       </c>
-      <c r="C2970" s="31" t="inlineStr">
+      <c r="C2970" s="28" t="inlineStr">
         <is>
           <t>SAB PALMOLIVE 150GR MANT CACAU E KARITE</t>
         </is>
       </c>
-      <c r="D2970" s="31" t="inlineStr">
+      <c r="D2970" s="28" t="inlineStr">
         <is>
           <t>SABONETE PALMOLIVE 150G MANTEIGA CACAU E KARITE</t>
         </is>
       </c>
-      <c r="E2970" s="31" t="inlineStr"/>
+      <c r="E2970" s="28" t="inlineStr"/>
     </row>
     <row r="2971">
       <c r="A2971" t="n">
@@ -60561,25 +60564,25 @@
       <c r="E2974" s="14" t="inlineStr"/>
     </row>
     <row r="2975">
-      <c r="A2975" s="31" t="n">
+      <c r="A2975" s="28" t="n">
         <v>121641</v>
       </c>
-      <c r="B2975" s="31" t="inlineStr">
+      <c r="B2975" s="28" t="inlineStr">
         <is>
           <t>#07 HIGIENE PESSOAL - SABONETE</t>
         </is>
       </c>
-      <c r="C2975" s="31" t="inlineStr">
+      <c r="C2975" s="28" t="inlineStr">
         <is>
           <t>SAB PALMOLIVE 150GR OLE ARGAN E OL COMPL</t>
         </is>
       </c>
-      <c r="D2975" s="31" t="inlineStr">
+      <c r="D2975" s="28" t="inlineStr">
         <is>
           <t>SABONETE PALMOLIVE 150G ÓLEO ARGAN E ÓLEO COMPLETO</t>
         </is>
       </c>
-      <c r="E2975" s="31" t="inlineStr"/>
+      <c r="E2975" s="28" t="inlineStr"/>
     </row>
     <row r="2976">
       <c r="A2976" t="n">
@@ -60704,25 +60707,25 @@
       </c>
     </row>
     <row r="2982">
-      <c r="A2982" s="31" t="n">
+      <c r="A2982" s="28" t="n">
         <v>144261</v>
       </c>
-      <c r="B2982" s="31" t="inlineStr">
+      <c r="B2982" s="28" t="inlineStr">
         <is>
           <t>#07 HIGIENE PESSOAL - SABONETE</t>
         </is>
       </c>
-      <c r="C2982" s="31" t="inlineStr">
+      <c r="C2982" s="28" t="inlineStr">
         <is>
           <t>SAB PALM NATURALS T.SEGREDO SEDUTOR 150G</t>
         </is>
       </c>
-      <c r="D2982" s="31" t="inlineStr">
+      <c r="D2982" s="28" t="inlineStr">
         <is>
           <t>SABONETE PALMOLIVE 150G NATURALS SEGREDO SEDUTOR</t>
         </is>
       </c>
-      <c r="E2982" s="31" t="inlineStr"/>
+      <c r="E2982" s="28" t="inlineStr"/>
     </row>
     <row r="2983">
       <c r="A2983" t="n">
@@ -60745,25 +60748,25 @@
       </c>
     </row>
     <row r="2984">
-      <c r="A2984" s="31" t="n">
+      <c r="A2984" s="28" t="n">
         <v>157417</v>
       </c>
-      <c r="B2984" s="31" t="inlineStr">
+      <c r="B2984" s="28" t="inlineStr">
         <is>
           <t>#07 HIGIENE PESSOAL - SABONETE</t>
         </is>
       </c>
-      <c r="C2984" s="31" t="inlineStr">
+      <c r="C2984" s="28" t="inlineStr">
         <is>
           <t>SAB PALMOLIVE 150GR GELEIA REAL E PROT</t>
         </is>
       </c>
-      <c r="D2984" s="31" t="inlineStr">
+      <c r="D2984" s="28" t="inlineStr">
         <is>
           <t>SABONETE PALMOLIVE 150G GELEIA REAL E PROTEÇÃO</t>
         </is>
       </c>
-      <c r="E2984" s="31" t="inlineStr"/>
+      <c r="E2984" s="28" t="inlineStr"/>
     </row>
     <row r="2985">
       <c r="A2985" s="14" t="n">
@@ -60787,25 +60790,25 @@
       <c r="E2985" s="14" t="inlineStr"/>
     </row>
     <row r="2986">
-      <c r="A2986" s="31" t="n">
+      <c r="A2986" s="28" t="n">
         <v>167507</v>
       </c>
-      <c r="B2986" s="31" t="inlineStr">
+      <c r="B2986" s="28" t="inlineStr">
         <is>
           <t>#07 HIGIENE PESSOAL - SABONETE</t>
         </is>
       </c>
-      <c r="C2986" s="31" t="inlineStr">
+      <c r="C2986" s="28" t="inlineStr">
         <is>
           <t>SAB PALMOLIVE 150GR OL.NUTRI</t>
         </is>
       </c>
-      <c r="D2986" s="31" t="inlineStr">
+      <c r="D2986" s="28" t="inlineStr">
         <is>
           <t>SABONETE PALMOLIVE 150G ÓLEO NUTRITIVO</t>
         </is>
       </c>
-      <c r="E2986" s="31" t="inlineStr"/>
+      <c r="E2986" s="28" t="inlineStr"/>
     </row>
     <row r="2987">
       <c r="A2987" s="14" t="n">
@@ -60849,25 +60852,25 @@
       </c>
     </row>
     <row r="2989">
-      <c r="A2989" s="31" t="n">
+      <c r="A2989" s="28" t="n">
         <v>190286</v>
       </c>
-      <c r="B2989" s="31" t="inlineStr">
+      <c r="B2989" s="28" t="inlineStr">
         <is>
           <t>#07 HIGIENE PESSOAL - SABONETE</t>
         </is>
       </c>
-      <c r="C2989" s="31" t="inlineStr">
+      <c r="C2989" s="28" t="inlineStr">
         <is>
           <t>SABONETE NATURALS JASMIM 150G</t>
         </is>
       </c>
-      <c r="D2989" s="31" t="inlineStr">
+      <c r="D2989" s="28" t="inlineStr">
         <is>
           <t>SABONETE PALMOLIVE 150G NATURALS JASMIM</t>
         </is>
       </c>
-      <c r="E2989" s="31" t="inlineStr"/>
+      <c r="E2989" s="28" t="inlineStr"/>
     </row>
     <row r="2990">
       <c r="A2990" s="14" t="n">
@@ -61783,25 +61786,25 @@
       </c>
     </row>
     <row r="3035">
-      <c r="A3035" s="31" t="n">
+      <c r="A3035" s="28" t="n">
         <v>228933</v>
       </c>
-      <c r="B3035" s="31" t="inlineStr">
+      <c r="B3035" s="28" t="inlineStr">
         <is>
           <t>#07 HIGIENE PESSOAL - SABONETE</t>
         </is>
       </c>
-      <c r="C3035" s="31" t="inlineStr">
+      <c r="C3035" s="28" t="inlineStr">
         <is>
           <t>SABONETE PALMOLIVE 150GR SENSACAO PURIFI</t>
         </is>
       </c>
-      <c r="D3035" s="31" t="inlineStr">
+      <c r="D3035" s="28" t="inlineStr">
         <is>
           <t>SABONETE PALMOLIVE 150G SENSACAO PURIFICANTE</t>
         </is>
       </c>
-      <c r="E3035" s="31" t="inlineStr"/>
+      <c r="E3035" s="28" t="inlineStr"/>
     </row>
     <row r="3036">
       <c r="A3036" s="14" t="n">
@@ -62445,25 +62448,25 @@
       </c>
     </row>
     <row r="3068">
-      <c r="A3068" s="31" t="n">
+      <c r="A3068" s="28" t="n">
         <v>301365</v>
       </c>
-      <c r="B3068" s="31" t="inlineStr">
+      <c r="B3068" s="28" t="inlineStr">
         <is>
           <t>#07 HIGIENE PESSOAL - SABONETE</t>
         </is>
       </c>
-      <c r="C3068" s="31" t="inlineStr">
+      <c r="C3068" s="28" t="inlineStr">
         <is>
           <t>SABONETE PALMOLIVE 150GR MELANCIA E LICH</t>
         </is>
       </c>
-      <c r="D3068" s="31" t="inlineStr">
+      <c r="D3068" s="28" t="inlineStr">
         <is>
           <t>SABONETE PALMOLIVE 150G MELANCIA E LICHIA</t>
         </is>
       </c>
-      <c r="E3068" s="31" t="inlineStr"/>
+      <c r="E3068" s="28" t="inlineStr"/>
     </row>
     <row r="3069">
       <c r="A3069" s="14" t="n">
@@ -62487,25 +62490,25 @@
       <c r="E3069" s="14" t="inlineStr"/>
     </row>
     <row r="3070">
-      <c r="A3070" s="31" t="n">
+      <c r="A3070" s="28" t="n">
         <v>306134</v>
       </c>
-      <c r="B3070" s="31" t="inlineStr">
+      <c r="B3070" s="28" t="inlineStr">
         <is>
           <t>#07 HIGIENE PESSOAL - SABONETE</t>
         </is>
       </c>
-      <c r="C3070" s="31" t="inlineStr">
+      <c r="C3070" s="28" t="inlineStr">
         <is>
           <t>SABONETE PALMOLIVE 150GR TANGERINA E ALE</t>
         </is>
       </c>
-      <c r="D3070" s="31" t="inlineStr">
+      <c r="D3070" s="28" t="inlineStr">
         <is>
           <t>SABONETE PALMOLIVE 150G TANGERINA E ALECRIM</t>
         </is>
       </c>
-      <c r="E3070" s="31" t="inlineStr"/>
+      <c r="E3070" s="28" t="inlineStr"/>
     </row>
     <row r="3071">
       <c r="A3071" s="14" t="n">
@@ -62790,25 +62793,25 @@
       </c>
     </row>
     <row r="3085">
-      <c r="A3085" s="31" t="n">
+      <c r="A3085" s="28" t="n">
         <v>324239</v>
       </c>
-      <c r="B3085" s="31" t="inlineStr">
+      <c r="B3085" s="28" t="inlineStr">
         <is>
           <t>#07 HIGIENE PESSOAL - SABONETE</t>
         </is>
       </c>
-      <c r="C3085" s="31" t="inlineStr">
+      <c r="C3085" s="28" t="inlineStr">
         <is>
           <t>SABONETE PALMOLIVE 150GR ARGILA PRETA E</t>
         </is>
       </c>
-      <c r="D3085" s="31" t="inlineStr">
+      <c r="D3085" s="28" t="inlineStr">
         <is>
           <t>SABONETE PALMOLIVE 150G ARGILA PRETA E EUCALIPTO</t>
         </is>
       </c>
-      <c r="E3085" s="31" t="inlineStr"/>
+      <c r="E3085" s="28" t="inlineStr"/>
     </row>
     <row r="3086">
       <c r="A3086" s="14" t="n">
@@ -62832,25 +62835,25 @@
       <c r="E3086" s="14" t="inlineStr"/>
     </row>
     <row r="3087">
-      <c r="A3087" s="31" t="n">
+      <c r="A3087" s="28" t="n">
         <v>343876</v>
       </c>
-      <c r="B3087" s="31" t="inlineStr">
+      <c r="B3087" s="28" t="inlineStr">
         <is>
           <t>#07 HIGIENE PESSOAL - SABONETE</t>
         </is>
       </c>
-      <c r="C3087" s="31" t="inlineStr">
+      <c r="C3087" s="28" t="inlineStr">
         <is>
           <t>SAB PALMOLIVE 150GR CAFE E OLEO AMEN</t>
         </is>
       </c>
-      <c r="D3087" s="31" t="inlineStr">
+      <c r="D3087" s="28" t="inlineStr">
         <is>
           <t>SABONETE PALMOLIVE 150G CAFE E OLEO AMENDOAS</t>
         </is>
       </c>
-      <c r="E3087" s="31" t="inlineStr"/>
+      <c r="E3087" s="28" t="inlineStr"/>
     </row>
     <row r="3088">
       <c r="A3088" s="14" t="n">
@@ -63759,25 +63762,25 @@
       </c>
     </row>
     <row r="3133">
-      <c r="A3133" s="25" t="n">
+      <c r="A3133" s="32" t="n">
         <v>101818</v>
       </c>
-      <c r="B3133" s="25" t="inlineStr">
+      <c r="B3133" s="32" t="inlineStr">
         <is>
           <t>#08 BAZAR - LIMPEZA</t>
         </is>
       </c>
-      <c r="C3133" s="25" t="inlineStr">
+      <c r="C3133" s="32" t="inlineStr">
         <is>
           <t>VASSOURA SANTA MARIA PHENIX 956</t>
         </is>
       </c>
-      <c r="D3133" s="25" t="inlineStr">
+      <c r="D3133" s="32" t="inlineStr">
         <is>
           <t>VASSOURA SANTA MARIA PHENIX 956</t>
         </is>
       </c>
-      <c r="E3133" s="25" t="inlineStr"/>
+      <c r="E3133" s="32" t="inlineStr"/>
     </row>
     <row r="3134">
       <c r="A3134" t="n">
@@ -63820,46 +63823,46 @@
       </c>
     </row>
     <row r="3136">
-      <c r="A3136" s="27" t="n">
+      <c r="A3136" s="28" t="n">
         <v>111807</v>
       </c>
-      <c r="B3136" s="27" t="inlineStr">
+      <c r="B3136" s="28" t="inlineStr">
         <is>
           <t>#08 BAZAR - LIMPEZA</t>
         </is>
       </c>
-      <c r="C3136" s="27" t="inlineStr">
+      <c r="C3136" s="28" t="inlineStr">
         <is>
           <t>VASSOURA BETTANIN VARRY 1000</t>
         </is>
       </c>
-      <c r="D3136" s="27" t="inlineStr">
+      <c r="D3136" s="28" t="inlineStr">
         <is>
           <t>VASSOURA BETTANIN VARRY 1000</t>
         </is>
       </c>
-      <c r="E3136" s="27" t="inlineStr"/>
+      <c r="E3136" s="28" t="inlineStr"/>
     </row>
     <row r="3137">
-      <c r="A3137" s="27" t="n">
+      <c r="A3137" s="28" t="n">
         <v>114250</v>
       </c>
-      <c r="B3137" s="27" t="inlineStr">
+      <c r="B3137" s="28" t="inlineStr">
         <is>
           <t>#08 BAZAR - LIMPEZA</t>
         </is>
       </c>
-      <c r="C3137" s="27" t="inlineStr">
+      <c r="C3137" s="28" t="inlineStr">
         <is>
           <t>PREND. ROUPA GABOARDI GIGANTE 12UN PLAST</t>
         </is>
       </c>
-      <c r="D3137" s="27" t="inlineStr">
+      <c r="D3137" s="28" t="inlineStr">
         <is>
           <t>PRENDEDOR DE ROUPAS PLÁSTICO GABOARDI 12UN GIGANTE</t>
         </is>
       </c>
-      <c r="E3137" s="27" t="inlineStr"/>
+      <c r="E3137" s="28" t="inlineStr"/>
     </row>
     <row r="3138">
       <c r="A3138" t="n">
@@ -65007,133 +65010,280 @@
       </c>
     </row>
     <row r="3195">
-      <c r="A3195" s="31" t="n">
+      <c r="A3195" s="28" t="n">
         <v>345807</v>
       </c>
-      <c r="B3195" s="31" t="inlineStr">
+      <c r="B3195" s="28" t="inlineStr">
         <is>
           <t>#07 HIGIENE PESSOAL - HIGIENE BUCAL</t>
         </is>
       </c>
-      <c r="C3195" s="31" t="inlineStr">
+      <c r="C3195" s="28" t="inlineStr">
         <is>
           <t>CREME DENTAL COLGATE 180GR TOTAL12 PREVE</t>
         </is>
       </c>
-      <c r="D3195" s="31" t="inlineStr">
+      <c r="D3195" s="28" t="inlineStr">
         <is>
           <t>CREME DENTAL COLGATE 180G TOTAL 12 PREVENÇÃO ATIVA</t>
         </is>
       </c>
-      <c r="E3195" s="31" t="inlineStr"/>
+      <c r="E3195" s="28" t="inlineStr"/>
     </row>
     <row r="3196">
-      <c r="A3196" s="31" t="n">
+      <c r="A3196" s="28" t="n">
         <v>345808</v>
       </c>
-      <c r="B3196" s="31" t="inlineStr">
+      <c r="B3196" s="28" t="inlineStr">
         <is>
           <t>#07 HIGIENE PESSOAL - HIGIENE BUCAL</t>
         </is>
       </c>
-      <c r="C3196" s="31" t="inlineStr">
+      <c r="C3196" s="28" t="inlineStr">
         <is>
           <t>CREME DENTAL COLGATE 90GR TOTAL PREVENCA</t>
         </is>
       </c>
-      <c r="D3196" s="31" t="inlineStr">
+      <c r="D3196" s="28" t="inlineStr">
         <is>
           <t>CREME DENTAL COLGATE 90G TOTAL PREVENÇÃO ATIVA</t>
         </is>
       </c>
-      <c r="E3196" s="31" t="inlineStr"/>
+      <c r="E3196" s="28" t="inlineStr"/>
     </row>
     <row r="3197">
-      <c r="A3197" s="31" t="n">
+      <c r="A3197" s="29" t="n">
         <v>315316</v>
       </c>
-      <c r="B3197" s="31" t="inlineStr">
-        <is>
-          <t>SEÇÃO NÃO ESPECIFICADA</t>
-        </is>
-      </c>
-      <c r="C3197" s="31" t="inlineStr">
+      <c r="B3197" s="29" t="inlineStr">
+        <is>
+          <t>#02 MERCEARIA - CONGELADOS - BATATAS</t>
+        </is>
+      </c>
+      <c r="C3197" s="29" t="inlineStr">
         <is>
           <t>BATATA PALITO CANCAO 400GR CONGELADO</t>
         </is>
       </c>
-      <c r="D3197" s="31" t="inlineStr">
-        <is>
-          <t>BATATA PALITO CANCAO 400GR CONGELADO</t>
-        </is>
-      </c>
-      <c r="E3197" s="31" t="inlineStr"/>
+      <c r="D3197" s="29" t="inlineStr">
+        <is>
+          <t>BATATAS CONGELADAS CANÇÃO 400G PALITO</t>
+        </is>
+      </c>
+      <c r="E3197" s="29" t="inlineStr"/>
     </row>
     <row r="3198">
-      <c r="A3198" s="31" t="n">
+      <c r="A3198" s="29" t="n">
         <v>116018</v>
       </c>
-      <c r="B3198" s="31" t="inlineStr">
-        <is>
-          <t>SEÇÃO NÃO ESPECIFICADA</t>
-        </is>
-      </c>
-      <c r="C3198" s="31" t="inlineStr">
+      <c r="B3198" s="29" t="inlineStr">
+        <is>
+          <t>#02 MERCEARIA - GORDURAS E MARGARINAS</t>
+        </is>
+      </c>
+      <c r="C3198" s="29" t="inlineStr">
         <is>
           <t>MANTEIGA COMUM CABECA TOURO C/ SAL 500GR</t>
         </is>
       </c>
-      <c r="D3198" s="31" t="inlineStr">
-        <is>
-          <t>MANTEIGA COMUM CABECA TOURO C/ SAL 500GR</t>
-        </is>
-      </c>
-      <c r="E3198" s="31" t="inlineStr"/>
+      <c r="D3198" s="29" t="inlineStr">
+        <is>
+          <t>MANTEIGA CABEÇA TOURO 500G COMUM COM SAL</t>
+        </is>
+      </c>
+      <c r="E3198" s="29" t="inlineStr"/>
     </row>
     <row r="3199">
-      <c r="A3199" s="31" t="n">
+      <c r="A3199" s="29" t="n">
         <v>173681</v>
       </c>
-      <c r="B3199" s="31" t="inlineStr">
-        <is>
-          <t>SEÇÃO NÃO ESPECIFICADA</t>
-        </is>
-      </c>
-      <c r="C3199" s="31" t="inlineStr">
+      <c r="B3199" s="29" t="inlineStr">
+        <is>
+          <t>#02 MERCEARIA - GORDURAS E MARGARINAS</t>
+        </is>
+      </c>
+      <c r="C3199" s="29" t="inlineStr">
         <is>
           <t>MANTEIGA REAL LATA 500G</t>
         </is>
       </c>
-      <c r="D3199" s="31" t="inlineStr">
+      <c r="D3199" s="29" t="inlineStr">
         <is>
           <t>MANTEIGA REAL LATA 500G</t>
         </is>
       </c>
-      <c r="E3199" s="31" t="inlineStr"/>
+      <c r="E3199" s="29" t="inlineStr"/>
     </row>
     <row r="3200">
-      <c r="A3200" s="31" t="n">
+      <c r="A3200" s="29" t="n">
         <v>180722</v>
       </c>
-      <c r="B3200" s="31" t="inlineStr">
-        <is>
-          <t>SEÇÃO NÃO ESPECIFICADA</t>
-        </is>
-      </c>
-      <c r="C3200" s="31" t="inlineStr">
+      <c r="B3200" s="29" t="inlineStr">
+        <is>
+          <t>#03 AÇOUGUE - #06 EMBUTIDOS E FRIOS</t>
+        </is>
+      </c>
+      <c r="C3200" s="29" t="inlineStr">
         <is>
           <t>MORTADELA PERDIGAO MISTA FAT. 200GR</t>
         </is>
       </c>
-      <c r="D3200" s="31" t="inlineStr">
-        <is>
-          <t>MORTADELA PERDIGAO MISTA FAT. 200GR</t>
-        </is>
-      </c>
-      <c r="E3200" s="31" t="inlineStr"/>
+      <c r="D3200" s="29" t="inlineStr">
+        <is>
+          <t>MORTADELA MISTA PERDIGÃO 200G FATIADAS</t>
+        </is>
+      </c>
+      <c r="E3200" s="29" t="inlineStr"/>
+    </row>
+    <row r="3201">
+      <c r="A3201" s="29" t="n">
+        <v>104978</v>
+      </c>
+      <c r="B3201" s="29" t="inlineStr">
+        <is>
+          <t>#04 HORTIFRUTI - FRUTAS</t>
+        </is>
+      </c>
+      <c r="C3201" s="29" t="inlineStr">
+        <is>
+          <t>MACA IMPORTADA ARGENTINA KG</t>
+        </is>
+      </c>
+      <c r="D3201" s="29" t="inlineStr">
+        <is>
+          <t>MAÇÃ ARGENTINA KG IMPORTANTE</t>
+        </is>
+      </c>
+      <c r="E3201" s="29" t="inlineStr"/>
+    </row>
+    <row r="3202">
+      <c r="A3202" s="29" t="n">
+        <v>105068</v>
+      </c>
+      <c r="B3202" s="29" t="inlineStr">
+        <is>
+          <t>#04 HORTIFRUTI - FRUTAS</t>
+        </is>
+      </c>
+      <c r="C3202" s="29" t="inlineStr">
+        <is>
+          <t>PERA DANJOU KG</t>
+        </is>
+      </c>
+      <c r="D3202" s="29" t="inlineStr">
+        <is>
+          <t>PERA D'ANJOU KG</t>
+        </is>
+      </c>
+      <c r="E3202" s="29" t="inlineStr"/>
+    </row>
+    <row r="3203">
+      <c r="A3203" s="32" t="n">
+        <v>345989</v>
+      </c>
+      <c r="B3203" s="32" t="inlineStr">
+        <is>
+          <t>#02 MERCEARIA - CONDIMENTOS E TEMPEROS</t>
+        </is>
+      </c>
+      <c r="C3203" s="32" t="inlineStr">
+        <is>
+          <t>AZEITONA RIVOLI 150GR C/CAROCO DOYPACK</t>
+        </is>
+      </c>
+      <c r="D3203" s="32" t="inlineStr">
+        <is>
+          <t>AZEITONAS RIVOLI DOYPACK 150G COM CAROÇO</t>
+        </is>
+      </c>
+      <c r="E3203" s="32" t="inlineStr"/>
+    </row>
+    <row r="3204">
+      <c r="A3204" s="32" t="n">
+        <v>198520</v>
+      </c>
+      <c r="B3204" s="32" t="inlineStr">
+        <is>
+          <t>#02 MERCEARIA - FARINHAS E DERIVADOS</t>
+        </is>
+      </c>
+      <c r="C3204" s="32" t="inlineStr">
+        <is>
+          <t>MIST BOLO ADORALLE 400GR CHOCOLATE</t>
+        </is>
+      </c>
+      <c r="D3204" s="32" t="inlineStr">
+        <is>
+          <t>MISTURA PARA BOLOS ADORALLE 400G CHOCOLATE</t>
+        </is>
+      </c>
+      <c r="E3204" s="32" t="inlineStr"/>
+    </row>
+    <row r="3205">
+      <c r="A3205" s="32" t="n">
+        <v>245618</v>
+      </c>
+      <c r="B3205" s="32" t="inlineStr">
+        <is>
+          <t>#02 MERCEARIA - BISCOITOS E SALGADINHOS</t>
+        </is>
+      </c>
+      <c r="C3205" s="32" t="inlineStr">
+        <is>
+          <t>ROSCA MICOS LEITE 300G</t>
+        </is>
+      </c>
+      <c r="D3205" s="32" t="inlineStr">
+        <is>
+          <t>BISCOITO ROQUINHA MICOS 300G LEITE</t>
+        </is>
+      </c>
+      <c r="E3205" s="32" t="inlineStr"/>
+    </row>
+    <row r="3206">
+      <c r="A3206" s="34" t="n">
+        <v>183189</v>
+      </c>
+      <c r="B3206" s="34" t="inlineStr">
+        <is>
+          <t>#03 AÇOUGUE - #06 EMBUTIDOS E FRIOS</t>
+        </is>
+      </c>
+      <c r="C3206" s="34" t="inlineStr">
+        <is>
+          <t>LING PERDIGAO NABRASA C/ C/PIMENTA BIQUI</t>
+        </is>
+      </c>
+      <c r="D3206" s="34" t="inlineStr">
+        <is>
+          <t>LINGUIÇA TOSCANA PERDIGÃO NABRASA 600G COM PIMENTA BIQUINHO</t>
+        </is>
+      </c>
+      <c r="E3206" s="34" t="inlineStr"/>
+    </row>
+    <row r="3207">
+      <c r="A3207" s="34" t="n">
+        <v>336817</v>
+      </c>
+      <c r="B3207" s="34" t="inlineStr">
+        <is>
+          <t>#02 MERCEARIA - GORDURAS E MARGARINAS</t>
+        </is>
+      </c>
+      <c r="C3207" s="34" t="inlineStr">
+        <is>
+          <t>MANTEIGA QUEIJOLEITE 500GR DE PRIMEIRA Q</t>
+        </is>
+      </c>
+      <c r="D3207" s="34" t="inlineStr">
+        <is>
+          <t>MANTEIGA QUEIJOLEITE 500G DE PRIMEIRA QUALIDADE</t>
+        </is>
+      </c>
+      <c r="E3207" s="34" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E3200">
+  <autoFilter ref="A1:E3207">
     <sortState ref="A2:E3194">
       <sortCondition ref="B1:B3194"/>
     </sortState>
